--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,33 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Japan J1 League</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Gamba Osaka</t>
+  </si>
+  <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>['31', '54']</t>
+  </si>
+  <si>
+    <t>['7', '46', '52', '63', '90+4']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +806,212 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7778073</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45702.29166666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <v>7</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2">
+        <v>2.6</v>
+      </c>
+      <c r="R2">
+        <v>2.12</v>
+      </c>
+      <c r="S2">
+        <v>4.3</v>
+      </c>
+      <c r="T2">
+        <v>1.44</v>
+      </c>
+      <c r="U2">
+        <v>2.6</v>
+      </c>
+      <c r="V2">
+        <v>2.9</v>
+      </c>
+      <c r="W2">
+        <v>1.36</v>
+      </c>
+      <c r="X2">
+        <v>7.5</v>
+      </c>
+      <c r="Y2">
+        <v>1.06</v>
+      </c>
+      <c r="Z2">
+        <v>1.98</v>
+      </c>
+      <c r="AA2">
+        <v>3.39</v>
+      </c>
+      <c r="AB2">
+        <v>3.69</v>
+      </c>
+      <c r="AC2">
+        <v>1.05</v>
+      </c>
+      <c r="AD2">
+        <v>8</v>
+      </c>
+      <c r="AE2">
+        <v>1.34</v>
+      </c>
+      <c r="AF2">
+        <v>3</v>
+      </c>
+      <c r="AG2">
+        <v>2.2</v>
+      </c>
+      <c r="AH2">
+        <v>1.67</v>
+      </c>
+      <c r="AI2">
+        <v>1.84</v>
+      </c>
+      <c r="AJ2">
+        <v>1.87</v>
+      </c>
+      <c r="AK2">
+        <v>1.27</v>
+      </c>
+      <c r="AL2">
+        <v>1.29</v>
+      </c>
+      <c r="AM2">
+        <v>1.73</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>8</v>
+      </c>
+      <c r="AW2">
+        <v>13</v>
+      </c>
+      <c r="AX2">
+        <v>5</v>
+      </c>
+      <c r="AY2">
+        <v>19</v>
+      </c>
+      <c r="AZ2">
+        <v>14</v>
+      </c>
+      <c r="BA2">
+        <v>6</v>
+      </c>
+      <c r="BB2">
+        <v>3</v>
+      </c>
+      <c r="BC2">
+        <v>9</v>
+      </c>
+      <c r="BD2">
+        <v>1.68</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.43</v>
+      </c>
+      <c r="BG2">
+        <v>1.42</v>
+      </c>
+      <c r="BH2">
+        <v>2.55</v>
+      </c>
+      <c r="BI2">
+        <v>1.72</v>
+      </c>
+      <c r="BJ2">
+        <v>1.93</v>
+      </c>
+      <c r="BK2">
+        <v>1.92</v>
+      </c>
+      <c r="BL2">
+        <v>1.88</v>
+      </c>
+      <c r="BM2">
+        <v>2.8</v>
+      </c>
+      <c r="BN2">
+        <v>1.35</v>
+      </c>
+      <c r="BO2">
+        <v>3.8</v>
+      </c>
+      <c r="BP2">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -229,13 +229,79 @@
     <t>Gamba Osaka</t>
   </si>
   <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Yokohama</t>
+  </si>
+  <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>Yokohama F. Marinos</t>
+  </si>
+  <si>
+    <t>Kawasaki Frontale</t>
+  </si>
+  <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
+    <t>Kyoto Sanga</t>
+  </si>
+  <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Kashiwa Reysol</t>
+  </si>
+  <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Kashima Antlers</t>
+  </si>
+  <si>
     <t>['31', '54']</t>
   </si>
   <si>
+    <t>['23', '36']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['58', '67', '79', '87']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['26']</t>
   </si>
 </sst>
 </file>
@@ -597,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -829,7 +895,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -850,10 +916,10 @@
         <v>7</v>
       </c>
       <c r="O2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1010,6 +1076,1448 @@
       </c>
       <c r="BP2">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7778081</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>2.1</v>
+      </c>
+      <c r="S3">
+        <v>2.88</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.25</v>
+      </c>
+      <c r="W3">
+        <v>1.33</v>
+      </c>
+      <c r="X3">
+        <v>9</v>
+      </c>
+      <c r="Y3">
+        <v>1.07</v>
+      </c>
+      <c r="Z3">
+        <v>3.07</v>
+      </c>
+      <c r="AA3">
+        <v>3.65</v>
+      </c>
+      <c r="AB3">
+        <v>2.12</v>
+      </c>
+      <c r="AC3">
+        <v>1.06</v>
+      </c>
+      <c r="AD3">
+        <v>8.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.36</v>
+      </c>
+      <c r="AF3">
+        <v>3.1</v>
+      </c>
+      <c r="AG3">
+        <v>1.98</v>
+      </c>
+      <c r="AH3">
+        <v>1.77</v>
+      </c>
+      <c r="AI3">
+        <v>1.91</v>
+      </c>
+      <c r="AJ3">
+        <v>1.91</v>
+      </c>
+      <c r="AK3">
+        <v>1.65</v>
+      </c>
+      <c r="AL3">
+        <v>1.25</v>
+      </c>
+      <c r="AM3">
+        <v>1.33</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>4</v>
+      </c>
+      <c r="AV3">
+        <v>6</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>22</v>
+      </c>
+      <c r="BA3">
+        <v>4</v>
+      </c>
+      <c r="BB3">
+        <v>11</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>2.23</v>
+      </c>
+      <c r="BE3">
+        <v>6.1</v>
+      </c>
+      <c r="BF3">
+        <v>1.81</v>
+      </c>
+      <c r="BG3">
+        <v>1.52</v>
+      </c>
+      <c r="BH3">
+        <v>2.28</v>
+      </c>
+      <c r="BI3">
+        <v>1.86</v>
+      </c>
+      <c r="BJ3">
+        <v>1.79</v>
+      </c>
+      <c r="BK3">
+        <v>2.38</v>
+      </c>
+      <c r="BL3">
+        <v>1.48</v>
+      </c>
+      <c r="BM3">
+        <v>3.15</v>
+      </c>
+      <c r="BN3">
+        <v>1.28</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7778080</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4">
+        <v>2.4</v>
+      </c>
+      <c r="R4">
+        <v>2.1</v>
+      </c>
+      <c r="S4">
+        <v>5.5</v>
+      </c>
+      <c r="T4">
+        <v>1.44</v>
+      </c>
+      <c r="U4">
+        <v>2.63</v>
+      </c>
+      <c r="V4">
+        <v>3.25</v>
+      </c>
+      <c r="W4">
+        <v>1.33</v>
+      </c>
+      <c r="X4">
+        <v>9</v>
+      </c>
+      <c r="Y4">
+        <v>1.07</v>
+      </c>
+      <c r="Z4">
+        <v>1.71</v>
+      </c>
+      <c r="AA4">
+        <v>3.64</v>
+      </c>
+      <c r="AB4">
+        <v>4.8</v>
+      </c>
+      <c r="AC4">
+        <v>1.05</v>
+      </c>
+      <c r="AD4">
+        <v>8</v>
+      </c>
+      <c r="AE4">
+        <v>1.35</v>
+      </c>
+      <c r="AF4">
+        <v>2.9</v>
+      </c>
+      <c r="AG4">
+        <v>1.95</v>
+      </c>
+      <c r="AH4">
+        <v>1.7</v>
+      </c>
+      <c r="AI4">
+        <v>2</v>
+      </c>
+      <c r="AJ4">
+        <v>1.75</v>
+      </c>
+      <c r="AK4">
+        <v>1.18</v>
+      </c>
+      <c r="AL4">
+        <v>1.26</v>
+      </c>
+      <c r="AM4">
+        <v>2.01</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>2</v>
+      </c>
+      <c r="AV4">
+        <v>7</v>
+      </c>
+      <c r="AW4">
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>7</v>
+      </c>
+      <c r="AZ4">
+        <v>28</v>
+      </c>
+      <c r="BA4">
+        <v>3</v>
+      </c>
+      <c r="BB4">
+        <v>9</v>
+      </c>
+      <c r="BC4">
+        <v>12</v>
+      </c>
+      <c r="BD4">
+        <v>1.55</v>
+      </c>
+      <c r="BE4">
+        <v>6.75</v>
+      </c>
+      <c r="BF4">
+        <v>2.7</v>
+      </c>
+      <c r="BG4">
+        <v>1.27</v>
+      </c>
+      <c r="BH4">
+        <v>3.15</v>
+      </c>
+      <c r="BI4">
+        <v>1.48</v>
+      </c>
+      <c r="BJ4">
+        <v>2.35</v>
+      </c>
+      <c r="BK4">
+        <v>1.78</v>
+      </c>
+      <c r="BL4">
+        <v>1.86</v>
+      </c>
+      <c r="BM4">
+        <v>2.23</v>
+      </c>
+      <c r="BN4">
+        <v>1.54</v>
+      </c>
+      <c r="BO4">
+        <v>2.88</v>
+      </c>
+      <c r="BP4">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7778078</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q5">
+        <v>3.75</v>
+      </c>
+      <c r="R5">
+        <v>2.1</v>
+      </c>
+      <c r="S5">
+        <v>2.88</v>
+      </c>
+      <c r="T5">
+        <v>1.44</v>
+      </c>
+      <c r="U5">
+        <v>2.63</v>
+      </c>
+      <c r="V5">
+        <v>3.25</v>
+      </c>
+      <c r="W5">
+        <v>1.33</v>
+      </c>
+      <c r="X5">
+        <v>9</v>
+      </c>
+      <c r="Y5">
+        <v>1.07</v>
+      </c>
+      <c r="Z5">
+        <v>2.73</v>
+      </c>
+      <c r="AA5">
+        <v>3.67</v>
+      </c>
+      <c r="AB5">
+        <v>2.32</v>
+      </c>
+      <c r="AC5">
+        <v>1.06</v>
+      </c>
+      <c r="AD5">
+        <v>8.5</v>
+      </c>
+      <c r="AE5">
+        <v>1.33</v>
+      </c>
+      <c r="AF5">
+        <v>3.25</v>
+      </c>
+      <c r="AG5">
+        <v>2</v>
+      </c>
+      <c r="AH5">
+        <v>1.67</v>
+      </c>
+      <c r="AI5">
+        <v>1.8</v>
+      </c>
+      <c r="AJ5">
+        <v>1.95</v>
+      </c>
+      <c r="AK5">
+        <v>1.57</v>
+      </c>
+      <c r="AL5">
+        <v>1.25</v>
+      </c>
+      <c r="AM5">
+        <v>1.38</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5">
+        <v>10</v>
+      </c>
+      <c r="AX5">
+        <v>6</v>
+      </c>
+      <c r="AY5">
+        <v>19</v>
+      </c>
+      <c r="AZ5">
+        <v>10</v>
+      </c>
+      <c r="BA5">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>2.12</v>
+      </c>
+      <c r="BE5">
+        <v>6.25</v>
+      </c>
+      <c r="BF5">
+        <v>1.9</v>
+      </c>
+      <c r="BG5">
+        <v>1.42</v>
+      </c>
+      <c r="BH5">
+        <v>2.55</v>
+      </c>
+      <c r="BI5">
+        <v>1.73</v>
+      </c>
+      <c r="BJ5">
+        <v>1.92</v>
+      </c>
+      <c r="BK5">
+        <v>2.18</v>
+      </c>
+      <c r="BL5">
+        <v>1.56</v>
+      </c>
+      <c r="BM5">
+        <v>2.85</v>
+      </c>
+      <c r="BN5">
+        <v>1.34</v>
+      </c>
+      <c r="BO5">
+        <v>3.8</v>
+      </c>
+      <c r="BP5">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7778082</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <v>1.83</v>
+      </c>
+      <c r="S6">
+        <v>3.5</v>
+      </c>
+      <c r="T6">
+        <v>1.62</v>
+      </c>
+      <c r="U6">
+        <v>2.2</v>
+      </c>
+      <c r="V6">
+        <v>4</v>
+      </c>
+      <c r="W6">
+        <v>1.22</v>
+      </c>
+      <c r="X6">
+        <v>15</v>
+      </c>
+      <c r="Y6">
+        <v>1.03</v>
+      </c>
+      <c r="Z6">
+        <v>3.06</v>
+      </c>
+      <c r="AA6">
+        <v>2.82</v>
+      </c>
+      <c r="AB6">
+        <v>2.57</v>
+      </c>
+      <c r="AC6">
+        <v>1.12</v>
+      </c>
+      <c r="AD6">
+        <v>6</v>
+      </c>
+      <c r="AE6">
+        <v>1.55</v>
+      </c>
+      <c r="AF6">
+        <v>2.2</v>
+      </c>
+      <c r="AG6">
+        <v>2.82</v>
+      </c>
+      <c r="AH6">
+        <v>1.4</v>
+      </c>
+      <c r="AI6">
+        <v>2.25</v>
+      </c>
+      <c r="AJ6">
+        <v>1.57</v>
+      </c>
+      <c r="AK6">
+        <v>1.49</v>
+      </c>
+      <c r="AL6">
+        <v>1.36</v>
+      </c>
+      <c r="AM6">
+        <v>1.37</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>3</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>2</v>
+      </c>
+      <c r="AV6">
+        <v>5</v>
+      </c>
+      <c r="AW6">
+        <v>7</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>13</v>
+      </c>
+      <c r="AZ6">
+        <v>15</v>
+      </c>
+      <c r="BA6">
+        <v>2</v>
+      </c>
+      <c r="BB6">
+        <v>6</v>
+      </c>
+      <c r="BC6">
+        <v>8</v>
+      </c>
+      <c r="BD6">
+        <v>2.08</v>
+      </c>
+      <c r="BE6">
+        <v>6.25</v>
+      </c>
+      <c r="BF6">
+        <v>1.93</v>
+      </c>
+      <c r="BG6">
+        <v>1.55</v>
+      </c>
+      <c r="BH6">
+        <v>2.2</v>
+      </c>
+      <c r="BI6">
+        <v>2</v>
+      </c>
+      <c r="BJ6">
+        <v>1.8</v>
+      </c>
+      <c r="BK6">
+        <v>2.48</v>
+      </c>
+      <c r="BL6">
+        <v>1.44</v>
+      </c>
+      <c r="BM6">
+        <v>3.3</v>
+      </c>
+      <c r="BN6">
+        <v>1.26</v>
+      </c>
+      <c r="BO6">
+        <v>4.6</v>
+      </c>
+      <c r="BP6">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7778077</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q7">
+        <v>2.63</v>
+      </c>
+      <c r="R7">
+        <v>2.3</v>
+      </c>
+      <c r="S7">
+        <v>3.6</v>
+      </c>
+      <c r="T7">
+        <v>1.3</v>
+      </c>
+      <c r="U7">
+        <v>3.4</v>
+      </c>
+      <c r="V7">
+        <v>2.5</v>
+      </c>
+      <c r="W7">
+        <v>1.5</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <v>1.13</v>
+      </c>
+      <c r="Z7">
+        <v>2.1</v>
+      </c>
+      <c r="AA7">
+        <v>3.58</v>
+      </c>
+      <c r="AB7">
+        <v>3.19</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>11</v>
+      </c>
+      <c r="AE7">
+        <v>1.18</v>
+      </c>
+      <c r="AF7">
+        <v>4.4</v>
+      </c>
+      <c r="AG7">
+        <v>1.57</v>
+      </c>
+      <c r="AH7">
+        <v>2.15</v>
+      </c>
+      <c r="AI7">
+        <v>1.53</v>
+      </c>
+      <c r="AJ7">
+        <v>2.38</v>
+      </c>
+      <c r="AK7">
+        <v>1.33</v>
+      </c>
+      <c r="AL7">
+        <v>1.27</v>
+      </c>
+      <c r="AM7">
+        <v>1.68</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>6</v>
+      </c>
+      <c r="AW7">
+        <v>5</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>22</v>
+      </c>
+      <c r="BA7">
+        <v>3</v>
+      </c>
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BC7">
+        <v>6</v>
+      </c>
+      <c r="BD7">
+        <v>1.73</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>2.32</v>
+      </c>
+      <c r="BG7">
+        <v>1.21</v>
+      </c>
+      <c r="BH7">
+        <v>3.65</v>
+      </c>
+      <c r="BI7">
+        <v>1.38</v>
+      </c>
+      <c r="BJ7">
+        <v>2.65</v>
+      </c>
+      <c r="BK7">
+        <v>1.63</v>
+      </c>
+      <c r="BL7">
+        <v>2.06</v>
+      </c>
+      <c r="BM7">
+        <v>2</v>
+      </c>
+      <c r="BN7">
+        <v>1.67</v>
+      </c>
+      <c r="BO7">
+        <v>2.5</v>
+      </c>
+      <c r="BP7">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7778076</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45703.125</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8">
+        <v>2.5</v>
+      </c>
+      <c r="R8">
+        <v>2.25</v>
+      </c>
+      <c r="S8">
+        <v>4.33</v>
+      </c>
+      <c r="T8">
+        <v>1.36</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>2.63</v>
+      </c>
+      <c r="W8">
+        <v>1.44</v>
+      </c>
+      <c r="X8">
+        <v>7</v>
+      </c>
+      <c r="Y8">
+        <v>1.1</v>
+      </c>
+      <c r="Z8">
+        <v>1.84</v>
+      </c>
+      <c r="AA8">
+        <v>3.73</v>
+      </c>
+      <c r="AB8">
+        <v>3.88</v>
+      </c>
+      <c r="AC8">
+        <v>1.02</v>
+      </c>
+      <c r="AD8">
+        <v>10</v>
+      </c>
+      <c r="AE8">
+        <v>1.25</v>
+      </c>
+      <c r="AF8">
+        <v>3.65</v>
+      </c>
+      <c r="AG8">
+        <v>1.79</v>
+      </c>
+      <c r="AH8">
+        <v>1.95</v>
+      </c>
+      <c r="AI8">
+        <v>1.75</v>
+      </c>
+      <c r="AJ8">
+        <v>2</v>
+      </c>
+      <c r="AK8">
+        <v>1.24</v>
+      </c>
+      <c r="AL8">
+        <v>1.26</v>
+      </c>
+      <c r="AM8">
+        <v>1.87</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>8</v>
+      </c>
+      <c r="AX8">
+        <v>9</v>
+      </c>
+      <c r="AY8">
+        <v>16</v>
+      </c>
+      <c r="AZ8">
+        <v>9</v>
+      </c>
+      <c r="BA8">
+        <v>6</v>
+      </c>
+      <c r="BB8">
+        <v>5</v>
+      </c>
+      <c r="BC8">
+        <v>11</v>
+      </c>
+      <c r="BD8">
+        <v>1.65</v>
+      </c>
+      <c r="BE8">
+        <v>6.25</v>
+      </c>
+      <c r="BF8">
+        <v>2.55</v>
+      </c>
+      <c r="BG8">
+        <v>1.36</v>
+      </c>
+      <c r="BH8">
+        <v>2.75</v>
+      </c>
+      <c r="BI8">
+        <v>1.63</v>
+      </c>
+      <c r="BJ8">
+        <v>2.07</v>
+      </c>
+      <c r="BK8">
+        <v>2.02</v>
+      </c>
+      <c r="BL8">
+        <v>1.66</v>
+      </c>
+      <c r="BM8">
+        <v>2.6</v>
+      </c>
+      <c r="BN8">
+        <v>1.4</v>
+      </c>
+      <c r="BO8">
+        <v>3.4</v>
+      </c>
+      <c r="BP8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7778079</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45703.125</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9">
+        <v>4.33</v>
+      </c>
+      <c r="R9">
+        <v>2.1</v>
+      </c>
+      <c r="S9">
+        <v>2.75</v>
+      </c>
+      <c r="T9">
+        <v>1.44</v>
+      </c>
+      <c r="U9">
+        <v>2.63</v>
+      </c>
+      <c r="V9">
+        <v>3.25</v>
+      </c>
+      <c r="W9">
+        <v>1.33</v>
+      </c>
+      <c r="X9">
+        <v>9</v>
+      </c>
+      <c r="Y9">
+        <v>1.07</v>
+      </c>
+      <c r="Z9">
+        <v>3.53</v>
+      </c>
+      <c r="AA9">
+        <v>3.3</v>
+      </c>
+      <c r="AB9">
+        <v>2.07</v>
+      </c>
+      <c r="AC9">
+        <v>1.02</v>
+      </c>
+      <c r="AD9">
+        <v>7.9</v>
+      </c>
+      <c r="AE9">
+        <v>1.35</v>
+      </c>
+      <c r="AF9">
+        <v>2.95</v>
+      </c>
+      <c r="AG9">
+        <v>2</v>
+      </c>
+      <c r="AH9">
+        <v>1.67</v>
+      </c>
+      <c r="AI9">
+        <v>1.91</v>
+      </c>
+      <c r="AJ9">
+        <v>1.91</v>
+      </c>
+      <c r="AK9">
+        <v>1.71</v>
+      </c>
+      <c r="AL9">
+        <v>1.29</v>
+      </c>
+      <c r="AM9">
+        <v>1.28</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>9</v>
+      </c>
+      <c r="AV9">
+        <v>8</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>5</v>
+      </c>
+      <c r="AY9">
+        <v>19</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>9</v>
+      </c>
+      <c r="BB9">
+        <v>10</v>
+      </c>
+      <c r="BC9">
+        <v>19</v>
+      </c>
+      <c r="BD9">
+        <v>2.4</v>
+      </c>
+      <c r="BE9">
+        <v>6.4</v>
+      </c>
+      <c r="BF9">
+        <v>1.71</v>
+      </c>
+      <c r="BG9">
+        <v>1.35</v>
+      </c>
+      <c r="BH9">
+        <v>2.8</v>
+      </c>
+      <c r="BI9">
+        <v>1.58</v>
+      </c>
+      <c r="BJ9">
+        <v>2.14</v>
+      </c>
+      <c r="BK9">
+        <v>1.82</v>
+      </c>
+      <c r="BL9">
+        <v>1.98</v>
+      </c>
+      <c r="BM9">
+        <v>2.5</v>
+      </c>
+      <c r="BN9">
+        <v>1.43</v>
+      </c>
+      <c r="BO9">
+        <v>3.3</v>
+      </c>
+      <c r="BP9">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,12 @@
     <t>Shonan Bellmare</t>
   </si>
   <si>
+    <t>Machida Zelvia</t>
+  </si>
+  <si>
+    <t>Tokyo Verdy</t>
+  </si>
+  <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
@@ -274,6 +280,12 @@
     <t>Kashima Antlers</t>
   </si>
   <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
+    <t>Shimizu S-Pulse</t>
+  </si>
+  <si>
     <t>['31', '54']</t>
   </si>
   <si>
@@ -292,6 +304,9 @@
     <t>['64']</t>
   </si>
   <si>
+    <t>['26']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -301,7 +316,10 @@
     <t>['75']</t>
   </si>
   <si>
-    <t>['26']</t>
+    <t>['59', '77']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
 </sst>
 </file>
@@ -663,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -895,7 +913,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -916,10 +934,10 @@
         <v>7</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1101,7 +1119,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1122,10 +1140,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1307,7 +1325,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1328,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
@@ -1513,7 +1531,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1534,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1719,7 +1737,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1740,10 +1758,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -1925,7 +1943,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1946,10 +1964,10 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>2.63</v>
@@ -2131,7 +2149,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2152,10 +2170,10 @@
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2337,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2358,10 +2376,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2518,6 +2536,418 @@
       </c>
       <c r="BP9">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7778075</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45704.08333333334</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>2.1</v>
+      </c>
+      <c r="S10">
+        <v>2.88</v>
+      </c>
+      <c r="T10">
+        <v>1.44</v>
+      </c>
+      <c r="U10">
+        <v>2.63</v>
+      </c>
+      <c r="V10">
+        <v>3.25</v>
+      </c>
+      <c r="W10">
+        <v>1.33</v>
+      </c>
+      <c r="X10">
+        <v>9</v>
+      </c>
+      <c r="Y10">
+        <v>1.07</v>
+      </c>
+      <c r="Z10">
+        <v>3.4</v>
+      </c>
+      <c r="AA10">
+        <v>3.32</v>
+      </c>
+      <c r="AB10">
+        <v>2.11</v>
+      </c>
+      <c r="AC10">
+        <v>1.02</v>
+      </c>
+      <c r="AD10">
+        <v>8.1</v>
+      </c>
+      <c r="AE10">
+        <v>1.33</v>
+      </c>
+      <c r="AF10">
+        <v>3.2</v>
+      </c>
+      <c r="AG10">
+        <v>1.95</v>
+      </c>
+      <c r="AH10">
+        <v>1.7</v>
+      </c>
+      <c r="AI10">
+        <v>1.8</v>
+      </c>
+      <c r="AJ10">
+        <v>1.95</v>
+      </c>
+      <c r="AK10">
+        <v>1.68</v>
+      </c>
+      <c r="AL10">
+        <v>1.25</v>
+      </c>
+      <c r="AM10">
+        <v>1.3</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>2</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>5</v>
+      </c>
+      <c r="AX10">
+        <v>12</v>
+      </c>
+      <c r="AY10">
+        <v>12</v>
+      </c>
+      <c r="AZ10">
+        <v>24</v>
+      </c>
+      <c r="BA10">
+        <v>3</v>
+      </c>
+      <c r="BB10">
+        <v>7</v>
+      </c>
+      <c r="BC10">
+        <v>10</v>
+      </c>
+      <c r="BD10">
+        <v>2.23</v>
+      </c>
+      <c r="BE10">
+        <v>6.75</v>
+      </c>
+      <c r="BF10">
+        <v>1.8</v>
+      </c>
+      <c r="BG10">
+        <v>1.28</v>
+      </c>
+      <c r="BH10">
+        <v>3.1</v>
+      </c>
+      <c r="BI10">
+        <v>1.5</v>
+      </c>
+      <c r="BJ10">
+        <v>2.33</v>
+      </c>
+      <c r="BK10">
+        <v>1.95</v>
+      </c>
+      <c r="BL10">
+        <v>1.85</v>
+      </c>
+      <c r="BM10">
+        <v>2.28</v>
+      </c>
+      <c r="BN10">
+        <v>1.52</v>
+      </c>
+      <c r="BO10">
+        <v>2.95</v>
+      </c>
+      <c r="BP10">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7778074</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45704.08333333334</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P11" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>2.05</v>
+      </c>
+      <c r="S11">
+        <v>3.75</v>
+      </c>
+      <c r="T11">
+        <v>1.44</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>3.25</v>
+      </c>
+      <c r="W11">
+        <v>1.33</v>
+      </c>
+      <c r="X11">
+        <v>10</v>
+      </c>
+      <c r="Y11">
+        <v>1.06</v>
+      </c>
+      <c r="Z11">
+        <v>2.15</v>
+      </c>
+      <c r="AA11">
+        <v>3.25</v>
+      </c>
+      <c r="AB11">
+        <v>3.1</v>
+      </c>
+      <c r="AC11">
+        <v>1.07</v>
+      </c>
+      <c r="AD11">
+        <v>8</v>
+      </c>
+      <c r="AE11">
+        <v>1.38</v>
+      </c>
+      <c r="AF11">
+        <v>3</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>1.7</v>
+      </c>
+      <c r="AI11">
+        <v>1.8</v>
+      </c>
+      <c r="AJ11">
+        <v>1.95</v>
+      </c>
+      <c r="AK11">
+        <v>1.3</v>
+      </c>
+      <c r="AL11">
+        <v>1.3</v>
+      </c>
+      <c r="AM11">
+        <v>1.62</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>3</v>
+      </c>
+      <c r="AV11">
+        <v>3</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>7</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>12</v>
+      </c>
+      <c r="BA11">
+        <v>6</v>
+      </c>
+      <c r="BB11">
+        <v>5</v>
+      </c>
+      <c r="BC11">
+        <v>11</v>
+      </c>
+      <c r="BD11">
+        <v>1.77</v>
+      </c>
+      <c r="BE11">
+        <v>6.4</v>
+      </c>
+      <c r="BF11">
+        <v>2.3</v>
+      </c>
+      <c r="BG11">
+        <v>1.3</v>
+      </c>
+      <c r="BH11">
+        <v>3</v>
+      </c>
+      <c r="BI11">
+        <v>1.54</v>
+      </c>
+      <c r="BJ11">
+        <v>2.23</v>
+      </c>
+      <c r="BK11">
+        <v>1.87</v>
+      </c>
+      <c r="BL11">
+        <v>1.77</v>
+      </c>
+      <c r="BM11">
+        <v>2.35</v>
+      </c>
+      <c r="BN11">
+        <v>1.49</v>
+      </c>
+      <c r="BO11">
+        <v>3.05</v>
+      </c>
+      <c r="BP11">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -256,36 +256,36 @@
     <t>Tokyo Verdy</t>
   </si>
   <si>
+    <t>Kashiwa Reysol</t>
+  </si>
+  <si>
+    <t>Shimizu S-Pulse</t>
+  </si>
+  <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Kyoto Sanga</t>
+  </si>
+  <si>
+    <t>Kashima Antlers</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
-    <t>Kyoto Sanga</t>
-  </si>
-  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Kashiwa Reysol</t>
-  </si>
-  <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
-    <t>Kashima Antlers</t>
-  </si>
-  <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
-    <t>Shimizu S-Pulse</t>
-  </si>
-  <si>
     <t>['31', '54']</t>
   </si>
   <si>
@@ -307,6 +307,24 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['45+2', '62']</t>
+  </si>
+  <si>
+    <t>['56', '85']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['22', '58']</t>
+  </si>
+  <si>
+    <t>['22', '25', '42', '75']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -320,6 +338,24 @@
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['70', '75']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['32', '51']</t>
   </si>
 </sst>
 </file>
@@ -681,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -913,7 +949,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -937,7 +973,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1015,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1119,7 +1155,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1325,7 +1361,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1531,7 +1567,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1555,7 +1591,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1633,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>3</v>
@@ -1737,7 +1773,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1761,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -1943,7 +1979,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2048,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2149,7 +2185,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2355,7 +2391,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2561,7 +2597,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2585,7 +2621,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2767,7 +2803,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2791,7 +2827,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2948,6 +2984,1860 @@
       </c>
       <c r="BP11">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7778084</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12">
+        <v>3.1</v>
+      </c>
+      <c r="R12">
+        <v>2.25</v>
+      </c>
+      <c r="S12">
+        <v>3.2</v>
+      </c>
+      <c r="T12">
+        <v>1.35</v>
+      </c>
+      <c r="U12">
+        <v>2.95</v>
+      </c>
+      <c r="V12">
+        <v>2.5</v>
+      </c>
+      <c r="W12">
+        <v>1.47</v>
+      </c>
+      <c r="X12">
+        <v>5.7</v>
+      </c>
+      <c r="Y12">
+        <v>1.11</v>
+      </c>
+      <c r="Z12">
+        <v>2.4</v>
+      </c>
+      <c r="AA12">
+        <v>3.51</v>
+      </c>
+      <c r="AB12">
+        <v>2.72</v>
+      </c>
+      <c r="AC12">
+        <v>1.05</v>
+      </c>
+      <c r="AD12">
+        <v>9.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.23</v>
+      </c>
+      <c r="AF12">
+        <v>3.75</v>
+      </c>
+      <c r="AG12">
+        <v>1.7</v>
+      </c>
+      <c r="AH12">
+        <v>1.95</v>
+      </c>
+      <c r="AI12">
+        <v>1.6</v>
+      </c>
+      <c r="AJ12">
+        <v>2.2</v>
+      </c>
+      <c r="AK12">
+        <v>1.47</v>
+      </c>
+      <c r="AL12">
+        <v>1.28</v>
+      </c>
+      <c r="AM12">
+        <v>1.49</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>4</v>
+      </c>
+      <c r="AV12">
+        <v>3</v>
+      </c>
+      <c r="AW12">
+        <v>7</v>
+      </c>
+      <c r="AX12">
+        <v>7</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>7</v>
+      </c>
+      <c r="BB12">
+        <v>4</v>
+      </c>
+      <c r="BC12">
+        <v>11</v>
+      </c>
+      <c r="BD12">
+        <v>1.98</v>
+      </c>
+      <c r="BE12">
+        <v>6.4</v>
+      </c>
+      <c r="BF12">
+        <v>2</v>
+      </c>
+      <c r="BG12">
+        <v>1.34</v>
+      </c>
+      <c r="BH12">
+        <v>2.85</v>
+      </c>
+      <c r="BI12">
+        <v>1.58</v>
+      </c>
+      <c r="BJ12">
+        <v>2.14</v>
+      </c>
+      <c r="BK12">
+        <v>1.95</v>
+      </c>
+      <c r="BL12">
+        <v>1.71</v>
+      </c>
+      <c r="BM12">
+        <v>2.5</v>
+      </c>
+      <c r="BN12">
+        <v>1.43</v>
+      </c>
+      <c r="BO12">
+        <v>3.3</v>
+      </c>
+      <c r="BP12">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7778086</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>1.5</v>
+      </c>
+      <c r="U13">
+        <v>2.5</v>
+      </c>
+      <c r="V13">
+        <v>3.5</v>
+      </c>
+      <c r="W13">
+        <v>1.29</v>
+      </c>
+      <c r="X13">
+        <v>11</v>
+      </c>
+      <c r="Y13">
+        <v>1.05</v>
+      </c>
+      <c r="Z13">
+        <v>1.83</v>
+      </c>
+      <c r="AA13">
+        <v>3.4</v>
+      </c>
+      <c r="AB13">
+        <v>4.33</v>
+      </c>
+      <c r="AC13">
+        <v>1.08</v>
+      </c>
+      <c r="AD13">
+        <v>7.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.44</v>
+      </c>
+      <c r="AF13">
+        <v>2.75</v>
+      </c>
+      <c r="AG13">
+        <v>2.28</v>
+      </c>
+      <c r="AH13">
+        <v>1.55</v>
+      </c>
+      <c r="AI13">
+        <v>1.95</v>
+      </c>
+      <c r="AJ13">
+        <v>1.8</v>
+      </c>
+      <c r="AK13">
+        <v>1.3</v>
+      </c>
+      <c r="AL13">
+        <v>1.3</v>
+      </c>
+      <c r="AM13">
+        <v>1.65</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.5</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>1.76</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>1.76</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>3</v>
+      </c>
+      <c r="AW13">
+        <v>5</v>
+      </c>
+      <c r="AX13">
+        <v>9</v>
+      </c>
+      <c r="AY13">
+        <v>9</v>
+      </c>
+      <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>7</v>
+      </c>
+      <c r="BC13">
+        <v>11</v>
+      </c>
+      <c r="BD13">
+        <v>1.67</v>
+      </c>
+      <c r="BE13">
+        <v>6.25</v>
+      </c>
+      <c r="BF13">
+        <v>2.5</v>
+      </c>
+      <c r="BG13">
+        <v>1.36</v>
+      </c>
+      <c r="BH13">
+        <v>2.75</v>
+      </c>
+      <c r="BI13">
+        <v>1.62</v>
+      </c>
+      <c r="BJ13">
+        <v>2.08</v>
+      </c>
+      <c r="BK13">
+        <v>2</v>
+      </c>
+      <c r="BL13">
+        <v>1.67</v>
+      </c>
+      <c r="BM13">
+        <v>2.6</v>
+      </c>
+      <c r="BN13">
+        <v>1.4</v>
+      </c>
+      <c r="BO13">
+        <v>3.4</v>
+      </c>
+      <c r="BP13">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7778087</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q14">
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <v>2.2</v>
+      </c>
+      <c r="S14">
+        <v>3.6</v>
+      </c>
+      <c r="T14">
+        <v>1.4</v>
+      </c>
+      <c r="U14">
+        <v>2.75</v>
+      </c>
+      <c r="V14">
+        <v>2.75</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>2.62</v>
+      </c>
+      <c r="AA14">
+        <v>3.27</v>
+      </c>
+      <c r="AB14">
+        <v>2.62</v>
+      </c>
+      <c r="AC14">
+        <v>1.06</v>
+      </c>
+      <c r="AD14">
+        <v>8.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
+        <v>3.4</v>
+      </c>
+      <c r="AG14">
+        <v>1.83</v>
+      </c>
+      <c r="AH14">
+        <v>1.91</v>
+      </c>
+      <c r="AI14">
+        <v>1.67</v>
+      </c>
+      <c r="AJ14">
+        <v>2.1</v>
+      </c>
+      <c r="AK14">
+        <v>1.36</v>
+      </c>
+      <c r="AL14">
+        <v>1.25</v>
+      </c>
+      <c r="AM14">
+        <v>1.57</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>1</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0.5</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>1.77</v>
+      </c>
+      <c r="AT14">
+        <v>1.77</v>
+      </c>
+      <c r="AU14">
+        <v>3</v>
+      </c>
+      <c r="AV14">
+        <v>5</v>
+      </c>
+      <c r="AW14">
+        <v>12</v>
+      </c>
+      <c r="AX14">
+        <v>2</v>
+      </c>
+      <c r="AY14">
+        <v>16</v>
+      </c>
+      <c r="AZ14">
+        <v>7</v>
+      </c>
+      <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
+        <v>6</v>
+      </c>
+      <c r="BC14">
+        <v>13</v>
+      </c>
+      <c r="BD14">
+        <v>1.84</v>
+      </c>
+      <c r="BE14">
+        <v>6.4</v>
+      </c>
+      <c r="BF14">
+        <v>2.18</v>
+      </c>
+      <c r="BG14">
+        <v>1.37</v>
+      </c>
+      <c r="BH14">
+        <v>2.7</v>
+      </c>
+      <c r="BI14">
+        <v>1.64</v>
+      </c>
+      <c r="BJ14">
+        <v>2.04</v>
+      </c>
+      <c r="BK14">
+        <v>2.04</v>
+      </c>
+      <c r="BL14">
+        <v>1.64</v>
+      </c>
+      <c r="BM14">
+        <v>2.65</v>
+      </c>
+      <c r="BN14">
+        <v>1.38</v>
+      </c>
+      <c r="BO14">
+        <v>3.45</v>
+      </c>
+      <c r="BP14">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7778088</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15">
+        <v>4.3</v>
+      </c>
+      <c r="R15">
+        <v>2.03</v>
+      </c>
+      <c r="S15">
+        <v>2.75</v>
+      </c>
+      <c r="T15">
+        <v>1.5</v>
+      </c>
+      <c r="U15">
+        <v>2.4</v>
+      </c>
+      <c r="V15">
+        <v>3.2</v>
+      </c>
+      <c r="W15">
+        <v>1.31</v>
+      </c>
+      <c r="X15">
+        <v>9</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>3.8</v>
+      </c>
+      <c r="AA15">
+        <v>3.4</v>
+      </c>
+      <c r="AB15">
+        <v>1.95</v>
+      </c>
+      <c r="AC15">
+        <v>1.08</v>
+      </c>
+      <c r="AD15">
+        <v>7.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.41</v>
+      </c>
+      <c r="AF15">
+        <v>2.65</v>
+      </c>
+      <c r="AG15">
+        <v>2.15</v>
+      </c>
+      <c r="AH15">
+        <v>1.57</v>
+      </c>
+      <c r="AI15">
+        <v>1.97</v>
+      </c>
+      <c r="AJ15">
+        <v>1.76</v>
+      </c>
+      <c r="AK15">
+        <v>1.68</v>
+      </c>
+      <c r="AL15">
+        <v>1.31</v>
+      </c>
+      <c r="AM15">
+        <v>1.28</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>5</v>
+      </c>
+      <c r="AV15">
+        <v>9</v>
+      </c>
+      <c r="AW15">
+        <v>5</v>
+      </c>
+      <c r="AX15">
+        <v>7</v>
+      </c>
+      <c r="AY15">
+        <v>11</v>
+      </c>
+      <c r="AZ15">
+        <v>18</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>6</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>2.43</v>
+      </c>
+      <c r="BE15">
+        <v>6.75</v>
+      </c>
+      <c r="BF15">
+        <v>1.67</v>
+      </c>
+      <c r="BG15">
+        <v>1.22</v>
+      </c>
+      <c r="BH15">
+        <v>3.55</v>
+      </c>
+      <c r="BI15">
+        <v>1.4</v>
+      </c>
+      <c r="BJ15">
+        <v>2.6</v>
+      </c>
+      <c r="BK15">
+        <v>1.67</v>
+      </c>
+      <c r="BL15">
+        <v>2</v>
+      </c>
+      <c r="BM15">
+        <v>2.05</v>
+      </c>
+      <c r="BN15">
+        <v>1.64</v>
+      </c>
+      <c r="BO15">
+        <v>2.6</v>
+      </c>
+      <c r="BP15">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7778089</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q16">
+        <v>3.4</v>
+      </c>
+      <c r="R16">
+        <v>2.13</v>
+      </c>
+      <c r="S16">
+        <v>3.15</v>
+      </c>
+      <c r="T16">
+        <v>1.42</v>
+      </c>
+      <c r="U16">
+        <v>2.65</v>
+      </c>
+      <c r="V16">
+        <v>2.8</v>
+      </c>
+      <c r="W16">
+        <v>1.38</v>
+      </c>
+      <c r="X16">
+        <v>7.7</v>
+      </c>
+      <c r="Y16">
+        <v>1.03</v>
+      </c>
+      <c r="Z16">
+        <v>2.74</v>
+      </c>
+      <c r="AA16">
+        <v>3.31</v>
+      </c>
+      <c r="AB16">
+        <v>2.48</v>
+      </c>
+      <c r="AC16">
+        <v>1.06</v>
+      </c>
+      <c r="AD16">
+        <v>8.5</v>
+      </c>
+      <c r="AE16">
+        <v>1.31</v>
+      </c>
+      <c r="AF16">
+        <v>3.15</v>
+      </c>
+      <c r="AG16">
+        <v>1.94</v>
+      </c>
+      <c r="AH16">
+        <v>1.79</v>
+      </c>
+      <c r="AI16">
+        <v>1.74</v>
+      </c>
+      <c r="AJ16">
+        <v>1.98</v>
+      </c>
+      <c r="AK16">
+        <v>1.5</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>1.43</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>2.17</v>
+      </c>
+      <c r="AT16">
+        <v>2.17</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>6</v>
+      </c>
+      <c r="AW16">
+        <v>8</v>
+      </c>
+      <c r="AX16">
+        <v>8</v>
+      </c>
+      <c r="AY16">
+        <v>16</v>
+      </c>
+      <c r="AZ16">
+        <v>15</v>
+      </c>
+      <c r="BA16">
+        <v>6</v>
+      </c>
+      <c r="BB16">
+        <v>3</v>
+      </c>
+      <c r="BC16">
+        <v>9</v>
+      </c>
+      <c r="BD16">
+        <v>1.98</v>
+      </c>
+      <c r="BE16">
+        <v>6.75</v>
+      </c>
+      <c r="BF16">
+        <v>2.02</v>
+      </c>
+      <c r="BG16">
+        <v>1.22</v>
+      </c>
+      <c r="BH16">
+        <v>3.55</v>
+      </c>
+      <c r="BI16">
+        <v>1.41</v>
+      </c>
+      <c r="BJ16">
+        <v>2.55</v>
+      </c>
+      <c r="BK16">
+        <v>1.66</v>
+      </c>
+      <c r="BL16">
+        <v>2</v>
+      </c>
+      <c r="BM16">
+        <v>2.02</v>
+      </c>
+      <c r="BN16">
+        <v>1.65</v>
+      </c>
+      <c r="BO16">
+        <v>2.55</v>
+      </c>
+      <c r="BP16">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7778090</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45710.125</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17" t="s">
+        <v>101</v>
+      </c>
+      <c r="P17" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17">
+        <v>2.7</v>
+      </c>
+      <c r="R17">
+        <v>1.97</v>
+      </c>
+      <c r="S17">
+        <v>4.9</v>
+      </c>
+      <c r="T17">
+        <v>1.56</v>
+      </c>
+      <c r="U17">
+        <v>2.3</v>
+      </c>
+      <c r="V17">
+        <v>3.5</v>
+      </c>
+      <c r="W17">
+        <v>1.27</v>
+      </c>
+      <c r="X17">
+        <v>11</v>
+      </c>
+      <c r="Y17">
+        <v>1.02</v>
+      </c>
+      <c r="Z17">
+        <v>1.97</v>
+      </c>
+      <c r="AA17">
+        <v>3.12</v>
+      </c>
+      <c r="AB17">
+        <v>4.1</v>
+      </c>
+      <c r="AC17">
+        <v>1.1</v>
+      </c>
+      <c r="AD17">
+        <v>6.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.58</v>
+      </c>
+      <c r="AF17">
+        <v>2.39</v>
+      </c>
+      <c r="AG17">
+        <v>2.37</v>
+      </c>
+      <c r="AH17">
+        <v>1.48</v>
+      </c>
+      <c r="AI17">
+        <v>2.15</v>
+      </c>
+      <c r="AJ17">
+        <v>1.63</v>
+      </c>
+      <c r="AK17">
+        <v>1.23</v>
+      </c>
+      <c r="AL17">
+        <v>1.32</v>
+      </c>
+      <c r="AM17">
+        <v>1.75</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.5</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>2.07</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>2.07</v>
+      </c>
+      <c r="AU17">
+        <v>3</v>
+      </c>
+      <c r="AV17">
+        <v>7</v>
+      </c>
+      <c r="AW17">
+        <v>5</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>3</v>
+      </c>
+      <c r="BB17">
+        <v>8</v>
+      </c>
+      <c r="BC17">
+        <v>11</v>
+      </c>
+      <c r="BD17">
+        <v>1.58</v>
+      </c>
+      <c r="BE17">
+        <v>6.75</v>
+      </c>
+      <c r="BF17">
+        <v>2.55</v>
+      </c>
+      <c r="BG17">
+        <v>1.3</v>
+      </c>
+      <c r="BH17">
+        <v>3.05</v>
+      </c>
+      <c r="BI17">
+        <v>1.53</v>
+      </c>
+      <c r="BJ17">
+        <v>2.25</v>
+      </c>
+      <c r="BK17">
+        <v>1.85</v>
+      </c>
+      <c r="BL17">
+        <v>1.79</v>
+      </c>
+      <c r="BM17">
+        <v>2.33</v>
+      </c>
+      <c r="BN17">
+        <v>1.5</v>
+      </c>
+      <c r="BO17">
+        <v>3</v>
+      </c>
+      <c r="BP17">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7778083</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45710.125</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
+      <c r="L18">
+        <v>4</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
+      <c r="O18" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q18">
+        <v>2.8</v>
+      </c>
+      <c r="R18">
+        <v>2.03</v>
+      </c>
+      <c r="S18">
+        <v>4.2</v>
+      </c>
+      <c r="T18">
+        <v>1.5</v>
+      </c>
+      <c r="U18">
+        <v>2.45</v>
+      </c>
+      <c r="V18">
+        <v>3.15</v>
+      </c>
+      <c r="W18">
+        <v>1.31</v>
+      </c>
+      <c r="X18">
+        <v>8.4</v>
+      </c>
+      <c r="Y18">
+        <v>1.01</v>
+      </c>
+      <c r="Z18">
+        <v>2.11</v>
+      </c>
+      <c r="AA18">
+        <v>3.14</v>
+      </c>
+      <c r="AB18">
+        <v>3.61</v>
+      </c>
+      <c r="AC18">
+        <v>1.08</v>
+      </c>
+      <c r="AD18">
+        <v>7.5</v>
+      </c>
+      <c r="AE18">
+        <v>1.4</v>
+      </c>
+      <c r="AF18">
+        <v>2.7</v>
+      </c>
+      <c r="AG18">
+        <v>2.15</v>
+      </c>
+      <c r="AH18">
+        <v>1.57</v>
+      </c>
+      <c r="AI18">
+        <v>1.94</v>
+      </c>
+      <c r="AJ18">
+        <v>1.78</v>
+      </c>
+      <c r="AK18">
+        <v>1.28</v>
+      </c>
+      <c r="AL18">
+        <v>1.32</v>
+      </c>
+      <c r="AM18">
+        <v>1.65</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>10</v>
+      </c>
+      <c r="AV18">
+        <v>3</v>
+      </c>
+      <c r="AW18">
+        <v>6</v>
+      </c>
+      <c r="AX18">
+        <v>3</v>
+      </c>
+      <c r="AY18">
+        <v>19</v>
+      </c>
+      <c r="AZ18">
+        <v>9</v>
+      </c>
+      <c r="BA18">
+        <v>6</v>
+      </c>
+      <c r="BB18">
+        <v>2</v>
+      </c>
+      <c r="BC18">
+        <v>8</v>
+      </c>
+      <c r="BD18">
+        <v>1.71</v>
+      </c>
+      <c r="BE18">
+        <v>6.4</v>
+      </c>
+      <c r="BF18">
+        <v>2.4</v>
+      </c>
+      <c r="BG18">
+        <v>1.46</v>
+      </c>
+      <c r="BH18">
+        <v>2.43</v>
+      </c>
+      <c r="BI18">
+        <v>1.77</v>
+      </c>
+      <c r="BJ18">
+        <v>1.88</v>
+      </c>
+      <c r="BK18">
+        <v>2.25</v>
+      </c>
+      <c r="BL18">
+        <v>1.53</v>
+      </c>
+      <c r="BM18">
+        <v>2.95</v>
+      </c>
+      <c r="BN18">
+        <v>1.32</v>
+      </c>
+      <c r="BO18">
+        <v>3.95</v>
+      </c>
+      <c r="BP18">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7778085</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45710.125</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>92</v>
+      </c>
+      <c r="P19" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q19">
+        <v>4</v>
+      </c>
+      <c r="R19">
+        <v>2.06</v>
+      </c>
+      <c r="S19">
+        <v>2.9</v>
+      </c>
+      <c r="T19">
+        <v>1.48</v>
+      </c>
+      <c r="U19">
+        <v>2.5</v>
+      </c>
+      <c r="V19">
+        <v>3.05</v>
+      </c>
+      <c r="W19">
+        <v>1.33</v>
+      </c>
+      <c r="X19">
+        <v>7.9</v>
+      </c>
+      <c r="Y19">
+        <v>1.02</v>
+      </c>
+      <c r="Z19">
+        <v>3.26</v>
+      </c>
+      <c r="AA19">
+        <v>3.45</v>
+      </c>
+      <c r="AB19">
+        <v>2.12</v>
+      </c>
+      <c r="AC19">
+        <v>1.06</v>
+      </c>
+      <c r="AD19">
+        <v>8.5</v>
+      </c>
+      <c r="AE19">
+        <v>1.37</v>
+      </c>
+      <c r="AF19">
+        <v>2.8</v>
+      </c>
+      <c r="AG19">
+        <v>2.05</v>
+      </c>
+      <c r="AH19">
+        <v>1.61</v>
+      </c>
+      <c r="AI19">
+        <v>1.88</v>
+      </c>
+      <c r="AJ19">
+        <v>1.83</v>
+      </c>
+      <c r="AK19">
+        <v>1.63</v>
+      </c>
+      <c r="AL19">
+        <v>1.3</v>
+      </c>
+      <c r="AM19">
+        <v>1.32</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>3</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>2</v>
+      </c>
+      <c r="AV19">
+        <v>2</v>
+      </c>
+      <c r="AW19">
+        <v>11</v>
+      </c>
+      <c r="AX19">
+        <v>7</v>
+      </c>
+      <c r="AY19">
+        <v>14</v>
+      </c>
+      <c r="AZ19">
+        <v>10</v>
+      </c>
+      <c r="BA19">
+        <v>5</v>
+      </c>
+      <c r="BB19">
+        <v>4</v>
+      </c>
+      <c r="BC19">
+        <v>9</v>
+      </c>
+      <c r="BD19">
+        <v>2.3</v>
+      </c>
+      <c r="BE19">
+        <v>6.25</v>
+      </c>
+      <c r="BF19">
+        <v>1.76</v>
+      </c>
+      <c r="BG19">
+        <v>1.42</v>
+      </c>
+      <c r="BH19">
+        <v>2.55</v>
+      </c>
+      <c r="BI19">
+        <v>1.72</v>
+      </c>
+      <c r="BJ19">
+        <v>1.93</v>
+      </c>
+      <c r="BK19">
+        <v>2.16</v>
+      </c>
+      <c r="BL19">
+        <v>1.57</v>
+      </c>
+      <c r="BM19">
+        <v>2.8</v>
+      </c>
+      <c r="BN19">
+        <v>1.34</v>
+      </c>
+      <c r="BO19">
+        <v>3.8</v>
+      </c>
+      <c r="BP19">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7778091</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45710.125</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>97</v>
+      </c>
+      <c r="P20" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q20">
+        <v>2.55</v>
+      </c>
+      <c r="R20">
+        <v>2.24</v>
+      </c>
+      <c r="S20">
+        <v>4</v>
+      </c>
+      <c r="T20">
+        <v>1.37</v>
+      </c>
+      <c r="U20">
+        <v>2.9</v>
+      </c>
+      <c r="V20">
+        <v>2.55</v>
+      </c>
+      <c r="W20">
+        <v>1.45</v>
+      </c>
+      <c r="X20">
+        <v>6.1</v>
+      </c>
+      <c r="Y20">
+        <v>1.1</v>
+      </c>
+      <c r="Z20">
+        <v>2.01</v>
+      </c>
+      <c r="AA20">
+        <v>3.52</v>
+      </c>
+      <c r="AB20">
+        <v>3.47</v>
+      </c>
+      <c r="AC20">
+        <v>1.05</v>
+      </c>
+      <c r="AD20">
+        <v>9.5</v>
+      </c>
+      <c r="AE20">
+        <v>1.25</v>
+      </c>
+      <c r="AF20">
+        <v>3.55</v>
+      </c>
+      <c r="AG20">
+        <v>1.8</v>
+      </c>
+      <c r="AH20">
+        <v>1.94</v>
+      </c>
+      <c r="AI20">
+        <v>1.67</v>
+      </c>
+      <c r="AJ20">
+        <v>2.08</v>
+      </c>
+      <c r="AK20">
+        <v>1.3</v>
+      </c>
+      <c r="AL20">
+        <v>1.27</v>
+      </c>
+      <c r="AM20">
+        <v>1.73</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>3</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>5</v>
+      </c>
+      <c r="AV20">
+        <v>8</v>
+      </c>
+      <c r="AW20">
+        <v>9</v>
+      </c>
+      <c r="AX20">
+        <v>7</v>
+      </c>
+      <c r="AY20">
+        <v>19</v>
+      </c>
+      <c r="AZ20">
+        <v>19</v>
+      </c>
+      <c r="BA20">
+        <v>7</v>
+      </c>
+      <c r="BB20">
+        <v>7</v>
+      </c>
+      <c r="BC20">
+        <v>14</v>
+      </c>
+      <c r="BD20">
+        <v>1.73</v>
+      </c>
+      <c r="BE20">
+        <v>6.4</v>
+      </c>
+      <c r="BF20">
+        <v>2.33</v>
+      </c>
+      <c r="BG20">
+        <v>1.35</v>
+      </c>
+      <c r="BH20">
+        <v>2.8</v>
+      </c>
+      <c r="BI20">
+        <v>1.58</v>
+      </c>
+      <c r="BJ20">
+        <v>2.12</v>
+      </c>
+      <c r="BK20">
+        <v>1.97</v>
+      </c>
+      <c r="BL20">
+        <v>1.7</v>
+      </c>
+      <c r="BM20">
+        <v>2.55</v>
+      </c>
+      <c r="BN20">
+        <v>1.42</v>
+      </c>
+      <c r="BO20">
+        <v>3.3</v>
+      </c>
+      <c r="BP20">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -277,15 +277,15 @@
     <t>Cerezo Osaka</t>
   </si>
   <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
-    <t>Sanfrecce Hiroshima</t>
-  </si>
-  <si>
     <t>['31', '54']</t>
   </si>
   <si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>['22', '25', '42', '75']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
   <si>
     <t>['7', '46', '52', '63', '90+4']</t>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +976,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1361,7 +1364,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1591,7 +1594,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1797,7 +1800,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -1979,7 +1982,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2597,7 +2600,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2621,7 +2624,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2827,7 +2830,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3033,7 +3036,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3421,7 +3424,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -3651,7 +3654,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3833,7 +3836,7 @@
         <v>83</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3857,7 +3860,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4063,7 +4066,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4475,7 +4478,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4681,7 +4684,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -4838,6 +4841,212 @@
       </c>
       <c r="BP20">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7778092</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>103</v>
+      </c>
+      <c r="P21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q21">
+        <v>2.06</v>
+      </c>
+      <c r="R21">
+        <v>2.6</v>
+      </c>
+      <c r="S21">
+        <v>4.6</v>
+      </c>
+      <c r="T21">
+        <v>1.23</v>
+      </c>
+      <c r="U21">
+        <v>3.8</v>
+      </c>
+      <c r="V21">
+        <v>2.06</v>
+      </c>
+      <c r="W21">
+        <v>1.69</v>
+      </c>
+      <c r="X21">
+        <v>4.25</v>
+      </c>
+      <c r="Y21">
+        <v>1.19</v>
+      </c>
+      <c r="Z21">
+        <v>1.59</v>
+      </c>
+      <c r="AA21">
+        <v>4.6</v>
+      </c>
+      <c r="AB21">
+        <v>4.4</v>
+      </c>
+      <c r="AC21">
+        <v>1.02</v>
+      </c>
+      <c r="AD21">
+        <v>21</v>
+      </c>
+      <c r="AE21">
+        <v>1.13</v>
+      </c>
+      <c r="AF21">
+        <v>5.4</v>
+      </c>
+      <c r="AG21">
+        <v>1.43</v>
+      </c>
+      <c r="AH21">
+        <v>2.7</v>
+      </c>
+      <c r="AI21">
+        <v>1.49</v>
+      </c>
+      <c r="AJ21">
+        <v>2.43</v>
+      </c>
+      <c r="AK21">
+        <v>1.2</v>
+      </c>
+      <c r="AL21">
+        <v>1.19</v>
+      </c>
+      <c r="AM21">
+        <v>2.18</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>5</v>
+      </c>
+      <c r="AV21">
+        <v>2</v>
+      </c>
+      <c r="AW21">
+        <v>4</v>
+      </c>
+      <c r="AX21">
+        <v>7</v>
+      </c>
+      <c r="AY21">
+        <v>10</v>
+      </c>
+      <c r="AZ21">
+        <v>11</v>
+      </c>
+      <c r="BA21">
+        <v>3</v>
+      </c>
+      <c r="BB21">
+        <v>1</v>
+      </c>
+      <c r="BC21">
+        <v>4</v>
+      </c>
+      <c r="BD21">
+        <v>1.56</v>
+      </c>
+      <c r="BE21">
+        <v>6.75</v>
+      </c>
+      <c r="BF21">
+        <v>2.65</v>
+      </c>
+      <c r="BG21">
+        <v>1.25</v>
+      </c>
+      <c r="BH21">
+        <v>3.3</v>
+      </c>
+      <c r="BI21">
+        <v>1.46</v>
+      </c>
+      <c r="BJ21">
+        <v>2.43</v>
+      </c>
+      <c r="BK21">
+        <v>1.76</v>
+      </c>
+      <c r="BL21">
+        <v>1.88</v>
+      </c>
+      <c r="BM21">
+        <v>2.2</v>
+      </c>
+      <c r="BN21">
+        <v>1.55</v>
+      </c>
+      <c r="BO21">
+        <v>2.8</v>
+      </c>
+      <c r="BP21">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -328,6 +328,30 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['10', '78']</t>
+  </si>
+  <si>
+    <t>['45', '48']</t>
+  </si>
+  <si>
+    <t>['90+11']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['26', '49']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['31', '59', '90+6']</t>
+  </si>
+  <si>
+    <t>['66', '74']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -359,6 +383,21 @@
   </si>
   <si>
     <t>['32', '51']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['42', '85']</t>
   </si>
 </sst>
 </file>
@@ -720,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -976,7 +1015,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1057,7 +1096,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1263,7 +1302,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1469,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1594,7 +1633,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1800,7 +1839,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2087,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2624,7 +2663,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2705,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="AQ10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2830,7 +2869,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3036,7 +3075,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3114,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3526,10 +3565,10 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3654,7 +3693,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3860,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -3941,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4066,7 +4105,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4353,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4478,7 +4517,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4556,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -4684,7 +4723,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -5047,6 +5086,2066 @@
       </c>
       <c r="BP21">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7778093</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P22" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q22">
+        <v>2.7</v>
+      </c>
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>3.8</v>
+      </c>
+      <c r="T22">
+        <v>1.42</v>
+      </c>
+      <c r="U22">
+        <v>2.6</v>
+      </c>
+      <c r="V22">
+        <v>2.9</v>
+      </c>
+      <c r="W22">
+        <v>1.36</v>
+      </c>
+      <c r="X22">
+        <v>7.75</v>
+      </c>
+      <c r="Y22">
+        <v>1.07</v>
+      </c>
+      <c r="Z22">
+        <v>2.01</v>
+      </c>
+      <c r="AA22">
+        <v>3.32</v>
+      </c>
+      <c r="AB22">
+        <v>3.69</v>
+      </c>
+      <c r="AC22">
+        <v>1.01</v>
+      </c>
+      <c r="AD22">
+        <v>8.4</v>
+      </c>
+      <c r="AE22">
+        <v>1.35</v>
+      </c>
+      <c r="AF22">
+        <v>2.95</v>
+      </c>
+      <c r="AG22">
+        <v>2</v>
+      </c>
+      <c r="AH22">
+        <v>1.67</v>
+      </c>
+      <c r="AI22">
+        <v>1.85</v>
+      </c>
+      <c r="AJ22">
+        <v>1.83</v>
+      </c>
+      <c r="AK22">
+        <v>1.3</v>
+      </c>
+      <c r="AL22">
+        <v>1.32</v>
+      </c>
+      <c r="AM22">
+        <v>1.66</v>
+      </c>
+      <c r="AN22">
+        <v>3</v>
+      </c>
+      <c r="AO22">
+        <v>0.5</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
+        <v>0.33</v>
+      </c>
+      <c r="AR22">
+        <v>2.08</v>
+      </c>
+      <c r="AS22">
+        <v>1.39</v>
+      </c>
+      <c r="AT22">
+        <v>3.47</v>
+      </c>
+      <c r="AU22">
+        <v>5</v>
+      </c>
+      <c r="AV22">
+        <v>6</v>
+      </c>
+      <c r="AW22">
+        <v>9</v>
+      </c>
+      <c r="AX22">
+        <v>6</v>
+      </c>
+      <c r="AY22">
+        <v>15</v>
+      </c>
+      <c r="AZ22">
+        <v>12</v>
+      </c>
+      <c r="BA22">
+        <v>5</v>
+      </c>
+      <c r="BB22">
+        <v>3</v>
+      </c>
+      <c r="BC22">
+        <v>8</v>
+      </c>
+      <c r="BD22">
+        <v>1.79</v>
+      </c>
+      <c r="BE22">
+        <v>6.4</v>
+      </c>
+      <c r="BF22">
+        <v>2.23</v>
+      </c>
+      <c r="BG22">
+        <v>1.44</v>
+      </c>
+      <c r="BH22">
+        <v>2.48</v>
+      </c>
+      <c r="BI22">
+        <v>1.74</v>
+      </c>
+      <c r="BJ22">
+        <v>1.91</v>
+      </c>
+      <c r="BK22">
+        <v>2.18</v>
+      </c>
+      <c r="BL22">
+        <v>1.56</v>
+      </c>
+      <c r="BM22">
+        <v>2.88</v>
+      </c>
+      <c r="BN22">
+        <v>1.33</v>
+      </c>
+      <c r="BO22">
+        <v>3.9</v>
+      </c>
+      <c r="BP22">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7778101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>105</v>
+      </c>
+      <c r="P23" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q23">
+        <v>4</v>
+      </c>
+      <c r="R23">
+        <v>1.95</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+      <c r="T23">
+        <v>1.53</v>
+      </c>
+      <c r="U23">
+        <v>2.38</v>
+      </c>
+      <c r="V23">
+        <v>3.5</v>
+      </c>
+      <c r="W23">
+        <v>1.29</v>
+      </c>
+      <c r="X23">
+        <v>11</v>
+      </c>
+      <c r="Y23">
+        <v>1.05</v>
+      </c>
+      <c r="Z23">
+        <v>3.23</v>
+      </c>
+      <c r="AA23">
+        <v>3.25</v>
+      </c>
+      <c r="AB23">
+        <v>2.21</v>
+      </c>
+      <c r="AC23">
+        <v>1.08</v>
+      </c>
+      <c r="AD23">
+        <v>7.5</v>
+      </c>
+      <c r="AE23">
+        <v>1.45</v>
+      </c>
+      <c r="AF23">
+        <v>2.5</v>
+      </c>
+      <c r="AG23">
+        <v>2.1</v>
+      </c>
+      <c r="AH23">
+        <v>1.6</v>
+      </c>
+      <c r="AI23">
+        <v>2.05</v>
+      </c>
+      <c r="AJ23">
+        <v>1.7</v>
+      </c>
+      <c r="AK23">
+        <v>1.63</v>
+      </c>
+      <c r="AL23">
+        <v>1.32</v>
+      </c>
+      <c r="AM23">
+        <v>1.32</v>
+      </c>
+      <c r="AN23">
+        <v>3</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>3</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>1.24</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>1.24</v>
+      </c>
+      <c r="AU23">
+        <v>-1</v>
+      </c>
+      <c r="AV23">
+        <v>-1</v>
+      </c>
+      <c r="AW23">
+        <v>-1</v>
+      </c>
+      <c r="AX23">
+        <v>-1</v>
+      </c>
+      <c r="AY23">
+        <v>-1</v>
+      </c>
+      <c r="AZ23">
+        <v>-1</v>
+      </c>
+      <c r="BA23">
+        <v>-1</v>
+      </c>
+      <c r="BB23">
+        <v>-1</v>
+      </c>
+      <c r="BC23">
+        <v>-1</v>
+      </c>
+      <c r="BD23">
+        <v>2.33</v>
+      </c>
+      <c r="BE23">
+        <v>6.1</v>
+      </c>
+      <c r="BF23">
+        <v>1.74</v>
+      </c>
+      <c r="BG23">
+        <v>1.49</v>
+      </c>
+      <c r="BH23">
+        <v>2.35</v>
+      </c>
+      <c r="BI23">
+        <v>1.82</v>
+      </c>
+      <c r="BJ23">
+        <v>1.82</v>
+      </c>
+      <c r="BK23">
+        <v>2.32</v>
+      </c>
+      <c r="BL23">
+        <v>1.5</v>
+      </c>
+      <c r="BM23">
+        <v>3.05</v>
+      </c>
+      <c r="BN23">
+        <v>1.3</v>
+      </c>
+      <c r="BO23">
+        <v>4.1</v>
+      </c>
+      <c r="BP23">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7778100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24" t="s">
+        <v>106</v>
+      </c>
+      <c r="P24" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q24">
+        <v>2.2</v>
+      </c>
+      <c r="R24">
+        <v>2.2</v>
+      </c>
+      <c r="S24">
+        <v>4.75</v>
+      </c>
+      <c r="T24">
+        <v>1.35</v>
+      </c>
+      <c r="U24">
+        <v>2.9</v>
+      </c>
+      <c r="V24">
+        <v>2.65</v>
+      </c>
+      <c r="W24">
+        <v>1.42</v>
+      </c>
+      <c r="X24">
+        <v>6.5</v>
+      </c>
+      <c r="Y24">
+        <v>1.09</v>
+      </c>
+      <c r="Z24">
+        <v>1.65</v>
+      </c>
+      <c r="AA24">
+        <v>3.98</v>
+      </c>
+      <c r="AB24">
+        <v>4.75</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>9</v>
+      </c>
+      <c r="AE24">
+        <v>1.28</v>
+      </c>
+      <c r="AF24">
+        <v>3.3</v>
+      </c>
+      <c r="AG24">
+        <v>1.85</v>
+      </c>
+      <c r="AH24">
+        <v>1.89</v>
+      </c>
+      <c r="AI24">
+        <v>1.85</v>
+      </c>
+      <c r="AJ24">
+        <v>1.83</v>
+      </c>
+      <c r="AK24">
+        <v>1.18</v>
+      </c>
+      <c r="AL24">
+        <v>1.24</v>
+      </c>
+      <c r="AM24">
+        <v>2.15</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>1</v>
+      </c>
+      <c r="AQ24">
+        <v>0.5</v>
+      </c>
+      <c r="AR24">
+        <v>0.78</v>
+      </c>
+      <c r="AS24">
+        <v>2.08</v>
+      </c>
+      <c r="AT24">
+        <v>2.86</v>
+      </c>
+      <c r="AU24">
+        <v>-1</v>
+      </c>
+      <c r="AV24">
+        <v>-1</v>
+      </c>
+      <c r="AW24">
+        <v>-1</v>
+      </c>
+      <c r="AX24">
+        <v>-1</v>
+      </c>
+      <c r="AY24">
+        <v>-1</v>
+      </c>
+      <c r="AZ24">
+        <v>-1</v>
+      </c>
+      <c r="BA24">
+        <v>-1</v>
+      </c>
+      <c r="BB24">
+        <v>-1</v>
+      </c>
+      <c r="BC24">
+        <v>-1</v>
+      </c>
+      <c r="BD24">
+        <v>1.52</v>
+      </c>
+      <c r="BE24">
+        <v>6.5</v>
+      </c>
+      <c r="BF24">
+        <v>2.8</v>
+      </c>
+      <c r="BG24">
+        <v>1.36</v>
+      </c>
+      <c r="BH24">
+        <v>2.75</v>
+      </c>
+      <c r="BI24">
+        <v>1.63</v>
+      </c>
+      <c r="BJ24">
+        <v>2.06</v>
+      </c>
+      <c r="BK24">
+        <v>2.02</v>
+      </c>
+      <c r="BL24">
+        <v>1.65</v>
+      </c>
+      <c r="BM24">
+        <v>2.6</v>
+      </c>
+      <c r="BN24">
+        <v>1.4</v>
+      </c>
+      <c r="BO24">
+        <v>3.4</v>
+      </c>
+      <c r="BP24">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7778099</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>107</v>
+      </c>
+      <c r="P25" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q25">
+        <v>4.33</v>
+      </c>
+      <c r="R25">
+        <v>2.25</v>
+      </c>
+      <c r="S25">
+        <v>2.5</v>
+      </c>
+      <c r="T25">
+        <v>1.36</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>2.63</v>
+      </c>
+      <c r="W25">
+        <v>1.44</v>
+      </c>
+      <c r="X25">
+        <v>7</v>
+      </c>
+      <c r="Y25">
+        <v>1.1</v>
+      </c>
+      <c r="Z25">
+        <v>3.75</v>
+      </c>
+      <c r="AA25">
+        <v>3.78</v>
+      </c>
+      <c r="AB25">
+        <v>1.85</v>
+      </c>
+      <c r="AC25">
+        <v>1.05</v>
+      </c>
+      <c r="AD25">
+        <v>9.5</v>
+      </c>
+      <c r="AE25">
+        <v>1.25</v>
+      </c>
+      <c r="AF25">
+        <v>3.6</v>
+      </c>
+      <c r="AG25">
+        <v>1.82</v>
+      </c>
+      <c r="AH25">
+        <v>1.92</v>
+      </c>
+      <c r="AI25">
+        <v>1.7</v>
+      </c>
+      <c r="AJ25">
+        <v>2.05</v>
+      </c>
+      <c r="AK25">
+        <v>1.93</v>
+      </c>
+      <c r="AL25">
+        <v>1.27</v>
+      </c>
+      <c r="AM25">
+        <v>1.22</v>
+      </c>
+      <c r="AN25">
+        <v>3</v>
+      </c>
+      <c r="AO25">
+        <v>3</v>
+      </c>
+      <c r="AP25">
+        <v>2</v>
+      </c>
+      <c r="AQ25">
+        <v>2</v>
+      </c>
+      <c r="AR25">
+        <v>1.58</v>
+      </c>
+      <c r="AS25">
+        <v>1.76</v>
+      </c>
+      <c r="AT25">
+        <v>3.34</v>
+      </c>
+      <c r="AU25">
+        <v>-1</v>
+      </c>
+      <c r="AV25">
+        <v>-1</v>
+      </c>
+      <c r="AW25">
+        <v>-1</v>
+      </c>
+      <c r="AX25">
+        <v>-1</v>
+      </c>
+      <c r="AY25">
+        <v>-1</v>
+      </c>
+      <c r="AZ25">
+        <v>-1</v>
+      </c>
+      <c r="BA25">
+        <v>-1</v>
+      </c>
+      <c r="BB25">
+        <v>-1</v>
+      </c>
+      <c r="BC25">
+        <v>-1</v>
+      </c>
+      <c r="BD25">
+        <v>2.55</v>
+      </c>
+      <c r="BE25">
+        <v>6.5</v>
+      </c>
+      <c r="BF25">
+        <v>1.64</v>
+      </c>
+      <c r="BG25">
+        <v>1.35</v>
+      </c>
+      <c r="BH25">
+        <v>2.8</v>
+      </c>
+      <c r="BI25">
+        <v>1.62</v>
+      </c>
+      <c r="BJ25">
+        <v>2.08</v>
+      </c>
+      <c r="BK25">
+        <v>2</v>
+      </c>
+      <c r="BL25">
+        <v>1.67</v>
+      </c>
+      <c r="BM25">
+        <v>2.6</v>
+      </c>
+      <c r="BN25">
+        <v>1.4</v>
+      </c>
+      <c r="BO25">
+        <v>3.4</v>
+      </c>
+      <c r="BP25">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7778098</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26" t="s">
+        <v>108</v>
+      </c>
+      <c r="P26" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q26">
+        <v>3.8</v>
+      </c>
+      <c r="R26">
+        <v>2.05</v>
+      </c>
+      <c r="S26">
+        <v>2.65</v>
+      </c>
+      <c r="T26">
+        <v>1.4</v>
+      </c>
+      <c r="U26">
+        <v>2.7</v>
+      </c>
+      <c r="V26">
+        <v>2.8</v>
+      </c>
+      <c r="W26">
+        <v>1.38</v>
+      </c>
+      <c r="X26">
+        <v>7.25</v>
+      </c>
+      <c r="Y26">
+        <v>1.08</v>
+      </c>
+      <c r="Z26">
+        <v>2.65</v>
+      </c>
+      <c r="AA26">
+        <v>3.23</v>
+      </c>
+      <c r="AB26">
+        <v>2.61</v>
+      </c>
+      <c r="AC26">
+        <v>1.01</v>
+      </c>
+      <c r="AD26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE26">
+        <v>1.34</v>
+      </c>
+      <c r="AF26">
+        <v>3</v>
+      </c>
+      <c r="AG26">
+        <v>2.03</v>
+      </c>
+      <c r="AH26">
+        <v>1.72</v>
+      </c>
+      <c r="AI26">
+        <v>1.8</v>
+      </c>
+      <c r="AJ26">
+        <v>1.88</v>
+      </c>
+      <c r="AK26">
+        <v>1.7</v>
+      </c>
+      <c r="AL26">
+        <v>1.3</v>
+      </c>
+      <c r="AM26">
+        <v>1.3</v>
+      </c>
+      <c r="AN26">
+        <v>3</v>
+      </c>
+      <c r="AO26">
+        <v>1</v>
+      </c>
+      <c r="AP26">
+        <v>3</v>
+      </c>
+      <c r="AQ26">
+        <v>0.67</v>
+      </c>
+      <c r="AR26">
+        <v>2</v>
+      </c>
+      <c r="AS26">
+        <v>1.9</v>
+      </c>
+      <c r="AT26">
+        <v>3.9</v>
+      </c>
+      <c r="AU26">
+        <v>-1</v>
+      </c>
+      <c r="AV26">
+        <v>-1</v>
+      </c>
+      <c r="AW26">
+        <v>-1</v>
+      </c>
+      <c r="AX26">
+        <v>-1</v>
+      </c>
+      <c r="AY26">
+        <v>-1</v>
+      </c>
+      <c r="AZ26">
+        <v>-1</v>
+      </c>
+      <c r="BA26">
+        <v>-1</v>
+      </c>
+      <c r="BB26">
+        <v>-1</v>
+      </c>
+      <c r="BC26">
+        <v>-1</v>
+      </c>
+      <c r="BD26">
+        <v>2.23</v>
+      </c>
+      <c r="BE26">
+        <v>6.25</v>
+      </c>
+      <c r="BF26">
+        <v>1.8</v>
+      </c>
+      <c r="BG26">
+        <v>1.41</v>
+      </c>
+      <c r="BH26">
+        <v>2.55</v>
+      </c>
+      <c r="BI26">
+        <v>1.7</v>
+      </c>
+      <c r="BJ26">
+        <v>1.96</v>
+      </c>
+      <c r="BK26">
+        <v>2.14</v>
+      </c>
+      <c r="BL26">
+        <v>1.58</v>
+      </c>
+      <c r="BM26">
+        <v>2.8</v>
+      </c>
+      <c r="BN26">
+        <v>1.35</v>
+      </c>
+      <c r="BO26">
+        <v>3.75</v>
+      </c>
+      <c r="BP26">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7778102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>109</v>
+      </c>
+      <c r="P27" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q27">
+        <v>3.9</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>2.75</v>
+      </c>
+      <c r="T27">
+        <v>1.44</v>
+      </c>
+      <c r="U27">
+        <v>2.55</v>
+      </c>
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <v>1.33</v>
+      </c>
+      <c r="X27">
+        <v>8.25</v>
+      </c>
+      <c r="Y27">
+        <v>1.06</v>
+      </c>
+      <c r="Z27">
+        <v>3.25</v>
+      </c>
+      <c r="AA27">
+        <v>3.14</v>
+      </c>
+      <c r="AB27">
+        <v>2.25</v>
+      </c>
+      <c r="AC27">
+        <v>1.02</v>
+      </c>
+      <c r="AD27">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE27">
+        <v>1.36</v>
+      </c>
+      <c r="AF27">
+        <v>2.85</v>
+      </c>
+      <c r="AG27">
+        <v>2.05</v>
+      </c>
+      <c r="AH27">
+        <v>1.61</v>
+      </c>
+      <c r="AI27">
+        <v>1.88</v>
+      </c>
+      <c r="AJ27">
+        <v>1.8</v>
+      </c>
+      <c r="AK27">
+        <v>1.68</v>
+      </c>
+      <c r="AL27">
+        <v>1.32</v>
+      </c>
+      <c r="AM27">
+        <v>1.29</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>1</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>2</v>
+      </c>
+      <c r="AR27">
+        <v>0.91</v>
+      </c>
+      <c r="AS27">
+        <v>1.15</v>
+      </c>
+      <c r="AT27">
+        <v>2.06</v>
+      </c>
+      <c r="AU27">
+        <v>-1</v>
+      </c>
+      <c r="AV27">
+        <v>-1</v>
+      </c>
+      <c r="AW27">
+        <v>-1</v>
+      </c>
+      <c r="AX27">
+        <v>-1</v>
+      </c>
+      <c r="AY27">
+        <v>-1</v>
+      </c>
+      <c r="AZ27">
+        <v>-1</v>
+      </c>
+      <c r="BA27">
+        <v>-1</v>
+      </c>
+      <c r="BB27">
+        <v>-1</v>
+      </c>
+      <c r="BC27">
+        <v>-1</v>
+      </c>
+      <c r="BD27">
+        <v>2.4</v>
+      </c>
+      <c r="BE27">
+        <v>6.4</v>
+      </c>
+      <c r="BF27">
+        <v>1.7</v>
+      </c>
+      <c r="BG27">
+        <v>1.42</v>
+      </c>
+      <c r="BH27">
+        <v>2.55</v>
+      </c>
+      <c r="BI27">
+        <v>1.71</v>
+      </c>
+      <c r="BJ27">
+        <v>1.94</v>
+      </c>
+      <c r="BK27">
+        <v>2.14</v>
+      </c>
+      <c r="BL27">
+        <v>1.58</v>
+      </c>
+      <c r="BM27">
+        <v>2.8</v>
+      </c>
+      <c r="BN27">
+        <v>1.35</v>
+      </c>
+      <c r="BO27">
+        <v>3.7</v>
+      </c>
+      <c r="BP27">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7778096</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>92</v>
+      </c>
+      <c r="P28" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28">
+        <v>2.75</v>
+      </c>
+      <c r="R28">
+        <v>1.95</v>
+      </c>
+      <c r="S28">
+        <v>4.1</v>
+      </c>
+      <c r="T28">
+        <v>1.49</v>
+      </c>
+      <c r="U28">
+        <v>2.4</v>
+      </c>
+      <c r="V28">
+        <v>3.3</v>
+      </c>
+      <c r="W28">
+        <v>1.29</v>
+      </c>
+      <c r="X28">
+        <v>9.25</v>
+      </c>
+      <c r="Y28">
+        <v>1.05</v>
+      </c>
+      <c r="Z28">
+        <v>2.01</v>
+      </c>
+      <c r="AA28">
+        <v>3.12</v>
+      </c>
+      <c r="AB28">
+        <v>3.97</v>
+      </c>
+      <c r="AC28">
+        <v>1.03</v>
+      </c>
+      <c r="AD28">
+        <v>7.3</v>
+      </c>
+      <c r="AE28">
+        <v>1.5</v>
+      </c>
+      <c r="AF28">
+        <v>2.4</v>
+      </c>
+      <c r="AG28">
+        <v>2.25</v>
+      </c>
+      <c r="AH28">
+        <v>1.53</v>
+      </c>
+      <c r="AI28">
+        <v>2.05</v>
+      </c>
+      <c r="AJ28">
+        <v>1.68</v>
+      </c>
+      <c r="AK28">
+        <v>1.28</v>
+      </c>
+      <c r="AL28">
+        <v>1.33</v>
+      </c>
+      <c r="AM28">
+        <v>1.7</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>1.5</v>
+      </c>
+      <c r="AR28">
+        <v>0.8</v>
+      </c>
+      <c r="AS28">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT28">
+        <v>1.74</v>
+      </c>
+      <c r="AU28">
+        <v>-1</v>
+      </c>
+      <c r="AV28">
+        <v>-1</v>
+      </c>
+      <c r="AW28">
+        <v>-1</v>
+      </c>
+      <c r="AX28">
+        <v>-1</v>
+      </c>
+      <c r="AY28">
+        <v>-1</v>
+      </c>
+      <c r="AZ28">
+        <v>-1</v>
+      </c>
+      <c r="BA28">
+        <v>-1</v>
+      </c>
+      <c r="BB28">
+        <v>-1</v>
+      </c>
+      <c r="BC28">
+        <v>-1</v>
+      </c>
+      <c r="BD28">
+        <v>1.7</v>
+      </c>
+      <c r="BE28">
+        <v>6.25</v>
+      </c>
+      <c r="BF28">
+        <v>2.4</v>
+      </c>
+      <c r="BG28">
+        <v>1.46</v>
+      </c>
+      <c r="BH28">
+        <v>2.4</v>
+      </c>
+      <c r="BI28">
+        <v>1.79</v>
+      </c>
+      <c r="BJ28">
+        <v>1.85</v>
+      </c>
+      <c r="BK28">
+        <v>2.28</v>
+      </c>
+      <c r="BL28">
+        <v>1.52</v>
+      </c>
+      <c r="BM28">
+        <v>2.95</v>
+      </c>
+      <c r="BN28">
+        <v>1.32</v>
+      </c>
+      <c r="BO28">
+        <v>3.95</v>
+      </c>
+      <c r="BP28">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7778095</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29" t="s">
+        <v>110</v>
+      </c>
+      <c r="P29" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q29">
+        <v>3.2</v>
+      </c>
+      <c r="R29">
+        <v>1.95</v>
+      </c>
+      <c r="S29">
+        <v>3.4</v>
+      </c>
+      <c r="T29">
+        <v>1.47</v>
+      </c>
+      <c r="U29">
+        <v>2.5</v>
+      </c>
+      <c r="V29">
+        <v>3.1</v>
+      </c>
+      <c r="W29">
+        <v>1.32</v>
+      </c>
+      <c r="X29">
+        <v>8.5</v>
+      </c>
+      <c r="Y29">
+        <v>1.06</v>
+      </c>
+      <c r="Z29">
+        <v>2.59</v>
+      </c>
+      <c r="AA29">
+        <v>3.05</v>
+      </c>
+      <c r="AB29">
+        <v>2.81</v>
+      </c>
+      <c r="AC29">
+        <v>1.03</v>
+      </c>
+      <c r="AD29">
+        <v>7.3</v>
+      </c>
+      <c r="AE29">
+        <v>1.5</v>
+      </c>
+      <c r="AF29">
+        <v>2.4</v>
+      </c>
+      <c r="AG29">
+        <v>2.1</v>
+      </c>
+      <c r="AH29">
+        <v>1.6</v>
+      </c>
+      <c r="AI29">
+        <v>1.9</v>
+      </c>
+      <c r="AJ29">
+        <v>1.8</v>
+      </c>
+      <c r="AK29">
+        <v>1.42</v>
+      </c>
+      <c r="AL29">
+        <v>1.34</v>
+      </c>
+      <c r="AM29">
+        <v>1.47</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>1.5</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>1.17</v>
+      </c>
+      <c r="AS29">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT29">
+        <v>1.98</v>
+      </c>
+      <c r="AU29">
+        <v>-1</v>
+      </c>
+      <c r="AV29">
+        <v>-1</v>
+      </c>
+      <c r="AW29">
+        <v>-1</v>
+      </c>
+      <c r="AX29">
+        <v>-1</v>
+      </c>
+      <c r="AY29">
+        <v>-1</v>
+      </c>
+      <c r="AZ29">
+        <v>-1</v>
+      </c>
+      <c r="BA29">
+        <v>-1</v>
+      </c>
+      <c r="BB29">
+        <v>-1</v>
+      </c>
+      <c r="BC29">
+        <v>-1</v>
+      </c>
+      <c r="BD29">
+        <v>1.92</v>
+      </c>
+      <c r="BE29">
+        <v>6.25</v>
+      </c>
+      <c r="BF29">
+        <v>2.08</v>
+      </c>
+      <c r="BG29">
+        <v>1.52</v>
+      </c>
+      <c r="BH29">
+        <v>2.28</v>
+      </c>
+      <c r="BI29">
+        <v>1.86</v>
+      </c>
+      <c r="BJ29">
+        <v>1.78</v>
+      </c>
+      <c r="BK29">
+        <v>2.38</v>
+      </c>
+      <c r="BL29">
+        <v>1.47</v>
+      </c>
+      <c r="BM29">
+        <v>3.15</v>
+      </c>
+      <c r="BN29">
+        <v>1.28</v>
+      </c>
+      <c r="BO29">
+        <v>4.35</v>
+      </c>
+      <c r="BP29">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7778094</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="s">
+        <v>111</v>
+      </c>
+      <c r="P30" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q30">
+        <v>2.95</v>
+      </c>
+      <c r="R30">
+        <v>1.95</v>
+      </c>
+      <c r="S30">
+        <v>3.6</v>
+      </c>
+      <c r="T30">
+        <v>1.47</v>
+      </c>
+      <c r="U30">
+        <v>2.5</v>
+      </c>
+      <c r="V30">
+        <v>3.1</v>
+      </c>
+      <c r="W30">
+        <v>1.32</v>
+      </c>
+      <c r="X30">
+        <v>8.5</v>
+      </c>
+      <c r="Y30">
+        <v>1.06</v>
+      </c>
+      <c r="Z30">
+        <v>2.05</v>
+      </c>
+      <c r="AA30">
+        <v>3.27</v>
+      </c>
+      <c r="AB30">
+        <v>3.62</v>
+      </c>
+      <c r="AC30">
+        <v>1.02</v>
+      </c>
+      <c r="AD30">
+        <v>8.1</v>
+      </c>
+      <c r="AE30">
+        <v>1.37</v>
+      </c>
+      <c r="AF30">
+        <v>2.85</v>
+      </c>
+      <c r="AG30">
+        <v>2.05</v>
+      </c>
+      <c r="AH30">
+        <v>1.61</v>
+      </c>
+      <c r="AI30">
+        <v>1.87</v>
+      </c>
+      <c r="AJ30">
+        <v>1.82</v>
+      </c>
+      <c r="AK30">
+        <v>1.35</v>
+      </c>
+      <c r="AL30">
+        <v>1.34</v>
+      </c>
+      <c r="AM30">
+        <v>1.57</v>
+      </c>
+      <c r="AN30">
+        <v>1</v>
+      </c>
+      <c r="AO30">
+        <v>3</v>
+      </c>
+      <c r="AP30">
+        <v>2</v>
+      </c>
+      <c r="AQ30">
+        <v>1.5</v>
+      </c>
+      <c r="AR30">
+        <v>1.39</v>
+      </c>
+      <c r="AS30">
+        <v>1.77</v>
+      </c>
+      <c r="AT30">
+        <v>3.16</v>
+      </c>
+      <c r="AU30">
+        <v>5</v>
+      </c>
+      <c r="AV30">
+        <v>4</v>
+      </c>
+      <c r="AW30">
+        <v>7</v>
+      </c>
+      <c r="AX30">
+        <v>8</v>
+      </c>
+      <c r="AY30">
+        <v>14</v>
+      </c>
+      <c r="AZ30">
+        <v>14</v>
+      </c>
+      <c r="BA30">
+        <v>4</v>
+      </c>
+      <c r="BB30">
+        <v>5</v>
+      </c>
+      <c r="BC30">
+        <v>9</v>
+      </c>
+      <c r="BD30">
+        <v>1.83</v>
+      </c>
+      <c r="BE30">
+        <v>6.1</v>
+      </c>
+      <c r="BF30">
+        <v>2.23</v>
+      </c>
+      <c r="BG30">
+        <v>1.46</v>
+      </c>
+      <c r="BH30">
+        <v>2.4</v>
+      </c>
+      <c r="BI30">
+        <v>1.78</v>
+      </c>
+      <c r="BJ30">
+        <v>1.86</v>
+      </c>
+      <c r="BK30">
+        <v>2.25</v>
+      </c>
+      <c r="BL30">
+        <v>1.52</v>
+      </c>
+      <c r="BM30">
+        <v>3</v>
+      </c>
+      <c r="BN30">
+        <v>1.3</v>
+      </c>
+      <c r="BO30">
+        <v>4</v>
+      </c>
+      <c r="BP30">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7778097</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45714.29166666666</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>92</v>
+      </c>
+      <c r="P31" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q31">
+        <v>2.6</v>
+      </c>
+      <c r="R31">
+        <v>2.2</v>
+      </c>
+      <c r="S31">
+        <v>4.33</v>
+      </c>
+      <c r="T31">
+        <v>1.4</v>
+      </c>
+      <c r="U31">
+        <v>2.75</v>
+      </c>
+      <c r="V31">
+        <v>3</v>
+      </c>
+      <c r="W31">
+        <v>1.36</v>
+      </c>
+      <c r="X31">
+        <v>8</v>
+      </c>
+      <c r="Y31">
+        <v>1.08</v>
+      </c>
+      <c r="Z31">
+        <v>1.8</v>
+      </c>
+      <c r="AA31">
+        <v>3.29</v>
+      </c>
+      <c r="AB31">
+        <v>4.8</v>
+      </c>
+      <c r="AC31">
+        <v>1.06</v>
+      </c>
+      <c r="AD31">
+        <v>8.75</v>
+      </c>
+      <c r="AE31">
+        <v>1.3</v>
+      </c>
+      <c r="AF31">
+        <v>3.25</v>
+      </c>
+      <c r="AG31">
+        <v>1.92</v>
+      </c>
+      <c r="AH31">
+        <v>1.82</v>
+      </c>
+      <c r="AI31">
+        <v>1.8</v>
+      </c>
+      <c r="AJ31">
+        <v>1.95</v>
+      </c>
+      <c r="AK31">
+        <v>1.25</v>
+      </c>
+      <c r="AL31">
+        <v>1.29</v>
+      </c>
+      <c r="AM31">
+        <v>1.83</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1</v>
+      </c>
+      <c r="AQ31">
+        <v>1</v>
+      </c>
+      <c r="AR31">
+        <v>1.14</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>1.14</v>
+      </c>
+      <c r="AU31">
+        <v>-1</v>
+      </c>
+      <c r="AV31">
+        <v>-1</v>
+      </c>
+      <c r="AW31">
+        <v>-1</v>
+      </c>
+      <c r="AX31">
+        <v>-1</v>
+      </c>
+      <c r="AY31">
+        <v>-1</v>
+      </c>
+      <c r="AZ31">
+        <v>-1</v>
+      </c>
+      <c r="BA31">
+        <v>-1</v>
+      </c>
+      <c r="BB31">
+        <v>-1</v>
+      </c>
+      <c r="BC31">
+        <v>-1</v>
+      </c>
+      <c r="BD31">
+        <v>1.7</v>
+      </c>
+      <c r="BE31">
+        <v>6.4</v>
+      </c>
+      <c r="BF31">
+        <v>2.4</v>
+      </c>
+      <c r="BG31">
+        <v>1.38</v>
+      </c>
+      <c r="BH31">
+        <v>2.7</v>
+      </c>
+      <c r="BI31">
+        <v>1.66</v>
+      </c>
+      <c r="BJ31">
+        <v>2.02</v>
+      </c>
+      <c r="BK31">
+        <v>2.06</v>
+      </c>
+      <c r="BL31">
+        <v>1.63</v>
+      </c>
+      <c r="BM31">
+        <v>2.65</v>
+      </c>
+      <c r="BN31">
+        <v>1.38</v>
+      </c>
+      <c r="BO31">
+        <v>3.55</v>
+      </c>
+      <c r="BP31">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -5434,31 +5434,31 @@
         <v>1.24</v>
       </c>
       <c r="AU23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AX23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY23">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AZ23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD23">
         <v>2.33</v>
@@ -5640,31 +5640,31 @@
         <v>2.86</v>
       </c>
       <c r="AU24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW24">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AX24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY24">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AZ24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD24">
         <v>1.52</v>
@@ -5846,31 +5846,31 @@
         <v>3.34</v>
       </c>
       <c r="AU25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AX25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ25">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BA25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD25">
         <v>2.55</v>
@@ -6052,31 +6052,31 @@
         <v>3.9</v>
       </c>
       <c r="AU26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY26">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AZ26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BB26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD26">
         <v>2.23</v>
@@ -6258,31 +6258,31 @@
         <v>2.06</v>
       </c>
       <c r="AU27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY27">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ27">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD27">
         <v>2.4</v>
@@ -6464,31 +6464,31 @@
         <v>1.74</v>
       </c>
       <c r="AU28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY28">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD28">
         <v>1.7</v>
@@ -6670,31 +6670,31 @@
         <v>1.98</v>
       </c>
       <c r="AU29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AZ29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BA29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD29">
         <v>1.92</v>
@@ -7082,31 +7082,31 @@
         <v>1.14</v>
       </c>
       <c r="AU31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX31">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AY31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AZ31">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="BA31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD31">
         <v>1.7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -6073,10 +6073,10 @@
         <v>10</v>
       </c>
       <c r="BB26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD26">
         <v>2.23</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="131">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -352,6 +352,12 @@
     <t>['66', '74']</t>
   </si>
   <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['74', '90+1']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -398,6 +404,9 @@
   </si>
   <si>
     <t>['42', '85']</t>
+  </si>
+  <si>
+    <t>['55']</t>
   </si>
 </sst>
 </file>
@@ -759,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1015,7 +1024,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1302,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1505,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ4">
         <v>0.67</v>
@@ -1633,7 +1642,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1714,7 +1723,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1839,7 +1848,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2329,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -2663,7 +2672,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2869,7 +2878,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3075,7 +3084,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3693,7 +3702,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3899,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4105,7 +4114,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4186,7 +4195,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR17">
         <v>2.07</v>
@@ -4517,7 +4526,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4723,7 +4732,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -4804,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="AQ20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5135,7 +5144,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -5547,7 +5556,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5625,10 +5634,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ24">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -5753,7 +5762,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5959,7 +5968,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6165,7 +6174,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6371,7 +6380,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6783,7 +6792,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7146,6 +7155,830 @@
       </c>
       <c r="BP31">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7778107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45717.04166666666</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>112</v>
+      </c>
+      <c r="P32" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q32">
+        <v>2.63</v>
+      </c>
+      <c r="R32">
+        <v>2.38</v>
+      </c>
+      <c r="S32">
+        <v>3.75</v>
+      </c>
+      <c r="T32">
+        <v>1.3</v>
+      </c>
+      <c r="U32">
+        <v>3.4</v>
+      </c>
+      <c r="V32">
+        <v>2.5</v>
+      </c>
+      <c r="W32">
+        <v>1.5</v>
+      </c>
+      <c r="X32">
+        <v>6</v>
+      </c>
+      <c r="Y32">
+        <v>1.13</v>
+      </c>
+      <c r="Z32">
+        <v>1.92</v>
+      </c>
+      <c r="AA32">
+        <v>3.88</v>
+      </c>
+      <c r="AB32">
+        <v>3.45</v>
+      </c>
+      <c r="AC32">
+        <v>1.04</v>
+      </c>
+      <c r="AD32">
+        <v>10</v>
+      </c>
+      <c r="AE32">
+        <v>1.22</v>
+      </c>
+      <c r="AF32">
+        <v>4.2</v>
+      </c>
+      <c r="AG32">
+        <v>1.55</v>
+      </c>
+      <c r="AH32">
+        <v>2.2</v>
+      </c>
+      <c r="AI32">
+        <v>1.53</v>
+      </c>
+      <c r="AJ32">
+        <v>2.38</v>
+      </c>
+      <c r="AK32">
+        <v>1.37</v>
+      </c>
+      <c r="AL32">
+        <v>1.28</v>
+      </c>
+      <c r="AM32">
+        <v>1.63</v>
+      </c>
+      <c r="AN32">
+        <v>1</v>
+      </c>
+      <c r="AO32">
+        <v>3</v>
+      </c>
+      <c r="AP32">
+        <v>1</v>
+      </c>
+      <c r="AQ32">
+        <v>2</v>
+      </c>
+      <c r="AR32">
+        <v>1.12</v>
+      </c>
+      <c r="AS32">
+        <v>1.88</v>
+      </c>
+      <c r="AT32">
+        <v>3</v>
+      </c>
+      <c r="AU32">
+        <v>4</v>
+      </c>
+      <c r="AV32">
+        <v>6</v>
+      </c>
+      <c r="AW32">
+        <v>8</v>
+      </c>
+      <c r="AX32">
+        <v>4</v>
+      </c>
+      <c r="AY32">
+        <v>13</v>
+      </c>
+      <c r="AZ32">
+        <v>10</v>
+      </c>
+      <c r="BA32">
+        <v>3</v>
+      </c>
+      <c r="BB32">
+        <v>6</v>
+      </c>
+      <c r="BC32">
+        <v>9</v>
+      </c>
+      <c r="BD32">
+        <v>1.75</v>
+      </c>
+      <c r="BE32">
+        <v>6.4</v>
+      </c>
+      <c r="BF32">
+        <v>2.3</v>
+      </c>
+      <c r="BG32">
+        <v>1.32</v>
+      </c>
+      <c r="BH32">
+        <v>2.95</v>
+      </c>
+      <c r="BI32">
+        <v>1.55</v>
+      </c>
+      <c r="BJ32">
+        <v>2.2</v>
+      </c>
+      <c r="BK32">
+        <v>1.91</v>
+      </c>
+      <c r="BL32">
+        <v>1.74</v>
+      </c>
+      <c r="BM32">
+        <v>2.43</v>
+      </c>
+      <c r="BN32">
+        <v>1.46</v>
+      </c>
+      <c r="BO32">
+        <v>3.15</v>
+      </c>
+      <c r="BP32">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7778103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>113</v>
+      </c>
+      <c r="P33" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q33">
+        <v>2.6</v>
+      </c>
+      <c r="R33">
+        <v>2.05</v>
+      </c>
+      <c r="S33">
+        <v>5</v>
+      </c>
+      <c r="T33">
+        <v>1.5</v>
+      </c>
+      <c r="U33">
+        <v>2.5</v>
+      </c>
+      <c r="V33">
+        <v>3.4</v>
+      </c>
+      <c r="W33">
+        <v>1.3</v>
+      </c>
+      <c r="X33">
+        <v>10</v>
+      </c>
+      <c r="Y33">
+        <v>1.06</v>
+      </c>
+      <c r="Z33">
+        <v>1.85</v>
+      </c>
+      <c r="AA33">
+        <v>3.35</v>
+      </c>
+      <c r="AB33">
+        <v>4.33</v>
+      </c>
+      <c r="AC33">
+        <v>1.08</v>
+      </c>
+      <c r="AD33">
+        <v>7.5</v>
+      </c>
+      <c r="AE33">
+        <v>1.42</v>
+      </c>
+      <c r="AF33">
+        <v>2.85</v>
+      </c>
+      <c r="AG33">
+        <v>2.1</v>
+      </c>
+      <c r="AH33">
+        <v>1.6</v>
+      </c>
+      <c r="AI33">
+        <v>2</v>
+      </c>
+      <c r="AJ33">
+        <v>1.75</v>
+      </c>
+      <c r="AK33">
+        <v>1.21</v>
+      </c>
+      <c r="AL33">
+        <v>1.31</v>
+      </c>
+      <c r="AM33">
+        <v>1.88</v>
+      </c>
+      <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>3</v>
+      </c>
+      <c r="AP33">
+        <v>3</v>
+      </c>
+      <c r="AQ33">
+        <v>1.5</v>
+      </c>
+      <c r="AR33">
+        <v>1.86</v>
+      </c>
+      <c r="AS33">
+        <v>0.88</v>
+      </c>
+      <c r="AT33">
+        <v>2.74</v>
+      </c>
+      <c r="AU33">
+        <v>9</v>
+      </c>
+      <c r="AV33">
+        <v>2</v>
+      </c>
+      <c r="AW33">
+        <v>8</v>
+      </c>
+      <c r="AX33">
+        <v>11</v>
+      </c>
+      <c r="AY33">
+        <v>20</v>
+      </c>
+      <c r="AZ33">
+        <v>14</v>
+      </c>
+      <c r="BA33">
+        <v>7</v>
+      </c>
+      <c r="BB33">
+        <v>5</v>
+      </c>
+      <c r="BC33">
+        <v>12</v>
+      </c>
+      <c r="BD33">
+        <v>1.63</v>
+      </c>
+      <c r="BE33">
+        <v>6.4</v>
+      </c>
+      <c r="BF33">
+        <v>2.55</v>
+      </c>
+      <c r="BG33">
+        <v>1.46</v>
+      </c>
+      <c r="BH33">
+        <v>2.43</v>
+      </c>
+      <c r="BI33">
+        <v>1.78</v>
+      </c>
+      <c r="BJ33">
+        <v>1.86</v>
+      </c>
+      <c r="BK33">
+        <v>2.28</v>
+      </c>
+      <c r="BL33">
+        <v>1.52</v>
+      </c>
+      <c r="BM33">
+        <v>3</v>
+      </c>
+      <c r="BN33">
+        <v>1.3</v>
+      </c>
+      <c r="BO33">
+        <v>4</v>
+      </c>
+      <c r="BP33">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7778106</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45717.125</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" t="s">
+        <v>83</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
+        <v>92</v>
+      </c>
+      <c r="P34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q34">
+        <v>2.38</v>
+      </c>
+      <c r="R34">
+        <v>2.3</v>
+      </c>
+      <c r="S34">
+        <v>4.5</v>
+      </c>
+      <c r="T34">
+        <v>1.33</v>
+      </c>
+      <c r="U34">
+        <v>3.25</v>
+      </c>
+      <c r="V34">
+        <v>2.63</v>
+      </c>
+      <c r="W34">
+        <v>1.44</v>
+      </c>
+      <c r="X34">
+        <v>6.5</v>
+      </c>
+      <c r="Y34">
+        <v>1.11</v>
+      </c>
+      <c r="Z34">
+        <v>1.76</v>
+      </c>
+      <c r="AA34">
+        <v>3.74</v>
+      </c>
+      <c r="AB34">
+        <v>4.3</v>
+      </c>
+      <c r="AC34">
+        <v>1.04</v>
+      </c>
+      <c r="AD34">
+        <v>10</v>
+      </c>
+      <c r="AE34">
+        <v>1.22</v>
+      </c>
+      <c r="AF34">
+        <v>4.2</v>
+      </c>
+      <c r="AG34">
+        <v>1.67</v>
+      </c>
+      <c r="AH34">
+        <v>2</v>
+      </c>
+      <c r="AI34">
+        <v>1.7</v>
+      </c>
+      <c r="AJ34">
+        <v>2.05</v>
+      </c>
+      <c r="AK34">
+        <v>1.22</v>
+      </c>
+      <c r="AL34">
+        <v>1.25</v>
+      </c>
+      <c r="AM34">
+        <v>2</v>
+      </c>
+      <c r="AN34">
+        <v>3</v>
+      </c>
+      <c r="AO34">
+        <v>0.5</v>
+      </c>
+      <c r="AP34">
+        <v>1.5</v>
+      </c>
+      <c r="AQ34">
+        <v>1.33</v>
+      </c>
+      <c r="AR34">
+        <v>1.99</v>
+      </c>
+      <c r="AS34">
+        <v>1.54</v>
+      </c>
+      <c r="AT34">
+        <v>3.53</v>
+      </c>
+      <c r="AU34">
+        <v>5</v>
+      </c>
+      <c r="AV34">
+        <v>4</v>
+      </c>
+      <c r="AW34">
+        <v>13</v>
+      </c>
+      <c r="AX34">
+        <v>6</v>
+      </c>
+      <c r="AY34">
+        <v>23</v>
+      </c>
+      <c r="AZ34">
+        <v>12</v>
+      </c>
+      <c r="BA34">
+        <v>6</v>
+      </c>
+      <c r="BB34">
+        <v>7</v>
+      </c>
+      <c r="BC34">
+        <v>13</v>
+      </c>
+      <c r="BD34">
+        <v>1.58</v>
+      </c>
+      <c r="BE34">
+        <v>6.5</v>
+      </c>
+      <c r="BF34">
+        <v>2.63</v>
+      </c>
+      <c r="BG34">
+        <v>1.36</v>
+      </c>
+      <c r="BH34">
+        <v>2.75</v>
+      </c>
+      <c r="BI34">
+        <v>1.62</v>
+      </c>
+      <c r="BJ34">
+        <v>2.08</v>
+      </c>
+      <c r="BK34">
+        <v>2</v>
+      </c>
+      <c r="BL34">
+        <v>1.67</v>
+      </c>
+      <c r="BM34">
+        <v>2.6</v>
+      </c>
+      <c r="BN34">
+        <v>1.4</v>
+      </c>
+      <c r="BO34">
+        <v>3.4</v>
+      </c>
+      <c r="BP34">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7778110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45717.125</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>92</v>
+      </c>
+      <c r="P35" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q35">
+        <v>2.5</v>
+      </c>
+      <c r="R35">
+        <v>1.95</v>
+      </c>
+      <c r="S35">
+        <v>6</v>
+      </c>
+      <c r="T35">
+        <v>1.57</v>
+      </c>
+      <c r="U35">
+        <v>2.25</v>
+      </c>
+      <c r="V35">
+        <v>3.75</v>
+      </c>
+      <c r="W35">
+        <v>1.25</v>
+      </c>
+      <c r="X35">
+        <v>11</v>
+      </c>
+      <c r="Y35">
+        <v>1.05</v>
+      </c>
+      <c r="Z35">
+        <v>1.73</v>
+      </c>
+      <c r="AA35">
+        <v>3.45</v>
+      </c>
+      <c r="AB35">
+        <v>4.9</v>
+      </c>
+      <c r="AC35">
+        <v>1.1</v>
+      </c>
+      <c r="AD35">
+        <v>6.5</v>
+      </c>
+      <c r="AE35">
+        <v>1.48</v>
+      </c>
+      <c r="AF35">
+        <v>2.37</v>
+      </c>
+      <c r="AG35">
+        <v>2.54</v>
+      </c>
+      <c r="AH35">
+        <v>1.48</v>
+      </c>
+      <c r="AI35">
+        <v>2.38</v>
+      </c>
+      <c r="AJ35">
+        <v>1.53</v>
+      </c>
+      <c r="AK35">
+        <v>1.17</v>
+      </c>
+      <c r="AL35">
+        <v>1.31</v>
+      </c>
+      <c r="AM35">
+        <v>2</v>
+      </c>
+      <c r="AN35">
+        <v>1</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>0.67</v>
+      </c>
+      <c r="AQ35">
+        <v>1.5</v>
+      </c>
+      <c r="AR35">
+        <v>1.47</v>
+      </c>
+      <c r="AS35">
+        <v>2.23</v>
+      </c>
+      <c r="AT35">
+        <v>3.7</v>
+      </c>
+      <c r="AU35">
+        <v>2</v>
+      </c>
+      <c r="AV35">
+        <v>3</v>
+      </c>
+      <c r="AW35">
+        <v>10</v>
+      </c>
+      <c r="AX35">
+        <v>10</v>
+      </c>
+      <c r="AY35">
+        <v>12</v>
+      </c>
+      <c r="AZ35">
+        <v>16</v>
+      </c>
+      <c r="BA35">
+        <v>2</v>
+      </c>
+      <c r="BB35">
+        <v>3</v>
+      </c>
+      <c r="BC35">
+        <v>5</v>
+      </c>
+      <c r="BD35">
+        <v>1.5</v>
+      </c>
+      <c r="BE35">
+        <v>6.4</v>
+      </c>
+      <c r="BF35">
+        <v>2.9</v>
+      </c>
+      <c r="BG35">
+        <v>1.53</v>
+      </c>
+      <c r="BH35">
+        <v>2.25</v>
+      </c>
+      <c r="BI35">
+        <v>1.9</v>
+      </c>
+      <c r="BJ35">
+        <v>1.75</v>
+      </c>
+      <c r="BK35">
+        <v>2.45</v>
+      </c>
+      <c r="BL35">
+        <v>1.44</v>
+      </c>
+      <c r="BM35">
+        <v>3.3</v>
+      </c>
+      <c r="BN35">
+        <v>1.26</v>
+      </c>
+      <c r="BO35">
+        <v>4.4</v>
+      </c>
+      <c r="BP35">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="139">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -280,12 +280,12 @@
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Albirex Niigata</t>
-  </si>
-  <si>
     <t>['31', '54']</t>
   </si>
   <si>
@@ -358,15 +358,24 @@
     <t>['74', '90+1']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['17', '62']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
     <t>['61']</t>
   </si>
   <si>
-    <t>['75']</t>
-  </si>
-  <si>
     <t>['59', '77']</t>
   </si>
   <si>
@@ -407,6 +416,21 @@
   </si>
   <si>
     <t>['55']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['28', '90+1']</t>
+  </si>
+  <si>
+    <t>['13', '74']</t>
+  </si>
+  <si>
+    <t>['14', '31']</t>
   </si>
 </sst>
 </file>
@@ -768,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1024,7 +1048,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1105,7 +1129,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1308,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -1412,7 +1436,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1642,7 +1666,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1848,7 +1872,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2030,7 +2054,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2672,7 +2696,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2878,7 +2902,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2959,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="AQ11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3084,7 +3108,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3472,7 +3496,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -3702,7 +3726,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3780,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -3884,7 +3908,7 @@
         <v>83</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3908,7 +3932,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4114,7 +4138,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4526,7 +4550,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4732,7 +4756,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -5120,7 +5144,7 @@
         <v>84</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -5144,7 +5168,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -5428,10 +5452,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -5556,7 +5580,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5762,7 +5786,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5944,7 +5968,7 @@
         <v>77</v>
       </c>
       <c r="H26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -5968,7 +5992,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6174,7 +6198,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6380,7 +6404,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6792,7 +6816,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -6873,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.39</v>
@@ -7079,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>1.14</v>
@@ -7204,7 +7228,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7822,7 +7846,7 @@
         <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -7979,6 +8003,1242 @@
       </c>
       <c r="BP35">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7778111</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
+      </c>
+      <c r="O36" t="s">
+        <v>114</v>
+      </c>
+      <c r="P36" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q36">
+        <v>3.6</v>
+      </c>
+      <c r="R36">
+        <v>2</v>
+      </c>
+      <c r="S36">
+        <v>3.4</v>
+      </c>
+      <c r="T36">
+        <v>1.5</v>
+      </c>
+      <c r="U36">
+        <v>2.5</v>
+      </c>
+      <c r="V36">
+        <v>3.5</v>
+      </c>
+      <c r="W36">
+        <v>1.29</v>
+      </c>
+      <c r="X36">
+        <v>11</v>
+      </c>
+      <c r="Y36">
+        <v>1.05</v>
+      </c>
+      <c r="Z36">
+        <v>2.95</v>
+      </c>
+      <c r="AA36">
+        <v>2.95</v>
+      </c>
+      <c r="AB36">
+        <v>2.55</v>
+      </c>
+      <c r="AC36">
+        <v>1.09</v>
+      </c>
+      <c r="AD36">
+        <v>7</v>
+      </c>
+      <c r="AE36">
+        <v>1.5</v>
+      </c>
+      <c r="AF36">
+        <v>2.58</v>
+      </c>
+      <c r="AG36">
+        <v>2.15</v>
+      </c>
+      <c r="AH36">
+        <v>1.57</v>
+      </c>
+      <c r="AI36">
+        <v>1.95</v>
+      </c>
+      <c r="AJ36">
+        <v>1.8</v>
+      </c>
+      <c r="AK36">
+        <v>1.52</v>
+      </c>
+      <c r="AL36">
+        <v>1.34</v>
+      </c>
+      <c r="AM36">
+        <v>1.38</v>
+      </c>
+      <c r="AN36">
+        <v>3</v>
+      </c>
+      <c r="AO36">
+        <v>3</v>
+      </c>
+      <c r="AP36">
+        <v>2.33</v>
+      </c>
+      <c r="AQ36">
+        <v>2</v>
+      </c>
+      <c r="AR36">
+        <v>1.59</v>
+      </c>
+      <c r="AS36">
+        <v>1.08</v>
+      </c>
+      <c r="AT36">
+        <v>2.67</v>
+      </c>
+      <c r="AU36">
+        <v>7</v>
+      </c>
+      <c r="AV36">
+        <v>4</v>
+      </c>
+      <c r="AW36">
+        <v>8</v>
+      </c>
+      <c r="AX36">
+        <v>10</v>
+      </c>
+      <c r="AY36">
+        <v>16</v>
+      </c>
+      <c r="AZ36">
+        <v>17</v>
+      </c>
+      <c r="BA36">
+        <v>7</v>
+      </c>
+      <c r="BB36">
+        <v>8</v>
+      </c>
+      <c r="BC36">
+        <v>15</v>
+      </c>
+      <c r="BD36">
+        <v>2.04</v>
+      </c>
+      <c r="BE36">
+        <v>6.65</v>
+      </c>
+      <c r="BF36">
+        <v>2.21</v>
+      </c>
+      <c r="BG36">
+        <v>1.49</v>
+      </c>
+      <c r="BH36">
+        <v>2.33</v>
+      </c>
+      <c r="BI36">
+        <v>1.85</v>
+      </c>
+      <c r="BJ36">
+        <v>1.8</v>
+      </c>
+      <c r="BK36">
+        <v>2.38</v>
+      </c>
+      <c r="BL36">
+        <v>1.48</v>
+      </c>
+      <c r="BM36">
+        <v>3.1</v>
+      </c>
+      <c r="BN36">
+        <v>1.28</v>
+      </c>
+      <c r="BO36">
+        <v>4.1</v>
+      </c>
+      <c r="BP36">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7778105</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>92</v>
+      </c>
+      <c r="P37" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q37">
+        <v>3.5</v>
+      </c>
+      <c r="R37">
+        <v>1.91</v>
+      </c>
+      <c r="S37">
+        <v>3.75</v>
+      </c>
+      <c r="T37">
+        <v>1.57</v>
+      </c>
+      <c r="U37">
+        <v>2.25</v>
+      </c>
+      <c r="V37">
+        <v>3.75</v>
+      </c>
+      <c r="W37">
+        <v>1.25</v>
+      </c>
+      <c r="X37">
+        <v>13</v>
+      </c>
+      <c r="Y37">
+        <v>1.04</v>
+      </c>
+      <c r="Z37">
+        <v>2.72</v>
+      </c>
+      <c r="AA37">
+        <v>3.09</v>
+      </c>
+      <c r="AB37">
+        <v>2.64</v>
+      </c>
+      <c r="AC37">
+        <v>1.1</v>
+      </c>
+      <c r="AD37">
+        <v>6.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.48</v>
+      </c>
+      <c r="AF37">
+        <v>2.37</v>
+      </c>
+      <c r="AG37">
+        <v>2.63</v>
+      </c>
+      <c r="AH37">
+        <v>1.45</v>
+      </c>
+      <c r="AI37">
+        <v>2.1</v>
+      </c>
+      <c r="AJ37">
+        <v>1.67</v>
+      </c>
+      <c r="AK37">
+        <v>1.34</v>
+      </c>
+      <c r="AL37">
+        <v>1.36</v>
+      </c>
+      <c r="AM37">
+        <v>1.55</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>1.5</v>
+      </c>
+      <c r="AR37">
+        <v>1.08</v>
+      </c>
+      <c r="AS37">
+        <v>0.71</v>
+      </c>
+      <c r="AT37">
+        <v>1.79</v>
+      </c>
+      <c r="AU37">
+        <v>4</v>
+      </c>
+      <c r="AV37">
+        <v>5</v>
+      </c>
+      <c r="AW37">
+        <v>9</v>
+      </c>
+      <c r="AX37">
+        <v>17</v>
+      </c>
+      <c r="AY37">
+        <v>17</v>
+      </c>
+      <c r="AZ37">
+        <v>32</v>
+      </c>
+      <c r="BA37">
+        <v>6</v>
+      </c>
+      <c r="BB37">
+        <v>14</v>
+      </c>
+      <c r="BC37">
+        <v>20</v>
+      </c>
+      <c r="BD37">
+        <v>1.59</v>
+      </c>
+      <c r="BE37">
+        <v>6.85</v>
+      </c>
+      <c r="BF37">
+        <v>3.14</v>
+      </c>
+      <c r="BG37">
+        <v>1.27</v>
+      </c>
+      <c r="BH37">
+        <v>3.14</v>
+      </c>
+      <c r="BI37">
+        <v>1.52</v>
+      </c>
+      <c r="BJ37">
+        <v>2.3</v>
+      </c>
+      <c r="BK37">
+        <v>1.95</v>
+      </c>
+      <c r="BL37">
+        <v>1.77</v>
+      </c>
+      <c r="BM37">
+        <v>2.5</v>
+      </c>
+      <c r="BN37">
+        <v>1.44</v>
+      </c>
+      <c r="BO37">
+        <v>3.34</v>
+      </c>
+      <c r="BP37">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7778108</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>2</v>
+      </c>
+      <c r="N38">
+        <v>4</v>
+      </c>
+      <c r="O38" t="s">
+        <v>115</v>
+      </c>
+      <c r="P38" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q38">
+        <v>3.1</v>
+      </c>
+      <c r="R38">
+        <v>2.05</v>
+      </c>
+      <c r="S38">
+        <v>3.75</v>
+      </c>
+      <c r="T38">
+        <v>1.44</v>
+      </c>
+      <c r="U38">
+        <v>2.63</v>
+      </c>
+      <c r="V38">
+        <v>3.25</v>
+      </c>
+      <c r="W38">
+        <v>1.33</v>
+      </c>
+      <c r="X38">
+        <v>9</v>
+      </c>
+      <c r="Y38">
+        <v>1.07</v>
+      </c>
+      <c r="Z38">
+        <v>2.14</v>
+      </c>
+      <c r="AA38">
+        <v>3.32</v>
+      </c>
+      <c r="AB38">
+        <v>3.33</v>
+      </c>
+      <c r="AC38">
+        <v>1.07</v>
+      </c>
+      <c r="AD38">
+        <v>8</v>
+      </c>
+      <c r="AE38">
+        <v>1.4</v>
+      </c>
+      <c r="AF38">
+        <v>2.9</v>
+      </c>
+      <c r="AG38">
+        <v>2</v>
+      </c>
+      <c r="AH38">
+        <v>1.67</v>
+      </c>
+      <c r="AI38">
+        <v>1.91</v>
+      </c>
+      <c r="AJ38">
+        <v>1.91</v>
+      </c>
+      <c r="AK38">
+        <v>1.31</v>
+      </c>
+      <c r="AL38">
+        <v>1.32</v>
+      </c>
+      <c r="AM38">
+        <v>1.66</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>1.5</v>
+      </c>
+      <c r="AP38">
+        <v>1</v>
+      </c>
+      <c r="AQ38">
+        <v>1.33</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>1.59</v>
+      </c>
+      <c r="AT38">
+        <v>1.59</v>
+      </c>
+      <c r="AU38">
+        <v>5</v>
+      </c>
+      <c r="AV38">
+        <v>5</v>
+      </c>
+      <c r="AW38">
+        <v>12</v>
+      </c>
+      <c r="AX38">
+        <v>6</v>
+      </c>
+      <c r="AY38">
+        <v>18</v>
+      </c>
+      <c r="AZ38">
+        <v>12</v>
+      </c>
+      <c r="BA38">
+        <v>9</v>
+      </c>
+      <c r="BB38">
+        <v>5</v>
+      </c>
+      <c r="BC38">
+        <v>14</v>
+      </c>
+      <c r="BD38">
+        <v>1.71</v>
+      </c>
+      <c r="BE38">
+        <v>6.65</v>
+      </c>
+      <c r="BF38">
+        <v>2.79</v>
+      </c>
+      <c r="BG38">
+        <v>1.24</v>
+      </c>
+      <c r="BH38">
+        <v>3.34</v>
+      </c>
+      <c r="BI38">
+        <v>1.48</v>
+      </c>
+      <c r="BJ38">
+        <v>2.4</v>
+      </c>
+      <c r="BK38">
+        <v>1.85</v>
+      </c>
+      <c r="BL38">
+        <v>1.85</v>
+      </c>
+      <c r="BM38">
+        <v>2.38</v>
+      </c>
+      <c r="BN38">
+        <v>1.49</v>
+      </c>
+      <c r="BO38">
+        <v>3.14</v>
+      </c>
+      <c r="BP38">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7778109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>82</v>
+      </c>
+      <c r="H39" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>2</v>
+      </c>
+      <c r="N39">
+        <v>3</v>
+      </c>
+      <c r="O39" t="s">
+        <v>116</v>
+      </c>
+      <c r="P39" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q39">
+        <v>3.75</v>
+      </c>
+      <c r="R39">
+        <v>1.91</v>
+      </c>
+      <c r="S39">
+        <v>3.4</v>
+      </c>
+      <c r="T39">
+        <v>1.57</v>
+      </c>
+      <c r="U39">
+        <v>2.25</v>
+      </c>
+      <c r="V39">
+        <v>3.75</v>
+      </c>
+      <c r="W39">
+        <v>1.25</v>
+      </c>
+      <c r="X39">
+        <v>13</v>
+      </c>
+      <c r="Y39">
+        <v>1.04</v>
+      </c>
+      <c r="Z39">
+        <v>3.1</v>
+      </c>
+      <c r="AA39">
+        <v>2.86</v>
+      </c>
+      <c r="AB39">
+        <v>2.51</v>
+      </c>
+      <c r="AC39">
+        <v>1.12</v>
+      </c>
+      <c r="AD39">
+        <v>5.75</v>
+      </c>
+      <c r="AE39">
+        <v>1.48</v>
+      </c>
+      <c r="AF39">
+        <v>2.37</v>
+      </c>
+      <c r="AG39">
+        <v>2.74</v>
+      </c>
+      <c r="AH39">
+        <v>1.42</v>
+      </c>
+      <c r="AI39">
+        <v>2.1</v>
+      </c>
+      <c r="AJ39">
+        <v>1.67</v>
+      </c>
+      <c r="AK39">
+        <v>1.47</v>
+      </c>
+      <c r="AL39">
+        <v>1.39</v>
+      </c>
+      <c r="AM39">
+        <v>1.37</v>
+      </c>
+      <c r="AN39">
+        <v>1</v>
+      </c>
+      <c r="AO39">
+        <v>3</v>
+      </c>
+      <c r="AP39">
+        <v>0.5</v>
+      </c>
+      <c r="AQ39">
+        <v>3</v>
+      </c>
+      <c r="AR39">
+        <v>1.35</v>
+      </c>
+      <c r="AS39">
+        <v>1.13</v>
+      </c>
+      <c r="AT39">
+        <v>2.48</v>
+      </c>
+      <c r="AU39">
+        <v>3</v>
+      </c>
+      <c r="AV39">
+        <v>3</v>
+      </c>
+      <c r="AW39">
+        <v>3</v>
+      </c>
+      <c r="AX39">
+        <v>4</v>
+      </c>
+      <c r="AY39">
+        <v>6</v>
+      </c>
+      <c r="AZ39">
+        <v>10</v>
+      </c>
+      <c r="BA39">
+        <v>3</v>
+      </c>
+      <c r="BB39">
+        <v>2</v>
+      </c>
+      <c r="BC39">
+        <v>5</v>
+      </c>
+      <c r="BD39">
+        <v>2.15</v>
+      </c>
+      <c r="BE39">
+        <v>6.1</v>
+      </c>
+      <c r="BF39">
+        <v>1.89</v>
+      </c>
+      <c r="BG39">
+        <v>1.53</v>
+      </c>
+      <c r="BH39">
+        <v>2.25</v>
+      </c>
+      <c r="BI39">
+        <v>1.9</v>
+      </c>
+      <c r="BJ39">
+        <v>1.75</v>
+      </c>
+      <c r="BK39">
+        <v>2.43</v>
+      </c>
+      <c r="BL39">
+        <v>1.45</v>
+      </c>
+      <c r="BM39">
+        <v>3.25</v>
+      </c>
+      <c r="BN39">
+        <v>1.26</v>
+      </c>
+      <c r="BO39">
+        <v>4.35</v>
+      </c>
+      <c r="BP39">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7778112</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45718.10416666666</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H40" t="s">
+        <v>73</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>117</v>
+      </c>
+      <c r="P40" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q40">
+        <v>2.3</v>
+      </c>
+      <c r="R40">
+        <v>2.2</v>
+      </c>
+      <c r="S40">
+        <v>5.5</v>
+      </c>
+      <c r="T40">
+        <v>1.36</v>
+      </c>
+      <c r="U40">
+        <v>3</v>
+      </c>
+      <c r="V40">
+        <v>2.75</v>
+      </c>
+      <c r="W40">
+        <v>1.4</v>
+      </c>
+      <c r="X40">
+        <v>8</v>
+      </c>
+      <c r="Y40">
+        <v>1.08</v>
+      </c>
+      <c r="Z40">
+        <v>1.56</v>
+      </c>
+      <c r="AA40">
+        <v>4.3</v>
+      </c>
+      <c r="AB40">
+        <v>5.1</v>
+      </c>
+      <c r="AC40">
+        <v>1.06</v>
+      </c>
+      <c r="AD40">
+        <v>8.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.35</v>
+      </c>
+      <c r="AF40">
+        <v>3.1</v>
+      </c>
+      <c r="AG40">
+        <v>1.83</v>
+      </c>
+      <c r="AH40">
+        <v>1.91</v>
+      </c>
+      <c r="AI40">
+        <v>1.95</v>
+      </c>
+      <c r="AJ40">
+        <v>1.8</v>
+      </c>
+      <c r="AK40">
+        <v>1.16</v>
+      </c>
+      <c r="AL40">
+        <v>1.26</v>
+      </c>
+      <c r="AM40">
+        <v>2.15</v>
+      </c>
+      <c r="AN40">
+        <v>3</v>
+      </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
+      <c r="AP40">
+        <v>3</v>
+      </c>
+      <c r="AQ40">
+        <v>0.5</v>
+      </c>
+      <c r="AR40">
+        <v>1.25</v>
+      </c>
+      <c r="AS40">
+        <v>1.73</v>
+      </c>
+      <c r="AT40">
+        <v>2.98</v>
+      </c>
+      <c r="AU40">
+        <v>4</v>
+      </c>
+      <c r="AV40">
+        <v>2</v>
+      </c>
+      <c r="AW40">
+        <v>12</v>
+      </c>
+      <c r="AX40">
+        <v>3</v>
+      </c>
+      <c r="AY40">
+        <v>22</v>
+      </c>
+      <c r="AZ40">
+        <v>6</v>
+      </c>
+      <c r="BA40">
+        <v>3</v>
+      </c>
+      <c r="BB40">
+        <v>2</v>
+      </c>
+      <c r="BC40">
+        <v>5</v>
+      </c>
+      <c r="BD40">
+        <v>1.5</v>
+      </c>
+      <c r="BE40">
+        <v>6.75</v>
+      </c>
+      <c r="BF40">
+        <v>2.9</v>
+      </c>
+      <c r="BG40">
+        <v>1.46</v>
+      </c>
+      <c r="BH40">
+        <v>2.43</v>
+      </c>
+      <c r="BI40">
+        <v>1.77</v>
+      </c>
+      <c r="BJ40">
+        <v>1.88</v>
+      </c>
+      <c r="BK40">
+        <v>2.23</v>
+      </c>
+      <c r="BL40">
+        <v>1.54</v>
+      </c>
+      <c r="BM40">
+        <v>2.9</v>
+      </c>
+      <c r="BN40">
+        <v>1.33</v>
+      </c>
+      <c r="BO40">
+        <v>3.9</v>
+      </c>
+      <c r="BP40">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7778104</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45718.125</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s">
+        <v>80</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41" t="s">
+        <v>92</v>
+      </c>
+      <c r="P41" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q41">
+        <v>2.88</v>
+      </c>
+      <c r="R41">
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <v>4.33</v>
+      </c>
+      <c r="T41">
+        <v>1.53</v>
+      </c>
+      <c r="U41">
+        <v>2.38</v>
+      </c>
+      <c r="V41">
+        <v>3.5</v>
+      </c>
+      <c r="W41">
+        <v>1.29</v>
+      </c>
+      <c r="X41">
+        <v>11</v>
+      </c>
+      <c r="Y41">
+        <v>1.05</v>
+      </c>
+      <c r="Z41">
+        <v>2.05</v>
+      </c>
+      <c r="AA41">
+        <v>3.27</v>
+      </c>
+      <c r="AB41">
+        <v>3.63</v>
+      </c>
+      <c r="AC41">
+        <v>1.09</v>
+      </c>
+      <c r="AD41">
+        <v>7</v>
+      </c>
+      <c r="AE41">
+        <v>1.45</v>
+      </c>
+      <c r="AF41">
+        <v>2.7</v>
+      </c>
+      <c r="AG41">
+        <v>2.05</v>
+      </c>
+      <c r="AH41">
+        <v>1.65</v>
+      </c>
+      <c r="AI41">
+        <v>2</v>
+      </c>
+      <c r="AJ41">
+        <v>1.75</v>
+      </c>
+      <c r="AK41">
+        <v>1.32</v>
+      </c>
+      <c r="AL41">
+        <v>1.34</v>
+      </c>
+      <c r="AM41">
+        <v>1.61</v>
+      </c>
+      <c r="AN41">
+        <v>0</v>
+      </c>
+      <c r="AO41">
+        <v>3</v>
+      </c>
+      <c r="AP41">
+        <v>0</v>
+      </c>
+      <c r="AQ41">
+        <v>3</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>1.46</v>
+      </c>
+      <c r="AT41">
+        <v>1.46</v>
+      </c>
+      <c r="AU41">
+        <v>8</v>
+      </c>
+      <c r="AV41">
+        <v>5</v>
+      </c>
+      <c r="AW41">
+        <v>10</v>
+      </c>
+      <c r="AX41">
+        <v>2</v>
+      </c>
+      <c r="AY41">
+        <v>20</v>
+      </c>
+      <c r="AZ41">
+        <v>8</v>
+      </c>
+      <c r="BA41">
+        <v>7</v>
+      </c>
+      <c r="BB41">
+        <v>4</v>
+      </c>
+      <c r="BC41">
+        <v>11</v>
+      </c>
+      <c r="BD41">
+        <v>2.03</v>
+      </c>
+      <c r="BE41">
+        <v>6.4</v>
+      </c>
+      <c r="BF41">
+        <v>2.25</v>
+      </c>
+      <c r="BG41">
+        <v>1.27</v>
+      </c>
+      <c r="BH41">
+        <v>3.14</v>
+      </c>
+      <c r="BI41">
+        <v>1.7</v>
+      </c>
+      <c r="BJ41">
+        <v>2.05</v>
+      </c>
+      <c r="BK41">
+        <v>1.95</v>
+      </c>
+      <c r="BL41">
+        <v>1.77</v>
+      </c>
+      <c r="BM41">
+        <v>2.51</v>
+      </c>
+      <c r="BN41">
+        <v>1.44</v>
+      </c>
+      <c r="BO41">
+        <v>3.42</v>
+      </c>
+      <c r="BP41">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="145">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -370,6 +370,15 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['42', '58']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -431,6 +440,15 @@
   </si>
   <si>
     <t>['14', '31']</t>
+  </si>
+  <si>
+    <t>['10', '75']</t>
+  </si>
+  <si>
+    <t>['26', '50', '62']</t>
+  </si>
+  <si>
+    <t>['51', '86']</t>
   </si>
 </sst>
 </file>
@@ -792,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP41"/>
+  <dimension ref="A1:BP48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1048,7 +1066,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1126,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1666,7 +1684,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1744,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2365,7 +2383,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2571,7 +2589,7 @@
         <v>3</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2696,7 +2714,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2902,7 +2920,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2983,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3108,7 +3126,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3186,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>2</v>
@@ -3392,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>0</v>
@@ -3726,7 +3744,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3932,7 +3950,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4138,7 +4156,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4216,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.5</v>
@@ -4425,7 +4443,7 @@
         <v>3</v>
       </c>
       <c r="AQ18">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4550,7 +4568,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4628,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -4756,7 +4774,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -4834,10 +4852,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5168,7 +5186,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -5580,7 +5598,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5786,7 +5804,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5992,7 +6010,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6198,7 +6216,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6404,7 +6422,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6485,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>0.8</v>
@@ -6688,10 +6706,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -6816,7 +6834,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -6894,7 +6912,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7228,7 +7246,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7309,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR32">
         <v>1.12</v>
@@ -7846,7 +7864,7 @@
         <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8052,7 +8070,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -8133,7 +8151,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -8258,7 +8276,7 @@
         <v>92</v>
       </c>
       <c r="P37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8464,7 +8482,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q38">
         <v>3.1</v>
@@ -8670,7 +8688,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q39">
         <v>3.75</v>
@@ -9082,7 +9100,7 @@
         <v>92</v>
       </c>
       <c r="P41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9160,7 +9178,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>3</v>
@@ -9239,6 +9257,1448 @@
       </c>
       <c r="BP41">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7778113</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45724.08333333334</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s">
+        <v>71</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>103</v>
+      </c>
+      <c r="P42" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q42">
+        <v>3.1</v>
+      </c>
+      <c r="R42">
+        <v>2.05</v>
+      </c>
+      <c r="S42">
+        <v>3.75</v>
+      </c>
+      <c r="T42">
+        <v>1.44</v>
+      </c>
+      <c r="U42">
+        <v>2.63</v>
+      </c>
+      <c r="V42">
+        <v>3.4</v>
+      </c>
+      <c r="W42">
+        <v>1.3</v>
+      </c>
+      <c r="X42">
+        <v>10</v>
+      </c>
+      <c r="Y42">
+        <v>1.06</v>
+      </c>
+      <c r="Z42">
+        <v>2.56</v>
+      </c>
+      <c r="AA42">
+        <v>3.15</v>
+      </c>
+      <c r="AB42">
+        <v>2.76</v>
+      </c>
+      <c r="AC42">
+        <v>1.08</v>
+      </c>
+      <c r="AD42">
+        <v>7.5</v>
+      </c>
+      <c r="AE42">
+        <v>1.4</v>
+      </c>
+      <c r="AF42">
+        <v>2.88</v>
+      </c>
+      <c r="AG42">
+        <v>1.98</v>
+      </c>
+      <c r="AH42">
+        <v>1.77</v>
+      </c>
+      <c r="AI42">
+        <v>1.91</v>
+      </c>
+      <c r="AJ42">
+        <v>1.91</v>
+      </c>
+      <c r="AK42">
+        <v>1.33</v>
+      </c>
+      <c r="AL42">
+        <v>1.3</v>
+      </c>
+      <c r="AM42">
+        <v>1.62</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>1.5</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>2.05</v>
+      </c>
+      <c r="AS42">
+        <v>1.24</v>
+      </c>
+      <c r="AT42">
+        <v>3.29</v>
+      </c>
+      <c r="AU42">
+        <v>4</v>
+      </c>
+      <c r="AV42">
+        <v>2</v>
+      </c>
+      <c r="AW42">
+        <v>9</v>
+      </c>
+      <c r="AX42">
+        <v>8</v>
+      </c>
+      <c r="AY42">
+        <v>15</v>
+      </c>
+      <c r="AZ42">
+        <v>12</v>
+      </c>
+      <c r="BA42">
+        <v>5</v>
+      </c>
+      <c r="BB42">
+        <v>3</v>
+      </c>
+      <c r="BC42">
+        <v>8</v>
+      </c>
+      <c r="BD42">
+        <v>1.72</v>
+      </c>
+      <c r="BE42">
+        <v>6.75</v>
+      </c>
+      <c r="BF42">
+        <v>2.32</v>
+      </c>
+      <c r="BG42">
+        <v>1.22</v>
+      </c>
+      <c r="BH42">
+        <v>3.65</v>
+      </c>
+      <c r="BI42">
+        <v>1.4</v>
+      </c>
+      <c r="BJ42">
+        <v>2.63</v>
+      </c>
+      <c r="BK42">
+        <v>1.65</v>
+      </c>
+      <c r="BL42">
+        <v>2.02</v>
+      </c>
+      <c r="BM42">
+        <v>2.02</v>
+      </c>
+      <c r="BN42">
+        <v>1.65</v>
+      </c>
+      <c r="BO42">
+        <v>2.55</v>
+      </c>
+      <c r="BP42">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7778117</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45724.08680555555</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" t="s">
+        <v>79</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>2</v>
+      </c>
+      <c r="N43">
+        <v>4</v>
+      </c>
+      <c r="O43" t="s">
+        <v>118</v>
+      </c>
+      <c r="P43" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q43">
+        <v>3.2</v>
+      </c>
+      <c r="R43">
+        <v>1.91</v>
+      </c>
+      <c r="S43">
+        <v>3.55</v>
+      </c>
+      <c r="T43">
+        <v>1.5</v>
+      </c>
+      <c r="U43">
+        <v>2.4</v>
+      </c>
+      <c r="V43">
+        <v>3.3</v>
+      </c>
+      <c r="W43">
+        <v>1.28</v>
+      </c>
+      <c r="X43">
+        <v>9.1</v>
+      </c>
+      <c r="Y43">
+        <v>1</v>
+      </c>
+      <c r="Z43">
+        <v>2.39</v>
+      </c>
+      <c r="AA43">
+        <v>3.03</v>
+      </c>
+      <c r="AB43">
+        <v>3.11</v>
+      </c>
+      <c r="AC43">
+        <v>1.1</v>
+      </c>
+      <c r="AD43">
+        <v>6.5</v>
+      </c>
+      <c r="AE43">
+        <v>1.48</v>
+      </c>
+      <c r="AF43">
+        <v>2.6</v>
+      </c>
+      <c r="AG43">
+        <v>2.3</v>
+      </c>
+      <c r="AH43">
+        <v>1.5</v>
+      </c>
+      <c r="AI43">
+        <v>1.95</v>
+      </c>
+      <c r="AJ43">
+        <v>1.73</v>
+      </c>
+      <c r="AK43">
+        <v>1.38</v>
+      </c>
+      <c r="AL43">
+        <v>1.3</v>
+      </c>
+      <c r="AM43">
+        <v>1.5</v>
+      </c>
+      <c r="AN43">
+        <v>1</v>
+      </c>
+      <c r="AO43">
+        <v>1.5</v>
+      </c>
+      <c r="AP43">
+        <v>1</v>
+      </c>
+      <c r="AQ43">
+        <v>1.33</v>
+      </c>
+      <c r="AR43">
+        <v>1.74</v>
+      </c>
+      <c r="AS43">
+        <v>1.01</v>
+      </c>
+      <c r="AT43">
+        <v>2.75</v>
+      </c>
+      <c r="AU43">
+        <v>5</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>4</v>
+      </c>
+      <c r="AX43">
+        <v>5</v>
+      </c>
+      <c r="AY43">
+        <v>11</v>
+      </c>
+      <c r="AZ43">
+        <v>11</v>
+      </c>
+      <c r="BA43">
+        <v>3</v>
+      </c>
+      <c r="BB43">
+        <v>1</v>
+      </c>
+      <c r="BC43">
+        <v>4</v>
+      </c>
+      <c r="BD43">
+        <v>1.85</v>
+      </c>
+      <c r="BE43">
+        <v>6.4</v>
+      </c>
+      <c r="BF43">
+        <v>2.15</v>
+      </c>
+      <c r="BG43">
+        <v>1.29</v>
+      </c>
+      <c r="BH43">
+        <v>3.1</v>
+      </c>
+      <c r="BI43">
+        <v>1.5</v>
+      </c>
+      <c r="BJ43">
+        <v>2.32</v>
+      </c>
+      <c r="BK43">
+        <v>1.82</v>
+      </c>
+      <c r="BL43">
+        <v>1.82</v>
+      </c>
+      <c r="BM43">
+        <v>2.28</v>
+      </c>
+      <c r="BN43">
+        <v>1.52</v>
+      </c>
+      <c r="BO43">
+        <v>2.95</v>
+      </c>
+      <c r="BP43">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7778119</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45724.125</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>70</v>
+      </c>
+      <c r="H44" t="s">
+        <v>81</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>119</v>
+      </c>
+      <c r="P44" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q44">
+        <v>3.25</v>
+      </c>
+      <c r="R44">
+        <v>1.95</v>
+      </c>
+      <c r="S44">
+        <v>4</v>
+      </c>
+      <c r="T44">
+        <v>1.57</v>
+      </c>
+      <c r="U44">
+        <v>2.25</v>
+      </c>
+      <c r="V44">
+        <v>3.75</v>
+      </c>
+      <c r="W44">
+        <v>1.25</v>
+      </c>
+      <c r="X44">
+        <v>11</v>
+      </c>
+      <c r="Y44">
+        <v>1.05</v>
+      </c>
+      <c r="Z44">
+        <v>2.09</v>
+      </c>
+      <c r="AA44">
+        <v>3.23</v>
+      </c>
+      <c r="AB44">
+        <v>3.57</v>
+      </c>
+      <c r="AC44">
+        <v>1.1</v>
+      </c>
+      <c r="AD44">
+        <v>6.5</v>
+      </c>
+      <c r="AE44">
+        <v>1.5</v>
+      </c>
+      <c r="AF44">
+        <v>2.55</v>
+      </c>
+      <c r="AG44">
+        <v>2.37</v>
+      </c>
+      <c r="AH44">
+        <v>1.48</v>
+      </c>
+      <c r="AI44">
+        <v>2.05</v>
+      </c>
+      <c r="AJ44">
+        <v>1.7</v>
+      </c>
+      <c r="AK44">
+        <v>1.33</v>
+      </c>
+      <c r="AL44">
+        <v>1.3</v>
+      </c>
+      <c r="AM44">
+        <v>1.55</v>
+      </c>
+      <c r="AN44">
+        <v>1.5</v>
+      </c>
+      <c r="AO44">
+        <v>2</v>
+      </c>
+      <c r="AP44">
+        <v>2</v>
+      </c>
+      <c r="AQ44">
+        <v>1.33</v>
+      </c>
+      <c r="AR44">
+        <v>1.53</v>
+      </c>
+      <c r="AS44">
+        <v>1.36</v>
+      </c>
+      <c r="AT44">
+        <v>2.89</v>
+      </c>
+      <c r="AU44">
+        <v>6</v>
+      </c>
+      <c r="AV44">
+        <v>3</v>
+      </c>
+      <c r="AW44">
+        <v>11</v>
+      </c>
+      <c r="AX44">
+        <v>9</v>
+      </c>
+      <c r="AY44">
+        <v>20</v>
+      </c>
+      <c r="AZ44">
+        <v>16</v>
+      </c>
+      <c r="BA44">
+        <v>4</v>
+      </c>
+      <c r="BB44">
+        <v>2</v>
+      </c>
+      <c r="BC44">
+        <v>6</v>
+      </c>
+      <c r="BD44">
+        <v>1.84</v>
+      </c>
+      <c r="BE44">
+        <v>6.75</v>
+      </c>
+      <c r="BF44">
+        <v>2.15</v>
+      </c>
+      <c r="BG44">
+        <v>1.23</v>
+      </c>
+      <c r="BH44">
+        <v>3.45</v>
+      </c>
+      <c r="BI44">
+        <v>1.42</v>
+      </c>
+      <c r="BJ44">
+        <v>2.55</v>
+      </c>
+      <c r="BK44">
+        <v>1.71</v>
+      </c>
+      <c r="BL44">
+        <v>1.95</v>
+      </c>
+      <c r="BM44">
+        <v>2.1</v>
+      </c>
+      <c r="BN44">
+        <v>1.6</v>
+      </c>
+      <c r="BO44">
+        <v>2.65</v>
+      </c>
+      <c r="BP44">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7778114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45724.16666666666</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="s">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s">
+        <v>84</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>3</v>
+      </c>
+      <c r="N45">
+        <v>4</v>
+      </c>
+      <c r="O45" t="s">
+        <v>97</v>
+      </c>
+      <c r="P45" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q45">
+        <v>3.35</v>
+      </c>
+      <c r="R45">
+        <v>1.93</v>
+      </c>
+      <c r="S45">
+        <v>3.3</v>
+      </c>
+      <c r="T45">
+        <v>1.48</v>
+      </c>
+      <c r="U45">
+        <v>2.45</v>
+      </c>
+      <c r="V45">
+        <v>3.2</v>
+      </c>
+      <c r="W45">
+        <v>1.3</v>
+      </c>
+      <c r="X45">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y45">
+        <v>1.02</v>
+      </c>
+      <c r="Z45">
+        <v>2.78</v>
+      </c>
+      <c r="AA45">
+        <v>2.98</v>
+      </c>
+      <c r="AB45">
+        <v>2.67</v>
+      </c>
+      <c r="AC45">
+        <v>1.1</v>
+      </c>
+      <c r="AD45">
+        <v>6.5</v>
+      </c>
+      <c r="AE45">
+        <v>1.45</v>
+      </c>
+      <c r="AF45">
+        <v>2.7</v>
+      </c>
+      <c r="AG45">
+        <v>2.25</v>
+      </c>
+      <c r="AH45">
+        <v>1.53</v>
+      </c>
+      <c r="AI45">
+        <v>1.91</v>
+      </c>
+      <c r="AJ45">
+        <v>1.77</v>
+      </c>
+      <c r="AK45">
+        <v>1.45</v>
+      </c>
+      <c r="AL45">
+        <v>1.33</v>
+      </c>
+      <c r="AM45">
+        <v>1.42</v>
+      </c>
+      <c r="AN45">
+        <v>2</v>
+      </c>
+      <c r="AO45">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>1.33</v>
+      </c>
+      <c r="AQ45">
+        <v>1.5</v>
+      </c>
+      <c r="AR45">
+        <v>1.45</v>
+      </c>
+      <c r="AS45">
+        <v>1.78</v>
+      </c>
+      <c r="AT45">
+        <v>3.23</v>
+      </c>
+      <c r="AU45">
+        <v>5</v>
+      </c>
+      <c r="AV45">
+        <v>6</v>
+      </c>
+      <c r="AW45">
+        <v>6</v>
+      </c>
+      <c r="AX45">
+        <v>8</v>
+      </c>
+      <c r="AY45">
+        <v>14</v>
+      </c>
+      <c r="AZ45">
+        <v>15</v>
+      </c>
+      <c r="BA45">
+        <v>8</v>
+      </c>
+      <c r="BB45">
+        <v>5</v>
+      </c>
+      <c r="BC45">
+        <v>13</v>
+      </c>
+      <c r="BD45">
+        <v>1.98</v>
+      </c>
+      <c r="BE45">
+        <v>6.75</v>
+      </c>
+      <c r="BF45">
+        <v>1.98</v>
+      </c>
+      <c r="BG45">
+        <v>1.24</v>
+      </c>
+      <c r="BH45">
+        <v>3.4</v>
+      </c>
+      <c r="BI45">
+        <v>1.43</v>
+      </c>
+      <c r="BJ45">
+        <v>2.5</v>
+      </c>
+      <c r="BK45">
+        <v>1.71</v>
+      </c>
+      <c r="BL45">
+        <v>1.94</v>
+      </c>
+      <c r="BM45">
+        <v>2.1</v>
+      </c>
+      <c r="BN45">
+        <v>1.6</v>
+      </c>
+      <c r="BO45">
+        <v>2.65</v>
+      </c>
+      <c r="BP45">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7778115</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45724.16666666666</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>85</v>
+      </c>
+      <c r="H46" t="s">
+        <v>77</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>92</v>
+      </c>
+      <c r="P46" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q46">
+        <v>3.2</v>
+      </c>
+      <c r="R46">
+        <v>2</v>
+      </c>
+      <c r="S46">
+        <v>3.25</v>
+      </c>
+      <c r="T46">
+        <v>1.42</v>
+      </c>
+      <c r="U46">
+        <v>2.62</v>
+      </c>
+      <c r="V46">
+        <v>2.9</v>
+      </c>
+      <c r="W46">
+        <v>1.36</v>
+      </c>
+      <c r="X46">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y46">
+        <v>1.01</v>
+      </c>
+      <c r="Z46">
+        <v>2.65</v>
+      </c>
+      <c r="AA46">
+        <v>3.1</v>
+      </c>
+      <c r="AB46">
+        <v>2.7</v>
+      </c>
+      <c r="AC46">
+        <v>1.07</v>
+      </c>
+      <c r="AD46">
+        <v>8</v>
+      </c>
+      <c r="AE46">
+        <v>1.38</v>
+      </c>
+      <c r="AF46">
+        <v>3</v>
+      </c>
+      <c r="AG46">
+        <v>2.05</v>
+      </c>
+      <c r="AH46">
+        <v>1.65</v>
+      </c>
+      <c r="AI46">
+        <v>1.77</v>
+      </c>
+      <c r="AJ46">
+        <v>1.91</v>
+      </c>
+      <c r="AK46">
+        <v>1.45</v>
+      </c>
+      <c r="AL46">
+        <v>1.3</v>
+      </c>
+      <c r="AM46">
+        <v>1.45</v>
+      </c>
+      <c r="AN46">
+        <v>1.5</v>
+      </c>
+      <c r="AO46">
+        <v>2</v>
+      </c>
+      <c r="AP46">
+        <v>1.33</v>
+      </c>
+      <c r="AQ46">
+        <v>1.67</v>
+      </c>
+      <c r="AR46">
+        <v>1.37</v>
+      </c>
+      <c r="AS46">
+        <v>1.67</v>
+      </c>
+      <c r="AT46">
+        <v>3.04</v>
+      </c>
+      <c r="AU46">
+        <v>3</v>
+      </c>
+      <c r="AV46">
+        <v>0</v>
+      </c>
+      <c r="AW46">
+        <v>10</v>
+      </c>
+      <c r="AX46">
+        <v>4</v>
+      </c>
+      <c r="AY46">
+        <v>15</v>
+      </c>
+      <c r="AZ46">
+        <v>4</v>
+      </c>
+      <c r="BA46">
+        <v>5</v>
+      </c>
+      <c r="BB46">
+        <v>2</v>
+      </c>
+      <c r="BC46">
+        <v>7</v>
+      </c>
+      <c r="BD46">
+        <v>1.9</v>
+      </c>
+      <c r="BE46">
+        <v>6.75</v>
+      </c>
+      <c r="BF46">
+        <v>2.07</v>
+      </c>
+      <c r="BG46">
+        <v>1.27</v>
+      </c>
+      <c r="BH46">
+        <v>3.2</v>
+      </c>
+      <c r="BI46">
+        <v>1.47</v>
+      </c>
+      <c r="BJ46">
+        <v>2.38</v>
+      </c>
+      <c r="BK46">
+        <v>1.78</v>
+      </c>
+      <c r="BL46">
+        <v>1.87</v>
+      </c>
+      <c r="BM46">
+        <v>2.23</v>
+      </c>
+      <c r="BN46">
+        <v>1.54</v>
+      </c>
+      <c r="BO46">
+        <v>2.88</v>
+      </c>
+      <c r="BP46">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7778116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45724.16666666666</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" t="s">
+        <v>78</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>2</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47" t="s">
+        <v>92</v>
+      </c>
+      <c r="P47" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q47">
+        <v>4.33</v>
+      </c>
+      <c r="R47">
+        <v>1.91</v>
+      </c>
+      <c r="S47">
+        <v>3.1</v>
+      </c>
+      <c r="T47">
+        <v>1.57</v>
+      </c>
+      <c r="U47">
+        <v>2.25</v>
+      </c>
+      <c r="V47">
+        <v>3.75</v>
+      </c>
+      <c r="W47">
+        <v>1.25</v>
+      </c>
+      <c r="X47">
+        <v>13</v>
+      </c>
+      <c r="Y47">
+        <v>1.04</v>
+      </c>
+      <c r="Z47">
+        <v>3.25</v>
+      </c>
+      <c r="AA47">
+        <v>3.25</v>
+      </c>
+      <c r="AB47">
+        <v>2.2</v>
+      </c>
+      <c r="AC47">
+        <v>1.1</v>
+      </c>
+      <c r="AD47">
+        <v>6.5</v>
+      </c>
+      <c r="AE47">
+        <v>1.48</v>
+      </c>
+      <c r="AF47">
+        <v>2.37</v>
+      </c>
+      <c r="AG47">
+        <v>2.17</v>
+      </c>
+      <c r="AH47">
+        <v>1.62</v>
+      </c>
+      <c r="AI47">
+        <v>2.1</v>
+      </c>
+      <c r="AJ47">
+        <v>1.67</v>
+      </c>
+      <c r="AK47">
+        <v>1.62</v>
+      </c>
+      <c r="AL47">
+        <v>1.33</v>
+      </c>
+      <c r="AM47">
+        <v>1.3</v>
+      </c>
+      <c r="AN47">
+        <v>1.5</v>
+      </c>
+      <c r="AO47">
+        <v>3</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
+      <c r="AQ47">
+        <v>3</v>
+      </c>
+      <c r="AR47">
+        <v>1.47</v>
+      </c>
+      <c r="AS47">
+        <v>1.01</v>
+      </c>
+      <c r="AT47">
+        <v>2.48</v>
+      </c>
+      <c r="AU47">
+        <v>2</v>
+      </c>
+      <c r="AV47">
+        <v>5</v>
+      </c>
+      <c r="AW47">
+        <v>4</v>
+      </c>
+      <c r="AX47">
+        <v>9</v>
+      </c>
+      <c r="AY47">
+        <v>6</v>
+      </c>
+      <c r="AZ47">
+        <v>16</v>
+      </c>
+      <c r="BA47">
+        <v>1</v>
+      </c>
+      <c r="BB47">
+        <v>4</v>
+      </c>
+      <c r="BC47">
+        <v>5</v>
+      </c>
+      <c r="BD47">
+        <v>2.18</v>
+      </c>
+      <c r="BE47">
+        <v>6.5</v>
+      </c>
+      <c r="BF47">
+        <v>1.82</v>
+      </c>
+      <c r="BG47">
+        <v>1.3</v>
+      </c>
+      <c r="BH47">
+        <v>3.05</v>
+      </c>
+      <c r="BI47">
+        <v>1.52</v>
+      </c>
+      <c r="BJ47">
+        <v>2.28</v>
+      </c>
+      <c r="BK47">
+        <v>1.95</v>
+      </c>
+      <c r="BL47">
+        <v>1.85</v>
+      </c>
+      <c r="BM47">
+        <v>2.33</v>
+      </c>
+      <c r="BN47">
+        <v>1.5</v>
+      </c>
+      <c r="BO47">
+        <v>3</v>
+      </c>
+      <c r="BP47">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:68">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7778120</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45724.16666666666</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
+      </c>
+      <c r="O48" t="s">
+        <v>120</v>
+      </c>
+      <c r="P48" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q48">
+        <v>3.1</v>
+      </c>
+      <c r="R48">
+        <v>1.85</v>
+      </c>
+      <c r="S48">
+        <v>3.85</v>
+      </c>
+      <c r="T48">
+        <v>1.55</v>
+      </c>
+      <c r="U48">
+        <v>2.3</v>
+      </c>
+      <c r="V48">
+        <v>3.5</v>
+      </c>
+      <c r="W48">
+        <v>1.25</v>
+      </c>
+      <c r="X48">
+        <v>8.9</v>
+      </c>
+      <c r="Y48">
+        <v>1.01</v>
+      </c>
+      <c r="Z48">
+        <v>2.34</v>
+      </c>
+      <c r="AA48">
+        <v>3.03</v>
+      </c>
+      <c r="AB48">
+        <v>3.2</v>
+      </c>
+      <c r="AC48">
+        <v>1.11</v>
+      </c>
+      <c r="AD48">
+        <v>6.25</v>
+      </c>
+      <c r="AE48">
+        <v>1.48</v>
+      </c>
+      <c r="AF48">
+        <v>2.37</v>
+      </c>
+      <c r="AG48">
+        <v>2.4</v>
+      </c>
+      <c r="AH48">
+        <v>1.57</v>
+      </c>
+      <c r="AI48">
+        <v>2</v>
+      </c>
+      <c r="AJ48">
+        <v>1.7</v>
+      </c>
+      <c r="AK48">
+        <v>1.33</v>
+      </c>
+      <c r="AL48">
+        <v>1.33</v>
+      </c>
+      <c r="AM48">
+        <v>1.55</v>
+      </c>
+      <c r="AN48">
+        <v>0</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>0.5</v>
+      </c>
+      <c r="AQ48">
+        <v>0.33</v>
+      </c>
+      <c r="AR48">
+        <v>1.63</v>
+      </c>
+      <c r="AS48">
+        <v>1.32</v>
+      </c>
+      <c r="AT48">
+        <v>2.95</v>
+      </c>
+      <c r="AU48">
+        <v>4</v>
+      </c>
+      <c r="AV48">
+        <v>7</v>
+      </c>
+      <c r="AW48">
+        <v>20</v>
+      </c>
+      <c r="AX48">
+        <v>4</v>
+      </c>
+      <c r="AY48">
+        <v>33</v>
+      </c>
+      <c r="AZ48">
+        <v>12</v>
+      </c>
+      <c r="BA48">
+        <v>9</v>
+      </c>
+      <c r="BB48">
+        <v>6</v>
+      </c>
+      <c r="BC48">
+        <v>15</v>
+      </c>
+      <c r="BD48">
+        <v>1.74</v>
+      </c>
+      <c r="BE48">
+        <v>6.75</v>
+      </c>
+      <c r="BF48">
+        <v>2.32</v>
+      </c>
+      <c r="BG48">
+        <v>1.25</v>
+      </c>
+      <c r="BH48">
+        <v>3.35</v>
+      </c>
+      <c r="BI48">
+        <v>1.44</v>
+      </c>
+      <c r="BJ48">
+        <v>2.45</v>
+      </c>
+      <c r="BK48">
+        <v>1.72</v>
+      </c>
+      <c r="BL48">
+        <v>1.94</v>
+      </c>
+      <c r="BM48">
+        <v>2.12</v>
+      </c>
+      <c r="BN48">
+        <v>1.58</v>
+      </c>
+      <c r="BO48">
+        <v>2.75</v>
+      </c>
+      <c r="BP48">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="145">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -810,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP48"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4028,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16">
         <v>0.67</v>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>2.07</v>
@@ -7945,7 +7945,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>1.47</v>
@@ -10699,6 +10699,212 @@
       </c>
       <c r="BP48">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7778118</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" t="s">
+        <v>74</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>92</v>
+      </c>
+      <c r="P49" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q49">
+        <v>3.2</v>
+      </c>
+      <c r="R49">
+        <v>1.95</v>
+      </c>
+      <c r="S49">
+        <v>4</v>
+      </c>
+      <c r="T49">
+        <v>1.53</v>
+      </c>
+      <c r="U49">
+        <v>2.38</v>
+      </c>
+      <c r="V49">
+        <v>3.5</v>
+      </c>
+      <c r="W49">
+        <v>1.29</v>
+      </c>
+      <c r="X49">
+        <v>11</v>
+      </c>
+      <c r="Y49">
+        <v>1.05</v>
+      </c>
+      <c r="Z49">
+        <v>2.33</v>
+      </c>
+      <c r="AA49">
+        <v>3.27</v>
+      </c>
+      <c r="AB49">
+        <v>2.99</v>
+      </c>
+      <c r="AC49">
+        <v>1.08</v>
+      </c>
+      <c r="AD49">
+        <v>7.5</v>
+      </c>
+      <c r="AE49">
+        <v>1.45</v>
+      </c>
+      <c r="AF49">
+        <v>2.7</v>
+      </c>
+      <c r="AG49">
+        <v>2.25</v>
+      </c>
+      <c r="AH49">
+        <v>1.53</v>
+      </c>
+      <c r="AI49">
+        <v>2</v>
+      </c>
+      <c r="AJ49">
+        <v>1.75</v>
+      </c>
+      <c r="AK49">
+        <v>1.36</v>
+      </c>
+      <c r="AL49">
+        <v>1.3</v>
+      </c>
+      <c r="AM49">
+        <v>1.57</v>
+      </c>
+      <c r="AN49">
+        <v>1</v>
+      </c>
+      <c r="AO49">
+        <v>1.5</v>
+      </c>
+      <c r="AP49">
+        <v>0.5</v>
+      </c>
+      <c r="AQ49">
+        <v>2</v>
+      </c>
+      <c r="AR49">
+        <v>1.58</v>
+      </c>
+      <c r="AS49">
+        <v>1.84</v>
+      </c>
+      <c r="AT49">
+        <v>3.42</v>
+      </c>
+      <c r="AU49">
+        <v>6</v>
+      </c>
+      <c r="AV49">
+        <v>6</v>
+      </c>
+      <c r="AW49">
+        <v>3</v>
+      </c>
+      <c r="AX49">
+        <v>11</v>
+      </c>
+      <c r="AY49">
+        <v>9</v>
+      </c>
+      <c r="AZ49">
+        <v>18</v>
+      </c>
+      <c r="BA49">
+        <v>2</v>
+      </c>
+      <c r="BB49">
+        <v>2</v>
+      </c>
+      <c r="BC49">
+        <v>4</v>
+      </c>
+      <c r="BD49">
+        <v>1.74</v>
+      </c>
+      <c r="BE49">
+        <v>6.75</v>
+      </c>
+      <c r="BF49">
+        <v>2.28</v>
+      </c>
+      <c r="BG49">
+        <v>1.24</v>
+      </c>
+      <c r="BH49">
+        <v>3.4</v>
+      </c>
+      <c r="BI49">
+        <v>1.42</v>
+      </c>
+      <c r="BJ49">
+        <v>2.5</v>
+      </c>
+      <c r="BK49">
+        <v>1.7</v>
+      </c>
+      <c r="BL49">
+        <v>1.95</v>
+      </c>
+      <c r="BM49">
+        <v>2.1</v>
+      </c>
+      <c r="BN49">
+        <v>1.61</v>
+      </c>
+      <c r="BO49">
+        <v>2.7</v>
+      </c>
+      <c r="BP49">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="150">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -379,6 +379,18 @@
     <t>['45+4']</t>
   </si>
   <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['63', '73']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['27', '53']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -449,6 +461,9 @@
   </si>
   <si>
     <t>['51', '86']</t>
+  </si>
+  <si>
+    <t>['21']</t>
   </si>
 </sst>
 </file>
@@ -810,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP49"/>
+  <dimension ref="A1:BP53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1066,7 +1081,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1147,7 +1162,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1684,7 +1699,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1762,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1968,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -2177,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2383,7 +2398,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2714,7 +2729,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2792,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -2920,7 +2935,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2998,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.33</v>
@@ -3126,7 +3141,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3410,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>0</v>
@@ -3619,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3744,7 +3759,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3950,7 +3965,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4156,7 +4171,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4568,7 +4583,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4774,7 +4789,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -5186,7 +5201,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -5267,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="AQ22">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR22">
         <v>2.08</v>
@@ -5598,7 +5613,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5804,7 +5819,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -6010,7 +6025,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6216,7 +6231,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6294,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>2</v>
@@ -6422,7 +6437,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6500,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1.33</v>
@@ -6709,7 +6724,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ29">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -6834,7 +6849,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -6915,7 +6930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.39</v>
@@ -7246,7 +7261,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7533,7 +7548,7 @@
         <v>3</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.86</v>
@@ -7864,7 +7879,7 @@
         <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8070,7 +8085,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -8276,7 +8291,7 @@
         <v>92</v>
       </c>
       <c r="P37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8354,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>1.5</v>
@@ -8482,7 +8497,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q38">
         <v>3.1</v>
@@ -8563,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -8688,7 +8703,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="Q39">
         <v>3.75</v>
@@ -9100,7 +9115,7 @@
         <v>92</v>
       </c>
       <c r="P41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9512,7 +9527,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -9924,7 +9939,7 @@
         <v>97</v>
       </c>
       <c r="P45" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Q45">
         <v>3.35</v>
@@ -10336,7 +10351,7 @@
         <v>92</v>
       </c>
       <c r="P47" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10414,7 +10429,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>3</v>
@@ -10542,7 +10557,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -10623,7 +10638,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR48">
         <v>1.63</v>
@@ -10748,7 +10763,7 @@
         <v>92</v>
       </c>
       <c r="P49" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -10905,6 +10920,830 @@
       </c>
       <c r="BP49">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7778132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" t="s">
+        <v>85</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>121</v>
+      </c>
+      <c r="P50" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q50">
+        <v>3.25</v>
+      </c>
+      <c r="R50">
+        <v>1.91</v>
+      </c>
+      <c r="S50">
+        <v>4</v>
+      </c>
+      <c r="T50">
+        <v>1.62</v>
+      </c>
+      <c r="U50">
+        <v>2.2</v>
+      </c>
+      <c r="V50">
+        <v>4</v>
+      </c>
+      <c r="W50">
+        <v>1.22</v>
+      </c>
+      <c r="X50">
+        <v>13</v>
+      </c>
+      <c r="Y50">
+        <v>1.04</v>
+      </c>
+      <c r="Z50">
+        <v>2.32</v>
+      </c>
+      <c r="AA50">
+        <v>2.84</v>
+      </c>
+      <c r="AB50">
+        <v>3.47</v>
+      </c>
+      <c r="AC50">
+        <v>1.11</v>
+      </c>
+      <c r="AD50">
+        <v>6.25</v>
+      </c>
+      <c r="AE50">
+        <v>1.5</v>
+      </c>
+      <c r="AF50">
+        <v>2.3</v>
+      </c>
+      <c r="AG50">
+        <v>2.62</v>
+      </c>
+      <c r="AH50">
+        <v>1.43</v>
+      </c>
+      <c r="AI50">
+        <v>2.2</v>
+      </c>
+      <c r="AJ50">
+        <v>1.62</v>
+      </c>
+      <c r="AK50">
+        <v>1.34</v>
+      </c>
+      <c r="AL50">
+        <v>1.39</v>
+      </c>
+      <c r="AM50">
+        <v>1.6</v>
+      </c>
+      <c r="AN50">
+        <v>0</v>
+      </c>
+      <c r="AO50">
+        <v>1.5</v>
+      </c>
+      <c r="AP50">
+        <v>1</v>
+      </c>
+      <c r="AQ50">
+        <v>1</v>
+      </c>
+      <c r="AR50">
+        <v>1.12</v>
+      </c>
+      <c r="AS50">
+        <v>1.05</v>
+      </c>
+      <c r="AT50">
+        <v>2.17</v>
+      </c>
+      <c r="AU50">
+        <v>8</v>
+      </c>
+      <c r="AV50">
+        <v>5</v>
+      </c>
+      <c r="AW50">
+        <v>12</v>
+      </c>
+      <c r="AX50">
+        <v>1</v>
+      </c>
+      <c r="AY50">
+        <v>24</v>
+      </c>
+      <c r="AZ50">
+        <v>6</v>
+      </c>
+      <c r="BA50">
+        <v>3</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>3</v>
+      </c>
+      <c r="BD50">
+        <v>1.91</v>
+      </c>
+      <c r="BE50">
+        <v>8</v>
+      </c>
+      <c r="BF50">
+        <v>2.1</v>
+      </c>
+      <c r="BG50">
+        <v>1.47</v>
+      </c>
+      <c r="BH50">
+        <v>2.54</v>
+      </c>
+      <c r="BI50">
+        <v>1.74</v>
+      </c>
+      <c r="BJ50">
+        <v>2.05</v>
+      </c>
+      <c r="BK50">
+        <v>2.2</v>
+      </c>
+      <c r="BL50">
+        <v>1.64</v>
+      </c>
+      <c r="BM50">
+        <v>3.2</v>
+      </c>
+      <c r="BN50">
+        <v>1.28</v>
+      </c>
+      <c r="BO50">
+        <v>4.55</v>
+      </c>
+      <c r="BP50">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7778124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F51">
+        <v>6</v>
+      </c>
+      <c r="G51" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>3</v>
+      </c>
+      <c r="O51" t="s">
+        <v>122</v>
+      </c>
+      <c r="P51" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q51">
+        <v>3.4</v>
+      </c>
+      <c r="R51">
+        <v>1.83</v>
+      </c>
+      <c r="S51">
+        <v>4</v>
+      </c>
+      <c r="T51">
+        <v>1.67</v>
+      </c>
+      <c r="U51">
+        <v>2.1</v>
+      </c>
+      <c r="V51">
+        <v>4.33</v>
+      </c>
+      <c r="W51">
+        <v>1.2</v>
+      </c>
+      <c r="X51">
+        <v>15</v>
+      </c>
+      <c r="Y51">
+        <v>1.03</v>
+      </c>
+      <c r="Z51">
+        <v>2.5</v>
+      </c>
+      <c r="AA51">
+        <v>3.05</v>
+      </c>
+      <c r="AB51">
+        <v>2.92</v>
+      </c>
+      <c r="AC51">
+        <v>1.12</v>
+      </c>
+      <c r="AD51">
+        <v>6</v>
+      </c>
+      <c r="AE51">
+        <v>1.57</v>
+      </c>
+      <c r="AF51">
+        <v>2.15</v>
+      </c>
+      <c r="AG51">
+        <v>2.85</v>
+      </c>
+      <c r="AH51">
+        <v>1.37</v>
+      </c>
+      <c r="AI51">
+        <v>2.25</v>
+      </c>
+      <c r="AJ51">
+        <v>1.57</v>
+      </c>
+      <c r="AK51">
+        <v>1.35</v>
+      </c>
+      <c r="AL51">
+        <v>1.38</v>
+      </c>
+      <c r="AM51">
+        <v>1.51</v>
+      </c>
+      <c r="AN51">
+        <v>0</v>
+      </c>
+      <c r="AO51">
+        <v>0.33</v>
+      </c>
+      <c r="AP51">
+        <v>1</v>
+      </c>
+      <c r="AQ51">
+        <v>0.25</v>
+      </c>
+      <c r="AR51">
+        <v>1.28</v>
+      </c>
+      <c r="AS51">
+        <v>1.38</v>
+      </c>
+      <c r="AT51">
+        <v>2.66</v>
+      </c>
+      <c r="AU51">
+        <v>4</v>
+      </c>
+      <c r="AV51">
+        <v>5</v>
+      </c>
+      <c r="AW51">
+        <v>6</v>
+      </c>
+      <c r="AX51">
+        <v>4</v>
+      </c>
+      <c r="AY51">
+        <v>12</v>
+      </c>
+      <c r="AZ51">
+        <v>12</v>
+      </c>
+      <c r="BA51">
+        <v>5</v>
+      </c>
+      <c r="BB51">
+        <v>6</v>
+      </c>
+      <c r="BC51">
+        <v>11</v>
+      </c>
+      <c r="BD51">
+        <v>1.91</v>
+      </c>
+      <c r="BE51">
+        <v>8</v>
+      </c>
+      <c r="BF51">
+        <v>2.1</v>
+      </c>
+      <c r="BG51">
+        <v>1.33</v>
+      </c>
+      <c r="BH51">
+        <v>2.83</v>
+      </c>
+      <c r="BI51">
+        <v>1.55</v>
+      </c>
+      <c r="BJ51">
+        <v>2.34</v>
+      </c>
+      <c r="BK51">
+        <v>1.93</v>
+      </c>
+      <c r="BL51">
+        <v>1.86</v>
+      </c>
+      <c r="BM51">
+        <v>2.44</v>
+      </c>
+      <c r="BN51">
+        <v>1.51</v>
+      </c>
+      <c r="BO51">
+        <v>3.8</v>
+      </c>
+      <c r="BP51">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7778125</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>123</v>
+      </c>
+      <c r="P52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q52">
+        <v>2.75</v>
+      </c>
+      <c r="R52">
+        <v>1.95</v>
+      </c>
+      <c r="S52">
+        <v>5</v>
+      </c>
+      <c r="T52">
+        <v>1.53</v>
+      </c>
+      <c r="U52">
+        <v>2.38</v>
+      </c>
+      <c r="V52">
+        <v>3.75</v>
+      </c>
+      <c r="W52">
+        <v>1.25</v>
+      </c>
+      <c r="X52">
+        <v>11</v>
+      </c>
+      <c r="Y52">
+        <v>1.05</v>
+      </c>
+      <c r="Z52">
+        <v>2.01</v>
+      </c>
+      <c r="AA52">
+        <v>3.25</v>
+      </c>
+      <c r="AB52">
+        <v>3.77</v>
+      </c>
+      <c r="AC52">
+        <v>1.1</v>
+      </c>
+      <c r="AD52">
+        <v>6.5</v>
+      </c>
+      <c r="AE52">
+        <v>1.57</v>
+      </c>
+      <c r="AF52">
+        <v>2.42</v>
+      </c>
+      <c r="AG52">
+        <v>2.37</v>
+      </c>
+      <c r="AH52">
+        <v>1.48</v>
+      </c>
+      <c r="AI52">
+        <v>2.2</v>
+      </c>
+      <c r="AJ52">
+        <v>1.62</v>
+      </c>
+      <c r="AK52">
+        <v>1.24</v>
+      </c>
+      <c r="AL52">
+        <v>1.33</v>
+      </c>
+      <c r="AM52">
+        <v>1.85</v>
+      </c>
+      <c r="AN52">
+        <v>0</v>
+      </c>
+      <c r="AO52">
+        <v>0.33</v>
+      </c>
+      <c r="AP52">
+        <v>1</v>
+      </c>
+      <c r="AQ52">
+        <v>0.25</v>
+      </c>
+      <c r="AR52">
+        <v>1.02</v>
+      </c>
+      <c r="AS52">
+        <v>1.41</v>
+      </c>
+      <c r="AT52">
+        <v>2.43</v>
+      </c>
+      <c r="AU52">
+        <v>5</v>
+      </c>
+      <c r="AV52">
+        <v>2</v>
+      </c>
+      <c r="AW52">
+        <v>8</v>
+      </c>
+      <c r="AX52">
+        <v>4</v>
+      </c>
+      <c r="AY52">
+        <v>14</v>
+      </c>
+      <c r="AZ52">
+        <v>7</v>
+      </c>
+      <c r="BA52">
+        <v>6</v>
+      </c>
+      <c r="BB52">
+        <v>2</v>
+      </c>
+      <c r="BC52">
+        <v>8</v>
+      </c>
+      <c r="BD52">
+        <v>1.62</v>
+      </c>
+      <c r="BE52">
+        <v>8.5</v>
+      </c>
+      <c r="BF52">
+        <v>2.6</v>
+      </c>
+      <c r="BG52">
+        <v>1.29</v>
+      </c>
+      <c r="BH52">
+        <v>3.04</v>
+      </c>
+      <c r="BI52">
+        <v>1.59</v>
+      </c>
+      <c r="BJ52">
+        <v>2.26</v>
+      </c>
+      <c r="BK52">
+        <v>2</v>
+      </c>
+      <c r="BL52">
+        <v>1.8</v>
+      </c>
+      <c r="BM52">
+        <v>2.53</v>
+      </c>
+      <c r="BN52">
+        <v>1.47</v>
+      </c>
+      <c r="BO52">
+        <v>3.5</v>
+      </c>
+      <c r="BP52">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7778127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F53">
+        <v>6</v>
+      </c>
+      <c r="G53" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" t="s">
+        <v>86</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53" t="s">
+        <v>124</v>
+      </c>
+      <c r="P53" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q53">
+        <v>3.25</v>
+      </c>
+      <c r="R53">
+        <v>1.95</v>
+      </c>
+      <c r="S53">
+        <v>3.75</v>
+      </c>
+      <c r="T53">
+        <v>1.53</v>
+      </c>
+      <c r="U53">
+        <v>2.38</v>
+      </c>
+      <c r="V53">
+        <v>3.75</v>
+      </c>
+      <c r="W53">
+        <v>1.25</v>
+      </c>
+      <c r="X53">
+        <v>11</v>
+      </c>
+      <c r="Y53">
+        <v>1.05</v>
+      </c>
+      <c r="Z53">
+        <v>2.63</v>
+      </c>
+      <c r="AA53">
+        <v>3.09</v>
+      </c>
+      <c r="AB53">
+        <v>2.73</v>
+      </c>
+      <c r="AC53">
+        <v>1.09</v>
+      </c>
+      <c r="AD53">
+        <v>6.75</v>
+      </c>
+      <c r="AE53">
+        <v>1.47</v>
+      </c>
+      <c r="AF53">
+        <v>2.69</v>
+      </c>
+      <c r="AG53">
+        <v>2.3</v>
+      </c>
+      <c r="AH53">
+        <v>1.5</v>
+      </c>
+      <c r="AI53">
+        <v>2</v>
+      </c>
+      <c r="AJ53">
+        <v>1.75</v>
+      </c>
+      <c r="AK53">
+        <v>1.38</v>
+      </c>
+      <c r="AL53">
+        <v>1.37</v>
+      </c>
+      <c r="AM53">
+        <v>1.56</v>
+      </c>
+      <c r="AN53">
+        <v>1</v>
+      </c>
+      <c r="AO53">
+        <v>1.33</v>
+      </c>
+      <c r="AP53">
+        <v>1.5</v>
+      </c>
+      <c r="AQ53">
+        <v>1</v>
+      </c>
+      <c r="AR53">
+        <v>1.21</v>
+      </c>
+      <c r="AS53">
+        <v>1.52</v>
+      </c>
+      <c r="AT53">
+        <v>2.73</v>
+      </c>
+      <c r="AU53">
+        <v>5</v>
+      </c>
+      <c r="AV53">
+        <v>2</v>
+      </c>
+      <c r="AW53">
+        <v>7</v>
+      </c>
+      <c r="AX53">
+        <v>6</v>
+      </c>
+      <c r="AY53">
+        <v>13</v>
+      </c>
+      <c r="AZ53">
+        <v>9</v>
+      </c>
+      <c r="BA53">
+        <v>5</v>
+      </c>
+      <c r="BB53">
+        <v>3</v>
+      </c>
+      <c r="BC53">
+        <v>8</v>
+      </c>
+      <c r="BD53">
+        <v>1.85</v>
+      </c>
+      <c r="BE53">
+        <v>8.5</v>
+      </c>
+      <c r="BF53">
+        <v>2.15</v>
+      </c>
+      <c r="BG53">
+        <v>1.24</v>
+      </c>
+      <c r="BH53">
+        <v>3.34</v>
+      </c>
+      <c r="BI53">
+        <v>1.47</v>
+      </c>
+      <c r="BJ53">
+        <v>2.42</v>
+      </c>
+      <c r="BK53">
+        <v>1.85</v>
+      </c>
+      <c r="BL53">
+        <v>1.85</v>
+      </c>
+      <c r="BM53">
+        <v>2.34</v>
+      </c>
+      <c r="BN53">
+        <v>1.5</v>
+      </c>
+      <c r="BO53">
+        <v>3.14</v>
+      </c>
+      <c r="BP53">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="157">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -391,6 +391,21 @@
     <t>['27', '53']</t>
   </si>
   <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['20', '75']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -415,9 +430,6 @@
     <t>['87']</t>
   </si>
   <si>
-    <t>['82']</t>
-  </si>
-  <si>
     <t>['32', '51']</t>
   </si>
   <si>
@@ -464,6 +476,15 @@
   </si>
   <si>
     <t>['21']</t>
+  </si>
+  <si>
+    <t>['38', '67']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['24', '37']</t>
   </si>
 </sst>
 </file>
@@ -825,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP53"/>
+  <dimension ref="A1:BP59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1081,7 +1102,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1365,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1574,7 +1595,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1699,7 +1720,7 @@
         <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1986,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2189,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>0.25</v>
@@ -2601,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -2729,7 +2750,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2935,7 +2956,7 @@
         <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3141,7 +3162,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="Q12">
         <v>3.1</v>
@@ -3222,7 +3243,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3631,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>0.25</v>
@@ -3759,7 +3780,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="Q15">
         <v>4.3</v>
@@ -3840,7 +3861,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -3965,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4046,7 +4067,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4171,7 +4192,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -4455,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ18">
         <v>1.33</v>
@@ -4583,7 +4604,7 @@
         <v>92</v>
       </c>
       <c r="P19" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="Q19">
         <v>4</v>
@@ -4789,7 +4810,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -5073,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ21">
         <v>0</v>
@@ -5201,7 +5222,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -5279,7 +5300,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ22">
         <v>0.25</v>
@@ -5485,10 +5506,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -5613,7 +5634,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5694,7 +5715,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -5819,7 +5840,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5897,7 +5918,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6025,7 +6046,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6103,10 +6124,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR26">
         <v>2</v>
@@ -6231,7 +6252,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6312,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR27">
         <v>0.91</v>
@@ -6437,7 +6458,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6849,7 +6870,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7133,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -7261,7 +7282,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7339,7 +7360,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>1.67</v>
@@ -7545,7 +7566,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7754,7 +7775,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR34">
         <v>1.99</v>
@@ -7879,7 +7900,7 @@
         <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8085,7 +8106,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q36">
         <v>3.6</v>
@@ -8163,7 +8184,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8291,7 +8312,7 @@
         <v>92</v>
       </c>
       <c r="P37" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8372,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.08</v>
@@ -8497,7 +8518,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Q38">
         <v>3.1</v>
@@ -8703,7 +8724,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q39">
         <v>3.75</v>
@@ -8987,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
         <v>0.5</v>
@@ -9115,7 +9136,7 @@
         <v>92</v>
       </c>
       <c r="P41" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9196,7 +9217,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR41">
         <v>0</v>
@@ -9527,7 +9548,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -9939,7 +9960,7 @@
         <v>97</v>
       </c>
       <c r="P45" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="Q45">
         <v>3.35</v>
@@ -10351,7 +10372,7 @@
         <v>92</v>
       </c>
       <c r="P47" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10557,7 +10578,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -10763,7 +10784,7 @@
         <v>92</v>
       </c>
       <c r="P49" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -11175,7 +11196,7 @@
         <v>122</v>
       </c>
       <c r="P51" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11744,6 +11765,1242 @@
       </c>
       <c r="BP53">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7778129</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45732.04166666666</v>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54" t="s">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>2</v>
+      </c>
+      <c r="N54">
+        <v>3</v>
+      </c>
+      <c r="O54" t="s">
+        <v>125</v>
+      </c>
+      <c r="P54" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q54">
+        <v>3</v>
+      </c>
+      <c r="R54">
+        <v>2.05</v>
+      </c>
+      <c r="S54">
+        <v>4</v>
+      </c>
+      <c r="T54">
+        <v>1.44</v>
+      </c>
+      <c r="U54">
+        <v>2.63</v>
+      </c>
+      <c r="V54">
+        <v>3.25</v>
+      </c>
+      <c r="W54">
+        <v>1.33</v>
+      </c>
+      <c r="X54">
+        <v>10</v>
+      </c>
+      <c r="Y54">
+        <v>1.06</v>
+      </c>
+      <c r="Z54">
+        <v>2.17</v>
+      </c>
+      <c r="AA54">
+        <v>3.21</v>
+      </c>
+      <c r="AB54">
+        <v>3.36</v>
+      </c>
+      <c r="AC54">
+        <v>1.07</v>
+      </c>
+      <c r="AD54">
+        <v>8</v>
+      </c>
+      <c r="AE54">
+        <v>1.36</v>
+      </c>
+      <c r="AF54">
+        <v>3.1</v>
+      </c>
+      <c r="AG54">
+        <v>2</v>
+      </c>
+      <c r="AH54">
+        <v>1.67</v>
+      </c>
+      <c r="AI54">
+        <v>1.91</v>
+      </c>
+      <c r="AJ54">
+        <v>1.91</v>
+      </c>
+      <c r="AK54">
+        <v>1.34</v>
+      </c>
+      <c r="AL54">
+        <v>1.35</v>
+      </c>
+      <c r="AM54">
+        <v>1.64</v>
+      </c>
+      <c r="AN54">
+        <v>2</v>
+      </c>
+      <c r="AO54">
+        <v>1.33</v>
+      </c>
+      <c r="AP54">
+        <v>1.33</v>
+      </c>
+      <c r="AQ54">
+        <v>1.75</v>
+      </c>
+      <c r="AR54">
+        <v>1.44</v>
+      </c>
+      <c r="AS54">
+        <v>1.41</v>
+      </c>
+      <c r="AT54">
+        <v>2.85</v>
+      </c>
+      <c r="AU54">
+        <v>5</v>
+      </c>
+      <c r="AV54">
+        <v>5</v>
+      </c>
+      <c r="AW54">
+        <v>7</v>
+      </c>
+      <c r="AX54">
+        <v>5</v>
+      </c>
+      <c r="AY54">
+        <v>16</v>
+      </c>
+      <c r="AZ54">
+        <v>10</v>
+      </c>
+      <c r="BA54">
+        <v>5</v>
+      </c>
+      <c r="BB54">
+        <v>5</v>
+      </c>
+      <c r="BC54">
+        <v>10</v>
+      </c>
+      <c r="BD54">
+        <v>1.75</v>
+      </c>
+      <c r="BE54">
+        <v>8.5</v>
+      </c>
+      <c r="BF54">
+        <v>2.3</v>
+      </c>
+      <c r="BG54">
+        <v>1.19</v>
+      </c>
+      <c r="BH54">
+        <v>3.78</v>
+      </c>
+      <c r="BI54">
+        <v>1.39</v>
+      </c>
+      <c r="BJ54">
+        <v>2.67</v>
+      </c>
+      <c r="BK54">
+        <v>1.7</v>
+      </c>
+      <c r="BL54">
+        <v>2.05</v>
+      </c>
+      <c r="BM54">
+        <v>2.05</v>
+      </c>
+      <c r="BN54">
+        <v>1.7</v>
+      </c>
+      <c r="BO54">
+        <v>2.83</v>
+      </c>
+      <c r="BP54">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7778131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s">
+        <v>80</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55" t="s">
+        <v>126</v>
+      </c>
+      <c r="P55" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q55">
+        <v>2.38</v>
+      </c>
+      <c r="R55">
+        <v>2.1</v>
+      </c>
+      <c r="S55">
+        <v>5.5</v>
+      </c>
+      <c r="T55">
+        <v>1.44</v>
+      </c>
+      <c r="U55">
+        <v>2.63</v>
+      </c>
+      <c r="V55">
+        <v>3.25</v>
+      </c>
+      <c r="W55">
+        <v>1.33</v>
+      </c>
+      <c r="X55">
+        <v>10</v>
+      </c>
+      <c r="Y55">
+        <v>1.06</v>
+      </c>
+      <c r="Z55">
+        <v>1.67</v>
+      </c>
+      <c r="AA55">
+        <v>3.6</v>
+      </c>
+      <c r="AB55">
+        <v>5.1</v>
+      </c>
+      <c r="AC55">
+        <v>1.07</v>
+      </c>
+      <c r="AD55">
+        <v>8</v>
+      </c>
+      <c r="AE55">
+        <v>1.38</v>
+      </c>
+      <c r="AF55">
+        <v>3</v>
+      </c>
+      <c r="AG55">
+        <v>2.05</v>
+      </c>
+      <c r="AH55">
+        <v>1.61</v>
+      </c>
+      <c r="AI55">
+        <v>2.05</v>
+      </c>
+      <c r="AJ55">
+        <v>1.7</v>
+      </c>
+      <c r="AK55">
+        <v>1.18</v>
+      </c>
+      <c r="AL55">
+        <v>1.29</v>
+      </c>
+      <c r="AM55">
+        <v>2.15</v>
+      </c>
+      <c r="AN55">
+        <v>3</v>
+      </c>
+      <c r="AO55">
+        <v>3</v>
+      </c>
+      <c r="AP55">
+        <v>2.33</v>
+      </c>
+      <c r="AQ55">
+        <v>2.33</v>
+      </c>
+      <c r="AR55">
+        <v>1.46</v>
+      </c>
+      <c r="AS55">
+        <v>1.27</v>
+      </c>
+      <c r="AT55">
+        <v>2.73</v>
+      </c>
+      <c r="AU55">
+        <v>3</v>
+      </c>
+      <c r="AV55">
+        <v>6</v>
+      </c>
+      <c r="AW55">
+        <v>14</v>
+      </c>
+      <c r="AX55">
+        <v>5</v>
+      </c>
+      <c r="AY55">
+        <v>22</v>
+      </c>
+      <c r="AZ55">
+        <v>14</v>
+      </c>
+      <c r="BA55">
+        <v>5</v>
+      </c>
+      <c r="BB55">
+        <v>5</v>
+      </c>
+      <c r="BC55">
+        <v>10</v>
+      </c>
+      <c r="BD55">
+        <v>1.44</v>
+      </c>
+      <c r="BE55">
+        <v>9</v>
+      </c>
+      <c r="BF55">
+        <v>3</v>
+      </c>
+      <c r="BG55">
+        <v>1.21</v>
+      </c>
+      <c r="BH55">
+        <v>3.58</v>
+      </c>
+      <c r="BI55">
+        <v>1.42</v>
+      </c>
+      <c r="BJ55">
+        <v>2.57</v>
+      </c>
+      <c r="BK55">
+        <v>1.78</v>
+      </c>
+      <c r="BL55">
+        <v>2</v>
+      </c>
+      <c r="BM55">
+        <v>2.23</v>
+      </c>
+      <c r="BN55">
+        <v>1.62</v>
+      </c>
+      <c r="BO55">
+        <v>2.92</v>
+      </c>
+      <c r="BP55">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7778130</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" t="s">
+        <v>76</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>92</v>
+      </c>
+      <c r="P56" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q56">
+        <v>4.13</v>
+      </c>
+      <c r="R56">
+        <v>2.22</v>
+      </c>
+      <c r="S56">
+        <v>2.74</v>
+      </c>
+      <c r="T56">
+        <v>1.4</v>
+      </c>
+      <c r="U56">
+        <v>2.96</v>
+      </c>
+      <c r="V56">
+        <v>2.97</v>
+      </c>
+      <c r="W56">
+        <v>1.39</v>
+      </c>
+      <c r="X56">
+        <v>7.75</v>
+      </c>
+      <c r="Y56">
+        <v>1.07</v>
+      </c>
+      <c r="Z56">
+        <v>3.45</v>
+      </c>
+      <c r="AA56">
+        <v>3.31</v>
+      </c>
+      <c r="AB56">
+        <v>2.09</v>
+      </c>
+      <c r="AC56">
+        <v>1.06</v>
+      </c>
+      <c r="AD56">
+        <v>8.5</v>
+      </c>
+      <c r="AE56">
+        <v>1.33</v>
+      </c>
+      <c r="AF56">
+        <v>3.2</v>
+      </c>
+      <c r="AG56">
+        <v>1.94</v>
+      </c>
+      <c r="AH56">
+        <v>1.8</v>
+      </c>
+      <c r="AI56">
+        <v>1.8</v>
+      </c>
+      <c r="AJ56">
+        <v>1.88</v>
+      </c>
+      <c r="AK56">
+        <v>1.7</v>
+      </c>
+      <c r="AL56">
+        <v>1.31</v>
+      </c>
+      <c r="AM56">
+        <v>1.3</v>
+      </c>
+      <c r="AN56">
+        <v>2.33</v>
+      </c>
+      <c r="AO56">
+        <v>2</v>
+      </c>
+      <c r="AP56">
+        <v>2</v>
+      </c>
+      <c r="AQ56">
+        <v>1.67</v>
+      </c>
+      <c r="AR56">
+        <v>1.66</v>
+      </c>
+      <c r="AS56">
+        <v>1.39</v>
+      </c>
+      <c r="AT56">
+        <v>3.05</v>
+      </c>
+      <c r="AU56">
+        <v>3</v>
+      </c>
+      <c r="AV56">
+        <v>6</v>
+      </c>
+      <c r="AW56">
+        <v>7</v>
+      </c>
+      <c r="AX56">
+        <v>10</v>
+      </c>
+      <c r="AY56">
+        <v>10</v>
+      </c>
+      <c r="AZ56">
+        <v>17</v>
+      </c>
+      <c r="BA56">
+        <v>7</v>
+      </c>
+      <c r="BB56">
+        <v>6</v>
+      </c>
+      <c r="BC56">
+        <v>13</v>
+      </c>
+      <c r="BD56">
+        <v>2.05</v>
+      </c>
+      <c r="BE56">
+        <v>8.5</v>
+      </c>
+      <c r="BF56">
+        <v>1.91</v>
+      </c>
+      <c r="BG56">
+        <v>1.24</v>
+      </c>
+      <c r="BH56">
+        <v>3.45</v>
+      </c>
+      <c r="BI56">
+        <v>1.35</v>
+      </c>
+      <c r="BJ56">
+        <v>2.74</v>
+      </c>
+      <c r="BK56">
+        <v>1.64</v>
+      </c>
+      <c r="BL56">
+        <v>2.07</v>
+      </c>
+      <c r="BM56">
+        <v>2.05</v>
+      </c>
+      <c r="BN56">
+        <v>1.7</v>
+      </c>
+      <c r="BO56">
+        <v>2.71</v>
+      </c>
+      <c r="BP56">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7778126</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s">
+        <v>70</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57" t="s">
+        <v>127</v>
+      </c>
+      <c r="P57" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q57">
+        <v>2.75</v>
+      </c>
+      <c r="R57">
+        <v>2.2</v>
+      </c>
+      <c r="S57">
+        <v>4</v>
+      </c>
+      <c r="T57">
+        <v>1.36</v>
+      </c>
+      <c r="U57">
+        <v>3</v>
+      </c>
+      <c r="V57">
+        <v>2.75</v>
+      </c>
+      <c r="W57">
+        <v>1.4</v>
+      </c>
+      <c r="X57">
+        <v>8</v>
+      </c>
+      <c r="Y57">
+        <v>1.08</v>
+      </c>
+      <c r="Z57">
+        <v>1.99</v>
+      </c>
+      <c r="AA57">
+        <v>3.45</v>
+      </c>
+      <c r="AB57">
+        <v>3.6</v>
+      </c>
+      <c r="AC57">
+        <v>1.05</v>
+      </c>
+      <c r="AD57">
+        <v>9</v>
+      </c>
+      <c r="AE57">
+        <v>1.3</v>
+      </c>
+      <c r="AF57">
+        <v>3.45</v>
+      </c>
+      <c r="AG57">
+        <v>1.85</v>
+      </c>
+      <c r="AH57">
+        <v>1.89</v>
+      </c>
+      <c r="AI57">
+        <v>1.7</v>
+      </c>
+      <c r="AJ57">
+        <v>2.05</v>
+      </c>
+      <c r="AK57">
+        <v>1.31</v>
+      </c>
+      <c r="AL57">
+        <v>1.31</v>
+      </c>
+      <c r="AM57">
+        <v>1.76</v>
+      </c>
+      <c r="AN57">
+        <v>1</v>
+      </c>
+      <c r="AO57">
+        <v>1.5</v>
+      </c>
+      <c r="AP57">
+        <v>1.5</v>
+      </c>
+      <c r="AQ57">
+        <v>1</v>
+      </c>
+      <c r="AR57">
+        <v>1.24</v>
+      </c>
+      <c r="AS57">
+        <v>1.46</v>
+      </c>
+      <c r="AT57">
+        <v>2.7</v>
+      </c>
+      <c r="AU57">
+        <v>7</v>
+      </c>
+      <c r="AV57">
+        <v>12</v>
+      </c>
+      <c r="AW57">
+        <v>1</v>
+      </c>
+      <c r="AX57">
+        <v>12</v>
+      </c>
+      <c r="AY57">
+        <v>8</v>
+      </c>
+      <c r="AZ57">
+        <v>28</v>
+      </c>
+      <c r="BA57">
+        <v>2</v>
+      </c>
+      <c r="BB57">
+        <v>10</v>
+      </c>
+      <c r="BC57">
+        <v>12</v>
+      </c>
+      <c r="BD57">
+        <v>1.75</v>
+      </c>
+      <c r="BE57">
+        <v>8.5</v>
+      </c>
+      <c r="BF57">
+        <v>2.3</v>
+      </c>
+      <c r="BG57">
+        <v>1.3</v>
+      </c>
+      <c r="BH57">
+        <v>3</v>
+      </c>
+      <c r="BI57">
+        <v>1.35</v>
+      </c>
+      <c r="BJ57">
+        <v>2.74</v>
+      </c>
+      <c r="BK57">
+        <v>1.69</v>
+      </c>
+      <c r="BL57">
+        <v>2.11</v>
+      </c>
+      <c r="BM57">
+        <v>2.1</v>
+      </c>
+      <c r="BN57">
+        <v>1.7</v>
+      </c>
+      <c r="BO57">
+        <v>2.71</v>
+      </c>
+      <c r="BP57">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7778123</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H58" t="s">
+        <v>89</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58" t="s">
+        <v>128</v>
+      </c>
+      <c r="P58" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q58">
+        <v>3</v>
+      </c>
+      <c r="R58">
+        <v>2.05</v>
+      </c>
+      <c r="S58">
+        <v>4</v>
+      </c>
+      <c r="T58">
+        <v>1.44</v>
+      </c>
+      <c r="U58">
+        <v>2.63</v>
+      </c>
+      <c r="V58">
+        <v>3.4</v>
+      </c>
+      <c r="W58">
+        <v>1.3</v>
+      </c>
+      <c r="X58">
+        <v>10</v>
+      </c>
+      <c r="Y58">
+        <v>1.06</v>
+      </c>
+      <c r="Z58">
+        <v>2.25</v>
+      </c>
+      <c r="AA58">
+        <v>3.2</v>
+      </c>
+      <c r="AB58">
+        <v>3.19</v>
+      </c>
+      <c r="AC58">
+        <v>1.07</v>
+      </c>
+      <c r="AD58">
+        <v>8</v>
+      </c>
+      <c r="AE58">
+        <v>1.4</v>
+      </c>
+      <c r="AF58">
+        <v>2.9</v>
+      </c>
+      <c r="AG58">
+        <v>2.05</v>
+      </c>
+      <c r="AH58">
+        <v>1.61</v>
+      </c>
+      <c r="AI58">
+        <v>1.91</v>
+      </c>
+      <c r="AJ58">
+        <v>1.91</v>
+      </c>
+      <c r="AK58">
+        <v>1.41</v>
+      </c>
+      <c r="AL58">
+        <v>1.32</v>
+      </c>
+      <c r="AM58">
+        <v>1.58</v>
+      </c>
+      <c r="AN58">
+        <v>3</v>
+      </c>
+      <c r="AO58">
+        <v>0.67</v>
+      </c>
+      <c r="AP58">
+        <v>2.5</v>
+      </c>
+      <c r="AQ58">
+        <v>0.75</v>
+      </c>
+      <c r="AR58">
+        <v>1.91</v>
+      </c>
+      <c r="AS58">
+        <v>1.65</v>
+      </c>
+      <c r="AT58">
+        <v>3.56</v>
+      </c>
+      <c r="AU58">
+        <v>3</v>
+      </c>
+      <c r="AV58">
+        <v>8</v>
+      </c>
+      <c r="AW58">
+        <v>8</v>
+      </c>
+      <c r="AX58">
+        <v>6</v>
+      </c>
+      <c r="AY58">
+        <v>14</v>
+      </c>
+      <c r="AZ58">
+        <v>14</v>
+      </c>
+      <c r="BA58">
+        <v>9</v>
+      </c>
+      <c r="BB58">
+        <v>4</v>
+      </c>
+      <c r="BC58">
+        <v>13</v>
+      </c>
+      <c r="BD58">
+        <v>1.75</v>
+      </c>
+      <c r="BE58">
+        <v>8.5</v>
+      </c>
+      <c r="BF58">
+        <v>2.25</v>
+      </c>
+      <c r="BG58">
+        <v>1.22</v>
+      </c>
+      <c r="BH58">
+        <v>3.5</v>
+      </c>
+      <c r="BI58">
+        <v>1.47</v>
+      </c>
+      <c r="BJ58">
+        <v>2.56</v>
+      </c>
+      <c r="BK58">
+        <v>1.81</v>
+      </c>
+      <c r="BL58">
+        <v>1.99</v>
+      </c>
+      <c r="BM58">
+        <v>2.26</v>
+      </c>
+      <c r="BN58">
+        <v>1.6</v>
+      </c>
+      <c r="BO58">
+        <v>3.04</v>
+      </c>
+      <c r="BP58">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7778128</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45732.125</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>2</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59">
+        <v>3</v>
+      </c>
+      <c r="O59" t="s">
+        <v>129</v>
+      </c>
+      <c r="P59" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q59">
+        <v>3.25</v>
+      </c>
+      <c r="R59">
+        <v>2.1</v>
+      </c>
+      <c r="S59">
+        <v>3.4</v>
+      </c>
+      <c r="T59">
+        <v>1.44</v>
+      </c>
+      <c r="U59">
+        <v>2.63</v>
+      </c>
+      <c r="V59">
+        <v>3.25</v>
+      </c>
+      <c r="W59">
+        <v>1.33</v>
+      </c>
+      <c r="X59">
+        <v>9</v>
+      </c>
+      <c r="Y59">
+        <v>1.07</v>
+      </c>
+      <c r="Z59">
+        <v>2.9</v>
+      </c>
+      <c r="AA59">
+        <v>3.36</v>
+      </c>
+      <c r="AB59">
+        <v>2.34</v>
+      </c>
+      <c r="AC59">
+        <v>1.06</v>
+      </c>
+      <c r="AD59">
+        <v>8.5</v>
+      </c>
+      <c r="AE59">
+        <v>1.33</v>
+      </c>
+      <c r="AF59">
+        <v>3.2</v>
+      </c>
+      <c r="AG59">
+        <v>2</v>
+      </c>
+      <c r="AH59">
+        <v>1.75</v>
+      </c>
+      <c r="AI59">
+        <v>1.8</v>
+      </c>
+      <c r="AJ59">
+        <v>1.95</v>
+      </c>
+      <c r="AK59">
+        <v>1.46</v>
+      </c>
+      <c r="AL59">
+        <v>1.32</v>
+      </c>
+      <c r="AM59">
+        <v>1.53</v>
+      </c>
+      <c r="AN59">
+        <v>3</v>
+      </c>
+      <c r="AO59">
+        <v>1</v>
+      </c>
+      <c r="AP59">
+        <v>2</v>
+      </c>
+      <c r="AQ59">
+        <v>2</v>
+      </c>
+      <c r="AR59">
+        <v>1.93</v>
+      </c>
+      <c r="AS59">
+        <v>2.01</v>
+      </c>
+      <c r="AT59">
+        <v>3.94</v>
+      </c>
+      <c r="AU59">
+        <v>2</v>
+      </c>
+      <c r="AV59">
+        <v>4</v>
+      </c>
+      <c r="AW59">
+        <v>1</v>
+      </c>
+      <c r="AX59">
+        <v>2</v>
+      </c>
+      <c r="AY59">
+        <v>3</v>
+      </c>
+      <c r="AZ59">
+        <v>6</v>
+      </c>
+      <c r="BA59">
+        <v>1</v>
+      </c>
+      <c r="BB59">
+        <v>0</v>
+      </c>
+      <c r="BC59">
+        <v>1</v>
+      </c>
+      <c r="BD59">
+        <v>1.85</v>
+      </c>
+      <c r="BE59">
+        <v>8.5</v>
+      </c>
+      <c r="BF59">
+        <v>2.15</v>
+      </c>
+      <c r="BG59">
+        <v>1.21</v>
+      </c>
+      <c r="BH59">
+        <v>3.58</v>
+      </c>
+      <c r="BI59">
+        <v>1.47</v>
+      </c>
+      <c r="BJ59">
+        <v>2.53</v>
+      </c>
+      <c r="BK59">
+        <v>1.84</v>
+      </c>
+      <c r="BL59">
+        <v>1.95</v>
+      </c>
+      <c r="BM59">
+        <v>2.24</v>
+      </c>
+      <c r="BN59">
+        <v>1.6</v>
+      </c>
+      <c r="BO59">
+        <v>2.92</v>
+      </c>
+      <c r="BP59">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -229,18 +229,18 @@
     <t>Gamba Osaka</t>
   </si>
   <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Yokohama</t>
+  </si>
+  <si>
     <t>Fagiano Okayama</t>
   </si>
   <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
-    <t>Yokohama</t>
-  </si>
-  <si>
-    <t>Avispa Fukuoka</t>
-  </si>
-  <si>
     <t>Yokohama F. Marinos</t>
   </si>
   <si>
@@ -256,27 +256,27 @@
     <t>Tokyo Verdy</t>
   </si>
   <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
     <t>Kashiwa Reysol</t>
   </si>
   <si>
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
     <t>Kyoto Sanga</t>
   </si>
   <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
     <t>Kashima Antlers</t>
   </si>
   <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>['31', '54']</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>['23', '36']</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>['77']</t>
   </si>
   <si>
@@ -307,15 +307,15 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['56', '85']</t>
+  </si>
+  <si>
     <t>['57']</t>
   </si>
   <si>
     <t>['45+2', '62']</t>
   </si>
   <si>
-    <t>['56', '85']</t>
-  </si>
-  <si>
     <t>['60']</t>
   </si>
   <si>
@@ -328,24 +328,24 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['45', '48']</t>
+  </si>
+  <si>
+    <t>['90+11']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['26', '49']</t>
+  </si>
+  <si>
     <t>['10', '78']</t>
   </si>
   <si>
-    <t>['45', '48']</t>
-  </si>
-  <si>
-    <t>['90+11']</t>
-  </si>
-  <si>
-    <t>['12']</t>
-  </si>
-  <si>
-    <t>['26', '49']</t>
-  </si>
-  <si>
-    <t>['15']</t>
-  </si>
-  <si>
     <t>['31', '59', '90+6']</t>
   </si>
   <si>
@@ -358,15 +358,15 @@
     <t>['74', '90+1']</t>
   </si>
   <si>
+    <t>['17', '62']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
-    <t>['17', '62']</t>
-  </si>
-  <si>
-    <t>['20']</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -379,27 +379,27 @@
     <t>['45+4']</t>
   </si>
   <si>
+    <t>['27', '53']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['63', '73']</t>
+  </si>
+  <si>
     <t>['90+5']</t>
   </si>
   <si>
-    <t>['63', '73']</t>
-  </si>
-  <si>
-    <t>['25']</t>
-  </si>
-  <si>
-    <t>['27', '53']</t>
-  </si>
-  <si>
     <t>['82']</t>
   </si>
   <si>
+    <t>['20', '75']</t>
+  </si>
+  <si>
     <t>['72']</t>
   </si>
   <si>
-    <t>['20', '75']</t>
-  </si>
-  <si>
     <t>['90']</t>
   </si>
   <si>
@@ -418,61 +418,61 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['70', '75']</t>
+  </si>
+  <si>
     <t>['50']</t>
   </si>
   <si>
-    <t>['70', '75']</t>
-  </si>
-  <si>
     <t>['73']</t>
   </si>
   <si>
+    <t>['32', '51']</t>
+  </si>
+  <si>
     <t>['87']</t>
   </si>
   <si>
-    <t>['32', '51']</t>
+    <t>['42', '85']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['62']</t>
   </si>
   <si>
     <t>['44']</t>
   </si>
   <si>
-    <t>['13']</t>
-  </si>
-  <si>
-    <t>['65']</t>
-  </si>
-  <si>
-    <t>['62']</t>
-  </si>
-  <si>
-    <t>['42', '85']</t>
-  </si>
-  <si>
     <t>['55']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['28', '90+1']</t>
+  </si>
+  <si>
+    <t>['13', '74']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
-    <t>['85']</t>
-  </si>
-  <si>
-    <t>['28', '90+1']</t>
-  </si>
-  <si>
-    <t>['13', '74']</t>
-  </si>
-  <si>
     <t>['14', '31']</t>
   </si>
   <si>
     <t>['10', '75']</t>
   </si>
   <si>
+    <t>['51', '86']</t>
+  </si>
+  <si>
     <t>['26', '50', '62']</t>
-  </si>
-  <si>
-    <t>['51', '86']</t>
   </si>
   <si>
     <t>['21']</t>
@@ -1078,7 +1078,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -1266,7 +1266,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7778081</v>
+        <v>7778082</v>
       </c>
       <c r="C3" t="s">
         <v>68</v>
@@ -1284,187 +1284,187 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="Q3">
         <v>4</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
+        <v>1.62</v>
+      </c>
+      <c r="U3">
+        <v>2.2</v>
+      </c>
+      <c r="V3">
+        <v>4</v>
+      </c>
+      <c r="W3">
+        <v>1.22</v>
+      </c>
+      <c r="X3">
+        <v>15</v>
+      </c>
+      <c r="Y3">
+        <v>1.03</v>
+      </c>
+      <c r="Z3">
+        <v>3.06</v>
+      </c>
+      <c r="AA3">
+        <v>2.82</v>
+      </c>
+      <c r="AB3">
+        <v>2.57</v>
+      </c>
+      <c r="AC3">
+        <v>1.12</v>
+      </c>
+      <c r="AD3">
+        <v>6</v>
+      </c>
+      <c r="AE3">
+        <v>1.55</v>
+      </c>
+      <c r="AF3">
+        <v>2.2</v>
+      </c>
+      <c r="AG3">
+        <v>2.82</v>
+      </c>
+      <c r="AH3">
+        <v>1.4</v>
+      </c>
+      <c r="AI3">
+        <v>2.25</v>
+      </c>
+      <c r="AJ3">
+        <v>1.57</v>
+      </c>
+      <c r="AK3">
+        <v>1.49</v>
+      </c>
+      <c r="AL3">
+        <v>1.36</v>
+      </c>
+      <c r="AM3">
+        <v>1.37</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>2.33</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>2</v>
+      </c>
+      <c r="AV3">
+        <v>5</v>
+      </c>
+      <c r="AW3">
+        <v>7</v>
+      </c>
+      <c r="AX3">
+        <v>8</v>
+      </c>
+      <c r="AY3">
+        <v>13</v>
+      </c>
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
+        <v>2</v>
+      </c>
+      <c r="BB3">
+        <v>6</v>
+      </c>
+      <c r="BC3">
+        <v>8</v>
+      </c>
+      <c r="BD3">
+        <v>2.08</v>
+      </c>
+      <c r="BE3">
+        <v>6.25</v>
+      </c>
+      <c r="BF3">
+        <v>1.93</v>
+      </c>
+      <c r="BG3">
+        <v>1.55</v>
+      </c>
+      <c r="BH3">
+        <v>2.2</v>
+      </c>
+      <c r="BI3">
+        <v>2</v>
+      </c>
+      <c r="BJ3">
+        <v>1.8</v>
+      </c>
+      <c r="BK3">
+        <v>2.48</v>
+      </c>
+      <c r="BL3">
         <v>1.44</v>
       </c>
-      <c r="U3">
-        <v>2.63</v>
-      </c>
-      <c r="V3">
-        <v>3.25</v>
-      </c>
-      <c r="W3">
-        <v>1.33</v>
-      </c>
-      <c r="X3">
-        <v>9</v>
-      </c>
-      <c r="Y3">
-        <v>1.07</v>
-      </c>
-      <c r="Z3">
-        <v>3.07</v>
-      </c>
-      <c r="AA3">
-        <v>3.65</v>
-      </c>
-      <c r="AB3">
-        <v>2.12</v>
-      </c>
-      <c r="AC3">
-        <v>1.06</v>
-      </c>
-      <c r="AD3">
-        <v>8.5</v>
-      </c>
-      <c r="AE3">
-        <v>1.36</v>
-      </c>
-      <c r="AF3">
-        <v>3.1</v>
-      </c>
-      <c r="AG3">
-        <v>1.98</v>
-      </c>
-      <c r="AH3">
-        <v>1.77</v>
-      </c>
-      <c r="AI3">
-        <v>1.91</v>
-      </c>
-      <c r="AJ3">
-        <v>1.91</v>
-      </c>
-      <c r="AK3">
-        <v>1.65</v>
-      </c>
-      <c r="AL3">
-        <v>1.25</v>
-      </c>
-      <c r="AM3">
-        <v>1.33</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>2</v>
-      </c>
-      <c r="AQ3">
-        <v>1.75</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>4</v>
-      </c>
-      <c r="AV3">
-        <v>6</v>
-      </c>
-      <c r="AW3">
-        <v>6</v>
-      </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>22</v>
-      </c>
-      <c r="BA3">
-        <v>4</v>
-      </c>
-      <c r="BB3">
-        <v>11</v>
-      </c>
-      <c r="BC3">
-        <v>15</v>
-      </c>
-      <c r="BD3">
-        <v>2.23</v>
-      </c>
-      <c r="BE3">
-        <v>6.1</v>
-      </c>
-      <c r="BF3">
-        <v>1.81</v>
-      </c>
-      <c r="BG3">
-        <v>1.52</v>
-      </c>
-      <c r="BH3">
-        <v>2.28</v>
-      </c>
-      <c r="BI3">
-        <v>1.86</v>
-      </c>
-      <c r="BJ3">
-        <v>1.79</v>
-      </c>
-      <c r="BK3">
-        <v>2.38</v>
-      </c>
-      <c r="BL3">
-        <v>1.48</v>
-      </c>
       <c r="BM3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BN3">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="4" spans="1:68">
@@ -1511,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P5" t="s">
         <v>131</v>
@@ -1884,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>7778082</v>
+        <v>7778081</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
@@ -1902,187 +1902,187 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="s">
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="Q6">
         <v>4</v>
       </c>
       <c r="R6">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
+        <v>3.25</v>
+      </c>
+      <c r="W6">
+        <v>1.33</v>
+      </c>
+      <c r="X6">
+        <v>9</v>
+      </c>
+      <c r="Y6">
+        <v>1.07</v>
+      </c>
+      <c r="Z6">
+        <v>3.07</v>
+      </c>
+      <c r="AA6">
+        <v>3.65</v>
+      </c>
+      <c r="AB6">
+        <v>2.12</v>
+      </c>
+      <c r="AC6">
+        <v>1.06</v>
+      </c>
+      <c r="AD6">
+        <v>8.5</v>
+      </c>
+      <c r="AE6">
+        <v>1.36</v>
+      </c>
+      <c r="AF6">
+        <v>3.1</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6">
+        <v>1.77</v>
+      </c>
+      <c r="AI6">
+        <v>1.91</v>
+      </c>
+      <c r="AJ6">
+        <v>1.91</v>
+      </c>
+      <c r="AK6">
+        <v>1.65</v>
+      </c>
+      <c r="AL6">
+        <v>1.25</v>
+      </c>
+      <c r="AM6">
+        <v>1.33</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>2</v>
+      </c>
+      <c r="AQ6">
+        <v>1.75</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
         <v>4</v>
       </c>
-      <c r="W6">
-        <v>1.22</v>
-      </c>
-      <c r="X6">
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>14</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>22</v>
+      </c>
+      <c r="BA6">
+        <v>4</v>
+      </c>
+      <c r="BB6">
+        <v>11</v>
+      </c>
+      <c r="BC6">
         <v>15</v>
       </c>
-      <c r="Y6">
-        <v>1.03</v>
-      </c>
-      <c r="Z6">
-        <v>3.06</v>
-      </c>
-      <c r="AA6">
-        <v>2.82</v>
-      </c>
-      <c r="AB6">
-        <v>2.57</v>
-      </c>
-      <c r="AC6">
-        <v>1.12</v>
-      </c>
-      <c r="AD6">
-        <v>6</v>
-      </c>
-      <c r="AE6">
-        <v>1.55</v>
-      </c>
-      <c r="AF6">
-        <v>2.2</v>
-      </c>
-      <c r="AG6">
-        <v>2.82</v>
-      </c>
-      <c r="AH6">
-        <v>1.4</v>
-      </c>
-      <c r="AI6">
-        <v>2.25</v>
-      </c>
-      <c r="AJ6">
-        <v>1.57</v>
-      </c>
-      <c r="AK6">
-        <v>1.49</v>
-      </c>
-      <c r="AL6">
-        <v>1.36</v>
-      </c>
-      <c r="AM6">
-        <v>1.37</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6">
-        <v>2.33</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>2</v>
-      </c>
-      <c r="AV6">
-        <v>5</v>
-      </c>
-      <c r="AW6">
-        <v>7</v>
-      </c>
-      <c r="AX6">
-        <v>8</v>
-      </c>
-      <c r="AY6">
-        <v>13</v>
-      </c>
-      <c r="AZ6">
-        <v>15</v>
-      </c>
-      <c r="BA6">
-        <v>2</v>
-      </c>
-      <c r="BB6">
-        <v>6</v>
-      </c>
-      <c r="BC6">
-        <v>8</v>
-      </c>
       <c r="BD6">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="BE6">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="BF6">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BH6">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BI6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BJ6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BK6">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BL6">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BM6">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BN6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="7" spans="1:68">
@@ -2314,7 +2314,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2338,7 +2338,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2520,7 +2520,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2932,7 +2932,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P11" t="s">
         <v>133</v>
@@ -3120,7 +3120,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7778084</v>
+        <v>7778088</v>
       </c>
       <c r="C12" t="s">
         <v>68</v>
@@ -3138,7 +3138,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3150,13 +3150,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="s">
         <v>97</v>
@@ -3165,74 +3165,74 @@
         <v>134</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S12">
+        <v>2.75</v>
+      </c>
+      <c r="T12">
+        <v>1.5</v>
+      </c>
+      <c r="U12">
+        <v>2.4</v>
+      </c>
+      <c r="V12">
         <v>3.2</v>
       </c>
-      <c r="T12">
-        <v>1.35</v>
-      </c>
-      <c r="U12">
-        <v>2.95</v>
-      </c>
-      <c r="V12">
-        <v>2.5</v>
-      </c>
       <c r="W12">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="X12">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="Z12">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="AB12">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AD12">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AF12">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AH12">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AI12">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AJ12">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AK12">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AL12">
+        <v>1.31</v>
+      </c>
+      <c r="AM12">
         <v>1.28</v>
       </c>
-      <c r="AM12">
-        <v>1.49</v>
-      </c>
       <c r="AN12">
         <v>0</v>
       </c>
@@ -3240,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3255,70 +3255,70 @@
         <v>0</v>
       </c>
       <c r="AU12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AW12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX12">
         <v>7</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD12">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BE12">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF12">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG12">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="BH12">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="BI12">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="BJ12">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="BK12">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="BL12">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="BM12">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="BN12">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="BO12">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="BP12">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:68">
@@ -3326,7 +3326,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7778086</v>
+        <v>7778084</v>
       </c>
       <c r="C13" t="s">
         <v>68</v>
@@ -3341,10 +3341,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3359,85 +3359,85 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="U13">
+        <v>2.95</v>
+      </c>
+      <c r="V13">
         <v>2.5</v>
       </c>
-      <c r="V13">
-        <v>3.5</v>
-      </c>
       <c r="W13">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="X13">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="Y13">
+        <v>1.11</v>
+      </c>
+      <c r="Z13">
+        <v>2.4</v>
+      </c>
+      <c r="AA13">
+        <v>3.51</v>
+      </c>
+      <c r="AB13">
+        <v>2.72</v>
+      </c>
+      <c r="AC13">
         <v>1.05</v>
       </c>
-      <c r="Z13">
-        <v>1.83</v>
-      </c>
-      <c r="AA13">
-        <v>3.4</v>
-      </c>
-      <c r="AB13">
-        <v>4.33</v>
-      </c>
-      <c r="AC13">
-        <v>1.08</v>
-      </c>
       <c r="AD13">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE13">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AF13">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="AG13">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AH13">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AI13">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AJ13">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM13">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AN13">
         <v>0</v>
@@ -3446,19 +3446,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR13">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AS13">
         <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -3467,64 +3467,64 @@
         <v>3</v>
       </c>
       <c r="AW13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA13">
+        <v>7</v>
+      </c>
+      <c r="BB13">
         <v>4</v>
-      </c>
-      <c r="BB13">
-        <v>7</v>
       </c>
       <c r="BC13">
         <v>11</v>
       </c>
       <c r="BD13">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="BE13">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF13">
+        <v>2</v>
+      </c>
+      <c r="BG13">
+        <v>1.34</v>
+      </c>
+      <c r="BH13">
+        <v>2.85</v>
+      </c>
+      <c r="BI13">
+        <v>1.58</v>
+      </c>
+      <c r="BJ13">
+        <v>2.14</v>
+      </c>
+      <c r="BK13">
+        <v>1.95</v>
+      </c>
+      <c r="BL13">
+        <v>1.71</v>
+      </c>
+      <c r="BM13">
         <v>2.5</v>
       </c>
-      <c r="BG13">
-        <v>1.36</v>
-      </c>
-      <c r="BH13">
-        <v>2.75</v>
-      </c>
-      <c r="BI13">
-        <v>1.62</v>
-      </c>
-      <c r="BJ13">
-        <v>2.08</v>
-      </c>
-      <c r="BK13">
-        <v>2</v>
-      </c>
-      <c r="BL13">
-        <v>1.67</v>
-      </c>
-      <c r="BM13">
-        <v>2.6</v>
-      </c>
       <c r="BN13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP13">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="14" spans="1:68">
@@ -3532,7 +3532,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7778087</v>
+        <v>7778086</v>
       </c>
       <c r="C14" t="s">
         <v>68</v>
@@ -3547,190 +3547,190 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="s">
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q14">
         <v>3</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T14">
+        <v>1.5</v>
+      </c>
+      <c r="U14">
+        <v>2.5</v>
+      </c>
+      <c r="V14">
+        <v>3.5</v>
+      </c>
+      <c r="W14">
+        <v>1.29</v>
+      </c>
+      <c r="X14">
+        <v>11</v>
+      </c>
+      <c r="Y14">
+        <v>1.05</v>
+      </c>
+      <c r="Z14">
+        <v>1.83</v>
+      </c>
+      <c r="AA14">
+        <v>3.4</v>
+      </c>
+      <c r="AB14">
+        <v>4.33</v>
+      </c>
+      <c r="AC14">
+        <v>1.08</v>
+      </c>
+      <c r="AD14">
+        <v>7.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.44</v>
+      </c>
+      <c r="AF14">
+        <v>2.75</v>
+      </c>
+      <c r="AG14">
+        <v>2.28</v>
+      </c>
+      <c r="AH14">
+        <v>1.55</v>
+      </c>
+      <c r="AI14">
+        <v>1.95</v>
+      </c>
+      <c r="AJ14">
+        <v>1.8</v>
+      </c>
+      <c r="AK14">
+        <v>1.3</v>
+      </c>
+      <c r="AL14">
+        <v>1.3</v>
+      </c>
+      <c r="AM14">
+        <v>1.65</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.5</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>1.76</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>1.76</v>
+      </c>
+      <c r="AU14">
+        <v>4</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>5</v>
+      </c>
+      <c r="AX14">
+        <v>9</v>
+      </c>
+      <c r="AY14">
+        <v>9</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14">
+        <v>4</v>
+      </c>
+      <c r="BB14">
+        <v>7</v>
+      </c>
+      <c r="BC14">
+        <v>11</v>
+      </c>
+      <c r="BD14">
+        <v>1.67</v>
+      </c>
+      <c r="BE14">
+        <v>6.25</v>
+      </c>
+      <c r="BF14">
+        <v>2.5</v>
+      </c>
+      <c r="BG14">
+        <v>1.36</v>
+      </c>
+      <c r="BH14">
+        <v>2.75</v>
+      </c>
+      <c r="BI14">
+        <v>1.62</v>
+      </c>
+      <c r="BJ14">
+        <v>2.08</v>
+      </c>
+      <c r="BK14">
+        <v>2</v>
+      </c>
+      <c r="BL14">
+        <v>1.67</v>
+      </c>
+      <c r="BM14">
+        <v>2.6</v>
+      </c>
+      <c r="BN14">
         <v>1.4</v>
       </c>
-      <c r="U14">
-        <v>2.75</v>
-      </c>
-      <c r="V14">
-        <v>2.75</v>
-      </c>
-      <c r="W14">
-        <v>1.4</v>
-      </c>
-      <c r="X14">
-        <v>8</v>
-      </c>
-      <c r="Y14">
-        <v>1.08</v>
-      </c>
-      <c r="Z14">
-        <v>2.62</v>
-      </c>
-      <c r="AA14">
-        <v>3.27</v>
-      </c>
-      <c r="AB14">
-        <v>2.62</v>
-      </c>
-      <c r="AC14">
-        <v>1.06</v>
-      </c>
-      <c r="AD14">
-        <v>8.5</v>
-      </c>
-      <c r="AE14">
-        <v>1.3</v>
-      </c>
-      <c r="AF14">
+      <c r="BO14">
         <v>3.4</v>
       </c>
-      <c r="AG14">
-        <v>1.83</v>
-      </c>
-      <c r="AH14">
-        <v>1.91</v>
-      </c>
-      <c r="AI14">
-        <v>1.67</v>
-      </c>
-      <c r="AJ14">
-        <v>2.1</v>
-      </c>
-      <c r="AK14">
-        <v>1.36</v>
-      </c>
-      <c r="AL14">
-        <v>1.25</v>
-      </c>
-      <c r="AM14">
-        <v>1.57</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>1</v>
-      </c>
-      <c r="AP14">
-        <v>1.33</v>
-      </c>
-      <c r="AQ14">
-        <v>0.25</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>1.77</v>
-      </c>
-      <c r="AT14">
-        <v>1.77</v>
-      </c>
-      <c r="AU14">
-        <v>3</v>
-      </c>
-      <c r="AV14">
-        <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>12</v>
-      </c>
-      <c r="AX14">
-        <v>2</v>
-      </c>
-      <c r="AY14">
-        <v>16</v>
-      </c>
-      <c r="AZ14">
-        <v>7</v>
-      </c>
-      <c r="BA14">
-        <v>7</v>
-      </c>
-      <c r="BB14">
-        <v>6</v>
-      </c>
-      <c r="BC14">
-        <v>13</v>
-      </c>
-      <c r="BD14">
-        <v>1.84</v>
-      </c>
-      <c r="BE14">
-        <v>6.4</v>
-      </c>
-      <c r="BF14">
-        <v>2.18</v>
-      </c>
-      <c r="BG14">
-        <v>1.37</v>
-      </c>
-      <c r="BH14">
-        <v>2.7</v>
-      </c>
-      <c r="BI14">
-        <v>1.64</v>
-      </c>
-      <c r="BJ14">
-        <v>2.04</v>
-      </c>
-      <c r="BK14">
-        <v>2.04</v>
-      </c>
-      <c r="BL14">
-        <v>1.64</v>
-      </c>
-      <c r="BM14">
-        <v>2.65</v>
-      </c>
-      <c r="BN14">
-        <v>1.38</v>
-      </c>
-      <c r="BO14">
-        <v>3.45</v>
-      </c>
       <c r="BP14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="15" spans="1:68">
@@ -3738,7 +3738,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>7778088</v>
+        <v>7778087</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
@@ -3756,187 +3756,187 @@
         <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>2</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15" t="s">
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="Q15">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
+        <v>3.6</v>
+      </c>
+      <c r="T15">
+        <v>1.4</v>
+      </c>
+      <c r="U15">
         <v>2.75</v>
       </c>
-      <c r="T15">
-        <v>1.5</v>
-      </c>
-      <c r="U15">
-        <v>2.4</v>
-      </c>
       <c r="V15">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="W15">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Z15">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA15">
+        <v>3.27</v>
+      </c>
+      <c r="AB15">
+        <v>2.62</v>
+      </c>
+      <c r="AC15">
+        <v>1.06</v>
+      </c>
+      <c r="AD15">
+        <v>8.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.3</v>
+      </c>
+      <c r="AF15">
         <v>3.4</v>
       </c>
-      <c r="AB15">
-        <v>1.95</v>
-      </c>
-      <c r="AC15">
-        <v>1.08</v>
-      </c>
-      <c r="AD15">
-        <v>7.5</v>
-      </c>
-      <c r="AE15">
-        <v>1.41</v>
-      </c>
-      <c r="AF15">
-        <v>2.65</v>
-      </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH15">
+        <v>1.91</v>
+      </c>
+      <c r="AI15">
+        <v>1.67</v>
+      </c>
+      <c r="AJ15">
+        <v>2.1</v>
+      </c>
+      <c r="AK15">
+        <v>1.36</v>
+      </c>
+      <c r="AL15">
+        <v>1.25</v>
+      </c>
+      <c r="AM15">
         <v>1.57</v>
       </c>
-      <c r="AI15">
-        <v>1.97</v>
-      </c>
-      <c r="AJ15">
-        <v>1.76</v>
-      </c>
-      <c r="AK15">
-        <v>1.68</v>
-      </c>
-      <c r="AL15">
-        <v>1.31</v>
-      </c>
-      <c r="AM15">
-        <v>1.28</v>
-      </c>
       <c r="AN15">
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>0</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU15">
+        <v>3</v>
+      </c>
+      <c r="AV15">
         <v>5</v>
       </c>
-      <c r="AV15">
-        <v>9</v>
-      </c>
       <c r="AW15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX15">
+        <v>2</v>
+      </c>
+      <c r="AY15">
+        <v>16</v>
+      </c>
+      <c r="AZ15">
         <v>7</v>
       </c>
-      <c r="AY15">
-        <v>11</v>
-      </c>
-      <c r="AZ15">
-        <v>18</v>
-      </c>
       <c r="BA15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB15">
         <v>6</v>
       </c>
       <c r="BC15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD15">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="BE15">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="BG15">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="BH15">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="BI15">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="BJ15">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="BK15">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="BL15">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="BM15">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="BN15">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="BO15">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP15">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16" spans="1:68">
@@ -4150,7 +4150,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>7778090</v>
+        <v>7778091</v>
       </c>
       <c r="C17" t="s">
         <v>68</v>
@@ -4165,190 +4165,190 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17">
         <v>3</v>
       </c>
       <c r="O17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P17" t="s">
         <v>137</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R17">
+        <v>2.24</v>
+      </c>
+      <c r="S17">
+        <v>4</v>
+      </c>
+      <c r="T17">
+        <v>1.37</v>
+      </c>
+      <c r="U17">
+        <v>2.9</v>
+      </c>
+      <c r="V17">
+        <v>2.55</v>
+      </c>
+      <c r="W17">
+        <v>1.45</v>
+      </c>
+      <c r="X17">
+        <v>6.1</v>
+      </c>
+      <c r="Y17">
+        <v>1.1</v>
+      </c>
+      <c r="Z17">
+        <v>2.01</v>
+      </c>
+      <c r="AA17">
+        <v>3.52</v>
+      </c>
+      <c r="AB17">
+        <v>3.47</v>
+      </c>
+      <c r="AC17">
+        <v>1.05</v>
+      </c>
+      <c r="AD17">
+        <v>9.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.25</v>
+      </c>
+      <c r="AF17">
+        <v>3.55</v>
+      </c>
+      <c r="AG17">
+        <v>1.8</v>
+      </c>
+      <c r="AH17">
+        <v>1.94</v>
+      </c>
+      <c r="AI17">
+        <v>1.67</v>
+      </c>
+      <c r="AJ17">
+        <v>2.08</v>
+      </c>
+      <c r="AK17">
+        <v>1.3</v>
+      </c>
+      <c r="AL17">
+        <v>1.27</v>
+      </c>
+      <c r="AM17">
+        <v>1.73</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0.5</v>
+      </c>
+      <c r="AQ17">
+        <v>1.67</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>5</v>
+      </c>
+      <c r="AV17">
+        <v>8</v>
+      </c>
+      <c r="AW17">
+        <v>9</v>
+      </c>
+      <c r="AX17">
+        <v>7</v>
+      </c>
+      <c r="AY17">
+        <v>19</v>
+      </c>
+      <c r="AZ17">
+        <v>19</v>
+      </c>
+      <c r="BA17">
+        <v>7</v>
+      </c>
+      <c r="BB17">
+        <v>7</v>
+      </c>
+      <c r="BC17">
+        <v>14</v>
+      </c>
+      <c r="BD17">
+        <v>1.73</v>
+      </c>
+      <c r="BE17">
+        <v>6.4</v>
+      </c>
+      <c r="BF17">
+        <v>2.33</v>
+      </c>
+      <c r="BG17">
+        <v>1.35</v>
+      </c>
+      <c r="BH17">
+        <v>2.8</v>
+      </c>
+      <c r="BI17">
+        <v>1.58</v>
+      </c>
+      <c r="BJ17">
+        <v>2.12</v>
+      </c>
+      <c r="BK17">
         <v>1.97</v>
       </c>
-      <c r="S17">
-        <v>4.9</v>
-      </c>
-      <c r="T17">
-        <v>1.56</v>
-      </c>
-      <c r="U17">
-        <v>2.3</v>
-      </c>
-      <c r="V17">
-        <v>3.5</v>
-      </c>
-      <c r="W17">
-        <v>1.27</v>
-      </c>
-      <c r="X17">
-        <v>11</v>
-      </c>
-      <c r="Y17">
-        <v>1.02</v>
-      </c>
-      <c r="Z17">
-        <v>1.97</v>
-      </c>
-      <c r="AA17">
-        <v>3.12</v>
-      </c>
-      <c r="AB17">
-        <v>4.1</v>
-      </c>
-      <c r="AC17">
-        <v>1.1</v>
-      </c>
-      <c r="AD17">
-        <v>6.5</v>
-      </c>
-      <c r="AE17">
-        <v>1.58</v>
-      </c>
-      <c r="AF17">
-        <v>2.39</v>
-      </c>
-      <c r="AG17">
-        <v>2.37</v>
-      </c>
-      <c r="AH17">
-        <v>1.48</v>
-      </c>
-      <c r="AI17">
-        <v>2.15</v>
-      </c>
-      <c r="AJ17">
-        <v>1.63</v>
-      </c>
-      <c r="AK17">
-        <v>1.23</v>
-      </c>
-      <c r="AL17">
-        <v>1.32</v>
-      </c>
-      <c r="AM17">
-        <v>1.75</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>2</v>
-      </c>
-      <c r="AQ17">
-        <v>2</v>
-      </c>
-      <c r="AR17">
-        <v>2.07</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>2.07</v>
-      </c>
-      <c r="AU17">
-        <v>3</v>
-      </c>
-      <c r="AV17">
-        <v>7</v>
-      </c>
-      <c r="AW17">
-        <v>5</v>
-      </c>
-      <c r="AX17">
-        <v>11</v>
-      </c>
-      <c r="AY17">
-        <v>8</v>
-      </c>
-      <c r="AZ17">
-        <v>21</v>
-      </c>
-      <c r="BA17">
-        <v>3</v>
-      </c>
-      <c r="BB17">
-        <v>8</v>
-      </c>
-      <c r="BC17">
-        <v>11</v>
-      </c>
-      <c r="BD17">
-        <v>1.58</v>
-      </c>
-      <c r="BE17">
-        <v>6.75</v>
-      </c>
-      <c r="BF17">
+      <c r="BL17">
+        <v>1.7</v>
+      </c>
+      <c r="BM17">
         <v>2.55</v>
       </c>
-      <c r="BG17">
-        <v>1.3</v>
-      </c>
-      <c r="BH17">
-        <v>3.05</v>
-      </c>
-      <c r="BI17">
-        <v>1.53</v>
-      </c>
-      <c r="BJ17">
-        <v>2.25</v>
-      </c>
-      <c r="BK17">
-        <v>1.85</v>
-      </c>
-      <c r="BL17">
-        <v>1.79</v>
-      </c>
-      <c r="BM17">
-        <v>2.33</v>
-      </c>
       <c r="BN17">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO17">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BP17">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="18" spans="1:68">
@@ -4356,7 +4356,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>7778083</v>
+        <v>7778090</v>
       </c>
       <c r="C18" t="s">
         <v>68</v>
@@ -4371,103 +4371,103 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
         <v>3</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>3</v>
-      </c>
-      <c r="L18">
-        <v>4</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>4</v>
-      </c>
       <c r="O18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="Q18">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="S18">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T18">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="W18">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X18">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Y18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z18">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AA18">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AB18">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="AC18">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD18">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE18">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AF18">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AG18">
+        <v>2.37</v>
+      </c>
+      <c r="AH18">
+        <v>1.48</v>
+      </c>
+      <c r="AI18">
         <v>2.15</v>
       </c>
-      <c r="AH18">
-        <v>1.57</v>
-      </c>
-      <c r="AI18">
-        <v>1.94</v>
-      </c>
       <c r="AJ18">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AK18">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL18">
         <v>1.32</v>
       </c>
       <c r="AM18">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AN18">
         <v>0</v>
@@ -4476,85 +4476,85 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS18">
         <v>0</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AV18">
+        <v>7</v>
+      </c>
+      <c r="AW18">
+        <v>5</v>
+      </c>
+      <c r="AX18">
+        <v>11</v>
+      </c>
+      <c r="AY18">
+        <v>8</v>
+      </c>
+      <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
         <v>3</v>
       </c>
-      <c r="AW18">
-        <v>6</v>
-      </c>
-      <c r="AX18">
+      <c r="BB18">
+        <v>8</v>
+      </c>
+      <c r="BC18">
+        <v>11</v>
+      </c>
+      <c r="BD18">
+        <v>1.58</v>
+      </c>
+      <c r="BE18">
+        <v>6.75</v>
+      </c>
+      <c r="BF18">
+        <v>2.55</v>
+      </c>
+      <c r="BG18">
+        <v>1.3</v>
+      </c>
+      <c r="BH18">
+        <v>3.05</v>
+      </c>
+      <c r="BI18">
+        <v>1.53</v>
+      </c>
+      <c r="BJ18">
+        <v>2.25</v>
+      </c>
+      <c r="BK18">
+        <v>1.85</v>
+      </c>
+      <c r="BL18">
+        <v>1.79</v>
+      </c>
+      <c r="BM18">
+        <v>2.33</v>
+      </c>
+      <c r="BN18">
+        <v>1.5</v>
+      </c>
+      <c r="BO18">
         <v>3</v>
       </c>
-      <c r="AY18">
-        <v>19</v>
-      </c>
-      <c r="AZ18">
-        <v>9</v>
-      </c>
-      <c r="BA18">
-        <v>6</v>
-      </c>
-      <c r="BB18">
-        <v>2</v>
-      </c>
-      <c r="BC18">
-        <v>8</v>
-      </c>
-      <c r="BD18">
-        <v>1.71</v>
-      </c>
-      <c r="BE18">
-        <v>6.4</v>
-      </c>
-      <c r="BF18">
-        <v>2.4</v>
-      </c>
-      <c r="BG18">
-        <v>1.46</v>
-      </c>
-      <c r="BH18">
-        <v>2.43</v>
-      </c>
-      <c r="BI18">
-        <v>1.77</v>
-      </c>
-      <c r="BJ18">
-        <v>1.88</v>
-      </c>
-      <c r="BK18">
-        <v>2.25</v>
-      </c>
-      <c r="BL18">
-        <v>1.53</v>
-      </c>
-      <c r="BM18">
-        <v>2.95</v>
-      </c>
-      <c r="BN18">
-        <v>1.32</v>
-      </c>
-      <c r="BO18">
-        <v>3.95</v>
-      </c>
       <c r="BP18">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" spans="1:68">
@@ -4601,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P19" t="s">
         <v>125</v>
@@ -4768,7 +4768,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>7778091</v>
+        <v>7778083</v>
       </c>
       <c r="C20" t="s">
         <v>68</v>
@@ -4786,187 +4786,187 @@
         <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20" t="s">
+        <v>102</v>
+      </c>
+      <c r="P20" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q20">
+        <v>2.8</v>
+      </c>
+      <c r="R20">
+        <v>2.03</v>
+      </c>
+      <c r="S20">
+        <v>4.2</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>2.45</v>
+      </c>
+      <c r="V20">
+        <v>3.15</v>
+      </c>
+      <c r="W20">
+        <v>1.31</v>
+      </c>
+      <c r="X20">
+        <v>8.4</v>
+      </c>
+      <c r="Y20">
+        <v>1.01</v>
+      </c>
+      <c r="Z20">
+        <v>2.11</v>
+      </c>
+      <c r="AA20">
+        <v>3.14</v>
+      </c>
+      <c r="AB20">
+        <v>3.61</v>
+      </c>
+      <c r="AC20">
+        <v>1.08</v>
+      </c>
+      <c r="AD20">
+        <v>7.5</v>
+      </c>
+      <c r="AE20">
+        <v>1.4</v>
+      </c>
+      <c r="AF20">
+        <v>2.7</v>
+      </c>
+      <c r="AG20">
+        <v>2.15</v>
+      </c>
+      <c r="AH20">
+        <v>1.57</v>
+      </c>
+      <c r="AI20">
+        <v>1.94</v>
+      </c>
+      <c r="AJ20">
+        <v>1.78</v>
+      </c>
+      <c r="AK20">
+        <v>1.28</v>
+      </c>
+      <c r="AL20">
+        <v>1.32</v>
+      </c>
+      <c r="AM20">
+        <v>1.65</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>2.5</v>
+      </c>
+      <c r="AQ20">
+        <v>1.33</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>10</v>
+      </c>
+      <c r="AV20">
         <v>3</v>
       </c>
-      <c r="O20" t="s">
-        <v>97</v>
-      </c>
-      <c r="P20" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q20">
-        <v>2.55</v>
-      </c>
-      <c r="R20">
-        <v>2.24</v>
-      </c>
-      <c r="S20">
-        <v>4</v>
-      </c>
-      <c r="T20">
-        <v>1.37</v>
-      </c>
-      <c r="U20">
-        <v>2.9</v>
-      </c>
-      <c r="V20">
-        <v>2.55</v>
-      </c>
-      <c r="W20">
-        <v>1.45</v>
-      </c>
-      <c r="X20">
-        <v>6.1</v>
-      </c>
-      <c r="Y20">
-        <v>1.1</v>
-      </c>
-      <c r="Z20">
-        <v>2.01</v>
-      </c>
-      <c r="AA20">
-        <v>3.52</v>
-      </c>
-      <c r="AB20">
-        <v>3.47</v>
-      </c>
-      <c r="AC20">
-        <v>1.05</v>
-      </c>
-      <c r="AD20">
-        <v>9.5</v>
-      </c>
-      <c r="AE20">
-        <v>1.25</v>
-      </c>
-      <c r="AF20">
-        <v>3.55</v>
-      </c>
-      <c r="AG20">
-        <v>1.8</v>
-      </c>
-      <c r="AH20">
-        <v>1.94</v>
-      </c>
-      <c r="AI20">
-        <v>1.67</v>
-      </c>
-      <c r="AJ20">
-        <v>2.08</v>
-      </c>
-      <c r="AK20">
-        <v>1.3</v>
-      </c>
-      <c r="AL20">
-        <v>1.27</v>
-      </c>
-      <c r="AM20">
-        <v>1.73</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0.5</v>
-      </c>
-      <c r="AQ20">
-        <v>1.67</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>5</v>
-      </c>
-      <c r="AV20">
-        <v>8</v>
-      </c>
       <c r="AW20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY20">
         <v>19</v>
       </c>
       <c r="AZ20">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BA20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BC20">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD20">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="BE20">
         <v>6.4</v>
       </c>
       <c r="BF20">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BG20">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="BH20">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="BI20">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BJ20">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="BK20">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="BL20">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BM20">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="BN20">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="BO20">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP20">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="21" spans="1:68">
@@ -5016,7 +5016,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21">
         <v>2.06</v>
@@ -5180,7 +5180,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>7778093</v>
+        <v>7778102</v>
       </c>
       <c r="C22" t="s">
         <v>68</v>
@@ -5195,10 +5195,10 @@
         <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -5210,10 +5210,10 @@
         <v>2</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22">
         <v>3</v>
@@ -5225,160 +5225,160 @@
         <v>139</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="T22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U22">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="W22">
+        <v>1.33</v>
+      </c>
+      <c r="X22">
+        <v>8.25</v>
+      </c>
+      <c r="Y22">
+        <v>1.06</v>
+      </c>
+      <c r="Z22">
+        <v>3.25</v>
+      </c>
+      <c r="AA22">
+        <v>3.14</v>
+      </c>
+      <c r="AB22">
+        <v>2.25</v>
+      </c>
+      <c r="AC22">
+        <v>1.02</v>
+      </c>
+      <c r="AD22">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE22">
         <v>1.36</v>
       </c>
-      <c r="X22">
-        <v>7.75</v>
-      </c>
-      <c r="Y22">
-        <v>1.07</v>
-      </c>
-      <c r="Z22">
-        <v>2.01</v>
-      </c>
-      <c r="AA22">
-        <v>3.32</v>
-      </c>
-      <c r="AB22">
-        <v>3.69</v>
-      </c>
-      <c r="AC22">
-        <v>1.01</v>
-      </c>
-      <c r="AD22">
-        <v>8.4</v>
-      </c>
-      <c r="AE22">
-        <v>1.35</v>
-      </c>
       <c r="AF22">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH22">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AI22">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AJ22">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL22">
         <v>1.32</v>
       </c>
       <c r="AM22">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AN22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP22">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>0.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR22">
-        <v>2.08</v>
+        <v>0.91</v>
       </c>
       <c r="AS22">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AT22">
-        <v>3.47</v>
+        <v>2.06</v>
       </c>
       <c r="AU22">
         <v>5</v>
       </c>
       <c r="AV22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY22">
         <v>15</v>
       </c>
       <c r="AZ22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD22">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="BE22">
         <v>6.4</v>
       </c>
       <c r="BF22">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="BG22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BH22">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BI22">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BJ22">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BK22">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BL22">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BM22">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BN22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BO22">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BP22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23" spans="1:68">
@@ -5401,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
         <v>70</v>
@@ -5428,7 +5428,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23">
         <v>4</v>
@@ -5813,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
         <v>87</v>
@@ -6210,7 +6210,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7778102</v>
+        <v>7778093</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -6225,10 +6225,10 @@
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -6240,10 +6240,10 @@
         <v>2</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -6255,160 +6255,160 @@
         <v>143</v>
       </c>
       <c r="Q27">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="R27">
         <v>2</v>
       </c>
       <c r="S27">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="W27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X27">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="Y27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>3.25</v>
+        <v>2.01</v>
       </c>
       <c r="AA27">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="AB27">
-        <v>2.25</v>
+        <v>3.69</v>
       </c>
       <c r="AC27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD27">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AE27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF27">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH27">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI27">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK27">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL27">
         <v>1.32</v>
       </c>
       <c r="AM27">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AQ27">
-        <v>1.67</v>
+        <v>0.25</v>
       </c>
       <c r="AR27">
-        <v>0.91</v>
+        <v>2.08</v>
       </c>
       <c r="AS27">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AT27">
-        <v>2.06</v>
+        <v>3.47</v>
       </c>
       <c r="AU27">
         <v>5</v>
       </c>
       <c r="AV27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY27">
         <v>15</v>
       </c>
       <c r="AZ27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BB27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD27">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="BE27">
         <v>6.4</v>
       </c>
       <c r="BF27">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="BG27">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BH27">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BI27">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BJ27">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BK27">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BL27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BM27">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BN27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO27">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BP27">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="28" spans="1:68">
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P28" t="s">
         <v>140</v>
@@ -6640,7 +6640,7 @@
         <v>85</v>
       </c>
       <c r="H29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -6843,10 +6843,10 @@
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -7073,10 +7073,10 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q31">
         <v>2.6</v>
@@ -7461,7 +7461,7 @@
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s">
         <v>85</v>
@@ -7488,7 +7488,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33">
         <v>2.6</v>
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P34" t="s">
         <v>103</v>
@@ -7876,7 +7876,7 @@
         <v>72</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P35" t="s">
         <v>133</v>
@@ -8064,7 +8064,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>7778111</v>
+        <v>7778105</v>
       </c>
       <c r="C36" t="s">
         <v>68</v>
@@ -8079,10 +8079,10 @@
         <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -8094,175 +8094,175 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="P36" t="s">
         <v>145</v>
       </c>
       <c r="Q36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S36">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T36">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U36">
+        <v>2.25</v>
+      </c>
+      <c r="V36">
+        <v>3.75</v>
+      </c>
+      <c r="W36">
+        <v>1.25</v>
+      </c>
+      <c r="X36">
+        <v>13</v>
+      </c>
+      <c r="Y36">
+        <v>1.04</v>
+      </c>
+      <c r="Z36">
+        <v>2.72</v>
+      </c>
+      <c r="AA36">
+        <v>3.09</v>
+      </c>
+      <c r="AB36">
+        <v>2.64</v>
+      </c>
+      <c r="AC36">
+        <v>1.1</v>
+      </c>
+      <c r="AD36">
+        <v>6.5</v>
+      </c>
+      <c r="AE36">
+        <v>1.48</v>
+      </c>
+      <c r="AF36">
+        <v>2.37</v>
+      </c>
+      <c r="AG36">
+        <v>2.63</v>
+      </c>
+      <c r="AH36">
+        <v>1.45</v>
+      </c>
+      <c r="AI36">
+        <v>2.1</v>
+      </c>
+      <c r="AJ36">
+        <v>1.67</v>
+      </c>
+      <c r="AK36">
+        <v>1.34</v>
+      </c>
+      <c r="AL36">
+        <v>1.36</v>
+      </c>
+      <c r="AM36">
+        <v>1.55</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1</v>
+      </c>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
+        <v>1.08</v>
+      </c>
+      <c r="AS36">
+        <v>0.71</v>
+      </c>
+      <c r="AT36">
+        <v>1.79</v>
+      </c>
+      <c r="AU36">
+        <v>4</v>
+      </c>
+      <c r="AV36">
+        <v>5</v>
+      </c>
+      <c r="AW36">
+        <v>9</v>
+      </c>
+      <c r="AX36">
+        <v>17</v>
+      </c>
+      <c r="AY36">
+        <v>17</v>
+      </c>
+      <c r="AZ36">
+        <v>32</v>
+      </c>
+      <c r="BA36">
+        <v>6</v>
+      </c>
+      <c r="BB36">
+        <v>14</v>
+      </c>
+      <c r="BC36">
+        <v>20</v>
+      </c>
+      <c r="BD36">
+        <v>1.59</v>
+      </c>
+      <c r="BE36">
+        <v>6.85</v>
+      </c>
+      <c r="BF36">
+        <v>3.14</v>
+      </c>
+      <c r="BG36">
+        <v>1.27</v>
+      </c>
+      <c r="BH36">
+        <v>3.14</v>
+      </c>
+      <c r="BI36">
+        <v>1.52</v>
+      </c>
+      <c r="BJ36">
+        <v>2.3</v>
+      </c>
+      <c r="BK36">
+        <v>1.95</v>
+      </c>
+      <c r="BL36">
+        <v>1.77</v>
+      </c>
+      <c r="BM36">
         <v>2.5</v>
       </c>
-      <c r="V36">
-        <v>3.5</v>
-      </c>
-      <c r="W36">
-        <v>1.29</v>
-      </c>
-      <c r="X36">
-        <v>11</v>
-      </c>
-      <c r="Y36">
-        <v>1.05</v>
-      </c>
-      <c r="Z36">
-        <v>2.95</v>
-      </c>
-      <c r="AA36">
-        <v>2.95</v>
-      </c>
-      <c r="AB36">
-        <v>2.55</v>
-      </c>
-      <c r="AC36">
-        <v>1.09</v>
-      </c>
-      <c r="AD36">
-        <v>7</v>
-      </c>
-      <c r="AE36">
-        <v>1.5</v>
-      </c>
-      <c r="AF36">
-        <v>2.58</v>
-      </c>
-      <c r="AG36">
-        <v>2.15</v>
-      </c>
-      <c r="AH36">
-        <v>1.57</v>
-      </c>
-      <c r="AI36">
-        <v>1.95</v>
-      </c>
-      <c r="AJ36">
-        <v>1.8</v>
-      </c>
-      <c r="AK36">
-        <v>1.52</v>
-      </c>
-      <c r="AL36">
-        <v>1.34</v>
-      </c>
-      <c r="AM36">
-        <v>1.38</v>
-      </c>
-      <c r="AN36">
-        <v>3</v>
-      </c>
-      <c r="AO36">
-        <v>3</v>
-      </c>
-      <c r="AP36">
-        <v>2</v>
-      </c>
-      <c r="AQ36">
-        <v>1.33</v>
-      </c>
-      <c r="AR36">
-        <v>1.59</v>
-      </c>
-      <c r="AS36">
-        <v>1.08</v>
-      </c>
-      <c r="AT36">
-        <v>2.67</v>
-      </c>
-      <c r="AU36">
-        <v>7</v>
-      </c>
-      <c r="AV36">
-        <v>4</v>
-      </c>
-      <c r="AW36">
-        <v>8</v>
-      </c>
-      <c r="AX36">
-        <v>10</v>
-      </c>
-      <c r="AY36">
-        <v>16</v>
-      </c>
-      <c r="AZ36">
-        <v>17</v>
-      </c>
-      <c r="BA36">
-        <v>7</v>
-      </c>
-      <c r="BB36">
-        <v>8</v>
-      </c>
-      <c r="BC36">
-        <v>15</v>
-      </c>
-      <c r="BD36">
-        <v>2.04</v>
-      </c>
-      <c r="BE36">
-        <v>6.65</v>
-      </c>
-      <c r="BF36">
-        <v>2.21</v>
-      </c>
-      <c r="BG36">
-        <v>1.49</v>
-      </c>
-      <c r="BH36">
-        <v>2.33</v>
-      </c>
-      <c r="BI36">
-        <v>1.85</v>
-      </c>
-      <c r="BJ36">
-        <v>1.8</v>
-      </c>
-      <c r="BK36">
-        <v>2.38</v>
-      </c>
-      <c r="BL36">
-        <v>1.48</v>
-      </c>
-      <c r="BM36">
-        <v>3.1</v>
-      </c>
       <c r="BN36">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="BO36">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="BP36">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="37" spans="1:68">
@@ -8270,7 +8270,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>7778105</v>
+        <v>7778108</v>
       </c>
       <c r="C37" t="s">
         <v>68</v>
@@ -8285,109 +8285,109 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="P37" t="s">
         <v>146</v>
       </c>
       <c r="Q37">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
         <v>3.75</v>
       </c>
       <c r="T37">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="U37">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V37">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="W37">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z37">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="AA37">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="AB37">
-        <v>2.64</v>
+        <v>3.33</v>
       </c>
       <c r="AC37">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AD37">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE37">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AF37">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="AG37">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AH37">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AI37">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AJ37">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK37">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AM37">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AN37">
         <v>0</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP37">
         <v>1</v>
@@ -8396,79 +8396,79 @@
         <v>1</v>
       </c>
       <c r="AR37">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>0.71</v>
+        <v>1.59</v>
       </c>
       <c r="AT37">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AU37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV37">
         <v>5</v>
       </c>
       <c r="AW37">
+        <v>12</v>
+      </c>
+      <c r="AX37">
+        <v>6</v>
+      </c>
+      <c r="AY37">
+        <v>18</v>
+      </c>
+      <c r="AZ37">
+        <v>12</v>
+      </c>
+      <c r="BA37">
         <v>9</v>
       </c>
-      <c r="AX37">
-        <v>17</v>
-      </c>
-      <c r="AY37">
-        <v>17</v>
-      </c>
-      <c r="AZ37">
-        <v>32</v>
-      </c>
-      <c r="BA37">
-        <v>6</v>
-      </c>
       <c r="BB37">
+        <v>5</v>
+      </c>
+      <c r="BC37">
         <v>14</v>
       </c>
-      <c r="BC37">
-        <v>20</v>
-      </c>
       <c r="BD37">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="BE37">
-        <v>6.85</v>
+        <v>6.65</v>
       </c>
       <c r="BF37">
+        <v>2.79</v>
+      </c>
+      <c r="BG37">
+        <v>1.24</v>
+      </c>
+      <c r="BH37">
+        <v>3.34</v>
+      </c>
+      <c r="BI37">
+        <v>1.48</v>
+      </c>
+      <c r="BJ37">
+        <v>2.4</v>
+      </c>
+      <c r="BK37">
+        <v>1.85</v>
+      </c>
+      <c r="BL37">
+        <v>1.85</v>
+      </c>
+      <c r="BM37">
+        <v>2.38</v>
+      </c>
+      <c r="BN37">
+        <v>1.49</v>
+      </c>
+      <c r="BO37">
         <v>3.14</v>
       </c>
-      <c r="BG37">
+      <c r="BP37">
         <v>1.27</v>
-      </c>
-      <c r="BH37">
-        <v>3.14</v>
-      </c>
-      <c r="BI37">
-        <v>1.52</v>
-      </c>
-      <c r="BJ37">
-        <v>2.3</v>
-      </c>
-      <c r="BK37">
-        <v>1.95</v>
-      </c>
-      <c r="BL37">
-        <v>1.77</v>
-      </c>
-      <c r="BM37">
-        <v>2.5</v>
-      </c>
-      <c r="BN37">
-        <v>1.44</v>
-      </c>
-      <c r="BO37">
-        <v>3.34</v>
-      </c>
-      <c r="BP37">
-        <v>1.24</v>
       </c>
     </row>
     <row r="38" spans="1:68">
@@ -8476,7 +8476,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>7778108</v>
+        <v>7778109</v>
       </c>
       <c r="C38" t="s">
         <v>68</v>
@@ -8491,10 +8491,10 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -8506,13 +8506,13 @@
         <v>2</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O38" t="s">
         <v>115</v>
@@ -8521,160 +8521,160 @@
         <v>147</v>
       </c>
       <c r="Q38">
+        <v>3.75</v>
+      </c>
+      <c r="R38">
+        <v>1.91</v>
+      </c>
+      <c r="S38">
+        <v>3.4</v>
+      </c>
+      <c r="T38">
+        <v>1.57</v>
+      </c>
+      <c r="U38">
+        <v>2.25</v>
+      </c>
+      <c r="V38">
+        <v>3.75</v>
+      </c>
+      <c r="W38">
+        <v>1.25</v>
+      </c>
+      <c r="X38">
+        <v>13</v>
+      </c>
+      <c r="Y38">
+        <v>1.04</v>
+      </c>
+      <c r="Z38">
         <v>3.1</v>
       </c>
-      <c r="R38">
-        <v>2.05</v>
-      </c>
-      <c r="S38">
-        <v>3.75</v>
-      </c>
-      <c r="T38">
-        <v>1.44</v>
-      </c>
-      <c r="U38">
-        <v>2.63</v>
-      </c>
-      <c r="V38">
+      <c r="AA38">
+        <v>2.86</v>
+      </c>
+      <c r="AB38">
+        <v>2.51</v>
+      </c>
+      <c r="AC38">
+        <v>1.12</v>
+      </c>
+      <c r="AD38">
+        <v>5.75</v>
+      </c>
+      <c r="AE38">
+        <v>1.48</v>
+      </c>
+      <c r="AF38">
+        <v>2.37</v>
+      </c>
+      <c r="AG38">
+        <v>2.74</v>
+      </c>
+      <c r="AH38">
+        <v>1.42</v>
+      </c>
+      <c r="AI38">
+        <v>2.1</v>
+      </c>
+      <c r="AJ38">
+        <v>1.67</v>
+      </c>
+      <c r="AK38">
+        <v>1.47</v>
+      </c>
+      <c r="AL38">
+        <v>1.39</v>
+      </c>
+      <c r="AM38">
+        <v>1.37</v>
+      </c>
+      <c r="AN38">
+        <v>1</v>
+      </c>
+      <c r="AO38">
+        <v>3</v>
+      </c>
+      <c r="AP38">
+        <v>0.5</v>
+      </c>
+      <c r="AQ38">
+        <v>3</v>
+      </c>
+      <c r="AR38">
+        <v>1.35</v>
+      </c>
+      <c r="AS38">
+        <v>1.13</v>
+      </c>
+      <c r="AT38">
+        <v>2.48</v>
+      </c>
+      <c r="AU38">
+        <v>3</v>
+      </c>
+      <c r="AV38">
+        <v>3</v>
+      </c>
+      <c r="AW38">
+        <v>3</v>
+      </c>
+      <c r="AX38">
+        <v>4</v>
+      </c>
+      <c r="AY38">
+        <v>6</v>
+      </c>
+      <c r="AZ38">
+        <v>10</v>
+      </c>
+      <c r="BA38">
+        <v>3</v>
+      </c>
+      <c r="BB38">
+        <v>2</v>
+      </c>
+      <c r="BC38">
+        <v>5</v>
+      </c>
+      <c r="BD38">
+        <v>2.15</v>
+      </c>
+      <c r="BE38">
+        <v>6.1</v>
+      </c>
+      <c r="BF38">
+        <v>1.89</v>
+      </c>
+      <c r="BG38">
+        <v>1.53</v>
+      </c>
+      <c r="BH38">
+        <v>2.25</v>
+      </c>
+      <c r="BI38">
+        <v>1.9</v>
+      </c>
+      <c r="BJ38">
+        <v>1.75</v>
+      </c>
+      <c r="BK38">
+        <v>2.43</v>
+      </c>
+      <c r="BL38">
+        <v>1.45</v>
+      </c>
+      <c r="BM38">
         <v>3.25</v>
       </c>
-      <c r="W38">
-        <v>1.33</v>
-      </c>
-      <c r="X38">
-        <v>9</v>
-      </c>
-      <c r="Y38">
-        <v>1.07</v>
-      </c>
-      <c r="Z38">
-        <v>2.14</v>
-      </c>
-      <c r="AA38">
-        <v>3.32</v>
-      </c>
-      <c r="AB38">
-        <v>3.33</v>
-      </c>
-      <c r="AC38">
-        <v>1.07</v>
-      </c>
-      <c r="AD38">
-        <v>8</v>
-      </c>
-      <c r="AE38">
-        <v>1.4</v>
-      </c>
-      <c r="AF38">
-        <v>2.9</v>
-      </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
-      <c r="AH38">
-        <v>1.67</v>
-      </c>
-      <c r="AI38">
-        <v>1.91</v>
-      </c>
-      <c r="AJ38">
-        <v>1.91</v>
-      </c>
-      <c r="AK38">
-        <v>1.31</v>
-      </c>
-      <c r="AL38">
-        <v>1.32</v>
-      </c>
-      <c r="AM38">
-        <v>1.66</v>
-      </c>
-      <c r="AN38">
-        <v>0</v>
-      </c>
-      <c r="AO38">
-        <v>1.5</v>
-      </c>
-      <c r="AP38">
-        <v>1</v>
-      </c>
-      <c r="AQ38">
-        <v>1</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>1.59</v>
-      </c>
-      <c r="AT38">
-        <v>1.59</v>
-      </c>
-      <c r="AU38">
-        <v>5</v>
-      </c>
-      <c r="AV38">
-        <v>5</v>
-      </c>
-      <c r="AW38">
-        <v>12</v>
-      </c>
-      <c r="AX38">
-        <v>6</v>
-      </c>
-      <c r="AY38">
-        <v>18</v>
-      </c>
-      <c r="AZ38">
-        <v>12</v>
-      </c>
-      <c r="BA38">
-        <v>9</v>
-      </c>
-      <c r="BB38">
-        <v>5</v>
-      </c>
-      <c r="BC38">
-        <v>14</v>
-      </c>
-      <c r="BD38">
-        <v>1.71</v>
-      </c>
-      <c r="BE38">
-        <v>6.65</v>
-      </c>
-      <c r="BF38">
-        <v>2.79</v>
-      </c>
-      <c r="BG38">
-        <v>1.24</v>
-      </c>
-      <c r="BH38">
-        <v>3.34</v>
-      </c>
-      <c r="BI38">
-        <v>1.48</v>
-      </c>
-      <c r="BJ38">
-        <v>2.4</v>
-      </c>
-      <c r="BK38">
-        <v>1.85</v>
-      </c>
-      <c r="BL38">
-        <v>1.85</v>
-      </c>
-      <c r="BM38">
-        <v>2.38</v>
-      </c>
       <c r="BN38">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="BO38">
-        <v>3.14</v>
+        <v>4.35</v>
       </c>
       <c r="BP38">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="39" spans="1:68">
@@ -8682,7 +8682,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7778109</v>
+        <v>7778111</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -8697,28 +8697,28 @@
         <v>4</v>
       </c>
       <c r="G39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39" t="s">
         <v>82</v>
       </c>
-      <c r="H39" t="s">
-        <v>78</v>
-      </c>
       <c r="I39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>1</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O39" t="s">
         <v>116</v>
@@ -8727,160 +8727,160 @@
         <v>148</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R39">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S39">
         <v>3.4</v>
       </c>
       <c r="T39">
+        <v>1.5</v>
+      </c>
+      <c r="U39">
+        <v>2.5</v>
+      </c>
+      <c r="V39">
+        <v>3.5</v>
+      </c>
+      <c r="W39">
+        <v>1.29</v>
+      </c>
+      <c r="X39">
+        <v>11</v>
+      </c>
+      <c r="Y39">
+        <v>1.05</v>
+      </c>
+      <c r="Z39">
+        <v>2.95</v>
+      </c>
+      <c r="AA39">
+        <v>2.95</v>
+      </c>
+      <c r="AB39">
+        <v>2.55</v>
+      </c>
+      <c r="AC39">
+        <v>1.09</v>
+      </c>
+      <c r="AD39">
+        <v>7</v>
+      </c>
+      <c r="AE39">
+        <v>1.5</v>
+      </c>
+      <c r="AF39">
+        <v>2.58</v>
+      </c>
+      <c r="AG39">
+        <v>2.15</v>
+      </c>
+      <c r="AH39">
         <v>1.57</v>
       </c>
-      <c r="U39">
-        <v>2.25</v>
-      </c>
-      <c r="V39">
-        <v>3.75</v>
-      </c>
-      <c r="W39">
-        <v>1.25</v>
-      </c>
-      <c r="X39">
-        <v>13</v>
-      </c>
-      <c r="Y39">
-        <v>1.04</v>
-      </c>
-      <c r="Z39">
-        <v>3.1</v>
-      </c>
-      <c r="AA39">
-        <v>2.86</v>
-      </c>
-      <c r="AB39">
-        <v>2.51</v>
-      </c>
-      <c r="AC39">
-        <v>1.12</v>
-      </c>
-      <c r="AD39">
-        <v>5.75</v>
-      </c>
-      <c r="AE39">
-        <v>1.48</v>
-      </c>
-      <c r="AF39">
-        <v>2.37</v>
-      </c>
-      <c r="AG39">
-        <v>2.74</v>
-      </c>
-      <c r="AH39">
-        <v>1.42</v>
-      </c>
       <c r="AI39">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ39">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AL39">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AM39">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AN39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO39">
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AS39">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AT39">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="AU39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW39">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX39">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY39">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AZ39">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BA39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BC39">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BD39">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="BE39">
-        <v>6.1</v>
+        <v>6.65</v>
       </c>
       <c r="BF39">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="BG39">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BH39">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BI39">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="BJ39">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BK39">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BL39">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BM39">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BN39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BO39">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="BP39">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="40" spans="1:68">
@@ -8930,7 +8930,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q40">
         <v>2.3</v>
@@ -9112,7 +9112,7 @@
         <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>2</v>
       </c>
       <c r="O41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P41" t="s">
         <v>149</v>
@@ -9318,7 +9318,7 @@
         <v>89</v>
       </c>
       <c r="H42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -9342,7 +9342,7 @@
         <v>103</v>
       </c>
       <c r="P42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9730,7 +9730,7 @@
         <v>70</v>
       </c>
       <c r="H44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -9754,7 +9754,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q44">
         <v>3.25</v>
@@ -9918,7 +9918,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>7778114</v>
+        <v>7778115</v>
       </c>
       <c r="C45" t="s">
         <v>68</v>
@@ -9933,190 +9933,190 @@
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>91</v>
+      </c>
+      <c r="P45" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q45">
+        <v>3.2</v>
+      </c>
+      <c r="R45">
+        <v>2</v>
+      </c>
+      <c r="S45">
+        <v>3.25</v>
+      </c>
+      <c r="T45">
+        <v>1.42</v>
+      </c>
+      <c r="U45">
+        <v>2.62</v>
+      </c>
+      <c r="V45">
+        <v>2.9</v>
+      </c>
+      <c r="W45">
+        <v>1.36</v>
+      </c>
+      <c r="X45">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y45">
+        <v>1.01</v>
+      </c>
+      <c r="Z45">
+        <v>2.65</v>
+      </c>
+      <c r="AA45">
+        <v>3.1</v>
+      </c>
+      <c r="AB45">
+        <v>2.7</v>
+      </c>
+      <c r="AC45">
+        <v>1.07</v>
+      </c>
+      <c r="AD45">
+        <v>8</v>
+      </c>
+      <c r="AE45">
+        <v>1.38</v>
+      </c>
+      <c r="AF45">
         <v>3</v>
       </c>
-      <c r="N45">
-        <v>4</v>
-      </c>
-      <c r="O45" t="s">
-        <v>97</v>
-      </c>
-      <c r="P45" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q45">
-        <v>3.35</v>
-      </c>
-      <c r="R45">
-        <v>1.93</v>
-      </c>
-      <c r="S45">
-        <v>3.3</v>
-      </c>
-      <c r="T45">
-        <v>1.48</v>
-      </c>
-      <c r="U45">
-        <v>2.45</v>
-      </c>
-      <c r="V45">
-        <v>3.2</v>
-      </c>
-      <c r="W45">
-        <v>1.3</v>
-      </c>
-      <c r="X45">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y45">
-        <v>1.02</v>
-      </c>
-      <c r="Z45">
-        <v>2.78</v>
-      </c>
-      <c r="AA45">
-        <v>2.98</v>
-      </c>
-      <c r="AB45">
-        <v>2.67</v>
-      </c>
-      <c r="AC45">
-        <v>1.1</v>
-      </c>
-      <c r="AD45">
-        <v>6.5</v>
-      </c>
-      <c r="AE45">
-        <v>1.45</v>
-      </c>
-      <c r="AF45">
-        <v>2.7</v>
-      </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH45">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI45">
+        <v>1.77</v>
+      </c>
+      <c r="AJ45">
         <v>1.91</v>
-      </c>
-      <c r="AJ45">
-        <v>1.77</v>
       </c>
       <c r="AK45">
         <v>1.45</v>
       </c>
       <c r="AL45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AM45">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AN45">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP45">
         <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AS45">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AT45">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="AU45">
+        <v>3</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>10</v>
+      </c>
+      <c r="AX45">
+        <v>4</v>
+      </c>
+      <c r="AY45">
+        <v>15</v>
+      </c>
+      <c r="AZ45">
+        <v>4</v>
+      </c>
+      <c r="BA45">
         <v>5</v>
       </c>
-      <c r="AV45">
-        <v>6</v>
-      </c>
-      <c r="AW45">
-        <v>6</v>
-      </c>
-      <c r="AX45">
-        <v>8</v>
-      </c>
-      <c r="AY45">
-        <v>14</v>
-      </c>
-      <c r="AZ45">
-        <v>15</v>
-      </c>
-      <c r="BA45">
-        <v>8</v>
-      </c>
       <c r="BB45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC45">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD45">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="BE45">
         <v>6.75</v>
       </c>
       <c r="BF45">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="BG45">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BH45">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BI45">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BJ45">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BK45">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="BL45">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="BM45">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="BN45">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BO45">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BP45">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="46" spans="1:68">
@@ -10124,7 +10124,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7778115</v>
+        <v>7778116</v>
       </c>
       <c r="C46" t="s">
         <v>68</v>
@@ -10139,10 +10139,10 @@
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -10157,172 +10157,172 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="Q46">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="R46">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S46">
+        <v>3.1</v>
+      </c>
+      <c r="T46">
+        <v>1.57</v>
+      </c>
+      <c r="U46">
+        <v>2.25</v>
+      </c>
+      <c r="V46">
+        <v>3.75</v>
+      </c>
+      <c r="W46">
+        <v>1.25</v>
+      </c>
+      <c r="X46">
+        <v>13</v>
+      </c>
+      <c r="Y46">
+        <v>1.04</v>
+      </c>
+      <c r="Z46">
         <v>3.25</v>
       </c>
-      <c r="T46">
-        <v>1.42</v>
-      </c>
-      <c r="U46">
-        <v>2.62</v>
-      </c>
-      <c r="V46">
-        <v>2.9</v>
-      </c>
-      <c r="W46">
-        <v>1.36</v>
-      </c>
-      <c r="X46">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Y46">
-        <v>1.01</v>
-      </c>
-      <c r="Z46">
-        <v>2.65</v>
-      </c>
       <c r="AA46">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AD46">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AE46">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AF46">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH46">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI46">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AJ46">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AK46">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL46">
+        <v>1.33</v>
+      </c>
+      <c r="AM46">
         <v>1.3</v>
-      </c>
-      <c r="AM46">
-        <v>1.45</v>
       </c>
       <c r="AN46">
         <v>1.5</v>
       </c>
       <c r="AO46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AR46">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AS46">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="AT46">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="AU46">
+        <v>2</v>
+      </c>
+      <c r="AV46">
+        <v>5</v>
+      </c>
+      <c r="AW46">
+        <v>4</v>
+      </c>
+      <c r="AX46">
+        <v>9</v>
+      </c>
+      <c r="AY46">
+        <v>6</v>
+      </c>
+      <c r="AZ46">
+        <v>16</v>
+      </c>
+      <c r="BA46">
+        <v>1</v>
+      </c>
+      <c r="BB46">
+        <v>4</v>
+      </c>
+      <c r="BC46">
+        <v>5</v>
+      </c>
+      <c r="BD46">
+        <v>2.18</v>
+      </c>
+      <c r="BE46">
+        <v>6.5</v>
+      </c>
+      <c r="BF46">
+        <v>1.82</v>
+      </c>
+      <c r="BG46">
+        <v>1.3</v>
+      </c>
+      <c r="BH46">
+        <v>3.05</v>
+      </c>
+      <c r="BI46">
+        <v>1.52</v>
+      </c>
+      <c r="BJ46">
+        <v>2.28</v>
+      </c>
+      <c r="BK46">
+        <v>1.95</v>
+      </c>
+      <c r="BL46">
+        <v>1.85</v>
+      </c>
+      <c r="BM46">
+        <v>2.33</v>
+      </c>
+      <c r="BN46">
+        <v>1.5</v>
+      </c>
+      <c r="BO46">
         <v>3</v>
       </c>
-      <c r="AV46">
-        <v>0</v>
-      </c>
-      <c r="AW46">
-        <v>10</v>
-      </c>
-      <c r="AX46">
-        <v>4</v>
-      </c>
-      <c r="AY46">
-        <v>15</v>
-      </c>
-      <c r="AZ46">
-        <v>4</v>
-      </c>
-      <c r="BA46">
-        <v>5</v>
-      </c>
-      <c r="BB46">
-        <v>2</v>
-      </c>
-      <c r="BC46">
-        <v>7</v>
-      </c>
-      <c r="BD46">
-        <v>1.9</v>
-      </c>
-      <c r="BE46">
-        <v>6.75</v>
-      </c>
-      <c r="BF46">
-        <v>2.07</v>
-      </c>
-      <c r="BG46">
-        <v>1.27</v>
-      </c>
-      <c r="BH46">
-        <v>3.2</v>
-      </c>
-      <c r="BI46">
-        <v>1.47</v>
-      </c>
-      <c r="BJ46">
-        <v>2.38</v>
-      </c>
-      <c r="BK46">
-        <v>1.78</v>
-      </c>
-      <c r="BL46">
-        <v>1.87</v>
-      </c>
-      <c r="BM46">
-        <v>2.23</v>
-      </c>
-      <c r="BN46">
-        <v>1.54</v>
-      </c>
-      <c r="BO46">
-        <v>2.88</v>
-      </c>
       <c r="BP46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="47" spans="1:68">
@@ -10330,7 +10330,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>7778116</v>
+        <v>7778120</v>
       </c>
       <c r="C47" t="s">
         <v>68</v>
@@ -10345,76 +10345,76 @@
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N47">
         <v>2</v>
       </c>
       <c r="O47" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="Q47">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S47">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="T47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W47">
         <v>1.25</v>
       </c>
       <c r="X47">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="Y47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z47">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="AA47">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AC47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AD47">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE47">
         <v>1.48</v>
@@ -10423,112 +10423,112 @@
         <v>2.37</v>
       </c>
       <c r="AG47">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AH47">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI47">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AJ47">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK47">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>1.33</v>
       </c>
       <c r="AM47">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AN47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AQ47">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="AR47">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AS47">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT47">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="AU47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW47">
+        <v>20</v>
+      </c>
+      <c r="AX47">
         <v>4</v>
       </c>
-      <c r="AX47">
+      <c r="AY47">
+        <v>33</v>
+      </c>
+      <c r="AZ47">
+        <v>12</v>
+      </c>
+      <c r="BA47">
         <v>9</v>
       </c>
-      <c r="AY47">
+      <c r="BB47">
         <v>6</v>
       </c>
-      <c r="AZ47">
-        <v>16</v>
-      </c>
-      <c r="BA47">
-        <v>1</v>
-      </c>
-      <c r="BB47">
-        <v>4</v>
-      </c>
       <c r="BC47">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BD47">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="BE47">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF47">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="BG47">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BH47">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BI47">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="BJ47">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="BK47">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="BL47">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="BM47">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="BN47">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BO47">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BP47">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="48" spans="1:68">
@@ -10536,7 +10536,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7778120</v>
+        <v>7778114</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -10551,16 +10551,16 @@
         <v>5</v>
       </c>
       <c r="G48" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" t="s">
         <v>86</v>
       </c>
-      <c r="H48" t="s">
-        <v>82</v>
-      </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -10569,172 +10569,172 @@
         <v>1</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O48" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R48">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S48">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="T48">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="U48">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="W48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X48">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z48">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="AA48">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="AB48">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="AC48">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD48">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE48">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AF48">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI48">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ48">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AL48">
         <v>1.33</v>
       </c>
       <c r="AM48">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AN48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO48">
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AS48">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="AT48">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="AU48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW48">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AX48">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY48">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AZ48">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD48">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="BE48">
         <v>6.75</v>
       </c>
       <c r="BF48">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="BG48">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BJ48">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BK48">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BL48">
         <v>1.94</v>
       </c>
       <c r="BM48">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BN48">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO48">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="BP48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="49" spans="1:68">
@@ -10760,7 +10760,7 @@
         <v>83</v>
       </c>
       <c r="H49" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -10781,7 +10781,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P49" t="s">
         <v>141</v>
@@ -10948,7 +10948,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>7778132</v>
+        <v>7778127</v>
       </c>
       <c r="C50" t="s">
         <v>68</v>
@@ -10963,190 +10963,190 @@
         <v>6</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" t="s">
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q50">
         <v>3.25</v>
       </c>
       <c r="R50">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S50">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T50">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X50">
+        <v>11</v>
+      </c>
+      <c r="Y50">
+        <v>1.05</v>
+      </c>
+      <c r="Z50">
+        <v>2.63</v>
+      </c>
+      <c r="AA50">
+        <v>3.09</v>
+      </c>
+      <c r="AB50">
+        <v>2.73</v>
+      </c>
+      <c r="AC50">
+        <v>1.09</v>
+      </c>
+      <c r="AD50">
+        <v>6.75</v>
+      </c>
+      <c r="AE50">
+        <v>1.47</v>
+      </c>
+      <c r="AF50">
+        <v>2.69</v>
+      </c>
+      <c r="AG50">
+        <v>2.3</v>
+      </c>
+      <c r="AH50">
+        <v>1.5</v>
+      </c>
+      <c r="AI50">
+        <v>2</v>
+      </c>
+      <c r="AJ50">
+        <v>1.75</v>
+      </c>
+      <c r="AK50">
+        <v>1.38</v>
+      </c>
+      <c r="AL50">
+        <v>1.37</v>
+      </c>
+      <c r="AM50">
+        <v>1.56</v>
+      </c>
+      <c r="AN50">
+        <v>1</v>
+      </c>
+      <c r="AO50">
+        <v>1.33</v>
+      </c>
+      <c r="AP50">
+        <v>1.5</v>
+      </c>
+      <c r="AQ50">
+        <v>1</v>
+      </c>
+      <c r="AR50">
+        <v>1.21</v>
+      </c>
+      <c r="AS50">
+        <v>1.52</v>
+      </c>
+      <c r="AT50">
+        <v>2.73</v>
+      </c>
+      <c r="AU50">
+        <v>5</v>
+      </c>
+      <c r="AV50">
+        <v>2</v>
+      </c>
+      <c r="AW50">
+        <v>7</v>
+      </c>
+      <c r="AX50">
+        <v>6</v>
+      </c>
+      <c r="AY50">
         <v>13</v>
       </c>
-      <c r="Y50">
-        <v>1.04</v>
-      </c>
-      <c r="Z50">
-        <v>2.32</v>
-      </c>
-      <c r="AA50">
-        <v>2.84</v>
-      </c>
-      <c r="AB50">
-        <v>3.47</v>
-      </c>
-      <c r="AC50">
-        <v>1.11</v>
-      </c>
-      <c r="AD50">
-        <v>6.25</v>
-      </c>
-      <c r="AE50">
+      <c r="AZ50">
+        <v>9</v>
+      </c>
+      <c r="BA50">
+        <v>5</v>
+      </c>
+      <c r="BB50">
+        <v>3</v>
+      </c>
+      <c r="BC50">
+        <v>8</v>
+      </c>
+      <c r="BD50">
+        <v>1.85</v>
+      </c>
+      <c r="BE50">
+        <v>8.5</v>
+      </c>
+      <c r="BF50">
+        <v>2.15</v>
+      </c>
+      <c r="BG50">
+        <v>1.24</v>
+      </c>
+      <c r="BH50">
+        <v>3.34</v>
+      </c>
+      <c r="BI50">
+        <v>1.47</v>
+      </c>
+      <c r="BJ50">
+        <v>2.42</v>
+      </c>
+      <c r="BK50">
+        <v>1.85</v>
+      </c>
+      <c r="BL50">
+        <v>1.85</v>
+      </c>
+      <c r="BM50">
+        <v>2.34</v>
+      </c>
+      <c r="BN50">
         <v>1.5</v>
       </c>
-      <c r="AF50">
-        <v>2.3</v>
-      </c>
-      <c r="AG50">
-        <v>2.62</v>
-      </c>
-      <c r="AH50">
-        <v>1.43</v>
-      </c>
-      <c r="AI50">
-        <v>2.2</v>
-      </c>
-      <c r="AJ50">
-        <v>1.62</v>
-      </c>
-      <c r="AK50">
-        <v>1.34</v>
-      </c>
-      <c r="AL50">
-        <v>1.39</v>
-      </c>
-      <c r="AM50">
-        <v>1.6</v>
-      </c>
-      <c r="AN50">
-        <v>0</v>
-      </c>
-      <c r="AO50">
-        <v>1.5</v>
-      </c>
-      <c r="AP50">
-        <v>1</v>
-      </c>
-      <c r="AQ50">
-        <v>1</v>
-      </c>
-      <c r="AR50">
-        <v>1.12</v>
-      </c>
-      <c r="AS50">
-        <v>1.05</v>
-      </c>
-      <c r="AT50">
-        <v>2.17</v>
-      </c>
-      <c r="AU50">
-        <v>8</v>
-      </c>
-      <c r="AV50">
-        <v>5</v>
-      </c>
-      <c r="AW50">
-        <v>12</v>
-      </c>
-      <c r="AX50">
-        <v>1</v>
-      </c>
-      <c r="AY50">
-        <v>24</v>
-      </c>
-      <c r="AZ50">
-        <v>6</v>
-      </c>
-      <c r="BA50">
-        <v>3</v>
-      </c>
-      <c r="BB50">
-        <v>0</v>
-      </c>
-      <c r="BC50">
-        <v>3</v>
-      </c>
-      <c r="BD50">
-        <v>1.91</v>
-      </c>
-      <c r="BE50">
-        <v>8</v>
-      </c>
-      <c r="BF50">
-        <v>2.1</v>
-      </c>
-      <c r="BG50">
-        <v>1.47</v>
-      </c>
-      <c r="BH50">
-        <v>2.54</v>
-      </c>
-      <c r="BI50">
-        <v>1.74</v>
-      </c>
-      <c r="BJ50">
-        <v>2.05</v>
-      </c>
-      <c r="BK50">
-        <v>2.2</v>
-      </c>
-      <c r="BL50">
-        <v>1.64</v>
-      </c>
-      <c r="BM50">
-        <v>3.2</v>
-      </c>
-      <c r="BN50">
-        <v>1.28</v>
-      </c>
       <c r="BO50">
-        <v>4.55</v>
+        <v>3.14</v>
       </c>
       <c r="BP50">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="51" spans="1:68">
@@ -11154,7 +11154,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7778124</v>
+        <v>7778125</v>
       </c>
       <c r="C51" t="s">
         <v>68</v>
@@ -11169,103 +11169,103 @@
         <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O51" t="s">
         <v>122</v>
       </c>
       <c r="P51" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y51">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z51">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AA51">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB51">
-        <v>2.92</v>
+        <v>3.77</v>
       </c>
       <c r="AC51">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AD51">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE51">
         <v>1.57</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AG51">
-        <v>2.85</v>
+        <v>2.37</v>
       </c>
       <c r="AH51">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AI51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ51">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AL51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AM51">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AN51">
         <v>0</v>
@@ -11280,79 +11280,79 @@
         <v>0.25</v>
       </c>
       <c r="AR51">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AS51">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT51">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AU51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX51">
         <v>4</v>
       </c>
       <c r="AY51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ51">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD51">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BE51">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF51">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="BG51">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BH51">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="BI51">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BJ51">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="BK51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BL51">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BM51">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BN51">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="BO51">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BP51">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="52" spans="1:68">
@@ -11360,7 +11360,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7778125</v>
+        <v>7778124</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -11375,103 +11375,103 @@
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O52" t="s">
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R52">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="U52">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="W52">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y52">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z52">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="AA52">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AB52">
-        <v>3.77</v>
+        <v>2.92</v>
       </c>
       <c r="AC52">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AD52">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AE52">
         <v>1.57</v>
       </c>
       <c r="AF52">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="AH52">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AI52">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ52">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK52">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AM52">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AN52">
         <v>0</v>
@@ -11486,79 +11486,79 @@
         <v>0.25</v>
       </c>
       <c r="AR52">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AS52">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT52">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AU52">
+        <v>4</v>
+      </c>
+      <c r="AV52">
         <v>5</v>
       </c>
-      <c r="AV52">
-        <v>2</v>
-      </c>
       <c r="AW52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX52">
         <v>4</v>
       </c>
       <c r="AY52">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ52">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA52">
+        <v>5</v>
+      </c>
+      <c r="BB52">
         <v>6</v>
       </c>
-      <c r="BB52">
-        <v>2</v>
-      </c>
       <c r="BC52">
+        <v>11</v>
+      </c>
+      <c r="BD52">
+        <v>1.91</v>
+      </c>
+      <c r="BE52">
         <v>8</v>
       </c>
-      <c r="BD52">
-        <v>1.62</v>
-      </c>
-      <c r="BE52">
-        <v>8.5</v>
-      </c>
       <c r="BF52">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="BG52">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BH52">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="BI52">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BJ52">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BK52">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BL52">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="BM52">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BN52">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BO52">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP52">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="53" spans="1:68">
@@ -11566,7 +11566,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>7778127</v>
+        <v>7778132</v>
       </c>
       <c r="C53" t="s">
         <v>68</v>
@@ -11581,190 +11581,190 @@
         <v>6</v>
       </c>
       <c r="G53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" t="s">
         <v>124</v>
       </c>
       <c r="P53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
       </c>
       <c r="R53">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S53">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T53">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U53">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X53">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y53">
+        <v>1.04</v>
+      </c>
+      <c r="Z53">
+        <v>2.32</v>
+      </c>
+      <c r="AA53">
+        <v>2.84</v>
+      </c>
+      <c r="AB53">
+        <v>3.47</v>
+      </c>
+      <c r="AC53">
+        <v>1.11</v>
+      </c>
+      <c r="AD53">
+        <v>6.25</v>
+      </c>
+      <c r="AE53">
+        <v>1.5</v>
+      </c>
+      <c r="AF53">
+        <v>2.3</v>
+      </c>
+      <c r="AG53">
+        <v>2.62</v>
+      </c>
+      <c r="AH53">
+        <v>1.43</v>
+      </c>
+      <c r="AI53">
+        <v>2.2</v>
+      </c>
+      <c r="AJ53">
+        <v>1.62</v>
+      </c>
+      <c r="AK53">
+        <v>1.34</v>
+      </c>
+      <c r="AL53">
+        <v>1.39</v>
+      </c>
+      <c r="AM53">
+        <v>1.6</v>
+      </c>
+      <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
+        <v>1.5</v>
+      </c>
+      <c r="AP53">
+        <v>1</v>
+      </c>
+      <c r="AQ53">
+        <v>1</v>
+      </c>
+      <c r="AR53">
+        <v>1.12</v>
+      </c>
+      <c r="AS53">
         <v>1.05</v>
       </c>
-      <c r="Z53">
-        <v>2.63</v>
-      </c>
-      <c r="AA53">
-        <v>3.09</v>
-      </c>
-      <c r="AB53">
-        <v>2.73</v>
-      </c>
-      <c r="AC53">
-        <v>1.09</v>
-      </c>
-      <c r="AD53">
-        <v>6.75</v>
-      </c>
-      <c r="AE53">
+      <c r="AT53">
+        <v>2.17</v>
+      </c>
+      <c r="AU53">
+        <v>8</v>
+      </c>
+      <c r="AV53">
+        <v>5</v>
+      </c>
+      <c r="AW53">
+        <v>12</v>
+      </c>
+      <c r="AX53">
+        <v>1</v>
+      </c>
+      <c r="AY53">
+        <v>24</v>
+      </c>
+      <c r="AZ53">
+        <v>6</v>
+      </c>
+      <c r="BA53">
+        <v>3</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>3</v>
+      </c>
+      <c r="BD53">
+        <v>1.91</v>
+      </c>
+      <c r="BE53">
+        <v>8</v>
+      </c>
+      <c r="BF53">
+        <v>2.1</v>
+      </c>
+      <c r="BG53">
         <v>1.47</v>
       </c>
-      <c r="AF53">
-        <v>2.69</v>
-      </c>
-      <c r="AG53">
-        <v>2.3</v>
-      </c>
-      <c r="AH53">
-        <v>1.5</v>
-      </c>
-      <c r="AI53">
-        <v>2</v>
-      </c>
-      <c r="AJ53">
-        <v>1.75</v>
-      </c>
-      <c r="AK53">
-        <v>1.38</v>
-      </c>
-      <c r="AL53">
-        <v>1.37</v>
-      </c>
-      <c r="AM53">
-        <v>1.56</v>
-      </c>
-      <c r="AN53">
-        <v>1</v>
-      </c>
-      <c r="AO53">
-        <v>1.33</v>
-      </c>
-      <c r="AP53">
-        <v>1.5</v>
-      </c>
-      <c r="AQ53">
-        <v>1</v>
-      </c>
-      <c r="AR53">
-        <v>1.21</v>
-      </c>
-      <c r="AS53">
-        <v>1.52</v>
-      </c>
-      <c r="AT53">
-        <v>2.73</v>
-      </c>
-      <c r="AU53">
-        <v>5</v>
-      </c>
-      <c r="AV53">
-        <v>2</v>
-      </c>
-      <c r="AW53">
-        <v>7</v>
-      </c>
-      <c r="AX53">
-        <v>6</v>
-      </c>
-      <c r="AY53">
-        <v>13</v>
-      </c>
-      <c r="AZ53">
-        <v>9</v>
-      </c>
-      <c r="BA53">
-        <v>5</v>
-      </c>
-      <c r="BB53">
-        <v>3</v>
-      </c>
-      <c r="BC53">
-        <v>8</v>
-      </c>
-      <c r="BD53">
-        <v>1.85</v>
-      </c>
-      <c r="BE53">
-        <v>8.5</v>
-      </c>
-      <c r="BF53">
-        <v>2.15</v>
-      </c>
-      <c r="BG53">
-        <v>1.24</v>
-      </c>
       <c r="BH53">
-        <v>3.34</v>
+        <v>2.54</v>
       </c>
       <c r="BI53">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="BJ53">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="BK53">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BL53">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="BM53">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="BN53">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="BO53">
-        <v>3.14</v>
+        <v>4.55</v>
       </c>
       <c r="BP53">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="54" spans="1:68">
@@ -11787,7 +11787,7 @@
         <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s">
         <v>83</v>
@@ -11978,7 +11978,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>7778131</v>
+        <v>7778126</v>
       </c>
       <c r="C55" t="s">
         <v>68</v>
@@ -11993,25 +11993,25 @@
         <v>6</v>
       </c>
       <c r="G55" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55">
         <v>2</v>
@@ -12020,163 +12020,163 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="Q55">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R55">
+        <v>2.2</v>
+      </c>
+      <c r="S55">
+        <v>4</v>
+      </c>
+      <c r="T55">
+        <v>1.36</v>
+      </c>
+      <c r="U55">
+        <v>3</v>
+      </c>
+      <c r="V55">
+        <v>2.75</v>
+      </c>
+      <c r="W55">
+        <v>1.4</v>
+      </c>
+      <c r="X55">
+        <v>8</v>
+      </c>
+      <c r="Y55">
+        <v>1.08</v>
+      </c>
+      <c r="Z55">
+        <v>1.99</v>
+      </c>
+      <c r="AA55">
+        <v>3.45</v>
+      </c>
+      <c r="AB55">
+        <v>3.6</v>
+      </c>
+      <c r="AC55">
+        <v>1.05</v>
+      </c>
+      <c r="AD55">
+        <v>9</v>
+      </c>
+      <c r="AE55">
+        <v>1.3</v>
+      </c>
+      <c r="AF55">
+        <v>3.45</v>
+      </c>
+      <c r="AG55">
+        <v>1.85</v>
+      </c>
+      <c r="AH55">
+        <v>1.89</v>
+      </c>
+      <c r="AI55">
+        <v>1.7</v>
+      </c>
+      <c r="AJ55">
+        <v>2.05</v>
+      </c>
+      <c r="AK55">
+        <v>1.31</v>
+      </c>
+      <c r="AL55">
+        <v>1.31</v>
+      </c>
+      <c r="AM55">
+        <v>1.76</v>
+      </c>
+      <c r="AN55">
+        <v>1</v>
+      </c>
+      <c r="AO55">
+        <v>1.5</v>
+      </c>
+      <c r="AP55">
+        <v>1.5</v>
+      </c>
+      <c r="AQ55">
+        <v>1</v>
+      </c>
+      <c r="AR55">
+        <v>1.24</v>
+      </c>
+      <c r="AS55">
+        <v>1.46</v>
+      </c>
+      <c r="AT55">
+        <v>2.7</v>
+      </c>
+      <c r="AU55">
+        <v>7</v>
+      </c>
+      <c r="AV55">
+        <v>11</v>
+      </c>
+      <c r="AW55">
+        <v>1</v>
+      </c>
+      <c r="AX55">
+        <v>9</v>
+      </c>
+      <c r="AY55">
+        <v>8</v>
+      </c>
+      <c r="AZ55">
+        <v>24</v>
+      </c>
+      <c r="BA55">
+        <v>2</v>
+      </c>
+      <c r="BB55">
+        <v>10</v>
+      </c>
+      <c r="BC55">
+        <v>12</v>
+      </c>
+      <c r="BD55">
+        <v>1.75</v>
+      </c>
+      <c r="BE55">
+        <v>8.5</v>
+      </c>
+      <c r="BF55">
+        <v>2.3</v>
+      </c>
+      <c r="BG55">
+        <v>1.3</v>
+      </c>
+      <c r="BH55">
+        <v>3</v>
+      </c>
+      <c r="BI55">
+        <v>1.35</v>
+      </c>
+      <c r="BJ55">
+        <v>2.74</v>
+      </c>
+      <c r="BK55">
+        <v>1.69</v>
+      </c>
+      <c r="BL55">
+        <v>2.11</v>
+      </c>
+      <c r="BM55">
         <v>2.1</v>
       </c>
-      <c r="S55">
-        <v>5.5</v>
-      </c>
-      <c r="T55">
-        <v>1.44</v>
-      </c>
-      <c r="U55">
-        <v>2.63</v>
-      </c>
-      <c r="V55">
-        <v>3.25</v>
-      </c>
-      <c r="W55">
-        <v>1.33</v>
-      </c>
-      <c r="X55">
-        <v>10</v>
-      </c>
-      <c r="Y55">
-        <v>1.06</v>
-      </c>
-      <c r="Z55">
-        <v>1.67</v>
-      </c>
-      <c r="AA55">
-        <v>3.6</v>
-      </c>
-      <c r="AB55">
-        <v>5.1</v>
-      </c>
-      <c r="AC55">
-        <v>1.07</v>
-      </c>
-      <c r="AD55">
-        <v>8</v>
-      </c>
-      <c r="AE55">
+      <c r="BN55">
+        <v>1.7</v>
+      </c>
+      <c r="BO55">
+        <v>2.71</v>
+      </c>
+      <c r="BP55">
         <v>1.38</v>
-      </c>
-      <c r="AF55">
-        <v>3</v>
-      </c>
-      <c r="AG55">
-        <v>2.05</v>
-      </c>
-      <c r="AH55">
-        <v>1.61</v>
-      </c>
-      <c r="AI55">
-        <v>2.05</v>
-      </c>
-      <c r="AJ55">
-        <v>1.7</v>
-      </c>
-      <c r="AK55">
-        <v>1.18</v>
-      </c>
-      <c r="AL55">
-        <v>1.29</v>
-      </c>
-      <c r="AM55">
-        <v>2.15</v>
-      </c>
-      <c r="AN55">
-        <v>3</v>
-      </c>
-      <c r="AO55">
-        <v>3</v>
-      </c>
-      <c r="AP55">
-        <v>2.33</v>
-      </c>
-      <c r="AQ55">
-        <v>2.33</v>
-      </c>
-      <c r="AR55">
-        <v>1.46</v>
-      </c>
-      <c r="AS55">
-        <v>1.27</v>
-      </c>
-      <c r="AT55">
-        <v>2.73</v>
-      </c>
-      <c r="AU55">
-        <v>3</v>
-      </c>
-      <c r="AV55">
-        <v>6</v>
-      </c>
-      <c r="AW55">
-        <v>14</v>
-      </c>
-      <c r="AX55">
-        <v>5</v>
-      </c>
-      <c r="AY55">
-        <v>22</v>
-      </c>
-      <c r="AZ55">
-        <v>14</v>
-      </c>
-      <c r="BA55">
-        <v>5</v>
-      </c>
-      <c r="BB55">
-        <v>5</v>
-      </c>
-      <c r="BC55">
-        <v>10</v>
-      </c>
-      <c r="BD55">
-        <v>1.44</v>
-      </c>
-      <c r="BE55">
-        <v>9</v>
-      </c>
-      <c r="BF55">
-        <v>3</v>
-      </c>
-      <c r="BG55">
-        <v>1.21</v>
-      </c>
-      <c r="BH55">
-        <v>3.58</v>
-      </c>
-      <c r="BI55">
-        <v>1.42</v>
-      </c>
-      <c r="BJ55">
-        <v>2.57</v>
-      </c>
-      <c r="BK55">
-        <v>1.78</v>
-      </c>
-      <c r="BL55">
-        <v>2</v>
-      </c>
-      <c r="BM55">
-        <v>2.23</v>
-      </c>
-      <c r="BN55">
-        <v>1.62</v>
-      </c>
-      <c r="BO55">
-        <v>2.92</v>
-      </c>
-      <c r="BP55">
-        <v>1.31</v>
       </c>
     </row>
     <row r="56" spans="1:68">
@@ -12199,7 +12199,7 @@
         <v>6</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s">
         <v>76</v>
@@ -12223,10 +12223,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q56">
         <v>4.13</v>
@@ -12319,28 +12319,28 @@
         <v>3.05</v>
       </c>
       <c r="AU56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV56">
+        <v>2</v>
+      </c>
+      <c r="AW56">
+        <v>13</v>
+      </c>
+      <c r="AX56">
+        <v>8</v>
+      </c>
+      <c r="AY56">
+        <v>23</v>
+      </c>
+      <c r="AZ56">
+        <v>11</v>
+      </c>
+      <c r="BA56">
         <v>6</v>
       </c>
-      <c r="AW56">
+      <c r="BB56">
         <v>7</v>
-      </c>
-      <c r="AX56">
-        <v>10</v>
-      </c>
-      <c r="AY56">
-        <v>10</v>
-      </c>
-      <c r="AZ56">
-        <v>17</v>
-      </c>
-      <c r="BA56">
-        <v>7</v>
-      </c>
-      <c r="BB56">
-        <v>6</v>
       </c>
       <c r="BC56">
         <v>13</v>
@@ -12390,7 +12390,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>7778126</v>
+        <v>7778131</v>
       </c>
       <c r="C57" t="s">
         <v>68</v>
@@ -12405,25 +12405,25 @@
         <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -12432,163 +12432,163 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="Q57">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="R57">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="T57">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U57">
+        <v>2.63</v>
+      </c>
+      <c r="V57">
+        <v>3.25</v>
+      </c>
+      <c r="W57">
+        <v>1.33</v>
+      </c>
+      <c r="X57">
+        <v>10</v>
+      </c>
+      <c r="Y57">
+        <v>1.06</v>
+      </c>
+      <c r="Z57">
+        <v>1.67</v>
+      </c>
+      <c r="AA57">
+        <v>3.6</v>
+      </c>
+      <c r="AB57">
+        <v>5.1</v>
+      </c>
+      <c r="AC57">
+        <v>1.07</v>
+      </c>
+      <c r="AD57">
+        <v>8</v>
+      </c>
+      <c r="AE57">
+        <v>1.38</v>
+      </c>
+      <c r="AF57">
         <v>3</v>
       </c>
-      <c r="V57">
-        <v>2.75</v>
-      </c>
-      <c r="W57">
-        <v>1.4</v>
-      </c>
-      <c r="X57">
+      <c r="AG57">
+        <v>2.05</v>
+      </c>
+      <c r="AH57">
+        <v>1.61</v>
+      </c>
+      <c r="AI57">
+        <v>2.05</v>
+      </c>
+      <c r="AJ57">
+        <v>1.7</v>
+      </c>
+      <c r="AK57">
+        <v>1.18</v>
+      </c>
+      <c r="AL57">
+        <v>1.29</v>
+      </c>
+      <c r="AM57">
+        <v>2.15</v>
+      </c>
+      <c r="AN57">
+        <v>3</v>
+      </c>
+      <c r="AO57">
+        <v>3</v>
+      </c>
+      <c r="AP57">
+        <v>2.33</v>
+      </c>
+      <c r="AQ57">
+        <v>2.33</v>
+      </c>
+      <c r="AR57">
+        <v>1.46</v>
+      </c>
+      <c r="AS57">
+        <v>1.27</v>
+      </c>
+      <c r="AT57">
+        <v>2.73</v>
+      </c>
+      <c r="AU57">
+        <v>5</v>
+      </c>
+      <c r="AV57">
+        <v>5</v>
+      </c>
+      <c r="AW57">
         <v>8</v>
       </c>
-      <c r="Y57">
-        <v>1.08</v>
-      </c>
-      <c r="Z57">
-        <v>1.99</v>
-      </c>
-      <c r="AA57">
-        <v>3.45</v>
-      </c>
-      <c r="AB57">
-        <v>3.6</v>
-      </c>
-      <c r="AC57">
-        <v>1.05</v>
-      </c>
-      <c r="AD57">
+      <c r="AX57">
+        <v>1</v>
+      </c>
+      <c r="AY57">
+        <v>17</v>
+      </c>
+      <c r="AZ57">
+        <v>10</v>
+      </c>
+      <c r="BA57">
+        <v>5</v>
+      </c>
+      <c r="BB57">
+        <v>5</v>
+      </c>
+      <c r="BC57">
+        <v>10</v>
+      </c>
+      <c r="BD57">
+        <v>1.44</v>
+      </c>
+      <c r="BE57">
         <v>9</v>
       </c>
-      <c r="AE57">
-        <v>1.3</v>
-      </c>
-      <c r="AF57">
-        <v>3.45</v>
-      </c>
-      <c r="AG57">
-        <v>1.85</v>
-      </c>
-      <c r="AH57">
-        <v>1.89</v>
-      </c>
-      <c r="AI57">
-        <v>1.7</v>
-      </c>
-      <c r="AJ57">
-        <v>2.05</v>
-      </c>
-      <c r="AK57">
+      <c r="BF57">
+        <v>3</v>
+      </c>
+      <c r="BG57">
+        <v>1.21</v>
+      </c>
+      <c r="BH57">
+        <v>3.58</v>
+      </c>
+      <c r="BI57">
+        <v>1.42</v>
+      </c>
+      <c r="BJ57">
+        <v>2.57</v>
+      </c>
+      <c r="BK57">
+        <v>1.78</v>
+      </c>
+      <c r="BL57">
+        <v>2</v>
+      </c>
+      <c r="BM57">
+        <v>2.23</v>
+      </c>
+      <c r="BN57">
+        <v>1.62</v>
+      </c>
+      <c r="BO57">
+        <v>2.92</v>
+      </c>
+      <c r="BP57">
         <v>1.31</v>
-      </c>
-      <c r="AL57">
-        <v>1.31</v>
-      </c>
-      <c r="AM57">
-        <v>1.76</v>
-      </c>
-      <c r="AN57">
-        <v>1</v>
-      </c>
-      <c r="AO57">
-        <v>1.5</v>
-      </c>
-      <c r="AP57">
-        <v>1.5</v>
-      </c>
-      <c r="AQ57">
-        <v>1</v>
-      </c>
-      <c r="AR57">
-        <v>1.24</v>
-      </c>
-      <c r="AS57">
-        <v>1.46</v>
-      </c>
-      <c r="AT57">
-        <v>2.7</v>
-      </c>
-      <c r="AU57">
-        <v>7</v>
-      </c>
-      <c r="AV57">
-        <v>12</v>
-      </c>
-      <c r="AW57">
-        <v>1</v>
-      </c>
-      <c r="AX57">
-        <v>12</v>
-      </c>
-      <c r="AY57">
-        <v>8</v>
-      </c>
-      <c r="AZ57">
-        <v>28</v>
-      </c>
-      <c r="BA57">
-        <v>2</v>
-      </c>
-      <c r="BB57">
-        <v>10</v>
-      </c>
-      <c r="BC57">
-        <v>12</v>
-      </c>
-      <c r="BD57">
-        <v>1.75</v>
-      </c>
-      <c r="BE57">
-        <v>8.5</v>
-      </c>
-      <c r="BF57">
-        <v>2.3</v>
-      </c>
-      <c r="BG57">
-        <v>1.3</v>
-      </c>
-      <c r="BH57">
-        <v>3</v>
-      </c>
-      <c r="BI57">
-        <v>1.35</v>
-      </c>
-      <c r="BJ57">
-        <v>2.74</v>
-      </c>
-      <c r="BK57">
-        <v>1.69</v>
-      </c>
-      <c r="BL57">
-        <v>2.11</v>
-      </c>
-      <c r="BM57">
-        <v>2.1</v>
-      </c>
-      <c r="BN57">
-        <v>1.7</v>
-      </c>
-      <c r="BO57">
-        <v>2.71</v>
-      </c>
-      <c r="BP57">
-        <v>1.38</v>
       </c>
     </row>
     <row r="58" spans="1:68">
@@ -12611,7 +12611,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s">
         <v>89</v>
@@ -12731,22 +12731,22 @@
         <v>3.56</v>
       </c>
       <c r="AU58">
+        <v>4</v>
+      </c>
+      <c r="AV58">
+        <v>7</v>
+      </c>
+      <c r="AW58">
         <v>3</v>
-      </c>
-      <c r="AV58">
-        <v>8</v>
-      </c>
-      <c r="AW58">
-        <v>8</v>
       </c>
       <c r="AX58">
         <v>6</v>
       </c>
       <c r="AY58">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ58">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA58">
         <v>9</v>
@@ -12937,22 +12937,22 @@
         <v>3.94</v>
       </c>
       <c r="AU59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY59">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AZ59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA59">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -11913,16 +11913,16 @@
         <v>5</v>
       </c>
       <c r="AW54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX54">
         <v>5</v>
       </c>
       <c r="AY54">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ54">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA54">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -12319,7 +12319,7 @@
         <v>3.05</v>
       </c>
       <c r="AU56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV56">
         <v>2</v>
@@ -12331,10 +12331,10 @@
         <v>8</v>
       </c>
       <c r="AY56">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA56">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="164">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -409,6 +409,15 @@
     <t>['2']</t>
   </si>
   <si>
+    <t>['11', '28', '67']</t>
+  </si>
+  <si>
+    <t>['18', '74', '82']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -491,6 +500,12 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['43', '67', '90+7']</t>
+  </si>
+  <si>
+    <t>['55', '72', '83']</t>
   </si>
 </sst>
 </file>
@@ -852,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP60"/>
+  <dimension ref="A1:BP65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1108,7 +1123,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1726,7 +1741,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2756,7 +2771,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2962,7 +2977,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3168,7 +3183,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3249,7 +3264,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3374,7 +3389,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3452,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3864,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ15">
         <v>0.25</v>
@@ -3992,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4198,7 +4213,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4279,7 +4294,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4404,7 +4419,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4688,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -4894,10 +4909,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5228,7 +5243,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5309,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>0.91</v>
@@ -5640,7 +5655,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5846,7 +5861,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5924,7 +5939,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6052,7 +6067,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6258,7 +6273,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6336,7 +6351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ27">
         <v>0.25</v>
@@ -6464,7 +6479,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6545,7 +6560,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>0.8</v>
@@ -6748,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ29">
         <v>0.25</v>
@@ -6876,7 +6891,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -6954,7 +6969,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7288,7 +7303,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7369,7 +7384,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR32">
         <v>1.12</v>
@@ -7572,7 +7587,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -7906,7 +7921,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8112,7 +8127,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8318,7 +8333,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8524,7 +8539,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8730,7 +8745,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9142,7 +9157,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9554,7 +9569,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -9635,7 +9650,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR43">
         <v>1.74</v>
@@ -10044,10 +10059,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
         <v>1.37</v>
@@ -10172,7 +10187,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10378,7 +10393,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10584,7 +10599,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -10662,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -10790,7 +10805,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -11408,7 +11423,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11820,7 +11835,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11898,7 +11913,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
         <v>1.75</v>
@@ -12313,7 +12328,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR56">
         <v>1.66</v>
@@ -12438,7 +12453,7 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -12722,7 +12737,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ58">
         <v>0.8</v>
@@ -12850,7 +12865,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -12931,7 +12946,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13056,7 +13071,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13213,6 +13228,1036 @@
       </c>
       <c r="BP60">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7778138</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45745.04166666666</v>
+      </c>
+      <c r="F61">
+        <v>7</v>
+      </c>
+      <c r="G61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s">
+        <v>77</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>2</v>
+      </c>
+      <c r="L61">
+        <v>3</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="s">
+        <v>131</v>
+      </c>
+      <c r="P61" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q61">
+        <v>3.1</v>
+      </c>
+      <c r="R61">
+        <v>2.05</v>
+      </c>
+      <c r="S61">
+        <v>3.75</v>
+      </c>
+      <c r="T61">
+        <v>1.5</v>
+      </c>
+      <c r="U61">
+        <v>2.5</v>
+      </c>
+      <c r="V61">
+        <v>3.4</v>
+      </c>
+      <c r="W61">
+        <v>1.3</v>
+      </c>
+      <c r="X61">
+        <v>10</v>
+      </c>
+      <c r="Y61">
+        <v>1.06</v>
+      </c>
+      <c r="Z61">
+        <v>2.34</v>
+      </c>
+      <c r="AA61">
+        <v>3.3</v>
+      </c>
+      <c r="AB61">
+        <v>2.94</v>
+      </c>
+      <c r="AC61">
+        <v>1.07</v>
+      </c>
+      <c r="AD61">
+        <v>8</v>
+      </c>
+      <c r="AE61">
+        <v>1.38</v>
+      </c>
+      <c r="AF61">
+        <v>2.95</v>
+      </c>
+      <c r="AG61">
+        <v>2.1</v>
+      </c>
+      <c r="AH61">
+        <v>1.6</v>
+      </c>
+      <c r="AI61">
+        <v>1.95</v>
+      </c>
+      <c r="AJ61">
+        <v>1.8</v>
+      </c>
+      <c r="AK61">
+        <v>1.36</v>
+      </c>
+      <c r="AL61">
+        <v>1.28</v>
+      </c>
+      <c r="AM61">
+        <v>1.57</v>
+      </c>
+      <c r="AN61">
+        <v>1.33</v>
+      </c>
+      <c r="AO61">
+        <v>1.67</v>
+      </c>
+      <c r="AP61">
+        <v>1.75</v>
+      </c>
+      <c r="AQ61">
+        <v>1.25</v>
+      </c>
+      <c r="AR61">
+        <v>1.41</v>
+      </c>
+      <c r="AS61">
+        <v>1.28</v>
+      </c>
+      <c r="AT61">
+        <v>2.69</v>
+      </c>
+      <c r="AU61">
+        <v>-1</v>
+      </c>
+      <c r="AV61">
+        <v>-1</v>
+      </c>
+      <c r="AW61">
+        <v>-1</v>
+      </c>
+      <c r="AX61">
+        <v>-1</v>
+      </c>
+      <c r="AY61">
+        <v>-1</v>
+      </c>
+      <c r="AZ61">
+        <v>-1</v>
+      </c>
+      <c r="BA61">
+        <v>-1</v>
+      </c>
+      <c r="BB61">
+        <v>-1</v>
+      </c>
+      <c r="BC61">
+        <v>-1</v>
+      </c>
+      <c r="BD61">
+        <v>1.89</v>
+      </c>
+      <c r="BE61">
+        <v>6.7</v>
+      </c>
+      <c r="BF61">
+        <v>2.41</v>
+      </c>
+      <c r="BG61">
+        <v>1.24</v>
+      </c>
+      <c r="BH61">
+        <v>3.4</v>
+      </c>
+      <c r="BI61">
+        <v>1.33</v>
+      </c>
+      <c r="BJ61">
+        <v>2.83</v>
+      </c>
+      <c r="BK61">
+        <v>1.61</v>
+      </c>
+      <c r="BL61">
+        <v>2.12</v>
+      </c>
+      <c r="BM61">
+        <v>2.05</v>
+      </c>
+      <c r="BN61">
+        <v>1.7</v>
+      </c>
+      <c r="BO61">
+        <v>2.64</v>
+      </c>
+      <c r="BP61">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7778135</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
+      </c>
+      <c r="G62" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s">
+        <v>79</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>91</v>
+      </c>
+      <c r="P62" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q62">
+        <v>3.25</v>
+      </c>
+      <c r="R62">
+        <v>1.91</v>
+      </c>
+      <c r="S62">
+        <v>4</v>
+      </c>
+      <c r="T62">
+        <v>1.62</v>
+      </c>
+      <c r="U62">
+        <v>2.2</v>
+      </c>
+      <c r="V62">
+        <v>4</v>
+      </c>
+      <c r="W62">
+        <v>1.22</v>
+      </c>
+      <c r="X62">
+        <v>13</v>
+      </c>
+      <c r="Y62">
+        <v>1.04</v>
+      </c>
+      <c r="Z62">
+        <v>2.41</v>
+      </c>
+      <c r="AA62">
+        <v>3.01</v>
+      </c>
+      <c r="AB62">
+        <v>3.11</v>
+      </c>
+      <c r="AC62">
+        <v>1.11</v>
+      </c>
+      <c r="AD62">
+        <v>6.25</v>
+      </c>
+      <c r="AE62">
+        <v>1.53</v>
+      </c>
+      <c r="AF62">
+        <v>2.25</v>
+      </c>
+      <c r="AG62">
+        <v>2.67</v>
+      </c>
+      <c r="AH62">
+        <v>1.44</v>
+      </c>
+      <c r="AI62">
+        <v>2.2</v>
+      </c>
+      <c r="AJ62">
+        <v>1.62</v>
+      </c>
+      <c r="AK62">
+        <v>1.33</v>
+      </c>
+      <c r="AL62">
+        <v>1.33</v>
+      </c>
+      <c r="AM62">
+        <v>1.55</v>
+      </c>
+      <c r="AN62">
+        <v>1.33</v>
+      </c>
+      <c r="AO62">
+        <v>1.33</v>
+      </c>
+      <c r="AP62">
+        <v>1.25</v>
+      </c>
+      <c r="AQ62">
+        <v>1.25</v>
+      </c>
+      <c r="AR62">
+        <v>1.46</v>
+      </c>
+      <c r="AS62">
+        <v>1.03</v>
+      </c>
+      <c r="AT62">
+        <v>2.49</v>
+      </c>
+      <c r="AU62">
+        <v>-1</v>
+      </c>
+      <c r="AV62">
+        <v>-1</v>
+      </c>
+      <c r="AW62">
+        <v>-1</v>
+      </c>
+      <c r="AX62">
+        <v>-1</v>
+      </c>
+      <c r="AY62">
+        <v>-1</v>
+      </c>
+      <c r="AZ62">
+        <v>-1</v>
+      </c>
+      <c r="BA62">
+        <v>-1</v>
+      </c>
+      <c r="BB62">
+        <v>-1</v>
+      </c>
+      <c r="BC62">
+        <v>-1</v>
+      </c>
+      <c r="BD62">
+        <v>1.58</v>
+      </c>
+      <c r="BE62">
+        <v>6.85</v>
+      </c>
+      <c r="BF62">
+        <v>3.18</v>
+      </c>
+      <c r="BG62">
+        <v>1.23</v>
+      </c>
+      <c r="BH62">
+        <v>3.42</v>
+      </c>
+      <c r="BI62">
+        <v>1.45</v>
+      </c>
+      <c r="BJ62">
+        <v>2.48</v>
+      </c>
+      <c r="BK62">
+        <v>1.8</v>
+      </c>
+      <c r="BL62">
+        <v>1.91</v>
+      </c>
+      <c r="BM62">
+        <v>2.3</v>
+      </c>
+      <c r="BN62">
+        <v>1.52</v>
+      </c>
+      <c r="BO62">
+        <v>3.05</v>
+      </c>
+      <c r="BP62">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7778137</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s">
+        <v>70</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>3</v>
+      </c>
+      <c r="N63">
+        <v>6</v>
+      </c>
+      <c r="O63" t="s">
+        <v>132</v>
+      </c>
+      <c r="P63" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q63">
+        <v>3.25</v>
+      </c>
+      <c r="R63">
+        <v>2</v>
+      </c>
+      <c r="S63">
+        <v>3.75</v>
+      </c>
+      <c r="T63">
+        <v>1.5</v>
+      </c>
+      <c r="U63">
+        <v>2.5</v>
+      </c>
+      <c r="V63">
+        <v>3.5</v>
+      </c>
+      <c r="W63">
+        <v>1.29</v>
+      </c>
+      <c r="X63">
+        <v>11</v>
+      </c>
+      <c r="Y63">
+        <v>1.05</v>
+      </c>
+      <c r="Z63">
+        <v>2.48</v>
+      </c>
+      <c r="AA63">
+        <v>3.32</v>
+      </c>
+      <c r="AB63">
+        <v>2.74</v>
+      </c>
+      <c r="AC63">
+        <v>1.07</v>
+      </c>
+      <c r="AD63">
+        <v>8</v>
+      </c>
+      <c r="AE63">
+        <v>1.42</v>
+      </c>
+      <c r="AF63">
+        <v>2.8</v>
+      </c>
+      <c r="AG63">
+        <v>2.2</v>
+      </c>
+      <c r="AH63">
+        <v>1.6</v>
+      </c>
+      <c r="AI63">
+        <v>2</v>
+      </c>
+      <c r="AJ63">
+        <v>1.75</v>
+      </c>
+      <c r="AK63">
+        <v>1.42</v>
+      </c>
+      <c r="AL63">
+        <v>1.28</v>
+      </c>
+      <c r="AM63">
+        <v>1.5</v>
+      </c>
+      <c r="AN63">
+        <v>1</v>
+      </c>
+      <c r="AO63">
+        <v>1</v>
+      </c>
+      <c r="AP63">
+        <v>1</v>
+      </c>
+      <c r="AQ63">
+        <v>1</v>
+      </c>
+      <c r="AR63">
+        <v>1.47</v>
+      </c>
+      <c r="AS63">
+        <v>1.91</v>
+      </c>
+      <c r="AT63">
+        <v>3.38</v>
+      </c>
+      <c r="AU63">
+        <v>-1</v>
+      </c>
+      <c r="AV63">
+        <v>-1</v>
+      </c>
+      <c r="AW63">
+        <v>-1</v>
+      </c>
+      <c r="AX63">
+        <v>-1</v>
+      </c>
+      <c r="AY63">
+        <v>-1</v>
+      </c>
+      <c r="AZ63">
+        <v>-1</v>
+      </c>
+      <c r="BA63">
+        <v>-1</v>
+      </c>
+      <c r="BB63">
+        <v>-1</v>
+      </c>
+      <c r="BC63">
+        <v>-1</v>
+      </c>
+      <c r="BD63">
+        <v>1.75</v>
+      </c>
+      <c r="BE63">
+        <v>6.65</v>
+      </c>
+      <c r="BF63">
+        <v>2.69</v>
+      </c>
+      <c r="BG63">
+        <v>1.23</v>
+      </c>
+      <c r="BH63">
+        <v>3.42</v>
+      </c>
+      <c r="BI63">
+        <v>1.46</v>
+      </c>
+      <c r="BJ63">
+        <v>2.45</v>
+      </c>
+      <c r="BK63">
+        <v>1.82</v>
+      </c>
+      <c r="BL63">
+        <v>1.88</v>
+      </c>
+      <c r="BM63">
+        <v>2.32</v>
+      </c>
+      <c r="BN63">
+        <v>1.51</v>
+      </c>
+      <c r="BO63">
+        <v>3.08</v>
+      </c>
+      <c r="BP63">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7778134</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45745.125</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
+        <v>86</v>
+      </c>
+      <c r="H64" t="s">
+        <v>72</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>133</v>
+      </c>
+      <c r="P64" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q64">
+        <v>3.5</v>
+      </c>
+      <c r="R64">
+        <v>1.95</v>
+      </c>
+      <c r="S64">
+        <v>3.6</v>
+      </c>
+      <c r="T64">
+        <v>1.53</v>
+      </c>
+      <c r="U64">
+        <v>2.38</v>
+      </c>
+      <c r="V64">
+        <v>3.75</v>
+      </c>
+      <c r="W64">
+        <v>1.25</v>
+      </c>
+      <c r="X64">
+        <v>11</v>
+      </c>
+      <c r="Y64">
+        <v>1.05</v>
+      </c>
+      <c r="Z64">
+        <v>2.64</v>
+      </c>
+      <c r="AA64">
+        <v>3.04</v>
+      </c>
+      <c r="AB64">
+        <v>2.76</v>
+      </c>
+      <c r="AC64">
+        <v>1.1</v>
+      </c>
+      <c r="AD64">
+        <v>6.5</v>
+      </c>
+      <c r="AE64">
+        <v>1.48</v>
+      </c>
+      <c r="AF64">
+        <v>2.6</v>
+      </c>
+      <c r="AG64">
+        <v>2.3</v>
+      </c>
+      <c r="AH64">
+        <v>1.5</v>
+      </c>
+      <c r="AI64">
+        <v>2</v>
+      </c>
+      <c r="AJ64">
+        <v>1.75</v>
+      </c>
+      <c r="AK64">
+        <v>1.42</v>
+      </c>
+      <c r="AL64">
+        <v>1.33</v>
+      </c>
+      <c r="AM64">
+        <v>1.45</v>
+      </c>
+      <c r="AN64">
+        <v>2.5</v>
+      </c>
+      <c r="AO64">
+        <v>2</v>
+      </c>
+      <c r="AP64">
+        <v>2.6</v>
+      </c>
+      <c r="AQ64">
+        <v>1.33</v>
+      </c>
+      <c r="AR64">
+        <v>1.72</v>
+      </c>
+      <c r="AS64">
+        <v>1.58</v>
+      </c>
+      <c r="AT64">
+        <v>3.3</v>
+      </c>
+      <c r="AU64">
+        <v>5</v>
+      </c>
+      <c r="AV64">
+        <v>2</v>
+      </c>
+      <c r="AW64">
+        <v>5</v>
+      </c>
+      <c r="AX64">
+        <v>5</v>
+      </c>
+      <c r="AY64">
+        <v>12</v>
+      </c>
+      <c r="AZ64">
+        <v>7</v>
+      </c>
+      <c r="BA64">
+        <v>6</v>
+      </c>
+      <c r="BB64">
+        <v>7</v>
+      </c>
+      <c r="BC64">
+        <v>13</v>
+      </c>
+      <c r="BD64">
+        <v>2.19</v>
+      </c>
+      <c r="BE64">
+        <v>6.4</v>
+      </c>
+      <c r="BF64">
+        <v>2.08</v>
+      </c>
+      <c r="BG64">
+        <v>1.25</v>
+      </c>
+      <c r="BH64">
+        <v>3.28</v>
+      </c>
+      <c r="BI64">
+        <v>1.5</v>
+      </c>
+      <c r="BJ64">
+        <v>2.35</v>
+      </c>
+      <c r="BK64">
+        <v>1.91</v>
+      </c>
+      <c r="BL64">
+        <v>1.8</v>
+      </c>
+      <c r="BM64">
+        <v>2.42</v>
+      </c>
+      <c r="BN64">
+        <v>1.47</v>
+      </c>
+      <c r="BO64">
+        <v>3.2</v>
+      </c>
+      <c r="BP64">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7778136</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45745.20833333334</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" t="s">
+        <v>76</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>3</v>
+      </c>
+      <c r="N65">
+        <v>3</v>
+      </c>
+      <c r="O65" t="s">
+        <v>91</v>
+      </c>
+      <c r="P65" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q65">
+        <v>4.33</v>
+      </c>
+      <c r="R65">
+        <v>2.2</v>
+      </c>
+      <c r="S65">
+        <v>2.6</v>
+      </c>
+      <c r="T65">
+        <v>1.4</v>
+      </c>
+      <c r="U65">
+        <v>2.75</v>
+      </c>
+      <c r="V65">
+        <v>3</v>
+      </c>
+      <c r="W65">
+        <v>1.36</v>
+      </c>
+      <c r="X65">
+        <v>8</v>
+      </c>
+      <c r="Y65">
+        <v>1.08</v>
+      </c>
+      <c r="Z65">
+        <v>3.69</v>
+      </c>
+      <c r="AA65">
+        <v>3.45</v>
+      </c>
+      <c r="AB65">
+        <v>1.96</v>
+      </c>
+      <c r="AC65">
+        <v>1.06</v>
+      </c>
+      <c r="AD65">
+        <v>8.5</v>
+      </c>
+      <c r="AE65">
+        <v>1.3</v>
+      </c>
+      <c r="AF65">
+        <v>3.35</v>
+      </c>
+      <c r="AG65">
+        <v>1.89</v>
+      </c>
+      <c r="AH65">
+        <v>1.85</v>
+      </c>
+      <c r="AI65">
+        <v>1.75</v>
+      </c>
+      <c r="AJ65">
+        <v>2</v>
+      </c>
+      <c r="AK65">
+        <v>1.77</v>
+      </c>
+      <c r="AL65">
+        <v>1.25</v>
+      </c>
+      <c r="AM65">
+        <v>1.25</v>
+      </c>
+      <c r="AN65">
+        <v>1.33</v>
+      </c>
+      <c r="AO65">
+        <v>1.67</v>
+      </c>
+      <c r="AP65">
+        <v>1</v>
+      </c>
+      <c r="AQ65">
+        <v>2</v>
+      </c>
+      <c r="AR65">
+        <v>1.38</v>
+      </c>
+      <c r="AS65">
+        <v>1.32</v>
+      </c>
+      <c r="AT65">
+        <v>2.7</v>
+      </c>
+      <c r="AU65">
+        <v>-1</v>
+      </c>
+      <c r="AV65">
+        <v>-1</v>
+      </c>
+      <c r="AW65">
+        <v>-1</v>
+      </c>
+      <c r="AX65">
+        <v>-1</v>
+      </c>
+      <c r="AY65">
+        <v>-1</v>
+      </c>
+      <c r="AZ65">
+        <v>-1</v>
+      </c>
+      <c r="BA65">
+        <v>-1</v>
+      </c>
+      <c r="BB65">
+        <v>-1</v>
+      </c>
+      <c r="BC65">
+        <v>-1</v>
+      </c>
+      <c r="BD65">
+        <v>2.59</v>
+      </c>
+      <c r="BE65">
+        <v>6.6</v>
+      </c>
+      <c r="BF65">
+        <v>1.8</v>
+      </c>
+      <c r="BG65">
+        <v>1.21</v>
+      </c>
+      <c r="BH65">
+        <v>3.58</v>
+      </c>
+      <c r="BI65">
+        <v>1.43</v>
+      </c>
+      <c r="BJ65">
+        <v>2.54</v>
+      </c>
+      <c r="BK65">
+        <v>1.77</v>
+      </c>
+      <c r="BL65">
+        <v>1.95</v>
+      </c>
+      <c r="BM65">
+        <v>2.23</v>
+      </c>
+      <c r="BN65">
+        <v>1.55</v>
+      </c>
+      <c r="BO65">
+        <v>2.92</v>
+      </c>
+      <c r="BP65">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="168">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -409,15 +409,24 @@
     <t>['2']</t>
   </si>
   <si>
+    <t>['67']</t>
+  </si>
+  <si>
     <t>['11', '28', '67']</t>
   </si>
   <si>
     <t>['18', '74', '82']</t>
   </si>
   <si>
+    <t>['16', '54']</t>
+  </si>
+  <si>
     <t>['33']</t>
   </si>
   <si>
+    <t>['22', '65']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -503,6 +512,9 @@
   </si>
   <si>
     <t>['43', '67', '90+7']</t>
+  </si>
+  <si>
+    <t>['9', '84']</t>
   </si>
   <si>
     <t>['55', '72', '83']</t>
@@ -867,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP65"/>
+  <dimension ref="A1:BP69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1123,7 +1135,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1741,7 +1753,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2025,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -2771,7 +2783,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2852,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2977,7 +2989,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3183,7 +3195,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3261,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3389,7 +3401,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4007,7 +4019,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4085,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -4213,7 +4225,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4419,7 +4431,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4706,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5243,7 +5255,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5527,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -5655,7 +5667,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5861,7 +5873,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -5942,7 +5954,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6067,7 +6079,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6273,7 +6285,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6479,7 +6491,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6891,7 +6903,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7178,7 +7190,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR31">
         <v>1.14</v>
@@ -7303,7 +7315,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7921,7 +7933,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8127,7 +8139,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8333,7 +8345,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8539,7 +8551,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8617,10 +8629,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -8745,7 +8757,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -8823,7 +8835,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
@@ -9032,7 +9044,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR40">
         <v>1.25</v>
@@ -9157,7 +9169,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9569,7 +9581,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10187,7 +10199,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10268,7 +10280,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10393,7 +10405,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10599,7 +10611,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -10805,7 +10817,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -10883,7 +10895,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11423,7 +11435,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11835,7 +11847,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12325,7 +12337,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ56">
         <v>2</v>
@@ -12453,7 +12465,7 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -12865,7 +12877,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13071,7 +13083,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13235,7 +13247,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>7778138</v>
+        <v>7778141</v>
       </c>
       <c r="C61" t="s">
         <v>68</v>
@@ -13244,34 +13256,34 @@
         <v>69</v>
       </c>
       <c r="E61" s="2">
-        <v>45745.04166666666</v>
+        <v>45745.03819444445</v>
       </c>
       <c r="F61">
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O61" t="s">
         <v>131</v>
@@ -13280,160 +13292,160 @@
         <v>91</v>
       </c>
       <c r="Q61">
+        <v>3.4</v>
+      </c>
+      <c r="R61">
+        <v>2.1</v>
+      </c>
+      <c r="S61">
         <v>3.1</v>
       </c>
-      <c r="R61">
+      <c r="T61">
+        <v>1.4</v>
+      </c>
+      <c r="U61">
+        <v>2.75</v>
+      </c>
+      <c r="V61">
+        <v>3</v>
+      </c>
+      <c r="W61">
+        <v>1.36</v>
+      </c>
+      <c r="X61">
+        <v>8</v>
+      </c>
+      <c r="Y61">
+        <v>1.08</v>
+      </c>
+      <c r="Z61">
+        <v>2.85</v>
+      </c>
+      <c r="AA61">
+        <v>3.39</v>
+      </c>
+      <c r="AB61">
+        <v>2.36</v>
+      </c>
+      <c r="AC61">
+        <v>1.05</v>
+      </c>
+      <c r="AD61">
+        <v>9</v>
+      </c>
+      <c r="AE61">
+        <v>1.3</v>
+      </c>
+      <c r="AF61">
+        <v>3.45</v>
+      </c>
+      <c r="AG61">
+        <v>1.91</v>
+      </c>
+      <c r="AH61">
+        <v>1.83</v>
+      </c>
+      <c r="AI61">
+        <v>1.7</v>
+      </c>
+      <c r="AJ61">
         <v>2.05</v>
       </c>
-      <c r="S61">
-        <v>3.75</v>
-      </c>
-      <c r="T61">
-        <v>1.5</v>
-      </c>
-      <c r="U61">
+      <c r="AK61">
+        <v>1.55</v>
+      </c>
+      <c r="AL61">
+        <v>1.25</v>
+      </c>
+      <c r="AM61">
+        <v>1.42</v>
+      </c>
+      <c r="AN61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>0</v>
+      </c>
+      <c r="AP61">
+        <v>2.2</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>1.71</v>
+      </c>
+      <c r="AS61">
+        <v>0.93</v>
+      </c>
+      <c r="AT61">
+        <v>2.64</v>
+      </c>
+      <c r="AU61">
+        <v>5</v>
+      </c>
+      <c r="AV61">
+        <v>6</v>
+      </c>
+      <c r="AW61">
+        <v>5</v>
+      </c>
+      <c r="AX61">
+        <v>7</v>
+      </c>
+      <c r="AY61">
+        <v>10</v>
+      </c>
+      <c r="AZ61">
+        <v>16</v>
+      </c>
+      <c r="BA61">
+        <v>8</v>
+      </c>
+      <c r="BB61">
+        <v>2</v>
+      </c>
+      <c r="BC61">
+        <v>10</v>
+      </c>
+      <c r="BD61">
+        <v>2.09</v>
+      </c>
+      <c r="BE61">
+        <v>6.65</v>
+      </c>
+      <c r="BF61">
+        <v>2.15</v>
+      </c>
+      <c r="BG61">
+        <v>1.27</v>
+      </c>
+      <c r="BH61">
+        <v>3.2</v>
+      </c>
+      <c r="BI61">
+        <v>1.3</v>
+      </c>
+      <c r="BJ61">
+        <v>2.97</v>
+      </c>
+      <c r="BK61">
+        <v>1.55</v>
+      </c>
+      <c r="BL61">
+        <v>2.23</v>
+      </c>
+      <c r="BM61">
+        <v>1.91</v>
+      </c>
+      <c r="BN61">
+        <v>1.8</v>
+      </c>
+      <c r="BO61">
         <v>2.5</v>
       </c>
-      <c r="V61">
-        <v>3.4</v>
-      </c>
-      <c r="W61">
-        <v>1.3</v>
-      </c>
-      <c r="X61">
-        <v>10</v>
-      </c>
-      <c r="Y61">
-        <v>1.06</v>
-      </c>
-      <c r="Z61">
-        <v>2.34</v>
-      </c>
-      <c r="AA61">
-        <v>3.3</v>
-      </c>
-      <c r="AB61">
-        <v>2.94</v>
-      </c>
-      <c r="AC61">
-        <v>1.07</v>
-      </c>
-      <c r="AD61">
-        <v>8</v>
-      </c>
-      <c r="AE61">
-        <v>1.38</v>
-      </c>
-      <c r="AF61">
-        <v>2.95</v>
-      </c>
-      <c r="AG61">
-        <v>2.1</v>
-      </c>
-      <c r="AH61">
-        <v>1.6</v>
-      </c>
-      <c r="AI61">
-        <v>1.95</v>
-      </c>
-      <c r="AJ61">
-        <v>1.8</v>
-      </c>
-      <c r="AK61">
-        <v>1.36</v>
-      </c>
-      <c r="AL61">
-        <v>1.28</v>
-      </c>
-      <c r="AM61">
-        <v>1.57</v>
-      </c>
-      <c r="AN61">
-        <v>1.33</v>
-      </c>
-      <c r="AO61">
-        <v>1.67</v>
-      </c>
-      <c r="AP61">
-        <v>1.75</v>
-      </c>
-      <c r="AQ61">
-        <v>1.25</v>
-      </c>
-      <c r="AR61">
-        <v>1.41</v>
-      </c>
-      <c r="AS61">
-        <v>1.28</v>
-      </c>
-      <c r="AT61">
-        <v>2.69</v>
-      </c>
-      <c r="AU61">
-        <v>-1</v>
-      </c>
-      <c r="AV61">
-        <v>-1</v>
-      </c>
-      <c r="AW61">
-        <v>-1</v>
-      </c>
-      <c r="AX61">
-        <v>-1</v>
-      </c>
-      <c r="AY61">
-        <v>-1</v>
-      </c>
-      <c r="AZ61">
-        <v>-1</v>
-      </c>
-      <c r="BA61">
-        <v>-1</v>
-      </c>
-      <c r="BB61">
-        <v>-1</v>
-      </c>
-      <c r="BC61">
-        <v>-1</v>
-      </c>
-      <c r="BD61">
-        <v>1.89</v>
-      </c>
-      <c r="BE61">
-        <v>6.7</v>
-      </c>
-      <c r="BF61">
-        <v>2.41</v>
-      </c>
-      <c r="BG61">
-        <v>1.24</v>
-      </c>
-      <c r="BH61">
-        <v>3.4</v>
-      </c>
-      <c r="BI61">
-        <v>1.33</v>
-      </c>
-      <c r="BJ61">
-        <v>2.83</v>
-      </c>
-      <c r="BK61">
-        <v>1.61</v>
-      </c>
-      <c r="BL61">
-        <v>2.12</v>
-      </c>
-      <c r="BM61">
-        <v>2.05</v>
-      </c>
-      <c r="BN61">
-        <v>1.7</v>
-      </c>
-      <c r="BO61">
-        <v>2.64</v>
-      </c>
       <c r="BP61">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="62" spans="1:68">
@@ -13441,7 +13453,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>7778135</v>
+        <v>7778138</v>
       </c>
       <c r="C62" t="s">
         <v>68</v>
@@ -13450,196 +13462,196 @@
         <v>69</v>
       </c>
       <c r="E62" s="2">
-        <v>45745.08333333334</v>
+        <v>45745.04166666666</v>
       </c>
       <c r="F62">
         <v>7</v>
       </c>
       <c r="G62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O62" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="P62" t="s">
         <v>91</v>
       </c>
       <c r="Q62">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R62">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S62">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T62">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="U62">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V62">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="W62">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X62">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y62">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="AA62">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="AB62">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="AC62">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AD62">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AE62">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AF62">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AG62">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH62">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI62">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ62">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AK62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL62">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM62">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AN62">
         <v>1.33</v>
       </c>
       <c r="AO62">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
         <v>1.25</v>
       </c>
       <c r="AR62">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AT62">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AU62">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV62">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW62">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX62">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY62">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ62">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA62">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB62">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC62">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD62">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BE62">
-        <v>6.85</v>
+        <v>6.7</v>
       </c>
       <c r="BF62">
-        <v>3.18</v>
+        <v>2.41</v>
       </c>
       <c r="BG62">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BH62">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BI62">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BJ62">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="BK62">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="BL62">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="BM62">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BN62">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="BO62">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="BP62">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="63" spans="1:68">
@@ -13647,7 +13659,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>7778137</v>
+        <v>7778135</v>
       </c>
       <c r="C63" t="s">
         <v>68</v>
@@ -13662,160 +13674,160 @@
         <v>7</v>
       </c>
       <c r="G63" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="Q63">
         <v>3.25</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S63">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T63">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="W63">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X63">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y63">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z63">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AA63">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="AB63">
-        <v>2.74</v>
+        <v>3.11</v>
       </c>
       <c r="AC63">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AD63">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AE63">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AF63">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AG63">
+        <v>2.67</v>
+      </c>
+      <c r="AH63">
+        <v>1.44</v>
+      </c>
+      <c r="AI63">
         <v>2.2</v>
       </c>
-      <c r="AH63">
-        <v>1.6</v>
-      </c>
-      <c r="AI63">
-        <v>2</v>
-      </c>
       <c r="AJ63">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK63">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AL63">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AM63">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AN63">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO63">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS63">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AT63">
-        <v>3.38</v>
+        <v>2.49</v>
       </c>
       <c r="AU63">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV63">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW63">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX63">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AY63">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ63">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA63">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB63">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC63">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD63">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="BE63">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="BF63">
-        <v>2.69</v>
+        <v>3.18</v>
       </c>
       <c r="BG63">
         <v>1.23</v>
@@ -13824,25 +13836,25 @@
         <v>3.42</v>
       </c>
       <c r="BI63">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BJ63">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="BK63">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BL63">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="BM63">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BN63">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BO63">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="BP63">
         <v>1.28</v>
@@ -13853,7 +13865,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>7778134</v>
+        <v>7778137</v>
       </c>
       <c r="C64" t="s">
         <v>68</v>
@@ -13862,61 +13874,61 @@
         <v>69</v>
       </c>
       <c r="E64" s="2">
-        <v>45745.125</v>
+        <v>45745.08333333334</v>
       </c>
       <c r="F64">
         <v>7</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I64">
         <v>1</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O64" t="s">
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="Q64">
+        <v>3.25</v>
+      </c>
+      <c r="R64">
+        <v>2</v>
+      </c>
+      <c r="S64">
+        <v>3.75</v>
+      </c>
+      <c r="T64">
+        <v>1.5</v>
+      </c>
+      <c r="U64">
+        <v>2.5</v>
+      </c>
+      <c r="V64">
         <v>3.5</v>
       </c>
-      <c r="R64">
-        <v>1.95</v>
-      </c>
-      <c r="S64">
-        <v>3.6</v>
-      </c>
-      <c r="T64">
-        <v>1.53</v>
-      </c>
-      <c r="U64">
-        <v>2.38</v>
-      </c>
-      <c r="V64">
-        <v>3.75</v>
-      </c>
       <c r="W64">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X64">
         <v>11</v>
@@ -13925,31 +13937,31 @@
         <v>1.05</v>
       </c>
       <c r="Z64">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AA64">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AB64">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AC64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AD64">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE64">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AF64">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH64">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI64">
         <v>2</v>
@@ -13961,97 +13973,97 @@
         <v>1.42</v>
       </c>
       <c r="AL64">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM64">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AN64">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AO64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR64">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AS64">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AT64">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AU64">
+        <v>6</v>
+      </c>
+      <c r="AV64">
+        <v>6</v>
+      </c>
+      <c r="AW64">
+        <v>4</v>
+      </c>
+      <c r="AX64">
+        <v>12</v>
+      </c>
+      <c r="AY64">
+        <v>10</v>
+      </c>
+      <c r="AZ64">
+        <v>18</v>
+      </c>
+      <c r="BA64">
+        <v>3</v>
+      </c>
+      <c r="BB64">
         <v>5</v>
       </c>
-      <c r="AV64">
-        <v>2</v>
-      </c>
-      <c r="AW64">
-        <v>5</v>
-      </c>
-      <c r="AX64">
-        <v>5</v>
-      </c>
-      <c r="AY64">
-        <v>12</v>
-      </c>
-      <c r="AZ64">
-        <v>7</v>
-      </c>
-      <c r="BA64">
-        <v>6</v>
-      </c>
-      <c r="BB64">
-        <v>7</v>
-      </c>
       <c r="BC64">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD64">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="BE64">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="BF64">
-        <v>2.08</v>
+        <v>2.69</v>
       </c>
       <c r="BG64">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BH64">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="BI64">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BJ64">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="BK64">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="BL64">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BM64">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="BN64">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BO64">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="BP64">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="65" spans="1:68">
@@ -14059,7 +14071,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>7778136</v>
+        <v>7778139</v>
       </c>
       <c r="C65" t="s">
         <v>68</v>
@@ -14068,195 +14080,1019 @@
         <v>69</v>
       </c>
       <c r="E65" s="2">
-        <v>45745.20833333334</v>
+        <v>45745.08333333334</v>
       </c>
       <c r="F65">
         <v>7</v>
       </c>
       <c r="G65" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N65">
         <v>3</v>
       </c>
       <c r="O65" t="s">
+        <v>134</v>
+      </c>
+      <c r="P65" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q65">
+        <v>3.25</v>
+      </c>
+      <c r="R65">
+        <v>1.83</v>
+      </c>
+      <c r="S65">
+        <v>4.33</v>
+      </c>
+      <c r="T65">
+        <v>1.62</v>
+      </c>
+      <c r="U65">
+        <v>2.2</v>
+      </c>
+      <c r="V65">
+        <v>4</v>
+      </c>
+      <c r="W65">
+        <v>1.22</v>
+      </c>
+      <c r="X65">
+        <v>15</v>
+      </c>
+      <c r="Y65">
+        <v>1.03</v>
+      </c>
+      <c r="Z65">
+        <v>2.34</v>
+      </c>
+      <c r="AA65">
+        <v>2.91</v>
+      </c>
+      <c r="AB65">
+        <v>3.34</v>
+      </c>
+      <c r="AC65">
+        <v>1.12</v>
+      </c>
+      <c r="AD65">
+        <v>5.75</v>
+      </c>
+      <c r="AE65">
+        <v>1.55</v>
+      </c>
+      <c r="AF65">
+        <v>2.2</v>
+      </c>
+      <c r="AG65">
+        <v>2.82</v>
+      </c>
+      <c r="AH65">
+        <v>1.4</v>
+      </c>
+      <c r="AI65">
+        <v>2.25</v>
+      </c>
+      <c r="AJ65">
+        <v>1.57</v>
+      </c>
+      <c r="AK65">
+        <v>1.3</v>
+      </c>
+      <c r="AL65">
+        <v>1.35</v>
+      </c>
+      <c r="AM65">
+        <v>1.55</v>
+      </c>
+      <c r="AN65">
+        <v>0.5</v>
+      </c>
+      <c r="AO65">
+        <v>0.5</v>
+      </c>
+      <c r="AP65">
+        <v>1.33</v>
+      </c>
+      <c r="AQ65">
+        <v>0.33</v>
+      </c>
+      <c r="AR65">
+        <v>1.08</v>
+      </c>
+      <c r="AS65">
+        <v>1.22</v>
+      </c>
+      <c r="AT65">
+        <v>2.3</v>
+      </c>
+      <c r="AU65">
+        <v>5</v>
+      </c>
+      <c r="AV65">
+        <v>4</v>
+      </c>
+      <c r="AW65">
+        <v>2</v>
+      </c>
+      <c r="AX65">
+        <v>5</v>
+      </c>
+      <c r="AY65">
+        <v>8</v>
+      </c>
+      <c r="AZ65">
+        <v>10</v>
+      </c>
+      <c r="BA65">
+        <v>2</v>
+      </c>
+      <c r="BB65">
+        <v>5</v>
+      </c>
+      <c r="BC65">
+        <v>7</v>
+      </c>
+      <c r="BD65">
+        <v>2.84</v>
+      </c>
+      <c r="BE65">
+        <v>6.7</v>
+      </c>
+      <c r="BF65">
+        <v>1.69</v>
+      </c>
+      <c r="BG65">
+        <v>1.24</v>
+      </c>
+      <c r="BH65">
+        <v>3.34</v>
+      </c>
+      <c r="BI65">
+        <v>1.48</v>
+      </c>
+      <c r="BJ65">
+        <v>2.4</v>
+      </c>
+      <c r="BK65">
+        <v>1.85</v>
+      </c>
+      <c r="BL65">
+        <v>1.85</v>
+      </c>
+      <c r="BM65">
+        <v>2.38</v>
+      </c>
+      <c r="BN65">
+        <v>1.49</v>
+      </c>
+      <c r="BO65">
+        <v>3.14</v>
+      </c>
+      <c r="BP65">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7778140</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F66">
+        <v>7</v>
+      </c>
+      <c r="G66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s">
+        <v>87</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>100</v>
+      </c>
+      <c r="P66" t="s">
         <v>91</v>
       </c>
-      <c r="P65" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q65">
+      <c r="Q66">
         <v>4.33</v>
       </c>
-      <c r="R65">
+      <c r="R66">
+        <v>2.1</v>
+      </c>
+      <c r="S66">
+        <v>2.63</v>
+      </c>
+      <c r="T66">
+        <v>1.4</v>
+      </c>
+      <c r="U66">
+        <v>2.75</v>
+      </c>
+      <c r="V66">
+        <v>3</v>
+      </c>
+      <c r="W66">
+        <v>1.36</v>
+      </c>
+      <c r="X66">
+        <v>8</v>
+      </c>
+      <c r="Y66">
+        <v>1.08</v>
+      </c>
+      <c r="Z66">
+        <v>3.79</v>
+      </c>
+      <c r="AA66">
+        <v>3.5</v>
+      </c>
+      <c r="AB66">
+        <v>1.93</v>
+      </c>
+      <c r="AC66">
+        <v>1.06</v>
+      </c>
+      <c r="AD66">
+        <v>8.5</v>
+      </c>
+      <c r="AE66">
+        <v>1.33</v>
+      </c>
+      <c r="AF66">
+        <v>3.3</v>
+      </c>
+      <c r="AG66">
+        <v>1.98</v>
+      </c>
+      <c r="AH66">
+        <v>1.77</v>
+      </c>
+      <c r="AI66">
+        <v>1.8</v>
+      </c>
+      <c r="AJ66">
+        <v>1.95</v>
+      </c>
+      <c r="AK66">
+        <v>1.8</v>
+      </c>
+      <c r="AL66">
+        <v>1.25</v>
+      </c>
+      <c r="AM66">
+        <v>1.25</v>
+      </c>
+      <c r="AN66">
+        <v>0.5</v>
+      </c>
+      <c r="AO66">
+        <v>2</v>
+      </c>
+      <c r="AP66">
+        <v>1.33</v>
+      </c>
+      <c r="AQ66">
+        <v>1.33</v>
+      </c>
+      <c r="AR66">
+        <v>1.43</v>
+      </c>
+      <c r="AS66">
+        <v>1.64</v>
+      </c>
+      <c r="AT66">
+        <v>3.07</v>
+      </c>
+      <c r="AU66">
+        <v>3</v>
+      </c>
+      <c r="AV66">
+        <v>4</v>
+      </c>
+      <c r="AW66">
+        <v>4</v>
+      </c>
+      <c r="AX66">
+        <v>13</v>
+      </c>
+      <c r="AY66">
+        <v>7</v>
+      </c>
+      <c r="AZ66">
+        <v>22</v>
+      </c>
+      <c r="BA66">
+        <v>1</v>
+      </c>
+      <c r="BB66">
+        <v>9</v>
+      </c>
+      <c r="BC66">
+        <v>10</v>
+      </c>
+      <c r="BD66">
+        <v>3.18</v>
+      </c>
+      <c r="BE66">
+        <v>7.1</v>
+      </c>
+      <c r="BF66">
+        <v>1.57</v>
+      </c>
+      <c r="BG66">
+        <v>1.26</v>
+      </c>
+      <c r="BH66">
+        <v>3.25</v>
+      </c>
+      <c r="BI66">
+        <v>1.32</v>
+      </c>
+      <c r="BJ66">
+        <v>2.88</v>
+      </c>
+      <c r="BK66">
+        <v>1.6</v>
+      </c>
+      <c r="BL66">
+        <v>2.14</v>
+      </c>
+      <c r="BM66">
+        <v>2.05</v>
+      </c>
+      <c r="BN66">
+        <v>1.7</v>
+      </c>
+      <c r="BO66">
+        <v>2.6</v>
+      </c>
+      <c r="BP66">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7778134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45745.125</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
+        <v>86</v>
+      </c>
+      <c r="H67" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>135</v>
+      </c>
+      <c r="P67" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q67">
+        <v>3.5</v>
+      </c>
+      <c r="R67">
+        <v>1.95</v>
+      </c>
+      <c r="S67">
+        <v>3.6</v>
+      </c>
+      <c r="T67">
+        <v>1.53</v>
+      </c>
+      <c r="U67">
+        <v>2.38</v>
+      </c>
+      <c r="V67">
+        <v>3.75</v>
+      </c>
+      <c r="W67">
+        <v>1.25</v>
+      </c>
+      <c r="X67">
+        <v>11</v>
+      </c>
+      <c r="Y67">
+        <v>1.05</v>
+      </c>
+      <c r="Z67">
+        <v>2.64</v>
+      </c>
+      <c r="AA67">
+        <v>3.04</v>
+      </c>
+      <c r="AB67">
+        <v>2.76</v>
+      </c>
+      <c r="AC67">
+        <v>1.1</v>
+      </c>
+      <c r="AD67">
+        <v>6.5</v>
+      </c>
+      <c r="AE67">
+        <v>1.48</v>
+      </c>
+      <c r="AF67">
+        <v>2.6</v>
+      </c>
+      <c r="AG67">
+        <v>2.3</v>
+      </c>
+      <c r="AH67">
+        <v>1.5</v>
+      </c>
+      <c r="AI67">
+        <v>2</v>
+      </c>
+      <c r="AJ67">
+        <v>1.75</v>
+      </c>
+      <c r="AK67">
+        <v>1.42</v>
+      </c>
+      <c r="AL67">
+        <v>1.33</v>
+      </c>
+      <c r="AM67">
+        <v>1.45</v>
+      </c>
+      <c r="AN67">
+        <v>2.5</v>
+      </c>
+      <c r="AO67">
+        <v>2</v>
+      </c>
+      <c r="AP67">
+        <v>2.6</v>
+      </c>
+      <c r="AQ67">
+        <v>1.33</v>
+      </c>
+      <c r="AR67">
+        <v>1.72</v>
+      </c>
+      <c r="AS67">
+        <v>1.58</v>
+      </c>
+      <c r="AT67">
+        <v>3.3</v>
+      </c>
+      <c r="AU67">
+        <v>5</v>
+      </c>
+      <c r="AV67">
+        <v>2</v>
+      </c>
+      <c r="AW67">
+        <v>5</v>
+      </c>
+      <c r="AX67">
+        <v>5</v>
+      </c>
+      <c r="AY67">
+        <v>12</v>
+      </c>
+      <c r="AZ67">
+        <v>7</v>
+      </c>
+      <c r="BA67">
+        <v>6</v>
+      </c>
+      <c r="BB67">
+        <v>7</v>
+      </c>
+      <c r="BC67">
+        <v>13</v>
+      </c>
+      <c r="BD67">
+        <v>2.19</v>
+      </c>
+      <c r="BE67">
+        <v>6.4</v>
+      </c>
+      <c r="BF67">
+        <v>2.08</v>
+      </c>
+      <c r="BG67">
+        <v>1.25</v>
+      </c>
+      <c r="BH67">
+        <v>3.28</v>
+      </c>
+      <c r="BI67">
+        <v>1.5</v>
+      </c>
+      <c r="BJ67">
+        <v>2.35</v>
+      </c>
+      <c r="BK67">
+        <v>1.91</v>
+      </c>
+      <c r="BL67">
+        <v>1.8</v>
+      </c>
+      <c r="BM67">
+        <v>2.42</v>
+      </c>
+      <c r="BN67">
+        <v>1.47</v>
+      </c>
+      <c r="BO67">
+        <v>3.2</v>
+      </c>
+      <c r="BP67">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7778142</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45745.125</v>
+      </c>
+      <c r="F68">
+        <v>7</v>
+      </c>
+      <c r="G68" t="s">
+        <v>71</v>
+      </c>
+      <c r="H68" t="s">
+        <v>78</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>2</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68">
+        <v>4</v>
+      </c>
+      <c r="O68" t="s">
+        <v>136</v>
+      </c>
+      <c r="P68" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q68">
+        <v>4.5</v>
+      </c>
+      <c r="R68">
+        <v>1.8</v>
+      </c>
+      <c r="S68">
+        <v>3.25</v>
+      </c>
+      <c r="T68">
+        <v>1.67</v>
+      </c>
+      <c r="U68">
+        <v>2.1</v>
+      </c>
+      <c r="V68">
+        <v>4.5</v>
+      </c>
+      <c r="W68">
+        <v>1.18</v>
+      </c>
+      <c r="X68">
+        <v>15</v>
+      </c>
+      <c r="Y68">
+        <v>1.03</v>
+      </c>
+      <c r="Z68">
+        <v>3.3</v>
+      </c>
+      <c r="AA68">
+        <v>2.84</v>
+      </c>
+      <c r="AB68">
+        <v>2.41</v>
+      </c>
+      <c r="AC68">
+        <v>1.14</v>
+      </c>
+      <c r="AD68">
+        <v>5.5</v>
+      </c>
+      <c r="AE68">
+        <v>1.61</v>
+      </c>
+      <c r="AF68">
+        <v>2.05</v>
+      </c>
+      <c r="AG68">
+        <v>3.09</v>
+      </c>
+      <c r="AH68">
+        <v>1.34</v>
+      </c>
+      <c r="AI68">
+        <v>2.5</v>
+      </c>
+      <c r="AJ68">
+        <v>1.5</v>
+      </c>
+      <c r="AK68">
+        <v>1.57</v>
+      </c>
+      <c r="AL68">
+        <v>1.35</v>
+      </c>
+      <c r="AM68">
+        <v>1.3</v>
+      </c>
+      <c r="AN68">
+        <v>1</v>
+      </c>
+      <c r="AO68">
+        <v>3</v>
+      </c>
+      <c r="AP68">
+        <v>1</v>
+      </c>
+      <c r="AQ68">
+        <v>2.5</v>
+      </c>
+      <c r="AR68">
+        <v>1.51</v>
+      </c>
+      <c r="AS68">
+        <v>1.18</v>
+      </c>
+      <c r="AT68">
+        <v>2.69</v>
+      </c>
+      <c r="AU68">
+        <v>7</v>
+      </c>
+      <c r="AV68">
+        <v>6</v>
+      </c>
+      <c r="AW68">
+        <v>6</v>
+      </c>
+      <c r="AX68">
+        <v>7</v>
+      </c>
+      <c r="AY68">
+        <v>15</v>
+      </c>
+      <c r="AZ68">
+        <v>13</v>
+      </c>
+      <c r="BA68">
+        <v>5</v>
+      </c>
+      <c r="BB68">
+        <v>4</v>
+      </c>
+      <c r="BC68">
+        <v>9</v>
+      </c>
+      <c r="BD68">
+        <v>2.76</v>
+      </c>
+      <c r="BE68">
+        <v>6.25</v>
+      </c>
+      <c r="BF68">
+        <v>1.75</v>
+      </c>
+      <c r="BG68">
+        <v>1.52</v>
+      </c>
+      <c r="BH68">
+        <v>2.3</v>
+      </c>
+      <c r="BI68">
+        <v>1.91</v>
+      </c>
+      <c r="BJ68">
+        <v>1.8</v>
+      </c>
+      <c r="BK68">
+        <v>2.05</v>
+      </c>
+      <c r="BL68">
+        <v>1.7</v>
+      </c>
+      <c r="BM68">
+        <v>3.5</v>
+      </c>
+      <c r="BN68">
+        <v>1.22</v>
+      </c>
+      <c r="BO68">
+        <v>3.95</v>
+      </c>
+      <c r="BP68">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7778136</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45745.20833333334</v>
+      </c>
+      <c r="F69">
+        <v>7</v>
+      </c>
+      <c r="G69" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>3</v>
+      </c>
+      <c r="N69">
+        <v>3</v>
+      </c>
+      <c r="O69" t="s">
+        <v>91</v>
+      </c>
+      <c r="P69" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q69">
+        <v>4.33</v>
+      </c>
+      <c r="R69">
         <v>2.2</v>
       </c>
-      <c r="S65">
+      <c r="S69">
         <v>2.6</v>
       </c>
-      <c r="T65">
+      <c r="T69">
         <v>1.4</v>
       </c>
-      <c r="U65">
+      <c r="U69">
         <v>2.75</v>
       </c>
-      <c r="V65">
+      <c r="V69">
         <v>3</v>
       </c>
-      <c r="W65">
+      <c r="W69">
         <v>1.36</v>
       </c>
-      <c r="X65">
+      <c r="X69">
         <v>8</v>
       </c>
-      <c r="Y65">
+      <c r="Y69">
         <v>1.08</v>
       </c>
-      <c r="Z65">
+      <c r="Z69">
         <v>3.69</v>
       </c>
-      <c r="AA65">
+      <c r="AA69">
         <v>3.45</v>
       </c>
-      <c r="AB65">
+      <c r="AB69">
         <v>1.96</v>
       </c>
-      <c r="AC65">
+      <c r="AC69">
         <v>1.06</v>
       </c>
-      <c r="AD65">
+      <c r="AD69">
         <v>8.5</v>
       </c>
-      <c r="AE65">
+      <c r="AE69">
         <v>1.3</v>
       </c>
-      <c r="AF65">
+      <c r="AF69">
         <v>3.35</v>
       </c>
-      <c r="AG65">
+      <c r="AG69">
         <v>1.89</v>
       </c>
-      <c r="AH65">
+      <c r="AH69">
         <v>1.85</v>
       </c>
-      <c r="AI65">
+      <c r="AI69">
         <v>1.75</v>
       </c>
-      <c r="AJ65">
-        <v>2</v>
-      </c>
-      <c r="AK65">
+      <c r="AJ69">
+        <v>2</v>
+      </c>
+      <c r="AK69">
         <v>1.77</v>
       </c>
-      <c r="AL65">
+      <c r="AL69">
         <v>1.25</v>
       </c>
-      <c r="AM65">
+      <c r="AM69">
         <v>1.25</v>
       </c>
-      <c r="AN65">
+      <c r="AN69">
         <v>1.33</v>
       </c>
-      <c r="AO65">
+      <c r="AO69">
         <v>1.67</v>
       </c>
-      <c r="AP65">
-        <v>1</v>
-      </c>
-      <c r="AQ65">
-        <v>2</v>
-      </c>
-      <c r="AR65">
+      <c r="AP69">
+        <v>1</v>
+      </c>
+      <c r="AQ69">
+        <v>2</v>
+      </c>
+      <c r="AR69">
         <v>1.38</v>
       </c>
-      <c r="AS65">
+      <c r="AS69">
         <v>1.32</v>
       </c>
-      <c r="AT65">
+      <c r="AT69">
         <v>2.7</v>
       </c>
-      <c r="AU65">
-        <v>-1</v>
-      </c>
-      <c r="AV65">
-        <v>-1</v>
-      </c>
-      <c r="AW65">
-        <v>-1</v>
-      </c>
-      <c r="AX65">
-        <v>-1</v>
-      </c>
-      <c r="AY65">
-        <v>-1</v>
-      </c>
-      <c r="AZ65">
-        <v>-1</v>
-      </c>
-      <c r="BA65">
-        <v>-1</v>
-      </c>
-      <c r="BB65">
-        <v>-1</v>
-      </c>
-      <c r="BC65">
-        <v>-1</v>
-      </c>
-      <c r="BD65">
+      <c r="AU69">
+        <v>3</v>
+      </c>
+      <c r="AV69">
+        <v>7</v>
+      </c>
+      <c r="AW69">
+        <v>7</v>
+      </c>
+      <c r="AX69">
+        <v>5</v>
+      </c>
+      <c r="AY69">
+        <v>10</v>
+      </c>
+      <c r="AZ69">
+        <v>12</v>
+      </c>
+      <c r="BA69">
+        <v>6</v>
+      </c>
+      <c r="BB69">
+        <v>3</v>
+      </c>
+      <c r="BC69">
+        <v>9</v>
+      </c>
+      <c r="BD69">
         <v>2.59</v>
       </c>
-      <c r="BE65">
+      <c r="BE69">
         <v>6.6</v>
       </c>
-      <c r="BF65">
+      <c r="BF69">
         <v>1.8</v>
       </c>
-      <c r="BG65">
+      <c r="BG69">
         <v>1.21</v>
       </c>
-      <c r="BH65">
+      <c r="BH69">
         <v>3.58</v>
       </c>
-      <c r="BI65">
+      <c r="BI69">
         <v>1.43</v>
       </c>
-      <c r="BJ65">
+      <c r="BJ69">
         <v>2.54</v>
       </c>
-      <c r="BK65">
+      <c r="BK69">
         <v>1.77</v>
       </c>
-      <c r="BL65">
+      <c r="BL69">
         <v>1.95</v>
       </c>
-      <c r="BM65">
+      <c r="BM69">
         <v>2.23</v>
       </c>
-      <c r="BN65">
+      <c r="BN69">
         <v>1.55</v>
       </c>
-      <c r="BO65">
+      <c r="BO69">
         <v>2.92</v>
       </c>
-      <c r="BP65">
+      <c r="BP69">
         <v>1.31</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="179">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,27 @@
     <t>['22', '65']</t>
   </si>
   <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['3', '45+3']</t>
+  </si>
+  <si>
+    <t>['90+8']</t>
+  </si>
+  <si>
+    <t>['51', '84']</t>
+  </si>
+  <si>
+    <t>['50', '90+2']</t>
+  </si>
+  <si>
+    <t>['20', '52']</t>
+  </si>
+  <si>
+    <t>['4', '59']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -518,6 +539,18 @@
   </si>
   <si>
     <t>['55', '72', '83']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['43', '89']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['79']</t>
   </si>
 </sst>
 </file>
@@ -879,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP69"/>
+  <dimension ref="A1:BP79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1135,7 +1168,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1213,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1422,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1753,7 +1786,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1831,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2449,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>0.25</v>
@@ -2658,7 +2691,7 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2783,7 +2816,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -2989,7 +3022,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3070,7 +3103,7 @@
         <v>1</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3195,7 +3228,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3273,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3401,7 +3434,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3685,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -4019,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4097,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -4225,7 +4258,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4303,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4431,7 +4464,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4509,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR18">
         <v>2.07</v>
@@ -4718,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5127,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21">
         <v>0</v>
@@ -5255,7 +5288,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5667,7 +5700,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5873,7 +5906,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -6079,7 +6112,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6285,7 +6318,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6491,7 +6524,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6903,7 +6936,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7315,7 +7348,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7396,7 +7429,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.12</v>
@@ -7805,7 +7838,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
         <v>1.75</v>
@@ -7933,7 +7966,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8014,7 +8047,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR35">
         <v>1.47</v>
@@ -8139,7 +8172,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8345,7 +8378,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8423,7 +8456,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -8551,7 +8584,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8629,10 +8662,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ38">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -8757,7 +8790,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -8838,7 +8871,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -9041,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ40">
         <v>0.33</v>
@@ -9169,7 +9202,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9247,10 +9280,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>0</v>
@@ -9453,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>0</v>
@@ -9581,7 +9614,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -9659,7 +9692,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ43">
         <v>1.25</v>
@@ -9865,10 +9898,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.53</v>
@@ -10074,7 +10107,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.37</v>
@@ -10199,7 +10232,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10277,10 +10310,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ46">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10405,7 +10438,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10483,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47">
         <v>0.25</v>
@@ -10611,7 +10644,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -10692,7 +10725,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.45</v>
@@ -10817,7 +10850,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -10895,10 +10928,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11101,7 +11134,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11435,7 +11468,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11847,7 +11880,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12465,7 +12498,7 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -12543,10 +12576,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.46</v>
@@ -12877,7 +12910,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -12958,7 +12991,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13083,7 +13116,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13161,7 +13194,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ60">
         <v>0.8</v>
@@ -13576,7 +13609,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -13907,7 +13940,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -13985,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14191,7 +14224,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
         <v>0.33</v>
@@ -14397,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
@@ -14606,7 +14639,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ67">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR67">
         <v>1.72</v>
@@ -14731,7 +14764,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -14812,7 +14845,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR68">
         <v>1.51</v>
@@ -14937,7 +14970,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15094,6 +15127,2066 @@
       </c>
       <c r="BP69">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7778152</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+      <c r="G70" t="s">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s">
+        <v>86</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>137</v>
+      </c>
+      <c r="P70" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q70">
+        <v>2.5</v>
+      </c>
+      <c r="R70">
+        <v>2.1</v>
+      </c>
+      <c r="S70">
+        <v>4.75</v>
+      </c>
+      <c r="T70">
+        <v>1.44</v>
+      </c>
+      <c r="U70">
+        <v>2.63</v>
+      </c>
+      <c r="V70">
+        <v>3.25</v>
+      </c>
+      <c r="W70">
+        <v>1.33</v>
+      </c>
+      <c r="X70">
+        <v>9</v>
+      </c>
+      <c r="Y70">
+        <v>1.07</v>
+      </c>
+      <c r="Z70">
+        <v>1.82</v>
+      </c>
+      <c r="AA70">
+        <v>3.63</v>
+      </c>
+      <c r="AB70">
+        <v>4.1</v>
+      </c>
+      <c r="AC70">
+        <v>1.06</v>
+      </c>
+      <c r="AD70">
+        <v>8.5</v>
+      </c>
+      <c r="AE70">
+        <v>1.35</v>
+      </c>
+      <c r="AF70">
+        <v>3.1</v>
+      </c>
+      <c r="AG70">
+        <v>1.95</v>
+      </c>
+      <c r="AH70">
+        <v>1.7</v>
+      </c>
+      <c r="AI70">
+        <v>1.95</v>
+      </c>
+      <c r="AJ70">
+        <v>1.8</v>
+      </c>
+      <c r="AK70">
+        <v>1.22</v>
+      </c>
+      <c r="AL70">
+        <v>1.29</v>
+      </c>
+      <c r="AM70">
+        <v>1.9</v>
+      </c>
+      <c r="AN70">
+        <v>2.33</v>
+      </c>
+      <c r="AO70">
+        <v>1.5</v>
+      </c>
+      <c r="AP70">
+        <v>2.5</v>
+      </c>
+      <c r="AQ70">
+        <v>1</v>
+      </c>
+      <c r="AR70">
+        <v>1.48</v>
+      </c>
+      <c r="AS70">
+        <v>1.69</v>
+      </c>
+      <c r="AT70">
+        <v>3.17</v>
+      </c>
+      <c r="AU70">
+        <v>4</v>
+      </c>
+      <c r="AV70">
+        <v>2</v>
+      </c>
+      <c r="AW70">
+        <v>9</v>
+      </c>
+      <c r="AX70">
+        <v>14</v>
+      </c>
+      <c r="AY70">
+        <v>16</v>
+      </c>
+      <c r="AZ70">
+        <v>22</v>
+      </c>
+      <c r="BA70">
+        <v>5</v>
+      </c>
+      <c r="BB70">
+        <v>8</v>
+      </c>
+      <c r="BC70">
+        <v>13</v>
+      </c>
+      <c r="BD70">
+        <v>1.53</v>
+      </c>
+      <c r="BE70">
+        <v>6.75</v>
+      </c>
+      <c r="BF70">
+        <v>2.8</v>
+      </c>
+      <c r="BG70">
+        <v>1.37</v>
+      </c>
+      <c r="BH70">
+        <v>2.7</v>
+      </c>
+      <c r="BI70">
+        <v>1.64</v>
+      </c>
+      <c r="BJ70">
+        <v>2.04</v>
+      </c>
+      <c r="BK70">
+        <v>2.02</v>
+      </c>
+      <c r="BL70">
+        <v>1.65</v>
+      </c>
+      <c r="BM70">
+        <v>2.63</v>
+      </c>
+      <c r="BN70">
+        <v>1.4</v>
+      </c>
+      <c r="BO70">
+        <v>3.45</v>
+      </c>
+      <c r="BP70">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7778151</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="G71" t="s">
+        <v>84</v>
+      </c>
+      <c r="H71" t="s">
+        <v>74</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71" t="s">
+        <v>138</v>
+      </c>
+      <c r="P71" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q71">
+        <v>2.88</v>
+      </c>
+      <c r="R71">
+        <v>2.05</v>
+      </c>
+      <c r="S71">
+        <v>4</v>
+      </c>
+      <c r="T71">
+        <v>1.5</v>
+      </c>
+      <c r="U71">
+        <v>2.5</v>
+      </c>
+      <c r="V71">
+        <v>3.4</v>
+      </c>
+      <c r="W71">
+        <v>1.3</v>
+      </c>
+      <c r="X71">
+        <v>10</v>
+      </c>
+      <c r="Y71">
+        <v>1.06</v>
+      </c>
+      <c r="Z71">
+        <v>2.16</v>
+      </c>
+      <c r="AA71">
+        <v>3.27</v>
+      </c>
+      <c r="AB71">
+        <v>3.31</v>
+      </c>
+      <c r="AC71">
+        <v>1.07</v>
+      </c>
+      <c r="AD71">
+        <v>7.5</v>
+      </c>
+      <c r="AE71">
+        <v>1.38</v>
+      </c>
+      <c r="AF71">
+        <v>2.8</v>
+      </c>
+      <c r="AG71">
+        <v>2.1</v>
+      </c>
+      <c r="AH71">
+        <v>1.61</v>
+      </c>
+      <c r="AI71">
+        <v>1.95</v>
+      </c>
+      <c r="AJ71">
+        <v>1.8</v>
+      </c>
+      <c r="AK71">
+        <v>1.31</v>
+      </c>
+      <c r="AL71">
+        <v>1.32</v>
+      </c>
+      <c r="AM71">
+        <v>1.66</v>
+      </c>
+      <c r="AN71">
+        <v>0.67</v>
+      </c>
+      <c r="AO71">
+        <v>0</v>
+      </c>
+      <c r="AP71">
+        <v>1.25</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>1.83</v>
+      </c>
+      <c r="AS71">
+        <v>1.17</v>
+      </c>
+      <c r="AT71">
+        <v>3</v>
+      </c>
+      <c r="AU71">
+        <v>7</v>
+      </c>
+      <c r="AV71">
+        <v>6</v>
+      </c>
+      <c r="AW71">
+        <v>14</v>
+      </c>
+      <c r="AX71">
+        <v>11</v>
+      </c>
+      <c r="AY71">
+        <v>22</v>
+      </c>
+      <c r="AZ71">
+        <v>20</v>
+      </c>
+      <c r="BA71">
+        <v>5</v>
+      </c>
+      <c r="BB71">
+        <v>6</v>
+      </c>
+      <c r="BC71">
+        <v>11</v>
+      </c>
+      <c r="BD71">
+        <v>1.65</v>
+      </c>
+      <c r="BE71">
+        <v>6.75</v>
+      </c>
+      <c r="BF71">
+        <v>2.48</v>
+      </c>
+      <c r="BG71">
+        <v>1.26</v>
+      </c>
+      <c r="BH71">
+        <v>3.25</v>
+      </c>
+      <c r="BI71">
+        <v>1.47</v>
+      </c>
+      <c r="BJ71">
+        <v>2.38</v>
+      </c>
+      <c r="BK71">
+        <v>1.78</v>
+      </c>
+      <c r="BL71">
+        <v>1.86</v>
+      </c>
+      <c r="BM71">
+        <v>2.23</v>
+      </c>
+      <c r="BN71">
+        <v>1.54</v>
+      </c>
+      <c r="BO71">
+        <v>2.8</v>
+      </c>
+      <c r="BP71">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7778150</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="G72" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" t="s">
+        <v>78</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>91</v>
+      </c>
+      <c r="P72" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q72">
+        <v>4</v>
+      </c>
+      <c r="R72">
+        <v>1.95</v>
+      </c>
+      <c r="S72">
+        <v>3.25</v>
+      </c>
+      <c r="T72">
+        <v>1.57</v>
+      </c>
+      <c r="U72">
+        <v>2.25</v>
+      </c>
+      <c r="V72">
+        <v>3.75</v>
+      </c>
+      <c r="W72">
+        <v>1.25</v>
+      </c>
+      <c r="X72">
+        <v>11</v>
+      </c>
+      <c r="Y72">
+        <v>1.05</v>
+      </c>
+      <c r="Z72">
+        <v>3.12</v>
+      </c>
+      <c r="AA72">
+        <v>3.04</v>
+      </c>
+      <c r="AB72">
+        <v>2.38</v>
+      </c>
+      <c r="AC72">
+        <v>1.1</v>
+      </c>
+      <c r="AD72">
+        <v>6.5</v>
+      </c>
+      <c r="AE72">
+        <v>1.5</v>
+      </c>
+      <c r="AF72">
+        <v>2.55</v>
+      </c>
+      <c r="AG72">
+        <v>2.37</v>
+      </c>
+      <c r="AH72">
+        <v>1.48</v>
+      </c>
+      <c r="AI72">
+        <v>2.05</v>
+      </c>
+      <c r="AJ72">
+        <v>1.7</v>
+      </c>
+      <c r="AK72">
+        <v>1.55</v>
+      </c>
+      <c r="AL72">
+        <v>1.36</v>
+      </c>
+      <c r="AM72">
+        <v>1.35</v>
+      </c>
+      <c r="AN72">
+        <v>2</v>
+      </c>
+      <c r="AO72">
+        <v>2.5</v>
+      </c>
+      <c r="AP72">
+        <v>1.5</v>
+      </c>
+      <c r="AQ72">
+        <v>2.6</v>
+      </c>
+      <c r="AR72">
+        <v>1.64</v>
+      </c>
+      <c r="AS72">
+        <v>1.28</v>
+      </c>
+      <c r="AT72">
+        <v>2.92</v>
+      </c>
+      <c r="AU72">
+        <v>2</v>
+      </c>
+      <c r="AV72">
+        <v>3</v>
+      </c>
+      <c r="AW72">
+        <v>8</v>
+      </c>
+      <c r="AX72">
+        <v>9</v>
+      </c>
+      <c r="AY72">
+        <v>13</v>
+      </c>
+      <c r="AZ72">
+        <v>13</v>
+      </c>
+      <c r="BA72">
+        <v>3</v>
+      </c>
+      <c r="BB72">
+        <v>7</v>
+      </c>
+      <c r="BC72">
+        <v>10</v>
+      </c>
+      <c r="BD72">
+        <v>2.23</v>
+      </c>
+      <c r="BE72">
+        <v>6.4</v>
+      </c>
+      <c r="BF72">
+        <v>1.78</v>
+      </c>
+      <c r="BG72">
+        <v>1.33</v>
+      </c>
+      <c r="BH72">
+        <v>2.9</v>
+      </c>
+      <c r="BI72">
+        <v>1.56</v>
+      </c>
+      <c r="BJ72">
+        <v>2.17</v>
+      </c>
+      <c r="BK72">
+        <v>1.92</v>
+      </c>
+      <c r="BL72">
+        <v>1.74</v>
+      </c>
+      <c r="BM72">
+        <v>2.43</v>
+      </c>
+      <c r="BN72">
+        <v>1.46</v>
+      </c>
+      <c r="BO72">
+        <v>3.15</v>
+      </c>
+      <c r="BP72">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7778149</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s">
+        <v>81</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73" t="s">
+        <v>139</v>
+      </c>
+      <c r="P73" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q73">
+        <v>3.4</v>
+      </c>
+      <c r="R73">
+        <v>2.05</v>
+      </c>
+      <c r="S73">
+        <v>3.4</v>
+      </c>
+      <c r="T73">
+        <v>1.44</v>
+      </c>
+      <c r="U73">
+        <v>2.63</v>
+      </c>
+      <c r="V73">
+        <v>3.25</v>
+      </c>
+      <c r="W73">
+        <v>1.33</v>
+      </c>
+      <c r="X73">
+        <v>10</v>
+      </c>
+      <c r="Y73">
+        <v>1.06</v>
+      </c>
+      <c r="Z73">
+        <v>2.62</v>
+      </c>
+      <c r="AA73">
+        <v>3.1</v>
+      </c>
+      <c r="AB73">
+        <v>2.74</v>
+      </c>
+      <c r="AC73">
+        <v>1.07</v>
+      </c>
+      <c r="AD73">
+        <v>8</v>
+      </c>
+      <c r="AE73">
+        <v>1.38</v>
+      </c>
+      <c r="AF73">
+        <v>3</v>
+      </c>
+      <c r="AG73">
+        <v>2.05</v>
+      </c>
+      <c r="AH73">
+        <v>1.65</v>
+      </c>
+      <c r="AI73">
+        <v>1.8</v>
+      </c>
+      <c r="AJ73">
+        <v>1.95</v>
+      </c>
+      <c r="AK73">
+        <v>1.46</v>
+      </c>
+      <c r="AL73">
+        <v>1.34</v>
+      </c>
+      <c r="AM73">
+        <v>1.44</v>
+      </c>
+      <c r="AN73">
+        <v>1.33</v>
+      </c>
+      <c r="AO73">
+        <v>2.33</v>
+      </c>
+      <c r="AP73">
+        <v>1.25</v>
+      </c>
+      <c r="AQ73">
+        <v>2</v>
+      </c>
+      <c r="AR73">
+        <v>1.21</v>
+      </c>
+      <c r="AS73">
+        <v>1.22</v>
+      </c>
+      <c r="AT73">
+        <v>2.43</v>
+      </c>
+      <c r="AU73">
+        <v>4</v>
+      </c>
+      <c r="AV73">
+        <v>3</v>
+      </c>
+      <c r="AW73">
+        <v>13</v>
+      </c>
+      <c r="AX73">
+        <v>8</v>
+      </c>
+      <c r="AY73">
+        <v>17</v>
+      </c>
+      <c r="AZ73">
+        <v>11</v>
+      </c>
+      <c r="BA73">
+        <v>9</v>
+      </c>
+      <c r="BB73">
+        <v>2</v>
+      </c>
+      <c r="BC73">
+        <v>11</v>
+      </c>
+      <c r="BD73">
+        <v>1.93</v>
+      </c>
+      <c r="BE73">
+        <v>6.5</v>
+      </c>
+      <c r="BF73">
+        <v>2.05</v>
+      </c>
+      <c r="BG73">
+        <v>1.26</v>
+      </c>
+      <c r="BH73">
+        <v>3.3</v>
+      </c>
+      <c r="BI73">
+        <v>1.46</v>
+      </c>
+      <c r="BJ73">
+        <v>2.43</v>
+      </c>
+      <c r="BK73">
+        <v>1.74</v>
+      </c>
+      <c r="BL73">
+        <v>1.9</v>
+      </c>
+      <c r="BM73">
+        <v>2.16</v>
+      </c>
+      <c r="BN73">
+        <v>1.57</v>
+      </c>
+      <c r="BO73">
+        <v>2.75</v>
+      </c>
+      <c r="BP73">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7778148</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74" t="s">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s">
+        <v>75</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>2</v>
+      </c>
+      <c r="O74" t="s">
+        <v>140</v>
+      </c>
+      <c r="P74" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q74">
+        <v>3.2</v>
+      </c>
+      <c r="R74">
+        <v>2.1</v>
+      </c>
+      <c r="S74">
+        <v>3.4</v>
+      </c>
+      <c r="T74">
+        <v>1.4</v>
+      </c>
+      <c r="U74">
+        <v>2.75</v>
+      </c>
+      <c r="V74">
+        <v>3</v>
+      </c>
+      <c r="W74">
+        <v>1.36</v>
+      </c>
+      <c r="X74">
+        <v>9</v>
+      </c>
+      <c r="Y74">
+        <v>1.07</v>
+      </c>
+      <c r="Z74">
+        <v>2.55</v>
+      </c>
+      <c r="AA74">
+        <v>3.34</v>
+      </c>
+      <c r="AB74">
+        <v>2.64</v>
+      </c>
+      <c r="AC74">
+        <v>1.06</v>
+      </c>
+      <c r="AD74">
+        <v>8.5</v>
+      </c>
+      <c r="AE74">
+        <v>1.33</v>
+      </c>
+      <c r="AF74">
+        <v>3.25</v>
+      </c>
+      <c r="AG74">
+        <v>1.95</v>
+      </c>
+      <c r="AH74">
+        <v>1.79</v>
+      </c>
+      <c r="AI74">
+        <v>1.8</v>
+      </c>
+      <c r="AJ74">
+        <v>1.95</v>
+      </c>
+      <c r="AK74">
+        <v>1.46</v>
+      </c>
+      <c r="AL74">
+        <v>1.3</v>
+      </c>
+      <c r="AM74">
+        <v>1.49</v>
+      </c>
+      <c r="AN74">
+        <v>1.33</v>
+      </c>
+      <c r="AO74">
+        <v>0</v>
+      </c>
+      <c r="AP74">
+        <v>1.75</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>1.09</v>
+      </c>
+      <c r="AS74">
+        <v>1.26</v>
+      </c>
+      <c r="AT74">
+        <v>2.35</v>
+      </c>
+      <c r="AU74">
+        <v>9</v>
+      </c>
+      <c r="AV74">
+        <v>2</v>
+      </c>
+      <c r="AW74">
+        <v>13</v>
+      </c>
+      <c r="AX74">
+        <v>7</v>
+      </c>
+      <c r="AY74">
+        <v>27</v>
+      </c>
+      <c r="AZ74">
+        <v>12</v>
+      </c>
+      <c r="BA74">
+        <v>9</v>
+      </c>
+      <c r="BB74">
+        <v>7</v>
+      </c>
+      <c r="BC74">
+        <v>16</v>
+      </c>
+      <c r="BD74">
+        <v>1.88</v>
+      </c>
+      <c r="BE74">
+        <v>6.5</v>
+      </c>
+      <c r="BF74">
+        <v>2.1</v>
+      </c>
+      <c r="BG74">
+        <v>1.28</v>
+      </c>
+      <c r="BH74">
+        <v>3.15</v>
+      </c>
+      <c r="BI74">
+        <v>1.49</v>
+      </c>
+      <c r="BJ74">
+        <v>2.35</v>
+      </c>
+      <c r="BK74">
+        <v>1.8</v>
+      </c>
+      <c r="BL74">
+        <v>1.85</v>
+      </c>
+      <c r="BM74">
+        <v>2.25</v>
+      </c>
+      <c r="BN74">
+        <v>1.53</v>
+      </c>
+      <c r="BO74">
+        <v>2.9</v>
+      </c>
+      <c r="BP74">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7778147</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s">
+        <v>71</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>91</v>
+      </c>
+      <c r="P75" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q75">
+        <v>3.2</v>
+      </c>
+      <c r="R75">
+        <v>1.91</v>
+      </c>
+      <c r="S75">
+        <v>4.33</v>
+      </c>
+      <c r="T75">
+        <v>1.62</v>
+      </c>
+      <c r="U75">
+        <v>2.2</v>
+      </c>
+      <c r="V75">
+        <v>4</v>
+      </c>
+      <c r="W75">
+        <v>1.22</v>
+      </c>
+      <c r="X75">
+        <v>13</v>
+      </c>
+      <c r="Y75">
+        <v>1.04</v>
+      </c>
+      <c r="Z75">
+        <v>2.31</v>
+      </c>
+      <c r="AA75">
+        <v>3.08</v>
+      </c>
+      <c r="AB75">
+        <v>3.2</v>
+      </c>
+      <c r="AC75">
+        <v>1.1</v>
+      </c>
+      <c r="AD75">
+        <v>6.5</v>
+      </c>
+      <c r="AE75">
+        <v>1.5</v>
+      </c>
+      <c r="AF75">
+        <v>2.3</v>
+      </c>
+      <c r="AG75">
+        <v>2.63</v>
+      </c>
+      <c r="AH75">
+        <v>1.45</v>
+      </c>
+      <c r="AI75">
+        <v>2.2</v>
+      </c>
+      <c r="AJ75">
+        <v>1.62</v>
+      </c>
+      <c r="AK75">
+        <v>1.33</v>
+      </c>
+      <c r="AL75">
+        <v>1.35</v>
+      </c>
+      <c r="AM75">
+        <v>1.58</v>
+      </c>
+      <c r="AN75">
+        <v>1</v>
+      </c>
+      <c r="AO75">
+        <v>2</v>
+      </c>
+      <c r="AP75">
+        <v>0.75</v>
+      </c>
+      <c r="AQ75">
+        <v>2.25</v>
+      </c>
+      <c r="AR75">
+        <v>1.45</v>
+      </c>
+      <c r="AS75">
+        <v>1.84</v>
+      </c>
+      <c r="AT75">
+        <v>3.29</v>
+      </c>
+      <c r="AU75">
+        <v>6</v>
+      </c>
+      <c r="AV75">
+        <v>6</v>
+      </c>
+      <c r="AW75">
+        <v>12</v>
+      </c>
+      <c r="AX75">
+        <v>8</v>
+      </c>
+      <c r="AY75">
+        <v>24</v>
+      </c>
+      <c r="AZ75">
+        <v>17</v>
+      </c>
+      <c r="BA75">
+        <v>8</v>
+      </c>
+      <c r="BB75">
+        <v>5</v>
+      </c>
+      <c r="BC75">
+        <v>13</v>
+      </c>
+      <c r="BD75">
+        <v>1.68</v>
+      </c>
+      <c r="BE75">
+        <v>6.5</v>
+      </c>
+      <c r="BF75">
+        <v>2.4</v>
+      </c>
+      <c r="BG75">
+        <v>1.37</v>
+      </c>
+      <c r="BH75">
+        <v>2.7</v>
+      </c>
+      <c r="BI75">
+        <v>1.63</v>
+      </c>
+      <c r="BJ75">
+        <v>2.05</v>
+      </c>
+      <c r="BK75">
+        <v>2.02</v>
+      </c>
+      <c r="BL75">
+        <v>1.66</v>
+      </c>
+      <c r="BM75">
+        <v>2.6</v>
+      </c>
+      <c r="BN75">
+        <v>1.4</v>
+      </c>
+      <c r="BO75">
+        <v>3.4</v>
+      </c>
+      <c r="BP75">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7778145</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F76">
+        <v>8</v>
+      </c>
+      <c r="G76" t="s">
+        <v>76</v>
+      </c>
+      <c r="H76" t="s">
+        <v>77</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76" t="s">
+        <v>141</v>
+      </c>
+      <c r="P76" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q76">
+        <v>2.5</v>
+      </c>
+      <c r="R76">
+        <v>2.25</v>
+      </c>
+      <c r="S76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>1.33</v>
+      </c>
+      <c r="U76">
+        <v>3.25</v>
+      </c>
+      <c r="V76">
+        <v>2.63</v>
+      </c>
+      <c r="W76">
+        <v>1.44</v>
+      </c>
+      <c r="X76">
+        <v>6.5</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>1.9</v>
+      </c>
+      <c r="AA76">
+        <v>3.67</v>
+      </c>
+      <c r="AB76">
+        <v>3.67</v>
+      </c>
+      <c r="AC76">
+        <v>1.05</v>
+      </c>
+      <c r="AD76">
+        <v>9.5</v>
+      </c>
+      <c r="AE76">
+        <v>1.25</v>
+      </c>
+      <c r="AF76">
+        <v>3.95</v>
+      </c>
+      <c r="AG76">
+        <v>1.67</v>
+      </c>
+      <c r="AH76">
+        <v>2</v>
+      </c>
+      <c r="AI76">
+        <v>1.67</v>
+      </c>
+      <c r="AJ76">
+        <v>2.1</v>
+      </c>
+      <c r="AK76">
+        <v>1.27</v>
+      </c>
+      <c r="AL76">
+        <v>1.27</v>
+      </c>
+      <c r="AM76">
+        <v>1.83</v>
+      </c>
+      <c r="AN76">
+        <v>1.5</v>
+      </c>
+      <c r="AO76">
+        <v>1.25</v>
+      </c>
+      <c r="AP76">
+        <v>2</v>
+      </c>
+      <c r="AQ76">
+        <v>1</v>
+      </c>
+      <c r="AR76">
+        <v>1.89</v>
+      </c>
+      <c r="AS76">
+        <v>1.23</v>
+      </c>
+      <c r="AT76">
+        <v>3.12</v>
+      </c>
+      <c r="AU76">
+        <v>5</v>
+      </c>
+      <c r="AV76">
+        <v>0</v>
+      </c>
+      <c r="AW76">
+        <v>12</v>
+      </c>
+      <c r="AX76">
+        <v>6</v>
+      </c>
+      <c r="AY76">
+        <v>21</v>
+      </c>
+      <c r="AZ76">
+        <v>9</v>
+      </c>
+      <c r="BA76">
+        <v>9</v>
+      </c>
+      <c r="BB76">
+        <v>3</v>
+      </c>
+      <c r="BC76">
+        <v>12</v>
+      </c>
+      <c r="BD76">
+        <v>1.67</v>
+      </c>
+      <c r="BE76">
+        <v>6.75</v>
+      </c>
+      <c r="BF76">
+        <v>2.43</v>
+      </c>
+      <c r="BG76">
+        <v>1.22</v>
+      </c>
+      <c r="BH76">
+        <v>3.55</v>
+      </c>
+      <c r="BI76">
+        <v>1.4</v>
+      </c>
+      <c r="BJ76">
+        <v>2.63</v>
+      </c>
+      <c r="BK76">
+        <v>1.66</v>
+      </c>
+      <c r="BL76">
+        <v>2.02</v>
+      </c>
+      <c r="BM76">
+        <v>2.06</v>
+      </c>
+      <c r="BN76">
+        <v>1.63</v>
+      </c>
+      <c r="BO76">
+        <v>2.63</v>
+      </c>
+      <c r="BP76">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7778144</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F77">
+        <v>8</v>
+      </c>
+      <c r="G77" t="s">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s">
+        <v>85</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>4</v>
+      </c>
+      <c r="O77" t="s">
+        <v>142</v>
+      </c>
+      <c r="P77" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q77">
+        <v>3.1</v>
+      </c>
+      <c r="R77">
+        <v>1.91</v>
+      </c>
+      <c r="S77">
+        <v>4.5</v>
+      </c>
+      <c r="T77">
+        <v>1.62</v>
+      </c>
+      <c r="U77">
+        <v>2.2</v>
+      </c>
+      <c r="V77">
+        <v>4</v>
+      </c>
+      <c r="W77">
+        <v>1.22</v>
+      </c>
+      <c r="X77">
+        <v>13</v>
+      </c>
+      <c r="Y77">
+        <v>1.04</v>
+      </c>
+      <c r="Z77">
+        <v>2.17</v>
+      </c>
+      <c r="AA77">
+        <v>3.09</v>
+      </c>
+      <c r="AB77">
+        <v>3.5</v>
+      </c>
+      <c r="AC77">
+        <v>1.1</v>
+      </c>
+      <c r="AD77">
+        <v>6.5</v>
+      </c>
+      <c r="AE77">
+        <v>1.5</v>
+      </c>
+      <c r="AF77">
+        <v>2.3</v>
+      </c>
+      <c r="AG77">
+        <v>2.43</v>
+      </c>
+      <c r="AH77">
+        <v>1.52</v>
+      </c>
+      <c r="AI77">
+        <v>2.2</v>
+      </c>
+      <c r="AJ77">
+        <v>1.62</v>
+      </c>
+      <c r="AK77">
+        <v>1.32</v>
+      </c>
+      <c r="AL77">
+        <v>1.36</v>
+      </c>
+      <c r="AM77">
+        <v>1.58</v>
+      </c>
+      <c r="AN77">
+        <v>1</v>
+      </c>
+      <c r="AO77">
+        <v>1</v>
+      </c>
+      <c r="AP77">
+        <v>1</v>
+      </c>
+      <c r="AQ77">
+        <v>1</v>
+      </c>
+      <c r="AR77">
+        <v>1.28</v>
+      </c>
+      <c r="AS77">
+        <v>1.02</v>
+      </c>
+      <c r="AT77">
+        <v>2.3</v>
+      </c>
+      <c r="AU77">
+        <v>8</v>
+      </c>
+      <c r="AV77">
+        <v>4</v>
+      </c>
+      <c r="AW77">
+        <v>9</v>
+      </c>
+      <c r="AX77">
+        <v>5</v>
+      </c>
+      <c r="AY77">
+        <v>21</v>
+      </c>
+      <c r="AZ77">
+        <v>10</v>
+      </c>
+      <c r="BA77">
+        <v>6</v>
+      </c>
+      <c r="BB77">
+        <v>5</v>
+      </c>
+      <c r="BC77">
+        <v>11</v>
+      </c>
+      <c r="BD77">
+        <v>1.7</v>
+      </c>
+      <c r="BE77">
+        <v>6.5</v>
+      </c>
+      <c r="BF77">
+        <v>2.4</v>
+      </c>
+      <c r="BG77">
+        <v>1.36</v>
+      </c>
+      <c r="BH77">
+        <v>2.75</v>
+      </c>
+      <c r="BI77">
+        <v>1.62</v>
+      </c>
+      <c r="BJ77">
+        <v>2.08</v>
+      </c>
+      <c r="BK77">
+        <v>2</v>
+      </c>
+      <c r="BL77">
+        <v>1.67</v>
+      </c>
+      <c r="BM77">
+        <v>2.55</v>
+      </c>
+      <c r="BN77">
+        <v>1.41</v>
+      </c>
+      <c r="BO77">
+        <v>3.4</v>
+      </c>
+      <c r="BP77">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7778146</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45749.29166666666</v>
+      </c>
+      <c r="F78">
+        <v>8</v>
+      </c>
+      <c r="G78" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" t="s">
+        <v>72</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>91</v>
+      </c>
+      <c r="P78" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q78">
+        <v>4.33</v>
+      </c>
+      <c r="R78">
+        <v>1.91</v>
+      </c>
+      <c r="S78">
+        <v>3.1</v>
+      </c>
+      <c r="T78">
+        <v>1.57</v>
+      </c>
+      <c r="U78">
+        <v>2.25</v>
+      </c>
+      <c r="V78">
+        <v>3.75</v>
+      </c>
+      <c r="W78">
+        <v>1.25</v>
+      </c>
+      <c r="X78">
+        <v>13</v>
+      </c>
+      <c r="Y78">
+        <v>1.04</v>
+      </c>
+      <c r="Z78">
+        <v>3.47</v>
+      </c>
+      <c r="AA78">
+        <v>2.94</v>
+      </c>
+      <c r="AB78">
+        <v>2.27</v>
+      </c>
+      <c r="AC78">
+        <v>1.1</v>
+      </c>
+      <c r="AD78">
+        <v>6.25</v>
+      </c>
+      <c r="AE78">
+        <v>1.48</v>
+      </c>
+      <c r="AF78">
+        <v>2.37</v>
+      </c>
+      <c r="AG78">
+        <v>2.57</v>
+      </c>
+      <c r="AH78">
+        <v>1.47</v>
+      </c>
+      <c r="AI78">
+        <v>2.1</v>
+      </c>
+      <c r="AJ78">
+        <v>1.67</v>
+      </c>
+      <c r="AK78">
+        <v>1.61</v>
+      </c>
+      <c r="AL78">
+        <v>1.36</v>
+      </c>
+      <c r="AM78">
+        <v>1.3</v>
+      </c>
+      <c r="AN78">
+        <v>1.5</v>
+      </c>
+      <c r="AO78">
+        <v>1.33</v>
+      </c>
+      <c r="AP78">
+        <v>1.2</v>
+      </c>
+      <c r="AQ78">
+        <v>1.75</v>
+      </c>
+      <c r="AR78">
+        <v>1.29</v>
+      </c>
+      <c r="AS78">
+        <v>1.36</v>
+      </c>
+      <c r="AT78">
+        <v>2.65</v>
+      </c>
+      <c r="AU78">
+        <v>2</v>
+      </c>
+      <c r="AV78">
+        <v>3</v>
+      </c>
+      <c r="AW78">
+        <v>8</v>
+      </c>
+      <c r="AX78">
+        <v>8</v>
+      </c>
+      <c r="AY78">
+        <v>13</v>
+      </c>
+      <c r="AZ78">
+        <v>13</v>
+      </c>
+      <c r="BA78">
+        <v>5</v>
+      </c>
+      <c r="BB78">
+        <v>3</v>
+      </c>
+      <c r="BC78">
+        <v>8</v>
+      </c>
+      <c r="BD78">
+        <v>2.3</v>
+      </c>
+      <c r="BE78">
+        <v>6.5</v>
+      </c>
+      <c r="BF78">
+        <v>1.76</v>
+      </c>
+      <c r="BG78">
+        <v>1.32</v>
+      </c>
+      <c r="BH78">
+        <v>2.95</v>
+      </c>
+      <c r="BI78">
+        <v>1.55</v>
+      </c>
+      <c r="BJ78">
+        <v>2.2</v>
+      </c>
+      <c r="BK78">
+        <v>1.9</v>
+      </c>
+      <c r="BL78">
+        <v>1.75</v>
+      </c>
+      <c r="BM78">
+        <v>2.4</v>
+      </c>
+      <c r="BN78">
+        <v>1.46</v>
+      </c>
+      <c r="BO78">
+        <v>3.15</v>
+      </c>
+      <c r="BP78">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7778143</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45749.3125</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79" t="s">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s">
+        <v>82</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>3</v>
+      </c>
+      <c r="O79" t="s">
+        <v>143</v>
+      </c>
+      <c r="P79" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q79">
+        <v>2.75</v>
+      </c>
+      <c r="R79">
+        <v>2.05</v>
+      </c>
+      <c r="S79">
+        <v>4.33</v>
+      </c>
+      <c r="T79">
+        <v>1.44</v>
+      </c>
+      <c r="U79">
+        <v>2.63</v>
+      </c>
+      <c r="V79">
+        <v>3.4</v>
+      </c>
+      <c r="W79">
+        <v>1.3</v>
+      </c>
+      <c r="X79">
+        <v>10</v>
+      </c>
+      <c r="Y79">
+        <v>1.06</v>
+      </c>
+      <c r="Z79">
+        <v>2.05</v>
+      </c>
+      <c r="AA79">
+        <v>3.27</v>
+      </c>
+      <c r="AB79">
+        <v>3.63</v>
+      </c>
+      <c r="AC79">
+        <v>1.07</v>
+      </c>
+      <c r="AD79">
+        <v>8</v>
+      </c>
+      <c r="AE79">
+        <v>1.38</v>
+      </c>
+      <c r="AF79">
+        <v>3</v>
+      </c>
+      <c r="AG79">
+        <v>2.05</v>
+      </c>
+      <c r="AH79">
+        <v>1.65</v>
+      </c>
+      <c r="AI79">
+        <v>1.95</v>
+      </c>
+      <c r="AJ79">
+        <v>1.8</v>
+      </c>
+      <c r="AK79">
+        <v>1.28</v>
+      </c>
+      <c r="AL79">
+        <v>1.32</v>
+      </c>
+      <c r="AM79">
+        <v>1.71</v>
+      </c>
+      <c r="AN79">
+        <v>1.5</v>
+      </c>
+      <c r="AO79">
+        <v>1.33</v>
+      </c>
+      <c r="AP79">
+        <v>2</v>
+      </c>
+      <c r="AQ79">
+        <v>1</v>
+      </c>
+      <c r="AR79">
+        <v>1.78</v>
+      </c>
+      <c r="AS79">
+        <v>1.34</v>
+      </c>
+      <c r="AT79">
+        <v>3.12</v>
+      </c>
+      <c r="AU79">
+        <v>3</v>
+      </c>
+      <c r="AV79">
+        <v>6</v>
+      </c>
+      <c r="AW79">
+        <v>4</v>
+      </c>
+      <c r="AX79">
+        <v>10</v>
+      </c>
+      <c r="AY79">
+        <v>10</v>
+      </c>
+      <c r="AZ79">
+        <v>20</v>
+      </c>
+      <c r="BA79">
+        <v>1</v>
+      </c>
+      <c r="BB79">
+        <v>14</v>
+      </c>
+      <c r="BC79">
+        <v>15</v>
+      </c>
+      <c r="BD79">
+        <v>1.7</v>
+      </c>
+      <c r="BE79">
+        <v>6.75</v>
+      </c>
+      <c r="BF79">
+        <v>2.35</v>
+      </c>
+      <c r="BG79">
+        <v>1.27</v>
+      </c>
+      <c r="BH79">
+        <v>3.2</v>
+      </c>
+      <c r="BI79">
+        <v>1.48</v>
+      </c>
+      <c r="BJ79">
+        <v>2.38</v>
+      </c>
+      <c r="BK79">
+        <v>1.78</v>
+      </c>
+      <c r="BL79">
+        <v>1.87</v>
+      </c>
+      <c r="BM79">
+        <v>2.2</v>
+      </c>
+      <c r="BN79">
+        <v>1.55</v>
+      </c>
+      <c r="BO79">
+        <v>2.8</v>
+      </c>
+      <c r="BP79">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -16917,22 +16917,22 @@
         <v>2.65</v>
       </c>
       <c r="AU78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV78">
         <v>3</v>
       </c>
       <c r="AW78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX78">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY78">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ78">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA78">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="179">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -912,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP79"/>
+  <dimension ref="A1:BP80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7">
         <v>0.25</v>
@@ -4957,7 +4957,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR28">
         <v>0.8</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
         <v>0.33</v>
@@ -7426,7 +7426,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -9695,7 +9695,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR43">
         <v>1.74</v>
@@ -12164,7 +12164,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -13815,7 +13815,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -17187,6 +17187,212 @@
       </c>
       <c r="BP79">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7778156</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
+      </c>
+      <c r="G80" t="s">
+        <v>75</v>
+      </c>
+      <c r="H80" t="s">
+        <v>79</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>91</v>
+      </c>
+      <c r="P80" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q80">
+        <v>2.75</v>
+      </c>
+      <c r="R80">
+        <v>2.2</v>
+      </c>
+      <c r="S80">
+        <v>4</v>
+      </c>
+      <c r="T80">
+        <v>1.4</v>
+      </c>
+      <c r="U80">
+        <v>2.75</v>
+      </c>
+      <c r="V80">
+        <v>2.75</v>
+      </c>
+      <c r="W80">
+        <v>1.4</v>
+      </c>
+      <c r="X80">
+        <v>8</v>
+      </c>
+      <c r="Y80">
+        <v>1.08</v>
+      </c>
+      <c r="Z80">
+        <v>2.02</v>
+      </c>
+      <c r="AA80">
+        <v>3.47</v>
+      </c>
+      <c r="AB80">
+        <v>3.5</v>
+      </c>
+      <c r="AC80">
+        <v>1.77</v>
+      </c>
+      <c r="AD80">
+        <v>2.11</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>1.87</v>
+      </c>
+      <c r="AH80">
+        <v>1.87</v>
+      </c>
+      <c r="AI80">
+        <v>1.75</v>
+      </c>
+      <c r="AJ80">
+        <v>2</v>
+      </c>
+      <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>0</v>
+      </c>
+      <c r="AN80">
+        <v>1.5</v>
+      </c>
+      <c r="AO80">
+        <v>1.25</v>
+      </c>
+      <c r="AP80">
+        <v>1.4</v>
+      </c>
+      <c r="AQ80">
+        <v>1.2</v>
+      </c>
+      <c r="AR80">
+        <v>1.25</v>
+      </c>
+      <c r="AS80">
+        <v>1.21</v>
+      </c>
+      <c r="AT80">
+        <v>2.46</v>
+      </c>
+      <c r="AU80">
+        <v>3</v>
+      </c>
+      <c r="AV80">
+        <v>2</v>
+      </c>
+      <c r="AW80">
+        <v>5</v>
+      </c>
+      <c r="AX80">
+        <v>11</v>
+      </c>
+      <c r="AY80">
+        <v>9</v>
+      </c>
+      <c r="AZ80">
+        <v>17</v>
+      </c>
+      <c r="BA80">
+        <v>2</v>
+      </c>
+      <c r="BB80">
+        <v>3</v>
+      </c>
+      <c r="BC80">
+        <v>5</v>
+      </c>
+      <c r="BD80">
+        <v>0</v>
+      </c>
+      <c r="BE80">
+        <v>0</v>
+      </c>
+      <c r="BF80">
+        <v>0</v>
+      </c>
+      <c r="BG80">
+        <v>0</v>
+      </c>
+      <c r="BH80">
+        <v>0</v>
+      </c>
+      <c r="BI80">
+        <v>0</v>
+      </c>
+      <c r="BJ80">
+        <v>0</v>
+      </c>
+      <c r="BK80">
+        <v>0</v>
+      </c>
+      <c r="BL80">
+        <v>0</v>
+      </c>
+      <c r="BM80">
+        <v>0</v>
+      </c>
+      <c r="BN80">
+        <v>0</v>
+      </c>
+      <c r="BO80">
+        <v>0</v>
+      </c>
+      <c r="BP80">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="187">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,10 +448,31 @@
     <t>['4', '59']</t>
   </si>
   <si>
-    <t>['7', '46', '52', '63', '90+4']</t>
+    <t>['61']</t>
   </si>
   <si>
-    <t>['61']</t>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['34', '53']</t>
+  </si>
+  <si>
+    <t>['50', '90+7']</t>
+  </si>
+  <si>
+    <t>['18', '30', '90+2']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['10', '45']</t>
+  </si>
+  <si>
+    <t>['18', '86']</t>
+  </si>
+  <si>
+    <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
     <t>['59', '77']</t>
@@ -481,9 +502,6 @@
     <t>['13']</t>
   </si>
   <si>
-    <t>['65']</t>
-  </si>
-  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -500,9 +518,6 @@
   </si>
   <si>
     <t>['13', '74']</t>
-  </si>
-  <si>
-    <t>['68']</t>
   </si>
   <si>
     <t>['14', '31']</t>
@@ -551,6 +566,15 @@
   </si>
   <si>
     <t>['79']</t>
+  </si>
+  <si>
+    <t>['16', '73']</t>
+  </si>
+  <si>
+    <t>['61', '80', '82', '90+5']</t>
+  </si>
+  <si>
+    <t>['45+5']</t>
   </si>
 </sst>
 </file>
@@ -912,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP80"/>
+  <dimension ref="A1:BP89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1168,7 +1192,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1249,7 +1273,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1452,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
         <v>2</v>
@@ -1658,10 +1682,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
+        <v>0.5</v>
+      </c>
+      <c r="AQ4">
         <v>0.67</v>
-      </c>
-      <c r="AQ4">
-        <v>0.8</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1786,7 +1810,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -1864,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2070,10 +2094,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2279,7 +2303,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2485,7 +2509,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2688,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2816,7 +2840,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3022,7 +3046,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3103,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3228,7 +3252,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3434,7 +3458,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3512,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3718,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -3927,7 +3951,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ15">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4052,7 +4076,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4133,7 +4157,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4258,7 +4282,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4464,7 +4488,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4954,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ20">
         <v>1.2</v>
@@ -5160,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ21">
         <v>0</v>
@@ -5288,7 +5312,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5366,10 +5390,10 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR22">
         <v>0.91</v>
@@ -5572,10 +5596,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -5700,7 +5724,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -5778,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -5906,7 +5930,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="Q25">
         <v>4.33</v>
@@ -6112,7 +6136,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6190,10 +6214,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR26">
         <v>2</v>
@@ -6318,7 +6342,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6396,10 +6420,10 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ27">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6524,7 +6548,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6811,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -6936,7 +6960,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7014,10 +7038,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR30">
         <v>1.39</v>
@@ -7348,7 +7372,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7632,10 +7656,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR33">
         <v>1.86</v>
@@ -7841,7 +7865,7 @@
         <v>2</v>
       </c>
       <c r="AQ34">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR34">
         <v>1.99</v>
@@ -7966,7 +7990,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8044,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35">
         <v>2.25</v>
@@ -8172,7 +8196,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8253,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR36">
         <v>1.08</v>
@@ -8378,7 +8402,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8459,7 +8483,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR37">
         <v>0</v>
@@ -8584,7 +8608,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8790,7 +8814,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -8868,10 +8892,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -9074,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ40">
         <v>0.33</v>
@@ -9202,7 +9226,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9614,7 +9638,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -9901,7 +9925,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR44">
         <v>1.53</v>
@@ -10232,7 +10256,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10310,7 +10334,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46">
         <v>2.6</v>
@@ -10438,7 +10462,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10519,7 +10543,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR47">
         <v>1.63</v>
@@ -10644,7 +10668,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -10722,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -10850,7 +10874,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="Q49">
         <v>3.2</v>
@@ -11134,10 +11158,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR50">
         <v>1.21</v>
@@ -11343,7 +11367,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.02</v>
@@ -11468,7 +11492,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11549,7 +11573,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -11752,10 +11776,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1.12</v>
@@ -11880,7 +11904,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -11961,7 +11985,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ54">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR54">
         <v>1.44</v>
@@ -12167,7 +12191,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR55">
         <v>1.24</v>
@@ -12370,10 +12394,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ56">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR56">
         <v>1.66</v>
@@ -12498,7 +12522,7 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -12576,7 +12600,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ57">
         <v>2</v>
@@ -12782,10 +12806,10 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ58">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR58">
         <v>1.91</v>
@@ -12910,7 +12934,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -12988,7 +13012,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ59">
         <v>1.75</v>
@@ -13116,7 +13140,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13197,7 +13221,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
         <v>1.95</v>
@@ -13400,7 +13424,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ61">
         <v>0</v>
@@ -13812,7 +13836,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63">
         <v>1.2</v>
@@ -13940,7 +13964,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14021,7 +14045,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.47</v>
@@ -14636,7 +14660,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ67">
         <v>1.75</v>
@@ -14764,7 +14788,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -14842,7 +14866,7 @@
         <v>3</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
         <v>2.6</v>
@@ -14970,7 +14994,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15051,7 +15075,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15254,7 +15278,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15382,7 +15406,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15588,7 +15612,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16618,7 +16642,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16699,7 +16723,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
         <v>1.28</v>
@@ -16824,7 +16848,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q78">
         <v>4.33</v>
@@ -16902,7 +16926,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>1.75</v>
@@ -17030,7 +17054,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17111,7 +17135,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR79">
         <v>1.78</v>
@@ -17393,6 +17417,1860 @@
       </c>
       <c r="BP80">
         <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7778160</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45753.04166666666</v>
+      </c>
+      <c r="F81">
+        <v>9</v>
+      </c>
+      <c r="G81" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" t="s">
+        <v>85</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>144</v>
+      </c>
+      <c r="P81" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q81">
+        <v>3.1</v>
+      </c>
+      <c r="R81">
+        <v>2</v>
+      </c>
+      <c r="S81">
+        <v>4</v>
+      </c>
+      <c r="T81">
+        <v>1.5</v>
+      </c>
+      <c r="U81">
+        <v>2.5</v>
+      </c>
+      <c r="V81">
+        <v>3.5</v>
+      </c>
+      <c r="W81">
+        <v>1.29</v>
+      </c>
+      <c r="X81">
+        <v>11</v>
+      </c>
+      <c r="Y81">
+        <v>1.05</v>
+      </c>
+      <c r="Z81">
+        <v>2.32</v>
+      </c>
+      <c r="AA81">
+        <v>3.01</v>
+      </c>
+      <c r="AB81">
+        <v>3.25</v>
+      </c>
+      <c r="AC81">
+        <v>1.09</v>
+      </c>
+      <c r="AD81">
+        <v>6.75</v>
+      </c>
+      <c r="AE81">
+        <v>1.41</v>
+      </c>
+      <c r="AF81">
+        <v>2.65</v>
+      </c>
+      <c r="AG81">
+        <v>2.2</v>
+      </c>
+      <c r="AH81">
+        <v>1.55</v>
+      </c>
+      <c r="AI81">
+        <v>1.95</v>
+      </c>
+      <c r="AJ81">
+        <v>1.8</v>
+      </c>
+      <c r="AK81">
+        <v>1.33</v>
+      </c>
+      <c r="AL81">
+        <v>1.35</v>
+      </c>
+      <c r="AM81">
+        <v>1.58</v>
+      </c>
+      <c r="AN81">
+        <v>2.2</v>
+      </c>
+      <c r="AO81">
+        <v>1</v>
+      </c>
+      <c r="AP81">
+        <v>2.33</v>
+      </c>
+      <c r="AQ81">
+        <v>0.8</v>
+      </c>
+      <c r="AR81">
+        <v>1.63</v>
+      </c>
+      <c r="AS81">
+        <v>1.09</v>
+      </c>
+      <c r="AT81">
+        <v>2.72</v>
+      </c>
+      <c r="AU81">
+        <v>4</v>
+      </c>
+      <c r="AV81">
+        <v>4</v>
+      </c>
+      <c r="AW81">
+        <v>4</v>
+      </c>
+      <c r="AX81">
+        <v>10</v>
+      </c>
+      <c r="AY81">
+        <v>10</v>
+      </c>
+      <c r="AZ81">
+        <v>21</v>
+      </c>
+      <c r="BA81">
+        <v>6</v>
+      </c>
+      <c r="BB81">
+        <v>6</v>
+      </c>
+      <c r="BC81">
+        <v>12</v>
+      </c>
+      <c r="BD81">
+        <v>1.67</v>
+      </c>
+      <c r="BE81">
+        <v>6.85</v>
+      </c>
+      <c r="BF81">
+        <v>2.88</v>
+      </c>
+      <c r="BG81">
+        <v>0</v>
+      </c>
+      <c r="BH81">
+        <v>0</v>
+      </c>
+      <c r="BI81">
+        <v>1.39</v>
+      </c>
+      <c r="BJ81">
+        <v>2.59</v>
+      </c>
+      <c r="BK81">
+        <v>1.71</v>
+      </c>
+      <c r="BL81">
+        <v>1.97</v>
+      </c>
+      <c r="BM81">
+        <v>2.19</v>
+      </c>
+      <c r="BN81">
+        <v>1.6</v>
+      </c>
+      <c r="BO81">
+        <v>2.91</v>
+      </c>
+      <c r="BP81">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7778162</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F82">
+        <v>9</v>
+      </c>
+      <c r="G82" t="s">
+        <v>71</v>
+      </c>
+      <c r="H82" t="s">
+        <v>89</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>145</v>
+      </c>
+      <c r="P82" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q82">
+        <v>3.6</v>
+      </c>
+      <c r="R82">
+        <v>1.91</v>
+      </c>
+      <c r="S82">
+        <v>3.5</v>
+      </c>
+      <c r="T82">
+        <v>1.57</v>
+      </c>
+      <c r="U82">
+        <v>2.25</v>
+      </c>
+      <c r="V82">
+        <v>3.75</v>
+      </c>
+      <c r="W82">
+        <v>1.25</v>
+      </c>
+      <c r="X82">
+        <v>13</v>
+      </c>
+      <c r="Y82">
+        <v>1.04</v>
+      </c>
+      <c r="Z82">
+        <v>2.77</v>
+      </c>
+      <c r="AA82">
+        <v>3</v>
+      </c>
+      <c r="AB82">
+        <v>2.66</v>
+      </c>
+      <c r="AC82">
+        <v>1.04</v>
+      </c>
+      <c r="AD82">
+        <v>7.4</v>
+      </c>
+      <c r="AE82">
+        <v>1.48</v>
+      </c>
+      <c r="AF82">
+        <v>2.37</v>
+      </c>
+      <c r="AG82">
+        <v>2.57</v>
+      </c>
+      <c r="AH82">
+        <v>1.47</v>
+      </c>
+      <c r="AI82">
+        <v>2.05</v>
+      </c>
+      <c r="AJ82">
+        <v>1.7</v>
+      </c>
+      <c r="AK82">
+        <v>1.47</v>
+      </c>
+      <c r="AL82">
+        <v>1.38</v>
+      </c>
+      <c r="AM82">
+        <v>1.44</v>
+      </c>
+      <c r="AN82">
+        <v>1</v>
+      </c>
+      <c r="AO82">
+        <v>0.8</v>
+      </c>
+      <c r="AP82">
+        <v>1.4</v>
+      </c>
+      <c r="AQ82">
+        <v>0.67</v>
+      </c>
+      <c r="AR82">
+        <v>1.53</v>
+      </c>
+      <c r="AS82">
+        <v>1.67</v>
+      </c>
+      <c r="AT82">
+        <v>3.2</v>
+      </c>
+      <c r="AU82">
+        <v>5</v>
+      </c>
+      <c r="AV82">
+        <v>5</v>
+      </c>
+      <c r="AW82">
+        <v>7</v>
+      </c>
+      <c r="AX82">
+        <v>8</v>
+      </c>
+      <c r="AY82">
+        <v>12</v>
+      </c>
+      <c r="AZ82">
+        <v>15</v>
+      </c>
+      <c r="BA82">
+        <v>2</v>
+      </c>
+      <c r="BB82">
+        <v>4</v>
+      </c>
+      <c r="BC82">
+        <v>6</v>
+      </c>
+      <c r="BD82">
+        <v>1.92</v>
+      </c>
+      <c r="BE82">
+        <v>6.35</v>
+      </c>
+      <c r="BF82">
+        <v>2.41</v>
+      </c>
+      <c r="BG82">
+        <v>1.36</v>
+      </c>
+      <c r="BH82">
+        <v>2.88</v>
+      </c>
+      <c r="BI82">
+        <v>1.64</v>
+      </c>
+      <c r="BJ82">
+        <v>2.22</v>
+      </c>
+      <c r="BK82">
+        <v>2.04</v>
+      </c>
+      <c r="BL82">
+        <v>1.76</v>
+      </c>
+      <c r="BM82">
+        <v>2.5</v>
+      </c>
+      <c r="BN82">
+        <v>1.48</v>
+      </c>
+      <c r="BO82">
+        <v>3.3</v>
+      </c>
+      <c r="BP82">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7778155</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F83">
+        <v>9</v>
+      </c>
+      <c r="G83" t="s">
+        <v>78</v>
+      </c>
+      <c r="H83" t="s">
+        <v>76</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>2</v>
+      </c>
+      <c r="L83">
+        <v>2</v>
+      </c>
+      <c r="M83">
+        <v>2</v>
+      </c>
+      <c r="N83">
+        <v>4</v>
+      </c>
+      <c r="O83" t="s">
+        <v>146</v>
+      </c>
+      <c r="P83" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q83">
+        <v>3.4</v>
+      </c>
+      <c r="R83">
+        <v>2.05</v>
+      </c>
+      <c r="S83">
+        <v>3.4</v>
+      </c>
+      <c r="T83">
+        <v>1.44</v>
+      </c>
+      <c r="U83">
+        <v>2.63</v>
+      </c>
+      <c r="V83">
+        <v>3.25</v>
+      </c>
+      <c r="W83">
+        <v>1.33</v>
+      </c>
+      <c r="X83">
+        <v>10</v>
+      </c>
+      <c r="Y83">
+        <v>1.06</v>
+      </c>
+      <c r="Z83">
+        <v>2.66</v>
+      </c>
+      <c r="AA83">
+        <v>3.06</v>
+      </c>
+      <c r="AB83">
+        <v>2.73</v>
+      </c>
+      <c r="AC83">
+        <v>1.01</v>
+      </c>
+      <c r="AD83">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE83">
+        <v>1.32</v>
+      </c>
+      <c r="AF83">
+        <v>2.97</v>
+      </c>
+      <c r="AG83">
+        <v>2.05</v>
+      </c>
+      <c r="AH83">
+        <v>1.65</v>
+      </c>
+      <c r="AI83">
+        <v>1.91</v>
+      </c>
+      <c r="AJ83">
+        <v>1.91</v>
+      </c>
+      <c r="AK83">
+        <v>1.45</v>
+      </c>
+      <c r="AL83">
+        <v>1.37</v>
+      </c>
+      <c r="AM83">
+        <v>1.47</v>
+      </c>
+      <c r="AN83">
+        <v>1</v>
+      </c>
+      <c r="AO83">
+        <v>2</v>
+      </c>
+      <c r="AP83">
+        <v>1</v>
+      </c>
+      <c r="AQ83">
+        <v>1.8</v>
+      </c>
+      <c r="AR83">
+        <v>1.23</v>
+      </c>
+      <c r="AS83">
+        <v>1.39</v>
+      </c>
+      <c r="AT83">
+        <v>2.62</v>
+      </c>
+      <c r="AU83">
+        <v>3</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>8</v>
+      </c>
+      <c r="AX83">
+        <v>11</v>
+      </c>
+      <c r="AY83">
+        <v>13</v>
+      </c>
+      <c r="AZ83">
+        <v>24</v>
+      </c>
+      <c r="BA83">
+        <v>4</v>
+      </c>
+      <c r="BB83">
+        <v>6</v>
+      </c>
+      <c r="BC83">
+        <v>10</v>
+      </c>
+      <c r="BD83">
+        <v>1.93</v>
+      </c>
+      <c r="BE83">
+        <v>6.45</v>
+      </c>
+      <c r="BF83">
+        <v>2.38</v>
+      </c>
+      <c r="BG83">
+        <v>1.29</v>
+      </c>
+      <c r="BH83">
+        <v>3.3</v>
+      </c>
+      <c r="BI83">
+        <v>1.5</v>
+      </c>
+      <c r="BJ83">
+        <v>2.47</v>
+      </c>
+      <c r="BK83">
+        <v>1.85</v>
+      </c>
+      <c r="BL83">
+        <v>1.95</v>
+      </c>
+      <c r="BM83">
+        <v>2.31</v>
+      </c>
+      <c r="BN83">
+        <v>1.56</v>
+      </c>
+      <c r="BO83">
+        <v>2.9</v>
+      </c>
+      <c r="BP83">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7778157</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F84">
+        <v>9</v>
+      </c>
+      <c r="G84" t="s">
+        <v>73</v>
+      </c>
+      <c r="H84" t="s">
+        <v>82</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>2</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>147</v>
+      </c>
+      <c r="P84" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q84">
+        <v>3.75</v>
+      </c>
+      <c r="R84">
+        <v>1.91</v>
+      </c>
+      <c r="S84">
+        <v>3.6</v>
+      </c>
+      <c r="T84">
+        <v>1.62</v>
+      </c>
+      <c r="U84">
+        <v>2.2</v>
+      </c>
+      <c r="V84">
+        <v>4</v>
+      </c>
+      <c r="W84">
+        <v>1.22</v>
+      </c>
+      <c r="X84">
+        <v>13</v>
+      </c>
+      <c r="Y84">
+        <v>1.04</v>
+      </c>
+      <c r="Z84">
+        <v>2.79</v>
+      </c>
+      <c r="AA84">
+        <v>3.01</v>
+      </c>
+      <c r="AB84">
+        <v>2.63</v>
+      </c>
+      <c r="AC84">
+        <v>1.08</v>
+      </c>
+      <c r="AD84">
+        <v>6.1</v>
+      </c>
+      <c r="AE84">
+        <v>1.53</v>
+      </c>
+      <c r="AF84">
+        <v>2.5</v>
+      </c>
+      <c r="AG84">
+        <v>2.37</v>
+      </c>
+      <c r="AH84">
+        <v>1.48</v>
+      </c>
+      <c r="AI84">
+        <v>2.2</v>
+      </c>
+      <c r="AJ84">
+        <v>1.62</v>
+      </c>
+      <c r="AK84">
+        <v>1.48</v>
+      </c>
+      <c r="AL84">
+        <v>1.41</v>
+      </c>
+      <c r="AM84">
+        <v>1.4</v>
+      </c>
+      <c r="AN84">
+        <v>1.2</v>
+      </c>
+      <c r="AO84">
+        <v>1</v>
+      </c>
+      <c r="AP84">
+        <v>1.5</v>
+      </c>
+      <c r="AQ84">
+        <v>0.8</v>
+      </c>
+      <c r="AR84">
+        <v>1.19</v>
+      </c>
+      <c r="AS84">
+        <v>1.52</v>
+      </c>
+      <c r="AT84">
+        <v>2.71</v>
+      </c>
+      <c r="AU84">
+        <v>5</v>
+      </c>
+      <c r="AV84">
+        <v>0</v>
+      </c>
+      <c r="AW84">
+        <v>4</v>
+      </c>
+      <c r="AX84">
+        <v>14</v>
+      </c>
+      <c r="AY84">
+        <v>10</v>
+      </c>
+      <c r="AZ84">
+        <v>17</v>
+      </c>
+      <c r="BA84">
+        <v>1</v>
+      </c>
+      <c r="BB84">
+        <v>8</v>
+      </c>
+      <c r="BC84">
+        <v>9</v>
+      </c>
+      <c r="BD84">
+        <v>1.86</v>
+      </c>
+      <c r="BE84">
+        <v>6.5</v>
+      </c>
+      <c r="BF84">
+        <v>2.49</v>
+      </c>
+      <c r="BG84">
+        <v>1.23</v>
+      </c>
+      <c r="BH84">
+        <v>3.42</v>
+      </c>
+      <c r="BI84">
+        <v>1.46</v>
+      </c>
+      <c r="BJ84">
+        <v>2.45</v>
+      </c>
+      <c r="BK84">
+        <v>1.82</v>
+      </c>
+      <c r="BL84">
+        <v>1.88</v>
+      </c>
+      <c r="BM84">
+        <v>2.32</v>
+      </c>
+      <c r="BN84">
+        <v>1.51</v>
+      </c>
+      <c r="BO84">
+        <v>3.08</v>
+      </c>
+      <c r="BP84">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7778159</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F85">
+        <v>9</v>
+      </c>
+      <c r="G85" t="s">
+        <v>72</v>
+      </c>
+      <c r="H85" t="s">
+        <v>88</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
+        <v>91</v>
+      </c>
+      <c r="P85" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q85">
+        <v>2.6</v>
+      </c>
+      <c r="R85">
+        <v>2.1</v>
+      </c>
+      <c r="S85">
+        <v>4.75</v>
+      </c>
+      <c r="T85">
+        <v>1.44</v>
+      </c>
+      <c r="U85">
+        <v>2.63</v>
+      </c>
+      <c r="V85">
+        <v>3.25</v>
+      </c>
+      <c r="W85">
+        <v>1.33</v>
+      </c>
+      <c r="X85">
+        <v>10</v>
+      </c>
+      <c r="Y85">
+        <v>1.06</v>
+      </c>
+      <c r="Z85">
+        <v>1.93</v>
+      </c>
+      <c r="AA85">
+        <v>3.28</v>
+      </c>
+      <c r="AB85">
+        <v>4</v>
+      </c>
+      <c r="AC85">
+        <v>1.02</v>
+      </c>
+      <c r="AD85">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE85">
+        <v>1.33</v>
+      </c>
+      <c r="AF85">
+        <v>2.92</v>
+      </c>
+      <c r="AG85">
+        <v>2.1</v>
+      </c>
+      <c r="AH85">
+        <v>1.61</v>
+      </c>
+      <c r="AI85">
+        <v>1.95</v>
+      </c>
+      <c r="AJ85">
+        <v>1.8</v>
+      </c>
+      <c r="AK85">
+        <v>1.23</v>
+      </c>
+      <c r="AL85">
+        <v>1.32</v>
+      </c>
+      <c r="AM85">
+        <v>1.92</v>
+      </c>
+      <c r="AN85">
+        <v>0.67</v>
+      </c>
+      <c r="AO85">
+        <v>0.25</v>
+      </c>
+      <c r="AP85">
+        <v>0.5</v>
+      </c>
+      <c r="AQ85">
+        <v>0.8</v>
+      </c>
+      <c r="AR85">
+        <v>1.39</v>
+      </c>
+      <c r="AS85">
+        <v>1.23</v>
+      </c>
+      <c r="AT85">
+        <v>2.62</v>
+      </c>
+      <c r="AU85">
+        <v>5</v>
+      </c>
+      <c r="AV85">
+        <v>3</v>
+      </c>
+      <c r="AW85">
+        <v>13</v>
+      </c>
+      <c r="AX85">
+        <v>4</v>
+      </c>
+      <c r="AY85">
+        <v>22</v>
+      </c>
+      <c r="AZ85">
+        <v>8</v>
+      </c>
+      <c r="BA85">
+        <v>3</v>
+      </c>
+      <c r="BB85">
+        <v>4</v>
+      </c>
+      <c r="BC85">
+        <v>7</v>
+      </c>
+      <c r="BD85">
+        <v>1.54</v>
+      </c>
+      <c r="BE85">
+        <v>7</v>
+      </c>
+      <c r="BF85">
+        <v>3.32</v>
+      </c>
+      <c r="BG85">
+        <v>1.3</v>
+      </c>
+      <c r="BH85">
+        <v>3.2</v>
+      </c>
+      <c r="BI85">
+        <v>1.53</v>
+      </c>
+      <c r="BJ85">
+        <v>2.42</v>
+      </c>
+      <c r="BK85">
+        <v>1.9</v>
+      </c>
+      <c r="BL85">
+        <v>1.9</v>
+      </c>
+      <c r="BM85">
+        <v>2.39</v>
+      </c>
+      <c r="BN85">
+        <v>1.54</v>
+      </c>
+      <c r="BO85">
+        <v>3</v>
+      </c>
+      <c r="BP85">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7778153</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45753.125</v>
+      </c>
+      <c r="F86">
+        <v>9</v>
+      </c>
+      <c r="G86" t="s">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s">
+        <v>83</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>2</v>
+      </c>
+      <c r="L86">
+        <v>3</v>
+      </c>
+      <c r="M86">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <v>7</v>
+      </c>
+      <c r="O86" t="s">
+        <v>148</v>
+      </c>
+      <c r="P86" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q86">
+        <v>2.88</v>
+      </c>
+      <c r="R86">
+        <v>2.05</v>
+      </c>
+      <c r="S86">
+        <v>4</v>
+      </c>
+      <c r="T86">
+        <v>1.44</v>
+      </c>
+      <c r="U86">
+        <v>2.63</v>
+      </c>
+      <c r="V86">
+        <v>3.25</v>
+      </c>
+      <c r="W86">
+        <v>1.33</v>
+      </c>
+      <c r="X86">
+        <v>10</v>
+      </c>
+      <c r="Y86">
+        <v>1.06</v>
+      </c>
+      <c r="Z86">
+        <v>2.11</v>
+      </c>
+      <c r="AA86">
+        <v>3.25</v>
+      </c>
+      <c r="AB86">
+        <v>3.45</v>
+      </c>
+      <c r="AC86">
+        <v>1.05</v>
+      </c>
+      <c r="AD86">
+        <v>8</v>
+      </c>
+      <c r="AE86">
+        <v>1.31</v>
+      </c>
+      <c r="AF86">
+        <v>3.02</v>
+      </c>
+      <c r="AG86">
+        <v>1.95</v>
+      </c>
+      <c r="AH86">
+        <v>1.7</v>
+      </c>
+      <c r="AI86">
+        <v>1.91</v>
+      </c>
+      <c r="AJ86">
+        <v>1.91</v>
+      </c>
+      <c r="AK86">
+        <v>1.3</v>
+      </c>
+      <c r="AL86">
+        <v>1.34</v>
+      </c>
+      <c r="AM86">
+        <v>1.71</v>
+      </c>
+      <c r="AN86">
+        <v>2.6</v>
+      </c>
+      <c r="AO86">
+        <v>1.75</v>
+      </c>
+      <c r="AP86">
+        <v>2.17</v>
+      </c>
+      <c r="AQ86">
+        <v>2</v>
+      </c>
+      <c r="AR86">
+        <v>1.65</v>
+      </c>
+      <c r="AS86">
+        <v>1.42</v>
+      </c>
+      <c r="AT86">
+        <v>3.07</v>
+      </c>
+      <c r="AU86">
+        <v>8</v>
+      </c>
+      <c r="AV86">
+        <v>6</v>
+      </c>
+      <c r="AW86">
+        <v>8</v>
+      </c>
+      <c r="AX86">
+        <v>5</v>
+      </c>
+      <c r="AY86">
+        <v>20</v>
+      </c>
+      <c r="AZ86">
+        <v>12</v>
+      </c>
+      <c r="BA86">
+        <v>4</v>
+      </c>
+      <c r="BB86">
+        <v>6</v>
+      </c>
+      <c r="BC86">
+        <v>10</v>
+      </c>
+      <c r="BD86">
+        <v>1.52</v>
+      </c>
+      <c r="BE86">
+        <v>7.1</v>
+      </c>
+      <c r="BF86">
+        <v>3.4</v>
+      </c>
+      <c r="BG86">
+        <v>1.29</v>
+      </c>
+      <c r="BH86">
+        <v>3.3</v>
+      </c>
+      <c r="BI86">
+        <v>1.46</v>
+      </c>
+      <c r="BJ86">
+        <v>2.56</v>
+      </c>
+      <c r="BK86">
+        <v>1.83</v>
+      </c>
+      <c r="BL86">
+        <v>1.96</v>
+      </c>
+      <c r="BM86">
+        <v>2.24</v>
+      </c>
+      <c r="BN86">
+        <v>1.6</v>
+      </c>
+      <c r="BO86">
+        <v>2.9</v>
+      </c>
+      <c r="BP86">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7778154</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45753.125</v>
+      </c>
+      <c r="F87">
+        <v>9</v>
+      </c>
+      <c r="G87" t="s">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s">
+        <v>70</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
+        <v>149</v>
+      </c>
+      <c r="P87" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q87">
+        <v>3</v>
+      </c>
+      <c r="R87">
+        <v>2.05</v>
+      </c>
+      <c r="S87">
+        <v>4</v>
+      </c>
+      <c r="T87">
+        <v>1.5</v>
+      </c>
+      <c r="U87">
+        <v>2.5</v>
+      </c>
+      <c r="V87">
+        <v>3.4</v>
+      </c>
+      <c r="W87">
+        <v>1.3</v>
+      </c>
+      <c r="X87">
+        <v>10</v>
+      </c>
+      <c r="Y87">
+        <v>1.06</v>
+      </c>
+      <c r="Z87">
+        <v>2.19</v>
+      </c>
+      <c r="AA87">
+        <v>3.14</v>
+      </c>
+      <c r="AB87">
+        <v>3.39</v>
+      </c>
+      <c r="AC87">
+        <v>1.04</v>
+      </c>
+      <c r="AD87">
+        <v>7</v>
+      </c>
+      <c r="AE87">
+        <v>1.37</v>
+      </c>
+      <c r="AF87">
+        <v>2.74</v>
+      </c>
+      <c r="AG87">
+        <v>2.1</v>
+      </c>
+      <c r="AH87">
+        <v>1.6</v>
+      </c>
+      <c r="AI87">
+        <v>1.95</v>
+      </c>
+      <c r="AJ87">
+        <v>1.8</v>
+      </c>
+      <c r="AK87">
+        <v>1.32</v>
+      </c>
+      <c r="AL87">
+        <v>1.36</v>
+      </c>
+      <c r="AM87">
+        <v>1.67</v>
+      </c>
+      <c r="AN87">
+        <v>1.25</v>
+      </c>
+      <c r="AO87">
+        <v>1</v>
+      </c>
+      <c r="AP87">
+        <v>1.6</v>
+      </c>
+      <c r="AQ87">
+        <v>0.8</v>
+      </c>
+      <c r="AR87">
+        <v>1.34</v>
+      </c>
+      <c r="AS87">
+        <v>1.9</v>
+      </c>
+      <c r="AT87">
+        <v>3.24</v>
+      </c>
+      <c r="AU87">
+        <v>3</v>
+      </c>
+      <c r="AV87">
+        <v>2</v>
+      </c>
+      <c r="AW87">
+        <v>11</v>
+      </c>
+      <c r="AX87">
+        <v>7</v>
+      </c>
+      <c r="AY87">
+        <v>16</v>
+      </c>
+      <c r="AZ87">
+        <v>10</v>
+      </c>
+      <c r="BA87">
+        <v>8</v>
+      </c>
+      <c r="BB87">
+        <v>2</v>
+      </c>
+      <c r="BC87">
+        <v>10</v>
+      </c>
+      <c r="BD87">
+        <v>1.68</v>
+      </c>
+      <c r="BE87">
+        <v>6.65</v>
+      </c>
+      <c r="BF87">
+        <v>2.88</v>
+      </c>
+      <c r="BG87">
+        <v>1.29</v>
+      </c>
+      <c r="BH87">
+        <v>3.3</v>
+      </c>
+      <c r="BI87">
+        <v>1.47</v>
+      </c>
+      <c r="BJ87">
+        <v>2.52</v>
+      </c>
+      <c r="BK87">
+        <v>1.81</v>
+      </c>
+      <c r="BL87">
+        <v>1.98</v>
+      </c>
+      <c r="BM87">
+        <v>2.26</v>
+      </c>
+      <c r="BN87">
+        <v>1.59</v>
+      </c>
+      <c r="BO87">
+        <v>2.88</v>
+      </c>
+      <c r="BP87">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7778158</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45753.125</v>
+      </c>
+      <c r="F88">
+        <v>9</v>
+      </c>
+      <c r="G88" t="s">
+        <v>77</v>
+      </c>
+      <c r="H88" t="s">
+        <v>80</v>
+      </c>
+      <c r="I88">
+        <v>2</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>3</v>
+      </c>
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>3</v>
+      </c>
+      <c r="O88" t="s">
+        <v>150</v>
+      </c>
+      <c r="P88" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q88">
+        <v>3.2</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
+        <v>3.75</v>
+      </c>
+      <c r="T88">
+        <v>1.5</v>
+      </c>
+      <c r="U88">
+        <v>2.5</v>
+      </c>
+      <c r="V88">
+        <v>3.4</v>
+      </c>
+      <c r="W88">
+        <v>1.3</v>
+      </c>
+      <c r="X88">
+        <v>10</v>
+      </c>
+      <c r="Y88">
+        <v>1.06</v>
+      </c>
+      <c r="Z88">
+        <v>2.32</v>
+      </c>
+      <c r="AA88">
+        <v>3.21</v>
+      </c>
+      <c r="AB88">
+        <v>3.05</v>
+      </c>
+      <c r="AC88">
+        <v>1.04</v>
+      </c>
+      <c r="AD88">
+        <v>6.95</v>
+      </c>
+      <c r="AE88">
+        <v>1.38</v>
+      </c>
+      <c r="AF88">
+        <v>2.7</v>
+      </c>
+      <c r="AG88">
+        <v>2.15</v>
+      </c>
+      <c r="AH88">
+        <v>1.6</v>
+      </c>
+      <c r="AI88">
+        <v>1.95</v>
+      </c>
+      <c r="AJ88">
+        <v>1.8</v>
+      </c>
+      <c r="AK88">
+        <v>1.38</v>
+      </c>
+      <c r="AL88">
+        <v>1.35</v>
+      </c>
+      <c r="AM88">
+        <v>1.59</v>
+      </c>
+      <c r="AN88">
+        <v>2</v>
+      </c>
+      <c r="AO88">
+        <v>0.25</v>
+      </c>
+      <c r="AP88">
+        <v>2.25</v>
+      </c>
+      <c r="AQ88">
+        <v>0.2</v>
+      </c>
+      <c r="AR88">
+        <v>1.6</v>
+      </c>
+      <c r="AS88">
+        <v>1.36</v>
+      </c>
+      <c r="AT88">
+        <v>2.96</v>
+      </c>
+      <c r="AU88">
+        <v>7</v>
+      </c>
+      <c r="AV88">
+        <v>6</v>
+      </c>
+      <c r="AW88">
+        <v>2</v>
+      </c>
+      <c r="AX88">
+        <v>5</v>
+      </c>
+      <c r="AY88">
+        <v>10</v>
+      </c>
+      <c r="AZ88">
+        <v>14</v>
+      </c>
+      <c r="BA88">
+        <v>2</v>
+      </c>
+      <c r="BB88">
+        <v>2</v>
+      </c>
+      <c r="BC88">
+        <v>4</v>
+      </c>
+      <c r="BD88">
+        <v>1.86</v>
+      </c>
+      <c r="BE88">
+        <v>6.6</v>
+      </c>
+      <c r="BF88">
+        <v>2.47</v>
+      </c>
+      <c r="BG88">
+        <v>1.29</v>
+      </c>
+      <c r="BH88">
+        <v>3.4</v>
+      </c>
+      <c r="BI88">
+        <v>1.46</v>
+      </c>
+      <c r="BJ88">
+        <v>2.57</v>
+      </c>
+      <c r="BK88">
+        <v>1.79</v>
+      </c>
+      <c r="BL88">
+        <v>2.01</v>
+      </c>
+      <c r="BM88">
+        <v>2.22</v>
+      </c>
+      <c r="BN88">
+        <v>1.61</v>
+      </c>
+      <c r="BO88">
+        <v>2.8</v>
+      </c>
+      <c r="BP88">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7778161</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45753.125</v>
+      </c>
+      <c r="F89">
+        <v>9</v>
+      </c>
+      <c r="G89" t="s">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>2</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>3</v>
+      </c>
+      <c r="O89" t="s">
+        <v>151</v>
+      </c>
+      <c r="P89" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q89">
+        <v>2.2</v>
+      </c>
+      <c r="R89">
+        <v>2.25</v>
+      </c>
+      <c r="S89">
+        <v>5.5</v>
+      </c>
+      <c r="T89">
+        <v>1.4</v>
+      </c>
+      <c r="U89">
+        <v>2.75</v>
+      </c>
+      <c r="V89">
+        <v>2.75</v>
+      </c>
+      <c r="W89">
+        <v>1.4</v>
+      </c>
+      <c r="X89">
+        <v>8</v>
+      </c>
+      <c r="Y89">
+        <v>1.08</v>
+      </c>
+      <c r="Z89">
+        <v>1.6</v>
+      </c>
+      <c r="AA89">
+        <v>3.92</v>
+      </c>
+      <c r="AB89">
+        <v>5.3</v>
+      </c>
+      <c r="AC89">
+        <v>1.01</v>
+      </c>
+      <c r="AD89">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE89">
+        <v>1.27</v>
+      </c>
+      <c r="AF89">
+        <v>3.25</v>
+      </c>
+      <c r="AG89">
+        <v>1.87</v>
+      </c>
+      <c r="AH89">
+        <v>1.87</v>
+      </c>
+      <c r="AI89">
+        <v>1.95</v>
+      </c>
+      <c r="AJ89">
+        <v>1.8</v>
+      </c>
+      <c r="AK89">
+        <v>1.18</v>
+      </c>
+      <c r="AL89">
+        <v>1.27</v>
+      </c>
+      <c r="AM89">
+        <v>2.19</v>
+      </c>
+      <c r="AN89">
+        <v>2.5</v>
+      </c>
+      <c r="AO89">
+        <v>1</v>
+      </c>
+      <c r="AP89">
+        <v>2.6</v>
+      </c>
+      <c r="AQ89">
+        <v>0.8</v>
+      </c>
+      <c r="AR89">
+        <v>1.48</v>
+      </c>
+      <c r="AS89">
+        <v>1.4</v>
+      </c>
+      <c r="AT89">
+        <v>2.88</v>
+      </c>
+      <c r="AU89">
+        <v>5</v>
+      </c>
+      <c r="AV89">
+        <v>3</v>
+      </c>
+      <c r="AW89">
+        <v>6</v>
+      </c>
+      <c r="AX89">
+        <v>13</v>
+      </c>
+      <c r="AY89">
+        <v>12</v>
+      </c>
+      <c r="AZ89">
+        <v>17</v>
+      </c>
+      <c r="BA89">
+        <v>3</v>
+      </c>
+      <c r="BB89">
+        <v>3</v>
+      </c>
+      <c r="BC89">
+        <v>6</v>
+      </c>
+      <c r="BD89">
+        <v>1.41</v>
+      </c>
+      <c r="BE89">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF89">
+        <v>3.55</v>
+      </c>
+      <c r="BG89">
+        <v>1.25</v>
+      </c>
+      <c r="BH89">
+        <v>3.6</v>
+      </c>
+      <c r="BI89">
+        <v>1.42</v>
+      </c>
+      <c r="BJ89">
+        <v>2.62</v>
+      </c>
+      <c r="BK89">
+        <v>1.66</v>
+      </c>
+      <c r="BL89">
+        <v>2.16</v>
+      </c>
+      <c r="BM89">
+        <v>2.08</v>
+      </c>
+      <c r="BN89">
+        <v>1.71</v>
+      </c>
+      <c r="BO89">
+        <v>2.62</v>
+      </c>
+      <c r="BP89">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="189">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,9 @@
     <t>['18', '86']</t>
   </si>
   <si>
+    <t>['7', '66', '90+9']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -575,6 +578,9 @@
   </si>
   <si>
     <t>['45+5']</t>
+  </si>
+  <si>
+    <t>['41', '89', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -936,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1192,7 +1198,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2506,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
         <v>0.2</v>
@@ -2840,7 +2846,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3046,7 +3052,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3252,7 +3258,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3458,7 +3464,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4076,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4282,7 +4288,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4488,7 +4494,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5187,7 +5193,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5312,7 +5318,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5724,7 +5730,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6136,7 +6142,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -6342,7 +6348,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6548,7 +6554,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6960,7 +6966,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7372,7 +7378,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7862,7 +7868,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ34">
         <v>2</v>
@@ -7990,7 +7996,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8196,7 +8202,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8402,7 +8408,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8608,7 +8614,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9226,7 +9232,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9638,7 +9644,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10256,7 +10262,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10462,7 +10468,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10668,7 +10674,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11492,7 +11498,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11904,7 +11910,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12522,7 +12528,7 @@
         <v>127</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q57">
         <v>2.38</v>
@@ -12934,7 +12940,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13140,7 +13146,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13427,7 +13433,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -13964,7 +13970,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14788,7 +14794,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -14994,7 +15000,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15406,7 +15412,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15612,7 +15618,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16105,7 +16111,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR74">
         <v>1.09</v>
@@ -16514,7 +16520,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16642,7 +16648,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16848,7 +16854,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q78">
         <v>4.33</v>
@@ -17054,7 +17060,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17878,7 +17884,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18496,7 +18502,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18908,7 +18914,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19271,6 +19277,212 @@
       </c>
       <c r="BP89">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7778121</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45756.29166666666</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+      <c r="G90" t="s">
+        <v>76</v>
+      </c>
+      <c r="H90" t="s">
+        <v>75</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>2</v>
+      </c>
+      <c r="L90">
+        <v>3</v>
+      </c>
+      <c r="M90">
+        <v>3</v>
+      </c>
+      <c r="N90">
+        <v>6</v>
+      </c>
+      <c r="O90" t="s">
+        <v>152</v>
+      </c>
+      <c r="P90" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q90">
+        <v>2.1</v>
+      </c>
+      <c r="R90">
+        <v>2.35</v>
+      </c>
+      <c r="S90">
+        <v>4.5</v>
+      </c>
+      <c r="T90">
+        <v>1.28</v>
+      </c>
+      <c r="U90">
+        <v>3.3</v>
+      </c>
+      <c r="V90">
+        <v>2.25</v>
+      </c>
+      <c r="W90">
+        <v>1.57</v>
+      </c>
+      <c r="X90">
+        <v>5</v>
+      </c>
+      <c r="Y90">
+        <v>1.15</v>
+      </c>
+      <c r="Z90">
+        <v>1.62</v>
+      </c>
+      <c r="AA90">
+        <v>4.2</v>
+      </c>
+      <c r="AB90">
+        <v>4.7</v>
+      </c>
+      <c r="AC90">
+        <v>1.04</v>
+      </c>
+      <c r="AD90">
+        <v>10</v>
+      </c>
+      <c r="AE90">
+        <v>1.2</v>
+      </c>
+      <c r="AF90">
+        <v>4.5</v>
+      </c>
+      <c r="AG90">
+        <v>1.53</v>
+      </c>
+      <c r="AH90">
+        <v>2.25</v>
+      </c>
+      <c r="AI90">
+        <v>1.57</v>
+      </c>
+      <c r="AJ90">
+        <v>2.2</v>
+      </c>
+      <c r="AK90">
+        <v>1.18</v>
+      </c>
+      <c r="AL90">
+        <v>1.18</v>
+      </c>
+      <c r="AM90">
+        <v>2.15</v>
+      </c>
+      <c r="AN90">
+        <v>2</v>
+      </c>
+      <c r="AO90">
+        <v>0</v>
+      </c>
+      <c r="AP90">
+        <v>1.75</v>
+      </c>
+      <c r="AQ90">
+        <v>0.25</v>
+      </c>
+      <c r="AR90">
+        <v>1.9</v>
+      </c>
+      <c r="AS90">
+        <v>1.15</v>
+      </c>
+      <c r="AT90">
+        <v>3.05</v>
+      </c>
+      <c r="AU90">
+        <v>5</v>
+      </c>
+      <c r="AV90">
+        <v>6</v>
+      </c>
+      <c r="AW90">
+        <v>9</v>
+      </c>
+      <c r="AX90">
+        <v>10</v>
+      </c>
+      <c r="AY90">
+        <v>15</v>
+      </c>
+      <c r="AZ90">
+        <v>17</v>
+      </c>
+      <c r="BA90">
+        <v>6</v>
+      </c>
+      <c r="BB90">
+        <v>7</v>
+      </c>
+      <c r="BC90">
+        <v>13</v>
+      </c>
+      <c r="BD90">
+        <v>1.5</v>
+      </c>
+      <c r="BE90">
+        <v>6.75</v>
+      </c>
+      <c r="BF90">
+        <v>2.8</v>
+      </c>
+      <c r="BG90">
+        <v>1.26</v>
+      </c>
+      <c r="BH90">
+        <v>3.25</v>
+      </c>
+      <c r="BI90">
+        <v>1.46</v>
+      </c>
+      <c r="BJ90">
+        <v>2.4</v>
+      </c>
+      <c r="BK90">
+        <v>1.78</v>
+      </c>
+      <c r="BL90">
+        <v>1.87</v>
+      </c>
+      <c r="BM90">
+        <v>2.23</v>
+      </c>
+      <c r="BN90">
+        <v>1.54</v>
+      </c>
+      <c r="BO90">
+        <v>2.8</v>
+      </c>
+      <c r="BP90">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,12 @@
     <t>['53', '83']</t>
   </si>
   <si>
+    <t>['9002']</t>
+  </si>
+  <si>
+    <t>['3', '81']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -878,6 +884,9 @@
   </si>
   <si>
     <t>['4', '89']</t>
+  </si>
+  <si>
+    <t>['41', '71']</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1495,7 +1504,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1576,7 +1585,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2191,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5">
         <v>0.89</v>
@@ -3015,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9">
         <v>1.67</v>
@@ -3143,7 +3152,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3224,7 +3233,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ10">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3349,7 +3358,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3555,7 +3564,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3761,7 +3770,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3842,7 +3851,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4045,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ14">
         <v>0.5600000000000001</v>
@@ -4379,7 +4388,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4585,7 +4594,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4791,7 +4800,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5075,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5281,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ20">
         <v>1.1</v>
@@ -5615,7 +5624,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5696,7 +5705,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ22">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR22">
         <v>0.91</v>
@@ -6027,7 +6036,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6314,7 +6323,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6517,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>0.9</v>
@@ -6645,7 +6654,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6723,7 +6732,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ27">
         <v>0.89</v>
@@ -6851,7 +6860,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7135,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ29">
         <v>0.6</v>
@@ -7263,7 +7272,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7344,7 +7353,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR30">
         <v>1.39</v>
@@ -7675,7 +7684,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7959,7 +7968,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ33">
         <v>0.89</v>
@@ -8293,7 +8302,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8499,7 +8508,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8705,7 +8714,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8786,7 +8795,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ37">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
         <v>0</v>
@@ -8911,7 +8920,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -8992,7 +9001,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ38">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -9529,7 +9538,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9941,7 +9950,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10431,7 +10440,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ45">
         <v>1.1</v>
@@ -10559,7 +10568,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10637,10 +10646,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ46">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10765,7 +10774,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10971,7 +10980,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11461,10 +11470,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ50">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR50">
         <v>1.21</v>
@@ -11795,7 +11804,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12207,7 +12216,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12700,7 +12709,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ56">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR56">
         <v>1.66</v>
@@ -13109,7 +13118,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ58">
         <v>0.9</v>
@@ -13237,7 +13246,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13315,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ59">
         <v>1.78</v>
@@ -13443,7 +13452,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -14267,7 +14276,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14760,7 +14769,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ66">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -14963,7 +14972,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ67">
         <v>1.78</v>
@@ -15091,7 +15100,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15172,7 +15181,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ68">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR68">
         <v>1.51</v>
@@ -15297,7 +15306,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15375,10 +15384,10 @@
         <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15709,7 +15718,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15996,7 +16005,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ72">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR72">
         <v>1.64</v>
@@ -16945,7 +16954,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17229,7 +17238,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ78">
         <v>1.78</v>
@@ -17357,7 +17366,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -18181,7 +18190,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18262,7 +18271,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ83">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18465,7 +18474,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18799,7 +18808,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18877,7 +18886,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ86">
         <v>1.73</v>
@@ -19211,7 +19220,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19289,7 +19298,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
         <v>0.6</v>
@@ -19498,7 +19507,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ89">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19623,7 +19632,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19907,7 +19916,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ91">
         <v>1.9</v>
@@ -20035,7 +20044,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20322,7 +20331,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR93">
         <v>1.39</v>
@@ -20653,7 +20662,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21477,7 +21486,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21889,7 +21898,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22095,7 +22104,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22176,7 +22185,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ102">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR102">
         <v>1.55</v>
@@ -22301,7 +22310,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22507,7 +22516,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22791,7 +22800,7 @@
         <v>0.8</v>
       </c>
       <c r="AP105">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
         <v>0.9</v>
@@ -22919,7 +22928,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23125,7 +23134,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23331,7 +23340,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23412,7 +23421,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR108">
         <v>1.41</v>
@@ -23618,7 +23627,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ109">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR109">
         <v>1.57</v>
@@ -23949,7 +23958,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24027,7 +24036,7 @@
         <v>1.8</v>
       </c>
       <c r="AP111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111">
         <v>1.9</v>
@@ -24648,7 +24657,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ114">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR114">
         <v>1.46</v>
@@ -24773,7 +24782,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -24979,7 +24988,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25469,7 +25478,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ118">
         <v>0.6</v>
@@ -25678,7 +25687,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR119">
         <v>1.43</v>
@@ -25881,7 +25890,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ120">
         <v>0.9</v>
@@ -26009,7 +26018,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26215,7 +26224,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26293,7 +26302,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26421,7 +26430,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26627,7 +26636,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26705,7 +26714,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
         <v>1.67</v>
@@ -26833,7 +26842,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -27039,7 +27048,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27529,7 +27538,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ128">
         <v>1.11</v>
@@ -27657,7 +27666,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -27738,7 +27747,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ129">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR129">
         <v>2.07</v>
@@ -28069,7 +28078,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28275,7 +28284,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28971,10 +28980,10 @@
         <v>2.29</v>
       </c>
       <c r="AP135">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ135">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR135">
         <v>1.68</v>
@@ -29305,7 +29314,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29386,7 +29395,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ137">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR137">
         <v>1.5</v>
@@ -29511,7 +29520,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29592,7 +29601,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ138">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR138">
         <v>1.72</v>
@@ -29923,7 +29932,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30747,7 +30756,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31031,10 +31040,10 @@
         <v>0.8</v>
       </c>
       <c r="AP145">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ145">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR145">
         <v>1.48</v>
@@ -31237,7 +31246,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ146">
         <v>1.11</v>
@@ -31443,7 +31452,7 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ147">
         <v>1.78</v>
@@ -31777,7 +31786,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31858,7 +31867,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ149">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR149">
         <v>1.3</v>
@@ -32061,10 +32070,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ150">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR150">
         <v>1.64</v>
@@ -32189,7 +32198,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32395,7 +32404,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32682,7 +32691,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ153">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR153">
         <v>1.59</v>
@@ -33013,7 +33022,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33219,7 +33228,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33425,7 +33434,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33631,7 +33640,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33837,7 +33846,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34455,7 +34464,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34739,7 +34748,7 @@
         <v>1.25</v>
       </c>
       <c r="AP163">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -34945,7 +34954,7 @@
         <v>0.29</v>
       </c>
       <c r="AP164">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ164">
         <v>0.5600000000000001</v>
@@ -35073,7 +35082,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35360,7 +35369,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ166">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR166">
         <v>1.66</v>
@@ -35691,7 +35700,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35897,7 +35906,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36515,7 +36524,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36596,7 +36605,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ172">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR172">
         <v>1.66</v>
@@ -37005,7 +37014,7 @@
         <v>2</v>
       </c>
       <c r="AP174">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ174">
         <v>1.9</v>
@@ -37339,7 +37348,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37751,7 +37760,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37829,10 +37838,10 @@
         <v>1.43</v>
       </c>
       <c r="AP178">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ178">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR178">
         <v>1.49</v>
@@ -37957,7 +37966,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38244,7 +38253,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ180">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38575,7 +38584,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -38987,7 +38996,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39193,7 +39202,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39274,7 +39283,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ185">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR185">
         <v>1.69</v>
@@ -39399,7 +39408,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39889,7 +39898,7 @@
         <v>0.63</v>
       </c>
       <c r="AP188">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ188">
         <v>0.5600000000000001</v>
@@ -40017,7 +40026,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40380,6 +40389,830 @@
       </c>
       <c r="BP190">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7778267</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45822.22916666666</v>
+      </c>
+      <c r="F191">
+        <v>20</v>
+      </c>
+      <c r="G191" t="s">
+        <v>77</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>2</v>
+      </c>
+      <c r="O191" t="s">
+        <v>154</v>
+      </c>
+      <c r="P191" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q191">
+        <v>4.33</v>
+      </c>
+      <c r="R191">
+        <v>2.05</v>
+      </c>
+      <c r="S191">
+        <v>2.75</v>
+      </c>
+      <c r="T191">
+        <v>1.44</v>
+      </c>
+      <c r="U191">
+        <v>2.63</v>
+      </c>
+      <c r="V191">
+        <v>3.25</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>10</v>
+      </c>
+      <c r="Y191">
+        <v>1.06</v>
+      </c>
+      <c r="Z191">
+        <v>3.52</v>
+      </c>
+      <c r="AA191">
+        <v>3.07</v>
+      </c>
+      <c r="AB191">
+        <v>1.96</v>
+      </c>
+      <c r="AC191">
+        <v>1.09</v>
+      </c>
+      <c r="AD191">
+        <v>7</v>
+      </c>
+      <c r="AE191">
+        <v>1.42</v>
+      </c>
+      <c r="AF191">
+        <v>2.8</v>
+      </c>
+      <c r="AG191">
+        <v>2.27</v>
+      </c>
+      <c r="AH191">
+        <v>1.56</v>
+      </c>
+      <c r="AI191">
+        <v>1.95</v>
+      </c>
+      <c r="AJ191">
+        <v>1.8</v>
+      </c>
+      <c r="AK191">
+        <v>1.75</v>
+      </c>
+      <c r="AL191">
+        <v>1.3</v>
+      </c>
+      <c r="AM191">
+        <v>1.25</v>
+      </c>
+      <c r="AN191">
+        <v>1.44</v>
+      </c>
+      <c r="AO191">
+        <v>1.8</v>
+      </c>
+      <c r="AP191">
+        <v>1.4</v>
+      </c>
+      <c r="AQ191">
+        <v>1.73</v>
+      </c>
+      <c r="AR191">
+        <v>1.45</v>
+      </c>
+      <c r="AS191">
+        <v>1.45</v>
+      </c>
+      <c r="AT191">
+        <v>2.9</v>
+      </c>
+      <c r="AU191">
+        <v>4</v>
+      </c>
+      <c r="AV191">
+        <v>7</v>
+      </c>
+      <c r="AW191">
+        <v>7</v>
+      </c>
+      <c r="AX191">
+        <v>9</v>
+      </c>
+      <c r="AY191">
+        <v>11</v>
+      </c>
+      <c r="AZ191">
+        <v>16</v>
+      </c>
+      <c r="BA191">
+        <v>3</v>
+      </c>
+      <c r="BB191">
+        <v>10</v>
+      </c>
+      <c r="BC191">
+        <v>13</v>
+      </c>
+      <c r="BD191">
+        <v>2.32</v>
+      </c>
+      <c r="BE191">
+        <v>6.5</v>
+      </c>
+      <c r="BF191">
+        <v>1.74</v>
+      </c>
+      <c r="BG191">
+        <v>1.34</v>
+      </c>
+      <c r="BH191">
+        <v>2.85</v>
+      </c>
+      <c r="BI191">
+        <v>1.58</v>
+      </c>
+      <c r="BJ191">
+        <v>2.14</v>
+      </c>
+      <c r="BK191">
+        <v>1.95</v>
+      </c>
+      <c r="BL191">
+        <v>1.71</v>
+      </c>
+      <c r="BM191">
+        <v>2.48</v>
+      </c>
+      <c r="BN191">
+        <v>1.43</v>
+      </c>
+      <c r="BO191">
+        <v>3.25</v>
+      </c>
+      <c r="BP191">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7778266</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45822.25</v>
+      </c>
+      <c r="F192">
+        <v>20</v>
+      </c>
+      <c r="G192" t="s">
+        <v>73</v>
+      </c>
+      <c r="H192" t="s">
+        <v>76</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>91</v>
+      </c>
+      <c r="P192" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q192">
+        <v>4</v>
+      </c>
+      <c r="R192">
+        <v>2.05</v>
+      </c>
+      <c r="S192">
+        <v>2.62</v>
+      </c>
+      <c r="T192">
+        <v>1.42</v>
+      </c>
+      <c r="U192">
+        <v>2.62</v>
+      </c>
+      <c r="V192">
+        <v>2.95</v>
+      </c>
+      <c r="W192">
+        <v>1.35</v>
+      </c>
+      <c r="X192">
+        <v>9</v>
+      </c>
+      <c r="Y192">
+        <v>1.07</v>
+      </c>
+      <c r="Z192">
+        <v>3.5</v>
+      </c>
+      <c r="AA192">
+        <v>3.11</v>
+      </c>
+      <c r="AB192">
+        <v>1.95</v>
+      </c>
+      <c r="AC192">
+        <v>1.07</v>
+      </c>
+      <c r="AD192">
+        <v>8</v>
+      </c>
+      <c r="AE192">
+        <v>1.38</v>
+      </c>
+      <c r="AF192">
+        <v>3</v>
+      </c>
+      <c r="AG192">
+        <v>2.05</v>
+      </c>
+      <c r="AH192">
+        <v>1.68</v>
+      </c>
+      <c r="AI192">
+        <v>1.83</v>
+      </c>
+      <c r="AJ192">
+        <v>1.83</v>
+      </c>
+      <c r="AK192">
+        <v>1.73</v>
+      </c>
+      <c r="AL192">
+        <v>1.28</v>
+      </c>
+      <c r="AM192">
+        <v>1.28</v>
+      </c>
+      <c r="AN192">
+        <v>1.4</v>
+      </c>
+      <c r="AO192">
+        <v>1.44</v>
+      </c>
+      <c r="AP192">
+        <v>1.27</v>
+      </c>
+      <c r="AQ192">
+        <v>1.6</v>
+      </c>
+      <c r="AR192">
+        <v>1.3</v>
+      </c>
+      <c r="AS192">
+        <v>1.59</v>
+      </c>
+      <c r="AT192">
+        <v>2.89</v>
+      </c>
+      <c r="AU192">
+        <v>0</v>
+      </c>
+      <c r="AV192">
+        <v>3</v>
+      </c>
+      <c r="AW192">
+        <v>6</v>
+      </c>
+      <c r="AX192">
+        <v>3</v>
+      </c>
+      <c r="AY192">
+        <v>6</v>
+      </c>
+      <c r="AZ192">
+        <v>6</v>
+      </c>
+      <c r="BA192">
+        <v>3</v>
+      </c>
+      <c r="BB192">
+        <v>3</v>
+      </c>
+      <c r="BC192">
+        <v>6</v>
+      </c>
+      <c r="BD192">
+        <v>2.07</v>
+      </c>
+      <c r="BE192">
+        <v>6.5</v>
+      </c>
+      <c r="BF192">
+        <v>1.91</v>
+      </c>
+      <c r="BG192">
+        <v>1.32</v>
+      </c>
+      <c r="BH192">
+        <v>2.9</v>
+      </c>
+      <c r="BI192">
+        <v>1.55</v>
+      </c>
+      <c r="BJ192">
+        <v>2.2</v>
+      </c>
+      <c r="BK192">
+        <v>1.92</v>
+      </c>
+      <c r="BL192">
+        <v>1.73</v>
+      </c>
+      <c r="BM192">
+        <v>2.43</v>
+      </c>
+      <c r="BN192">
+        <v>1.45</v>
+      </c>
+      <c r="BO192">
+        <v>3.2</v>
+      </c>
+      <c r="BP192">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7778263</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45822.25</v>
+      </c>
+      <c r="F193">
+        <v>20</v>
+      </c>
+      <c r="G193" t="s">
+        <v>86</v>
+      </c>
+      <c r="H193" t="s">
+        <v>87</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>2</v>
+      </c>
+      <c r="O193" t="s">
+        <v>214</v>
+      </c>
+      <c r="P193" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q193">
+        <v>4</v>
+      </c>
+      <c r="R193">
+        <v>2.1</v>
+      </c>
+      <c r="S193">
+        <v>2.88</v>
+      </c>
+      <c r="T193">
+        <v>1.44</v>
+      </c>
+      <c r="U193">
+        <v>2.63</v>
+      </c>
+      <c r="V193">
+        <v>3.25</v>
+      </c>
+      <c r="W193">
+        <v>1.33</v>
+      </c>
+      <c r="X193">
+        <v>9</v>
+      </c>
+      <c r="Y193">
+        <v>1.07</v>
+      </c>
+      <c r="Z193">
+        <v>3.27</v>
+      </c>
+      <c r="AA193">
+        <v>3.12</v>
+      </c>
+      <c r="AB193">
+        <v>2.03</v>
+      </c>
+      <c r="AC193">
+        <v>1.07</v>
+      </c>
+      <c r="AD193">
+        <v>8</v>
+      </c>
+      <c r="AE193">
+        <v>1.38</v>
+      </c>
+      <c r="AF193">
+        <v>3</v>
+      </c>
+      <c r="AG193">
+        <v>2.15</v>
+      </c>
+      <c r="AH193">
+        <v>1.62</v>
+      </c>
+      <c r="AI193">
+        <v>1.91</v>
+      </c>
+      <c r="AJ193">
+        <v>1.91</v>
+      </c>
+      <c r="AK193">
+        <v>1.67</v>
+      </c>
+      <c r="AL193">
+        <v>1.28</v>
+      </c>
+      <c r="AM193">
+        <v>1.3</v>
+      </c>
+      <c r="AN193">
+        <v>2.5</v>
+      </c>
+      <c r="AO193">
+        <v>1.63</v>
+      </c>
+      <c r="AP193">
+        <v>2.36</v>
+      </c>
+      <c r="AQ193">
+        <v>1.56</v>
+      </c>
+      <c r="AR193">
+        <v>1.59</v>
+      </c>
+      <c r="AS193">
+        <v>1.64</v>
+      </c>
+      <c r="AT193">
+        <v>3.23</v>
+      </c>
+      <c r="AU193">
+        <v>5</v>
+      </c>
+      <c r="AV193">
+        <v>4</v>
+      </c>
+      <c r="AW193">
+        <v>13</v>
+      </c>
+      <c r="AX193">
+        <v>5</v>
+      </c>
+      <c r="AY193">
+        <v>18</v>
+      </c>
+      <c r="AZ193">
+        <v>9</v>
+      </c>
+      <c r="BA193">
+        <v>12</v>
+      </c>
+      <c r="BB193">
+        <v>3</v>
+      </c>
+      <c r="BC193">
+        <v>15</v>
+      </c>
+      <c r="BD193">
+        <v>2.48</v>
+      </c>
+      <c r="BE193">
+        <v>6.75</v>
+      </c>
+      <c r="BF193">
+        <v>1.65</v>
+      </c>
+      <c r="BG193">
+        <v>1.28</v>
+      </c>
+      <c r="BH193">
+        <v>3.15</v>
+      </c>
+      <c r="BI193">
+        <v>1.49</v>
+      </c>
+      <c r="BJ193">
+        <v>2.33</v>
+      </c>
+      <c r="BK193">
+        <v>1.82</v>
+      </c>
+      <c r="BL193">
+        <v>1.83</v>
+      </c>
+      <c r="BM193">
+        <v>2.3</v>
+      </c>
+      <c r="BN193">
+        <v>1.52</v>
+      </c>
+      <c r="BO193">
+        <v>3</v>
+      </c>
+      <c r="BP193">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7778264</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F194">
+        <v>20</v>
+      </c>
+      <c r="G194" t="s">
+        <v>85</v>
+      </c>
+      <c r="H194" t="s">
+        <v>84</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
+      </c>
+      <c r="N194">
+        <v>4</v>
+      </c>
+      <c r="O194" t="s">
+        <v>215</v>
+      </c>
+      <c r="P194" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q194">
+        <v>3.35</v>
+      </c>
+      <c r="R194">
+        <v>2.1</v>
+      </c>
+      <c r="S194">
+        <v>2.9</v>
+      </c>
+      <c r="T194">
+        <v>1.36</v>
+      </c>
+      <c r="U194">
+        <v>2.9</v>
+      </c>
+      <c r="V194">
+        <v>2.55</v>
+      </c>
+      <c r="W194">
+        <v>1.45</v>
+      </c>
+      <c r="X194">
+        <v>6</v>
+      </c>
+      <c r="Y194">
+        <v>1.11</v>
+      </c>
+      <c r="Z194">
+        <v>2.74</v>
+      </c>
+      <c r="AA194">
+        <v>3.23</v>
+      </c>
+      <c r="AB194">
+        <v>2.25</v>
+      </c>
+      <c r="AC194">
+        <v>1.05</v>
+      </c>
+      <c r="AD194">
+        <v>9.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.25</v>
+      </c>
+      <c r="AF194">
+        <v>3.75</v>
+      </c>
+      <c r="AG194">
+        <v>1.76</v>
+      </c>
+      <c r="AH194">
+        <v>1.94</v>
+      </c>
+      <c r="AI194">
+        <v>1.57</v>
+      </c>
+      <c r="AJ194">
+        <v>2.2</v>
+      </c>
+      <c r="AK194">
+        <v>1.55</v>
+      </c>
+      <c r="AL194">
+        <v>1.25</v>
+      </c>
+      <c r="AM194">
+        <v>1.4</v>
+      </c>
+      <c r="AN194">
+        <v>1.22</v>
+      </c>
+      <c r="AO194">
+        <v>1.1</v>
+      </c>
+      <c r="AP194">
+        <v>1.2</v>
+      </c>
+      <c r="AQ194">
+        <v>1.09</v>
+      </c>
+      <c r="AR194">
+        <v>1.44</v>
+      </c>
+      <c r="AS194">
+        <v>1.47</v>
+      </c>
+      <c r="AT194">
+        <v>2.91</v>
+      </c>
+      <c r="AU194">
+        <v>6</v>
+      </c>
+      <c r="AV194">
+        <v>7</v>
+      </c>
+      <c r="AW194">
+        <v>12</v>
+      </c>
+      <c r="AX194">
+        <v>5</v>
+      </c>
+      <c r="AY194">
+        <v>18</v>
+      </c>
+      <c r="AZ194">
+        <v>12</v>
+      </c>
+      <c r="BA194">
+        <v>4</v>
+      </c>
+      <c r="BB194">
+        <v>7</v>
+      </c>
+      <c r="BC194">
+        <v>11</v>
+      </c>
+      <c r="BD194">
+        <v>2.08</v>
+      </c>
+      <c r="BE194">
+        <v>6.75</v>
+      </c>
+      <c r="BF194">
+        <v>1.89</v>
+      </c>
+      <c r="BG194">
+        <v>1.25</v>
+      </c>
+      <c r="BH194">
+        <v>3.35</v>
+      </c>
+      <c r="BI194">
+        <v>1.44</v>
+      </c>
+      <c r="BJ194">
+        <v>2.48</v>
+      </c>
+      <c r="BK194">
+        <v>1.73</v>
+      </c>
+      <c r="BL194">
+        <v>1.92</v>
+      </c>
+      <c r="BM194">
+        <v>2.14</v>
+      </c>
+      <c r="BN194">
+        <v>1.58</v>
+      </c>
+      <c r="BO194">
+        <v>2.7</v>
+      </c>
+      <c r="BP194">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['3', '81']</t>
   </si>
   <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['4502']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -677,9 +683,6 @@
   </si>
   <si>
     <t>['50']</t>
-  </si>
-  <si>
-    <t>['73']</t>
   </si>
   <si>
     <t>['32', '51']</t>
@@ -887,6 +890,12 @@
   </si>
   <si>
     <t>['41', '71']</t>
+  </si>
+  <si>
+    <t>['27', '45', '9003']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1513,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1791,7 +1800,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1994,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>0.9</v>
@@ -2406,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>1.73</v>
@@ -2821,7 +2830,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ8">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3152,7 +3161,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3358,7 +3367,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3436,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3564,7 +3573,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3770,7 +3779,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4260,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ15">
         <v>0.89</v>
@@ -4388,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -4594,7 +4603,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4800,7 +4809,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4881,7 +4890,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
         <v>2.07</v>
@@ -5499,7 +5508,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5624,7 +5633,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5908,10 +5917,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ23">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -6036,7 +6045,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6114,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>1.73</v>
@@ -6320,7 +6329,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ25">
         <v>1.56</v>
@@ -6654,7 +6663,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6860,7 +6869,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7147,7 +7156,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ29">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -7272,7 +7281,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7684,7 +7693,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8302,7 +8311,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8380,10 +8389,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR35">
         <v>1.47</v>
@@ -8508,7 +8517,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8586,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR36">
         <v>1.08</v>
@@ -8714,7 +8723,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8792,7 +8801,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ37">
         <v>1.09</v>
@@ -8920,7 +8929,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9204,7 +9213,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9538,7 +9547,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9619,7 +9628,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ41">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>0</v>
@@ -9950,7 +9959,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10028,7 +10037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ43">
         <v>1.1</v>
@@ -10568,7 +10577,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10774,7 +10783,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10855,7 +10864,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ47">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR47">
         <v>1.63</v>
@@ -10980,7 +10989,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11267,7 +11276,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11804,7 +11813,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11882,10 +11891,10 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ52">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12216,7 +12225,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12294,7 +12303,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ54">
         <v>1.73</v>
@@ -12503,7 +12512,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR55">
         <v>1.24</v>
@@ -12706,7 +12715,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ56">
         <v>1.6</v>
@@ -12915,7 +12924,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ57">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.46</v>
@@ -13246,7 +13255,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13452,7 +13461,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13736,10 +13745,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -13942,7 +13951,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ62">
         <v>1.1</v>
@@ -14276,7 +14285,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14354,10 +14363,10 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR64">
         <v>1.47</v>
@@ -15100,7 +15109,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15306,7 +15315,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15718,7 +15727,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -16211,7 +16220,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16417,7 +16426,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR74">
         <v>1.09</v>
@@ -16620,10 +16629,10 @@
         <v>2</v>
       </c>
       <c r="AP75">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ75">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR75">
         <v>1.45</v>
@@ -16954,7 +16963,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17032,7 +17041,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ77">
         <v>0.89</v>
@@ -17366,7 +17375,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17856,7 +17865,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ81">
         <v>0.89</v>
@@ -18190,7 +18199,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18680,7 +18689,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ85">
         <v>0.89</v>
@@ -18808,7 +18817,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19095,7 +19104,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR87">
         <v>1.34</v>
@@ -19220,7 +19229,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19301,7 +19310,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19632,7 +19641,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19713,7 +19722,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ90">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR90">
         <v>1.9</v>
@@ -19919,7 +19928,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR91">
         <v>1.32</v>
@@ -20044,7 +20053,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20328,7 +20337,7 @@
         <v>1.8</v>
       </c>
       <c r="AP93">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ93">
         <v>1.6</v>
@@ -20537,7 +20546,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR94">
         <v>1.55</v>
@@ -20662,7 +20671,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20743,7 +20752,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -20946,7 +20955,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ96">
         <v>1.78</v>
@@ -21486,7 +21495,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21770,7 +21779,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ100">
         <v>0.5600000000000001</v>
@@ -21898,7 +21907,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22104,7 +22113,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22182,7 +22191,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>1.6</v>
@@ -22310,7 +22319,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22516,7 +22525,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22594,7 +22603,7 @@
         <v>1.67</v>
       </c>
       <c r="AP104">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ104">
         <v>1.73</v>
@@ -22803,7 +22812,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR105">
         <v>1.2</v>
@@ -22928,7 +22937,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23006,7 +23015,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ106">
         <v>1.67</v>
@@ -23134,7 +23143,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23212,10 +23221,10 @@
         <v>2.25</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ107">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR107">
         <v>1.41</v>
@@ -23340,7 +23349,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23624,7 +23633,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ109">
         <v>1.73</v>
@@ -23958,7 +23967,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24039,7 +24048,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ111">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR111">
         <v>1.52</v>
@@ -24451,7 +24460,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR113">
         <v>1.45</v>
@@ -24654,7 +24663,7 @@
         <v>0.8</v>
       </c>
       <c r="AP114">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ114">
         <v>1.09</v>
@@ -24782,7 +24791,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -24988,7 +24997,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25481,7 +25490,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ118">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25893,7 +25902,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ120">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR120">
         <v>1.31</v>
@@ -26018,7 +26027,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26224,7 +26233,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26430,7 +26439,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26636,7 +26645,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26842,7 +26851,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -26920,7 +26929,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ125">
         <v>1.1</v>
@@ -27048,7 +27057,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27129,7 +27138,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ126">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR126">
         <v>1.31</v>
@@ -27541,7 +27550,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ128">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -27666,7 +27675,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -27953,7 +27962,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ130">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28078,7 +28087,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28156,10 +28165,10 @@
         <v>0.14</v>
       </c>
       <c r="AP131">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ131">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR131">
         <v>1.34</v>
@@ -28284,7 +28293,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28362,7 +28371,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ132">
         <v>0.89</v>
@@ -28568,7 +28577,7 @@
         <v>0.8</v>
       </c>
       <c r="AP133">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.5600000000000001</v>
@@ -29314,7 +29323,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29520,7 +29529,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29598,7 +29607,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>1.09</v>
@@ -29932,7 +29941,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30013,7 +30022,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ140">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30628,7 +30637,7 @@
         <v>0.4</v>
       </c>
       <c r="AP143">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ143">
         <v>0.5600000000000001</v>
@@ -30756,7 +30765,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31249,7 +31258,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ146">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR146">
         <v>1.26</v>
@@ -31786,7 +31795,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31864,7 +31873,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32198,7 +32207,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32279,7 +32288,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ151">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32404,7 +32413,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32482,7 +32491,7 @@
         <v>1</v>
       </c>
       <c r="AP152">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ152">
         <v>0.9</v>
@@ -32897,7 +32906,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ154">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR154">
         <v>1.91</v>
@@ -33022,7 +33031,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33100,7 +33109,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ155">
         <v>1.1</v>
@@ -33228,7 +33237,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33309,7 +33318,7 @@
         <v>1</v>
       </c>
       <c r="AQ156">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR156">
         <v>1.35</v>
@@ -33434,7 +33443,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33640,7 +33649,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33846,7 +33855,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -33924,10 +33933,10 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ159">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34133,7 +34142,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ160">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR160">
         <v>1.42</v>
@@ -34464,7 +34473,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34545,7 +34554,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ162">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -35082,7 +35091,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35572,7 +35581,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ167">
         <v>0.89</v>
@@ -35700,7 +35709,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35906,7 +35915,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36193,7 +36202,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ170">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR170">
         <v>1.87</v>
@@ -36524,7 +36533,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36602,7 +36611,7 @@
         <v>1.89</v>
       </c>
       <c r="AP172">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ172">
         <v>1.73</v>
@@ -37017,7 +37026,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ174">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR174">
         <v>1.27</v>
@@ -37220,7 +37229,7 @@
         <v>1.22</v>
       </c>
       <c r="AP175">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ175">
         <v>1.1</v>
@@ -37348,7 +37357,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37426,7 +37435,7 @@
         <v>1.86</v>
       </c>
       <c r="AP176">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ176">
         <v>1.78</v>
@@ -37632,7 +37641,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ177">
         <v>1.73</v>
@@ -37760,7 +37769,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37966,7 +37975,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38047,7 +38056,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ179">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR179">
         <v>1.72</v>
@@ -38584,7 +38593,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -38665,7 +38674,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ182">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR182">
         <v>1.42</v>
@@ -38996,7 +39005,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39202,7 +39211,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39408,7 +39417,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -40026,7 +40035,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40438,7 +40447,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40644,7 +40653,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -41056,7 +41065,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41213,6 +41222,1036 @@
       </c>
       <c r="BP194">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7778268</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45823.08333333334</v>
+      </c>
+      <c r="F195">
+        <v>20</v>
+      </c>
+      <c r="G195" t="s">
+        <v>88</v>
+      </c>
+      <c r="H195" t="s">
+        <v>75</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>216</v>
+      </c>
+      <c r="P195" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q195">
+        <v>2.8</v>
+      </c>
+      <c r="R195">
+        <v>2.25</v>
+      </c>
+      <c r="S195">
+        <v>3.1</v>
+      </c>
+      <c r="T195">
+        <v>1.31</v>
+      </c>
+      <c r="U195">
+        <v>3.2</v>
+      </c>
+      <c r="V195">
+        <v>2.45</v>
+      </c>
+      <c r="W195">
+        <v>1.49</v>
+      </c>
+      <c r="X195">
+        <v>5.75</v>
+      </c>
+      <c r="Y195">
+        <v>1.11</v>
+      </c>
+      <c r="Z195">
+        <v>2.2</v>
+      </c>
+      <c r="AA195">
+        <v>3.55</v>
+      </c>
+      <c r="AB195">
+        <v>2.61</v>
+      </c>
+      <c r="AC195">
+        <v>1.03</v>
+      </c>
+      <c r="AD195">
+        <v>11.5</v>
+      </c>
+      <c r="AE195">
+        <v>1.22</v>
+      </c>
+      <c r="AF195">
+        <v>3.9</v>
+      </c>
+      <c r="AG195">
+        <v>1.56</v>
+      </c>
+      <c r="AH195">
+        <v>2.27</v>
+      </c>
+      <c r="AI195">
+        <v>1.6</v>
+      </c>
+      <c r="AJ195">
+        <v>2.15</v>
+      </c>
+      <c r="AK195">
+        <v>1.44</v>
+      </c>
+      <c r="AL195">
+        <v>1.27</v>
+      </c>
+      <c r="AM195">
+        <v>1.57</v>
+      </c>
+      <c r="AN195">
+        <v>0.89</v>
+      </c>
+      <c r="AO195">
+        <v>0.5</v>
+      </c>
+      <c r="AP195">
+        <v>1.1</v>
+      </c>
+      <c r="AQ195">
+        <v>0.44</v>
+      </c>
+      <c r="AR195">
+        <v>1.47</v>
+      </c>
+      <c r="AS195">
+        <v>1.4</v>
+      </c>
+      <c r="AT195">
+        <v>2.87</v>
+      </c>
+      <c r="AU195">
+        <v>7</v>
+      </c>
+      <c r="AV195">
+        <v>0</v>
+      </c>
+      <c r="AW195">
+        <v>6</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>13</v>
+      </c>
+      <c r="AZ195">
+        <v>4</v>
+      </c>
+      <c r="BA195">
+        <v>7</v>
+      </c>
+      <c r="BB195">
+        <v>3</v>
+      </c>
+      <c r="BC195">
+        <v>10</v>
+      </c>
+      <c r="BD195">
+        <v>2.01</v>
+      </c>
+      <c r="BE195">
+        <v>6.5</v>
+      </c>
+      <c r="BF195">
+        <v>2.26</v>
+      </c>
+      <c r="BG195">
+        <v>1.2</v>
+      </c>
+      <c r="BH195">
+        <v>3.7</v>
+      </c>
+      <c r="BI195">
+        <v>1.41</v>
+      </c>
+      <c r="BJ195">
+        <v>2.6</v>
+      </c>
+      <c r="BK195">
+        <v>1.74</v>
+      </c>
+      <c r="BL195">
+        <v>1.98</v>
+      </c>
+      <c r="BM195">
+        <v>2.19</v>
+      </c>
+      <c r="BN195">
+        <v>1.57</v>
+      </c>
+      <c r="BO195">
+        <v>2.88</v>
+      </c>
+      <c r="BP195">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7778265</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45823.25</v>
+      </c>
+      <c r="F196">
+        <v>20</v>
+      </c>
+      <c r="G196" t="s">
+        <v>79</v>
+      </c>
+      <c r="H196" t="s">
+        <v>81</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>3</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>91</v>
+      </c>
+      <c r="P196" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q196">
+        <v>4</v>
+      </c>
+      <c r="R196">
+        <v>1.95</v>
+      </c>
+      <c r="S196">
+        <v>3.25</v>
+      </c>
+      <c r="T196">
+        <v>1.53</v>
+      </c>
+      <c r="U196">
+        <v>2.38</v>
+      </c>
+      <c r="V196">
+        <v>3.75</v>
+      </c>
+      <c r="W196">
+        <v>1.25</v>
+      </c>
+      <c r="X196">
+        <v>11</v>
+      </c>
+      <c r="Y196">
+        <v>1.05</v>
+      </c>
+      <c r="Z196">
+        <v>2.94</v>
+      </c>
+      <c r="AA196">
+        <v>2.76</v>
+      </c>
+      <c r="AB196">
+        <v>2.39</v>
+      </c>
+      <c r="AC196">
+        <v>1.11</v>
+      </c>
+      <c r="AD196">
+        <v>6.86</v>
+      </c>
+      <c r="AE196">
+        <v>1.48</v>
+      </c>
+      <c r="AF196">
+        <v>2.3</v>
+      </c>
+      <c r="AG196">
+        <v>2.65</v>
+      </c>
+      <c r="AH196">
+        <v>1.41</v>
+      </c>
+      <c r="AI196">
+        <v>2.1</v>
+      </c>
+      <c r="AJ196">
+        <v>1.67</v>
+      </c>
+      <c r="AK196">
+        <v>1.5</v>
+      </c>
+      <c r="AL196">
+        <v>1.39</v>
+      </c>
+      <c r="AM196">
+        <v>1.36</v>
+      </c>
+      <c r="AN196">
+        <v>1.44</v>
+      </c>
+      <c r="AO196">
+        <v>1.9</v>
+      </c>
+      <c r="AP196">
+        <v>1.3</v>
+      </c>
+      <c r="AQ196">
+        <v>2</v>
+      </c>
+      <c r="AR196">
+        <v>1.39</v>
+      </c>
+      <c r="AS196">
+        <v>1.45</v>
+      </c>
+      <c r="AT196">
+        <v>2.84</v>
+      </c>
+      <c r="AU196">
+        <v>0</v>
+      </c>
+      <c r="AV196">
+        <v>6</v>
+      </c>
+      <c r="AW196">
+        <v>9</v>
+      </c>
+      <c r="AX196">
+        <v>6</v>
+      </c>
+      <c r="AY196">
+        <v>9</v>
+      </c>
+      <c r="AZ196">
+        <v>12</v>
+      </c>
+      <c r="BA196">
+        <v>3</v>
+      </c>
+      <c r="BB196">
+        <v>5</v>
+      </c>
+      <c r="BC196">
+        <v>8</v>
+      </c>
+      <c r="BD196">
+        <v>2.15</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>2.11</v>
+      </c>
+      <c r="BG196">
+        <v>1.24</v>
+      </c>
+      <c r="BH196">
+        <v>3.34</v>
+      </c>
+      <c r="BI196">
+        <v>1.47</v>
+      </c>
+      <c r="BJ196">
+        <v>2.42</v>
+      </c>
+      <c r="BK196">
+        <v>1.83</v>
+      </c>
+      <c r="BL196">
+        <v>1.87</v>
+      </c>
+      <c r="BM196">
+        <v>2.34</v>
+      </c>
+      <c r="BN196">
+        <v>1.5</v>
+      </c>
+      <c r="BO196">
+        <v>3.14</v>
+      </c>
+      <c r="BP196">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7778270</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45823.25</v>
+      </c>
+      <c r="F197">
+        <v>20</v>
+      </c>
+      <c r="G197" t="s">
+        <v>72</v>
+      </c>
+      <c r="H197" t="s">
+        <v>80</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>2</v>
+      </c>
+      <c r="O197" t="s">
+        <v>217</v>
+      </c>
+      <c r="P197" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q197">
+        <v>2.6</v>
+      </c>
+      <c r="R197">
+        <v>1.95</v>
+      </c>
+      <c r="S197">
+        <v>4.5</v>
+      </c>
+      <c r="T197">
+        <v>1.5</v>
+      </c>
+      <c r="U197">
+        <v>2.4</v>
+      </c>
+      <c r="V197">
+        <v>3.3</v>
+      </c>
+      <c r="W197">
+        <v>1.29</v>
+      </c>
+      <c r="X197">
+        <v>9.25</v>
+      </c>
+      <c r="Y197">
+        <v>1.05</v>
+      </c>
+      <c r="Z197">
+        <v>1.83</v>
+      </c>
+      <c r="AA197">
+        <v>3.06</v>
+      </c>
+      <c r="AB197">
+        <v>4</v>
+      </c>
+      <c r="AC197">
+        <v>1.09</v>
+      </c>
+      <c r="AD197">
+        <v>6.75</v>
+      </c>
+      <c r="AE197">
+        <v>1.43</v>
+      </c>
+      <c r="AF197">
+        <v>2.6</v>
+      </c>
+      <c r="AG197">
+        <v>2.13</v>
+      </c>
+      <c r="AH197">
+        <v>1.63</v>
+      </c>
+      <c r="AI197">
+        <v>2.1</v>
+      </c>
+      <c r="AJ197">
+        <v>1.65</v>
+      </c>
+      <c r="AK197">
+        <v>1.22</v>
+      </c>
+      <c r="AL197">
+        <v>1.33</v>
+      </c>
+      <c r="AM197">
+        <v>1.82</v>
+      </c>
+      <c r="AN197">
+        <v>1.56</v>
+      </c>
+      <c r="AO197">
+        <v>0.6</v>
+      </c>
+      <c r="AP197">
+        <v>1.5</v>
+      </c>
+      <c r="AQ197">
+        <v>0.64</v>
+      </c>
+      <c r="AR197">
+        <v>1.8</v>
+      </c>
+      <c r="AS197">
+        <v>1.25</v>
+      </c>
+      <c r="AT197">
+        <v>3.05</v>
+      </c>
+      <c r="AU197">
+        <v>5</v>
+      </c>
+      <c r="AV197">
+        <v>5</v>
+      </c>
+      <c r="AW197">
+        <v>10</v>
+      </c>
+      <c r="AX197">
+        <v>5</v>
+      </c>
+      <c r="AY197">
+        <v>15</v>
+      </c>
+      <c r="AZ197">
+        <v>10</v>
+      </c>
+      <c r="BA197">
+        <v>9</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>12</v>
+      </c>
+      <c r="BD197">
+        <v>1.59</v>
+      </c>
+      <c r="BE197">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF197">
+        <v>2.85</v>
+      </c>
+      <c r="BG197">
+        <v>1.24</v>
+      </c>
+      <c r="BH197">
+        <v>3.34</v>
+      </c>
+      <c r="BI197">
+        <v>1.48</v>
+      </c>
+      <c r="BJ197">
+        <v>2.4</v>
+      </c>
+      <c r="BK197">
+        <v>1.85</v>
+      </c>
+      <c r="BL197">
+        <v>1.85</v>
+      </c>
+      <c r="BM197">
+        <v>2.34</v>
+      </c>
+      <c r="BN197">
+        <v>1.5</v>
+      </c>
+      <c r="BO197">
+        <v>3.14</v>
+      </c>
+      <c r="BP197">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7778271</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45823.25</v>
+      </c>
+      <c r="F198">
+        <v>20</v>
+      </c>
+      <c r="G198" t="s">
+        <v>74</v>
+      </c>
+      <c r="H198" t="s">
+        <v>71</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
+        <v>91</v>
+      </c>
+      <c r="P198" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q198">
+        <v>3.3</v>
+      </c>
+      <c r="R198">
+        <v>1.75</v>
+      </c>
+      <c r="S198">
+        <v>4</v>
+      </c>
+      <c r="T198">
+        <v>1.66</v>
+      </c>
+      <c r="U198">
+        <v>2.05</v>
+      </c>
+      <c r="V198">
+        <v>4</v>
+      </c>
+      <c r="W198">
+        <v>1.21</v>
+      </c>
+      <c r="X198">
+        <v>12.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.02</v>
+      </c>
+      <c r="Z198">
+        <v>2.42</v>
+      </c>
+      <c r="AA198">
+        <v>2.61</v>
+      </c>
+      <c r="AB198">
+        <v>3.08</v>
+      </c>
+      <c r="AC198">
+        <v>1.14</v>
+      </c>
+      <c r="AD198">
+        <v>5</v>
+      </c>
+      <c r="AE198">
+        <v>1.6</v>
+      </c>
+      <c r="AF198">
+        <v>2.1</v>
+      </c>
+      <c r="AG198">
+        <v>2.92</v>
+      </c>
+      <c r="AH198">
+        <v>1.34</v>
+      </c>
+      <c r="AI198">
+        <v>2.3</v>
+      </c>
+      <c r="AJ198">
+        <v>1.53</v>
+      </c>
+      <c r="AK198">
+        <v>1.33</v>
+      </c>
+      <c r="AL198">
+        <v>1.42</v>
+      </c>
+      <c r="AM198">
+        <v>1.49</v>
+      </c>
+      <c r="AN198">
+        <v>1.8</v>
+      </c>
+      <c r="AO198">
+        <v>1.11</v>
+      </c>
+      <c r="AP198">
+        <v>1.64</v>
+      </c>
+      <c r="AQ198">
+        <v>1.3</v>
+      </c>
+      <c r="AR198">
+        <v>1.62</v>
+      </c>
+      <c r="AS198">
+        <v>1.63</v>
+      </c>
+      <c r="AT198">
+        <v>3.25</v>
+      </c>
+      <c r="AU198">
+        <v>2</v>
+      </c>
+      <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>5</v>
+      </c>
+      <c r="AX198">
+        <v>13</v>
+      </c>
+      <c r="AY198">
+        <v>7</v>
+      </c>
+      <c r="AZ198">
+        <v>17</v>
+      </c>
+      <c r="BA198">
+        <v>3</v>
+      </c>
+      <c r="BB198">
+        <v>4</v>
+      </c>
+      <c r="BC198">
+        <v>7</v>
+      </c>
+      <c r="BD198">
+        <v>1.86</v>
+      </c>
+      <c r="BE198">
+        <v>8.1</v>
+      </c>
+      <c r="BF198">
+        <v>2.31</v>
+      </c>
+      <c r="BG198">
+        <v>1.32</v>
+      </c>
+      <c r="BH198">
+        <v>2.98</v>
+      </c>
+      <c r="BI198">
+        <v>1.61</v>
+      </c>
+      <c r="BJ198">
+        <v>2.17</v>
+      </c>
+      <c r="BK198">
+        <v>2.01</v>
+      </c>
+      <c r="BL198">
+        <v>1.68</v>
+      </c>
+      <c r="BM198">
+        <v>2.62</v>
+      </c>
+      <c r="BN198">
+        <v>1.38</v>
+      </c>
+      <c r="BO198">
+        <v>2.9</v>
+      </c>
+      <c r="BP198">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7778269</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45823.27083333334</v>
+      </c>
+      <c r="F199">
+        <v>20</v>
+      </c>
+      <c r="G199" t="s">
+        <v>82</v>
+      </c>
+      <c r="H199" t="s">
+        <v>70</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>91</v>
+      </c>
+      <c r="P199" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q199">
+        <v>3.2</v>
+      </c>
+      <c r="R199">
+        <v>2.2</v>
+      </c>
+      <c r="S199">
+        <v>3.25</v>
+      </c>
+      <c r="T199">
+        <v>1.4</v>
+      </c>
+      <c r="U199">
+        <v>2.75</v>
+      </c>
+      <c r="V199">
+        <v>2.75</v>
+      </c>
+      <c r="W199">
+        <v>1.4</v>
+      </c>
+      <c r="X199">
+        <v>8</v>
+      </c>
+      <c r="Y199">
+        <v>1.08</v>
+      </c>
+      <c r="Z199">
+        <v>2.52</v>
+      </c>
+      <c r="AA199">
+        <v>3.15</v>
+      </c>
+      <c r="AB199">
+        <v>2.46</v>
+      </c>
+      <c r="AC199">
+        <v>1</v>
+      </c>
+      <c r="AD199">
+        <v>9.1</v>
+      </c>
+      <c r="AE199">
+        <v>1.3</v>
+      </c>
+      <c r="AF199">
+        <v>3.51</v>
+      </c>
+      <c r="AG199">
+        <v>1.91</v>
+      </c>
+      <c r="AH199">
+        <v>1.79</v>
+      </c>
+      <c r="AI199">
+        <v>1.75</v>
+      </c>
+      <c r="AJ199">
+        <v>2</v>
+      </c>
+      <c r="AK199">
+        <v>1.47</v>
+      </c>
+      <c r="AL199">
+        <v>1.32</v>
+      </c>
+      <c r="AM199">
+        <v>1.46</v>
+      </c>
+      <c r="AN199">
+        <v>1.67</v>
+      </c>
+      <c r="AO199">
+        <v>0.9</v>
+      </c>
+      <c r="AP199">
+        <v>1.6</v>
+      </c>
+      <c r="AQ199">
+        <v>0.91</v>
+      </c>
+      <c r="AR199">
+        <v>1.39</v>
+      </c>
+      <c r="AS199">
+        <v>1.57</v>
+      </c>
+      <c r="AT199">
+        <v>2.96</v>
+      </c>
+      <c r="AU199">
+        <v>10</v>
+      </c>
+      <c r="AV199">
+        <v>6</v>
+      </c>
+      <c r="AW199">
+        <v>8</v>
+      </c>
+      <c r="AX199">
+        <v>12</v>
+      </c>
+      <c r="AY199">
+        <v>18</v>
+      </c>
+      <c r="AZ199">
+        <v>18</v>
+      </c>
+      <c r="BA199">
+        <v>1</v>
+      </c>
+      <c r="BB199">
+        <v>7</v>
+      </c>
+      <c r="BC199">
+        <v>8</v>
+      </c>
+      <c r="BD199">
+        <v>1.88</v>
+      </c>
+      <c r="BE199">
+        <v>8.5</v>
+      </c>
+      <c r="BF199">
+        <v>2.25</v>
+      </c>
+      <c r="BG199">
+        <v>1.21</v>
+      </c>
+      <c r="BH199">
+        <v>3.58</v>
+      </c>
+      <c r="BI199">
+        <v>1.43</v>
+      </c>
+      <c r="BJ199">
+        <v>2.54</v>
+      </c>
+      <c r="BK199">
+        <v>1.77</v>
+      </c>
+      <c r="BL199">
+        <v>1.94</v>
+      </c>
+      <c r="BM199">
+        <v>2.23</v>
+      </c>
+      <c r="BN199">
+        <v>1.55</v>
+      </c>
+      <c r="BO199">
+        <v>2.97</v>
+      </c>
+      <c r="BP199">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -40746,19 +40746,19 @@
         <v>2.89</v>
       </c>
       <c r="AU192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV192">
         <v>3</v>
       </c>
       <c r="AW192">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX192">
         <v>3</v>
       </c>
       <c r="AY192">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ192">
         <v>6</v>
@@ -41167,13 +41167,13 @@
         <v>12</v>
       </c>
       <c r="AX194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY194">
         <v>18</v>
       </c>
       <c r="AZ194">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA194">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -41991,13 +41991,13 @@
         <v>5</v>
       </c>
       <c r="AX198">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY198">
         <v>7</v>
       </c>
       <c r="AZ198">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA198">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,18 @@
     <t>['4502']</t>
   </si>
   <si>
+    <t>['6', '34']</t>
+  </si>
+  <si>
+    <t>['9', '16', '45']</t>
+  </si>
+  <si>
+    <t>['20', '62']</t>
+  </si>
+  <si>
+    <t>['19', '31', '74']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -896,6 +908,21 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['4', '36']</t>
+  </si>
+  <si>
+    <t>['24', '53', '84']</t>
+  </si>
+  <si>
+    <t>['10', '52']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1540,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1797,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3">
         <v>2</v>
@@ -2418,7 +2445,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2621,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ7">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2827,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -3036,7 +3063,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3161,7 +3188,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3239,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>1.56</v>
@@ -3367,7 +3394,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3573,7 +3600,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3651,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3779,7 +3806,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3857,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ13">
         <v>1.6</v>
@@ -4066,7 +4093,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ14">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR14">
         <v>1.76</v>
@@ -4272,7 +4299,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ15">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4603,7 +4630,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4681,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17">
         <v>1.1</v>
@@ -4809,7 +4836,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5302,7 +5329,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ20">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5633,7 +5660,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5711,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ22">
         <v>1.6</v>
@@ -6045,7 +6072,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6126,7 +6153,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6663,7 +6690,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6744,7 +6771,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ27">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6869,7 +6896,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -6947,10 +6974,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.8</v>
@@ -7281,7 +7308,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7359,7 +7386,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>1.09</v>
@@ -7565,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ31">
         <v>0.5600000000000001</v>
@@ -7693,7 +7720,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7771,7 +7798,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ32">
         <v>1.1</v>
@@ -8183,10 +8210,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
         <v>1.99</v>
@@ -8311,7 +8338,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8517,7 +8544,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8723,7 +8750,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8929,7 +8956,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9007,7 +9034,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38">
         <v>1.73</v>
@@ -9547,7 +9574,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9834,7 +9861,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>2.05</v>
@@ -9959,7 +9986,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10040,7 +10067,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.74</v>
@@ -10577,7 +10604,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10783,7 +10810,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10861,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ47">
         <v>0.64</v>
@@ -10989,7 +11016,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11067,10 +11094,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.45</v>
@@ -11685,10 +11712,10 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.02</v>
@@ -11813,7 +11840,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12097,7 +12124,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ53">
         <v>0.89</v>
@@ -12225,7 +12252,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12306,7 +12333,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ54">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR54">
         <v>1.44</v>
@@ -12509,7 +12536,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ55">
         <v>0.91</v>
@@ -13255,7 +13282,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13336,7 +13363,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ59">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13461,7 +13488,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13539,7 +13566,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ60">
         <v>0.9</v>
@@ -14157,10 +14184,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14285,7 +14312,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14569,7 +14596,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ65">
         <v>0.5600000000000001</v>
@@ -14984,7 +15011,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR67">
         <v>1.72</v>
@@ -15109,7 +15136,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15187,7 +15214,7 @@
         <v>3</v>
       </c>
       <c r="AP68">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ68">
         <v>1.73</v>
@@ -15315,7 +15342,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15602,7 +15629,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ70">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.48</v>
@@ -15727,7 +15754,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15805,10 +15832,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ71">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -16423,7 +16450,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ74">
         <v>0.44</v>
@@ -16835,7 +16862,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ76">
         <v>1.1</v>
@@ -16963,7 +16990,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17250,7 +17277,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ78">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR78">
         <v>1.29</v>
@@ -17375,7 +17402,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17659,10 +17686,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ80">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR80">
         <v>1.25</v>
@@ -18071,7 +18098,7 @@
         <v>0.8</v>
       </c>
       <c r="AP82">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ82">
         <v>0.9</v>
@@ -18199,7 +18226,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18277,7 +18304,7 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.6</v>
@@ -18692,7 +18719,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ85">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR85">
         <v>1.39</v>
@@ -18817,7 +18844,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18898,7 +18925,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
         <v>1.65</v>
@@ -19101,7 +19128,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87">
         <v>0.91</v>
@@ -19229,7 +19256,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19641,7 +19668,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19719,7 +19746,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ90">
         <v>0.44</v>
@@ -20053,7 +20080,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20134,7 +20161,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ92">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR92">
         <v>1.46</v>
@@ -20671,7 +20698,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20749,7 +20776,7 @@
         <v>0.25</v>
       </c>
       <c r="AP95">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ95">
         <v>0.44</v>
@@ -20958,7 +20985,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ96">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR96">
         <v>1.47</v>
@@ -21161,10 +21188,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ97">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR97">
         <v>1.91</v>
@@ -21495,7 +21522,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21573,7 +21600,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21907,7 +21934,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -21985,7 +22012,7 @@
         <v>0.8</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22113,7 +22140,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22319,7 +22346,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22400,7 +22427,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22525,7 +22552,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22606,7 +22633,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ104">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR104">
         <v>1.53</v>
@@ -22937,7 +22964,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23018,7 +23045,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ106">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23143,7 +23170,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23349,7 +23376,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23427,7 +23454,7 @@
         <v>1.33</v>
       </c>
       <c r="AP108">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ108">
         <v>1.56</v>
@@ -23839,7 +23866,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ110">
         <v>0.89</v>
@@ -23967,7 +23994,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24251,10 +24278,10 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ112">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.78</v>
@@ -24791,7 +24818,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -24869,7 +24896,7 @@
         <v>0.83</v>
       </c>
       <c r="AP115">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>1.1</v>
@@ -24997,7 +25024,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25281,10 +25308,10 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ117">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR117">
         <v>1.59</v>
@@ -26027,7 +26054,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26105,10 +26132,10 @@
         <v>0.8</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ121">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR121">
         <v>1.42</v>
@@ -26233,7 +26260,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26439,7 +26466,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26520,7 +26547,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ123">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26645,7 +26672,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26726,7 +26753,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ124">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
         <v>1.26</v>
@@ -26851,7 +26878,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -26932,7 +26959,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ125">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.53</v>
@@ -27057,7 +27084,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27135,7 +27162,7 @@
         <v>2</v>
       </c>
       <c r="AP126">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ126">
         <v>2</v>
@@ -27344,7 +27371,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ127">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.65</v>
@@ -27675,7 +27702,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -27753,7 +27780,7 @@
         <v>2.17</v>
       </c>
       <c r="AP129">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ129">
         <v>1.73</v>
@@ -28087,7 +28114,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28293,7 +28320,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28580,7 +28607,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR133">
         <v>1.62</v>
@@ -29198,7 +29225,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ136">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.42</v>
@@ -29323,7 +29350,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29529,7 +29556,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29813,10 +29840,10 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ139">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR139">
         <v>1.63</v>
@@ -29941,7 +29968,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30225,10 +30252,10 @@
         <v>0.67</v>
       </c>
       <c r="AP141">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ141">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR141">
         <v>1.35</v>
@@ -30431,7 +30458,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30765,7 +30792,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -30843,10 +30870,10 @@
         <v>1.63</v>
       </c>
       <c r="AP144">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.36</v>
@@ -31464,7 +31491,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ147">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR147">
         <v>1.43</v>
@@ -31667,10 +31694,10 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ148">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -31795,7 +31822,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32207,7 +32234,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32413,7 +32440,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32903,7 +32930,7 @@
         <v>0.17</v>
       </c>
       <c r="AP154">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ154">
         <v>0.44</v>
@@ -33031,7 +33058,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33237,7 +33264,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33315,7 +33342,7 @@
         <v>2.14</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ156">
         <v>2</v>
@@ -33443,7 +33470,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33521,7 +33548,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ157">
         <v>0.5600000000000001</v>
@@ -33649,7 +33676,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33727,10 +33754,10 @@
         <v>1.78</v>
       </c>
       <c r="AP158">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ158">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR158">
         <v>1.35</v>
@@ -33855,7 +33882,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34139,7 +34166,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ160">
         <v>2</v>
@@ -34348,7 +34375,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ161">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR161">
         <v>1.68</v>
@@ -34473,7 +34500,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34551,7 +34578,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP162">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ162">
         <v>0.64</v>
@@ -35091,7 +35118,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35375,7 +35402,7 @@
         <v>1.25</v>
       </c>
       <c r="AP166">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166">
         <v>1.09</v>
@@ -35584,7 +35611,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ167">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR167">
         <v>1.53</v>
@@ -35709,7 +35736,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35787,7 +35814,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ168">
         <v>0.9</v>
@@ -35915,7 +35942,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -35993,10 +36020,10 @@
         <v>1.67</v>
       </c>
       <c r="AP169">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ169">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR169">
         <v>1.38</v>
@@ -36199,7 +36226,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ170">
         <v>1.3</v>
@@ -36405,7 +36432,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ171">
         <v>0.9</v>
@@ -36533,7 +36560,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36817,10 +36844,10 @@
         <v>1.71</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ173">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR173">
         <v>1.43</v>
@@ -37357,7 +37384,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37438,7 +37465,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR176">
         <v>1.33</v>
@@ -37644,7 +37671,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ177">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -37769,7 +37796,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37975,7 +38002,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38053,7 +38080,7 @@
         <v>0.89</v>
       </c>
       <c r="AP179">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ179">
         <v>0.91</v>
@@ -38465,10 +38492,10 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ181">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR181">
         <v>1.55</v>
@@ -38593,7 +38620,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -38671,7 +38698,7 @@
         <v>0.14</v>
       </c>
       <c r="AP182">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ182">
         <v>0.44</v>
@@ -38877,10 +38904,10 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ183">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR183">
         <v>1.56</v>
@@ -39005,7 +39032,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39083,10 +39110,10 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ184">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39211,7 +39238,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39417,7 +39444,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39498,7 +39525,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39910,7 +39937,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ188">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40035,7 +40062,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40113,7 +40140,7 @@
         <v>1.11</v>
       </c>
       <c r="AP189">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ189">
         <v>1</v>
@@ -40447,7 +40474,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40653,7 +40680,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -41065,7 +41092,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41477,7 +41504,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41889,7 +41916,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42252,6 +42279,1448 @@
       </c>
       <c r="BP199">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7778274</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45829.16666666666</v>
+      </c>
+      <c r="F200">
+        <v>21</v>
+      </c>
+      <c r="G200" t="s">
+        <v>78</v>
+      </c>
+      <c r="H200" t="s">
+        <v>86</v>
+      </c>
+      <c r="I200">
+        <v>2</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>2</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>3</v>
+      </c>
+      <c r="O200" t="s">
+        <v>218</v>
+      </c>
+      <c r="P200" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q200">
+        <v>2.75</v>
+      </c>
+      <c r="R200">
+        <v>2.05</v>
+      </c>
+      <c r="S200">
+        <v>3.8</v>
+      </c>
+      <c r="T200">
+        <v>1.44</v>
+      </c>
+      <c r="U200">
+        <v>2.6</v>
+      </c>
+      <c r="V200">
+        <v>3</v>
+      </c>
+      <c r="W200">
+        <v>1.33</v>
+      </c>
+      <c r="X200">
+        <v>7.9</v>
+      </c>
+      <c r="Y200">
+        <v>1.02</v>
+      </c>
+      <c r="Z200">
+        <v>2</v>
+      </c>
+      <c r="AA200">
+        <v>3.38</v>
+      </c>
+      <c r="AB200">
+        <v>3.09</v>
+      </c>
+      <c r="AC200">
+        <v>1.07</v>
+      </c>
+      <c r="AD200">
+        <v>8</v>
+      </c>
+      <c r="AE200">
+        <v>1.38</v>
+      </c>
+      <c r="AF200">
+        <v>3</v>
+      </c>
+      <c r="AG200">
+        <v>2.17</v>
+      </c>
+      <c r="AH200">
+        <v>1.61</v>
+      </c>
+      <c r="AI200">
+        <v>1.85</v>
+      </c>
+      <c r="AJ200">
+        <v>1.8</v>
+      </c>
+      <c r="AK200">
+        <v>1.3</v>
+      </c>
+      <c r="AL200">
+        <v>1.25</v>
+      </c>
+      <c r="AM200">
+        <v>1.67</v>
+      </c>
+      <c r="AN200">
+        <v>0.78</v>
+      </c>
+      <c r="AO200">
+        <v>1.67</v>
+      </c>
+      <c r="AP200">
+        <v>1</v>
+      </c>
+      <c r="AQ200">
+        <v>1.5</v>
+      </c>
+      <c r="AR200">
+        <v>1.42</v>
+      </c>
+      <c r="AS200">
+        <v>1.52</v>
+      </c>
+      <c r="AT200">
+        <v>2.94</v>
+      </c>
+      <c r="AU200">
+        <v>7</v>
+      </c>
+      <c r="AV200">
+        <v>4</v>
+      </c>
+      <c r="AW200">
+        <v>7</v>
+      </c>
+      <c r="AX200">
+        <v>7</v>
+      </c>
+      <c r="AY200">
+        <v>14</v>
+      </c>
+      <c r="AZ200">
+        <v>11</v>
+      </c>
+      <c r="BA200">
+        <v>3</v>
+      </c>
+      <c r="BB200">
+        <v>4</v>
+      </c>
+      <c r="BC200">
+        <v>7</v>
+      </c>
+      <c r="BD200">
+        <v>1.75</v>
+      </c>
+      <c r="BE200">
+        <v>6.4</v>
+      </c>
+      <c r="BF200">
+        <v>2.32</v>
+      </c>
+      <c r="BG200">
+        <v>1.42</v>
+      </c>
+      <c r="BH200">
+        <v>2.55</v>
+      </c>
+      <c r="BI200">
+        <v>1.71</v>
+      </c>
+      <c r="BJ200">
+        <v>1.95</v>
+      </c>
+      <c r="BK200">
+        <v>2.15</v>
+      </c>
+      <c r="BL200">
+        <v>1.57</v>
+      </c>
+      <c r="BM200">
+        <v>2.8</v>
+      </c>
+      <c r="BN200">
+        <v>1.35</v>
+      </c>
+      <c r="BO200">
+        <v>3.7</v>
+      </c>
+      <c r="BP200">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7778281</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45829.16666666666</v>
+      </c>
+      <c r="F201">
+        <v>21</v>
+      </c>
+      <c r="G201" t="s">
+        <v>71</v>
+      </c>
+      <c r="H201" t="s">
+        <v>88</v>
+      </c>
+      <c r="I201">
+        <v>3</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="K201">
+        <v>5</v>
+      </c>
+      <c r="L201">
+        <v>3</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>5</v>
+      </c>
+      <c r="O201" t="s">
+        <v>219</v>
+      </c>
+      <c r="P201" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q201">
+        <v>3.1</v>
+      </c>
+      <c r="R201">
+        <v>1.85</v>
+      </c>
+      <c r="S201">
+        <v>3.85</v>
+      </c>
+      <c r="T201">
+        <v>1.55</v>
+      </c>
+      <c r="U201">
+        <v>2.3</v>
+      </c>
+      <c r="V201">
+        <v>3.5</v>
+      </c>
+      <c r="W201">
+        <v>1.25</v>
+      </c>
+      <c r="X201">
+        <v>9</v>
+      </c>
+      <c r="Y201">
+        <v>1.01</v>
+      </c>
+      <c r="Z201">
+        <v>2.13</v>
+      </c>
+      <c r="AA201">
+        <v>2.84</v>
+      </c>
+      <c r="AB201">
+        <v>3.35</v>
+      </c>
+      <c r="AC201">
+        <v>1.11</v>
+      </c>
+      <c r="AD201">
+        <v>6.25</v>
+      </c>
+      <c r="AE201">
+        <v>1.5</v>
+      </c>
+      <c r="AF201">
+        <v>2.3</v>
+      </c>
+      <c r="AG201">
+        <v>2.6</v>
+      </c>
+      <c r="AH201">
+        <v>1.43</v>
+      </c>
+      <c r="AI201">
+        <v>2.05</v>
+      </c>
+      <c r="AJ201">
+        <v>1.67</v>
+      </c>
+      <c r="AK201">
+        <v>1.33</v>
+      </c>
+      <c r="AL201">
+        <v>1.33</v>
+      </c>
+      <c r="AM201">
+        <v>1.55</v>
+      </c>
+      <c r="AN201">
+        <v>1.3</v>
+      </c>
+      <c r="AO201">
+        <v>0.89</v>
+      </c>
+      <c r="AP201">
+        <v>1.45</v>
+      </c>
+      <c r="AQ201">
+        <v>0.8</v>
+      </c>
+      <c r="AR201">
+        <v>1.56</v>
+      </c>
+      <c r="AS201">
+        <v>1.12</v>
+      </c>
+      <c r="AT201">
+        <v>2.68</v>
+      </c>
+      <c r="AU201">
+        <v>6</v>
+      </c>
+      <c r="AV201">
+        <v>3</v>
+      </c>
+      <c r="AW201">
+        <v>4</v>
+      </c>
+      <c r="AX201">
+        <v>7</v>
+      </c>
+      <c r="AY201">
+        <v>10</v>
+      </c>
+      <c r="AZ201">
+        <v>10</v>
+      </c>
+      <c r="BA201">
+        <v>2</v>
+      </c>
+      <c r="BB201">
+        <v>3</v>
+      </c>
+      <c r="BC201">
+        <v>5</v>
+      </c>
+      <c r="BD201">
+        <v>1.79</v>
+      </c>
+      <c r="BE201">
+        <v>6.4</v>
+      </c>
+      <c r="BF201">
+        <v>2.23</v>
+      </c>
+      <c r="BG201">
+        <v>1.38</v>
+      </c>
+      <c r="BH201">
+        <v>2.65</v>
+      </c>
+      <c r="BI201">
+        <v>1.66</v>
+      </c>
+      <c r="BJ201">
+        <v>2.02</v>
+      </c>
+      <c r="BK201">
+        <v>2.08</v>
+      </c>
+      <c r="BL201">
+        <v>1.62</v>
+      </c>
+      <c r="BM201">
+        <v>2.65</v>
+      </c>
+      <c r="BN201">
+        <v>1.38</v>
+      </c>
+      <c r="BO201">
+        <v>3.55</v>
+      </c>
+      <c r="BP201">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7778280</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45829.27083333334</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>84</v>
+      </c>
+      <c r="H202" t="s">
+        <v>79</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>2</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>220</v>
+      </c>
+      <c r="P202" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q202">
+        <v>2.65</v>
+      </c>
+      <c r="R202">
+        <v>2.05</v>
+      </c>
+      <c r="S202">
+        <v>3.9</v>
+      </c>
+      <c r="T202">
+        <v>1.42</v>
+      </c>
+      <c r="U202">
+        <v>2.65</v>
+      </c>
+      <c r="V202">
+        <v>2.88</v>
+      </c>
+      <c r="W202">
+        <v>1.36</v>
+      </c>
+      <c r="X202">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y202">
+        <v>1.02</v>
+      </c>
+      <c r="Z202">
+        <v>1.97</v>
+      </c>
+      <c r="AA202">
+        <v>3.15</v>
+      </c>
+      <c r="AB202">
+        <v>3.4</v>
+      </c>
+      <c r="AC202">
+        <v>1.07</v>
+      </c>
+      <c r="AD202">
+        <v>8</v>
+      </c>
+      <c r="AE202">
+        <v>1.35</v>
+      </c>
+      <c r="AF202">
+        <v>3.1</v>
+      </c>
+      <c r="AG202">
+        <v>1.95</v>
+      </c>
+      <c r="AH202">
+        <v>1.75</v>
+      </c>
+      <c r="AI202">
+        <v>1.8</v>
+      </c>
+      <c r="AJ202">
+        <v>1.85</v>
+      </c>
+      <c r="AK202">
+        <v>1.3</v>
+      </c>
+      <c r="AL202">
+        <v>1.28</v>
+      </c>
+      <c r="AM202">
+        <v>1.7</v>
+      </c>
+      <c r="AN202">
+        <v>1.8</v>
+      </c>
+      <c r="AO202">
+        <v>1.1</v>
+      </c>
+      <c r="AP202">
+        <v>1.91</v>
+      </c>
+      <c r="AQ202">
+        <v>1</v>
+      </c>
+      <c r="AR202">
+        <v>1.88</v>
+      </c>
+      <c r="AS202">
+        <v>1.11</v>
+      </c>
+      <c r="AT202">
+        <v>2.99</v>
+      </c>
+      <c r="AU202">
+        <v>5</v>
+      </c>
+      <c r="AV202">
+        <v>2</v>
+      </c>
+      <c r="AW202">
+        <v>2</v>
+      </c>
+      <c r="AX202">
+        <v>4</v>
+      </c>
+      <c r="AY202">
+        <v>7</v>
+      </c>
+      <c r="AZ202">
+        <v>6</v>
+      </c>
+      <c r="BA202">
+        <v>5</v>
+      </c>
+      <c r="BB202">
+        <v>5</v>
+      </c>
+      <c r="BC202">
+        <v>10</v>
+      </c>
+      <c r="BD202">
+        <v>1.67</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>2.43</v>
+      </c>
+      <c r="BG202">
+        <v>1.28</v>
+      </c>
+      <c r="BH202">
+        <v>3.1</v>
+      </c>
+      <c r="BI202">
+        <v>1.5</v>
+      </c>
+      <c r="BJ202">
+        <v>2.3</v>
+      </c>
+      <c r="BK202">
+        <v>1.82</v>
+      </c>
+      <c r="BL202">
+        <v>1.83</v>
+      </c>
+      <c r="BM202">
+        <v>2.28</v>
+      </c>
+      <c r="BN202">
+        <v>1.52</v>
+      </c>
+      <c r="BO202">
+        <v>2.95</v>
+      </c>
+      <c r="BP202">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7778273</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>81</v>
+      </c>
+      <c r="H203" t="s">
+        <v>83</v>
+      </c>
+      <c r="I203">
+        <v>2</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>3</v>
+      </c>
+      <c r="L203">
+        <v>3</v>
+      </c>
+      <c r="M203">
+        <v>3</v>
+      </c>
+      <c r="N203">
+        <v>6</v>
+      </c>
+      <c r="O203" t="s">
+        <v>221</v>
+      </c>
+      <c r="P203" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q203">
+        <v>2.7</v>
+      </c>
+      <c r="R203">
+        <v>2</v>
+      </c>
+      <c r="S203">
+        <v>4</v>
+      </c>
+      <c r="T203">
+        <v>1.44</v>
+      </c>
+      <c r="U203">
+        <v>2.6</v>
+      </c>
+      <c r="V203">
+        <v>3</v>
+      </c>
+      <c r="W203">
+        <v>1.33</v>
+      </c>
+      <c r="X203">
+        <v>7.9</v>
+      </c>
+      <c r="Y203">
+        <v>1.02</v>
+      </c>
+      <c r="Z203">
+        <v>2.1</v>
+      </c>
+      <c r="AA203">
+        <v>3.15</v>
+      </c>
+      <c r="AB203">
+        <v>3.07</v>
+      </c>
+      <c r="AC203">
+        <v>1.07</v>
+      </c>
+      <c r="AD203">
+        <v>8</v>
+      </c>
+      <c r="AE203">
+        <v>1.38</v>
+      </c>
+      <c r="AF203">
+        <v>2.95</v>
+      </c>
+      <c r="AG203">
+        <v>1.88</v>
+      </c>
+      <c r="AH203">
+        <v>1.82</v>
+      </c>
+      <c r="AI203">
+        <v>1.85</v>
+      </c>
+      <c r="AJ203">
+        <v>1.83</v>
+      </c>
+      <c r="AK203">
+        <v>1.28</v>
+      </c>
+      <c r="AL203">
+        <v>1.28</v>
+      </c>
+      <c r="AM203">
+        <v>1.7</v>
+      </c>
+      <c r="AN203">
+        <v>1.67</v>
+      </c>
+      <c r="AO203">
+        <v>1.73</v>
+      </c>
+      <c r="AP203">
+        <v>1.6</v>
+      </c>
+      <c r="AQ203">
+        <v>1.67</v>
+      </c>
+      <c r="AR203">
+        <v>1.55</v>
+      </c>
+      <c r="AS203">
+        <v>1.38</v>
+      </c>
+      <c r="AT203">
+        <v>2.93</v>
+      </c>
+      <c r="AU203">
+        <v>9</v>
+      </c>
+      <c r="AV203">
+        <v>5</v>
+      </c>
+      <c r="AW203">
+        <v>7</v>
+      </c>
+      <c r="AX203">
+        <v>3</v>
+      </c>
+      <c r="AY203">
+        <v>16</v>
+      </c>
+      <c r="AZ203">
+        <v>8</v>
+      </c>
+      <c r="BA203">
+        <v>7</v>
+      </c>
+      <c r="BB203">
+        <v>3</v>
+      </c>
+      <c r="BC203">
+        <v>10</v>
+      </c>
+      <c r="BD203">
+        <v>1.61</v>
+      </c>
+      <c r="BE203">
+        <v>6.75</v>
+      </c>
+      <c r="BF203">
+        <v>2.55</v>
+      </c>
+      <c r="BG203">
+        <v>1.21</v>
+      </c>
+      <c r="BH203">
+        <v>3.65</v>
+      </c>
+      <c r="BI203">
+        <v>1.38</v>
+      </c>
+      <c r="BJ203">
+        <v>2.65</v>
+      </c>
+      <c r="BK203">
+        <v>1.64</v>
+      </c>
+      <c r="BL203">
+        <v>2.05</v>
+      </c>
+      <c r="BM203">
+        <v>2.02</v>
+      </c>
+      <c r="BN203">
+        <v>1.66</v>
+      </c>
+      <c r="BO203">
+        <v>2.55</v>
+      </c>
+      <c r="BP203">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7778275</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>76</v>
+      </c>
+      <c r="H204" t="s">
+        <v>72</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>2</v>
+      </c>
+      <c r="N204">
+        <v>3</v>
+      </c>
+      <c r="O204" t="s">
+        <v>167</v>
+      </c>
+      <c r="P204" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q204">
+        <v>3</v>
+      </c>
+      <c r="R204">
+        <v>2.05</v>
+      </c>
+      <c r="S204">
+        <v>3.3</v>
+      </c>
+      <c r="T204">
+        <v>1.4</v>
+      </c>
+      <c r="U204">
+        <v>2.75</v>
+      </c>
+      <c r="V204">
+        <v>2.75</v>
+      </c>
+      <c r="W204">
+        <v>1.4</v>
+      </c>
+      <c r="X204">
+        <v>6.95</v>
+      </c>
+      <c r="Y204">
+        <v>1.04</v>
+      </c>
+      <c r="Z204">
+        <v>2.42</v>
+      </c>
+      <c r="AA204">
+        <v>3.06</v>
+      </c>
+      <c r="AB204">
+        <v>2.63</v>
+      </c>
+      <c r="AC204">
+        <v>1.06</v>
+      </c>
+      <c r="AD204">
+        <v>8.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.3</v>
+      </c>
+      <c r="AF204">
+        <v>3.4</v>
+      </c>
+      <c r="AG204">
+        <v>1.91</v>
+      </c>
+      <c r="AH204">
+        <v>1.79</v>
+      </c>
+      <c r="AI204">
+        <v>1.67</v>
+      </c>
+      <c r="AJ204">
+        <v>2.05</v>
+      </c>
+      <c r="AK204">
+        <v>1.42</v>
+      </c>
+      <c r="AL204">
+        <v>1.28</v>
+      </c>
+      <c r="AM204">
+        <v>1.5</v>
+      </c>
+      <c r="AN204">
+        <v>1.78</v>
+      </c>
+      <c r="AO204">
+        <v>1.78</v>
+      </c>
+      <c r="AP204">
+        <v>1.6</v>
+      </c>
+      <c r="AQ204">
+        <v>1.9</v>
+      </c>
+      <c r="AR204">
+        <v>1.68</v>
+      </c>
+      <c r="AS204">
+        <v>1.49</v>
+      </c>
+      <c r="AT204">
+        <v>3.17</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>2</v>
+      </c>
+      <c r="AX204">
+        <v>3</v>
+      </c>
+      <c r="AY204">
+        <v>6</v>
+      </c>
+      <c r="AZ204">
+        <v>8</v>
+      </c>
+      <c r="BA204">
+        <v>4</v>
+      </c>
+      <c r="BB204">
+        <v>6</v>
+      </c>
+      <c r="BC204">
+        <v>10</v>
+      </c>
+      <c r="BD204">
+        <v>1.98</v>
+      </c>
+      <c r="BE204">
+        <v>6.5</v>
+      </c>
+      <c r="BF204">
+        <v>1.98</v>
+      </c>
+      <c r="BG204">
+        <v>1.25</v>
+      </c>
+      <c r="BH204">
+        <v>3.3</v>
+      </c>
+      <c r="BI204">
+        <v>1.44</v>
+      </c>
+      <c r="BJ204">
+        <v>2.45</v>
+      </c>
+      <c r="BK204">
+        <v>1.73</v>
+      </c>
+      <c r="BL204">
+        <v>1.92</v>
+      </c>
+      <c r="BM204">
+        <v>2.16</v>
+      </c>
+      <c r="BN204">
+        <v>1.57</v>
+      </c>
+      <c r="BO204">
+        <v>2.8</v>
+      </c>
+      <c r="BP204">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7778276</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>75</v>
+      </c>
+      <c r="H205" t="s">
+        <v>74</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
+        <v>91</v>
+      </c>
+      <c r="P205" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q205">
+        <v>3</v>
+      </c>
+      <c r="R205">
+        <v>2.05</v>
+      </c>
+      <c r="S205">
+        <v>3.3</v>
+      </c>
+      <c r="T205">
+        <v>1.4</v>
+      </c>
+      <c r="U205">
+        <v>2.75</v>
+      </c>
+      <c r="V205">
+        <v>2.75</v>
+      </c>
+      <c r="W205">
+        <v>1.4</v>
+      </c>
+      <c r="X205">
+        <v>6.4</v>
+      </c>
+      <c r="Y205">
+        <v>1.05</v>
+      </c>
+      <c r="Z205">
+        <v>2.27</v>
+      </c>
+      <c r="AA205">
+        <v>3.2</v>
+      </c>
+      <c r="AB205">
+        <v>2.73</v>
+      </c>
+      <c r="AC205">
+        <v>1.05</v>
+      </c>
+      <c r="AD205">
+        <v>9</v>
+      </c>
+      <c r="AE205">
+        <v>1.3</v>
+      </c>
+      <c r="AF205">
+        <v>3.45</v>
+      </c>
+      <c r="AG205">
+        <v>1.85</v>
+      </c>
+      <c r="AH205">
+        <v>1.85</v>
+      </c>
+      <c r="AI205">
+        <v>1.67</v>
+      </c>
+      <c r="AJ205">
+        <v>2.05</v>
+      </c>
+      <c r="AK205">
+        <v>1.42</v>
+      </c>
+      <c r="AL205">
+        <v>1.25</v>
+      </c>
+      <c r="AM205">
+        <v>1.53</v>
+      </c>
+      <c r="AN205">
+        <v>1</v>
+      </c>
+      <c r="AO205">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP205">
+        <v>0.91</v>
+      </c>
+      <c r="AQ205">
+        <v>0.8</v>
+      </c>
+      <c r="AR205">
+        <v>1.39</v>
+      </c>
+      <c r="AS205">
+        <v>1.29</v>
+      </c>
+      <c r="AT205">
+        <v>2.68</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>6</v>
+      </c>
+      <c r="AW205">
+        <v>9</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>14</v>
+      </c>
+      <c r="AZ205">
+        <v>11</v>
+      </c>
+      <c r="BA205">
+        <v>9</v>
+      </c>
+      <c r="BB205">
+        <v>6</v>
+      </c>
+      <c r="BC205">
+        <v>15</v>
+      </c>
+      <c r="BD205">
+        <v>1.79</v>
+      </c>
+      <c r="BE205">
+        <v>7</v>
+      </c>
+      <c r="BF205">
+        <v>2.18</v>
+      </c>
+      <c r="BG205">
+        <v>1.17</v>
+      </c>
+      <c r="BH205">
+        <v>4.1</v>
+      </c>
+      <c r="BI205">
+        <v>1.32</v>
+      </c>
+      <c r="BJ205">
+        <v>2.95</v>
+      </c>
+      <c r="BK205">
+        <v>1.53</v>
+      </c>
+      <c r="BL205">
+        <v>2.25</v>
+      </c>
+      <c r="BM205">
+        <v>1.84</v>
+      </c>
+      <c r="BN205">
+        <v>1.8</v>
+      </c>
+      <c r="BO205">
+        <v>2.3</v>
+      </c>
+      <c r="BP205">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7778278</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>80</v>
+      </c>
+      <c r="H206" t="s">
+        <v>82</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>95</v>
+      </c>
+      <c r="P206" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q206">
+        <v>2.8</v>
+      </c>
+      <c r="R206">
+        <v>2</v>
+      </c>
+      <c r="S206">
+        <v>3.8</v>
+      </c>
+      <c r="T206">
+        <v>1.45</v>
+      </c>
+      <c r="U206">
+        <v>2.55</v>
+      </c>
+      <c r="V206">
+        <v>3</v>
+      </c>
+      <c r="W206">
+        <v>1.33</v>
+      </c>
+      <c r="X206">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y206">
+        <v>1.01</v>
+      </c>
+      <c r="Z206">
+        <v>2.22</v>
+      </c>
+      <c r="AA206">
+        <v>2.87</v>
+      </c>
+      <c r="AB206">
+        <v>3.12</v>
+      </c>
+      <c r="AC206">
+        <v>1.07</v>
+      </c>
+      <c r="AD206">
+        <v>8</v>
+      </c>
+      <c r="AE206">
+        <v>1.42</v>
+      </c>
+      <c r="AF206">
+        <v>2.85</v>
+      </c>
+      <c r="AG206">
+        <v>2.07</v>
+      </c>
+      <c r="AH206">
+        <v>1.67</v>
+      </c>
+      <c r="AI206">
+        <v>1.85</v>
+      </c>
+      <c r="AJ206">
+        <v>1.8</v>
+      </c>
+      <c r="AK206">
+        <v>1.3</v>
+      </c>
+      <c r="AL206">
+        <v>1.28</v>
+      </c>
+      <c r="AM206">
+        <v>1.65</v>
+      </c>
+      <c r="AN206">
+        <v>1.89</v>
+      </c>
+      <c r="AO206">
+        <v>1</v>
+      </c>
+      <c r="AP206">
+        <v>1.8</v>
+      </c>
+      <c r="AQ206">
+        <v>1</v>
+      </c>
+      <c r="AR206">
+        <v>1.55</v>
+      </c>
+      <c r="AS206">
+        <v>1.55</v>
+      </c>
+      <c r="AT206">
+        <v>3.1</v>
+      </c>
+      <c r="AU206">
+        <v>2</v>
+      </c>
+      <c r="AV206">
+        <v>2</v>
+      </c>
+      <c r="AW206">
+        <v>1</v>
+      </c>
+      <c r="AX206">
+        <v>4</v>
+      </c>
+      <c r="AY206">
+        <v>3</v>
+      </c>
+      <c r="AZ206">
+        <v>6</v>
+      </c>
+      <c r="BA206">
+        <v>3</v>
+      </c>
+      <c r="BB206">
+        <v>6</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>1.74</v>
+      </c>
+      <c r="BE206">
+        <v>6.75</v>
+      </c>
+      <c r="BF206">
+        <v>2.3</v>
+      </c>
+      <c r="BG206">
+        <v>1.28</v>
+      </c>
+      <c r="BH206">
+        <v>3.15</v>
+      </c>
+      <c r="BI206">
+        <v>1.5</v>
+      </c>
+      <c r="BJ206">
+        <v>2.33</v>
+      </c>
+      <c r="BK206">
+        <v>1.82</v>
+      </c>
+      <c r="BL206">
+        <v>1.82</v>
+      </c>
+      <c r="BM206">
+        <v>2.28</v>
+      </c>
+      <c r="BN206">
+        <v>1.52</v>
+      </c>
+      <c r="BO206">
+        <v>2.95</v>
+      </c>
+      <c r="BP206">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,9 @@
     <t>['19', '31', '74']</t>
   </si>
   <si>
+    <t>['33', '9003']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -923,6 +926,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['17', '23', '39', '75']</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1540,7 +1546,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1618,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ2">
         <v>1.09</v>
@@ -2236,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3188,7 +3194,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3269,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3394,7 +3400,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3600,7 +3606,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3806,7 +3812,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4090,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14">
         <v>0.8</v>
@@ -4630,7 +4636,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4836,7 +4842,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4914,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ18">
         <v>1.3</v>
@@ -5660,7 +5666,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -6072,7 +6078,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6359,7 +6365,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6690,7 +6696,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6896,7 +6902,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7308,7 +7314,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7720,7 +7726,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8007,7 +8013,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ33">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR33">
         <v>1.86</v>
@@ -8338,7 +8344,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8544,7 +8550,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8750,7 +8756,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8956,7 +8962,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9574,7 +9580,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9986,7 +9992,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10270,7 +10276,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10604,7 +10610,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10682,7 +10688,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ46">
         <v>1.73</v>
@@ -10810,7 +10816,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -11016,7 +11022,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11506,7 +11512,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -11840,7 +11846,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12127,7 +12133,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ53">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1.12</v>
@@ -12252,7 +12258,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -13282,7 +13288,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13488,7 +13494,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -14312,7 +14318,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14805,7 +14811,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ66">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15136,7 +15142,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15342,7 +15348,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15754,7 +15760,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -16038,7 +16044,7 @@
         <v>2.5</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ72">
         <v>1.73</v>
@@ -16990,7 +16996,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17071,7 +17077,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ77">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
         <v>1.28</v>
@@ -17274,7 +17280,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ78">
         <v>1.9</v>
@@ -17402,7 +17408,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17895,7 +17901,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ81">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -18226,7 +18232,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18510,7 +18516,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18844,7 +18850,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19256,7 +19262,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19668,7 +19674,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20080,7 +20086,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20570,7 +20576,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ94">
         <v>0.64</v>
@@ -20698,7 +20704,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21522,7 +21528,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21934,7 +21940,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22140,7 +22146,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22346,7 +22352,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22552,7 +22558,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22836,7 +22842,7 @@
         <v>0.8</v>
       </c>
       <c r="AP105">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ105">
         <v>0.91</v>
@@ -22964,7 +22970,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23170,7 +23176,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23376,7 +23382,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23457,7 +23463,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ108">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR108">
         <v>1.41</v>
@@ -23869,7 +23875,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ110">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR110">
         <v>2.07</v>
@@ -23994,7 +24000,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24818,7 +24824,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25024,7 +25030,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25723,7 +25729,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR119">
         <v>1.43</v>
@@ -26054,7 +26060,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26260,7 +26266,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26466,7 +26472,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26672,7 +26678,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26750,7 +26756,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ124">
         <v>1.5</v>
@@ -26878,7 +26884,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -27084,7 +27090,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27368,7 +27374,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27702,7 +27708,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -28114,7 +28120,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28320,7 +28326,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28401,7 +28407,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ132">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR132">
         <v>1.52</v>
@@ -28810,7 +28816,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ134">
         <v>1.1</v>
@@ -29350,7 +29356,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29556,7 +29562,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29968,7 +29974,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30792,7 +30798,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31079,7 +31085,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ145">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR145">
         <v>1.48</v>
@@ -31282,7 +31288,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ146">
         <v>1.3</v>
@@ -31822,7 +31828,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32234,7 +32240,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32440,7 +32446,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32724,10 +32730,10 @@
         <v>1.17</v>
       </c>
       <c r="AP153">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ153">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR153">
         <v>1.59</v>
@@ -33058,7 +33064,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33264,7 +33270,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33470,7 +33476,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33676,7 +33682,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33882,7 +33888,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34500,7 +34506,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -35118,7 +35124,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35199,7 +35205,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ165">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35736,7 +35742,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35942,7 +35948,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36560,7 +36566,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -37050,7 +37056,7 @@
         <v>2</v>
       </c>
       <c r="AP174">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ174">
         <v>2</v>
@@ -37384,7 +37390,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37796,7 +37802,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37877,7 +37883,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ178">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR178">
         <v>1.49</v>
@@ -38002,7 +38008,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38620,7 +38626,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -39032,7 +39038,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39238,7 +39244,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39444,7 +39450,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39522,7 +39528,7 @@
         <v>1.5</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ186">
         <v>1.5</v>
@@ -39731,7 +39737,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ187">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR187">
         <v>1.58</v>
@@ -40062,7 +40068,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40474,7 +40480,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40680,7 +40686,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -40758,7 +40764,7 @@
         <v>1.44</v>
       </c>
       <c r="AP192">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ192">
         <v>1.6</v>
@@ -40967,7 +40973,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ193">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR193">
         <v>1.59</v>
@@ -41092,7 +41098,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41504,7 +41510,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41916,7 +41922,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42328,7 +42334,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -42534,7 +42540,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42946,7 +42952,7 @@
         <v>221</v>
       </c>
       <c r="P203" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q203">
         <v>2.7</v>
@@ -43152,7 +43158,7 @@
         <v>167</v>
       </c>
       <c r="P204" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43358,7 +43364,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43564,7 +43570,7 @@
         <v>95</v>
       </c>
       <c r="P206" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q206">
         <v>2.8</v>
@@ -43721,6 +43727,418 @@
       </c>
       <c r="BP206">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7778277</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45830.25</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>73</v>
+      </c>
+      <c r="H207" t="s">
+        <v>87</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>3</v>
+      </c>
+      <c r="K207">
+        <v>3</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>4</v>
+      </c>
+      <c r="N207">
+        <v>4</v>
+      </c>
+      <c r="O207" t="s">
+        <v>91</v>
+      </c>
+      <c r="P207" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q207">
+        <v>4.33</v>
+      </c>
+      <c r="R207">
+        <v>1.93</v>
+      </c>
+      <c r="S207">
+        <v>2.7</v>
+      </c>
+      <c r="T207">
+        <v>1.53</v>
+      </c>
+      <c r="U207">
+        <v>2.38</v>
+      </c>
+      <c r="V207">
+        <v>3.4</v>
+      </c>
+      <c r="W207">
+        <v>1.28</v>
+      </c>
+      <c r="X207">
+        <v>11</v>
+      </c>
+      <c r="Y207">
+        <v>1.05</v>
+      </c>
+      <c r="Z207">
+        <v>3.67</v>
+      </c>
+      <c r="AA207">
+        <v>2.96</v>
+      </c>
+      <c r="AB207">
+        <v>1.96</v>
+      </c>
+      <c r="AC207">
+        <v>1.1</v>
+      </c>
+      <c r="AD207">
+        <v>6.5</v>
+      </c>
+      <c r="AE207">
+        <v>1.5</v>
+      </c>
+      <c r="AF207">
+        <v>2.55</v>
+      </c>
+      <c r="AG207">
+        <v>2.38</v>
+      </c>
+      <c r="AH207">
+        <v>1.51</v>
+      </c>
+      <c r="AI207">
+        <v>2.1</v>
+      </c>
+      <c r="AJ207">
+        <v>1.62</v>
+      </c>
+      <c r="AK207">
+        <v>1.75</v>
+      </c>
+      <c r="AL207">
+        <v>1.3</v>
+      </c>
+      <c r="AM207">
+        <v>1.25</v>
+      </c>
+      <c r="AN207">
+        <v>1.27</v>
+      </c>
+      <c r="AO207">
+        <v>1.56</v>
+      </c>
+      <c r="AP207">
+        <v>1.17</v>
+      </c>
+      <c r="AQ207">
+        <v>1.7</v>
+      </c>
+      <c r="AR207">
+        <v>1.3</v>
+      </c>
+      <c r="AS207">
+        <v>1.6</v>
+      </c>
+      <c r="AT207">
+        <v>2.9</v>
+      </c>
+      <c r="AU207">
+        <v>0</v>
+      </c>
+      <c r="AV207">
+        <v>8</v>
+      </c>
+      <c r="AW207">
+        <v>8</v>
+      </c>
+      <c r="AX207">
+        <v>3</v>
+      </c>
+      <c r="AY207">
+        <v>8</v>
+      </c>
+      <c r="AZ207">
+        <v>11</v>
+      </c>
+      <c r="BA207">
+        <v>6</v>
+      </c>
+      <c r="BB207">
+        <v>7</v>
+      </c>
+      <c r="BC207">
+        <v>13</v>
+      </c>
+      <c r="BD207">
+        <v>2.43</v>
+      </c>
+      <c r="BE207">
+        <v>6.4</v>
+      </c>
+      <c r="BF207">
+        <v>1.68</v>
+      </c>
+      <c r="BG207">
+        <v>1.4</v>
+      </c>
+      <c r="BH207">
+        <v>2.6</v>
+      </c>
+      <c r="BI207">
+        <v>1.68</v>
+      </c>
+      <c r="BJ207">
+        <v>1.98</v>
+      </c>
+      <c r="BK207">
+        <v>2.1</v>
+      </c>
+      <c r="BL207">
+        <v>1.61</v>
+      </c>
+      <c r="BM207">
+        <v>2.7</v>
+      </c>
+      <c r="BN207">
+        <v>1.37</v>
+      </c>
+      <c r="BO207">
+        <v>3.55</v>
+      </c>
+      <c r="BP207">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7778279</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45830.27083333334</v>
+      </c>
+      <c r="F208">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>70</v>
+      </c>
+      <c r="H208" t="s">
+        <v>85</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>2</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208" t="s">
+        <v>222</v>
+      </c>
+      <c r="P208" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q208">
+        <v>2.5</v>
+      </c>
+      <c r="R208">
+        <v>2.1</v>
+      </c>
+      <c r="S208">
+        <v>4.2</v>
+      </c>
+      <c r="T208">
+        <v>1.38</v>
+      </c>
+      <c r="U208">
+        <v>2.8</v>
+      </c>
+      <c r="V208">
+        <v>2.75</v>
+      </c>
+      <c r="W208">
+        <v>1.4</v>
+      </c>
+      <c r="X208">
+        <v>7.5</v>
+      </c>
+      <c r="Y208">
+        <v>1.08</v>
+      </c>
+      <c r="Z208">
+        <v>1.9</v>
+      </c>
+      <c r="AA208">
+        <v>3.19</v>
+      </c>
+      <c r="AB208">
+        <v>3.59</v>
+      </c>
+      <c r="AC208">
+        <v>1.06</v>
+      </c>
+      <c r="AD208">
+        <v>8.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.33</v>
+      </c>
+      <c r="AF208">
+        <v>3.25</v>
+      </c>
+      <c r="AG208">
+        <v>1.94</v>
+      </c>
+      <c r="AH208">
+        <v>1.76</v>
+      </c>
+      <c r="AI208">
+        <v>1.77</v>
+      </c>
+      <c r="AJ208">
+        <v>1.91</v>
+      </c>
+      <c r="AK208">
+        <v>1.25</v>
+      </c>
+      <c r="AL208">
+        <v>1.25</v>
+      </c>
+      <c r="AM208">
+        <v>1.8</v>
+      </c>
+      <c r="AN208">
+        <v>1.67</v>
+      </c>
+      <c r="AO208">
+        <v>0.89</v>
+      </c>
+      <c r="AP208">
+        <v>1.8</v>
+      </c>
+      <c r="AQ208">
+        <v>0.8</v>
+      </c>
+      <c r="AR208">
+        <v>1.58</v>
+      </c>
+      <c r="AS208">
+        <v>1.23</v>
+      </c>
+      <c r="AT208">
+        <v>2.81</v>
+      </c>
+      <c r="AU208">
+        <v>6</v>
+      </c>
+      <c r="AV208">
+        <v>3</v>
+      </c>
+      <c r="AW208">
+        <v>5</v>
+      </c>
+      <c r="AX208">
+        <v>5</v>
+      </c>
+      <c r="AY208">
+        <v>11</v>
+      </c>
+      <c r="AZ208">
+        <v>8</v>
+      </c>
+      <c r="BA208">
+        <v>5</v>
+      </c>
+      <c r="BB208">
+        <v>1</v>
+      </c>
+      <c r="BC208">
+        <v>6</v>
+      </c>
+      <c r="BD208">
+        <v>1.74</v>
+      </c>
+      <c r="BE208">
+        <v>6.4</v>
+      </c>
+      <c r="BF208">
+        <v>2.32</v>
+      </c>
+      <c r="BG208">
+        <v>1.34</v>
+      </c>
+      <c r="BH208">
+        <v>2.85</v>
+      </c>
+      <c r="BI208">
+        <v>1.58</v>
+      </c>
+      <c r="BJ208">
+        <v>2.14</v>
+      </c>
+      <c r="BK208">
+        <v>1.94</v>
+      </c>
+      <c r="BL208">
+        <v>1.72</v>
+      </c>
+      <c r="BM208">
+        <v>2.48</v>
+      </c>
+      <c r="BN208">
+        <v>1.44</v>
+      </c>
+      <c r="BO208">
+        <v>3.2</v>
+      </c>
+      <c r="BP208">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -43869,13 +43869,13 @@
         <v>2.9</v>
       </c>
       <c r="AU207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV207">
         <v>8</v>
       </c>
       <c r="AW207">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX207">
         <v>3</v>
@@ -44075,22 +44075,22 @@
         <v>2.81</v>
       </c>
       <c r="AU208">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW208">
         <v>5</v>
       </c>
       <c r="AX208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY208">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ208">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA208">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,9 @@
     <t>['33', '9003']</t>
   </si>
   <si>
+    <t>['12', '35', '9001']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -929,6 +932,12 @@
   </si>
   <si>
     <t>['17', '23', '39', '75']</t>
+  </si>
+  <si>
+    <t>['9005']</t>
+  </si>
+  <si>
+    <t>['51', '68', '84']</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1546,7 +1555,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2245,7 +2254,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2654,10 +2663,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2860,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -3194,7 +3203,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3400,7 +3409,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3606,7 +3615,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3812,7 +3821,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4305,7 +4314,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ15">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4636,7 +4645,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4842,7 +4851,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5666,7 +5675,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -6078,7 +6087,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6696,7 +6705,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6777,7 +6786,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ27">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6902,7 +6911,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7314,7 +7323,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7598,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ31">
         <v>0.5600000000000001</v>
@@ -7726,7 +7735,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7804,7 +7813,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ32">
         <v>1.1</v>
@@ -8013,7 +8022,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ33">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.86</v>
@@ -8216,7 +8225,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
         <v>1.67</v>
@@ -8344,7 +8353,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8550,7 +8559,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8756,7 +8765,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8962,7 +8971,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9580,7 +9589,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9992,7 +10001,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10610,7 +10619,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10816,7 +10825,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -11022,7 +11031,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11721,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR51">
         <v>1.02</v>
@@ -11846,7 +11855,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12133,7 +12142,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.12</v>
@@ -12258,7 +12267,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12542,7 +12551,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ55">
         <v>0.91</v>
@@ -13288,7 +13297,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13494,7 +13503,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -14318,7 +14327,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -15142,7 +15151,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15348,7 +15357,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15760,7 +15769,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -16868,7 +16877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76">
         <v>1.1</v>
@@ -16996,7 +17005,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17077,7 +17086,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.28</v>
@@ -17408,7 +17417,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17692,7 +17701,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17901,7 +17910,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -18232,7 +18241,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18725,7 +18734,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ85">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR85">
         <v>1.39</v>
@@ -18850,7 +18859,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19262,7 +19271,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19674,7 +19683,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19752,7 +19761,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ90">
         <v>0.44</v>
@@ -20086,7 +20095,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20704,7 +20713,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21528,7 +21537,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21940,7 +21949,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22018,7 +22027,7 @@
         <v>0.8</v>
       </c>
       <c r="AP101">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22146,7 +22155,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22352,7 +22361,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22558,7 +22567,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22970,7 +22979,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23176,7 +23185,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23382,7 +23391,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23875,7 +23884,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ110">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>2.07</v>
@@ -24000,7 +24009,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24284,7 +24293,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24824,7 +24833,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25030,7 +25039,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -26060,7 +26069,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26141,7 +26150,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ121">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR121">
         <v>1.42</v>
@@ -26266,7 +26275,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26472,7 +26481,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26553,7 +26562,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ123">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26678,7 +26687,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26884,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -27090,7 +27099,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27708,7 +27717,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -28120,7 +28129,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28326,7 +28335,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28407,7 +28416,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ132">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.52</v>
@@ -29356,7 +29365,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29562,7 +29571,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29974,7 +29983,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30798,7 +30807,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31828,7 +31837,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32240,7 +32249,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32446,7 +32455,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -33064,7 +33073,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33270,7 +33279,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33348,7 +33357,7 @@
         <v>2.14</v>
       </c>
       <c r="AP156">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ156">
         <v>2</v>
@@ -33476,7 +33485,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33554,7 +33563,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ157">
         <v>0.5600000000000001</v>
@@ -33682,7 +33691,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33760,7 +33769,7 @@
         <v>1.78</v>
       </c>
       <c r="AP158">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ158">
         <v>1.67</v>
@@ -33888,7 +33897,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34506,7 +34515,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -35124,7 +35133,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35205,7 +35214,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ165">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35408,7 +35417,7 @@
         <v>1.25</v>
       </c>
       <c r="AP166">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ166">
         <v>1.09</v>
@@ -35617,7 +35626,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ167">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR167">
         <v>1.53</v>
@@ -35742,7 +35751,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35820,7 +35829,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ168">
         <v>0.9</v>
@@ -35948,7 +35957,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36026,7 +36035,7 @@
         <v>1.67</v>
       </c>
       <c r="AP169">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ169">
         <v>1.9</v>
@@ -36566,7 +36575,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36850,7 +36859,7 @@
         <v>1.71</v>
       </c>
       <c r="AP173">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ173">
         <v>1.5</v>
@@ -37390,7 +37399,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37802,7 +37811,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -38008,7 +38017,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38086,7 +38095,7 @@
         <v>0.89</v>
       </c>
       <c r="AP179">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ179">
         <v>0.91</v>
@@ -38501,7 +38510,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ181">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR181">
         <v>1.55</v>
@@ -38626,7 +38635,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -39038,7 +39047,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39244,7 +39253,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39450,7 +39459,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39737,7 +39746,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ187">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.58</v>
@@ -40068,7 +40077,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40480,7 +40489,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40686,7 +40695,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -41098,7 +41107,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41510,7 +41519,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41922,7 +41931,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42334,7 +42343,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -42540,7 +42549,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42621,7 +42630,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ201">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR201">
         <v>1.56</v>
@@ -42952,7 +42961,7 @@
         <v>221</v>
       </c>
       <c r="P203" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q203">
         <v>2.7</v>
@@ -43158,7 +43167,7 @@
         <v>167</v>
       </c>
       <c r="P204" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43236,7 +43245,7 @@
         <v>1.78</v>
       </c>
       <c r="AP204">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ204">
         <v>1.9</v>
@@ -43364,7 +43373,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43442,7 +43451,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP205">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ205">
         <v>0.8</v>
@@ -43463,25 +43472,25 @@
         <v>6</v>
       </c>
       <c r="AW205">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX205">
         <v>5</v>
       </c>
       <c r="AY205">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ205">
         <v>11</v>
       </c>
       <c r="BA205">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB205">
         <v>6</v>
       </c>
       <c r="BC205">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD205">
         <v>1.79</v>
@@ -43570,7 +43579,7 @@
         <v>95</v>
       </c>
       <c r="P206" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q206">
         <v>2.8</v>
@@ -43776,7 +43785,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -44063,7 +44072,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ208">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR208">
         <v>1.58</v>
@@ -44139,6 +44148,418 @@
       </c>
       <c r="BP208">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7778220</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45833.29166666666</v>
+      </c>
+      <c r="F209">
+        <v>15</v>
+      </c>
+      <c r="G209" t="s">
+        <v>76</v>
+      </c>
+      <c r="H209" t="s">
+        <v>88</v>
+      </c>
+      <c r="I209">
+        <v>2</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>3</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>4</v>
+      </c>
+      <c r="O209" t="s">
+        <v>223</v>
+      </c>
+      <c r="P209" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q209">
+        <v>2.35</v>
+      </c>
+      <c r="R209">
+        <v>2.25</v>
+      </c>
+      <c r="S209">
+        <v>4</v>
+      </c>
+      <c r="T209">
+        <v>1.31</v>
+      </c>
+      <c r="U209">
+        <v>3.1</v>
+      </c>
+      <c r="V209">
+        <v>2.4</v>
+      </c>
+      <c r="W209">
+        <v>1.49</v>
+      </c>
+      <c r="X209">
+        <v>5.75</v>
+      </c>
+      <c r="Y209">
+        <v>1.12</v>
+      </c>
+      <c r="Z209">
+        <v>1.69</v>
+      </c>
+      <c r="AA209">
+        <v>3.47</v>
+      </c>
+      <c r="AB209">
+        <v>4.1</v>
+      </c>
+      <c r="AC209">
+        <v>1.04</v>
+      </c>
+      <c r="AD209">
+        <v>10</v>
+      </c>
+      <c r="AE209">
+        <v>1.22</v>
+      </c>
+      <c r="AF209">
+        <v>4</v>
+      </c>
+      <c r="AG209">
+        <v>1.82</v>
+      </c>
+      <c r="AH209">
+        <v>1.88</v>
+      </c>
+      <c r="AI209">
+        <v>1.65</v>
+      </c>
+      <c r="AJ209">
+        <v>2.1</v>
+      </c>
+      <c r="AK209">
+        <v>1.25</v>
+      </c>
+      <c r="AL209">
+        <v>1.26</v>
+      </c>
+      <c r="AM209">
+        <v>1.9</v>
+      </c>
+      <c r="AN209">
+        <v>1.6</v>
+      </c>
+      <c r="AO209">
+        <v>0.8</v>
+      </c>
+      <c r="AP209">
+        <v>1.73</v>
+      </c>
+      <c r="AQ209">
+        <v>0.73</v>
+      </c>
+      <c r="AR209">
+        <v>1.68</v>
+      </c>
+      <c r="AS209">
+        <v>1.12</v>
+      </c>
+      <c r="AT209">
+        <v>2.8</v>
+      </c>
+      <c r="AU209">
+        <v>7</v>
+      </c>
+      <c r="AV209">
+        <v>7</v>
+      </c>
+      <c r="AW209">
+        <v>3</v>
+      </c>
+      <c r="AX209">
+        <v>8</v>
+      </c>
+      <c r="AY209">
+        <v>10</v>
+      </c>
+      <c r="AZ209">
+        <v>15</v>
+      </c>
+      <c r="BA209">
+        <v>2</v>
+      </c>
+      <c r="BB209">
+        <v>5</v>
+      </c>
+      <c r="BC209">
+        <v>7</v>
+      </c>
+      <c r="BD209">
+        <v>1.61</v>
+      </c>
+      <c r="BE209">
+        <v>7</v>
+      </c>
+      <c r="BF209">
+        <v>2.55</v>
+      </c>
+      <c r="BG209">
+        <v>1.28</v>
+      </c>
+      <c r="BH209">
+        <v>3.15</v>
+      </c>
+      <c r="BI209">
+        <v>1.49</v>
+      </c>
+      <c r="BJ209">
+        <v>2.33</v>
+      </c>
+      <c r="BK209">
+        <v>1.8</v>
+      </c>
+      <c r="BL209">
+        <v>1.85</v>
+      </c>
+      <c r="BM209">
+        <v>2.25</v>
+      </c>
+      <c r="BN209">
+        <v>1.53</v>
+      </c>
+      <c r="BO209">
+        <v>2.9</v>
+      </c>
+      <c r="BP209">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7778221</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45833.3125</v>
+      </c>
+      <c r="F210">
+        <v>15</v>
+      </c>
+      <c r="G210" t="s">
+        <v>75</v>
+      </c>
+      <c r="H210" t="s">
+        <v>85</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>3</v>
+      </c>
+      <c r="N210">
+        <v>3</v>
+      </c>
+      <c r="O210" t="s">
+        <v>91</v>
+      </c>
+      <c r="P210" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q210">
+        <v>2.92</v>
+      </c>
+      <c r="R210">
+        <v>2.19</v>
+      </c>
+      <c r="S210">
+        <v>3.4</v>
+      </c>
+      <c r="T210">
+        <v>1.32</v>
+      </c>
+      <c r="U210">
+        <v>2.98</v>
+      </c>
+      <c r="V210">
+        <v>2.48</v>
+      </c>
+      <c r="W210">
+        <v>1.45</v>
+      </c>
+      <c r="X210">
+        <v>5.65</v>
+      </c>
+      <c r="Y210">
+        <v>1.08</v>
+      </c>
+      <c r="Z210">
+        <v>2.14</v>
+      </c>
+      <c r="AA210">
+        <v>3.29</v>
+      </c>
+      <c r="AB210">
+        <v>2.88</v>
+      </c>
+      <c r="AC210">
+        <v>1.01</v>
+      </c>
+      <c r="AD210">
+        <v>11.8</v>
+      </c>
+      <c r="AE210">
+        <v>1.21</v>
+      </c>
+      <c r="AF210">
+        <v>3.74</v>
+      </c>
+      <c r="AG210">
+        <v>1.58</v>
+      </c>
+      <c r="AH210">
+        <v>2.22</v>
+      </c>
+      <c r="AI210">
+        <v>1.59</v>
+      </c>
+      <c r="AJ210">
+        <v>2.29</v>
+      </c>
+      <c r="AK210">
+        <v>1.42</v>
+      </c>
+      <c r="AL210">
+        <v>1.3</v>
+      </c>
+      <c r="AM210">
+        <v>1.56</v>
+      </c>
+      <c r="AN210">
+        <v>0.91</v>
+      </c>
+      <c r="AO210">
+        <v>0.8</v>
+      </c>
+      <c r="AP210">
+        <v>0.83</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
+        <v>1.39</v>
+      </c>
+      <c r="AS210">
+        <v>1.23</v>
+      </c>
+      <c r="AT210">
+        <v>2.62</v>
+      </c>
+      <c r="AU210">
+        <v>3</v>
+      </c>
+      <c r="AV210">
+        <v>8</v>
+      </c>
+      <c r="AW210">
+        <v>4</v>
+      </c>
+      <c r="AX210">
+        <v>6</v>
+      </c>
+      <c r="AY210">
+        <v>7</v>
+      </c>
+      <c r="AZ210">
+        <v>14</v>
+      </c>
+      <c r="BA210">
+        <v>6</v>
+      </c>
+      <c r="BB210">
+        <v>9</v>
+      </c>
+      <c r="BC210">
+        <v>15</v>
+      </c>
+      <c r="BD210">
+        <v>1.8</v>
+      </c>
+      <c r="BE210">
+        <v>6.75</v>
+      </c>
+      <c r="BF210">
+        <v>2.18</v>
+      </c>
+      <c r="BG210">
+        <v>1.24</v>
+      </c>
+      <c r="BH210">
+        <v>3.45</v>
+      </c>
+      <c r="BI210">
+        <v>1.42</v>
+      </c>
+      <c r="BJ210">
+        <v>2.55</v>
+      </c>
+      <c r="BK210">
+        <v>1.7</v>
+      </c>
+      <c r="BL210">
+        <v>1.97</v>
+      </c>
+      <c r="BM210">
+        <v>2.08</v>
+      </c>
+      <c r="BN210">
+        <v>1.62</v>
+      </c>
+      <c r="BO210">
+        <v>2.65</v>
+      </c>
+      <c r="BP210">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -910,7 +910,7 @@
     <t>['41', '71']</t>
   </si>
   <si>
-    <t>['27', '45', '9003']</t>
+    <t>['27', '4501', '9003']</t>
   </si>
   <si>
     <t>['69']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -40585,19 +40585,19 @@
         <v>4</v>
       </c>
       <c r="AV191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW191">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AX191">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY191">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AZ191">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41000,16 +41000,16 @@
         <v>4</v>
       </c>
       <c r="AW193">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AX193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY193">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA193">
         <v>12</v>
@@ -41612,22 +41612,22 @@
         <v>2.84</v>
       </c>
       <c r="AU196">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV196">
         <v>6</v>
       </c>
       <c r="AW196">
+        <v>5</v>
+      </c>
+      <c r="AX196">
+        <v>3</v>
+      </c>
+      <c r="AY196">
+        <v>4</v>
+      </c>
+      <c r="AZ196">
         <v>9</v>
-      </c>
-      <c r="AX196">
-        <v>6</v>
-      </c>
-      <c r="AY196">
-        <v>9</v>
-      </c>
-      <c r="AZ196">
-        <v>12</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -42230,22 +42230,22 @@
         <v>2.96</v>
       </c>
       <c r="AU199">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
         <v>6</v>
       </c>
-      <c r="AW199">
-        <v>8</v>
-      </c>
       <c r="AX199">
+        <v>5</v>
+      </c>
+      <c r="AY199">
+        <v>15</v>
+      </c>
+      <c r="AZ199">
         <v>12</v>
-      </c>
-      <c r="AY199">
-        <v>18</v>
-      </c>
-      <c r="AZ199">
-        <v>18</v>
       </c>
       <c r="BA199">
         <v>1</v>
@@ -42442,16 +42442,16 @@
         <v>4</v>
       </c>
       <c r="AW200">
+        <v>2</v>
+      </c>
+      <c r="AX200">
+        <v>3</v>
+      </c>
+      <c r="AY200">
+        <v>9</v>
+      </c>
+      <c r="AZ200">
         <v>7</v>
-      </c>
-      <c r="AX200">
-        <v>7</v>
-      </c>
-      <c r="AY200">
-        <v>14</v>
-      </c>
-      <c r="AZ200">
-        <v>11</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -42642,22 +42642,22 @@
         <v>2.68</v>
       </c>
       <c r="AU201">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV201">
         <v>3</v>
       </c>
       <c r="AW201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX201">
+        <v>3</v>
+      </c>
+      <c r="AY201">
         <v>7</v>
       </c>
-      <c r="AY201">
-        <v>10</v>
-      </c>
       <c r="AZ201">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA201">
         <v>2</v>
@@ -43054,22 +43054,22 @@
         <v>2.93</v>
       </c>
       <c r="AU203">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW203">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX203">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY203">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA203">
         <v>7</v>
@@ -43466,16 +43466,16 @@
         <v>2.68</v>
       </c>
       <c r="AU205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV205">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW205">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY205">
         <v>15</v>
@@ -43672,22 +43672,22 @@
         <v>3.1</v>
       </c>
       <c r="AU206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV206">
         <v>2</v>
       </c>
       <c r="AW206">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY206">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AZ206">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
@@ -43872,10 +43872,10 @@
         <v>1.3</v>
       </c>
       <c r="AS207">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AT207">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AU207">
         <v>2</v>
@@ -44290,22 +44290,22 @@
         <v>2.8</v>
       </c>
       <c r="AU209">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV209">
         <v>7</v>
       </c>
       <c r="AW209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX209">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ209">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA209">
         <v>2</v>
@@ -44499,7 +44499,7 @@
         <v>3</v>
       </c>
       <c r="AV210">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW210">
         <v>4</v>
@@ -44511,7 +44511,7 @@
         <v>7</v>
       </c>
       <c r="AZ210">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA210">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -40585,19 +40585,19 @@
         <v>4</v>
       </c>
       <c r="AV191">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW191">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AX191">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY191">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AZ191">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41000,16 +41000,16 @@
         <v>4</v>
       </c>
       <c r="AW193">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AX193">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY193">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AZ193">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA193">
         <v>12</v>
@@ -41612,22 +41612,22 @@
         <v>2.84</v>
       </c>
       <c r="AU196">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV196">
         <v>6</v>
       </c>
       <c r="AW196">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX196">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY196">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AZ196">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -42230,22 +42230,22 @@
         <v>2.96</v>
       </c>
       <c r="AU199">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV199">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW199">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX199">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY199">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ199">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA199">
         <v>1</v>
@@ -42442,16 +42442,16 @@
         <v>4</v>
       </c>
       <c r="AW200">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX200">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY200">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ200">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -42642,22 +42642,22 @@
         <v>2.68</v>
       </c>
       <c r="AU201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV201">
         <v>3</v>
       </c>
       <c r="AW201">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX201">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY201">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ201">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA201">
         <v>2</v>
@@ -43054,22 +43054,22 @@
         <v>2.93</v>
       </c>
       <c r="AU203">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW203">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX203">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY203">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ203">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA203">
         <v>7</v>
@@ -43466,16 +43466,16 @@
         <v>2.68</v>
       </c>
       <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
         <v>6</v>
       </c>
-      <c r="AV205">
-        <v>7</v>
-      </c>
       <c r="AW205">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX205">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY205">
         <v>15</v>
@@ -43672,22 +43672,22 @@
         <v>3.1</v>
       </c>
       <c r="AU206">
+        <v>2</v>
+      </c>
+      <c r="AV206">
+        <v>2</v>
+      </c>
+      <c r="AW206">
+        <v>1</v>
+      </c>
+      <c r="AX206">
+        <v>4</v>
+      </c>
+      <c r="AY206">
         <v>3</v>
       </c>
-      <c r="AV206">
-        <v>2</v>
-      </c>
-      <c r="AW206">
+      <c r="AZ206">
         <v>6</v>
-      </c>
-      <c r="AX206">
-        <v>5</v>
-      </c>
-      <c r="AY206">
-        <v>9</v>
-      </c>
-      <c r="AZ206">
-        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
@@ -43872,10 +43872,10 @@
         <v>1.3</v>
       </c>
       <c r="AS207">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AT207">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU207">
         <v>2</v>
@@ -44290,22 +44290,22 @@
         <v>2.8</v>
       </c>
       <c r="AU209">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV209">
         <v>7</v>
       </c>
       <c r="AW209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX209">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY209">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ209">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA209">
         <v>2</v>
@@ -44499,7 +44499,7 @@
         <v>3</v>
       </c>
       <c r="AV210">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW210">
         <v>4</v>
@@ -44511,7 +44511,7 @@
         <v>7</v>
       </c>
       <c r="AZ210">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA210">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="315">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,18 @@
     <t>['12', '35', '9001']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['17', '25', '52']</t>
+  </si>
+  <si>
+    <t>['85', '9014']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -938,6 +950,15 @@
   </si>
   <si>
     <t>['51', '68', '84']</t>
+  </si>
+  <si>
+    <t>['50', '59']</t>
+  </si>
+  <si>
+    <t>['8', '23']</t>
+  </si>
+  <si>
+    <t>['21', '40']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1555,7 +1576,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1839,10 +1860,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2872,7 +2893,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3075,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3203,7 +3224,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3409,7 +3430,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3615,7 +3636,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3696,7 +3717,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3821,7 +3842,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4108,7 +4129,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.76</v>
@@ -4311,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ15">
         <v>0.73</v>
@@ -4517,7 +4538,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16">
         <v>0.9</v>
@@ -4645,7 +4666,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4851,7 +4872,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5135,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19">
         <v>1.73</v>
@@ -5341,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5547,10 +5568,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5675,7 +5696,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5753,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
         <v>1.6</v>
@@ -5962,7 +5983,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ23">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -6087,7 +6108,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6371,7 +6392,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ25">
         <v>1.7</v>
@@ -6577,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ26">
         <v>0.9</v>
@@ -6705,7 +6726,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6783,7 +6804,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ27">
         <v>0.73</v>
@@ -6911,7 +6932,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7195,10 +7216,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -7323,7 +7344,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7610,7 +7631,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ31">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>1.14</v>
@@ -7735,7 +7756,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8019,7 +8040,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8353,7 +8374,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8559,7 +8580,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8640,7 +8661,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.08</v>
@@ -8765,7 +8786,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8971,7 +8992,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9461,10 +9482,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
         <v>1.25</v>
@@ -9589,7 +9610,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9670,7 +9691,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ41">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR41">
         <v>0</v>
@@ -9876,7 +9897,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>2.05</v>
@@ -10001,7 +10022,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10491,7 +10512,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
         <v>1.1</v>
@@ -10619,7 +10640,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10825,7 +10846,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10906,7 +10927,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ47">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR47">
         <v>1.63</v>
@@ -11031,7 +11052,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11315,7 +11336,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ49">
         <v>1.3</v>
@@ -11855,7 +11876,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11936,7 +11957,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12139,7 +12160,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12267,7 +12288,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12345,7 +12366,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ54">
         <v>1.67</v>
@@ -12554,7 +12575,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ55">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR55">
         <v>1.24</v>
@@ -12963,10 +12984,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR57">
         <v>1.46</v>
@@ -13169,7 +13190,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ58">
         <v>0.9</v>
@@ -13297,7 +13318,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13375,10 +13396,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13503,7 +13524,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13790,7 +13811,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -13993,7 +14014,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ62">
         <v>1.1</v>
@@ -14327,7 +14348,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14408,7 +14429,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ64">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR64">
         <v>1.47</v>
@@ -14614,7 +14635,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ65">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.08</v>
@@ -14817,7 +14838,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ66">
         <v>1.7</v>
@@ -15023,10 +15044,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ67">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR67">
         <v>1.72</v>
@@ -15151,7 +15172,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15229,7 +15250,7 @@
         <v>3</v>
       </c>
       <c r="AP68">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ68">
         <v>1.73</v>
@@ -15357,7 +15378,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15435,7 +15456,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ69">
         <v>1.6</v>
@@ -15641,7 +15662,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ70">
         <v>1.5</v>
@@ -15769,7 +15790,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15850,7 +15871,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ71">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -16259,10 +16280,10 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ73">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16468,7 +16489,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ74">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR74">
         <v>1.09</v>
@@ -17005,7 +17026,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17292,7 +17313,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ78">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR78">
         <v>1.29</v>
@@ -17417,7 +17438,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -18113,7 +18134,7 @@
         <v>0.8</v>
       </c>
       <c r="AP82">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82">
         <v>0.9</v>
@@ -18241,7 +18262,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18859,7 +18880,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18937,7 +18958,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ86">
         <v>1.67</v>
@@ -19146,7 +19167,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ87">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR87">
         <v>1.34</v>
@@ -19271,7 +19292,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19349,10 +19370,10 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19555,7 +19576,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ89">
         <v>1.09</v>
@@ -19683,7 +19704,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19764,7 +19785,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ90">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR90">
         <v>1.9</v>
@@ -19967,10 +19988,10 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR91">
         <v>1.32</v>
@@ -20095,7 +20116,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20173,10 +20194,10 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ92">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.46</v>
@@ -20379,7 +20400,7 @@
         <v>1.8</v>
       </c>
       <c r="AP93">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ93">
         <v>1.6</v>
@@ -20588,7 +20609,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR94">
         <v>1.55</v>
@@ -20713,7 +20734,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20791,10 +20812,10 @@
         <v>0.25</v>
       </c>
       <c r="AP95">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ95">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -21000,7 +21021,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ96">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR96">
         <v>1.47</v>
@@ -21409,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ98">
         <v>1.1</v>
@@ -21537,7 +21558,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21824,7 +21845,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ100">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR100">
         <v>1.56</v>
@@ -21949,7 +21970,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22155,7 +22176,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22361,7 +22382,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22567,7 +22588,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22854,7 +22875,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ105">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR105">
         <v>1.2</v>
@@ -22979,7 +23000,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23185,7 +23206,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23263,7 +23284,7 @@
         <v>2.25</v>
       </c>
       <c r="AP107">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ107">
         <v>1.3</v>
@@ -23391,7 +23412,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -24009,7 +24030,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24087,10 +24108,10 @@
         <v>1.8</v>
       </c>
       <c r="AP111">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR111">
         <v>1.52</v>
@@ -24502,7 +24523,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ113">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR113">
         <v>1.45</v>
@@ -24833,7 +24854,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25039,7 +25060,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25117,10 +25138,10 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ116">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR116">
         <v>1.54</v>
@@ -25323,10 +25344,10 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.59</v>
@@ -25529,10 +25550,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ118">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25941,10 +25962,10 @@
         <v>0.83</v>
       </c>
       <c r="AP120">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ120">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR120">
         <v>1.31</v>
@@ -26069,7 +26090,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26275,7 +26296,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26353,7 +26374,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26481,7 +26502,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26559,7 +26580,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ123">
         <v>0.73</v>
@@ -26687,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26893,7 +26914,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -27099,7 +27120,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27180,7 +27201,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ126">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR126">
         <v>1.31</v>
@@ -27589,7 +27610,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27717,7 +27738,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -28001,7 +28022,7 @@
         <v>1.67</v>
       </c>
       <c r="AP130">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130">
         <v>1.3</v>
@@ -28129,7 +28150,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28207,10 +28228,10 @@
         <v>0.14</v>
       </c>
       <c r="AP131">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ131">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR131">
         <v>1.34</v>
@@ -28335,7 +28356,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28622,7 +28643,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.62</v>
@@ -29031,7 +29052,7 @@
         <v>2.29</v>
       </c>
       <c r="AP135">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ135">
         <v>1.73</v>
@@ -29365,7 +29386,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29443,7 +29464,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ137">
         <v>1.09</v>
@@ -29571,7 +29592,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29855,7 +29876,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ139">
         <v>1.5</v>
@@ -29983,7 +30004,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30064,7 +30085,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ140">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30270,7 +30291,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ141">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.35</v>
@@ -30682,7 +30703,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ143">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR143">
         <v>1.48</v>
@@ -30807,7 +30828,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31091,7 +31112,7 @@
         <v>0.8</v>
       </c>
       <c r="AP145">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145">
         <v>1.7</v>
@@ -31503,10 +31524,10 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ147">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR147">
         <v>1.43</v>
@@ -31712,7 +31733,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ148">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -31837,7 +31858,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31915,7 +31936,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32121,7 +32142,7 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ150">
         <v>1.6</v>
@@ -32249,7 +32270,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32327,10 +32348,10 @@
         <v>0.5</v>
       </c>
       <c r="AP151">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ151">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32455,7 +32476,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32948,7 +32969,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ154">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR154">
         <v>1.91</v>
@@ -33073,7 +33094,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33279,7 +33300,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33360,7 +33381,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ156">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR156">
         <v>1.35</v>
@@ -33485,7 +33506,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33566,7 +33587,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ157">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR157">
         <v>1.64</v>
@@ -33691,7 +33712,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33897,7 +33918,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -33978,7 +33999,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ159">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34184,7 +34205,7 @@
         <v>1</v>
       </c>
       <c r="AQ160">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR160">
         <v>1.42</v>
@@ -34387,7 +34408,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34515,7 +34536,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34593,10 +34614,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP162">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ162">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34799,7 +34820,7 @@
         <v>1.25</v>
       </c>
       <c r="AP163">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -35005,10 +35026,10 @@
         <v>0.29</v>
       </c>
       <c r="AP164">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ164">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR164">
         <v>1.47</v>
@@ -35133,7 +35154,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35751,7 +35772,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35957,7 +35978,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36038,7 +36059,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ169">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR169">
         <v>1.38</v>
@@ -36575,7 +36596,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -37068,7 +37089,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ174">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR174">
         <v>1.27</v>
@@ -37399,7 +37420,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37477,10 +37498,10 @@
         <v>1.86</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ176">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR176">
         <v>1.33</v>
@@ -37811,7 +37832,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37889,7 +37910,7 @@
         <v>1.43</v>
       </c>
       <c r="AP178">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178">
         <v>1.7</v>
@@ -38017,7 +38038,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38098,7 +38119,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR179">
         <v>1.72</v>
@@ -38635,7 +38656,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -38716,7 +38737,7 @@
         <v>1</v>
       </c>
       <c r="AQ182">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR182">
         <v>1.42</v>
@@ -38919,7 +38940,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39047,7 +39068,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39128,7 +39149,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ184">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39253,7 +39274,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39331,7 +39352,7 @@
         <v>1.25</v>
       </c>
       <c r="AP185">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ185">
         <v>1.6</v>
@@ -39459,7 +39480,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39743,7 +39764,7 @@
         <v>1</v>
       </c>
       <c r="AP187">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -39949,10 +39970,10 @@
         <v>0.63</v>
       </c>
       <c r="AP188">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ188">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40077,7 +40098,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40364,7 +40385,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ190">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR190">
         <v>1.47</v>
@@ -40489,7 +40510,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40567,7 +40588,7 @@
         <v>1.8</v>
       </c>
       <c r="AP191">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ191">
         <v>1.73</v>
@@ -40695,7 +40716,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -40979,7 +41000,7 @@
         <v>1.63</v>
       </c>
       <c r="AP193">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AQ193">
         <v>1.7</v>
@@ -41107,7 +41128,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41185,7 +41206,7 @@
         <v>1.1</v>
       </c>
       <c r="AP194">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ194">
         <v>1.09</v>
@@ -41394,7 +41415,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ195">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR195">
         <v>1.47</v>
@@ -41519,7 +41540,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41600,7 +41621,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ196">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR196">
         <v>1.39</v>
@@ -41806,7 +41827,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR197">
         <v>1.8</v>
@@ -41931,7 +41952,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42215,10 +42236,10 @@
         <v>0.9</v>
       </c>
       <c r="AP199">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ199">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR199">
         <v>1.39</v>
@@ -42343,7 +42364,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -42549,7 +42570,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42627,7 +42648,7 @@
         <v>0.89</v>
       </c>
       <c r="AP201">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ201">
         <v>0.73</v>
@@ -42961,7 +42982,7 @@
         <v>221</v>
       </c>
       <c r="P203" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q203">
         <v>2.7</v>
@@ -43167,7 +43188,7 @@
         <v>167</v>
       </c>
       <c r="P204" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43248,7 +43269,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ204">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR204">
         <v>1.68</v>
@@ -43373,7 +43394,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43454,7 +43475,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ205">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.39</v>
@@ -43579,7 +43600,7 @@
         <v>95</v>
       </c>
       <c r="P206" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q206">
         <v>2.8</v>
@@ -43785,7 +43806,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -44197,7 +44218,7 @@
         <v>223</v>
       </c>
       <c r="P209" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q209">
         <v>2.35</v>
@@ -44403,7 +44424,7 @@
         <v>91</v>
       </c>
       <c r="P210" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q210">
         <v>2.92</v>
@@ -44560,6 +44581,1448 @@
       </c>
       <c r="BP210">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7778283</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45836.25</v>
+      </c>
+      <c r="F211">
+        <v>22</v>
+      </c>
+      <c r="G211" t="s">
+        <v>86</v>
+      </c>
+      <c r="H211" t="s">
+        <v>74</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>2</v>
+      </c>
+      <c r="N211">
+        <v>3</v>
+      </c>
+      <c r="O211" t="s">
+        <v>224</v>
+      </c>
+      <c r="P211" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q211">
+        <v>2.5</v>
+      </c>
+      <c r="R211">
+        <v>2.05</v>
+      </c>
+      <c r="S211">
+        <v>4.33</v>
+      </c>
+      <c r="T211">
+        <v>1.44</v>
+      </c>
+      <c r="U211">
+        <v>2.6</v>
+      </c>
+      <c r="V211">
+        <v>3</v>
+      </c>
+      <c r="W211">
+        <v>1.33</v>
+      </c>
+      <c r="X211">
+        <v>7.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.03</v>
+      </c>
+      <c r="Z211">
+        <v>1.82</v>
+      </c>
+      <c r="AA211">
+        <v>3.13</v>
+      </c>
+      <c r="AB211">
+        <v>4</v>
+      </c>
+      <c r="AC211">
+        <v>1.07</v>
+      </c>
+      <c r="AD211">
+        <v>8</v>
+      </c>
+      <c r="AE211">
+        <v>1.4</v>
+      </c>
+      <c r="AF211">
+        <v>2.9</v>
+      </c>
+      <c r="AG211">
+        <v>2.1</v>
+      </c>
+      <c r="AH211">
+        <v>1.65</v>
+      </c>
+      <c r="AI211">
+        <v>1.91</v>
+      </c>
+      <c r="AJ211">
+        <v>1.77</v>
+      </c>
+      <c r="AK211">
+        <v>1.25</v>
+      </c>
+      <c r="AL211">
+        <v>1.28</v>
+      </c>
+      <c r="AM211">
+        <v>1.8</v>
+      </c>
+      <c r="AN211">
+        <v>2.36</v>
+      </c>
+      <c r="AO211">
+        <v>0.8</v>
+      </c>
+      <c r="AP211">
+        <v>2.17</v>
+      </c>
+      <c r="AQ211">
+        <v>1</v>
+      </c>
+      <c r="AR211">
+        <v>1.62</v>
+      </c>
+      <c r="AS211">
+        <v>1.29</v>
+      </c>
+      <c r="AT211">
+        <v>2.91</v>
+      </c>
+      <c r="AU211">
+        <v>5</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>9</v>
+      </c>
+      <c r="AX211">
+        <v>4</v>
+      </c>
+      <c r="AY211">
+        <v>14</v>
+      </c>
+      <c r="AZ211">
+        <v>8</v>
+      </c>
+      <c r="BA211">
+        <v>13</v>
+      </c>
+      <c r="BB211">
+        <v>3</v>
+      </c>
+      <c r="BC211">
+        <v>16</v>
+      </c>
+      <c r="BD211">
+        <v>1.52</v>
+      </c>
+      <c r="BE211">
+        <v>7</v>
+      </c>
+      <c r="BF211">
+        <v>2.7</v>
+      </c>
+      <c r="BG211">
+        <v>1.24</v>
+      </c>
+      <c r="BH211">
+        <v>3.4</v>
+      </c>
+      <c r="BI211">
+        <v>1.43</v>
+      </c>
+      <c r="BJ211">
+        <v>2.5</v>
+      </c>
+      <c r="BK211">
+        <v>1.7</v>
+      </c>
+      <c r="BL211">
+        <v>1.96</v>
+      </c>
+      <c r="BM211">
+        <v>2.1</v>
+      </c>
+      <c r="BN211">
+        <v>1.61</v>
+      </c>
+      <c r="BO211">
+        <v>2.65</v>
+      </c>
+      <c r="BP211">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7778288</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45836.27083333334</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>82</v>
+      </c>
+      <c r="H212" t="s">
+        <v>81</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>2</v>
+      </c>
+      <c r="K212">
+        <v>2</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>2</v>
+      </c>
+      <c r="N212">
+        <v>2</v>
+      </c>
+      <c r="O212" t="s">
+        <v>91</v>
+      </c>
+      <c r="P212" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q212">
+        <v>3.5</v>
+      </c>
+      <c r="R212">
+        <v>2.05</v>
+      </c>
+      <c r="S212">
+        <v>2.88</v>
+      </c>
+      <c r="T212">
+        <v>1.4</v>
+      </c>
+      <c r="U212">
+        <v>2.75</v>
+      </c>
+      <c r="V212">
+        <v>2.75</v>
+      </c>
+      <c r="W212">
+        <v>1.4</v>
+      </c>
+      <c r="X212">
+        <v>7.7</v>
+      </c>
+      <c r="Y212">
+        <v>1.02</v>
+      </c>
+      <c r="Z212">
+        <v>2.8</v>
+      </c>
+      <c r="AA212">
+        <v>3.31</v>
+      </c>
+      <c r="AB212">
+        <v>2.17</v>
+      </c>
+      <c r="AC212">
+        <v>1.05</v>
+      </c>
+      <c r="AD212">
+        <v>9</v>
+      </c>
+      <c r="AE212">
+        <v>1.3</v>
+      </c>
+      <c r="AF212">
+        <v>3.45</v>
+      </c>
+      <c r="AG212">
+        <v>1.77</v>
+      </c>
+      <c r="AH212">
+        <v>1.93</v>
+      </c>
+      <c r="AI212">
+        <v>1.67</v>
+      </c>
+      <c r="AJ212">
+        <v>2.05</v>
+      </c>
+      <c r="AK212">
+        <v>1.6</v>
+      </c>
+      <c r="AL212">
+        <v>1.25</v>
+      </c>
+      <c r="AM212">
+        <v>1.38</v>
+      </c>
+      <c r="AN212">
+        <v>1.6</v>
+      </c>
+      <c r="AO212">
+        <v>2</v>
+      </c>
+      <c r="AP212">
+        <v>1.45</v>
+      </c>
+      <c r="AQ212">
+        <v>2.08</v>
+      </c>
+      <c r="AR212">
+        <v>1.47</v>
+      </c>
+      <c r="AS212">
+        <v>1.45</v>
+      </c>
+      <c r="AT212">
+        <v>2.92</v>
+      </c>
+      <c r="AU212">
+        <v>2</v>
+      </c>
+      <c r="AV212">
+        <v>4</v>
+      </c>
+      <c r="AW212">
+        <v>12</v>
+      </c>
+      <c r="AX212">
+        <v>12</v>
+      </c>
+      <c r="AY212">
+        <v>14</v>
+      </c>
+      <c r="AZ212">
+        <v>16</v>
+      </c>
+      <c r="BA212">
+        <v>6</v>
+      </c>
+      <c r="BB212">
+        <v>5</v>
+      </c>
+      <c r="BC212">
+        <v>11</v>
+      </c>
+      <c r="BD212">
+        <v>2.05</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>1.93</v>
+      </c>
+      <c r="BG212">
+        <v>1.2</v>
+      </c>
+      <c r="BH212">
+        <v>3.8</v>
+      </c>
+      <c r="BI212">
+        <v>1.36</v>
+      </c>
+      <c r="BJ212">
+        <v>2.75</v>
+      </c>
+      <c r="BK212">
+        <v>1.6</v>
+      </c>
+      <c r="BL212">
+        <v>2.1</v>
+      </c>
+      <c r="BM212">
+        <v>1.95</v>
+      </c>
+      <c r="BN212">
+        <v>1.71</v>
+      </c>
+      <c r="BO212">
+        <v>2.43</v>
+      </c>
+      <c r="BP212">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7778291</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>71</v>
+      </c>
+      <c r="H213" t="s">
+        <v>72</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213" t="s">
+        <v>91</v>
+      </c>
+      <c r="P213" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q213">
+        <v>4.2</v>
+      </c>
+      <c r="R213">
+        <v>1.95</v>
+      </c>
+      <c r="S213">
+        <v>2.7</v>
+      </c>
+      <c r="T213">
+        <v>1.5</v>
+      </c>
+      <c r="U213">
+        <v>2.4</v>
+      </c>
+      <c r="V213">
+        <v>3.35</v>
+      </c>
+      <c r="W213">
+        <v>1.28</v>
+      </c>
+      <c r="X213">
+        <v>9.4</v>
+      </c>
+      <c r="Y213">
+        <v>1</v>
+      </c>
+      <c r="Z213">
+        <v>3.52</v>
+      </c>
+      <c r="AA213">
+        <v>3.2</v>
+      </c>
+      <c r="AB213">
+        <v>1.91</v>
+      </c>
+      <c r="AC213">
+        <v>1.08</v>
+      </c>
+      <c r="AD213">
+        <v>7.5</v>
+      </c>
+      <c r="AE213">
+        <v>1.5</v>
+      </c>
+      <c r="AF213">
+        <v>2.4</v>
+      </c>
+      <c r="AG213">
+        <v>2.1</v>
+      </c>
+      <c r="AH213">
+        <v>1.65</v>
+      </c>
+      <c r="AI213">
+        <v>2.05</v>
+      </c>
+      <c r="AJ213">
+        <v>1.67</v>
+      </c>
+      <c r="AK213">
+        <v>1.75</v>
+      </c>
+      <c r="AL213">
+        <v>1.28</v>
+      </c>
+      <c r="AM213">
+        <v>1.25</v>
+      </c>
+      <c r="AN213">
+        <v>1.45</v>
+      </c>
+      <c r="AO213">
+        <v>1.9</v>
+      </c>
+      <c r="AP213">
+        <v>1.42</v>
+      </c>
+      <c r="AQ213">
+        <v>1.82</v>
+      </c>
+      <c r="AR213">
+        <v>1.54</v>
+      </c>
+      <c r="AS213">
+        <v>1.49</v>
+      </c>
+      <c r="AT213">
+        <v>3.03</v>
+      </c>
+      <c r="AU213">
+        <v>2</v>
+      </c>
+      <c r="AV213">
+        <v>3</v>
+      </c>
+      <c r="AW213">
+        <v>1</v>
+      </c>
+      <c r="AX213">
+        <v>7</v>
+      </c>
+      <c r="AY213">
+        <v>3</v>
+      </c>
+      <c r="AZ213">
+        <v>10</v>
+      </c>
+      <c r="BA213">
+        <v>8</v>
+      </c>
+      <c r="BB213">
+        <v>5</v>
+      </c>
+      <c r="BC213">
+        <v>13</v>
+      </c>
+      <c r="BD213">
+        <v>2.43</v>
+      </c>
+      <c r="BE213">
+        <v>6.75</v>
+      </c>
+      <c r="BF213">
+        <v>1.68</v>
+      </c>
+      <c r="BG213">
+        <v>1.33</v>
+      </c>
+      <c r="BH213">
+        <v>2.88</v>
+      </c>
+      <c r="BI213">
+        <v>1.57</v>
+      </c>
+      <c r="BJ213">
+        <v>2.16</v>
+      </c>
+      <c r="BK213">
+        <v>1.92</v>
+      </c>
+      <c r="BL213">
+        <v>1.73</v>
+      </c>
+      <c r="BM213">
+        <v>2.43</v>
+      </c>
+      <c r="BN213">
+        <v>1.46</v>
+      </c>
+      <c r="BO213">
+        <v>3.15</v>
+      </c>
+      <c r="BP213">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7778289</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>83</v>
+      </c>
+      <c r="H214" t="s">
+        <v>70</v>
+      </c>
+      <c r="I214">
+        <v>2</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>2</v>
+      </c>
+      <c r="L214">
+        <v>3</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>4</v>
+      </c>
+      <c r="O214" t="s">
+        <v>225</v>
+      </c>
+      <c r="P214" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q214">
+        <v>3.18</v>
+      </c>
+      <c r="R214">
+        <v>2.05</v>
+      </c>
+      <c r="S214">
+        <v>3.45</v>
+      </c>
+      <c r="T214">
+        <v>1.41</v>
+      </c>
+      <c r="U214">
+        <v>2.6</v>
+      </c>
+      <c r="V214">
+        <v>2.93</v>
+      </c>
+      <c r="W214">
+        <v>1.33</v>
+      </c>
+      <c r="X214">
+        <v>7.1</v>
+      </c>
+      <c r="Y214">
+        <v>1.04</v>
+      </c>
+      <c r="Z214">
+        <v>2.44</v>
+      </c>
+      <c r="AA214">
+        <v>3.08</v>
+      </c>
+      <c r="AB214">
+        <v>2.6</v>
+      </c>
+      <c r="AC214">
+        <v>1.02</v>
+      </c>
+      <c r="AD214">
+        <v>7.8</v>
+      </c>
+      <c r="AE214">
+        <v>1.32</v>
+      </c>
+      <c r="AF214">
+        <v>2.97</v>
+      </c>
+      <c r="AG214">
+        <v>1.95</v>
+      </c>
+      <c r="AH214">
+        <v>1.75</v>
+      </c>
+      <c r="AI214">
+        <v>1.8</v>
+      </c>
+      <c r="AJ214">
+        <v>1.96</v>
+      </c>
+      <c r="AK214">
+        <v>1.44</v>
+      </c>
+      <c r="AL214">
+        <v>1.33</v>
+      </c>
+      <c r="AM214">
+        <v>1.5</v>
+      </c>
+      <c r="AN214">
+        <v>1.67</v>
+      </c>
+      <c r="AO214">
+        <v>0.91</v>
+      </c>
+      <c r="AP214">
+        <v>1.8</v>
+      </c>
+      <c r="AQ214">
+        <v>0.83</v>
+      </c>
+      <c r="AR214">
+        <v>1.58</v>
+      </c>
+      <c r="AS214">
+        <v>1.61</v>
+      </c>
+      <c r="AT214">
+        <v>3.19</v>
+      </c>
+      <c r="AU214">
+        <v>10</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>5</v>
+      </c>
+      <c r="AX214">
+        <v>4</v>
+      </c>
+      <c r="AY214">
+        <v>15</v>
+      </c>
+      <c r="AZ214">
+        <v>8</v>
+      </c>
+      <c r="BA214">
+        <v>4</v>
+      </c>
+      <c r="BB214">
+        <v>2</v>
+      </c>
+      <c r="BC214">
+        <v>6</v>
+      </c>
+      <c r="BD214">
+        <v>1.8</v>
+      </c>
+      <c r="BE214">
+        <v>6.75</v>
+      </c>
+      <c r="BF214">
+        <v>2.18</v>
+      </c>
+      <c r="BG214">
+        <v>1.26</v>
+      </c>
+      <c r="BH214">
+        <v>3.25</v>
+      </c>
+      <c r="BI214">
+        <v>1.47</v>
+      </c>
+      <c r="BJ214">
+        <v>2.38</v>
+      </c>
+      <c r="BK214">
+        <v>1.77</v>
+      </c>
+      <c r="BL214">
+        <v>1.87</v>
+      </c>
+      <c r="BM214">
+        <v>2.2</v>
+      </c>
+      <c r="BN214">
+        <v>1.55</v>
+      </c>
+      <c r="BO214">
+        <v>2.85</v>
+      </c>
+      <c r="BP214">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7778290</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>87</v>
+      </c>
+      <c r="H215" t="s">
+        <v>80</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>2</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215" t="s">
+        <v>128</v>
+      </c>
+      <c r="P215" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q215">
+        <v>2.7</v>
+      </c>
+      <c r="R215">
+        <v>1.95</v>
+      </c>
+      <c r="S215">
+        <v>4.2</v>
+      </c>
+      <c r="T215">
+        <v>1.5</v>
+      </c>
+      <c r="U215">
+        <v>2.4</v>
+      </c>
+      <c r="V215">
+        <v>3.3</v>
+      </c>
+      <c r="W215">
+        <v>1.28</v>
+      </c>
+      <c r="X215">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y215">
+        <v>1.01</v>
+      </c>
+      <c r="Z215">
+        <v>1.81</v>
+      </c>
+      <c r="AA215">
+        <v>3.1</v>
+      </c>
+      <c r="AB215">
+        <v>4.1</v>
+      </c>
+      <c r="AC215">
+        <v>1.09</v>
+      </c>
+      <c r="AD215">
+        <v>7</v>
+      </c>
+      <c r="AE215">
+        <v>1.45</v>
+      </c>
+      <c r="AF215">
+        <v>2.7</v>
+      </c>
+      <c r="AG215">
+        <v>2.1</v>
+      </c>
+      <c r="AH215">
+        <v>1.65</v>
+      </c>
+      <c r="AI215">
+        <v>2</v>
+      </c>
+      <c r="AJ215">
+        <v>1.7</v>
+      </c>
+      <c r="AK215">
+        <v>1.25</v>
+      </c>
+      <c r="AL215">
+        <v>1.28</v>
+      </c>
+      <c r="AM215">
+        <v>1.75</v>
+      </c>
+      <c r="AN215">
+        <v>1.9</v>
+      </c>
+      <c r="AO215">
+        <v>0.64</v>
+      </c>
+      <c r="AP215">
+        <v>1.73</v>
+      </c>
+      <c r="AQ215">
+        <v>0.83</v>
+      </c>
+      <c r="AR215">
+        <v>1.69</v>
+      </c>
+      <c r="AS215">
+        <v>1.25</v>
+      </c>
+      <c r="AT215">
+        <v>2.94</v>
+      </c>
+      <c r="AU215">
+        <v>5</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>12</v>
+      </c>
+      <c r="AX215">
+        <v>7</v>
+      </c>
+      <c r="AY215">
+        <v>17</v>
+      </c>
+      <c r="AZ215">
+        <v>11</v>
+      </c>
+      <c r="BA215">
+        <v>8</v>
+      </c>
+      <c r="BB215">
+        <v>2</v>
+      </c>
+      <c r="BC215">
+        <v>10</v>
+      </c>
+      <c r="BD215">
+        <v>1.5</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>2.8</v>
+      </c>
+      <c r="BG215">
+        <v>1.32</v>
+      </c>
+      <c r="BH215">
+        <v>2.9</v>
+      </c>
+      <c r="BI215">
+        <v>1.56</v>
+      </c>
+      <c r="BJ215">
+        <v>2.18</v>
+      </c>
+      <c r="BK215">
+        <v>1.91</v>
+      </c>
+      <c r="BL215">
+        <v>1.74</v>
+      </c>
+      <c r="BM215">
+        <v>2.43</v>
+      </c>
+      <c r="BN215">
+        <v>1.46</v>
+      </c>
+      <c r="BO215">
+        <v>3.15</v>
+      </c>
+      <c r="BP215">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7778284</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>85</v>
+      </c>
+      <c r="H216" t="s">
+        <v>73</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>2</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>3</v>
+      </c>
+      <c r="O216" t="s">
+        <v>226</v>
+      </c>
+      <c r="P216" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q216">
+        <v>3</v>
+      </c>
+      <c r="R216">
+        <v>1.93</v>
+      </c>
+      <c r="S216">
+        <v>3.7</v>
+      </c>
+      <c r="T216">
+        <v>1.49</v>
+      </c>
+      <c r="U216">
+        <v>2.4</v>
+      </c>
+      <c r="V216">
+        <v>3.25</v>
+      </c>
+      <c r="W216">
+        <v>1.29</v>
+      </c>
+      <c r="X216">
+        <v>9.25</v>
+      </c>
+      <c r="Y216">
+        <v>1.05</v>
+      </c>
+      <c r="Z216">
+        <v>2.35</v>
+      </c>
+      <c r="AA216">
+        <v>2.9</v>
+      </c>
+      <c r="AB216">
+        <v>2.87</v>
+      </c>
+      <c r="AC216">
+        <v>1.09</v>
+      </c>
+      <c r="AD216">
+        <v>6.75</v>
+      </c>
+      <c r="AE216">
+        <v>1.43</v>
+      </c>
+      <c r="AF216">
+        <v>2.6</v>
+      </c>
+      <c r="AG216">
+        <v>2.2</v>
+      </c>
+      <c r="AH216">
+        <v>1.59</v>
+      </c>
+      <c r="AI216">
+        <v>1.98</v>
+      </c>
+      <c r="AJ216">
+        <v>1.72</v>
+      </c>
+      <c r="AK216">
+        <v>1.35</v>
+      </c>
+      <c r="AL216">
+        <v>1.34</v>
+      </c>
+      <c r="AM216">
+        <v>1.57</v>
+      </c>
+      <c r="AN216">
+        <v>1.2</v>
+      </c>
+      <c r="AO216">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP216">
+        <v>1.36</v>
+      </c>
+      <c r="AQ216">
+        <v>0.5</v>
+      </c>
+      <c r="AR216">
+        <v>1.44</v>
+      </c>
+      <c r="AS216">
+        <v>1.23</v>
+      </c>
+      <c r="AT216">
+        <v>2.67</v>
+      </c>
+      <c r="AU216">
+        <v>8</v>
+      </c>
+      <c r="AV216">
+        <v>2</v>
+      </c>
+      <c r="AW216">
+        <v>8</v>
+      </c>
+      <c r="AX216">
+        <v>5</v>
+      </c>
+      <c r="AY216">
+        <v>16</v>
+      </c>
+      <c r="AZ216">
+        <v>7</v>
+      </c>
+      <c r="BA216">
+        <v>4</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>7</v>
+      </c>
+      <c r="BD216">
+        <v>1.85</v>
+      </c>
+      <c r="BE216">
+        <v>6.4</v>
+      </c>
+      <c r="BF216">
+        <v>2.17</v>
+      </c>
+      <c r="BG216">
+        <v>1.38</v>
+      </c>
+      <c r="BH216">
+        <v>2.7</v>
+      </c>
+      <c r="BI216">
+        <v>1.65</v>
+      </c>
+      <c r="BJ216">
+        <v>2.02</v>
+      </c>
+      <c r="BK216">
+        <v>2.05</v>
+      </c>
+      <c r="BL216">
+        <v>1.63</v>
+      </c>
+      <c r="BM216">
+        <v>2.65</v>
+      </c>
+      <c r="BN216">
+        <v>1.38</v>
+      </c>
+      <c r="BO216">
+        <v>3.5</v>
+      </c>
+      <c r="BP216">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7778286</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>77</v>
+      </c>
+      <c r="H217" t="s">
+        <v>75</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>227</v>
+      </c>
+      <c r="P217" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q217">
+        <v>2.95</v>
+      </c>
+      <c r="R217">
+        <v>2.15</v>
+      </c>
+      <c r="S217">
+        <v>3.1</v>
+      </c>
+      <c r="T217">
+        <v>1.34</v>
+      </c>
+      <c r="U217">
+        <v>3</v>
+      </c>
+      <c r="V217">
+        <v>2.5</v>
+      </c>
+      <c r="W217">
+        <v>1.46</v>
+      </c>
+      <c r="X217">
+        <v>6.25</v>
+      </c>
+      <c r="Y217">
+        <v>1.1</v>
+      </c>
+      <c r="Z217">
+        <v>2.27</v>
+      </c>
+      <c r="AA217">
+        <v>3.32</v>
+      </c>
+      <c r="AB217">
+        <v>2.65</v>
+      </c>
+      <c r="AC217">
+        <v>1.04</v>
+      </c>
+      <c r="AD217">
+        <v>10</v>
+      </c>
+      <c r="AE217">
+        <v>1.25</v>
+      </c>
+      <c r="AF217">
+        <v>3.6</v>
+      </c>
+      <c r="AG217">
+        <v>1.78</v>
+      </c>
+      <c r="AH217">
+        <v>1.92</v>
+      </c>
+      <c r="AI217">
+        <v>1.63</v>
+      </c>
+      <c r="AJ217">
+        <v>2.1</v>
+      </c>
+      <c r="AK217">
+        <v>1.44</v>
+      </c>
+      <c r="AL217">
+        <v>1.29</v>
+      </c>
+      <c r="AM217">
+        <v>1.51</v>
+      </c>
+      <c r="AN217">
+        <v>1.4</v>
+      </c>
+      <c r="AO217">
+        <v>0.44</v>
+      </c>
+      <c r="AP217">
+        <v>1.36</v>
+      </c>
+      <c r="AQ217">
+        <v>0.5</v>
+      </c>
+      <c r="AR217">
+        <v>1.42</v>
+      </c>
+      <c r="AS217">
+        <v>1.4</v>
+      </c>
+      <c r="AT217">
+        <v>2.82</v>
+      </c>
+      <c r="AU217">
+        <v>4</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>6</v>
+      </c>
+      <c r="AX217">
+        <v>8</v>
+      </c>
+      <c r="AY217">
+        <v>10</v>
+      </c>
+      <c r="AZ217">
+        <v>13</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>4</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>1.72</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>2.32</v>
+      </c>
+      <c r="BG217">
+        <v>1.18</v>
+      </c>
+      <c r="BH217">
+        <v>3.9</v>
+      </c>
+      <c r="BI217">
+        <v>1.34</v>
+      </c>
+      <c r="BJ217">
+        <v>2.8</v>
+      </c>
+      <c r="BK217">
+        <v>1.58</v>
+      </c>
+      <c r="BL217">
+        <v>2.15</v>
+      </c>
+      <c r="BM217">
+        <v>1.92</v>
+      </c>
+      <c r="BN217">
+        <v>1.73</v>
+      </c>
+      <c r="BO217">
+        <v>2.43</v>
+      </c>
+      <c r="BP217">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -960,6 +960,9 @@
   <si>
     <t>['21', '40']</t>
   </si>
+  <si>
+    <t>['43', '61', '67', '76']</t>
+  </si>
 </sst>
 </file>
 
@@ -1320,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3508,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3923,7 +3926,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ13">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5159,7 +5162,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5777,7 +5780,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ22">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR22">
         <v>0.91</v>
@@ -8658,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ36">
         <v>0.83</v>
@@ -8864,7 +8867,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>1.09</v>
@@ -9073,7 +9076,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ38">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -10100,7 +10103,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10721,7 +10724,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ46">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -11954,7 +11957,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ52">
         <v>0.83</v>
@@ -12781,7 +12784,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR56">
         <v>1.66</v>
@@ -14426,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -15253,7 +15256,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ68">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR68">
         <v>1.51</v>
@@ -15459,7 +15462,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ69">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -16077,7 +16080,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ72">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR72">
         <v>1.64</v>
@@ -16692,7 +16695,7 @@
         <v>2</v>
       </c>
       <c r="AP75">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
         <v>1.3</v>
@@ -17104,7 +17107,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -18343,7 +18346,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -20403,7 +20406,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ93">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>1.39</v>
@@ -21018,7 +21021,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ96">
         <v>1.82</v>
@@ -21842,7 +21845,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>0.5</v>
@@ -22257,7 +22260,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
         <v>1.55</v>
@@ -22666,7 +22669,7 @@
         <v>1.67</v>
       </c>
       <c r="AP104">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
         <v>1.67</v>
@@ -23699,7 +23702,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ109">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR109">
         <v>1.57</v>
@@ -24726,7 +24729,7 @@
         <v>0.8</v>
       </c>
       <c r="AP114">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114">
         <v>1.09</v>
@@ -27819,7 +27822,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ129">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR129">
         <v>2.07</v>
@@ -28434,7 +28437,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -29055,7 +29058,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ135">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR135">
         <v>1.68</v>
@@ -30700,7 +30703,7 @@
         <v>0.4</v>
       </c>
       <c r="AP143">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ143">
         <v>0.5</v>
@@ -31939,7 +31942,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ149">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR149">
         <v>1.3</v>
@@ -32145,7 +32148,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ150">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR150">
         <v>1.64</v>
@@ -32554,7 +32557,7 @@
         <v>1</v>
       </c>
       <c r="AP152">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ152">
         <v>0.9</v>
@@ -33172,7 +33175,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ155">
         <v>1.1</v>
@@ -36677,7 +36680,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ172">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR172">
         <v>1.66</v>
@@ -37292,7 +37295,7 @@
         <v>1.22</v>
       </c>
       <c r="AP175">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ175">
         <v>1.1</v>
@@ -37704,7 +37707,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ177">
         <v>1.67</v>
@@ -39355,7 +39358,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ185">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR185">
         <v>1.69</v>
@@ -40591,7 +40594,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ191">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR191">
         <v>1.45</v>
@@ -40797,7 +40800,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ192">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR192">
         <v>1.3</v>
@@ -41412,7 +41415,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ195">
         <v>0.5</v>
@@ -41618,7 +41621,7 @@
         <v>1.9</v>
       </c>
       <c r="AP196">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ196">
         <v>2.08</v>
@@ -46023,6 +46026,418 @@
       </c>
       <c r="BP217">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7778287</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45837.25</v>
+      </c>
+      <c r="F218">
+        <v>22</v>
+      </c>
+      <c r="G218" t="s">
+        <v>88</v>
+      </c>
+      <c r="H218" t="s">
+        <v>78</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>4</v>
+      </c>
+      <c r="N218">
+        <v>4</v>
+      </c>
+      <c r="O218" t="s">
+        <v>91</v>
+      </c>
+      <c r="P218" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q218">
+        <v>4.33</v>
+      </c>
+      <c r="R218">
+        <v>2</v>
+      </c>
+      <c r="S218">
+        <v>2.88</v>
+      </c>
+      <c r="T218">
+        <v>1.53</v>
+      </c>
+      <c r="U218">
+        <v>2.38</v>
+      </c>
+      <c r="V218">
+        <v>3.5</v>
+      </c>
+      <c r="W218">
+        <v>1.29</v>
+      </c>
+      <c r="X218">
+        <v>11</v>
+      </c>
+      <c r="Y218">
+        <v>1.05</v>
+      </c>
+      <c r="Z218">
+        <v>3.45</v>
+      </c>
+      <c r="AA218">
+        <v>2.94</v>
+      </c>
+      <c r="AB218">
+        <v>2.04</v>
+      </c>
+      <c r="AC218">
+        <v>1.1</v>
+      </c>
+      <c r="AD218">
+        <v>6.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.48</v>
+      </c>
+      <c r="AF218">
+        <v>2.65</v>
+      </c>
+      <c r="AG218">
+        <v>2.04</v>
+      </c>
+      <c r="AH218">
+        <v>1.69</v>
+      </c>
+      <c r="AI218">
+        <v>2.05</v>
+      </c>
+      <c r="AJ218">
+        <v>1.7</v>
+      </c>
+      <c r="AK218">
+        <v>1.68</v>
+      </c>
+      <c r="AL218">
+        <v>1.35</v>
+      </c>
+      <c r="AM218">
+        <v>1.27</v>
+      </c>
+      <c r="AN218">
+        <v>1.1</v>
+      </c>
+      <c r="AO218">
+        <v>1.73</v>
+      </c>
+      <c r="AP218">
+        <v>1</v>
+      </c>
+      <c r="AQ218">
+        <v>1.83</v>
+      </c>
+      <c r="AR218">
+        <v>1.47</v>
+      </c>
+      <c r="AS218">
+        <v>1.5</v>
+      </c>
+      <c r="AT218">
+        <v>2.97</v>
+      </c>
+      <c r="AU218">
+        <v>2</v>
+      </c>
+      <c r="AV218">
+        <v>11</v>
+      </c>
+      <c r="AW218">
+        <v>20</v>
+      </c>
+      <c r="AX218">
+        <v>13</v>
+      </c>
+      <c r="AY218">
+        <v>22</v>
+      </c>
+      <c r="AZ218">
+        <v>24</v>
+      </c>
+      <c r="BA218">
+        <v>6</v>
+      </c>
+      <c r="BB218">
+        <v>9</v>
+      </c>
+      <c r="BC218">
+        <v>15</v>
+      </c>
+      <c r="BD218">
+        <v>2.17</v>
+      </c>
+      <c r="BE218">
+        <v>6.25</v>
+      </c>
+      <c r="BF218">
+        <v>1.84</v>
+      </c>
+      <c r="BG218">
+        <v>1.47</v>
+      </c>
+      <c r="BH218">
+        <v>2.4</v>
+      </c>
+      <c r="BI218">
+        <v>1.78</v>
+      </c>
+      <c r="BJ218">
+        <v>1.86</v>
+      </c>
+      <c r="BK218">
+        <v>2.25</v>
+      </c>
+      <c r="BL218">
+        <v>1.53</v>
+      </c>
+      <c r="BM218">
+        <v>2.95</v>
+      </c>
+      <c r="BN218">
+        <v>1.32</v>
+      </c>
+      <c r="BO218">
+        <v>3.95</v>
+      </c>
+      <c r="BP218">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7778285</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45837.25</v>
+      </c>
+      <c r="F219">
+        <v>22</v>
+      </c>
+      <c r="G219" t="s">
+        <v>79</v>
+      </c>
+      <c r="H219" t="s">
+        <v>76</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
+        <v>172</v>
+      </c>
+      <c r="P219" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q219">
+        <v>4.33</v>
+      </c>
+      <c r="R219">
+        <v>2.1</v>
+      </c>
+      <c r="S219">
+        <v>2.75</v>
+      </c>
+      <c r="T219">
+        <v>1.44</v>
+      </c>
+      <c r="U219">
+        <v>2.63</v>
+      </c>
+      <c r="V219">
+        <v>3.25</v>
+      </c>
+      <c r="W219">
+        <v>1.33</v>
+      </c>
+      <c r="X219">
+        <v>9</v>
+      </c>
+      <c r="Y219">
+        <v>1.07</v>
+      </c>
+      <c r="Z219">
+        <v>3.5</v>
+      </c>
+      <c r="AA219">
+        <v>3.1</v>
+      </c>
+      <c r="AB219">
+        <v>1.96</v>
+      </c>
+      <c r="AC219">
+        <v>1.07</v>
+      </c>
+      <c r="AD219">
+        <v>7.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.37</v>
+      </c>
+      <c r="AF219">
+        <v>3.04</v>
+      </c>
+      <c r="AG219">
+        <v>2.02</v>
+      </c>
+      <c r="AH219">
+        <v>1.7</v>
+      </c>
+      <c r="AI219">
+        <v>1.95</v>
+      </c>
+      <c r="AJ219">
+        <v>1.8</v>
+      </c>
+      <c r="AK219">
+        <v>1.73</v>
+      </c>
+      <c r="AL219">
+        <v>1.32</v>
+      </c>
+      <c r="AM219">
+        <v>1.27</v>
+      </c>
+      <c r="AN219">
+        <v>1.3</v>
+      </c>
+      <c r="AO219">
+        <v>1.6</v>
+      </c>
+      <c r="AP219">
+        <v>1.45</v>
+      </c>
+      <c r="AQ219">
+        <v>1.45</v>
+      </c>
+      <c r="AR219">
+        <v>1.32</v>
+      </c>
+      <c r="AS219">
+        <v>1.59</v>
+      </c>
+      <c r="AT219">
+        <v>2.91</v>
+      </c>
+      <c r="AU219">
+        <v>3</v>
+      </c>
+      <c r="AV219">
+        <v>6</v>
+      </c>
+      <c r="AW219">
+        <v>7</v>
+      </c>
+      <c r="AX219">
+        <v>6</v>
+      </c>
+      <c r="AY219">
+        <v>10</v>
+      </c>
+      <c r="AZ219">
+        <v>12</v>
+      </c>
+      <c r="BA219">
+        <v>7</v>
+      </c>
+      <c r="BB219">
+        <v>3</v>
+      </c>
+      <c r="BC219">
+        <v>10</v>
+      </c>
+      <c r="BD219">
+        <v>2.23</v>
+      </c>
+      <c r="BE219">
+        <v>6.5</v>
+      </c>
+      <c r="BF219">
+        <v>1.79</v>
+      </c>
+      <c r="BG219">
+        <v>1.32</v>
+      </c>
+      <c r="BH219">
+        <v>2.95</v>
+      </c>
+      <c r="BI219">
+        <v>1.54</v>
+      </c>
+      <c r="BJ219">
+        <v>2.23</v>
+      </c>
+      <c r="BK219">
+        <v>1.88</v>
+      </c>
+      <c r="BL219">
+        <v>1.77</v>
+      </c>
+      <c r="BM219">
+        <v>2.38</v>
+      </c>
+      <c r="BN219">
+        <v>1.47</v>
+      </c>
+      <c r="BO219">
+        <v>3.1</v>
+      </c>
+      <c r="BP219">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,9 @@
     <t>['41']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -833,9 +836,6 @@
   </si>
   <si>
     <t>['49', '67', '77']</t>
-  </si>
-  <si>
-    <t>['66']</t>
   </si>
   <si>
     <t>['33', '50']</t>
@@ -1323,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1579,7 +1579,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4">
         <v>0.9</v>
@@ -3227,7 +3227,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3308,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3639,7 +3639,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3845,7 +3845,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4669,7 +4669,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4875,7 +4875,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5699,7 +5699,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -6111,7 +6111,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6189,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>1.67</v>
@@ -6398,7 +6398,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ25">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6729,7 +6729,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6935,7 +6935,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7347,7 +7347,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7759,7 +7759,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8377,7 +8377,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8455,7 +8455,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ35">
         <v>1.3</v>
@@ -8583,7 +8583,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8789,7 +8789,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8995,7 +8995,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9613,7 +9613,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10025,7 +10025,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10643,7 +10643,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10849,7 +10849,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -11055,7 +11055,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11879,7 +11879,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12291,7 +12291,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -13321,7 +13321,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13527,7 +13527,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -14351,7 +14351,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14844,7 +14844,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ66">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15175,7 +15175,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15381,7 +15381,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15793,7 +15793,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -17029,7 +17029,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17441,7 +17441,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -18265,7 +18265,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18755,7 +18755,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ85">
         <v>0.73</v>
@@ -18883,7 +18883,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19295,7 +19295,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19707,7 +19707,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20119,7 +20119,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20737,7 +20737,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21561,7 +21561,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21973,7 +21973,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22179,7 +22179,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22257,7 +22257,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
         <v>1.45</v>
@@ -22385,7 +22385,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22591,7 +22591,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -23003,7 +23003,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23209,7 +23209,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23415,7 +23415,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23496,7 +23496,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ108">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR108">
         <v>1.41</v>
@@ -23699,7 +23699,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ109">
         <v>1.83</v>
@@ -24033,7 +24033,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24857,7 +24857,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25063,7 +25063,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25762,7 +25762,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR119">
         <v>1.43</v>
@@ -26093,7 +26093,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26299,7 +26299,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26505,7 +26505,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26711,7 +26711,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26917,7 +26917,7 @@
         <v>91</v>
       </c>
       <c r="P125" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="Q125">
         <v>3.4</v>
@@ -28643,7 +28643,7 @@
         <v>0.8</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29673,7 +29673,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ138">
         <v>1.09</v>
@@ -31118,7 +31118,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ145">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR145">
         <v>1.48</v>
@@ -32766,7 +32766,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ153">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR153">
         <v>1.59</v>
@@ -33999,7 +33999,7 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ159">
         <v>0.83</v>
@@ -34539,7 +34539,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -37916,7 +37916,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR178">
         <v>1.49</v>
@@ -39483,7 +39483,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -40513,7 +40513,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40719,7 +40719,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -41006,7 +41006,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ193">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR193">
         <v>1.59</v>
@@ -41827,7 +41827,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ197">
         <v>0.83</v>
@@ -42367,7 +42367,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -43890,7 +43890,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ207">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR207">
         <v>1.3</v>
@@ -46438,6 +46438,212 @@
       </c>
       <c r="BP219">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7778122</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45840.29166666666</v>
+      </c>
+      <c r="F220">
+        <v>5</v>
+      </c>
+      <c r="G220" t="s">
+        <v>72</v>
+      </c>
+      <c r="H220" t="s">
+        <v>87</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>228</v>
+      </c>
+      <c r="P220" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q220">
+        <v>3</v>
+      </c>
+      <c r="R220">
+        <v>2</v>
+      </c>
+      <c r="S220">
+        <v>3.45</v>
+      </c>
+      <c r="T220">
+        <v>1.45</v>
+      </c>
+      <c r="U220">
+        <v>2.55</v>
+      </c>
+      <c r="V220">
+        <v>2.95</v>
+      </c>
+      <c r="W220">
+        <v>1.35</v>
+      </c>
+      <c r="X220">
+        <v>8.1</v>
+      </c>
+      <c r="Y220">
+        <v>1.02</v>
+      </c>
+      <c r="Z220">
+        <v>2.3</v>
+      </c>
+      <c r="AA220">
+        <v>2.97</v>
+      </c>
+      <c r="AB220">
+        <v>2.87</v>
+      </c>
+      <c r="AC220">
+        <v>1.08</v>
+      </c>
+      <c r="AD220">
+        <v>7.5</v>
+      </c>
+      <c r="AE220">
+        <v>1.4</v>
+      </c>
+      <c r="AF220">
+        <v>2.88</v>
+      </c>
+      <c r="AG220">
+        <v>2.17</v>
+      </c>
+      <c r="AH220">
+        <v>1.61</v>
+      </c>
+      <c r="AI220">
+        <v>1.83</v>
+      </c>
+      <c r="AJ220">
+        <v>1.83</v>
+      </c>
+      <c r="AK220">
+        <v>1.38</v>
+      </c>
+      <c r="AL220">
+        <v>1.3</v>
+      </c>
+      <c r="AM220">
+        <v>1.5</v>
+      </c>
+      <c r="AN220">
+        <v>1.5</v>
+      </c>
+      <c r="AO220">
+        <v>1.7</v>
+      </c>
+      <c r="AP220">
+        <v>1.64</v>
+      </c>
+      <c r="AQ220">
+        <v>1.55</v>
+      </c>
+      <c r="AR220">
+        <v>1.8</v>
+      </c>
+      <c r="AS220">
+        <v>1.57</v>
+      </c>
+      <c r="AT220">
+        <v>3.37</v>
+      </c>
+      <c r="AU220">
+        <v>7</v>
+      </c>
+      <c r="AV220">
+        <v>5</v>
+      </c>
+      <c r="AW220">
+        <v>4</v>
+      </c>
+      <c r="AX220">
+        <v>8</v>
+      </c>
+      <c r="AY220">
+        <v>11</v>
+      </c>
+      <c r="AZ220">
+        <v>13</v>
+      </c>
+      <c r="BA220">
+        <v>3</v>
+      </c>
+      <c r="BB220">
+        <v>3</v>
+      </c>
+      <c r="BC220">
+        <v>6</v>
+      </c>
+      <c r="BD220">
+        <v>1.94</v>
+      </c>
+      <c r="BE220">
+        <v>6.5</v>
+      </c>
+      <c r="BF220">
+        <v>2.05</v>
+      </c>
+      <c r="BG220">
+        <v>1.32</v>
+      </c>
+      <c r="BH220">
+        <v>2.9</v>
+      </c>
+      <c r="BI220">
+        <v>1.54</v>
+      </c>
+      <c r="BJ220">
+        <v>2.2</v>
+      </c>
+      <c r="BK220">
+        <v>1.88</v>
+      </c>
+      <c r="BL220">
+        <v>1.76</v>
+      </c>
+      <c r="BM220">
+        <v>2.35</v>
+      </c>
+      <c r="BN220">
+        <v>1.49</v>
+      </c>
+      <c r="BO220">
+        <v>3.05</v>
+      </c>
+      <c r="BP220">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,7 +658,7 @@
     <t>['53', '83']</t>
   </si>
   <si>
-    <t>['9002']</t>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['3', '81']</t>
@@ -667,7 +667,7 @@
     <t>['73']</t>
   </si>
   <si>
-    <t>['4502']</t>
+    <t>['44', '45+2']</t>
   </si>
   <si>
     <t>['6', '34']</t>
@@ -682,10 +682,10 @@
     <t>['19', '31', '74']</t>
   </si>
   <si>
-    <t>['33', '9003']</t>
+    <t>['33', '90+3']</t>
   </si>
   <si>
-    <t>['12', '35', '9001']</t>
+    <t>['12', '35', '90+1']</t>
   </si>
   <si>
     <t>['18']</t>
@@ -694,13 +694,25 @@
     <t>['17', '25', '52']</t>
   </si>
   <si>
-    <t>['85', '9014']</t>
+    <t>['85', '90+14']</t>
   </si>
   <si>
     <t>['41']</t>
   </si>
   <si>
     <t>['66']</t>
+  </si>
+  <si>
+    <t>['14', '75', '90+4']</t>
+  </si>
+  <si>
+    <t>['14', '48', '76', '90+3']</t>
+  </si>
+  <si>
+    <t>['34', '45+5']</t>
+  </si>
+  <si>
+    <t>['45+4', '58']</t>
   </si>
   <si>
     <t>['7', '46', '52', '63', '90+4']</t>
@@ -916,19 +928,28 @@
     <t>['50', '9001']</t>
   </si>
   <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['4', '89']</t>
+  </si>
+  <si>
+    <t>['45+2', '83']</t>
   </si>
   <si>
     <t>['41', '71']</t>
   </si>
   <si>
-    <t>['27', '4501', '9003']</t>
+    <t>['27', '45+1', '90+3']</t>
   </si>
   <si>
     <t>['69']</t>
   </si>
   <si>
     <t>['4', '36']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['24', '53', '84']</t>
@@ -946,9 +967,6 @@
     <t>['17', '23', '39', '75']</t>
   </si>
   <si>
-    <t>['9005']</t>
-  </si>
-  <si>
     <t>['51', '68', '84']</t>
   </si>
   <si>
@@ -962,6 +980,12 @@
   </si>
   <si>
     <t>['43', '61', '67', '76']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1579,7 +1603,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2069,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4">
         <v>0.9</v>
@@ -2275,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2481,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>1.67</v>
@@ -2690,7 +2714,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2893,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ8">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3099,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
+        <v>1.09</v>
+      </c>
+      <c r="AQ9">
         <v>1.36</v>
-      </c>
-      <c r="AQ9">
-        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3227,7 +3251,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3305,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3433,7 +3457,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3514,7 +3538,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3639,7 +3663,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3717,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
         <v>1.82</v>
@@ -3845,7 +3869,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3923,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ13">
         <v>1.45</v>
@@ -4129,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
         <v>1.76</v>
@@ -4338,7 +4362,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4541,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ16">
         <v>0.9</v>
@@ -4669,7 +4693,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4747,10 +4771,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4875,7 +4899,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5162,7 +5186,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ19">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5574,7 +5598,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5699,7 +5723,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5983,10 +6007,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.24</v>
@@ -6111,7 +6135,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6189,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ24">
         <v>1.67</v>
@@ -6398,7 +6422,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ25">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6601,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ26">
         <v>0.9</v>
@@ -6729,7 +6753,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6810,7 +6834,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ27">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6935,7 +6959,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7013,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7222,7 +7246,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -7347,7 +7371,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7425,7 +7449,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ30">
         <v>1.09</v>
@@ -7759,7 +7783,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7840,7 +7864,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ32">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.12</v>
@@ -8046,7 +8070,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR33">
         <v>1.86</v>
@@ -8249,7 +8273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ34">
         <v>1.67</v>
@@ -8377,7 +8401,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8455,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ35">
         <v>1.3</v>
@@ -8583,7 +8607,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8664,7 +8688,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.08</v>
@@ -8789,7 +8813,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8995,7 +9019,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9073,10 +9097,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -9279,10 +9303,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR39">
         <v>1.59</v>
@@ -9613,7 +9637,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9900,7 +9924,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR42">
         <v>2.05</v>
@@ -10025,7 +10049,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10312,7 +10336,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.53</v>
@@ -10518,7 +10542,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.37</v>
@@ -10643,7 +10667,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10721,10 +10745,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10849,7 +10873,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10927,10 +10951,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ47">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR47">
         <v>1.63</v>
@@ -11055,7 +11079,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11133,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR48">
         <v>1.45</v>
@@ -11339,7 +11363,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ49">
         <v>1.3</v>
@@ -11545,7 +11569,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -11751,10 +11775,10 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ51">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR51">
         <v>1.02</v>
@@ -11879,7 +11903,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11960,7 +11984,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12166,7 +12190,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR53">
         <v>1.12</v>
@@ -12291,7 +12315,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12578,7 +12602,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ55">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.24</v>
@@ -12781,7 +12805,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>1.45</v>
@@ -13321,7 +13345,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13399,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ59">
         <v>1.82</v>
@@ -13527,7 +13551,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13605,7 +13629,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ60">
         <v>0.9</v>
@@ -13811,10 +13835,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -14020,7 +14044,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ62">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14223,7 +14247,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ63">
         <v>1</v>
@@ -14351,7 +14375,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14432,7 +14456,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.47</v>
@@ -14635,7 +14659,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14841,10 +14865,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15175,7 +15199,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15256,7 +15280,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ68">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR68">
         <v>1.51</v>
@@ -15381,7 +15405,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15668,7 +15692,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
         <v>1.48</v>
@@ -15793,7 +15817,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -15871,10 +15895,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR71">
         <v>1.83</v>
@@ -16080,7 +16104,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ72">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR72">
         <v>1.64</v>
@@ -16283,7 +16307,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ73">
         <v>2.08</v>
@@ -16489,10 +16513,10 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR74">
         <v>1.09</v>
@@ -16901,10 +16925,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ76">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.89</v>
@@ -17029,7 +17053,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17110,7 +17134,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.28</v>
@@ -17313,7 +17337,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ78">
         <v>1.82</v>
@@ -17441,7 +17465,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17522,7 +17546,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR79">
         <v>1.78</v>
@@ -17931,10 +17955,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR81">
         <v>1.63</v>
@@ -18265,7 +18289,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18343,7 +18367,7 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
         <v>1.45</v>
@@ -18549,10 +18573,10 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR84">
         <v>1.19</v>
@@ -18755,10 +18779,10 @@
         <v>0.25</v>
       </c>
       <c r="AP85">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ85">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR85">
         <v>1.39</v>
@@ -18883,7 +18907,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19167,10 +19191,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ87">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.34</v>
@@ -19295,7 +19319,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19373,10 +19397,10 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ88">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19707,7 +19731,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19785,10 +19809,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ90">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR90">
         <v>1.9</v>
@@ -20119,7 +20143,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20200,7 +20224,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR92">
         <v>1.46</v>
@@ -20612,7 +20636,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR94">
         <v>1.55</v>
@@ -20737,7 +20761,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20818,7 +20842,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -21227,10 +21251,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR97">
         <v>1.91</v>
@@ -21433,10 +21457,10 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ98">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.39</v>
@@ -21561,7 +21585,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21639,7 +21663,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21973,7 +21997,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22054,7 +22078,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101">
         <v>1.19</v>
@@ -22179,7 +22203,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22257,7 +22281,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ102">
         <v>1.45</v>
@@ -22385,7 +22409,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22591,7 +22615,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22875,10 +22899,10 @@
         <v>0.8</v>
       </c>
       <c r="AP105">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ105">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.2</v>
@@ -23003,7 +23027,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23081,10 +23105,10 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23209,7 +23233,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23415,7 +23439,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23493,10 +23517,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ108">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR108">
         <v>1.41</v>
@@ -23699,10 +23723,10 @@
         <v>2.6</v>
       </c>
       <c r="AP109">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR109">
         <v>1.57</v>
@@ -23905,10 +23929,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR110">
         <v>2.07</v>
@@ -24033,7 +24057,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24111,7 +24135,7 @@
         <v>1.8</v>
       </c>
       <c r="AP111">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ111">
         <v>2.08</v>
@@ -24317,7 +24341,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24526,7 +24550,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR113">
         <v>1.45</v>
@@ -24857,7 +24881,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -24935,10 +24959,10 @@
         <v>0.83</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ115">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.31</v>
@@ -25063,7 +25087,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25141,7 +25165,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ116">
         <v>0.5</v>
@@ -25350,7 +25374,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR117">
         <v>1.59</v>
@@ -25556,7 +25580,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ118">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25762,7 +25786,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR119">
         <v>1.43</v>
@@ -25968,7 +25992,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ120">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.31</v>
@@ -26093,7 +26117,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26171,10 +26195,10 @@
         <v>0.8</v>
       </c>
       <c r="AP121">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ121">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR121">
         <v>1.42</v>
@@ -26299,7 +26323,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26380,7 +26404,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
         <v>1.41</v>
@@ -26505,7 +26529,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26586,7 +26610,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ123">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26711,7 +26735,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26789,10 +26813,10 @@
         <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ124">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR124">
         <v>1.26</v>
@@ -26995,7 +27019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27123,7 +27147,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27201,7 +27225,7 @@
         <v>2</v>
       </c>
       <c r="AP126">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ126">
         <v>2.08</v>
@@ -27613,7 +27637,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27741,7 +27765,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -27819,10 +27843,10 @@
         <v>2.17</v>
       </c>
       <c r="AP129">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ129">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR129">
         <v>2.07</v>
@@ -28153,7 +28177,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28234,7 +28258,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ131">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR131">
         <v>1.34</v>
@@ -28359,7 +28383,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28440,7 +28464,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
         <v>1.52</v>
@@ -28643,10 +28667,10 @@
         <v>0.8</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR133">
         <v>1.62</v>
@@ -28852,7 +28876,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ134">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.6</v>
@@ -29058,7 +29082,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ135">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR135">
         <v>1.68</v>
@@ -29389,7 +29413,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29467,7 +29491,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ137">
         <v>1.09</v>
@@ -29595,7 +29619,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29673,7 +29697,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ138">
         <v>1.09</v>
@@ -29882,7 +29906,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ139">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR139">
         <v>1.63</v>
@@ -30007,7 +30031,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30088,7 +30112,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ140">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30291,10 +30315,10 @@
         <v>0.67</v>
       </c>
       <c r="AP141">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR141">
         <v>1.35</v>
@@ -30497,10 +30521,10 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR142">
         <v>1.48</v>
@@ -30831,7 +30855,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -30909,7 +30933,7 @@
         <v>1.63</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ144">
         <v>1.67</v>
@@ -31115,10 +31139,10 @@
         <v>0.8</v>
       </c>
       <c r="AP145">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ145">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR145">
         <v>1.48</v>
@@ -31321,7 +31345,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ146">
         <v>1.3</v>
@@ -31733,10 +31757,10 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR148">
         <v>1.42</v>
@@ -31861,7 +31885,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31942,7 +31966,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ149">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR149">
         <v>1.3</v>
@@ -32273,7 +32297,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32351,10 +32375,10 @@
         <v>0.5</v>
       </c>
       <c r="AP151">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ151">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32479,7 +32503,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32766,7 +32790,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ153">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR153">
         <v>1.59</v>
@@ -32969,10 +32993,10 @@
         <v>0.17</v>
       </c>
       <c r="AP154">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ154">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR154">
         <v>1.91</v>
@@ -33097,7 +33121,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33178,7 +33202,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ155">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.4</v>
@@ -33303,7 +33327,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33509,7 +33533,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33587,7 +33611,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ157">
         <v>0.5</v>
@@ -33715,7 +33739,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33921,7 +33945,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -33999,10 +34023,10 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.74</v>
@@ -34205,7 +34229,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ160">
         <v>2.08</v>
@@ -34539,7 +34563,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34620,7 +34644,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ162">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34826,7 +34850,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR163">
         <v>1.63</v>
@@ -35029,7 +35053,7 @@
         <v>0.29</v>
       </c>
       <c r="AP164">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ164">
         <v>0.5</v>
@@ -35157,7 +35181,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35238,7 +35262,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35441,7 +35465,7 @@
         <v>1.25</v>
       </c>
       <c r="AP166">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ166">
         <v>1.09</v>
@@ -35647,10 +35671,10 @@
         <v>1.14</v>
       </c>
       <c r="AP167">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ167">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR167">
         <v>1.53</v>
@@ -35775,7 +35799,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35853,7 +35877,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ168">
         <v>0.9</v>
@@ -35981,7 +36005,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36265,7 +36289,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ170">
         <v>1.3</v>
@@ -36471,7 +36495,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ171">
         <v>0.9</v>
@@ -36599,7 +36623,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36677,10 +36701,10 @@
         <v>1.89</v>
       </c>
       <c r="AP172">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR172">
         <v>1.66</v>
@@ -36886,7 +36910,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ173">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR173">
         <v>1.43</v>
@@ -37089,7 +37113,7 @@
         <v>2</v>
       </c>
       <c r="AP174">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ174">
         <v>2.08</v>
@@ -37298,7 +37322,7 @@
         <v>1</v>
       </c>
       <c r="AQ175">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR175">
         <v>1.51</v>
@@ -37423,7 +37447,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37835,7 +37859,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37916,7 +37940,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR178">
         <v>1.49</v>
@@ -38041,7 +38065,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38119,10 +38143,10 @@
         <v>0.89</v>
       </c>
       <c r="AP179">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ179">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR179">
         <v>1.72</v>
@@ -38531,10 +38555,10 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ181">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR181">
         <v>1.55</v>
@@ -38659,7 +38683,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -38737,10 +38761,10 @@
         <v>0.14</v>
       </c>
       <c r="AP182">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ182">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR182">
         <v>1.42</v>
@@ -39071,7 +39095,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39149,7 +39173,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ184">
         <v>1.82</v>
@@ -39277,7 +39301,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39483,7 +39507,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39564,7 +39588,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ186">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39767,10 +39791,10 @@
         <v>1</v>
       </c>
       <c r="AP187">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ187">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR187">
         <v>1.58</v>
@@ -39877,25 +39901,25 @@
         <v>0</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188">
         <v>1</v>
       </c>
       <c r="M188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O188" t="s">
         <v>149</v>
       </c>
       <c r="P188" t="s">
-        <v>91</v>
+        <v>304</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39973,10 +39997,10 @@
         <v>0.63</v>
       </c>
       <c r="AP188">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40101,7 +40125,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40179,10 +40203,10 @@
         <v>1.11</v>
       </c>
       <c r="AP189">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ189">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR189">
         <v>1.88</v>
@@ -40495,25 +40519,25 @@
         <v>0</v>
       </c>
       <c r="J191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L191">
         <v>1</v>
       </c>
       <c r="M191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O191" t="s">
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40585,16 +40609,16 @@
         <v>1.25</v>
       </c>
       <c r="AN191">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO191">
         <v>1.8</v>
       </c>
       <c r="AP191">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ191">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR191">
         <v>1.45</v>
@@ -40719,7 +40743,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -40797,7 +40821,7 @@
         <v>1.44</v>
       </c>
       <c r="AP192">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ192">
         <v>1.45</v>
@@ -41006,7 +41030,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ193">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR193">
         <v>1.59</v>
@@ -41131,7 +41155,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41418,7 +41442,7 @@
         <v>1</v>
       </c>
       <c r="AQ195">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR195">
         <v>1.47</v>
@@ -41543,7 +41567,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41728,22 +41752,22 @@
         <v>80</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J197">
         <v>0</v>
       </c>
       <c r="K197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M197">
         <v>1</v>
       </c>
       <c r="N197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O197" t="s">
         <v>217</v>
@@ -41827,10 +41851,10 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ197">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR197">
         <v>1.8</v>
@@ -41955,7 +41979,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42033,7 +42057,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ198">
         <v>1.3</v>
@@ -42242,7 +42266,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ199">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR199">
         <v>1.39</v>
@@ -42367,7 +42391,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -42445,10 +42469,10 @@
         <v>1.67</v>
       </c>
       <c r="AP200">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ200">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR200">
         <v>1.42</v>
@@ -42573,7 +42597,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42654,7 +42678,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ201">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR201">
         <v>1.56</v>
@@ -42779,7 +42803,7 @@
         <v>220</v>
       </c>
       <c r="P202" t="s">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="Q202">
         <v>2.65</v>
@@ -42857,7 +42881,7 @@
         <v>1.1</v>
       </c>
       <c r="AP202">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ202">
         <v>1</v>
@@ -42985,7 +43009,7 @@
         <v>221</v>
       </c>
       <c r="P203" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Q203">
         <v>2.7</v>
@@ -43063,7 +43087,7 @@
         <v>1.73</v>
       </c>
       <c r="AP203">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ203">
         <v>1.67</v>
@@ -43191,7 +43215,7 @@
         <v>167</v>
       </c>
       <c r="P204" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43269,7 +43293,7 @@
         <v>1.78</v>
       </c>
       <c r="AP204">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ204">
         <v>1.82</v>
@@ -43397,7 +43421,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43472,13 +43496,13 @@
         <v>1</v>
       </c>
       <c r="AO205">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="AP205">
         <v>0.83</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR205">
         <v>1.39</v>
@@ -43603,7 +43627,7 @@
         <v>95</v>
       </c>
       <c r="P206" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q206">
         <v>2.8</v>
@@ -43681,10 +43705,10 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR206">
         <v>1.55</v>
@@ -43809,7 +43833,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -43887,10 +43911,10 @@
         <v>1.56</v>
       </c>
       <c r="AP207">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ207">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR207">
         <v>1.3</v>
@@ -44096,7 +44120,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ208">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR208">
         <v>1.58</v>
@@ -44221,7 +44245,7 @@
         <v>223</v>
       </c>
       <c r="P209" t="s">
-        <v>310</v>
+        <v>124</v>
       </c>
       <c r="Q209">
         <v>2.35</v>
@@ -44299,10 +44323,10 @@
         <v>0.8</v>
       </c>
       <c r="AP209">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ209">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR209">
         <v>1.68</v>
@@ -44427,7 +44451,7 @@
         <v>91</v>
       </c>
       <c r="P210" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q210">
         <v>2.92</v>
@@ -44508,7 +44532,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR210">
         <v>1.39</v>
@@ -44633,7 +44657,7 @@
         <v>224</v>
       </c>
       <c r="P211" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Q211">
         <v>2.5</v>
@@ -44708,13 +44732,13 @@
         <v>2.36</v>
       </c>
       <c r="AO211">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AP211">
         <v>2.17</v>
       </c>
       <c r="AQ211">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AR211">
         <v>1.62</v>
@@ -44839,7 +44863,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q212">
         <v>3.5</v>
@@ -45251,7 +45275,7 @@
         <v>225</v>
       </c>
       <c r="P214" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q214">
         <v>3.18</v>
@@ -45329,10 +45353,10 @@
         <v>0.91</v>
       </c>
       <c r="AP214">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ214">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR214">
         <v>1.58</v>
@@ -45457,7 +45481,7 @@
         <v>128</v>
       </c>
       <c r="P215" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Q215">
         <v>2.7</v>
@@ -45532,13 +45556,13 @@
         <v>1.9</v>
       </c>
       <c r="AO215">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="AP215">
         <v>1.73</v>
       </c>
       <c r="AQ215">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AR215">
         <v>1.69</v>
@@ -45663,7 +45687,7 @@
         <v>226</v>
       </c>
       <c r="P216" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -45941,16 +45965,16 @@
         <v>1.51</v>
       </c>
       <c r="AN217">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO217">
         <v>0.44</v>
       </c>
       <c r="AP217">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AQ217">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR217">
         <v>1.42</v>
@@ -46075,7 +46099,7 @@
         <v>91</v>
       </c>
       <c r="P218" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46150,13 +46174,13 @@
         <v>1.1</v>
       </c>
       <c r="AO218">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AP218">
         <v>1</v>
       </c>
       <c r="AQ218">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR218">
         <v>1.47</v>
@@ -46559,16 +46583,16 @@
         <v>1.5</v>
       </c>
       <c r="AN220">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AO220">
         <v>1.7</v>
       </c>
       <c r="AP220">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AQ220">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR220">
         <v>1.8</v>
@@ -46644,6 +46668,1860 @@
       </c>
       <c r="BP220">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7778294</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45843.25</v>
+      </c>
+      <c r="F221">
+        <v>23</v>
+      </c>
+      <c r="G221" t="s">
+        <v>78</v>
+      </c>
+      <c r="H221" t="s">
+        <v>82</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>3</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>229</v>
+      </c>
+      <c r="P221" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q221">
+        <v>2.5</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>4.5</v>
+      </c>
+      <c r="T221">
+        <v>1.4</v>
+      </c>
+      <c r="U221">
+        <v>2.75</v>
+      </c>
+      <c r="V221">
+        <v>3</v>
+      </c>
+      <c r="W221">
+        <v>1.36</v>
+      </c>
+      <c r="X221">
+        <v>8</v>
+      </c>
+      <c r="Y221">
+        <v>1.08</v>
+      </c>
+      <c r="Z221">
+        <v>1.84</v>
+      </c>
+      <c r="AA221">
+        <v>3.09</v>
+      </c>
+      <c r="AB221">
+        <v>3.94</v>
+      </c>
+      <c r="AC221">
+        <v>1.06</v>
+      </c>
+      <c r="AD221">
+        <v>8.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.36</v>
+      </c>
+      <c r="AF221">
+        <v>3.1</v>
+      </c>
+      <c r="AG221">
+        <v>1.95</v>
+      </c>
+      <c r="AH221">
+        <v>1.75</v>
+      </c>
+      <c r="AI221">
+        <v>1.91</v>
+      </c>
+      <c r="AJ221">
+        <v>1.91</v>
+      </c>
+      <c r="AK221">
+        <v>1.22</v>
+      </c>
+      <c r="AL221">
+        <v>1.25</v>
+      </c>
+      <c r="AM221">
+        <v>1.83</v>
+      </c>
+      <c r="AN221">
+        <v>1</v>
+      </c>
+      <c r="AO221">
+        <v>1</v>
+      </c>
+      <c r="AP221">
+        <v>1.18</v>
+      </c>
+      <c r="AQ221">
+        <v>0.92</v>
+      </c>
+      <c r="AR221">
+        <v>1.45</v>
+      </c>
+      <c r="AS221">
+        <v>1.47</v>
+      </c>
+      <c r="AT221">
+        <v>2.92</v>
+      </c>
+      <c r="AU221">
+        <v>7</v>
+      </c>
+      <c r="AV221">
+        <v>5</v>
+      </c>
+      <c r="AW221">
+        <v>8</v>
+      </c>
+      <c r="AX221">
+        <v>10</v>
+      </c>
+      <c r="AY221">
+        <v>15</v>
+      </c>
+      <c r="AZ221">
+        <v>15</v>
+      </c>
+      <c r="BA221">
+        <v>2</v>
+      </c>
+      <c r="BB221">
+        <v>1</v>
+      </c>
+      <c r="BC221">
+        <v>3</v>
+      </c>
+      <c r="BD221">
+        <v>1.7</v>
+      </c>
+      <c r="BE221">
+        <v>6.5</v>
+      </c>
+      <c r="BF221">
+        <v>2.4</v>
+      </c>
+      <c r="BG221">
+        <v>1.37</v>
+      </c>
+      <c r="BH221">
+        <v>2.7</v>
+      </c>
+      <c r="BI221">
+        <v>1.64</v>
+      </c>
+      <c r="BJ221">
+        <v>2.05</v>
+      </c>
+      <c r="BK221">
+        <v>2.04</v>
+      </c>
+      <c r="BL221">
+        <v>1.65</v>
+      </c>
+      <c r="BM221">
+        <v>2.63</v>
+      </c>
+      <c r="BN221">
+        <v>1.4</v>
+      </c>
+      <c r="BO221">
+        <v>3.45</v>
+      </c>
+      <c r="BP221">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7778301</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45843.28819444445</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>74</v>
+      </c>
+      <c r="H222" t="s">
+        <v>87</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>91</v>
+      </c>
+      <c r="P222" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q222">
+        <v>4.95</v>
+      </c>
+      <c r="R222">
+        <v>1.93</v>
+      </c>
+      <c r="S222">
+        <v>2.69</v>
+      </c>
+      <c r="T222">
+        <v>1.53</v>
+      </c>
+      <c r="U222">
+        <v>2.34</v>
+      </c>
+      <c r="V222">
+        <v>3.5</v>
+      </c>
+      <c r="W222">
+        <v>1.22</v>
+      </c>
+      <c r="X222">
+        <v>9</v>
+      </c>
+      <c r="Y222">
+        <v>1</v>
+      </c>
+      <c r="Z222">
+        <v>2.4</v>
+      </c>
+      <c r="AA222">
+        <v>3.05</v>
+      </c>
+      <c r="AB222">
+        <v>2.67</v>
+      </c>
+      <c r="AC222">
+        <v>1.06</v>
+      </c>
+      <c r="AD222">
+        <v>6.65</v>
+      </c>
+      <c r="AE222">
+        <v>1.48</v>
+      </c>
+      <c r="AF222">
+        <v>2.37</v>
+      </c>
+      <c r="AG222">
+        <v>2.19</v>
+      </c>
+      <c r="AH222">
+        <v>1.6</v>
+      </c>
+      <c r="AI222">
+        <v>2.17</v>
+      </c>
+      <c r="AJ222">
+        <v>1.61</v>
+      </c>
+      <c r="AK222">
+        <v>1.82</v>
+      </c>
+      <c r="AL222">
+        <v>1.35</v>
+      </c>
+      <c r="AM222">
+        <v>1.24</v>
+      </c>
+      <c r="AN222">
+        <v>1.64</v>
+      </c>
+      <c r="AO222">
+        <v>1.55</v>
+      </c>
+      <c r="AP222">
+        <v>1.5</v>
+      </c>
+      <c r="AQ222">
+        <v>1.67</v>
+      </c>
+      <c r="AR222">
+        <v>1.62</v>
+      </c>
+      <c r="AS222">
+        <v>1.57</v>
+      </c>
+      <c r="AT222">
+        <v>3.19</v>
+      </c>
+      <c r="AU222">
+        <v>4</v>
+      </c>
+      <c r="AV222">
+        <v>5</v>
+      </c>
+      <c r="AW222">
+        <v>4</v>
+      </c>
+      <c r="AX222">
+        <v>8</v>
+      </c>
+      <c r="AY222">
+        <v>8</v>
+      </c>
+      <c r="AZ222">
+        <v>13</v>
+      </c>
+      <c r="BA222">
+        <v>5</v>
+      </c>
+      <c r="BB222">
+        <v>13</v>
+      </c>
+      <c r="BC222">
+        <v>18</v>
+      </c>
+      <c r="BD222">
+        <v>2.55</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
+        <v>1.6</v>
+      </c>
+      <c r="BG222">
+        <v>1.27</v>
+      </c>
+      <c r="BH222">
+        <v>3.2</v>
+      </c>
+      <c r="BI222">
+        <v>1.48</v>
+      </c>
+      <c r="BJ222">
+        <v>2.38</v>
+      </c>
+      <c r="BK222">
+        <v>1.79</v>
+      </c>
+      <c r="BL222">
+        <v>1.86</v>
+      </c>
+      <c r="BM222">
+        <v>2.23</v>
+      </c>
+      <c r="BN222">
+        <v>1.54</v>
+      </c>
+      <c r="BO222">
+        <v>2.85</v>
+      </c>
+      <c r="BP222">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7778300</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F223">
+        <v>23</v>
+      </c>
+      <c r="G223" t="s">
+        <v>72</v>
+      </c>
+      <c r="H223" t="s">
+        <v>77</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>4</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>4</v>
+      </c>
+      <c r="O223" t="s">
+        <v>230</v>
+      </c>
+      <c r="P223" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q223">
+        <v>2.02</v>
+      </c>
+      <c r="R223">
+        <v>2.25</v>
+      </c>
+      <c r="S223">
+        <v>6.5</v>
+      </c>
+      <c r="T223">
+        <v>1.36</v>
+      </c>
+      <c r="U223">
+        <v>2.78</v>
+      </c>
+      <c r="V223">
+        <v>2.88</v>
+      </c>
+      <c r="W223">
+        <v>1.34</v>
+      </c>
+      <c r="X223">
+        <v>7.2</v>
+      </c>
+      <c r="Y223">
+        <v>1.03</v>
+      </c>
+      <c r="Z223">
+        <v>1.36</v>
+      </c>
+      <c r="AA223">
+        <v>4.5</v>
+      </c>
+      <c r="AB223">
+        <v>6.2</v>
+      </c>
+      <c r="AC223">
+        <v>1</v>
+      </c>
+      <c r="AD223">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE223">
+        <v>1.29</v>
+      </c>
+      <c r="AF223">
+        <v>3.12</v>
+      </c>
+      <c r="AG223">
+        <v>1.95</v>
+      </c>
+      <c r="AH223">
+        <v>1.75</v>
+      </c>
+      <c r="AI223">
+        <v>2.12</v>
+      </c>
+      <c r="AJ223">
+        <v>1.64</v>
+      </c>
+      <c r="AK223">
+        <v>1.1</v>
+      </c>
+      <c r="AL223">
+        <v>1.22</v>
+      </c>
+      <c r="AM223">
+        <v>2.64</v>
+      </c>
+      <c r="AN223">
+        <v>1.82</v>
+      </c>
+      <c r="AO223">
+        <v>1.1</v>
+      </c>
+      <c r="AP223">
+        <v>1.92</v>
+      </c>
+      <c r="AQ223">
+        <v>1</v>
+      </c>
+      <c r="AR223">
+        <v>1.8</v>
+      </c>
+      <c r="AS223">
+        <v>1.29</v>
+      </c>
+      <c r="AT223">
+        <v>3.09</v>
+      </c>
+      <c r="AU223">
+        <v>10</v>
+      </c>
+      <c r="AV223">
+        <v>4</v>
+      </c>
+      <c r="AW223">
+        <v>4</v>
+      </c>
+      <c r="AX223">
+        <v>2</v>
+      </c>
+      <c r="AY223">
+        <v>14</v>
+      </c>
+      <c r="AZ223">
+        <v>6</v>
+      </c>
+      <c r="BA223">
+        <v>6</v>
+      </c>
+      <c r="BB223">
+        <v>3</v>
+      </c>
+      <c r="BC223">
+        <v>9</v>
+      </c>
+      <c r="BD223">
+        <v>1.33</v>
+      </c>
+      <c r="BE223">
+        <v>7.5</v>
+      </c>
+      <c r="BF223">
+        <v>3.55</v>
+      </c>
+      <c r="BG223">
+        <v>1.26</v>
+      </c>
+      <c r="BH223">
+        <v>3.3</v>
+      </c>
+      <c r="BI223">
+        <v>1.46</v>
+      </c>
+      <c r="BJ223">
+        <v>2.43</v>
+      </c>
+      <c r="BK223">
+        <v>1.74</v>
+      </c>
+      <c r="BL223">
+        <v>1.91</v>
+      </c>
+      <c r="BM223">
+        <v>2.17</v>
+      </c>
+      <c r="BN223">
+        <v>1.57</v>
+      </c>
+      <c r="BO223">
+        <v>2.75</v>
+      </c>
+      <c r="BP223">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7778299</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F224">
+        <v>23</v>
+      </c>
+      <c r="G224" t="s">
+        <v>84</v>
+      </c>
+      <c r="H224" t="s">
+        <v>70</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224" t="s">
+        <v>91</v>
+      </c>
+      <c r="P224" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q224">
+        <v>2.88</v>
+      </c>
+      <c r="R224">
+        <v>2.15</v>
+      </c>
+      <c r="S224">
+        <v>3.25</v>
+      </c>
+      <c r="T224">
+        <v>1.33</v>
+      </c>
+      <c r="U224">
+        <v>3.1</v>
+      </c>
+      <c r="V224">
+        <v>2.4</v>
+      </c>
+      <c r="W224">
+        <v>1.5</v>
+      </c>
+      <c r="X224">
+        <v>6</v>
+      </c>
+      <c r="Y224">
+        <v>1.12</v>
+      </c>
+      <c r="Z224">
+        <v>2.21</v>
+      </c>
+      <c r="AA224">
+        <v>3.35</v>
+      </c>
+      <c r="AB224">
+        <v>2.71</v>
+      </c>
+      <c r="AC224">
+        <v>1.04</v>
+      </c>
+      <c r="AD224">
+        <v>10</v>
+      </c>
+      <c r="AE224">
+        <v>1.22</v>
+      </c>
+      <c r="AF224">
+        <v>4.2</v>
+      </c>
+      <c r="AG224">
+        <v>1.61</v>
+      </c>
+      <c r="AH224">
+        <v>2.17</v>
+      </c>
+      <c r="AI224">
+        <v>1.53</v>
+      </c>
+      <c r="AJ224">
+        <v>2.3</v>
+      </c>
+      <c r="AK224">
+        <v>1.42</v>
+      </c>
+      <c r="AL224">
+        <v>1.25</v>
+      </c>
+      <c r="AM224">
+        <v>1.57</v>
+      </c>
+      <c r="AN224">
+        <v>1.91</v>
+      </c>
+      <c r="AO224">
+        <v>0.83</v>
+      </c>
+      <c r="AP224">
+        <v>1.75</v>
+      </c>
+      <c r="AQ224">
+        <v>1</v>
+      </c>
+      <c r="AR224">
+        <v>1.88</v>
+      </c>
+      <c r="AS224">
+        <v>1.57</v>
+      </c>
+      <c r="AT224">
+        <v>3.45</v>
+      </c>
+      <c r="AU224">
+        <v>6</v>
+      </c>
+      <c r="AV224">
+        <v>5</v>
+      </c>
+      <c r="AW224">
+        <v>10</v>
+      </c>
+      <c r="AX224">
+        <v>4</v>
+      </c>
+      <c r="AY224">
+        <v>16</v>
+      </c>
+      <c r="AZ224">
+        <v>9</v>
+      </c>
+      <c r="BA224">
+        <v>5</v>
+      </c>
+      <c r="BB224">
+        <v>7</v>
+      </c>
+      <c r="BC224">
+        <v>12</v>
+      </c>
+      <c r="BD224">
+        <v>1.65</v>
+      </c>
+      <c r="BE224">
+        <v>6.75</v>
+      </c>
+      <c r="BF224">
+        <v>2.48</v>
+      </c>
+      <c r="BG224">
+        <v>1.19</v>
+      </c>
+      <c r="BH224">
+        <v>3.9</v>
+      </c>
+      <c r="BI224">
+        <v>1.35</v>
+      </c>
+      <c r="BJ224">
+        <v>2.8</v>
+      </c>
+      <c r="BK224">
+        <v>1.6</v>
+      </c>
+      <c r="BL224">
+        <v>2.12</v>
+      </c>
+      <c r="BM224">
+        <v>1.94</v>
+      </c>
+      <c r="BN224">
+        <v>1.71</v>
+      </c>
+      <c r="BO224">
+        <v>2.45</v>
+      </c>
+      <c r="BP224">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7778298</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F225">
+        <v>23</v>
+      </c>
+      <c r="G225" t="s">
+        <v>83</v>
+      </c>
+      <c r="H225" t="s">
+        <v>88</v>
+      </c>
+      <c r="I225">
+        <v>2</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>3</v>
+      </c>
+      <c r="L225">
+        <v>2</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>3</v>
+      </c>
+      <c r="O225" t="s">
+        <v>231</v>
+      </c>
+      <c r="P225" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q225">
+        <v>2.75</v>
+      </c>
+      <c r="R225">
+        <v>2.1</v>
+      </c>
+      <c r="S225">
+        <v>4.33</v>
+      </c>
+      <c r="T225">
+        <v>1.44</v>
+      </c>
+      <c r="U225">
+        <v>2.63</v>
+      </c>
+      <c r="V225">
+        <v>3.25</v>
+      </c>
+      <c r="W225">
+        <v>1.33</v>
+      </c>
+      <c r="X225">
+        <v>9</v>
+      </c>
+      <c r="Y225">
+        <v>1.07</v>
+      </c>
+      <c r="Z225">
+        <v>2.11</v>
+      </c>
+      <c r="AA225">
+        <v>3.06</v>
+      </c>
+      <c r="AB225">
+        <v>3.14</v>
+      </c>
+      <c r="AC225">
+        <v>1.07</v>
+      </c>
+      <c r="AD225">
+        <v>8</v>
+      </c>
+      <c r="AE225">
+        <v>1.38</v>
+      </c>
+      <c r="AF225">
+        <v>3</v>
+      </c>
+      <c r="AG225">
+        <v>1.95</v>
+      </c>
+      <c r="AH225">
+        <v>1.75</v>
+      </c>
+      <c r="AI225">
+        <v>1.95</v>
+      </c>
+      <c r="AJ225">
+        <v>1.8</v>
+      </c>
+      <c r="AK225">
+        <v>1.25</v>
+      </c>
+      <c r="AL225">
+        <v>1.28</v>
+      </c>
+      <c r="AM225">
+        <v>1.75</v>
+      </c>
+      <c r="AN225">
+        <v>1.8</v>
+      </c>
+      <c r="AO225">
+        <v>0.73</v>
+      </c>
+      <c r="AP225">
+        <v>1.91</v>
+      </c>
+      <c r="AQ225">
+        <v>0.67</v>
+      </c>
+      <c r="AR225">
+        <v>1.63</v>
+      </c>
+      <c r="AS225">
+        <v>1.18</v>
+      </c>
+      <c r="AT225">
+        <v>2.81</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>10</v>
+      </c>
+      <c r="AX225">
+        <v>8</v>
+      </c>
+      <c r="AY225">
+        <v>15</v>
+      </c>
+      <c r="AZ225">
+        <v>12</v>
+      </c>
+      <c r="BA225">
+        <v>6</v>
+      </c>
+      <c r="BB225">
+        <v>7</v>
+      </c>
+      <c r="BC225">
+        <v>13</v>
+      </c>
+      <c r="BD225">
+        <v>1.68</v>
+      </c>
+      <c r="BE225">
+        <v>6.75</v>
+      </c>
+      <c r="BF225">
+        <v>2.4</v>
+      </c>
+      <c r="BG225">
+        <v>1.3</v>
+      </c>
+      <c r="BH225">
+        <v>3.05</v>
+      </c>
+      <c r="BI225">
+        <v>1.52</v>
+      </c>
+      <c r="BJ225">
+        <v>2.28</v>
+      </c>
+      <c r="BK225">
+        <v>1.84</v>
+      </c>
+      <c r="BL225">
+        <v>1.8</v>
+      </c>
+      <c r="BM225">
+        <v>2.33</v>
+      </c>
+      <c r="BN225">
+        <v>1.49</v>
+      </c>
+      <c r="BO225">
+        <v>3.05</v>
+      </c>
+      <c r="BP225">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7778297</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F226">
+        <v>23</v>
+      </c>
+      <c r="G226" t="s">
+        <v>80</v>
+      </c>
+      <c r="H226" t="s">
+        <v>79</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226" t="s">
+        <v>91</v>
+      </c>
+      <c r="P226" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q226">
+        <v>3</v>
+      </c>
+      <c r="R226">
+        <v>1.91</v>
+      </c>
+      <c r="S226">
+        <v>4.75</v>
+      </c>
+      <c r="T226">
+        <v>1.62</v>
+      </c>
+      <c r="U226">
+        <v>2.2</v>
+      </c>
+      <c r="V226">
+        <v>4</v>
+      </c>
+      <c r="W226">
+        <v>1.22</v>
+      </c>
+      <c r="X226">
+        <v>13</v>
+      </c>
+      <c r="Y226">
+        <v>1.04</v>
+      </c>
+      <c r="Z226">
+        <v>2.09</v>
+      </c>
+      <c r="AA226">
+        <v>2.79</v>
+      </c>
+      <c r="AB226">
+        <v>3.55</v>
+      </c>
+      <c r="AC226">
+        <v>1.12</v>
+      </c>
+      <c r="AD226">
+        <v>5.75</v>
+      </c>
+      <c r="AE226">
+        <v>1.53</v>
+      </c>
+      <c r="AF226">
+        <v>2.25</v>
+      </c>
+      <c r="AG226">
+        <v>2.55</v>
+      </c>
+      <c r="AH226">
+        <v>1.45</v>
+      </c>
+      <c r="AI226">
+        <v>2.25</v>
+      </c>
+      <c r="AJ226">
+        <v>1.57</v>
+      </c>
+      <c r="AK226">
+        <v>1.25</v>
+      </c>
+      <c r="AL226">
+        <v>1.33</v>
+      </c>
+      <c r="AM226">
+        <v>1.67</v>
+      </c>
+      <c r="AN226">
+        <v>1.8</v>
+      </c>
+      <c r="AO226">
+        <v>1</v>
+      </c>
+      <c r="AP226">
+        <v>1.73</v>
+      </c>
+      <c r="AQ226">
+        <v>1</v>
+      </c>
+      <c r="AR226">
+        <v>1.44</v>
+      </c>
+      <c r="AS226">
+        <v>1.11</v>
+      </c>
+      <c r="AT226">
+        <v>2.55</v>
+      </c>
+      <c r="AU226">
+        <v>2</v>
+      </c>
+      <c r="AV226">
+        <v>5</v>
+      </c>
+      <c r="AW226">
+        <v>5</v>
+      </c>
+      <c r="AX226">
+        <v>4</v>
+      </c>
+      <c r="AY226">
+        <v>7</v>
+      </c>
+      <c r="AZ226">
+        <v>9</v>
+      </c>
+      <c r="BA226">
+        <v>4</v>
+      </c>
+      <c r="BB226">
+        <v>4</v>
+      </c>
+      <c r="BC226">
+        <v>8</v>
+      </c>
+      <c r="BD226">
+        <v>1.72</v>
+      </c>
+      <c r="BE226">
+        <v>6.5</v>
+      </c>
+      <c r="BF226">
+        <v>2.33</v>
+      </c>
+      <c r="BG226">
+        <v>1.38</v>
+      </c>
+      <c r="BH226">
+        <v>2.65</v>
+      </c>
+      <c r="BI226">
+        <v>1.65</v>
+      </c>
+      <c r="BJ226">
+        <v>2.02</v>
+      </c>
+      <c r="BK226">
+        <v>2.06</v>
+      </c>
+      <c r="BL226">
+        <v>1.63</v>
+      </c>
+      <c r="BM226">
+        <v>2.65</v>
+      </c>
+      <c r="BN226">
+        <v>1.38</v>
+      </c>
+      <c r="BO226">
+        <v>3.55</v>
+      </c>
+      <c r="BP226">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7778295</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F227">
+        <v>23</v>
+      </c>
+      <c r="G227" t="s">
+        <v>76</v>
+      </c>
+      <c r="H227" t="s">
+        <v>86</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>2</v>
+      </c>
+      <c r="L227">
+        <v>2</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>3</v>
+      </c>
+      <c r="O227" t="s">
+        <v>232</v>
+      </c>
+      <c r="P227" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q227">
+        <v>2.75</v>
+      </c>
+      <c r="R227">
+        <v>2.25</v>
+      </c>
+      <c r="S227">
+        <v>3.5</v>
+      </c>
+      <c r="T227">
+        <v>1.33</v>
+      </c>
+      <c r="U227">
+        <v>3.25</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>6.5</v>
+      </c>
+      <c r="Y227">
+        <v>1.11</v>
+      </c>
+      <c r="Z227">
+        <v>2.01</v>
+      </c>
+      <c r="AA227">
+        <v>3.41</v>
+      </c>
+      <c r="AB227">
+        <v>3.04</v>
+      </c>
+      <c r="AC227">
+        <v>1.05</v>
+      </c>
+      <c r="AD227">
+        <v>9.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.25</v>
+      </c>
+      <c r="AF227">
+        <v>3.8</v>
+      </c>
+      <c r="AG227">
+        <v>1.77</v>
+      </c>
+      <c r="AH227">
+        <v>1.93</v>
+      </c>
+      <c r="AI227">
+        <v>1.67</v>
+      </c>
+      <c r="AJ227">
+        <v>2.1</v>
+      </c>
+      <c r="AK227">
+        <v>1.35</v>
+      </c>
+      <c r="AL227">
+        <v>1.25</v>
+      </c>
+      <c r="AM227">
+        <v>1.65</v>
+      </c>
+      <c r="AN227">
+        <v>1.73</v>
+      </c>
+      <c r="AO227">
+        <v>1.5</v>
+      </c>
+      <c r="AP227">
+        <v>1.83</v>
+      </c>
+      <c r="AQ227">
+        <v>1.36</v>
+      </c>
+      <c r="AR227">
+        <v>1.64</v>
+      </c>
+      <c r="AS227">
+        <v>1.49</v>
+      </c>
+      <c r="AT227">
+        <v>3.13</v>
+      </c>
+      <c r="AU227">
+        <v>7</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>10</v>
+      </c>
+      <c r="AX227">
+        <v>8</v>
+      </c>
+      <c r="AY227">
+        <v>17</v>
+      </c>
+      <c r="AZ227">
+        <v>12</v>
+      </c>
+      <c r="BA227">
+        <v>7</v>
+      </c>
+      <c r="BB227">
+        <v>2</v>
+      </c>
+      <c r="BC227">
+        <v>9</v>
+      </c>
+      <c r="BD227">
+        <v>1.74</v>
+      </c>
+      <c r="BE227">
+        <v>6.75</v>
+      </c>
+      <c r="BF227">
+        <v>2.3</v>
+      </c>
+      <c r="BG227">
+        <v>1.25</v>
+      </c>
+      <c r="BH227">
+        <v>3.35</v>
+      </c>
+      <c r="BI227">
+        <v>1.44</v>
+      </c>
+      <c r="BJ227">
+        <v>2.48</v>
+      </c>
+      <c r="BK227">
+        <v>1.73</v>
+      </c>
+      <c r="BL227">
+        <v>1.93</v>
+      </c>
+      <c r="BM227">
+        <v>2.14</v>
+      </c>
+      <c r="BN227">
+        <v>1.58</v>
+      </c>
+      <c r="BO227">
+        <v>2.7</v>
+      </c>
+      <c r="BP227">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7778293</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F228">
+        <v>23</v>
+      </c>
+      <c r="G228" t="s">
+        <v>81</v>
+      </c>
+      <c r="H228" t="s">
+        <v>85</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>216</v>
+      </c>
+      <c r="P228" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q228">
+        <v>2.25</v>
+      </c>
+      <c r="R228">
+        <v>2.2</v>
+      </c>
+      <c r="S228">
+        <v>4.5</v>
+      </c>
+      <c r="T228">
+        <v>1.35</v>
+      </c>
+      <c r="U228">
+        <v>2.95</v>
+      </c>
+      <c r="V228">
+        <v>2.65</v>
+      </c>
+      <c r="W228">
+        <v>1.42</v>
+      </c>
+      <c r="X228">
+        <v>7</v>
+      </c>
+      <c r="Y228">
+        <v>1.1</v>
+      </c>
+      <c r="Z228">
+        <v>1.62</v>
+      </c>
+      <c r="AA228">
+        <v>3.75</v>
+      </c>
+      <c r="AB228">
+        <v>4.2</v>
+      </c>
+      <c r="AC228">
+        <v>1.05</v>
+      </c>
+      <c r="AD228">
+        <v>9.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.28</v>
+      </c>
+      <c r="AF228">
+        <v>3.55</v>
+      </c>
+      <c r="AG228">
+        <v>1.79</v>
+      </c>
+      <c r="AH228">
+        <v>1.91</v>
+      </c>
+      <c r="AI228">
+        <v>1.77</v>
+      </c>
+      <c r="AJ228">
+        <v>1.91</v>
+      </c>
+      <c r="AK228">
+        <v>1.2</v>
+      </c>
+      <c r="AL228">
+        <v>1.22</v>
+      </c>
+      <c r="AM228">
+        <v>2</v>
+      </c>
+      <c r="AN228">
+        <v>1.6</v>
+      </c>
+      <c r="AO228">
+        <v>1</v>
+      </c>
+      <c r="AP228">
+        <v>1.73</v>
+      </c>
+      <c r="AQ228">
+        <v>0.92</v>
+      </c>
+      <c r="AR228">
+        <v>1.58</v>
+      </c>
+      <c r="AS228">
+        <v>1.23</v>
+      </c>
+      <c r="AT228">
+        <v>2.81</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>6</v>
+      </c>
+      <c r="AW228">
+        <v>7</v>
+      </c>
+      <c r="AX228">
+        <v>4</v>
+      </c>
+      <c r="AY228">
+        <v>10</v>
+      </c>
+      <c r="AZ228">
+        <v>10</v>
+      </c>
+      <c r="BA228">
+        <v>4</v>
+      </c>
+      <c r="BB228">
+        <v>7</v>
+      </c>
+      <c r="BC228">
+        <v>11</v>
+      </c>
+      <c r="BD228">
+        <v>1.53</v>
+      </c>
+      <c r="BE228">
+        <v>6.75</v>
+      </c>
+      <c r="BF228">
+        <v>2.8</v>
+      </c>
+      <c r="BG228">
+        <v>1.24</v>
+      </c>
+      <c r="BH228">
+        <v>3.4</v>
+      </c>
+      <c r="BI228">
+        <v>1.44</v>
+      </c>
+      <c r="BJ228">
+        <v>2.48</v>
+      </c>
+      <c r="BK228">
+        <v>1.71</v>
+      </c>
+      <c r="BL228">
+        <v>1.94</v>
+      </c>
+      <c r="BM228">
+        <v>2.12</v>
+      </c>
+      <c r="BN228">
+        <v>1.6</v>
+      </c>
+      <c r="BO228">
+        <v>2.7</v>
+      </c>
+      <c r="BP228">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7778296</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F229">
+        <v>23</v>
+      </c>
+      <c r="G229" t="s">
+        <v>73</v>
+      </c>
+      <c r="H229" t="s">
+        <v>75</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>91</v>
+      </c>
+      <c r="P229" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q229">
+        <v>2.9</v>
+      </c>
+      <c r="R229">
+        <v>2.1</v>
+      </c>
+      <c r="S229">
+        <v>3.35</v>
+      </c>
+      <c r="T229">
+        <v>1.36</v>
+      </c>
+      <c r="U229">
+        <v>2.85</v>
+      </c>
+      <c r="V229">
+        <v>2.65</v>
+      </c>
+      <c r="W229">
+        <v>1.42</v>
+      </c>
+      <c r="X229">
+        <v>7</v>
+      </c>
+      <c r="Y229">
+        <v>1.1</v>
+      </c>
+      <c r="Z229">
+        <v>2.17</v>
+      </c>
+      <c r="AA229">
+        <v>3.21</v>
+      </c>
+      <c r="AB229">
+        <v>2.87</v>
+      </c>
+      <c r="AC229">
+        <v>1.05</v>
+      </c>
+      <c r="AD229">
+        <v>9</v>
+      </c>
+      <c r="AE229">
+        <v>1.28</v>
+      </c>
+      <c r="AF229">
+        <v>3.5</v>
+      </c>
+      <c r="AG229">
+        <v>1.77</v>
+      </c>
+      <c r="AH229">
+        <v>1.93</v>
+      </c>
+      <c r="AI229">
+        <v>1.65</v>
+      </c>
+      <c r="AJ229">
+        <v>2.05</v>
+      </c>
+      <c r="AK229">
+        <v>1.4</v>
+      </c>
+      <c r="AL229">
+        <v>1.25</v>
+      </c>
+      <c r="AM229">
+        <v>1.57</v>
+      </c>
+      <c r="AN229">
+        <v>1.17</v>
+      </c>
+      <c r="AO229">
+        <v>0.5</v>
+      </c>
+      <c r="AP229">
+        <v>1.08</v>
+      </c>
+      <c r="AQ229">
+        <v>0.73</v>
+      </c>
+      <c r="AR229">
+        <v>1.25</v>
+      </c>
+      <c r="AS229">
+        <v>1.4</v>
+      </c>
+      <c r="AT229">
+        <v>2.65</v>
+      </c>
+      <c r="AU229">
+        <v>2</v>
+      </c>
+      <c r="AV229">
+        <v>3</v>
+      </c>
+      <c r="AW229">
+        <v>5</v>
+      </c>
+      <c r="AX229">
+        <v>11</v>
+      </c>
+      <c r="AY229">
+        <v>7</v>
+      </c>
+      <c r="AZ229">
+        <v>14</v>
+      </c>
+      <c r="BA229">
+        <v>7</v>
+      </c>
+      <c r="BB229">
+        <v>2</v>
+      </c>
+      <c r="BC229">
+        <v>9</v>
+      </c>
+      <c r="BD229">
+        <v>1.65</v>
+      </c>
+      <c r="BE229">
+        <v>6.75</v>
+      </c>
+      <c r="BF229">
+        <v>2.45</v>
+      </c>
+      <c r="BG229">
+        <v>1.23</v>
+      </c>
+      <c r="BH229">
+        <v>3.5</v>
+      </c>
+      <c r="BI229">
+        <v>1.41</v>
+      </c>
+      <c r="BJ229">
+        <v>2.55</v>
+      </c>
+      <c r="BK229">
+        <v>1.68</v>
+      </c>
+      <c r="BL229">
+        <v>1.98</v>
+      </c>
+      <c r="BM229">
+        <v>2.08</v>
+      </c>
+      <c r="BN229">
+        <v>1.62</v>
+      </c>
+      <c r="BO229">
+        <v>2.65</v>
+      </c>
+      <c r="BP229">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -40633,19 +40633,19 @@
         <v>4</v>
       </c>
       <c r="AV191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW191">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AX191">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY191">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AZ191">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41048,16 +41048,16 @@
         <v>4</v>
       </c>
       <c r="AW193">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AX193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY193">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA193">
         <v>12</v>
@@ -41660,22 +41660,22 @@
         <v>2.84</v>
       </c>
       <c r="AU196">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV196">
         <v>6</v>
       </c>
       <c r="AW196">
+        <v>5</v>
+      </c>
+      <c r="AX196">
+        <v>3</v>
+      </c>
+      <c r="AY196">
+        <v>4</v>
+      </c>
+      <c r="AZ196">
         <v>9</v>
-      </c>
-      <c r="AX196">
-        <v>6</v>
-      </c>
-      <c r="AY196">
-        <v>9</v>
-      </c>
-      <c r="AZ196">
-        <v>12</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -42278,22 +42278,22 @@
         <v>2.96</v>
       </c>
       <c r="AU199">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
         <v>6</v>
       </c>
-      <c r="AW199">
-        <v>8</v>
-      </c>
       <c r="AX199">
+        <v>5</v>
+      </c>
+      <c r="AY199">
+        <v>15</v>
+      </c>
+      <c r="AZ199">
         <v>12</v>
-      </c>
-      <c r="AY199">
-        <v>18</v>
-      </c>
-      <c r="AZ199">
-        <v>18</v>
       </c>
       <c r="BA199">
         <v>1</v>
@@ -42490,16 +42490,16 @@
         <v>4</v>
       </c>
       <c r="AW200">
+        <v>2</v>
+      </c>
+      <c r="AX200">
+        <v>3</v>
+      </c>
+      <c r="AY200">
+        <v>9</v>
+      </c>
+      <c r="AZ200">
         <v>7</v>
-      </c>
-      <c r="AX200">
-        <v>7</v>
-      </c>
-      <c r="AY200">
-        <v>14</v>
-      </c>
-      <c r="AZ200">
-        <v>11</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -42690,22 +42690,22 @@
         <v>2.68</v>
       </c>
       <c r="AU201">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV201">
         <v>3</v>
       </c>
       <c r="AW201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX201">
+        <v>3</v>
+      </c>
+      <c r="AY201">
         <v>7</v>
       </c>
-      <c r="AY201">
-        <v>10</v>
-      </c>
       <c r="AZ201">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA201">
         <v>2</v>
@@ -43102,22 +43102,22 @@
         <v>2.93</v>
       </c>
       <c r="AU203">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW203">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX203">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY203">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA203">
         <v>7</v>
@@ -43514,16 +43514,16 @@
         <v>2.68</v>
       </c>
       <c r="AU205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV205">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW205">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY205">
         <v>15</v>
@@ -43720,22 +43720,22 @@
         <v>3.1</v>
       </c>
       <c r="AU206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV206">
         <v>2</v>
       </c>
       <c r="AW206">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY206">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AZ206">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
@@ -43920,10 +43920,10 @@
         <v>1.3</v>
       </c>
       <c r="AS207">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AT207">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AU207">
         <v>2</v>
@@ -44338,22 +44338,22 @@
         <v>2.8</v>
       </c>
       <c r="AU209">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV209">
         <v>7</v>
       </c>
       <c r="AW209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX209">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ209">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA209">
         <v>2</v>
@@ -44547,7 +44547,7 @@
         <v>3</v>
       </c>
       <c r="AV210">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW210">
         <v>4</v>
@@ -44559,7 +44559,7 @@
         <v>7</v>
       </c>
       <c r="AZ210">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA210">
         <v>6</v>
@@ -44741,13 +44741,13 @@
         <v>1.09</v>
       </c>
       <c r="AR211">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AS211">
         <v>1.29</v>
       </c>
       <c r="AT211">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AU211">
         <v>5</v>
@@ -44947,31 +44947,31 @@
         <v>2.08</v>
       </c>
       <c r="AR212">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AS212">
         <v>1.45</v>
       </c>
       <c r="AT212">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU212">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV212">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW212">
+        <v>5</v>
+      </c>
+      <c r="AX212">
+        <v>7</v>
+      </c>
+      <c r="AY212">
+        <v>10</v>
+      </c>
+      <c r="AZ212">
         <v>12</v>
-      </c>
-      <c r="AX212">
-        <v>12</v>
-      </c>
-      <c r="AY212">
-        <v>14</v>
-      </c>
-      <c r="AZ212">
-        <v>16</v>
       </c>
       <c r="BA212">
         <v>6</v>
@@ -45153,13 +45153,13 @@
         <v>1.82</v>
       </c>
       <c r="AR213">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AS213">
         <v>1.49</v>
       </c>
       <c r="AT213">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU213">
         <v>2</v>
@@ -45362,13 +45362,13 @@
         <v>1.58</v>
       </c>
       <c r="AS214">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AT214">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU214">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV214">
         <v>4</v>
@@ -45377,13 +45377,13 @@
         <v>5</v>
       </c>
       <c r="AX214">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY214">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ214">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA214">
         <v>4</v>
@@ -45580,16 +45580,16 @@
         <v>4</v>
       </c>
       <c r="AW215">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX215">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY215">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ215">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA215">
         <v>8</v>
@@ -45977,13 +45977,13 @@
         <v>0.73</v>
       </c>
       <c r="AR217">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS217">
         <v>1.4</v>
       </c>
       <c r="AT217">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AU217">
         <v>4</v>
@@ -45992,13 +45992,13 @@
         <v>5</v>
       </c>
       <c r="AW217">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX217">
         <v>8</v>
       </c>
       <c r="AY217">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ217">
         <v>13</v>
@@ -46186,28 +46186,28 @@
         <v>1.47</v>
       </c>
       <c r="AS218">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AT218">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AU218">
         <v>2</v>
       </c>
       <c r="AV218">
+        <v>9</v>
+      </c>
+      <c r="AW218">
+        <v>9</v>
+      </c>
+      <c r="AX218">
+        <v>12</v>
+      </c>
+      <c r="AY218">
         <v>11</v>
       </c>
-      <c r="AW218">
-        <v>20</v>
-      </c>
-      <c r="AX218">
-        <v>13</v>
-      </c>
-      <c r="AY218">
-        <v>22</v>
-      </c>
       <c r="AZ218">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA218">
         <v>6</v>
@@ -46389,13 +46389,13 @@
         <v>1.45</v>
       </c>
       <c r="AR219">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS219">
         <v>1.59</v>
       </c>
       <c r="AT219">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="AU219">
         <v>3</v>
@@ -46404,16 +46404,16 @@
         <v>6</v>
       </c>
       <c r="AW219">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX219">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY219">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ219">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA219">
         <v>7</v>
@@ -46598,10 +46598,10 @@
         <v>1.8</v>
       </c>
       <c r="AS220">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AT220">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="AU220">
         <v>7</v>
@@ -46610,13 +46610,13 @@
         <v>5</v>
       </c>
       <c r="AW220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX220">
         <v>8</v>
       </c>
       <c r="AY220">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ220">
         <v>13</v>
@@ -46801,13 +46801,13 @@
         <v>0.92</v>
       </c>
       <c r="AR221">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AS221">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AT221">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AU221">
         <v>7</v>
@@ -47010,10 +47010,10 @@
         <v>1.62</v>
       </c>
       <c r="AS222">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AT222">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="AU222">
         <v>4</v>
@@ -47625,13 +47625,13 @@
         <v>0.67</v>
       </c>
       <c r="AR225">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AS225">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AT225">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU225">
         <v>5</v>
@@ -47831,13 +47831,13 @@
         <v>1</v>
       </c>
       <c r="AR226">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AS226">
         <v>1.11</v>
       </c>
       <c r="AT226">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AU226">
         <v>2</v>
@@ -48037,13 +48037,13 @@
         <v>1.36</v>
       </c>
       <c r="AR227">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AS227">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AT227">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AU227">
         <v>7</v>
@@ -48243,13 +48243,13 @@
         <v>0.92</v>
       </c>
       <c r="AR228">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AS228">
         <v>1.23</v>
       </c>
       <c r="AT228">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AU228">
         <v>3</v>
@@ -48449,13 +48449,13 @@
         <v>0.73</v>
       </c>
       <c r="AR229">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AS229">
         <v>1.4</v>
       </c>
       <c r="AT229">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU229">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -40633,19 +40633,19 @@
         <v>4</v>
       </c>
       <c r="AV191">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW191">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AX191">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY191">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AZ191">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41048,16 +41048,16 @@
         <v>4</v>
       </c>
       <c r="AW193">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AX193">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY193">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AZ193">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA193">
         <v>12</v>
@@ -41660,22 +41660,22 @@
         <v>2.84</v>
       </c>
       <c r="AU196">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV196">
         <v>6</v>
       </c>
       <c r="AW196">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX196">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY196">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AZ196">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -42278,22 +42278,22 @@
         <v>2.96</v>
       </c>
       <c r="AU199">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV199">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW199">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX199">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY199">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ199">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA199">
         <v>1</v>
@@ -42490,16 +42490,16 @@
         <v>4</v>
       </c>
       <c r="AW200">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX200">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY200">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ200">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA200">
         <v>3</v>
@@ -42690,22 +42690,22 @@
         <v>2.68</v>
       </c>
       <c r="AU201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV201">
         <v>3</v>
       </c>
       <c r="AW201">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX201">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY201">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ201">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA201">
         <v>2</v>
@@ -43102,22 +43102,22 @@
         <v>2.93</v>
       </c>
       <c r="AU203">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW203">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX203">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY203">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ203">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA203">
         <v>7</v>
@@ -43514,16 +43514,16 @@
         <v>2.68</v>
       </c>
       <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
         <v>6</v>
       </c>
-      <c r="AV205">
-        <v>7</v>
-      </c>
       <c r="AW205">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX205">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY205">
         <v>15</v>
@@ -43720,22 +43720,22 @@
         <v>3.1</v>
       </c>
       <c r="AU206">
+        <v>2</v>
+      </c>
+      <c r="AV206">
+        <v>2</v>
+      </c>
+      <c r="AW206">
+        <v>1</v>
+      </c>
+      <c r="AX206">
+        <v>4</v>
+      </c>
+      <c r="AY206">
         <v>3</v>
       </c>
-      <c r="AV206">
-        <v>2</v>
-      </c>
-      <c r="AW206">
+      <c r="AZ206">
         <v>6</v>
-      </c>
-      <c r="AX206">
-        <v>5</v>
-      </c>
-      <c r="AY206">
-        <v>9</v>
-      </c>
-      <c r="AZ206">
-        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
@@ -43920,10 +43920,10 @@
         <v>1.3</v>
       </c>
       <c r="AS207">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AT207">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU207">
         <v>2</v>
@@ -44338,22 +44338,22 @@
         <v>2.8</v>
       </c>
       <c r="AU209">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV209">
         <v>7</v>
       </c>
       <c r="AW209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX209">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY209">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ209">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA209">
         <v>2</v>
@@ -44547,7 +44547,7 @@
         <v>3</v>
       </c>
       <c r="AV210">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW210">
         <v>4</v>
@@ -44559,7 +44559,7 @@
         <v>7</v>
       </c>
       <c r="AZ210">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA210">
         <v>6</v>
@@ -44741,13 +44741,13 @@
         <v>1.09</v>
       </c>
       <c r="AR211">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AS211">
         <v>1.29</v>
       </c>
       <c r="AT211">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AU211">
         <v>5</v>
@@ -44947,31 +44947,31 @@
         <v>2.08</v>
       </c>
       <c r="AR212">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AS212">
         <v>1.45</v>
       </c>
       <c r="AT212">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="AU212">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW212">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX212">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY212">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ212">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA212">
         <v>6</v>
@@ -45153,13 +45153,13 @@
         <v>1.82</v>
       </c>
       <c r="AR213">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AS213">
         <v>1.49</v>
       </c>
       <c r="AT213">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="AU213">
         <v>2</v>
@@ -45362,13 +45362,13 @@
         <v>1.58</v>
       </c>
       <c r="AS214">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AT214">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU214">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV214">
         <v>4</v>
@@ -45377,13 +45377,13 @@
         <v>5</v>
       </c>
       <c r="AX214">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY214">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ214">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA214">
         <v>4</v>
@@ -45580,16 +45580,16 @@
         <v>4</v>
       </c>
       <c r="AW215">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX215">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY215">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ215">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA215">
         <v>8</v>
@@ -45977,13 +45977,13 @@
         <v>0.73</v>
       </c>
       <c r="AR217">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AS217">
         <v>1.4</v>
       </c>
       <c r="AT217">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="AU217">
         <v>4</v>
@@ -45992,13 +45992,13 @@
         <v>5</v>
       </c>
       <c r="AW217">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX217">
         <v>8</v>
       </c>
       <c r="AY217">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ217">
         <v>13</v>
@@ -46186,28 +46186,28 @@
         <v>1.47</v>
       </c>
       <c r="AS218">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AT218">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AU218">
         <v>2</v>
       </c>
       <c r="AV218">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW218">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX218">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY218">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AZ218">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA218">
         <v>6</v>
@@ -46389,13 +46389,13 @@
         <v>1.45</v>
       </c>
       <c r="AR219">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS219">
         <v>1.59</v>
       </c>
       <c r="AT219">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="AU219">
         <v>3</v>
@@ -46404,16 +46404,16 @@
         <v>6</v>
       </c>
       <c r="AW219">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX219">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY219">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ219">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA219">
         <v>7</v>
@@ -46598,10 +46598,10 @@
         <v>1.8</v>
       </c>
       <c r="AS220">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AT220">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="AU220">
         <v>7</v>
@@ -46801,13 +46801,13 @@
         <v>0.92</v>
       </c>
       <c r="AR221">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS221">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AT221">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AU221">
         <v>7</v>
@@ -47010,10 +47010,10 @@
         <v>1.62</v>
       </c>
       <c r="AS222">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AT222">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="AU222">
         <v>4</v>
@@ -47625,13 +47625,13 @@
         <v>0.67</v>
       </c>
       <c r="AR225">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AS225">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AT225">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU225">
         <v>5</v>
@@ -47831,13 +47831,13 @@
         <v>1</v>
       </c>
       <c r="AR226">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AS226">
         <v>1.11</v>
       </c>
       <c r="AT226">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AU226">
         <v>2</v>
@@ -48037,13 +48037,13 @@
         <v>1.36</v>
       </c>
       <c r="AR227">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AS227">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT227">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AU227">
         <v>7</v>
@@ -48243,13 +48243,13 @@
         <v>0.92</v>
       </c>
       <c r="AR228">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AS228">
         <v>1.23</v>
       </c>
       <c r="AT228">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AU228">
         <v>3</v>
@@ -48449,13 +48449,13 @@
         <v>0.73</v>
       </c>
       <c r="AR229">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AS229">
         <v>1.4</v>
       </c>
       <c r="AT229">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU229">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -47025,13 +47025,13 @@
         <v>4</v>
       </c>
       <c r="AX222">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY222">
         <v>8</v>
       </c>
       <c r="AZ222">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA222">
         <v>5</v>
@@ -47428,7 +47428,7 @@
         <v>3.45</v>
       </c>
       <c r="AU224">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV224">
         <v>5</v>
@@ -47440,7 +47440,7 @@
         <v>4</v>
       </c>
       <c r="AY224">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ224">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,12 @@
     <t>['45+4', '58']</t>
   </si>
   <si>
+    <t>['6', '66', '88']</t>
+  </si>
+  <si>
+    <t>['14', '42', '89']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -986,6 +992,12 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['15', '20']</t>
+  </si>
+  <si>
+    <t>['6', '47', '73']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1615,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1684,7 +1696,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2096,7 +2108,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ4">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3123,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
         <v>1.36</v>
@@ -3251,7 +3263,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3457,7 +3469,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3663,7 +3675,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3869,7 +3881,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4568,7 +4580,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ16">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4693,7 +4705,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4899,7 +4911,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5183,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>2</v>
@@ -5723,7 +5735,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -6135,7 +6147,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6625,10 +6637,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ26">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR26">
         <v>2</v>
@@ -6753,7 +6765,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6959,7 +6971,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7243,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -7371,7 +7383,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7452,7 +7464,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>1.39</v>
@@ -7783,7 +7795,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8401,7 +8413,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8607,7 +8619,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8813,7 +8825,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8894,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
         <v>0</v>
@@ -9019,7 +9031,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9637,7 +9649,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10049,7 +10061,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10539,7 +10551,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10667,7 +10679,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10873,7 +10885,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -11079,7 +11091,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11572,7 +11584,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ50">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR50">
         <v>1.21</v>
@@ -11903,7 +11915,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12315,7 +12327,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -13220,7 +13232,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ58">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR58">
         <v>1.91</v>
@@ -13345,7 +13357,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13423,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
         <v>1.82</v>
@@ -13551,7 +13563,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13632,7 +13644,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR60">
         <v>1.95</v>
@@ -14375,7 +14387,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -15199,7 +15211,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15405,7 +15417,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15483,7 +15495,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>1.45</v>
@@ -15817,7 +15829,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -17053,7 +17065,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17465,7 +17477,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -18164,7 +18176,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ82">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -18289,7 +18301,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18907,7 +18919,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19319,7 +19331,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19397,7 +19409,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ88">
         <v>0.75</v>
@@ -19606,7 +19618,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ89">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19731,7 +19743,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20015,7 +20027,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>2.08</v>
@@ -20143,7 +20155,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20761,7 +20773,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21585,7 +21597,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21666,7 +21678,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ99">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21997,7 +22009,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22203,7 +22215,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22409,7 +22421,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22615,7 +22627,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -23027,7 +23039,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23233,7 +23245,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23439,7 +23451,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -24057,7 +24069,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24135,7 +24147,7 @@
         <v>1.8</v>
       </c>
       <c r="AP111">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
         <v>2.08</v>
@@ -24756,7 +24768,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ114">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.46</v>
@@ -24881,7 +24893,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25087,7 +25099,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25989,7 +26001,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26117,7 +26129,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26323,7 +26335,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26401,7 +26413,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>0.92</v>
@@ -26529,7 +26541,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26735,7 +26747,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27147,7 +27159,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27637,7 +27649,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27765,7 +27777,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -28177,7 +28189,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28383,7 +28395,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29413,7 +29425,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29494,7 +29506,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ137">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR137">
         <v>1.5</v>
@@ -29619,7 +29631,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29700,7 +29712,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ138">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.72</v>
@@ -30031,7 +30043,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30855,7 +30867,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31139,7 +31151,7 @@
         <v>0.8</v>
       </c>
       <c r="AP145">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ145">
         <v>1.67</v>
@@ -31551,7 +31563,7 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147">
         <v>1.82</v>
@@ -31885,7 +31897,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32297,7 +32309,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32503,7 +32515,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32584,7 +32596,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR152">
         <v>1.53</v>
@@ -33121,7 +33133,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33327,7 +33339,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33533,7 +33545,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33739,7 +33751,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33945,7 +33957,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34563,7 +34575,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -35053,7 +35065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP164">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164">
         <v>0.5</v>
@@ -35181,7 +35193,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35468,7 +35480,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ166">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR166">
         <v>1.66</v>
@@ -35799,7 +35811,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -35880,7 +35892,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ168">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR168">
         <v>1.69</v>
@@ -36005,7 +36017,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36498,7 +36510,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ171">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR171">
         <v>1.32</v>
@@ -36623,7 +36635,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -37447,7 +37459,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37859,7 +37871,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37937,7 +37949,7 @@
         <v>1.43</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ178">
         <v>1.67</v>
@@ -38065,7 +38077,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38352,7 +38364,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ180">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38683,7 +38695,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -39095,7 +39107,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39301,7 +39313,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39507,7 +39519,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39919,7 +39931,7 @@
         <v>149</v>
       </c>
       <c r="P188" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39997,7 +40009,7 @@
         <v>0.63</v>
       </c>
       <c r="AP188">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ188">
         <v>1.09</v>
@@ -40125,7 +40137,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40537,7 +40549,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40615,7 +40627,7 @@
         <v>1.8</v>
       </c>
       <c r="AP191">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ191">
         <v>2</v>
@@ -40743,7 +40755,7 @@
         <v>91</v>
       </c>
       <c r="P192" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q192">
         <v>4</v>
@@ -41155,7 +41167,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41233,10 +41245,10 @@
         <v>1.1</v>
       </c>
       <c r="AP194">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ194">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR194">
         <v>1.44</v>
@@ -41567,7 +41579,7 @@
         <v>91</v>
       </c>
       <c r="P196" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41979,7 +41991,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q198">
         <v>3.3</v>
@@ -42391,7 +42403,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -42597,7 +42609,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42803,7 +42815,7 @@
         <v>220</v>
       </c>
       <c r="P202" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q202">
         <v>2.65</v>
@@ -43009,7 +43021,7 @@
         <v>221</v>
       </c>
       <c r="P203" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q203">
         <v>2.7</v>
@@ -43215,7 +43227,7 @@
         <v>167</v>
       </c>
       <c r="P204" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43421,7 +43433,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43627,7 +43639,7 @@
         <v>95</v>
       </c>
       <c r="P206" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q206">
         <v>2.8</v>
@@ -43833,7 +43845,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -44451,7 +44463,7 @@
         <v>91</v>
       </c>
       <c r="P210" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q210">
         <v>2.92</v>
@@ -44657,7 +44669,7 @@
         <v>224</v>
       </c>
       <c r="P211" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q211">
         <v>2.5</v>
@@ -44863,7 +44875,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q212">
         <v>3.5</v>
@@ -45275,7 +45287,7 @@
         <v>225</v>
       </c>
       <c r="P214" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q214">
         <v>3.18</v>
@@ -45481,7 +45493,7 @@
         <v>128</v>
       </c>
       <c r="P215" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q215">
         <v>2.7</v>
@@ -45687,7 +45699,7 @@
         <v>226</v>
       </c>
       <c r="P216" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -45765,7 +45777,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP216">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ216">
         <v>0.5</v>
@@ -45971,7 +45983,7 @@
         <v>0.44</v>
       </c>
       <c r="AP217">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ217">
         <v>0.73</v>
@@ -46099,7 +46111,7 @@
         <v>91</v>
       </c>
       <c r="P218" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46923,7 +46935,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q222">
         <v>4.95</v>
@@ -47541,7 +47553,7 @@
         <v>231</v>
       </c>
       <c r="P225" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q225">
         <v>2.75</v>
@@ -48522,6 +48534,418 @@
       </c>
       <c r="BP229">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7778304</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F230">
+        <v>24</v>
+      </c>
+      <c r="G230" t="s">
+        <v>85</v>
+      </c>
+      <c r="H230" t="s">
+        <v>89</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>2</v>
+      </c>
+      <c r="K230">
+        <v>3</v>
+      </c>
+      <c r="L230">
+        <v>3</v>
+      </c>
+      <c r="M230">
+        <v>2</v>
+      </c>
+      <c r="N230">
+        <v>5</v>
+      </c>
+      <c r="O230" t="s">
+        <v>233</v>
+      </c>
+      <c r="P230" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q230">
+        <v>3.2</v>
+      </c>
+      <c r="R230">
+        <v>2.05</v>
+      </c>
+      <c r="S230">
+        <v>3.2</v>
+      </c>
+      <c r="T230">
+        <v>1.4</v>
+      </c>
+      <c r="U230">
+        <v>2.75</v>
+      </c>
+      <c r="V230">
+        <v>2.8</v>
+      </c>
+      <c r="W230">
+        <v>1.38</v>
+      </c>
+      <c r="X230">
+        <v>7</v>
+      </c>
+      <c r="Y230">
+        <v>1.08</v>
+      </c>
+      <c r="Z230">
+        <v>2.4</v>
+      </c>
+      <c r="AA230">
+        <v>3.26</v>
+      </c>
+      <c r="AB230">
+        <v>2.52</v>
+      </c>
+      <c r="AC230">
+        <v>1.06</v>
+      </c>
+      <c r="AD230">
+        <v>8.5</v>
+      </c>
+      <c r="AE230">
+        <v>1.3</v>
+      </c>
+      <c r="AF230">
+        <v>3.35</v>
+      </c>
+      <c r="AG230">
+        <v>1.87</v>
+      </c>
+      <c r="AH230">
+        <v>1.83</v>
+      </c>
+      <c r="AI230">
+        <v>1.7</v>
+      </c>
+      <c r="AJ230">
+        <v>2</v>
+      </c>
+      <c r="AK230">
+        <v>1.48</v>
+      </c>
+      <c r="AL230">
+        <v>1.28</v>
+      </c>
+      <c r="AM230">
+        <v>1.48</v>
+      </c>
+      <c r="AN230">
+        <v>1.36</v>
+      </c>
+      <c r="AO230">
+        <v>0.9</v>
+      </c>
+      <c r="AP230">
+        <v>1.5</v>
+      </c>
+      <c r="AQ230">
+        <v>0.82</v>
+      </c>
+      <c r="AR230">
+        <v>1.44</v>
+      </c>
+      <c r="AS230">
+        <v>1.45</v>
+      </c>
+      <c r="AT230">
+        <v>2.89</v>
+      </c>
+      <c r="AU230">
+        <v>6</v>
+      </c>
+      <c r="AV230">
+        <v>5</v>
+      </c>
+      <c r="AW230">
+        <v>11</v>
+      </c>
+      <c r="AX230">
+        <v>5</v>
+      </c>
+      <c r="AY230">
+        <v>17</v>
+      </c>
+      <c r="AZ230">
+        <v>10</v>
+      </c>
+      <c r="BA230">
+        <v>6</v>
+      </c>
+      <c r="BB230">
+        <v>4</v>
+      </c>
+      <c r="BC230">
+        <v>10</v>
+      </c>
+      <c r="BD230">
+        <v>2.08</v>
+      </c>
+      <c r="BE230">
+        <v>8.5</v>
+      </c>
+      <c r="BF230">
+        <v>2.08</v>
+      </c>
+      <c r="BG230">
+        <v>1.32</v>
+      </c>
+      <c r="BH230">
+        <v>2.95</v>
+      </c>
+      <c r="BI230">
+        <v>1.54</v>
+      </c>
+      <c r="BJ230">
+        <v>2.2</v>
+      </c>
+      <c r="BK230">
+        <v>1.95</v>
+      </c>
+      <c r="BL230">
+        <v>1.85</v>
+      </c>
+      <c r="BM230">
+        <v>2.4</v>
+      </c>
+      <c r="BN230">
+        <v>1.47</v>
+      </c>
+      <c r="BO230">
+        <v>3.1</v>
+      </c>
+      <c r="BP230">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7778307</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F231">
+        <v>24</v>
+      </c>
+      <c r="G231" t="s">
+        <v>77</v>
+      </c>
+      <c r="H231" t="s">
+        <v>84</v>
+      </c>
+      <c r="I231">
+        <v>2</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>3</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>3</v>
+      </c>
+      <c r="N231">
+        <v>6</v>
+      </c>
+      <c r="O231" t="s">
+        <v>234</v>
+      </c>
+      <c r="P231" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q231">
+        <v>3.35</v>
+      </c>
+      <c r="R231">
+        <v>2.15</v>
+      </c>
+      <c r="S231">
+        <v>2.8</v>
+      </c>
+      <c r="T231">
+        <v>1.33</v>
+      </c>
+      <c r="U231">
+        <v>3</v>
+      </c>
+      <c r="V231">
+        <v>2.45</v>
+      </c>
+      <c r="W231">
+        <v>1.48</v>
+      </c>
+      <c r="X231">
+        <v>6</v>
+      </c>
+      <c r="Y231">
+        <v>1.12</v>
+      </c>
+      <c r="Z231">
+        <v>2.74</v>
+      </c>
+      <c r="AA231">
+        <v>3.41</v>
+      </c>
+      <c r="AB231">
+        <v>2.16</v>
+      </c>
+      <c r="AC231">
+        <v>1.05</v>
+      </c>
+      <c r="AD231">
+        <v>9.5</v>
+      </c>
+      <c r="AE231">
+        <v>1.25</v>
+      </c>
+      <c r="AF231">
+        <v>3.95</v>
+      </c>
+      <c r="AG231">
+        <v>1.76</v>
+      </c>
+      <c r="AH231">
+        <v>1.94</v>
+      </c>
+      <c r="AI231">
+        <v>1.55</v>
+      </c>
+      <c r="AJ231">
+        <v>2.25</v>
+      </c>
+      <c r="AK231">
+        <v>1.57</v>
+      </c>
+      <c r="AL231">
+        <v>1.25</v>
+      </c>
+      <c r="AM231">
+        <v>1.4</v>
+      </c>
+      <c r="AN231">
+        <v>1.09</v>
+      </c>
+      <c r="AO231">
+        <v>1.09</v>
+      </c>
+      <c r="AP231">
+        <v>1.08</v>
+      </c>
+      <c r="AQ231">
+        <v>1.08</v>
+      </c>
+      <c r="AR231">
+        <v>1.42</v>
+      </c>
+      <c r="AS231">
+        <v>1.47</v>
+      </c>
+      <c r="AT231">
+        <v>2.89</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>8</v>
+      </c>
+      <c r="AW231">
+        <v>4</v>
+      </c>
+      <c r="AX231">
+        <v>7</v>
+      </c>
+      <c r="AY231">
+        <v>11</v>
+      </c>
+      <c r="AZ231">
+        <v>15</v>
+      </c>
+      <c r="BA231">
+        <v>4</v>
+      </c>
+      <c r="BB231">
+        <v>7</v>
+      </c>
+      <c r="BC231">
+        <v>11</v>
+      </c>
+      <c r="BD231">
+        <v>1.91</v>
+      </c>
+      <c r="BE231">
+        <v>8.5</v>
+      </c>
+      <c r="BF231">
+        <v>2.28</v>
+      </c>
+      <c r="BG231">
+        <v>1.21</v>
+      </c>
+      <c r="BH231">
+        <v>3.7</v>
+      </c>
+      <c r="BI231">
+        <v>1.38</v>
+      </c>
+      <c r="BJ231">
+        <v>2.7</v>
+      </c>
+      <c r="BK231">
+        <v>1.61</v>
+      </c>
+      <c r="BL231">
+        <v>2.1</v>
+      </c>
+      <c r="BM231">
+        <v>1.95</v>
+      </c>
+      <c r="BN231">
+        <v>1.7</v>
+      </c>
+      <c r="BO231">
+        <v>2.45</v>
+      </c>
+      <c r="BP231">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -670,10 +670,10 @@
     <t>['44', '45+2']</t>
   </si>
   <si>
-    <t>['6', '34']</t>
+    <t>['9', '16', '45']</t>
   </si>
   <si>
-    <t>['9', '16', '45']</t>
+    <t>['6', '34']</t>
   </si>
   <si>
     <t>['20', '62']</t>
@@ -691,13 +691,13 @@
     <t>['18']</t>
   </si>
   <si>
-    <t>['17', '25', '52']</t>
-  </si>
-  <si>
     <t>['85', '90+14']</t>
   </si>
   <si>
     <t>['41']</t>
+  </si>
+  <si>
+    <t>['17', '25', '52']</t>
   </si>
   <si>
     <t>['66']</t>
@@ -706,13 +706,13 @@
     <t>['14', '75', '90+4']</t>
   </si>
   <si>
-    <t>['14', '48', '76', '90+3']</t>
+    <t>['45+4', '58']</t>
   </si>
   <si>
     <t>['34', '45+5']</t>
   </si>
   <si>
-    <t>['45+4', '58']</t>
+    <t>['14', '48', '76', '90+3']</t>
   </si>
   <si>
     <t>['6', '66', '88']</t>
@@ -946,10 +946,10 @@
     <t>['41', '71']</t>
   </si>
   <si>
-    <t>['27', '45+1', '90+3']</t>
+    <t>['69']</t>
   </si>
   <si>
-    <t>['69']</t>
+    <t>['27', '45+1', '90+3']</t>
   </si>
   <si>
     <t>['4', '36']</t>
@@ -958,16 +958,16 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
     <t>['24', '53', '84']</t>
   </si>
   <si>
     <t>['10', '52']</t>
-  </si>
-  <si>
-    <t>['17']</t>
-  </si>
-  <si>
-    <t>['88']</t>
   </si>
   <si>
     <t>['17', '23', '39', '75']</t>
@@ -40713,7 +40713,7 @@
         <v>191</v>
       </c>
       <c r="B192">
-        <v>7778266</v>
+        <v>7778263</v>
       </c>
       <c r="C192" t="s">
         <v>68</v>
@@ -40728,55 +40728,55 @@
         <v>20</v>
       </c>
       <c r="G192" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H192" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I192">
         <v>0</v>
       </c>
       <c r="J192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M192">
         <v>1</v>
       </c>
       <c r="N192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O192" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="P192" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="Q192">
         <v>4</v>
       </c>
       <c r="R192">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S192">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T192">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U192">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V192">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="W192">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X192">
         <v>9</v>
@@ -40785,13 +40785,13 @@
         <v>1.07</v>
       </c>
       <c r="Z192">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AA192">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="AB192">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC192">
         <v>1.07</v>
@@ -40806,112 +40806,112 @@
         <v>3</v>
       </c>
       <c r="AG192">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH192">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AI192">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ192">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK192">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL192">
         <v>1.28</v>
       </c>
       <c r="AM192">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN192">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AO192">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AP192">
-        <v>1.08</v>
+        <v>2.17</v>
       </c>
       <c r="AQ192">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR192">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AS192">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AT192">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="AU192">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW192">
+        <v>13</v>
+      </c>
+      <c r="AX192">
         <v>5</v>
       </c>
-      <c r="AX192">
-        <v>3</v>
-      </c>
       <c r="AY192">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AZ192">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA192">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BB192">
         <v>3</v>
       </c>
       <c r="BC192">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BD192">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="BE192">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF192">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="BG192">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BH192">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BI192">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="BJ192">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="BK192">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="BL192">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BM192">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="BN192">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO192">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BP192">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="193" spans="1:68">
@@ -40919,7 +40919,7 @@
         <v>192</v>
       </c>
       <c r="B193">
-        <v>7778263</v>
+        <v>7778266</v>
       </c>
       <c r="C193" t="s">
         <v>68</v>
@@ -40934,55 +40934,55 @@
         <v>20</v>
       </c>
       <c r="G193" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H193" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I193">
         <v>0</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193">
         <v>1</v>
       </c>
       <c r="N193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193" t="s">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="P193" t="s">
-        <v>162</v>
+        <v>266</v>
       </c>
       <c r="Q193">
         <v>4</v>
       </c>
       <c r="R193">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S193">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T193">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U193">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V193">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="W193">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X193">
         <v>9</v>
@@ -40991,13 +40991,13 @@
         <v>1.07</v>
       </c>
       <c r="Z193">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="AA193">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AB193">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC193">
         <v>1.07</v>
@@ -41012,112 +41012,112 @@
         <v>3</v>
       </c>
       <c r="AG193">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH193">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AI193">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ193">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AK193">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL193">
         <v>1.28</v>
       </c>
       <c r="AM193">
+        <v>1.28</v>
+      </c>
+      <c r="AN193">
+        <v>1.4</v>
+      </c>
+      <c r="AO193">
+        <v>1.44</v>
+      </c>
+      <c r="AP193">
+        <v>1.08</v>
+      </c>
+      <c r="AQ193">
+        <v>1.45</v>
+      </c>
+      <c r="AR193">
         <v>1.3</v>
       </c>
-      <c r="AN193">
-        <v>2.5</v>
-      </c>
-      <c r="AO193">
-        <v>1.63</v>
-      </c>
-      <c r="AP193">
-        <v>2.17</v>
-      </c>
-      <c r="AQ193">
-        <v>1.67</v>
-      </c>
-      <c r="AR193">
+      <c r="AS193">
         <v>1.59</v>
       </c>
-      <c r="AS193">
-        <v>1.64</v>
-      </c>
       <c r="AT193">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="AU193">
+        <v>2</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
         <v>5</v>
       </c>
-      <c r="AV193">
-        <v>4</v>
-      </c>
-      <c r="AW193">
-        <v>13</v>
-      </c>
       <c r="AX193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY193">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA193">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="BB193">
         <v>3</v>
       </c>
       <c r="BC193">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BD193">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="BE193">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF193">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="BG193">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BH193">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BI193">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="BJ193">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BK193">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BL193">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="BM193">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="BN193">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BO193">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP193">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="194" spans="1:68">
@@ -41537,7 +41537,7 @@
         <v>195</v>
       </c>
       <c r="B196">
-        <v>7778265</v>
+        <v>7778270</v>
       </c>
       <c r="C196" t="s">
         <v>68</v>
@@ -41552,160 +41552,160 @@
         <v>20</v>
       </c>
       <c r="G196" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H196" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K196">
         <v>2</v>
       </c>
       <c r="L196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N196">
         <v>3</v>
       </c>
       <c r="O196" t="s">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="P196" t="s">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="Q196">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R196">
         <v>1.95</v>
       </c>
       <c r="S196">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="T196">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U196">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V196">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="W196">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X196">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="Y196">
         <v>1.05</v>
       </c>
       <c r="Z196">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="AA196">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="AB196">
-        <v>2.39</v>
+        <v>4</v>
       </c>
       <c r="AC196">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AD196">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="AE196">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AF196">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AG196">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AH196">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AI196">
         <v>2.1</v>
       </c>
       <c r="AJ196">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AK196">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AL196">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AM196">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AN196">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO196">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="AP196">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="AQ196">
-        <v>2.08</v>
+        <v>0.75</v>
       </c>
       <c r="AR196">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AS196">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT196">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AU196">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV196">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW196">
+        <v>10</v>
+      </c>
+      <c r="AX196">
+        <v>5</v>
+      </c>
+      <c r="AY196">
+        <v>15</v>
+      </c>
+      <c r="AZ196">
+        <v>10</v>
+      </c>
+      <c r="BA196">
         <v>9</v>
       </c>
-      <c r="AX196">
-        <v>6</v>
-      </c>
-      <c r="AY196">
-        <v>9</v>
-      </c>
-      <c r="AZ196">
+      <c r="BB196">
+        <v>3</v>
+      </c>
+      <c r="BC196">
         <v>12</v>
       </c>
-      <c r="BA196">
-        <v>3</v>
-      </c>
-      <c r="BB196">
-        <v>5</v>
-      </c>
-      <c r="BC196">
-        <v>8</v>
-      </c>
       <c r="BD196">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="BE196">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF196">
-        <v>2.11</v>
+        <v>2.85</v>
       </c>
       <c r="BG196">
         <v>1.24</v>
@@ -41714,16 +41714,16 @@
         <v>3.34</v>
       </c>
       <c r="BI196">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BJ196">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BK196">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BL196">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BM196">
         <v>2.34</v>
@@ -41743,7 +41743,7 @@
         <v>196</v>
       </c>
       <c r="B197">
-        <v>7778270</v>
+        <v>7778271</v>
       </c>
       <c r="C197" t="s">
         <v>68</v>
@@ -41758,190 +41758,190 @@
         <v>20</v>
       </c>
       <c r="G197" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H197" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I197">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J197">
         <v>0</v>
       </c>
       <c r="K197">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L197">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M197">
         <v>1</v>
       </c>
       <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>91</v>
+      </c>
+      <c r="P197" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q197">
+        <v>3.3</v>
+      </c>
+      <c r="R197">
+        <v>1.75</v>
+      </c>
+      <c r="S197">
+        <v>4</v>
+      </c>
+      <c r="T197">
+        <v>1.66</v>
+      </c>
+      <c r="U197">
+        <v>2.05</v>
+      </c>
+      <c r="V197">
+        <v>4</v>
+      </c>
+      <c r="W197">
+        <v>1.21</v>
+      </c>
+      <c r="X197">
+        <v>12.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.02</v>
+      </c>
+      <c r="Z197">
+        <v>2.42</v>
+      </c>
+      <c r="AA197">
+        <v>2.61</v>
+      </c>
+      <c r="AB197">
+        <v>3.08</v>
+      </c>
+      <c r="AC197">
+        <v>1.14</v>
+      </c>
+      <c r="AD197">
+        <v>5</v>
+      </c>
+      <c r="AE197">
+        <v>1.6</v>
+      </c>
+      <c r="AF197">
+        <v>2.1</v>
+      </c>
+      <c r="AG197">
+        <v>2.92</v>
+      </c>
+      <c r="AH197">
+        <v>1.34</v>
+      </c>
+      <c r="AI197">
+        <v>2.3</v>
+      </c>
+      <c r="AJ197">
+        <v>1.53</v>
+      </c>
+      <c r="AK197">
+        <v>1.33</v>
+      </c>
+      <c r="AL197">
+        <v>1.42</v>
+      </c>
+      <c r="AM197">
+        <v>1.49</v>
+      </c>
+      <c r="AN197">
+        <v>1.8</v>
+      </c>
+      <c r="AO197">
+        <v>1.11</v>
+      </c>
+      <c r="AP197">
+        <v>1.5</v>
+      </c>
+      <c r="AQ197">
+        <v>1.3</v>
+      </c>
+      <c r="AR197">
+        <v>1.62</v>
+      </c>
+      <c r="AS197">
+        <v>1.63</v>
+      </c>
+      <c r="AT197">
+        <v>3.25</v>
+      </c>
+      <c r="AU197">
+        <v>2</v>
+      </c>
+      <c r="AV197">
+        <v>4</v>
+      </c>
+      <c r="AW197">
+        <v>5</v>
+      </c>
+      <c r="AX197">
+        <v>12</v>
+      </c>
+      <c r="AY197">
+        <v>7</v>
+      </c>
+      <c r="AZ197">
+        <v>16</v>
+      </c>
+      <c r="BA197">
         <v>3</v>
       </c>
-      <c r="O197" t="s">
-        <v>217</v>
-      </c>
-      <c r="P197" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q197">
-        <v>2.6</v>
-      </c>
-      <c r="R197">
-        <v>1.95</v>
-      </c>
-      <c r="S197">
-        <v>4.5</v>
-      </c>
-      <c r="T197">
-        <v>1.5</v>
-      </c>
-      <c r="U197">
-        <v>2.4</v>
-      </c>
-      <c r="V197">
-        <v>3.3</v>
-      </c>
-      <c r="W197">
-        <v>1.29</v>
-      </c>
-      <c r="X197">
-        <v>9.25</v>
-      </c>
-      <c r="Y197">
-        <v>1.05</v>
-      </c>
-      <c r="Z197">
-        <v>1.83</v>
-      </c>
-      <c r="AA197">
-        <v>3.06</v>
-      </c>
-      <c r="AB197">
+      <c r="BB197">
         <v>4</v>
       </c>
-      <c r="AC197">
-        <v>1.09</v>
-      </c>
-      <c r="AD197">
-        <v>6.75</v>
-      </c>
-      <c r="AE197">
-        <v>1.43</v>
-      </c>
-      <c r="AF197">
-        <v>2.6</v>
-      </c>
-      <c r="AG197">
-        <v>2.13</v>
-      </c>
-      <c r="AH197">
-        <v>1.63</v>
-      </c>
-      <c r="AI197">
-        <v>2.1</v>
-      </c>
-      <c r="AJ197">
-        <v>1.65</v>
-      </c>
-      <c r="AK197">
-        <v>1.22</v>
-      </c>
-      <c r="AL197">
+      <c r="BC197">
+        <v>7</v>
+      </c>
+      <c r="BD197">
+        <v>1.86</v>
+      </c>
+      <c r="BE197">
+        <v>8.1</v>
+      </c>
+      <c r="BF197">
+        <v>2.31</v>
+      </c>
+      <c r="BG197">
+        <v>1.32</v>
+      </c>
+      <c r="BH197">
+        <v>2.98</v>
+      </c>
+      <c r="BI197">
+        <v>1.61</v>
+      </c>
+      <c r="BJ197">
+        <v>2.17</v>
+      </c>
+      <c r="BK197">
+        <v>2.01</v>
+      </c>
+      <c r="BL197">
+        <v>1.68</v>
+      </c>
+      <c r="BM197">
+        <v>2.62</v>
+      </c>
+      <c r="BN197">
+        <v>1.38</v>
+      </c>
+      <c r="BO197">
+        <v>2.9</v>
+      </c>
+      <c r="BP197">
         <v>1.33</v>
-      </c>
-      <c r="AM197">
-        <v>1.82</v>
-      </c>
-      <c r="AN197">
-        <v>1.56</v>
-      </c>
-      <c r="AO197">
-        <v>0.6</v>
-      </c>
-      <c r="AP197">
-        <v>1.92</v>
-      </c>
-      <c r="AQ197">
-        <v>0.75</v>
-      </c>
-      <c r="AR197">
-        <v>1.8</v>
-      </c>
-      <c r="AS197">
-        <v>1.25</v>
-      </c>
-      <c r="AT197">
-        <v>3.05</v>
-      </c>
-      <c r="AU197">
-        <v>5</v>
-      </c>
-      <c r="AV197">
-        <v>5</v>
-      </c>
-      <c r="AW197">
-        <v>10</v>
-      </c>
-      <c r="AX197">
-        <v>5</v>
-      </c>
-      <c r="AY197">
-        <v>15</v>
-      </c>
-      <c r="AZ197">
-        <v>10</v>
-      </c>
-      <c r="BA197">
-        <v>9</v>
-      </c>
-      <c r="BB197">
-        <v>3</v>
-      </c>
-      <c r="BC197">
-        <v>12</v>
-      </c>
-      <c r="BD197">
-        <v>1.59</v>
-      </c>
-      <c r="BE197">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF197">
-        <v>2.85</v>
-      </c>
-      <c r="BG197">
-        <v>1.24</v>
-      </c>
-      <c r="BH197">
-        <v>3.34</v>
-      </c>
-      <c r="BI197">
-        <v>1.48</v>
-      </c>
-      <c r="BJ197">
-        <v>2.4</v>
-      </c>
-      <c r="BK197">
-        <v>1.85</v>
-      </c>
-      <c r="BL197">
-        <v>1.85</v>
-      </c>
-      <c r="BM197">
-        <v>2.34</v>
-      </c>
-      <c r="BN197">
-        <v>1.5</v>
-      </c>
-      <c r="BO197">
-        <v>3.14</v>
-      </c>
-      <c r="BP197">
-        <v>1.27</v>
       </c>
     </row>
     <row r="198" spans="1:68">
@@ -41949,7 +41949,7 @@
         <v>197</v>
       </c>
       <c r="B198">
-        <v>7778271</v>
+        <v>7778265</v>
       </c>
       <c r="C198" t="s">
         <v>68</v>
@@ -41964,28 +41964,28 @@
         <v>20</v>
       </c>
       <c r="G198" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H198" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I198">
         <v>0</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L198">
         <v>0</v>
       </c>
       <c r="M198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O198" t="s">
         <v>91</v>
@@ -41994,160 +41994,160 @@
         <v>311</v>
       </c>
       <c r="Q198">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R198">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="S198">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T198">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="U198">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="V198">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W198">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X198">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y198">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z198">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="AA198">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="AB198">
-        <v>3.08</v>
+        <v>2.39</v>
       </c>
       <c r="AC198">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD198">
-        <v>5</v>
+        <v>6.86</v>
       </c>
       <c r="AE198">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AF198">
+        <v>2.3</v>
+      </c>
+      <c r="AG198">
+        <v>2.65</v>
+      </c>
+      <c r="AH198">
+        <v>1.41</v>
+      </c>
+      <c r="AI198">
         <v>2.1</v>
       </c>
-      <c r="AG198">
-        <v>2.92</v>
-      </c>
-      <c r="AH198">
-        <v>1.34</v>
-      </c>
-      <c r="AI198">
-        <v>2.3</v>
-      </c>
       <c r="AJ198">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AK198">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL198">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AM198">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AN198">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AO198">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="AP198">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ198">
-        <v>1.3</v>
+        <v>2.08</v>
       </c>
       <c r="AR198">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AS198">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AT198">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="AU198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV198">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW198">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX198">
+        <v>6</v>
+      </c>
+      <c r="AY198">
+        <v>9</v>
+      </c>
+      <c r="AZ198">
         <v>12</v>
-      </c>
-      <c r="AY198">
-        <v>7</v>
-      </c>
-      <c r="AZ198">
-        <v>16</v>
       </c>
       <c r="BA198">
         <v>3</v>
       </c>
       <c r="BB198">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC198">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD198">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="BE198">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="BF198">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="BG198">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="BH198">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="BI198">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="BJ198">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="BK198">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="BL198">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="BM198">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="BN198">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO198">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="BP198">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="199" spans="1:68">
@@ -42361,7 +42361,7 @@
         <v>199</v>
       </c>
       <c r="B200">
-        <v>7778274</v>
+        <v>7778281</v>
       </c>
       <c r="C200" t="s">
         <v>68</v>
@@ -42376,190 +42376,190 @@
         <v>21</v>
       </c>
       <c r="G200" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H200" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K200">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N200">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O200" t="s">
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="Q200">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R200">
+        <v>1.85</v>
+      </c>
+      <c r="S200">
+        <v>3.85</v>
+      </c>
+      <c r="T200">
+        <v>1.55</v>
+      </c>
+      <c r="U200">
+        <v>2.3</v>
+      </c>
+      <c r="V200">
+        <v>3.5</v>
+      </c>
+      <c r="W200">
+        <v>1.25</v>
+      </c>
+      <c r="X200">
+        <v>9</v>
+      </c>
+      <c r="Y200">
+        <v>1.01</v>
+      </c>
+      <c r="Z200">
+        <v>2.13</v>
+      </c>
+      <c r="AA200">
+        <v>2.84</v>
+      </c>
+      <c r="AB200">
+        <v>3.35</v>
+      </c>
+      <c r="AC200">
+        <v>1.11</v>
+      </c>
+      <c r="AD200">
+        <v>6.25</v>
+      </c>
+      <c r="AE200">
+        <v>1.5</v>
+      </c>
+      <c r="AF200">
+        <v>2.3</v>
+      </c>
+      <c r="AG200">
+        <v>2.6</v>
+      </c>
+      <c r="AH200">
+        <v>1.43</v>
+      </c>
+      <c r="AI200">
         <v>2.05</v>
       </c>
-      <c r="S200">
-        <v>3.8</v>
-      </c>
-      <c r="T200">
-        <v>1.44</v>
-      </c>
-      <c r="U200">
-        <v>2.6</v>
-      </c>
-      <c r="V200">
+      <c r="AJ200">
+        <v>1.67</v>
+      </c>
+      <c r="AK200">
+        <v>1.33</v>
+      </c>
+      <c r="AL200">
+        <v>1.33</v>
+      </c>
+      <c r="AM200">
+        <v>1.55</v>
+      </c>
+      <c r="AN200">
+        <v>1.3</v>
+      </c>
+      <c r="AO200">
+        <v>0.89</v>
+      </c>
+      <c r="AP200">
+        <v>1.42</v>
+      </c>
+      <c r="AQ200">
+        <v>0.67</v>
+      </c>
+      <c r="AR200">
+        <v>1.56</v>
+      </c>
+      <c r="AS200">
+        <v>1.12</v>
+      </c>
+      <c r="AT200">
+        <v>2.68</v>
+      </c>
+      <c r="AU200">
+        <v>6</v>
+      </c>
+      <c r="AV200">
         <v>3</v>
       </c>
-      <c r="W200">
-        <v>1.33</v>
-      </c>
-      <c r="X200">
-        <v>7.9</v>
-      </c>
-      <c r="Y200">
-        <v>1.02</v>
-      </c>
-      <c r="Z200">
-        <v>2</v>
-      </c>
-      <c r="AA200">
-        <v>3.38</v>
-      </c>
-      <c r="AB200">
-        <v>3.09</v>
-      </c>
-      <c r="AC200">
-        <v>1.07</v>
-      </c>
-      <c r="AD200">
-        <v>8</v>
-      </c>
-      <c r="AE200">
-        <v>1.38</v>
-      </c>
-      <c r="AF200">
-        <v>3</v>
-      </c>
-      <c r="AG200">
-        <v>2.17</v>
-      </c>
-      <c r="AH200">
-        <v>1.61</v>
-      </c>
-      <c r="AI200">
-        <v>1.85</v>
-      </c>
-      <c r="AJ200">
-        <v>1.8</v>
-      </c>
-      <c r="AK200">
-        <v>1.3</v>
-      </c>
-      <c r="AL200">
-        <v>1.25</v>
-      </c>
-      <c r="AM200">
-        <v>1.67</v>
-      </c>
-      <c r="AN200">
-        <v>0.78</v>
-      </c>
-      <c r="AO200">
-        <v>1.67</v>
-      </c>
-      <c r="AP200">
-        <v>1.18</v>
-      </c>
-      <c r="AQ200">
-        <v>1.36</v>
-      </c>
-      <c r="AR200">
-        <v>1.42</v>
-      </c>
-      <c r="AS200">
-        <v>1.52</v>
-      </c>
-      <c r="AT200">
-        <v>2.94</v>
-      </c>
-      <c r="AU200">
-        <v>7</v>
-      </c>
-      <c r="AV200">
+      <c r="AW200">
         <v>4</v>
-      </c>
-      <c r="AW200">
-        <v>7</v>
       </c>
       <c r="AX200">
         <v>7</v>
       </c>
       <c r="AY200">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ200">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA200">
+        <v>2</v>
+      </c>
+      <c r="BB200">
         <v>3</v>
       </c>
-      <c r="BB200">
-        <v>4</v>
-      </c>
       <c r="BC200">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD200">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="BE200">
         <v>6.4</v>
       </c>
       <c r="BF200">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="BG200">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BH200">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BI200">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BJ200">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BK200">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="BL200">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BM200">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BN200">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO200">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BP200">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="201" spans="1:68">
@@ -42567,7 +42567,7 @@
         <v>200</v>
       </c>
       <c r="B201">
-        <v>7778281</v>
+        <v>7778274</v>
       </c>
       <c r="C201" t="s">
         <v>68</v>
@@ -42582,190 +42582,190 @@
         <v>21</v>
       </c>
       <c r="G201" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H201" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>2</v>
+      </c>
+      <c r="L201">
+        <v>2</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
         <v>3</v>
-      </c>
-      <c r="J201">
-        <v>2</v>
-      </c>
-      <c r="K201">
-        <v>5</v>
-      </c>
-      <c r="L201">
-        <v>3</v>
-      </c>
-      <c r="M201">
-        <v>2</v>
-      </c>
-      <c r="N201">
-        <v>5</v>
       </c>
       <c r="O201" t="s">
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>312</v>
+        <v>246</v>
       </c>
       <c r="Q201">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R201">
+        <v>2.05</v>
+      </c>
+      <c r="S201">
+        <v>3.8</v>
+      </c>
+      <c r="T201">
+        <v>1.44</v>
+      </c>
+      <c r="U201">
+        <v>2.6</v>
+      </c>
+      <c r="V201">
+        <v>3</v>
+      </c>
+      <c r="W201">
+        <v>1.33</v>
+      </c>
+      <c r="X201">
+        <v>7.9</v>
+      </c>
+      <c r="Y201">
+        <v>1.02</v>
+      </c>
+      <c r="Z201">
+        <v>2</v>
+      </c>
+      <c r="AA201">
+        <v>3.38</v>
+      </c>
+      <c r="AB201">
+        <v>3.09</v>
+      </c>
+      <c r="AC201">
+        <v>1.07</v>
+      </c>
+      <c r="AD201">
+        <v>8</v>
+      </c>
+      <c r="AE201">
+        <v>1.38</v>
+      </c>
+      <c r="AF201">
+        <v>3</v>
+      </c>
+      <c r="AG201">
+        <v>2.17</v>
+      </c>
+      <c r="AH201">
+        <v>1.61</v>
+      </c>
+      <c r="AI201">
         <v>1.85</v>
       </c>
-      <c r="S201">
-        <v>3.85</v>
-      </c>
-      <c r="T201">
-        <v>1.55</v>
-      </c>
-      <c r="U201">
-        <v>2.3</v>
-      </c>
-      <c r="V201">
-        <v>3.5</v>
-      </c>
-      <c r="W201">
+      <c r="AJ201">
+        <v>1.8</v>
+      </c>
+      <c r="AK201">
+        <v>1.3</v>
+      </c>
+      <c r="AL201">
         <v>1.25</v>
       </c>
-      <c r="X201">
-        <v>9</v>
-      </c>
-      <c r="Y201">
-        <v>1.01</v>
-      </c>
-      <c r="Z201">
-        <v>2.13</v>
-      </c>
-      <c r="AA201">
-        <v>2.84</v>
-      </c>
-      <c r="AB201">
-        <v>3.35</v>
-      </c>
-      <c r="AC201">
-        <v>1.11</v>
-      </c>
-      <c r="AD201">
-        <v>6.25</v>
-      </c>
-      <c r="AE201">
-        <v>1.5</v>
-      </c>
-      <c r="AF201">
-        <v>2.3</v>
-      </c>
-      <c r="AG201">
-        <v>2.6</v>
-      </c>
-      <c r="AH201">
-        <v>1.43</v>
-      </c>
-      <c r="AI201">
-        <v>2.05</v>
-      </c>
-      <c r="AJ201">
+      <c r="AM201">
         <v>1.67</v>
       </c>
-      <c r="AK201">
-        <v>1.33</v>
-      </c>
-      <c r="AL201">
-        <v>1.33</v>
-      </c>
-      <c r="AM201">
-        <v>1.55</v>
-      </c>
       <c r="AN201">
-        <v>1.3</v>
+        <v>0.78</v>
       </c>
       <c r="AO201">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="AP201">
+        <v>1.18</v>
+      </c>
+      <c r="AQ201">
+        <v>1.36</v>
+      </c>
+      <c r="AR201">
         <v>1.42</v>
       </c>
-      <c r="AQ201">
-        <v>0.67</v>
-      </c>
-      <c r="AR201">
-        <v>1.56</v>
-      </c>
       <c r="AS201">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AT201">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="AU201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV201">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW201">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX201">
         <v>7</v>
       </c>
       <c r="AY201">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ201">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA201">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB201">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC201">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD201">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BE201">
         <v>6.4</v>
       </c>
       <c r="BF201">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="BG201">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BH201">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BI201">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="BJ201">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BK201">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BL201">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BM201">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BN201">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO201">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BP201">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="202" spans="1:68">
@@ -42979,7 +42979,7 @@
         <v>202</v>
       </c>
       <c r="B203">
-        <v>7778273</v>
+        <v>7778276</v>
       </c>
       <c r="C203" t="s">
         <v>68</v>
@@ -42994,190 +42994,190 @@
         <v>21</v>
       </c>
       <c r="G203" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H203" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I203">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J203">
         <v>1</v>
       </c>
       <c r="K203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N203">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O203" t="s">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="P203" t="s">
         <v>314</v>
       </c>
       <c r="Q203">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R203">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S203">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T203">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U203">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V203">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W203">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X203">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="Y203">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z203">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AA203">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AB203">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="AC203">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD203">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE203">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF203">
+        <v>3.45</v>
+      </c>
+      <c r="AG203">
+        <v>1.85</v>
+      </c>
+      <c r="AH203">
+        <v>1.85</v>
+      </c>
+      <c r="AI203">
+        <v>1.67</v>
+      </c>
+      <c r="AJ203">
+        <v>2.05</v>
+      </c>
+      <c r="AK203">
+        <v>1.42</v>
+      </c>
+      <c r="AL203">
+        <v>1.25</v>
+      </c>
+      <c r="AM203">
+        <v>1.53</v>
+      </c>
+      <c r="AN203">
+        <v>1</v>
+      </c>
+      <c r="AO203">
+        <v>0.67</v>
+      </c>
+      <c r="AP203">
+        <v>0.83</v>
+      </c>
+      <c r="AQ203">
+        <v>1.09</v>
+      </c>
+      <c r="AR203">
+        <v>1.39</v>
+      </c>
+      <c r="AS203">
+        <v>1.29</v>
+      </c>
+      <c r="AT203">
+        <v>2.68</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>6</v>
+      </c>
+      <c r="AW203">
+        <v>10</v>
+      </c>
+      <c r="AX203">
+        <v>5</v>
+      </c>
+      <c r="AY203">
+        <v>15</v>
+      </c>
+      <c r="AZ203">
+        <v>11</v>
+      </c>
+      <c r="BA203">
+        <v>10</v>
+      </c>
+      <c r="BB203">
+        <v>6</v>
+      </c>
+      <c r="BC203">
+        <v>16</v>
+      </c>
+      <c r="BD203">
+        <v>1.79</v>
+      </c>
+      <c r="BE203">
+        <v>7</v>
+      </c>
+      <c r="BF203">
+        <v>2.18</v>
+      </c>
+      <c r="BG203">
+        <v>1.17</v>
+      </c>
+      <c r="BH203">
+        <v>4.1</v>
+      </c>
+      <c r="BI203">
+        <v>1.32</v>
+      </c>
+      <c r="BJ203">
         <v>2.95</v>
       </c>
-      <c r="AG203">
-        <v>1.88</v>
-      </c>
-      <c r="AH203">
-        <v>1.82</v>
-      </c>
-      <c r="AI203">
-        <v>1.85</v>
-      </c>
-      <c r="AJ203">
-        <v>1.83</v>
-      </c>
-      <c r="AK203">
-        <v>1.28</v>
-      </c>
-      <c r="AL203">
-        <v>1.28</v>
-      </c>
-      <c r="AM203">
-        <v>1.7</v>
-      </c>
-      <c r="AN203">
-        <v>1.67</v>
-      </c>
-      <c r="AO203">
-        <v>1.73</v>
-      </c>
-      <c r="AP203">
-        <v>1.73</v>
-      </c>
-      <c r="AQ203">
-        <v>1.67</v>
-      </c>
-      <c r="AR203">
-        <v>1.55</v>
-      </c>
-      <c r="AS203">
-        <v>1.38</v>
-      </c>
-      <c r="AT203">
-        <v>2.93</v>
-      </c>
-      <c r="AU203">
-        <v>9</v>
-      </c>
-      <c r="AV203">
-        <v>5</v>
-      </c>
-      <c r="AW203">
-        <v>7</v>
-      </c>
-      <c r="AX203">
-        <v>3</v>
-      </c>
-      <c r="AY203">
-        <v>16</v>
-      </c>
-      <c r="AZ203">
-        <v>8</v>
-      </c>
-      <c r="BA203">
-        <v>7</v>
-      </c>
-      <c r="BB203">
-        <v>3</v>
-      </c>
-      <c r="BC203">
-        <v>10</v>
-      </c>
-      <c r="BD203">
-        <v>1.61</v>
-      </c>
-      <c r="BE203">
-        <v>6.75</v>
-      </c>
-      <c r="BF203">
-        <v>2.55</v>
-      </c>
-      <c r="BG203">
-        <v>1.21</v>
-      </c>
-      <c r="BH203">
-        <v>3.65</v>
-      </c>
-      <c r="BI203">
-        <v>1.38</v>
-      </c>
-      <c r="BJ203">
-        <v>2.65</v>
-      </c>
       <c r="BK203">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BL203">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BM203">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="BN203">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="BO203">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="BP203">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="204" spans="1:68">
@@ -43185,7 +43185,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>7778275</v>
+        <v>7778278</v>
       </c>
       <c r="C204" t="s">
         <v>68</v>
@@ -43200,190 +43200,190 @@
         <v>21</v>
       </c>
       <c r="G204" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H204" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L204">
         <v>1</v>
       </c>
       <c r="M204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O204" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="P204" t="s">
         <v>315</v>
       </c>
       <c r="Q204">
+        <v>2.8</v>
+      </c>
+      <c r="R204">
+        <v>2</v>
+      </c>
+      <c r="S204">
+        <v>3.8</v>
+      </c>
+      <c r="T204">
+        <v>1.45</v>
+      </c>
+      <c r="U204">
+        <v>2.55</v>
+      </c>
+      <c r="V204">
         <v>3</v>
       </c>
-      <c r="R204">
-        <v>2.05</v>
-      </c>
-      <c r="S204">
-        <v>3.3</v>
-      </c>
-      <c r="T204">
-        <v>1.4</v>
-      </c>
-      <c r="U204">
-        <v>2.75</v>
-      </c>
-      <c r="V204">
-        <v>2.75</v>
-      </c>
       <c r="W204">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X204">
-        <v>6.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y204">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z204">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="AA204">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="AB204">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="AC204">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AD204">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE204">
+        <v>1.42</v>
+      </c>
+      <c r="AF204">
+        <v>2.85</v>
+      </c>
+      <c r="AG204">
+        <v>2.07</v>
+      </c>
+      <c r="AH204">
+        <v>1.67</v>
+      </c>
+      <c r="AI204">
+        <v>1.85</v>
+      </c>
+      <c r="AJ204">
+        <v>1.8</v>
+      </c>
+      <c r="AK204">
         <v>1.3</v>
-      </c>
-      <c r="AF204">
-        <v>3.4</v>
-      </c>
-      <c r="AG204">
-        <v>1.91</v>
-      </c>
-      <c r="AH204">
-        <v>1.79</v>
-      </c>
-      <c r="AI204">
-        <v>1.67</v>
-      </c>
-      <c r="AJ204">
-        <v>2.05</v>
-      </c>
-      <c r="AK204">
-        <v>1.42</v>
       </c>
       <c r="AL204">
         <v>1.28</v>
       </c>
       <c r="AM204">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AN204">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AO204">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AQ204">
-        <v>1.82</v>
+        <v>0.92</v>
       </c>
       <c r="AR204">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS204">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AT204">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="AU204">
+        <v>2</v>
+      </c>
+      <c r="AV204">
+        <v>2</v>
+      </c>
+      <c r="AW204">
+        <v>1</v>
+      </c>
+      <c r="AX204">
         <v>4</v>
       </c>
-      <c r="AV204">
-        <v>5</v>
-      </c>
-      <c r="AW204">
-        <v>2</v>
-      </c>
-      <c r="AX204">
+      <c r="AY204">
         <v>3</v>
       </c>
-      <c r="AY204">
+      <c r="AZ204">
         <v>6</v>
       </c>
-      <c r="AZ204">
-        <v>8</v>
-      </c>
       <c r="BA204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB204">
         <v>6</v>
       </c>
       <c r="BC204">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD204">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="BE204">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF204">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="BG204">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BH204">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI204">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BJ204">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BK204">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BL204">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="BM204">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="BN204">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BO204">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="BP204">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="205" spans="1:68">
@@ -43391,7 +43391,7 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>7778276</v>
+        <v>7778273</v>
       </c>
       <c r="C205" t="s">
         <v>68</v>
@@ -43406,190 +43406,190 @@
         <v>21</v>
       </c>
       <c r="G205" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H205" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J205">
         <v>1</v>
       </c>
       <c r="K205">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M205">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N205">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O205" t="s">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="P205" t="s">
         <v>316</v>
       </c>
       <c r="Q205">
+        <v>2.7</v>
+      </c>
+      <c r="R205">
+        <v>2</v>
+      </c>
+      <c r="S205">
+        <v>4</v>
+      </c>
+      <c r="T205">
+        <v>1.44</v>
+      </c>
+      <c r="U205">
+        <v>2.6</v>
+      </c>
+      <c r="V205">
         <v>3</v>
       </c>
-      <c r="R205">
+      <c r="W205">
+        <v>1.33</v>
+      </c>
+      <c r="X205">
+        <v>7.9</v>
+      </c>
+      <c r="Y205">
+        <v>1.02</v>
+      </c>
+      <c r="Z205">
+        <v>2.1</v>
+      </c>
+      <c r="AA205">
+        <v>3.15</v>
+      </c>
+      <c r="AB205">
+        <v>3.07</v>
+      </c>
+      <c r="AC205">
+        <v>1.07</v>
+      </c>
+      <c r="AD205">
+        <v>8</v>
+      </c>
+      <c r="AE205">
+        <v>1.38</v>
+      </c>
+      <c r="AF205">
+        <v>2.95</v>
+      </c>
+      <c r="AG205">
+        <v>1.88</v>
+      </c>
+      <c r="AH205">
+        <v>1.82</v>
+      </c>
+      <c r="AI205">
+        <v>1.85</v>
+      </c>
+      <c r="AJ205">
+        <v>1.83</v>
+      </c>
+      <c r="AK205">
+        <v>1.28</v>
+      </c>
+      <c r="AL205">
+        <v>1.28</v>
+      </c>
+      <c r="AM205">
+        <v>1.7</v>
+      </c>
+      <c r="AN205">
+        <v>1.67</v>
+      </c>
+      <c r="AO205">
+        <v>1.73</v>
+      </c>
+      <c r="AP205">
+        <v>1.73</v>
+      </c>
+      <c r="AQ205">
+        <v>1.67</v>
+      </c>
+      <c r="AR205">
+        <v>1.55</v>
+      </c>
+      <c r="AS205">
+        <v>1.38</v>
+      </c>
+      <c r="AT205">
+        <v>2.93</v>
+      </c>
+      <c r="AU205">
+        <v>9</v>
+      </c>
+      <c r="AV205">
+        <v>5</v>
+      </c>
+      <c r="AW205">
+        <v>7</v>
+      </c>
+      <c r="AX205">
+        <v>3</v>
+      </c>
+      <c r="AY205">
+        <v>16</v>
+      </c>
+      <c r="AZ205">
+        <v>8</v>
+      </c>
+      <c r="BA205">
+        <v>7</v>
+      </c>
+      <c r="BB205">
+        <v>3</v>
+      </c>
+      <c r="BC205">
+        <v>10</v>
+      </c>
+      <c r="BD205">
+        <v>1.61</v>
+      </c>
+      <c r="BE205">
+        <v>6.75</v>
+      </c>
+      <c r="BF205">
+        <v>2.55</v>
+      </c>
+      <c r="BG205">
+        <v>1.21</v>
+      </c>
+      <c r="BH205">
+        <v>3.65</v>
+      </c>
+      <c r="BI205">
+        <v>1.38</v>
+      </c>
+      <c r="BJ205">
+        <v>2.65</v>
+      </c>
+      <c r="BK205">
+        <v>1.64</v>
+      </c>
+      <c r="BL205">
         <v>2.05</v>
       </c>
-      <c r="S205">
-        <v>3.3</v>
-      </c>
-      <c r="T205">
-        <v>1.4</v>
-      </c>
-      <c r="U205">
-        <v>2.75</v>
-      </c>
-      <c r="V205">
-        <v>2.75</v>
-      </c>
-      <c r="W205">
-        <v>1.4</v>
-      </c>
-      <c r="X205">
-        <v>6.4</v>
-      </c>
-      <c r="Y205">
-        <v>1.05</v>
-      </c>
-      <c r="Z205">
-        <v>2.27</v>
-      </c>
-      <c r="AA205">
-        <v>3.2</v>
-      </c>
-      <c r="AB205">
-        <v>2.73</v>
-      </c>
-      <c r="AC205">
-        <v>1.05</v>
-      </c>
-      <c r="AD205">
-        <v>9</v>
-      </c>
-      <c r="AE205">
-        <v>1.3</v>
-      </c>
-      <c r="AF205">
-        <v>3.45</v>
-      </c>
-      <c r="AG205">
-        <v>1.85</v>
-      </c>
-      <c r="AH205">
-        <v>1.85</v>
-      </c>
-      <c r="AI205">
-        <v>1.67</v>
-      </c>
-      <c r="AJ205">
-        <v>2.05</v>
-      </c>
-      <c r="AK205">
+      <c r="BM205">
+        <v>2.02</v>
+      </c>
+      <c r="BN205">
+        <v>1.66</v>
+      </c>
+      <c r="BO205">
+        <v>2.55</v>
+      </c>
+      <c r="BP205">
         <v>1.42</v>
-      </c>
-      <c r="AL205">
-        <v>1.25</v>
-      </c>
-      <c r="AM205">
-        <v>1.53</v>
-      </c>
-      <c r="AN205">
-        <v>1</v>
-      </c>
-      <c r="AO205">
-        <v>0.67</v>
-      </c>
-      <c r="AP205">
-        <v>0.83</v>
-      </c>
-      <c r="AQ205">
-        <v>1.09</v>
-      </c>
-      <c r="AR205">
-        <v>1.39</v>
-      </c>
-      <c r="AS205">
-        <v>1.29</v>
-      </c>
-      <c r="AT205">
-        <v>2.68</v>
-      </c>
-      <c r="AU205">
-        <v>5</v>
-      </c>
-      <c r="AV205">
-        <v>6</v>
-      </c>
-      <c r="AW205">
-        <v>10</v>
-      </c>
-      <c r="AX205">
-        <v>5</v>
-      </c>
-      <c r="AY205">
-        <v>15</v>
-      </c>
-      <c r="AZ205">
-        <v>11</v>
-      </c>
-      <c r="BA205">
-        <v>10</v>
-      </c>
-      <c r="BB205">
-        <v>6</v>
-      </c>
-      <c r="BC205">
-        <v>16</v>
-      </c>
-      <c r="BD205">
-        <v>1.79</v>
-      </c>
-      <c r="BE205">
-        <v>7</v>
-      </c>
-      <c r="BF205">
-        <v>2.18</v>
-      </c>
-      <c r="BG205">
-        <v>1.17</v>
-      </c>
-      <c r="BH205">
-        <v>4.1</v>
-      </c>
-      <c r="BI205">
-        <v>1.32</v>
-      </c>
-      <c r="BJ205">
-        <v>2.95</v>
-      </c>
-      <c r="BK205">
-        <v>1.53</v>
-      </c>
-      <c r="BL205">
-        <v>2.25</v>
-      </c>
-      <c r="BM205">
-        <v>1.84</v>
-      </c>
-      <c r="BN205">
-        <v>1.8</v>
-      </c>
-      <c r="BO205">
-        <v>2.3</v>
-      </c>
-      <c r="BP205">
-        <v>1.5</v>
       </c>
     </row>
     <row r="206" spans="1:68">
@@ -43597,7 +43597,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>7778278</v>
+        <v>7778275</v>
       </c>
       <c r="C206" t="s">
         <v>68</v>
@@ -43612,190 +43612,190 @@
         <v>21</v>
       </c>
       <c r="G206" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H206" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L206">
         <v>1</v>
       </c>
       <c r="M206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O206" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="P206" t="s">
         <v>317</v>
       </c>
       <c r="Q206">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R206">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S206">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T206">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="U206">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V206">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W206">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X206">
-        <v>8.800000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="Y206">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z206">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="AA206">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="AB206">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="AC206">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AD206">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AE206">
+        <v>1.3</v>
+      </c>
+      <c r="AF206">
+        <v>3.4</v>
+      </c>
+      <c r="AG206">
+        <v>1.91</v>
+      </c>
+      <c r="AH206">
+        <v>1.79</v>
+      </c>
+      <c r="AI206">
+        <v>1.67</v>
+      </c>
+      <c r="AJ206">
+        <v>2.05</v>
+      </c>
+      <c r="AK206">
         <v>1.42</v>
-      </c>
-      <c r="AF206">
-        <v>2.85</v>
-      </c>
-      <c r="AG206">
-        <v>2.07</v>
-      </c>
-      <c r="AH206">
-        <v>1.67</v>
-      </c>
-      <c r="AI206">
-        <v>1.85</v>
-      </c>
-      <c r="AJ206">
-        <v>1.8</v>
-      </c>
-      <c r="AK206">
-        <v>1.3</v>
       </c>
       <c r="AL206">
         <v>1.28</v>
       </c>
       <c r="AM206">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AN206">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AO206">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="AP206">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ206">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="AR206">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AS206">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AT206">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="AU206">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV206">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX206">
+        <v>3</v>
+      </c>
+      <c r="AY206">
+        <v>6</v>
+      </c>
+      <c r="AZ206">
+        <v>8</v>
+      </c>
+      <c r="BA206">
         <v>4</v>
-      </c>
-      <c r="AY206">
-        <v>3</v>
-      </c>
-      <c r="AZ206">
-        <v>6</v>
-      </c>
-      <c r="BA206">
-        <v>3</v>
       </c>
       <c r="BB206">
         <v>6</v>
       </c>
       <c r="BC206">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD206">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="BE206">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF206">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="BG206">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BH206">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BI206">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BJ206">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="BK206">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="BL206">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BM206">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BN206">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BO206">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="BP206">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="207" spans="1:68">
@@ -45039,7 +45039,7 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>7778291</v>
+        <v>7778284</v>
       </c>
       <c r="C213" t="s">
         <v>68</v>
@@ -45054,190 +45054,190 @@
         <v>22</v>
       </c>
       <c r="G213" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H213" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I213">
         <v>0</v>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O213" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>91</v>
+        <v>293</v>
       </c>
       <c r="Q213">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R213">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S213">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="T213">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U213">
         <v>2.4</v>
       </c>
       <c r="V213">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="W213">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X213">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="Y213">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Z213">
-        <v>3.52</v>
+        <v>2.35</v>
       </c>
       <c r="AA213">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB213">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="AC213">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AD213">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AE213">
+        <v>1.43</v>
+      </c>
+      <c r="AF213">
+        <v>2.6</v>
+      </c>
+      <c r="AG213">
+        <v>2.2</v>
+      </c>
+      <c r="AH213">
+        <v>1.59</v>
+      </c>
+      <c r="AI213">
+        <v>1.98</v>
+      </c>
+      <c r="AJ213">
+        <v>1.72</v>
+      </c>
+      <c r="AK213">
+        <v>1.35</v>
+      </c>
+      <c r="AL213">
+        <v>1.34</v>
+      </c>
+      <c r="AM213">
+        <v>1.57</v>
+      </c>
+      <c r="AN213">
+        <v>1.2</v>
+      </c>
+      <c r="AO213">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP213">
         <v>1.5</v>
       </c>
-      <c r="AF213">
-        <v>2.4</v>
-      </c>
-      <c r="AG213">
-        <v>2.1</v>
-      </c>
-      <c r="AH213">
+      <c r="AQ213">
+        <v>0.5</v>
+      </c>
+      <c r="AR213">
+        <v>1.44</v>
+      </c>
+      <c r="AS213">
+        <v>1.23</v>
+      </c>
+      <c r="AT213">
+        <v>2.67</v>
+      </c>
+      <c r="AU213">
+        <v>8</v>
+      </c>
+      <c r="AV213">
+        <v>2</v>
+      </c>
+      <c r="AW213">
+        <v>8</v>
+      </c>
+      <c r="AX213">
+        <v>5</v>
+      </c>
+      <c r="AY213">
+        <v>16</v>
+      </c>
+      <c r="AZ213">
+        <v>7</v>
+      </c>
+      <c r="BA213">
+        <v>4</v>
+      </c>
+      <c r="BB213">
+        <v>3</v>
+      </c>
+      <c r="BC213">
+        <v>7</v>
+      </c>
+      <c r="BD213">
+        <v>1.85</v>
+      </c>
+      <c r="BE213">
+        <v>6.4</v>
+      </c>
+      <c r="BF213">
+        <v>2.17</v>
+      </c>
+      <c r="BG213">
+        <v>1.38</v>
+      </c>
+      <c r="BH213">
+        <v>2.7</v>
+      </c>
+      <c r="BI213">
         <v>1.65</v>
       </c>
-      <c r="AI213">
+      <c r="BJ213">
+        <v>2.02</v>
+      </c>
+      <c r="BK213">
         <v>2.05</v>
       </c>
-      <c r="AJ213">
-        <v>1.67</v>
-      </c>
-      <c r="AK213">
-        <v>1.75</v>
-      </c>
-      <c r="AL213">
-        <v>1.28</v>
-      </c>
-      <c r="AM213">
-        <v>1.25</v>
-      </c>
-      <c r="AN213">
-        <v>1.45</v>
-      </c>
-      <c r="AO213">
-        <v>1.9</v>
-      </c>
-      <c r="AP213">
-        <v>1.42</v>
-      </c>
-      <c r="AQ213">
-        <v>1.82</v>
-      </c>
-      <c r="AR213">
-        <v>1.54</v>
-      </c>
-      <c r="AS213">
-        <v>1.49</v>
-      </c>
-      <c r="AT213">
-        <v>3.03</v>
-      </c>
-      <c r="AU213">
-        <v>2</v>
-      </c>
-      <c r="AV213">
-        <v>3</v>
-      </c>
-      <c r="AW213">
-        <v>1</v>
-      </c>
-      <c r="AX213">
-        <v>7</v>
-      </c>
-      <c r="AY213">
-        <v>3</v>
-      </c>
-      <c r="AZ213">
-        <v>10</v>
-      </c>
-      <c r="BA213">
-        <v>8</v>
-      </c>
-      <c r="BB213">
-        <v>5</v>
-      </c>
-      <c r="BC213">
-        <v>13</v>
-      </c>
-      <c r="BD213">
-        <v>2.43</v>
-      </c>
-      <c r="BE213">
-        <v>6.75</v>
-      </c>
-      <c r="BF213">
-        <v>1.68</v>
-      </c>
-      <c r="BG213">
-        <v>1.33</v>
-      </c>
-      <c r="BH213">
-        <v>2.88</v>
-      </c>
-      <c r="BI213">
-        <v>1.57</v>
-      </c>
-      <c r="BJ213">
-        <v>2.16</v>
-      </c>
-      <c r="BK213">
-        <v>1.92</v>
-      </c>
       <c r="BL213">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="BM213">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="BN213">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="BO213">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP213">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="214" spans="1:68">
@@ -45245,7 +45245,7 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>7778289</v>
+        <v>7778286</v>
       </c>
       <c r="C214" t="s">
         <v>68</v>
@@ -45260,190 +45260,190 @@
         <v>22</v>
       </c>
       <c r="G214" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H214" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J214">
         <v>0</v>
       </c>
       <c r="K214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>2</v>
+      </c>
+      <c r="O214" t="s">
+        <v>226</v>
+      </c>
+      <c r="P214" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q214">
+        <v>2.95</v>
+      </c>
+      <c r="R214">
+        <v>2.15</v>
+      </c>
+      <c r="S214">
+        <v>3.1</v>
+      </c>
+      <c r="T214">
+        <v>1.34</v>
+      </c>
+      <c r="U214">
         <v>3</v>
       </c>
-      <c r="M214">
-        <v>1</v>
-      </c>
-      <c r="N214">
-        <v>4</v>
-      </c>
-      <c r="O214" t="s">
-        <v>225</v>
-      </c>
-      <c r="P214" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q214">
-        <v>3.18</v>
-      </c>
-      <c r="R214">
-        <v>2.05</v>
-      </c>
-      <c r="S214">
-        <v>3.45</v>
-      </c>
-      <c r="T214">
-        <v>1.41</v>
-      </c>
-      <c r="U214">
-        <v>2.6</v>
-      </c>
       <c r="V214">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="W214">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="X214">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="Y214">
+        <v>1.1</v>
+      </c>
+      <c r="Z214">
+        <v>2.27</v>
+      </c>
+      <c r="AA214">
+        <v>3.32</v>
+      </c>
+      <c r="AB214">
+        <v>2.65</v>
+      </c>
+      <c r="AC214">
         <v>1.04</v>
       </c>
-      <c r="Z214">
-        <v>2.44</v>
-      </c>
-      <c r="AA214">
-        <v>3.08</v>
-      </c>
-      <c r="AB214">
-        <v>2.6</v>
-      </c>
-      <c r="AC214">
-        <v>1.02</v>
-      </c>
       <c r="AD214">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AE214">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF214">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AG214">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH214">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AI214">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AJ214">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AK214">
         <v>1.44</v>
       </c>
       <c r="AL214">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM214">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AN214">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="AO214">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="AP214">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ214">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AR214">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AS214">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AT214">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="AU214">
+        <v>4</v>
+      </c>
+      <c r="AV214">
+        <v>5</v>
+      </c>
+      <c r="AW214">
+        <v>6</v>
+      </c>
+      <c r="AX214">
+        <v>8</v>
+      </c>
+      <c r="AY214">
         <v>10</v>
       </c>
-      <c r="AV214">
+      <c r="AZ214">
+        <v>13</v>
+      </c>
+      <c r="BA214">
+        <v>5</v>
+      </c>
+      <c r="BB214">
         <v>4</v>
       </c>
-      <c r="AW214">
-        <v>5</v>
-      </c>
-      <c r="AX214">
-        <v>4</v>
-      </c>
-      <c r="AY214">
-        <v>15</v>
-      </c>
-      <c r="AZ214">
-        <v>8</v>
-      </c>
-      <c r="BA214">
-        <v>4</v>
-      </c>
-      <c r="BB214">
-        <v>2</v>
-      </c>
       <c r="BC214">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD214">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="BE214">
         <v>6.75</v>
       </c>
       <c r="BF214">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="BG214">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BH214">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="BI214">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="BJ214">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="BK214">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BL214">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="BM214">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="BN214">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BO214">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="BP214">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="215" spans="1:68">
@@ -45451,7 +45451,7 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>7778290</v>
+        <v>7778291</v>
       </c>
       <c r="C215" t="s">
         <v>68</v>
@@ -45466,43 +45466,43 @@
         <v>22</v>
       </c>
       <c r="G215" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H215" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N215">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O215" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c r="Q215">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="R215">
         <v>1.95</v>
       </c>
       <c r="S215">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="T215">
         <v>1.5</v>
@@ -45511,37 +45511,37 @@
         <v>2.4</v>
       </c>
       <c r="V215">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W215">
         <v>1.28</v>
       </c>
       <c r="X215">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y215">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Z215">
-        <v>1.81</v>
+        <v>3.52</v>
       </c>
       <c r="AA215">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB215">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC215">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AD215">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AE215">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF215">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG215">
         <v>2.1</v>
@@ -45550,94 +45550,94 @@
         <v>1.65</v>
       </c>
       <c r="AI215">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ215">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK215">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL215">
         <v>1.28</v>
       </c>
       <c r="AM215">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AN215">
+        <v>1.45</v>
+      </c>
+      <c r="AO215">
         <v>1.9</v>
       </c>
-      <c r="AO215">
-        <v>0.55</v>
-      </c>
       <c r="AP215">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AQ215">
-        <v>0.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR215">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS215">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AT215">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="AU215">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW215">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX215">
         <v>7</v>
       </c>
       <c r="AY215">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AZ215">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA215">
         <v>8</v>
       </c>
       <c r="BB215">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC215">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD215">
-        <v>1.5</v>
+        <v>2.43</v>
       </c>
       <c r="BE215">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF215">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="BG215">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BH215">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI215">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BJ215">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BK215">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BL215">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BM215">
         <v>2.43</v>
@@ -45657,7 +45657,7 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>7778284</v>
+        <v>7778289</v>
       </c>
       <c r="C216" t="s">
         <v>68</v>
@@ -45672,190 +45672,190 @@
         <v>22</v>
       </c>
       <c r="G216" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M216">
         <v>1</v>
       </c>
       <c r="N216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O216" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P216" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="Q216">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R216">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S216">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T216">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="U216">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V216">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="W216">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X216">
-        <v>9.25</v>
+        <v>7.1</v>
       </c>
       <c r="Y216">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z216">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AA216">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB216">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AC216">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AD216">
-        <v>6.75</v>
+        <v>7.8</v>
       </c>
       <c r="AE216">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AF216">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AG216">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH216">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AI216">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AJ216">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AK216">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL216">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AM216">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AN216">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AO216">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AP216">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AQ216">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR216">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AS216">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="AT216">
-        <v>2.67</v>
+        <v>3.19</v>
       </c>
       <c r="AU216">
+        <v>10</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>5</v>
+      </c>
+      <c r="AX216">
+        <v>4</v>
+      </c>
+      <c r="AY216">
+        <v>15</v>
+      </c>
+      <c r="AZ216">
         <v>8</v>
-      </c>
-      <c r="AV216">
-        <v>2</v>
-      </c>
-      <c r="AW216">
-        <v>8</v>
-      </c>
-      <c r="AX216">
-        <v>5</v>
-      </c>
-      <c r="AY216">
-        <v>16</v>
-      </c>
-      <c r="AZ216">
-        <v>7</v>
       </c>
       <c r="BA216">
         <v>4</v>
       </c>
       <c r="BB216">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC216">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD216">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BE216">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF216">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BG216">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="BH216">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="BI216">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="BJ216">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BK216">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="BL216">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="BM216">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="BN216">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BO216">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="BP216">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="217" spans="1:68">
@@ -45863,7 +45863,7 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>7778286</v>
+        <v>7778290</v>
       </c>
       <c r="C217" t="s">
         <v>68</v>
@@ -45878,190 +45878,190 @@
         <v>22</v>
       </c>
       <c r="G217" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L217">
         <v>1</v>
       </c>
       <c r="M217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N217">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O217" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="P217" t="s">
-        <v>144</v>
+        <v>322</v>
       </c>
       <c r="Q217">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R217">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S217">
+        <v>4.2</v>
+      </c>
+      <c r="T217">
+        <v>1.5</v>
+      </c>
+      <c r="U217">
+        <v>2.4</v>
+      </c>
+      <c r="V217">
+        <v>3.3</v>
+      </c>
+      <c r="W217">
+        <v>1.28</v>
+      </c>
+      <c r="X217">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y217">
+        <v>1.01</v>
+      </c>
+      <c r="Z217">
+        <v>1.81</v>
+      </c>
+      <c r="AA217">
         <v>3.1</v>
       </c>
-      <c r="T217">
-        <v>1.34</v>
-      </c>
-      <c r="U217">
-        <v>3</v>
-      </c>
-      <c r="V217">
-        <v>2.5</v>
-      </c>
-      <c r="W217">
+      <c r="AB217">
+        <v>4.1</v>
+      </c>
+      <c r="AC217">
+        <v>1.09</v>
+      </c>
+      <c r="AD217">
+        <v>7</v>
+      </c>
+      <c r="AE217">
+        <v>1.45</v>
+      </c>
+      <c r="AF217">
+        <v>2.7</v>
+      </c>
+      <c r="AG217">
+        <v>2.1</v>
+      </c>
+      <c r="AH217">
+        <v>1.65</v>
+      </c>
+      <c r="AI217">
+        <v>2</v>
+      </c>
+      <c r="AJ217">
+        <v>1.7</v>
+      </c>
+      <c r="AK217">
+        <v>1.25</v>
+      </c>
+      <c r="AL217">
+        <v>1.28</v>
+      </c>
+      <c r="AM217">
+        <v>1.75</v>
+      </c>
+      <c r="AN217">
+        <v>1.9</v>
+      </c>
+      <c r="AO217">
+        <v>0.55</v>
+      </c>
+      <c r="AP217">
+        <v>1.73</v>
+      </c>
+      <c r="AQ217">
+        <v>0.75</v>
+      </c>
+      <c r="AR217">
+        <v>1.69</v>
+      </c>
+      <c r="AS217">
+        <v>1.25</v>
+      </c>
+      <c r="AT217">
+        <v>2.94</v>
+      </c>
+      <c r="AU217">
+        <v>5</v>
+      </c>
+      <c r="AV217">
+        <v>4</v>
+      </c>
+      <c r="AW217">
+        <v>12</v>
+      </c>
+      <c r="AX217">
+        <v>7</v>
+      </c>
+      <c r="AY217">
+        <v>17</v>
+      </c>
+      <c r="AZ217">
+        <v>11</v>
+      </c>
+      <c r="BA217">
+        <v>8</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>10</v>
+      </c>
+      <c r="BD217">
+        <v>1.5</v>
+      </c>
+      <c r="BE217">
+        <v>7</v>
+      </c>
+      <c r="BF217">
+        <v>2.8</v>
+      </c>
+      <c r="BG217">
+        <v>1.32</v>
+      </c>
+      <c r="BH217">
+        <v>2.9</v>
+      </c>
+      <c r="BI217">
+        <v>1.56</v>
+      </c>
+      <c r="BJ217">
+        <v>2.18</v>
+      </c>
+      <c r="BK217">
+        <v>1.91</v>
+      </c>
+      <c r="BL217">
+        <v>1.74</v>
+      </c>
+      <c r="BM217">
+        <v>2.43</v>
+      </c>
+      <c r="BN217">
         <v>1.46</v>
       </c>
-      <c r="X217">
-        <v>6.25</v>
-      </c>
-      <c r="Y217">
-        <v>1.1</v>
-      </c>
-      <c r="Z217">
-        <v>2.27</v>
-      </c>
-      <c r="AA217">
-        <v>3.32</v>
-      </c>
-      <c r="AB217">
-        <v>2.65</v>
-      </c>
-      <c r="AC217">
-        <v>1.04</v>
-      </c>
-      <c r="AD217">
-        <v>10</v>
-      </c>
-      <c r="AE217">
-        <v>1.25</v>
-      </c>
-      <c r="AF217">
-        <v>3.6</v>
-      </c>
-      <c r="AG217">
-        <v>1.78</v>
-      </c>
-      <c r="AH217">
-        <v>1.92</v>
-      </c>
-      <c r="AI217">
-        <v>1.63</v>
-      </c>
-      <c r="AJ217">
-        <v>2.1</v>
-      </c>
-      <c r="AK217">
-        <v>1.44</v>
-      </c>
-      <c r="AL217">
-        <v>1.29</v>
-      </c>
-      <c r="AM217">
-        <v>1.51</v>
-      </c>
-      <c r="AN217">
-        <v>1.1</v>
-      </c>
-      <c r="AO217">
-        <v>0.44</v>
-      </c>
-      <c r="AP217">
-        <v>1.08</v>
-      </c>
-      <c r="AQ217">
-        <v>0.73</v>
-      </c>
-      <c r="AR217">
-        <v>1.42</v>
-      </c>
-      <c r="AS217">
-        <v>1.4</v>
-      </c>
-      <c r="AT217">
-        <v>2.82</v>
-      </c>
-      <c r="AU217">
-        <v>4</v>
-      </c>
-      <c r="AV217">
-        <v>5</v>
-      </c>
-      <c r="AW217">
-        <v>6</v>
-      </c>
-      <c r="AX217">
-        <v>8</v>
-      </c>
-      <c r="AY217">
-        <v>10</v>
-      </c>
-      <c r="AZ217">
-        <v>13</v>
-      </c>
-      <c r="BA217">
-        <v>5</v>
-      </c>
-      <c r="BB217">
-        <v>4</v>
-      </c>
-      <c r="BC217">
-        <v>9</v>
-      </c>
-      <c r="BD217">
-        <v>1.72</v>
-      </c>
-      <c r="BE217">
-        <v>6.75</v>
-      </c>
-      <c r="BF217">
-        <v>2.32</v>
-      </c>
-      <c r="BG217">
-        <v>1.18</v>
-      </c>
-      <c r="BH217">
-        <v>3.9</v>
-      </c>
-      <c r="BI217">
-        <v>1.34</v>
-      </c>
-      <c r="BJ217">
-        <v>2.8</v>
-      </c>
-      <c r="BK217">
-        <v>1.58</v>
-      </c>
-      <c r="BL217">
-        <v>2.15</v>
-      </c>
-      <c r="BM217">
-        <v>1.92</v>
-      </c>
-      <c r="BN217">
-        <v>1.73</v>
-      </c>
       <c r="BO217">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="BP217">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="218" spans="1:68">
@@ -46069,7 +46069,7 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>7778287</v>
+        <v>7778285</v>
       </c>
       <c r="C218" t="s">
         <v>68</v>
@@ -46084,190 +46084,190 @@
         <v>22</v>
       </c>
       <c r="G218" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H218" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218">
         <v>1</v>
       </c>
       <c r="L218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N218">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O218" t="s">
+        <v>172</v>
+      </c>
+      <c r="P218" t="s">
         <v>91</v>
-      </c>
-      <c r="P218" t="s">
-        <v>323</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
       </c>
       <c r="R218">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S218">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T218">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="U218">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V218">
+        <v>3.25</v>
+      </c>
+      <c r="W218">
+        <v>1.33</v>
+      </c>
+      <c r="X218">
+        <v>9</v>
+      </c>
+      <c r="Y218">
+        <v>1.07</v>
+      </c>
+      <c r="Z218">
         <v>3.5</v>
       </c>
-      <c r="W218">
-        <v>1.29</v>
-      </c>
-      <c r="X218">
-        <v>11</v>
-      </c>
-      <c r="Y218">
-        <v>1.05</v>
-      </c>
-      <c r="Z218">
-        <v>3.45</v>
-      </c>
       <c r="AA218">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB218">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AC218">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AD218">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE218">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AF218">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="AG218">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH218">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI218">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ218">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AK218">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL218">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AM218">
         <v>1.27</v>
       </c>
       <c r="AN218">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AO218">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AP218">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AQ218">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AR218">
+        <v>1.32</v>
+      </c>
+      <c r="AS218">
+        <v>1.59</v>
+      </c>
+      <c r="AT218">
+        <v>2.91</v>
+      </c>
+      <c r="AU218">
+        <v>3</v>
+      </c>
+      <c r="AV218">
+        <v>6</v>
+      </c>
+      <c r="AW218">
+        <v>7</v>
+      </c>
+      <c r="AX218">
+        <v>6</v>
+      </c>
+      <c r="AY218">
+        <v>10</v>
+      </c>
+      <c r="AZ218">
+        <v>12</v>
+      </c>
+      <c r="BA218">
+        <v>7</v>
+      </c>
+      <c r="BB218">
+        <v>3</v>
+      </c>
+      <c r="BC218">
+        <v>10</v>
+      </c>
+      <c r="BD218">
+        <v>2.23</v>
+      </c>
+      <c r="BE218">
+        <v>6.5</v>
+      </c>
+      <c r="BF218">
+        <v>1.79</v>
+      </c>
+      <c r="BG218">
+        <v>1.32</v>
+      </c>
+      <c r="BH218">
+        <v>2.95</v>
+      </c>
+      <c r="BI218">
+        <v>1.54</v>
+      </c>
+      <c r="BJ218">
+        <v>2.23</v>
+      </c>
+      <c r="BK218">
+        <v>1.88</v>
+      </c>
+      <c r="BL218">
+        <v>1.77</v>
+      </c>
+      <c r="BM218">
+        <v>2.38</v>
+      </c>
+      <c r="BN218">
         <v>1.47</v>
       </c>
-      <c r="AS218">
-        <v>1.5</v>
-      </c>
-      <c r="AT218">
-        <v>2.97</v>
-      </c>
-      <c r="AU218">
-        <v>2</v>
-      </c>
-      <c r="AV218">
-        <v>11</v>
-      </c>
-      <c r="AW218">
-        <v>20</v>
-      </c>
-      <c r="AX218">
-        <v>13</v>
-      </c>
-      <c r="AY218">
-        <v>22</v>
-      </c>
-      <c r="AZ218">
-        <v>24</v>
-      </c>
-      <c r="BA218">
-        <v>6</v>
-      </c>
-      <c r="BB218">
-        <v>9</v>
-      </c>
-      <c r="BC218">
-        <v>15</v>
-      </c>
-      <c r="BD218">
-        <v>2.17</v>
-      </c>
-      <c r="BE218">
-        <v>6.25</v>
-      </c>
-      <c r="BF218">
-        <v>1.84</v>
-      </c>
-      <c r="BG218">
-        <v>1.47</v>
-      </c>
-      <c r="BH218">
-        <v>2.4</v>
-      </c>
-      <c r="BI218">
-        <v>1.78</v>
-      </c>
-      <c r="BJ218">
-        <v>1.86</v>
-      </c>
-      <c r="BK218">
-        <v>2.25</v>
-      </c>
-      <c r="BL218">
-        <v>1.53</v>
-      </c>
-      <c r="BM218">
-        <v>2.95</v>
-      </c>
-      <c r="BN218">
-        <v>1.32</v>
-      </c>
       <c r="BO218">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="BP218">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="219" spans="1:68">
@@ -46275,7 +46275,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>7778285</v>
+        <v>7778287</v>
       </c>
       <c r="C219" t="s">
         <v>68</v>
@@ -46290,190 +46290,190 @@
         <v>22</v>
       </c>
       <c r="G219" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H219" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K219">
         <v>1</v>
       </c>
       <c r="L219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N219">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O219" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
       </c>
       <c r="R219">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S219">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T219">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="U219">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V219">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="W219">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X219">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y219">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z219">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA219">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AB219">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AC219">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AD219">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE219">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AF219">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="AG219">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH219">
+        <v>1.69</v>
+      </c>
+      <c r="AI219">
+        <v>2.05</v>
+      </c>
+      <c r="AJ219">
         <v>1.7</v>
       </c>
-      <c r="AI219">
-        <v>1.95</v>
-      </c>
-      <c r="AJ219">
-        <v>1.8</v>
-      </c>
       <c r="AK219">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL219">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AM219">
         <v>1.27</v>
       </c>
       <c r="AN219">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AO219">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AP219">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AQ219">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AR219">
+        <v>1.47</v>
+      </c>
+      <c r="AS219">
+        <v>1.5</v>
+      </c>
+      <c r="AT219">
+        <v>2.97</v>
+      </c>
+      <c r="AU219">
+        <v>2</v>
+      </c>
+      <c r="AV219">
+        <v>11</v>
+      </c>
+      <c r="AW219">
+        <v>20</v>
+      </c>
+      <c r="AX219">
+        <v>13</v>
+      </c>
+      <c r="AY219">
+        <v>22</v>
+      </c>
+      <c r="AZ219">
+        <v>24</v>
+      </c>
+      <c r="BA219">
+        <v>6</v>
+      </c>
+      <c r="BB219">
+        <v>9</v>
+      </c>
+      <c r="BC219">
+        <v>15</v>
+      </c>
+      <c r="BD219">
+        <v>2.17</v>
+      </c>
+      <c r="BE219">
+        <v>6.25</v>
+      </c>
+      <c r="BF219">
+        <v>1.84</v>
+      </c>
+      <c r="BG219">
+        <v>1.47</v>
+      </c>
+      <c r="BH219">
+        <v>2.4</v>
+      </c>
+      <c r="BI219">
+        <v>1.78</v>
+      </c>
+      <c r="BJ219">
+        <v>1.86</v>
+      </c>
+      <c r="BK219">
+        <v>2.25</v>
+      </c>
+      <c r="BL219">
+        <v>1.53</v>
+      </c>
+      <c r="BM219">
+        <v>2.95</v>
+      </c>
+      <c r="BN219">
         <v>1.32</v>
       </c>
-      <c r="AS219">
-        <v>1.59</v>
-      </c>
-      <c r="AT219">
-        <v>2.91</v>
-      </c>
-      <c r="AU219">
-        <v>3</v>
-      </c>
-      <c r="AV219">
-        <v>6</v>
-      </c>
-      <c r="AW219">
-        <v>7</v>
-      </c>
-      <c r="AX219">
-        <v>6</v>
-      </c>
-      <c r="AY219">
-        <v>10</v>
-      </c>
-      <c r="AZ219">
-        <v>12</v>
-      </c>
-      <c r="BA219">
-        <v>7</v>
-      </c>
-      <c r="BB219">
-        <v>3</v>
-      </c>
-      <c r="BC219">
-        <v>10</v>
-      </c>
-      <c r="BD219">
-        <v>2.23</v>
-      </c>
-      <c r="BE219">
-        <v>6.5</v>
-      </c>
-      <c r="BF219">
-        <v>1.79</v>
-      </c>
-      <c r="BG219">
-        <v>1.32</v>
-      </c>
-      <c r="BH219">
-        <v>2.95</v>
-      </c>
-      <c r="BI219">
-        <v>1.54</v>
-      </c>
-      <c r="BJ219">
-        <v>2.23</v>
-      </c>
-      <c r="BK219">
-        <v>1.88</v>
-      </c>
-      <c r="BL219">
-        <v>1.77</v>
-      </c>
-      <c r="BM219">
-        <v>2.38</v>
-      </c>
-      <c r="BN219">
-        <v>1.47</v>
-      </c>
       <c r="BO219">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP219">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="220" spans="1:68">
@@ -47099,7 +47099,7 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>7778300</v>
+        <v>7778293</v>
       </c>
       <c r="C223" t="s">
         <v>68</v>
@@ -47114,190 +47114,190 @@
         <v>23</v>
       </c>
       <c r="G223" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H223" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M223">
         <v>0</v>
       </c>
       <c r="N223">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O223" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="P223" t="s">
         <v>91</v>
       </c>
       <c r="Q223">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="R223">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S223">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="T223">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U223">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V223">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="W223">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X223">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y223">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z223">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AA223">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB223">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AC223">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AD223">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AE223">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF223">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="AG223">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AH223">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AI223">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AJ223">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AK223">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL223">
         <v>1.22</v>
       </c>
       <c r="AM223">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AN223">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AO223">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP223">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR223">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS223">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AT223">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="AU223">
+        <v>3</v>
+      </c>
+      <c r="AV223">
+        <v>6</v>
+      </c>
+      <c r="AW223">
+        <v>7</v>
+      </c>
+      <c r="AX223">
+        <v>4</v>
+      </c>
+      <c r="AY223">
         <v>10</v>
       </c>
-      <c r="AV223">
+      <c r="AZ223">
+        <v>10</v>
+      </c>
+      <c r="BA223">
         <v>4</v>
       </c>
-      <c r="AW223">
-        <v>4</v>
-      </c>
-      <c r="AX223">
-        <v>2</v>
-      </c>
-      <c r="AY223">
-        <v>14</v>
-      </c>
-      <c r="AZ223">
-        <v>6</v>
-      </c>
-      <c r="BA223">
-        <v>6</v>
-      </c>
       <c r="BB223">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC223">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD223">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BE223">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF223">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="BG223">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BH223">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI223">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BJ223">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="BK223">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BL223">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BM223">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BN223">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO223">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BP223">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="224" spans="1:68">
@@ -47305,7 +47305,7 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>7778299</v>
+        <v>7778295</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -47320,190 +47320,190 @@
         <v>23</v>
       </c>
       <c r="G224" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H224" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="I224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M224">
         <v>1</v>
       </c>
       <c r="N224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O224" t="s">
-        <v>91</v>
+        <v>230</v>
       </c>
       <c r="P224" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="Q224">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R224">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S224">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T224">
         <v>1.33</v>
       </c>
       <c r="U224">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V224">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="W224">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X224">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y224">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z224">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AA224">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="AB224">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="AC224">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD224">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AE224">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF224">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG224">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AH224">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AI224">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ224">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK224">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AL224">
         <v>1.25</v>
       </c>
       <c r="AM224">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AN224">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AO224">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="AP224">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR224">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AS224">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AT224">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="AU224">
         <v>7</v>
       </c>
       <c r="AV224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW224">
         <v>10</v>
       </c>
       <c r="AX224">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY224">
         <v>17</v>
       </c>
       <c r="AZ224">
+        <v>12</v>
+      </c>
+      <c r="BA224">
+        <v>7</v>
+      </c>
+      <c r="BB224">
+        <v>2</v>
+      </c>
+      <c r="BC224">
         <v>9</v>
       </c>
-      <c r="BA224">
-        <v>5</v>
-      </c>
-      <c r="BB224">
-        <v>7</v>
-      </c>
-      <c r="BC224">
-        <v>12</v>
-      </c>
       <c r="BD224">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BE224">
         <v>6.75</v>
       </c>
       <c r="BF224">
+        <v>2.3</v>
+      </c>
+      <c r="BG224">
+        <v>1.25</v>
+      </c>
+      <c r="BH224">
+        <v>3.35</v>
+      </c>
+      <c r="BI224">
+        <v>1.44</v>
+      </c>
+      <c r="BJ224">
         <v>2.48</v>
       </c>
-      <c r="BG224">
-        <v>1.19</v>
-      </c>
-      <c r="BH224">
-        <v>3.9</v>
-      </c>
-      <c r="BI224">
-        <v>1.35</v>
-      </c>
-      <c r="BJ224">
-        <v>2.8</v>
-      </c>
       <c r="BK224">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BL224">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="BM224">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="BN224">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BO224">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="BP224">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="225" spans="1:68">
@@ -47511,7 +47511,7 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>7778298</v>
+        <v>7778296</v>
       </c>
       <c r="C225" t="s">
         <v>68</v>
@@ -47526,190 +47526,190 @@
         <v>23</v>
       </c>
       <c r="G225" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H225" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K225">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M225">
         <v>1</v>
       </c>
       <c r="N225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O225" t="s">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>117</v>
       </c>
       <c r="Q225">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R225">
         <v>2.1</v>
       </c>
       <c r="S225">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="T225">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U225">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="V225">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="W225">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X225">
+        <v>7</v>
+      </c>
+      <c r="Y225">
+        <v>1.1</v>
+      </c>
+      <c r="Z225">
+        <v>2.17</v>
+      </c>
+      <c r="AA225">
+        <v>3.21</v>
+      </c>
+      <c r="AB225">
+        <v>2.87</v>
+      </c>
+      <c r="AC225">
+        <v>1.05</v>
+      </c>
+      <c r="AD225">
         <v>9</v>
       </c>
-      <c r="Y225">
-        <v>1.07</v>
-      </c>
-      <c r="Z225">
-        <v>2.11</v>
-      </c>
-      <c r="AA225">
-        <v>3.06</v>
-      </c>
-      <c r="AB225">
-        <v>3.14</v>
-      </c>
-      <c r="AC225">
-        <v>1.07</v>
-      </c>
-      <c r="AD225">
-        <v>8</v>
-      </c>
       <c r="AE225">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF225">
+        <v>3.5</v>
+      </c>
+      <c r="AG225">
+        <v>1.77</v>
+      </c>
+      <c r="AH225">
+        <v>1.93</v>
+      </c>
+      <c r="AI225">
+        <v>1.65</v>
+      </c>
+      <c r="AJ225">
+        <v>2.05</v>
+      </c>
+      <c r="AK225">
+        <v>1.4</v>
+      </c>
+      <c r="AL225">
+        <v>1.25</v>
+      </c>
+      <c r="AM225">
+        <v>1.57</v>
+      </c>
+      <c r="AN225">
+        <v>1.17</v>
+      </c>
+      <c r="AO225">
+        <v>0.5</v>
+      </c>
+      <c r="AP225">
+        <v>1.08</v>
+      </c>
+      <c r="AQ225">
+        <v>0.73</v>
+      </c>
+      <c r="AR225">
+        <v>1.25</v>
+      </c>
+      <c r="AS225">
+        <v>1.4</v>
+      </c>
+      <c r="AT225">
+        <v>2.65</v>
+      </c>
+      <c r="AU225">
+        <v>2</v>
+      </c>
+      <c r="AV225">
         <v>3</v>
       </c>
-      <c r="AG225">
-        <v>1.95</v>
-      </c>
-      <c r="AH225">
-        <v>1.75</v>
-      </c>
-      <c r="AI225">
-        <v>1.95</v>
-      </c>
-      <c r="AJ225">
-        <v>1.8</v>
-      </c>
-      <c r="AK225">
-        <v>1.25</v>
-      </c>
-      <c r="AL225">
-        <v>1.28</v>
-      </c>
-      <c r="AM225">
-        <v>1.75</v>
-      </c>
-      <c r="AN225">
-        <v>1.8</v>
-      </c>
-      <c r="AO225">
-        <v>0.73</v>
-      </c>
-      <c r="AP225">
-        <v>1.91</v>
-      </c>
-      <c r="AQ225">
-        <v>0.67</v>
-      </c>
-      <c r="AR225">
-        <v>1.63</v>
-      </c>
-      <c r="AS225">
-        <v>1.18</v>
-      </c>
-      <c r="AT225">
-        <v>2.81</v>
-      </c>
-      <c r="AU225">
+      <c r="AW225">
         <v>5</v>
       </c>
-      <c r="AV225">
-        <v>4</v>
-      </c>
-      <c r="AW225">
-        <v>10</v>
-      </c>
       <c r="AX225">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY225">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AZ225">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA225">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB225">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BC225">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD225">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BE225">
         <v>6.75</v>
       </c>
       <c r="BF225">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BG225">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BH225">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BI225">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="BJ225">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BK225">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="BL225">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="BM225">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="BN225">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BO225">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="BP225">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="226" spans="1:68">
@@ -47923,7 +47923,7 @@
         <v>226</v>
       </c>
       <c r="B227">
-        <v>7778295</v>
+        <v>7778298</v>
       </c>
       <c r="C227" t="s">
         <v>68</v>
@@ -47938,19 +47938,19 @@
         <v>23</v>
       </c>
       <c r="G227" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H227" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J227">
         <v>1</v>
       </c>
       <c r="K227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L227">
         <v>2</v>
@@ -47962,103 +47962,103 @@
         <v>3</v>
       </c>
       <c r="O227" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P227" t="s">
-        <v>122</v>
+        <v>325</v>
       </c>
       <c r="Q227">
         <v>2.75</v>
       </c>
       <c r="R227">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S227">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T227">
+        <v>1.44</v>
+      </c>
+      <c r="U227">
+        <v>2.63</v>
+      </c>
+      <c r="V227">
+        <v>3.25</v>
+      </c>
+      <c r="W227">
         <v>1.33</v>
       </c>
-      <c r="U227">
-        <v>3.25</v>
-      </c>
-      <c r="V227">
-        <v>2.63</v>
-      </c>
-      <c r="W227">
-        <v>1.44</v>
-      </c>
       <c r="X227">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Y227">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z227">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AA227">
-        <v>3.41</v>
+        <v>3.06</v>
       </c>
       <c r="AB227">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AC227">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD227">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AE227">
+        <v>1.38</v>
+      </c>
+      <c r="AF227">
+        <v>3</v>
+      </c>
+      <c r="AG227">
+        <v>1.95</v>
+      </c>
+      <c r="AH227">
+        <v>1.75</v>
+      </c>
+      <c r="AI227">
+        <v>1.95</v>
+      </c>
+      <c r="AJ227">
+        <v>1.8</v>
+      </c>
+      <c r="AK227">
         <v>1.25</v>
       </c>
-      <c r="AF227">
-        <v>3.8</v>
-      </c>
-      <c r="AG227">
-        <v>1.77</v>
-      </c>
-      <c r="AH227">
-        <v>1.93</v>
-      </c>
-      <c r="AI227">
-        <v>1.67</v>
-      </c>
-      <c r="AJ227">
-        <v>2.1</v>
-      </c>
-      <c r="AK227">
-        <v>1.35</v>
-      </c>
       <c r="AL227">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM227">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AN227">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AO227">
-        <v>1.5</v>
+        <v>0.73</v>
       </c>
       <c r="AP227">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AQ227">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
       <c r="AR227">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AS227">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AT227">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="AU227">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV227">
         <v>4</v>
@@ -48070,58 +48070,58 @@
         <v>8</v>
       </c>
       <c r="AY227">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ227">
         <v>12</v>
       </c>
       <c r="BA227">
+        <v>6</v>
+      </c>
+      <c r="BB227">
         <v>7</v>
       </c>
-      <c r="BB227">
-        <v>2</v>
-      </c>
       <c r="BC227">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD227">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BE227">
         <v>6.75</v>
       </c>
       <c r="BF227">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BG227">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BH227">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BI227">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BJ227">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="BK227">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="BL227">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BM227">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="BN227">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="BO227">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP227">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="228" spans="1:68">
@@ -48129,7 +48129,7 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>7778293</v>
+        <v>7778299</v>
       </c>
       <c r="C228" t="s">
         <v>68</v>
@@ -48144,10 +48144,10 @@
         <v>23</v>
       </c>
       <c r="G228" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H228" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -48159,175 +48159,175 @@
         <v>0</v>
       </c>
       <c r="L228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N228">
         <v>1</v>
       </c>
       <c r="O228" t="s">
-        <v>216</v>
+        <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="Q228">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="R228">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S228">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="T228">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U228">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V228">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="W228">
+        <v>1.5</v>
+      </c>
+      <c r="X228">
+        <v>6</v>
+      </c>
+      <c r="Y228">
+        <v>1.12</v>
+      </c>
+      <c r="Z228">
+        <v>2.21</v>
+      </c>
+      <c r="AA228">
+        <v>3.35</v>
+      </c>
+      <c r="AB228">
+        <v>2.71</v>
+      </c>
+      <c r="AC228">
+        <v>1.04</v>
+      </c>
+      <c r="AD228">
+        <v>10</v>
+      </c>
+      <c r="AE228">
+        <v>1.22</v>
+      </c>
+      <c r="AF228">
+        <v>4.2</v>
+      </c>
+      <c r="AG228">
+        <v>1.61</v>
+      </c>
+      <c r="AH228">
+        <v>2.17</v>
+      </c>
+      <c r="AI228">
+        <v>1.53</v>
+      </c>
+      <c r="AJ228">
+        <v>2.3</v>
+      </c>
+      <c r="AK228">
         <v>1.42</v>
       </c>
-      <c r="X228">
+      <c r="AL228">
+        <v>1.25</v>
+      </c>
+      <c r="AM228">
+        <v>1.57</v>
+      </c>
+      <c r="AN228">
+        <v>1.91</v>
+      </c>
+      <c r="AO228">
+        <v>0.83</v>
+      </c>
+      <c r="AP228">
+        <v>1.75</v>
+      </c>
+      <c r="AQ228">
+        <v>1</v>
+      </c>
+      <c r="AR228">
+        <v>1.88</v>
+      </c>
+      <c r="AS228">
+        <v>1.57</v>
+      </c>
+      <c r="AT228">
+        <v>3.45</v>
+      </c>
+      <c r="AU228">
         <v>7</v>
       </c>
-      <c r="Y228">
-        <v>1.1</v>
-      </c>
-      <c r="Z228">
-        <v>1.62</v>
-      </c>
-      <c r="AA228">
-        <v>3.75</v>
-      </c>
-      <c r="AB228">
-        <v>4.2</v>
-      </c>
-      <c r="AC228">
-        <v>1.05</v>
-      </c>
-      <c r="AD228">
-        <v>9.5</v>
-      </c>
-      <c r="AE228">
-        <v>1.28</v>
-      </c>
-      <c r="AF228">
-        <v>3.55</v>
-      </c>
-      <c r="AG228">
-        <v>1.79</v>
-      </c>
-      <c r="AH228">
-        <v>1.91</v>
-      </c>
-      <c r="AI228">
-        <v>1.77</v>
-      </c>
-      <c r="AJ228">
-        <v>1.91</v>
-      </c>
-      <c r="AK228">
-        <v>1.2</v>
-      </c>
-      <c r="AL228">
-        <v>1.22</v>
-      </c>
-      <c r="AM228">
-        <v>2</v>
-      </c>
-      <c r="AN228">
-        <v>1.6</v>
-      </c>
-      <c r="AO228">
-        <v>1</v>
-      </c>
-      <c r="AP228">
-        <v>1.73</v>
-      </c>
-      <c r="AQ228">
-        <v>0.92</v>
-      </c>
-      <c r="AR228">
-        <v>1.58</v>
-      </c>
-      <c r="AS228">
-        <v>1.23</v>
-      </c>
-      <c r="AT228">
-        <v>2.81</v>
-      </c>
-      <c r="AU228">
-        <v>3</v>
-      </c>
       <c r="AV228">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW228">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX228">
         <v>4</v>
       </c>
       <c r="AY228">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ228">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB228">
         <v>7</v>
       </c>
       <c r="BC228">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD228">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BE228">
         <v>6.75</v>
       </c>
       <c r="BF228">
+        <v>2.48</v>
+      </c>
+      <c r="BG228">
+        <v>1.19</v>
+      </c>
+      <c r="BH228">
+        <v>3.9</v>
+      </c>
+      <c r="BI228">
+        <v>1.35</v>
+      </c>
+      <c r="BJ228">
         <v>2.8</v>
       </c>
-      <c r="BG228">
-        <v>1.24</v>
-      </c>
-      <c r="BH228">
-        <v>3.4</v>
-      </c>
-      <c r="BI228">
-        <v>1.44</v>
-      </c>
-      <c r="BJ228">
-        <v>2.48</v>
-      </c>
       <c r="BK228">
+        <v>1.6</v>
+      </c>
+      <c r="BL228">
+        <v>2.12</v>
+      </c>
+      <c r="BM228">
+        <v>1.94</v>
+      </c>
+      <c r="BN228">
         <v>1.71</v>
       </c>
-      <c r="BL228">
-        <v>1.94</v>
-      </c>
-      <c r="BM228">
-        <v>2.12</v>
-      </c>
-      <c r="BN228">
-        <v>1.6</v>
-      </c>
       <c r="BO228">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="BP228">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="229" spans="1:68">
@@ -48335,7 +48335,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>7778296</v>
+        <v>7778300</v>
       </c>
       <c r="C229" t="s">
         <v>68</v>
@@ -48350,190 +48350,190 @@
         <v>23</v>
       </c>
       <c r="G229" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H229" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229">
         <v>0</v>
       </c>
       <c r="K229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N229">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O229" t="s">
+        <v>232</v>
+      </c>
+      <c r="P229" t="s">
         <v>91</v>
       </c>
-      <c r="P229" t="s">
-        <v>117</v>
-      </c>
       <c r="Q229">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="R229">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S229">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="T229">
         <v>1.36</v>
       </c>
       <c r="U229">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="V229">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="W229">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="X229">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y229">
+        <v>1.03</v>
+      </c>
+      <c r="Z229">
+        <v>1.36</v>
+      </c>
+      <c r="AA229">
+        <v>4.5</v>
+      </c>
+      <c r="AB229">
+        <v>6.2</v>
+      </c>
+      <c r="AC229">
+        <v>1</v>
+      </c>
+      <c r="AD229">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE229">
+        <v>1.29</v>
+      </c>
+      <c r="AF229">
+        <v>3.12</v>
+      </c>
+      <c r="AG229">
+        <v>1.95</v>
+      </c>
+      <c r="AH229">
+        <v>1.75</v>
+      </c>
+      <c r="AI229">
+        <v>2.12</v>
+      </c>
+      <c r="AJ229">
+        <v>1.64</v>
+      </c>
+      <c r="AK229">
         <v>1.1</v>
       </c>
-      <c r="Z229">
-        <v>2.17</v>
-      </c>
-      <c r="AA229">
-        <v>3.21</v>
-      </c>
-      <c r="AB229">
-        <v>2.87</v>
-      </c>
-      <c r="AC229">
-        <v>1.05</v>
-      </c>
-      <c r="AD229">
-        <v>9</v>
-      </c>
-      <c r="AE229">
-        <v>1.28</v>
-      </c>
-      <c r="AF229">
-        <v>3.5</v>
-      </c>
-      <c r="AG229">
-        <v>1.77</v>
-      </c>
-      <c r="AH229">
-        <v>1.93</v>
-      </c>
-      <c r="AI229">
-        <v>1.65</v>
-      </c>
-      <c r="AJ229">
-        <v>2.05</v>
-      </c>
-      <c r="AK229">
-        <v>1.4</v>
-      </c>
       <c r="AL229">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM229">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="AN229">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AO229">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="AP229">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ229">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AR229">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AS229">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AT229">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
       <c r="AU229">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AV229">
+        <v>4</v>
+      </c>
+      <c r="AW229">
+        <v>4</v>
+      </c>
+      <c r="AX229">
+        <v>2</v>
+      </c>
+      <c r="AY229">
+        <v>14</v>
+      </c>
+      <c r="AZ229">
+        <v>6</v>
+      </c>
+      <c r="BA229">
+        <v>6</v>
+      </c>
+      <c r="BB229">
         <v>3</v>
-      </c>
-      <c r="AW229">
-        <v>5</v>
-      </c>
-      <c r="AX229">
-        <v>11</v>
-      </c>
-      <c r="AY229">
-        <v>7</v>
-      </c>
-      <c r="AZ229">
-        <v>14</v>
-      </c>
-      <c r="BA229">
-        <v>7</v>
-      </c>
-      <c r="BB229">
-        <v>2</v>
       </c>
       <c r="BC229">
         <v>9</v>
       </c>
       <c r="BD229">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="BE229">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF229">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG229">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BH229">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BI229">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BJ229">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BK229">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="BL229">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="BM229">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BN229">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO229">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="BP229">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="230" spans="1:68">
@@ -48685,13 +48685,13 @@
         <v>11</v>
       </c>
       <c r="AX230">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY230">
         <v>17</v>
       </c>
       <c r="AZ230">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA230">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,18 @@
     <t>['14', '42', '89']</t>
   </si>
   <si>
+    <t>['5', '39', '90+4']</t>
+  </si>
+  <si>
+    <t>['59', '72']</t>
+  </si>
+  <si>
+    <t>['35', '45+2', '90+4']</t>
+  </si>
+  <si>
+    <t>['45+3', '57']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -998,6 +1010,18 @@
   </si>
   <si>
     <t>['6', '47', '73']</t>
+  </si>
+  <si>
+    <t>['43', '76']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['2', '48']</t>
+  </si>
+  <si>
+    <t>['30', '64']</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1639,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1693,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ2">
         <v>1.08</v>
@@ -1902,7 +1926,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2517,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6">
         <v>1.67</v>
@@ -2723,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>0.67</v>
@@ -2932,7 +2956,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ8">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3263,7 +3287,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3344,7 +3368,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3469,7 +3493,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3547,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
         <v>0.92</v>
@@ -3675,7 +3699,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3756,7 +3780,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3881,7 +3905,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3962,7 +3986,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4371,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4705,7 +4729,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4911,7 +4935,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -4989,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ18">
         <v>1.3</v>
@@ -5198,7 +5222,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5401,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5735,7 +5759,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5816,7 +5840,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ22">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR22">
         <v>0.91</v>
@@ -6019,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6147,7 +6171,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6431,10 +6455,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6765,7 +6789,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6843,7 +6867,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ27">
         <v>0.67</v>
@@ -6971,7 +6995,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7258,7 +7282,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR29">
         <v>1.17</v>
@@ -7383,7 +7407,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7667,10 +7691,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR31">
         <v>1.14</v>
@@ -7795,7 +7819,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7873,7 +7897,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8079,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ33">
         <v>0.92</v>
@@ -8413,7 +8437,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8619,7 +8643,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8697,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8825,7 +8849,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8903,7 +8927,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37">
         <v>1.08</v>
@@ -9031,7 +9055,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9112,7 +9136,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR38">
         <v>1.35</v>
@@ -9315,7 +9339,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>0.92</v>
@@ -9524,7 +9548,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR40">
         <v>1.25</v>
@@ -9649,7 +9673,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9730,7 +9754,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ41">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR41">
         <v>0</v>
@@ -10061,7 +10085,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10139,7 +10163,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10345,7 +10369,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ44">
         <v>0.92</v>
@@ -10679,7 +10703,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10760,7 +10784,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10885,7 +10909,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -10966,7 +10990,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR47">
         <v>1.63</v>
@@ -11091,7 +11115,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11915,7 +11939,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11993,10 +12017,10 @@
         <v>0.33</v>
       </c>
       <c r="AP52">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ52">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12327,7 +12351,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12405,7 +12429,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ54">
         <v>1.67</v>
@@ -12611,7 +12635,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12817,10 +12841,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.66</v>
@@ -13026,7 +13050,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR57">
         <v>1.46</v>
@@ -13229,7 +13253,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ58">
         <v>0.82</v>
@@ -13357,7 +13381,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13438,7 +13462,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR59">
         <v>1.93</v>
@@ -13563,7 +13587,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -13847,7 +13871,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ61">
         <v>0.73</v>
@@ -14053,7 +14077,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14387,7 +14411,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -14465,7 +14489,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14674,7 +14698,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR65">
         <v>1.08</v>
@@ -14880,7 +14904,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15083,10 +15107,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ67">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR67">
         <v>1.72</v>
@@ -15211,7 +15235,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15292,7 +15316,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR68">
         <v>1.51</v>
@@ -15417,7 +15441,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15498,7 +15522,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR69">
         <v>1.38</v>
@@ -15829,7 +15853,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -16113,10 +16137,10 @@
         <v>2.5</v>
       </c>
       <c r="AP72">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ72">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR72">
         <v>1.64</v>
@@ -16322,7 +16346,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ73">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR73">
         <v>1.21</v>
@@ -16731,7 +16755,7 @@
         <v>2</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75">
         <v>1.3</v>
@@ -17065,7 +17089,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17143,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ77">
         <v>0.92</v>
@@ -17352,7 +17376,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ78">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR78">
         <v>1.29</v>
@@ -17477,7 +17501,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17761,7 +17785,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17967,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81">
         <v>0.92</v>
@@ -18301,7 +18325,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18382,7 +18406,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18919,7 +18943,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18997,7 +19021,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ86">
         <v>1.67</v>
@@ -19331,7 +19355,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19412,7 +19436,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19743,7 +19767,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20030,7 +20054,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR91">
         <v>1.32</v>
@@ -20155,7 +20179,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20439,10 +20463,10 @@
         <v>1.8</v>
       </c>
       <c r="AP93">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.39</v>
@@ -20645,10 +20669,10 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ94">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR94">
         <v>1.55</v>
@@ -20773,7 +20797,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21057,10 +21081,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ96">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR96">
         <v>1.47</v>
@@ -21597,7 +21621,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21881,10 +21905,10 @@
         <v>0.33</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ100">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR100">
         <v>1.56</v>
@@ -22009,7 +22033,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22087,7 +22111,7 @@
         <v>0.8</v>
       </c>
       <c r="AP101">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ101">
         <v>0.92</v>
@@ -22215,7 +22239,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22296,7 +22320,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
         <v>1.55</v>
@@ -22421,7 +22445,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22627,7 +22651,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22705,7 +22729,7 @@
         <v>1.67</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ104">
         <v>1.67</v>
@@ -23039,7 +23063,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23117,7 +23141,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106">
         <v>1.36</v>
@@ -23245,7 +23269,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23323,7 +23347,7 @@
         <v>2.25</v>
       </c>
       <c r="AP107">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ107">
         <v>1.3</v>
@@ -23451,7 +23475,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -23532,7 +23556,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ108">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR108">
         <v>1.41</v>
@@ -23738,7 +23762,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR109">
         <v>1.57</v>
@@ -24069,7 +24093,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24150,7 +24174,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR111">
         <v>1.52</v>
@@ -24765,7 +24789,7 @@
         <v>0.8</v>
       </c>
       <c r="AP114">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -24893,7 +24917,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25099,7 +25123,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25180,7 +25204,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ116">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR116">
         <v>1.54</v>
@@ -25589,10 +25613,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ118">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR118">
         <v>1.72</v>
@@ -25798,7 +25822,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ119">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR119">
         <v>1.43</v>
@@ -26129,7 +26153,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26335,7 +26359,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26541,7 +26565,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26747,7 +26771,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27031,7 +27055,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27159,7 +27183,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27240,7 +27264,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ126">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR126">
         <v>1.31</v>
@@ -27443,7 +27467,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27777,7 +27801,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -27858,7 +27882,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ129">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR129">
         <v>2.07</v>
@@ -28189,7 +28213,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28267,10 +28291,10 @@
         <v>0.14</v>
       </c>
       <c r="AP131">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ131">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR131">
         <v>1.34</v>
@@ -28395,7 +28419,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28473,7 +28497,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132">
         <v>0.92</v>
@@ -28885,7 +28909,7 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29091,10 +29115,10 @@
         <v>2.29</v>
       </c>
       <c r="AP135">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ135">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR135">
         <v>1.68</v>
@@ -29425,7 +29449,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29631,7 +29655,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30043,7 +30067,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30739,10 +30763,10 @@
         <v>0.4</v>
       </c>
       <c r="AP143">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR143">
         <v>1.48</v>
@@ -30867,7 +30891,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -31154,7 +31178,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ145">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR145">
         <v>1.48</v>
@@ -31566,7 +31590,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ147">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR147">
         <v>1.43</v>
@@ -31897,7 +31921,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31975,10 +31999,10 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ149">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR149">
         <v>1.3</v>
@@ -32181,10 +32205,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ150">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR150">
         <v>1.64</v>
@@ -32309,7 +32333,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32390,7 +32414,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ151">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32515,7 +32539,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -32593,7 +32617,7 @@
         <v>1</v>
       </c>
       <c r="AP152">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ152">
         <v>0.82</v>
@@ -32799,10 +32823,10 @@
         <v>1.17</v>
       </c>
       <c r="AP153">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ153">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR153">
         <v>1.59</v>
@@ -33133,7 +33157,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33211,7 +33235,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33339,7 +33363,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33417,10 +33441,10 @@
         <v>2.14</v>
       </c>
       <c r="AP156">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ156">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR156">
         <v>1.35</v>
@@ -33545,7 +33569,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33626,7 +33650,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ157">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR157">
         <v>1.64</v>
@@ -33751,7 +33775,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33829,7 +33853,7 @@
         <v>1.78</v>
       </c>
       <c r="AP158">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ158">
         <v>1.67</v>
@@ -33957,7 +33981,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34244,7 +34268,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ160">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR160">
         <v>1.42</v>
@@ -34575,7 +34599,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34656,7 +34680,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ162">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34859,7 +34883,7 @@
         <v>1.25</v>
       </c>
       <c r="AP163">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ163">
         <v>0.92</v>
@@ -35068,7 +35092,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR164">
         <v>1.47</v>
@@ -35193,7 +35217,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35683,7 +35707,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ167">
         <v>0.67</v>
@@ -35811,7 +35835,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -36017,7 +36041,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36095,10 +36119,10 @@
         <v>1.67</v>
       </c>
       <c r="AP169">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ169">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR169">
         <v>1.38</v>
@@ -36635,7 +36659,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -36713,10 +36737,10 @@
         <v>1.89</v>
       </c>
       <c r="AP172">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ172">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR172">
         <v>1.66</v>
@@ -36919,7 +36943,7 @@
         <v>1.71</v>
       </c>
       <c r="AP173">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>1.36</v>
@@ -37128,7 +37152,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ174">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR174">
         <v>1.27</v>
@@ -37331,7 +37355,7 @@
         <v>1.22</v>
       </c>
       <c r="AP175">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37459,7 +37483,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37537,10 +37561,10 @@
         <v>1.86</v>
       </c>
       <c r="AP176">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ176">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR176">
         <v>1.33</v>
@@ -37743,7 +37767,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ177">
         <v>1.67</v>
@@ -37871,7 +37895,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -37952,7 +37976,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ178">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR178">
         <v>1.49</v>
@@ -38077,7 +38101,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38695,7 +38719,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -39107,7 +39131,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39188,7 +39212,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ184">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR184">
         <v>1.55</v>
@@ -39313,7 +39337,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39394,7 +39418,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ185">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR185">
         <v>1.69</v>
@@ -39519,7 +39543,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39597,7 +39621,7 @@
         <v>1.5</v>
       </c>
       <c r="AP186">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ186">
         <v>1.36</v>
@@ -39931,7 +39955,7 @@
         <v>149</v>
       </c>
       <c r="P188" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40137,7 +40161,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40424,7 +40448,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ190">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR190">
         <v>1.47</v>
@@ -40549,7 +40573,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40630,7 +40654,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ191">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR191">
         <v>1.45</v>
@@ -40833,10 +40857,10 @@
         <v>1.63</v>
       </c>
       <c r="AP192">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ192">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR192">
         <v>1.59</v>
@@ -40961,7 +40985,7 @@
         <v>91</v>
       </c>
       <c r="P193" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q193">
         <v>4</v>
@@ -41042,7 +41066,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ193">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR193">
         <v>1.3</v>
@@ -41167,7 +41191,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41451,7 +41475,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ195">
         <v>0.73</v>
@@ -41660,7 +41684,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ196">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR196">
         <v>1.8</v>
@@ -41785,7 +41809,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q197">
         <v>3.3</v>
@@ -41863,7 +41887,7 @@
         <v>1.11</v>
       </c>
       <c r="AP197">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ197">
         <v>1.3</v>
@@ -41991,7 +42015,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q198">
         <v>4</v>
@@ -42069,10 +42093,10 @@
         <v>1.9</v>
       </c>
       <c r="AP198">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ198">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR198">
         <v>1.39</v>
@@ -42275,7 +42299,7 @@
         <v>0.9</v>
       </c>
       <c r="AP199">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ199">
         <v>1</v>
@@ -42403,7 +42427,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q200">
         <v>3.1</v>
@@ -42609,7 +42633,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q201">
         <v>2.75</v>
@@ -42815,7 +42839,7 @@
         <v>220</v>
       </c>
       <c r="P202" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q202">
         <v>2.65</v>
@@ -43021,7 +43045,7 @@
         <v>91</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43099,7 +43123,7 @@
         <v>0.67</v>
       </c>
       <c r="AP203">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ203">
         <v>1.09</v>
@@ -43227,7 +43251,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q204">
         <v>2.8</v>
@@ -43433,7 +43457,7 @@
         <v>221</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>2.7</v>
@@ -43639,7 +43663,7 @@
         <v>167</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q206">
         <v>3</v>
@@ -43720,7 +43744,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ206">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR206">
         <v>1.68</v>
@@ -43845,7 +43869,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -43926,7 +43950,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ207">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR207">
         <v>1.3</v>
@@ -44129,7 +44153,7 @@
         <v>0.89</v>
       </c>
       <c r="AP208">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ208">
         <v>0.92</v>
@@ -44463,7 +44487,7 @@
         <v>91</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q210">
         <v>2.92</v>
@@ -44541,7 +44565,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ210">
         <v>0.92</v>
@@ -44669,7 +44693,7 @@
         <v>224</v>
       </c>
       <c r="P211" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q211">
         <v>2.5</v>
@@ -44747,7 +44771,7 @@
         <v>0.9</v>
       </c>
       <c r="AP211">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ211">
         <v>1.09</v>
@@ -44875,7 +44899,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q212">
         <v>3.5</v>
@@ -44953,10 +44977,10 @@
         <v>2</v>
       </c>
       <c r="AP212">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ212">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR212">
         <v>1.47</v>
@@ -45081,7 +45105,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q213">
         <v>3</v>
@@ -45162,7 +45186,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ213">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR213">
         <v>1.44</v>
@@ -45574,7 +45598,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ215">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR215">
         <v>1.54</v>
@@ -45699,7 +45723,7 @@
         <v>227</v>
       </c>
       <c r="P216" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q216">
         <v>3.18</v>
@@ -45905,7 +45929,7 @@
         <v>128</v>
       </c>
       <c r="P217" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q217">
         <v>2.7</v>
@@ -45986,7 +46010,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ217">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR217">
         <v>1.69</v>
@@ -46189,10 +46213,10 @@
         <v>1.6</v>
       </c>
       <c r="AP218">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ218">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR218">
         <v>1.32</v>
@@ -46317,7 +46341,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46395,10 +46419,10 @@
         <v>1.91</v>
       </c>
       <c r="AP219">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ219">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR219">
         <v>1.47</v>
@@ -46604,7 +46628,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ220">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR220">
         <v>1.8</v>
@@ -46935,7 +46959,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q222">
         <v>4.95</v>
@@ -47013,10 +47037,10 @@
         <v>1.55</v>
       </c>
       <c r="AP222">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ222">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR222">
         <v>1.62</v>
@@ -47965,7 +47989,7 @@
         <v>231</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q227">
         <v>2.75</v>
@@ -48583,7 +48607,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q230">
         <v>3.2</v>
@@ -48789,7 +48813,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q231">
         <v>3.35</v>
@@ -48945,6 +48969,1448 @@
         <v>2.45</v>
       </c>
       <c r="BP231">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7778303</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45858.25</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>86</v>
+      </c>
+      <c r="H232" t="s">
+        <v>81</v>
+      </c>
+      <c r="I232">
+        <v>2</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>3</v>
+      </c>
+      <c r="L232">
+        <v>3</v>
+      </c>
+      <c r="M232">
+        <v>2</v>
+      </c>
+      <c r="N232">
+        <v>5</v>
+      </c>
+      <c r="O232" t="s">
+        <v>235</v>
+      </c>
+      <c r="P232" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q232">
+        <v>3.2</v>
+      </c>
+      <c r="R232">
+        <v>2.2</v>
+      </c>
+      <c r="S232">
+        <v>3.25</v>
+      </c>
+      <c r="T232">
+        <v>1.4</v>
+      </c>
+      <c r="U232">
+        <v>2.75</v>
+      </c>
+      <c r="V232">
+        <v>2.75</v>
+      </c>
+      <c r="W232">
+        <v>1.4</v>
+      </c>
+      <c r="X232">
+        <v>8</v>
+      </c>
+      <c r="Y232">
+        <v>1.08</v>
+      </c>
+      <c r="Z232">
+        <v>2.48</v>
+      </c>
+      <c r="AA232">
+        <v>3.19</v>
+      </c>
+      <c r="AB232">
+        <v>2.49</v>
+      </c>
+      <c r="AC232">
+        <v>1.06</v>
+      </c>
+      <c r="AD232">
+        <v>8.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.33</v>
+      </c>
+      <c r="AF232">
+        <v>3.25</v>
+      </c>
+      <c r="AG232">
+        <v>1.89</v>
+      </c>
+      <c r="AH232">
+        <v>1.81</v>
+      </c>
+      <c r="AI232">
+        <v>1.7</v>
+      </c>
+      <c r="AJ232">
+        <v>2.05</v>
+      </c>
+      <c r="AK232">
+        <v>1.46</v>
+      </c>
+      <c r="AL232">
+        <v>1.31</v>
+      </c>
+      <c r="AM232">
+        <v>1.47</v>
+      </c>
+      <c r="AN232">
+        <v>2.17</v>
+      </c>
+      <c r="AO232">
+        <v>2.08</v>
+      </c>
+      <c r="AP232">
+        <v>2.23</v>
+      </c>
+      <c r="AQ232">
+        <v>1.92</v>
+      </c>
+      <c r="AR232">
+        <v>1.62</v>
+      </c>
+      <c r="AS232">
+        <v>1.46</v>
+      </c>
+      <c r="AT232">
+        <v>3.08</v>
+      </c>
+      <c r="AU232">
+        <v>4</v>
+      </c>
+      <c r="AV232">
+        <v>5</v>
+      </c>
+      <c r="AW232">
+        <v>3</v>
+      </c>
+      <c r="AX232">
+        <v>14</v>
+      </c>
+      <c r="AY232">
+        <v>7</v>
+      </c>
+      <c r="AZ232">
+        <v>19</v>
+      </c>
+      <c r="BA232">
+        <v>0</v>
+      </c>
+      <c r="BB232">
+        <v>2</v>
+      </c>
+      <c r="BC232">
+        <v>2</v>
+      </c>
+      <c r="BD232">
+        <v>2.06</v>
+      </c>
+      <c r="BE232">
+        <v>8.5</v>
+      </c>
+      <c r="BF232">
+        <v>2.08</v>
+      </c>
+      <c r="BG232">
+        <v>1.19</v>
+      </c>
+      <c r="BH232">
+        <v>3.82</v>
+      </c>
+      <c r="BI232">
+        <v>1.39</v>
+      </c>
+      <c r="BJ232">
+        <v>2.67</v>
+      </c>
+      <c r="BK232">
+        <v>1.7</v>
+      </c>
+      <c r="BL232">
+        <v>2.03</v>
+      </c>
+      <c r="BM232">
+        <v>2.14</v>
+      </c>
+      <c r="BN232">
+        <v>1.6</v>
+      </c>
+      <c r="BO232">
+        <v>2.78</v>
+      </c>
+      <c r="BP232">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7778305</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45858.25</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>79</v>
+      </c>
+      <c r="H233" t="s">
+        <v>78</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>1</v>
+      </c>
+      <c r="O233" t="s">
+        <v>91</v>
+      </c>
+      <c r="P233" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q233">
+        <v>5</v>
+      </c>
+      <c r="R233">
+        <v>1.95</v>
+      </c>
+      <c r="S233">
+        <v>2.75</v>
+      </c>
+      <c r="T233">
+        <v>1.53</v>
+      </c>
+      <c r="U233">
+        <v>2.38</v>
+      </c>
+      <c r="V233">
+        <v>3.75</v>
+      </c>
+      <c r="W233">
+        <v>1.25</v>
+      </c>
+      <c r="X233">
+        <v>11</v>
+      </c>
+      <c r="Y233">
+        <v>1.05</v>
+      </c>
+      <c r="Z233">
+        <v>3.81</v>
+      </c>
+      <c r="AA233">
+        <v>2.93</v>
+      </c>
+      <c r="AB233">
+        <v>1.94</v>
+      </c>
+      <c r="AC233">
+        <v>1.11</v>
+      </c>
+      <c r="AD233">
+        <v>6.25</v>
+      </c>
+      <c r="AE233">
+        <v>1.48</v>
+      </c>
+      <c r="AF233">
+        <v>2.37</v>
+      </c>
+      <c r="AG233">
+        <v>2.5</v>
+      </c>
+      <c r="AH233">
+        <v>1.46</v>
+      </c>
+      <c r="AI233">
+        <v>2.2</v>
+      </c>
+      <c r="AJ233">
+        <v>1.62</v>
+      </c>
+      <c r="AK233">
+        <v>1.73</v>
+      </c>
+      <c r="AL233">
+        <v>1.35</v>
+      </c>
+      <c r="AM233">
+        <v>1.24</v>
+      </c>
+      <c r="AN233">
+        <v>1.45</v>
+      </c>
+      <c r="AO233">
+        <v>2</v>
+      </c>
+      <c r="AP233">
+        <v>1.33</v>
+      </c>
+      <c r="AQ233">
+        <v>2.08</v>
+      </c>
+      <c r="AR233">
+        <v>1.3</v>
+      </c>
+      <c r="AS233">
+        <v>1.6</v>
+      </c>
+      <c r="AT233">
+        <v>2.9</v>
+      </c>
+      <c r="AU233">
+        <v>5</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>13</v>
+      </c>
+      <c r="AX233">
+        <v>4</v>
+      </c>
+      <c r="AY233">
+        <v>18</v>
+      </c>
+      <c r="AZ233">
+        <v>7</v>
+      </c>
+      <c r="BA233">
+        <v>4</v>
+      </c>
+      <c r="BB233">
+        <v>1</v>
+      </c>
+      <c r="BC233">
+        <v>5</v>
+      </c>
+      <c r="BD233">
+        <v>2.55</v>
+      </c>
+      <c r="BE233">
+        <v>8.5</v>
+      </c>
+      <c r="BF233">
+        <v>1.73</v>
+      </c>
+      <c r="BG233">
+        <v>1.3</v>
+      </c>
+      <c r="BH233">
+        <v>2.97</v>
+      </c>
+      <c r="BI233">
+        <v>1.57</v>
+      </c>
+      <c r="BJ233">
+        <v>2.19</v>
+      </c>
+      <c r="BK233">
+        <v>2</v>
+      </c>
+      <c r="BL233">
+        <v>1.72</v>
+      </c>
+      <c r="BM233">
+        <v>2.6</v>
+      </c>
+      <c r="BN233">
+        <v>1.41</v>
+      </c>
+      <c r="BO233">
+        <v>3.58</v>
+      </c>
+      <c r="BP233">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7778309</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45858.27083333334</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>82</v>
+      </c>
+      <c r="H234" t="s">
+        <v>73</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>236</v>
+      </c>
+      <c r="P234" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q234">
+        <v>2.7</v>
+      </c>
+      <c r="R234">
+        <v>1.98</v>
+      </c>
+      <c r="S234">
+        <v>4</v>
+      </c>
+      <c r="T234">
+        <v>1.46</v>
+      </c>
+      <c r="U234">
+        <v>2.5</v>
+      </c>
+      <c r="V234">
+        <v>3.1</v>
+      </c>
+      <c r="W234">
+        <v>1.32</v>
+      </c>
+      <c r="X234">
+        <v>8.5</v>
+      </c>
+      <c r="Y234">
+        <v>1.06</v>
+      </c>
+      <c r="Z234">
+        <v>1.98</v>
+      </c>
+      <c r="AA234">
+        <v>3.16</v>
+      </c>
+      <c r="AB234">
+        <v>3.34</v>
+      </c>
+      <c r="AC234">
+        <v>1.08</v>
+      </c>
+      <c r="AD234">
+        <v>7.25</v>
+      </c>
+      <c r="AE234">
+        <v>1.39</v>
+      </c>
+      <c r="AF234">
+        <v>2.75</v>
+      </c>
+      <c r="AG234">
+        <v>2.2</v>
+      </c>
+      <c r="AH234">
+        <v>1.59</v>
+      </c>
+      <c r="AI234">
+        <v>1.95</v>
+      </c>
+      <c r="AJ234">
+        <v>1.73</v>
+      </c>
+      <c r="AK234">
+        <v>1.27</v>
+      </c>
+      <c r="AL234">
+        <v>1.32</v>
+      </c>
+      <c r="AM234">
+        <v>1.71</v>
+      </c>
+      <c r="AN234">
+        <v>1.45</v>
+      </c>
+      <c r="AO234">
+        <v>0.5</v>
+      </c>
+      <c r="AP234">
+        <v>1.58</v>
+      </c>
+      <c r="AQ234">
+        <v>0.45</v>
+      </c>
+      <c r="AR234">
+        <v>1.46</v>
+      </c>
+      <c r="AS234">
+        <v>1.23</v>
+      </c>
+      <c r="AT234">
+        <v>2.69</v>
+      </c>
+      <c r="AU234">
+        <v>3</v>
+      </c>
+      <c r="AV234">
+        <v>5</v>
+      </c>
+      <c r="AW234">
+        <v>4</v>
+      </c>
+      <c r="AX234">
+        <v>3</v>
+      </c>
+      <c r="AY234">
+        <v>7</v>
+      </c>
+      <c r="AZ234">
+        <v>8</v>
+      </c>
+      <c r="BA234">
+        <v>8</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>10</v>
+      </c>
+      <c r="BD234">
+        <v>1.85</v>
+      </c>
+      <c r="BE234">
+        <v>8.5</v>
+      </c>
+      <c r="BF234">
+        <v>2.35</v>
+      </c>
+      <c r="BG234">
+        <v>1.25</v>
+      </c>
+      <c r="BH234">
+        <v>3.28</v>
+      </c>
+      <c r="BI234">
+        <v>1.48</v>
+      </c>
+      <c r="BJ234">
+        <v>2.4</v>
+      </c>
+      <c r="BK234">
+        <v>1.85</v>
+      </c>
+      <c r="BL234">
+        <v>1.85</v>
+      </c>
+      <c r="BM234">
+        <v>2.38</v>
+      </c>
+      <c r="BN234">
+        <v>1.49</v>
+      </c>
+      <c r="BO234">
+        <v>3.14</v>
+      </c>
+      <c r="BP234">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7778306</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>75</v>
+      </c>
+      <c r="H235" t="s">
+        <v>80</v>
+      </c>
+      <c r="I235">
+        <v>2</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>2</v>
+      </c>
+      <c r="L235">
+        <v>3</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>3</v>
+      </c>
+      <c r="O235" t="s">
+        <v>237</v>
+      </c>
+      <c r="P235" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q235">
+        <v>3.4</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>2.95</v>
+      </c>
+      <c r="T235">
+        <v>1.41</v>
+      </c>
+      <c r="U235">
+        <v>2.65</v>
+      </c>
+      <c r="V235">
+        <v>2.85</v>
+      </c>
+      <c r="W235">
+        <v>1.37</v>
+      </c>
+      <c r="X235">
+        <v>7.5</v>
+      </c>
+      <c r="Y235">
+        <v>1.08</v>
+      </c>
+      <c r="Z235">
+        <v>2.79</v>
+      </c>
+      <c r="AA235">
+        <v>3.08</v>
+      </c>
+      <c r="AB235">
+        <v>2.29</v>
+      </c>
+      <c r="AC235">
+        <v>1.06</v>
+      </c>
+      <c r="AD235">
+        <v>8.25</v>
+      </c>
+      <c r="AE235">
+        <v>1.32</v>
+      </c>
+      <c r="AF235">
+        <v>3.1</v>
+      </c>
+      <c r="AG235">
+        <v>1.96</v>
+      </c>
+      <c r="AH235">
+        <v>1.74</v>
+      </c>
+      <c r="AI235">
+        <v>1.78</v>
+      </c>
+      <c r="AJ235">
+        <v>1.9</v>
+      </c>
+      <c r="AK235">
+        <v>1.53</v>
+      </c>
+      <c r="AL235">
+        <v>1.32</v>
+      </c>
+      <c r="AM235">
+        <v>1.4</v>
+      </c>
+      <c r="AN235">
+        <v>0.83</v>
+      </c>
+      <c r="AO235">
+        <v>0.75</v>
+      </c>
+      <c r="AP235">
+        <v>1</v>
+      </c>
+      <c r="AQ235">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR235">
+        <v>1.39</v>
+      </c>
+      <c r="AS235">
+        <v>1.24</v>
+      </c>
+      <c r="AT235">
+        <v>2.63</v>
+      </c>
+      <c r="AU235">
+        <v>6</v>
+      </c>
+      <c r="AV235">
+        <v>5</v>
+      </c>
+      <c r="AW235">
+        <v>3</v>
+      </c>
+      <c r="AX235">
+        <v>11</v>
+      </c>
+      <c r="AY235">
+        <v>9</v>
+      </c>
+      <c r="AZ235">
+        <v>16</v>
+      </c>
+      <c r="BA235">
+        <v>7</v>
+      </c>
+      <c r="BB235">
+        <v>6</v>
+      </c>
+      <c r="BC235">
+        <v>13</v>
+      </c>
+      <c r="BD235">
+        <v>1.89</v>
+      </c>
+      <c r="BE235">
+        <v>8.5</v>
+      </c>
+      <c r="BF235">
+        <v>2.32</v>
+      </c>
+      <c r="BG235">
+        <v>1.17</v>
+      </c>
+      <c r="BH235">
+        <v>3.94</v>
+      </c>
+      <c r="BI235">
+        <v>1.37</v>
+      </c>
+      <c r="BJ235">
+        <v>2.75</v>
+      </c>
+      <c r="BK235">
+        <v>1.67</v>
+      </c>
+      <c r="BL235">
+        <v>2.08</v>
+      </c>
+      <c r="BM235">
+        <v>2.07</v>
+      </c>
+      <c r="BN235">
+        <v>1.64</v>
+      </c>
+      <c r="BO235">
+        <v>2.7</v>
+      </c>
+      <c r="BP235">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7778308</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>88</v>
+      </c>
+      <c r="H236" t="s">
+        <v>87</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>2</v>
+      </c>
+      <c r="N236">
+        <v>2</v>
+      </c>
+      <c r="O236" t="s">
+        <v>91</v>
+      </c>
+      <c r="P236" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q236">
+        <v>4.75</v>
+      </c>
+      <c r="R236">
+        <v>2.2</v>
+      </c>
+      <c r="S236">
+        <v>2.4</v>
+      </c>
+      <c r="T236">
+        <v>1.4</v>
+      </c>
+      <c r="U236">
+        <v>2.75</v>
+      </c>
+      <c r="V236">
+        <v>2.75</v>
+      </c>
+      <c r="W236">
+        <v>1.4</v>
+      </c>
+      <c r="X236">
+        <v>8</v>
+      </c>
+      <c r="Y236">
+        <v>1.08</v>
+      </c>
+      <c r="Z236">
+        <v>3.99</v>
+      </c>
+      <c r="AA236">
+        <v>3.36</v>
+      </c>
+      <c r="AB236">
+        <v>1.75</v>
+      </c>
+      <c r="AC236">
+        <v>1.06</v>
+      </c>
+      <c r="AD236">
+        <v>8.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.33</v>
+      </c>
+      <c r="AF236">
+        <v>3.25</v>
+      </c>
+      <c r="AG236">
+        <v>1.94</v>
+      </c>
+      <c r="AH236">
+        <v>1.76</v>
+      </c>
+      <c r="AI236">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236">
+        <v>1.91</v>
+      </c>
+      <c r="AK236">
+        <v>1.93</v>
+      </c>
+      <c r="AL236">
+        <v>1.28</v>
+      </c>
+      <c r="AM236">
+        <v>1.22</v>
+      </c>
+      <c r="AN236">
+        <v>1</v>
+      </c>
+      <c r="AO236">
+        <v>1.67</v>
+      </c>
+      <c r="AP236">
+        <v>0.92</v>
+      </c>
+      <c r="AQ236">
+        <v>1.77</v>
+      </c>
+      <c r="AR236">
+        <v>1.51</v>
+      </c>
+      <c r="AS236">
+        <v>1.57</v>
+      </c>
+      <c r="AT236">
+        <v>3.08</v>
+      </c>
+      <c r="AU236">
+        <v>2</v>
+      </c>
+      <c r="AV236">
+        <v>9</v>
+      </c>
+      <c r="AW236">
+        <v>13</v>
+      </c>
+      <c r="AX236">
+        <v>10</v>
+      </c>
+      <c r="AY236">
+        <v>15</v>
+      </c>
+      <c r="AZ236">
+        <v>19</v>
+      </c>
+      <c r="BA236">
+        <v>5</v>
+      </c>
+      <c r="BB236">
+        <v>2</v>
+      </c>
+      <c r="BC236">
+        <v>7</v>
+      </c>
+      <c r="BD236">
+        <v>2.95</v>
+      </c>
+      <c r="BE236">
+        <v>8.5</v>
+      </c>
+      <c r="BF236">
+        <v>1.6</v>
+      </c>
+      <c r="BG236">
+        <v>1.2</v>
+      </c>
+      <c r="BH236">
+        <v>3.72</v>
+      </c>
+      <c r="BI236">
+        <v>1.41</v>
+      </c>
+      <c r="BJ236">
+        <v>2.6</v>
+      </c>
+      <c r="BK236">
+        <v>1.73</v>
+      </c>
+      <c r="BL236">
+        <v>1.99</v>
+      </c>
+      <c r="BM236">
+        <v>2.17</v>
+      </c>
+      <c r="BN236">
+        <v>1.58</v>
+      </c>
+      <c r="BO236">
+        <v>2.83</v>
+      </c>
+      <c r="BP236">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7778310</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>70</v>
+      </c>
+      <c r="H237" t="s">
+        <v>76</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>2</v>
+      </c>
+      <c r="L237">
+        <v>2</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>3</v>
+      </c>
+      <c r="O237" t="s">
+        <v>238</v>
+      </c>
+      <c r="P237" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q237">
+        <v>3.25</v>
+      </c>
+      <c r="R237">
+        <v>2.25</v>
+      </c>
+      <c r="S237">
+        <v>3.1</v>
+      </c>
+      <c r="T237">
+        <v>1.33</v>
+      </c>
+      <c r="U237">
+        <v>3.25</v>
+      </c>
+      <c r="V237">
+        <v>2.63</v>
+      </c>
+      <c r="W237">
+        <v>1.44</v>
+      </c>
+      <c r="X237">
+        <v>6.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.11</v>
+      </c>
+      <c r="Z237">
+        <v>2.47</v>
+      </c>
+      <c r="AA237">
+        <v>3.23</v>
+      </c>
+      <c r="AB237">
+        <v>2.47</v>
+      </c>
+      <c r="AC237">
+        <v>1.05</v>
+      </c>
+      <c r="AD237">
+        <v>9.5</v>
+      </c>
+      <c r="AE237">
+        <v>1.25</v>
+      </c>
+      <c r="AF237">
+        <v>3.7</v>
+      </c>
+      <c r="AG237">
+        <v>1.76</v>
+      </c>
+      <c r="AH237">
+        <v>1.94</v>
+      </c>
+      <c r="AI237">
+        <v>1.62</v>
+      </c>
+      <c r="AJ237">
+        <v>2.2</v>
+      </c>
+      <c r="AK237">
+        <v>1.5</v>
+      </c>
+      <c r="AL237">
+        <v>1.29</v>
+      </c>
+      <c r="AM237">
+        <v>1.46</v>
+      </c>
+      <c r="AN237">
+        <v>1.8</v>
+      </c>
+      <c r="AO237">
+        <v>1.45</v>
+      </c>
+      <c r="AP237">
+        <v>1.91</v>
+      </c>
+      <c r="AQ237">
+        <v>1.33</v>
+      </c>
+      <c r="AR237">
+        <v>1.58</v>
+      </c>
+      <c r="AS237">
+        <v>1.58</v>
+      </c>
+      <c r="AT237">
+        <v>3.16</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>8</v>
+      </c>
+      <c r="AW237">
+        <v>15</v>
+      </c>
+      <c r="AX237">
+        <v>6</v>
+      </c>
+      <c r="AY237">
+        <v>20</v>
+      </c>
+      <c r="AZ237">
+        <v>14</v>
+      </c>
+      <c r="BA237">
+        <v>9</v>
+      </c>
+      <c r="BB237">
+        <v>8</v>
+      </c>
+      <c r="BC237">
+        <v>17</v>
+      </c>
+      <c r="BD237">
+        <v>1.95</v>
+      </c>
+      <c r="BE237">
+        <v>8.5</v>
+      </c>
+      <c r="BF237">
+        <v>2.2</v>
+      </c>
+      <c r="BG237">
+        <v>1.22</v>
+      </c>
+      <c r="BH237">
+        <v>3.48</v>
+      </c>
+      <c r="BI237">
+        <v>1.45</v>
+      </c>
+      <c r="BJ237">
+        <v>2.48</v>
+      </c>
+      <c r="BK237">
+        <v>1.81</v>
+      </c>
+      <c r="BL237">
+        <v>1.89</v>
+      </c>
+      <c r="BM237">
+        <v>2.3</v>
+      </c>
+      <c r="BN237">
+        <v>1.52</v>
+      </c>
+      <c r="BO237">
+        <v>3.05</v>
+      </c>
+      <c r="BP237">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7778311</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>74</v>
+      </c>
+      <c r="H238" t="s">
+        <v>72</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>1</v>
+      </c>
+      <c r="M238">
+        <v>2</v>
+      </c>
+      <c r="N238">
+        <v>3</v>
+      </c>
+      <c r="O238" t="s">
+        <v>124</v>
+      </c>
+      <c r="P238" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q238">
+        <v>4.8</v>
+      </c>
+      <c r="R238">
+        <v>2</v>
+      </c>
+      <c r="S238">
+        <v>2.37</v>
+      </c>
+      <c r="T238">
+        <v>1.46</v>
+      </c>
+      <c r="U238">
+        <v>2.5</v>
+      </c>
+      <c r="V238">
+        <v>3.1</v>
+      </c>
+      <c r="W238">
+        <v>1.31</v>
+      </c>
+      <c r="X238">
+        <v>8.75</v>
+      </c>
+      <c r="Y238">
+        <v>1.06</v>
+      </c>
+      <c r="Z238">
+        <v>4.6</v>
+      </c>
+      <c r="AA238">
+        <v>3.28</v>
+      </c>
+      <c r="AB238">
+        <v>1.68</v>
+      </c>
+      <c r="AC238">
+        <v>1.08</v>
+      </c>
+      <c r="AD238">
+        <v>7.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.4</v>
+      </c>
+      <c r="AF238">
+        <v>2.7</v>
+      </c>
+      <c r="AG238">
+        <v>2.13</v>
+      </c>
+      <c r="AH238">
+        <v>1.63</v>
+      </c>
+      <c r="AI238">
+        <v>2.1</v>
+      </c>
+      <c r="AJ238">
+        <v>1.65</v>
+      </c>
+      <c r="AK238">
+        <v>1.98</v>
+      </c>
+      <c r="AL238">
+        <v>1.29</v>
+      </c>
+      <c r="AM238">
+        <v>1.19</v>
+      </c>
+      <c r="AN238">
+        <v>1.5</v>
+      </c>
+      <c r="AO238">
+        <v>1.82</v>
+      </c>
+      <c r="AP238">
+        <v>1.38</v>
+      </c>
+      <c r="AQ238">
+        <v>1.92</v>
+      </c>
+      <c r="AR238">
+        <v>1.62</v>
+      </c>
+      <c r="AS238">
+        <v>1.49</v>
+      </c>
+      <c r="AT238">
+        <v>3.11</v>
+      </c>
+      <c r="AU238">
+        <v>2</v>
+      </c>
+      <c r="AV238">
+        <v>10</v>
+      </c>
+      <c r="AW238">
+        <v>3</v>
+      </c>
+      <c r="AX238">
+        <v>8</v>
+      </c>
+      <c r="AY238">
+        <v>5</v>
+      </c>
+      <c r="AZ238">
+        <v>18</v>
+      </c>
+      <c r="BA238">
+        <v>6</v>
+      </c>
+      <c r="BB238">
+        <v>4</v>
+      </c>
+      <c r="BC238">
+        <v>10</v>
+      </c>
+      <c r="BD238">
+        <v>3</v>
+      </c>
+      <c r="BE238">
+        <v>9.5</v>
+      </c>
+      <c r="BF238">
+        <v>1.55</v>
+      </c>
+      <c r="BG238">
+        <v>1.18</v>
+      </c>
+      <c r="BH238">
+        <v>4</v>
+      </c>
+      <c r="BI238">
+        <v>1.3</v>
+      </c>
+      <c r="BJ238">
+        <v>2.97</v>
+      </c>
+      <c r="BK238">
+        <v>1.56</v>
+      </c>
+      <c r="BL238">
+        <v>2.21</v>
+      </c>
+      <c r="BM238">
+        <v>1.95</v>
+      </c>
+      <c r="BN238">
+        <v>1.76</v>
+      </c>
+      <c r="BO238">
+        <v>2.51</v>
+      </c>
+      <c r="BP238">
         <v>1.44</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -48709,13 +48709,13 @@
         <v>11</v>
       </c>
       <c r="AX230">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY230">
         <v>17</v>
       </c>
       <c r="AZ230">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA230">
         <v>6</v>
@@ -48909,13 +48909,13 @@
         <v>7</v>
       </c>
       <c r="AV231">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW231">
         <v>4</v>
       </c>
       <c r="AX231">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY231">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['45+3', '57']</t>
   </si>
   <si>
+    <t>['90+3', '90+5']</t>
+  </si>
+  <si>
     <t>['7', '46', '52', '63', '90+4']</t>
   </si>
   <si>
@@ -1022,6 +1025,9 @@
   </si>
   <si>
     <t>['30', '64']</t>
+  </si>
+  <si>
+    <t>['53', '58']</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1645,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1923,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
         <v>1.92</v>
@@ -2544,7 +2550,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3287,7 +3293,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3493,7 +3499,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3699,7 +3705,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>4.3</v>
@@ -3905,7 +3911,7 @@
         <v>98</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4729,7 +4735,7 @@
         <v>98</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -4935,7 +4941,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q18">
         <v>2.7</v>
@@ -5759,7 +5765,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>3.9</v>
@@ -5837,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
         <v>1.33</v>
@@ -6171,7 +6177,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.2</v>
@@ -6252,7 +6258,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6789,7 +6795,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6995,7 +7001,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7407,7 +7413,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -7819,7 +7825,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -8312,7 +8318,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ34">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR34">
         <v>1.99</v>
@@ -8437,7 +8443,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -8643,7 +8649,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q36">
         <v>3.5</v>
@@ -8849,7 +8855,7 @@
         <v>114</v>
       </c>
       <c r="P37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9055,7 +9061,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>3.75</v>
@@ -9673,7 +9679,7 @@
         <v>91</v>
       </c>
       <c r="P41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -10085,7 +10091,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q43">
         <v>3.2</v>
@@ -10703,7 +10709,7 @@
         <v>91</v>
       </c>
       <c r="P46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10909,7 +10915,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -11115,7 +11121,7 @@
         <v>98</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>3.35</v>
@@ -11939,7 +11945,7 @@
         <v>123</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12223,7 +12229,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ53">
         <v>0.92</v>
@@ -12351,7 +12357,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -12432,7 +12438,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR54">
         <v>1.44</v>
@@ -13381,7 +13387,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q59">
         <v>3.25</v>
@@ -13587,7 +13593,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q60">
         <v>3.4</v>
@@ -14411,7 +14417,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>3.25</v>
@@ -15235,7 +15241,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q68">
         <v>4.5</v>
@@ -15313,7 +15319,7 @@
         <v>3</v>
       </c>
       <c r="AP68">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ68">
         <v>2.08</v>
@@ -15441,7 +15447,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15853,7 +15859,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71">
         <v>2.88</v>
@@ -17089,7 +17095,7 @@
         <v>142</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17501,7 +17507,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -18197,7 +18203,7 @@
         <v>0.8</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ82">
         <v>0.82</v>
@@ -18325,7 +18331,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83">
         <v>3.4</v>
@@ -18943,7 +18949,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19024,7 +19030,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ86">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR86">
         <v>1.65</v>
@@ -19355,7 +19361,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>3.2</v>
@@ -19767,7 +19773,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20179,7 +20185,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>2.2</v>
@@ -20797,7 +20803,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20875,7 +20881,7 @@
         <v>0.25</v>
       </c>
       <c r="AP95">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ95">
         <v>0.73</v>
@@ -21621,7 +21627,7 @@
         <v>91</v>
       </c>
       <c r="P99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -22033,7 +22039,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22239,7 +22245,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22445,7 +22451,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q103">
         <v>2.7</v>
@@ -22526,7 +22532,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR103">
         <v>1.47</v>
@@ -22651,7 +22657,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -22732,7 +22738,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ104">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR104">
         <v>1.53</v>
@@ -23063,7 +23069,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106">
         <v>3.75</v>
@@ -23269,7 +23275,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q107">
         <v>4</v>
@@ -23475,7 +23481,7 @@
         <v>166</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q108">
         <v>4.75</v>
@@ -24093,7 +24099,7 @@
         <v>91</v>
       </c>
       <c r="P111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q111">
         <v>3.6</v>
@@ -24917,7 +24923,7 @@
         <v>91</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>2.75</v>
@@ -25123,7 +25129,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25407,7 +25413,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117">
         <v>1.09</v>
@@ -26153,7 +26159,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -26359,7 +26365,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26565,7 +26571,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q123">
         <v>2.2</v>
@@ -26771,7 +26777,7 @@
         <v>91</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27183,7 +27189,7 @@
         <v>130</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27470,7 +27476,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR127">
         <v>1.65</v>
@@ -27801,7 +27807,7 @@
         <v>174</v>
       </c>
       <c r="P129" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q129">
         <v>3.4</v>
@@ -28213,7 +28219,7 @@
         <v>91</v>
       </c>
       <c r="P131" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q131">
         <v>3</v>
@@ -28419,7 +28425,7 @@
         <v>176</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29449,7 +29455,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q137">
         <v>3.25</v>
@@ -29655,7 +29661,7 @@
         <v>182</v>
       </c>
       <c r="P138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29939,7 +29945,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139">
         <v>1.36</v>
@@ -30067,7 +30073,7 @@
         <v>91</v>
       </c>
       <c r="P140" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30891,7 +30897,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q144">
         <v>2.63</v>
@@ -30972,7 +30978,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR144">
         <v>1.36</v>
@@ -31921,7 +31927,7 @@
         <v>188</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32333,7 +32339,7 @@
         <v>190</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32539,7 +32545,7 @@
         <v>191</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q152">
         <v>3.6</v>
@@ -33157,7 +33163,7 @@
         <v>91</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>3.1</v>
@@ -33363,7 +33369,7 @@
         <v>91</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q156">
         <v>3.2</v>
@@ -33569,7 +33575,7 @@
         <v>193</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33775,7 +33781,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q158">
         <v>2.88</v>
@@ -33856,7 +33862,7 @@
         <v>1</v>
       </c>
       <c r="AQ158">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR158">
         <v>1.35</v>
@@ -33981,7 +33987,7 @@
         <v>194</v>
       </c>
       <c r="P159" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q159">
         <v>2.6</v>
@@ -34599,7 +34605,7 @@
         <v>124</v>
       </c>
       <c r="P162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q162">
         <v>3.4</v>
@@ -34677,7 +34683,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP162">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ162">
         <v>0.6899999999999999</v>
@@ -35217,7 +35223,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>2.6</v>
@@ -35835,7 +35841,7 @@
         <v>200</v>
       </c>
       <c r="P168" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -36041,7 +36047,7 @@
         <v>164</v>
       </c>
       <c r="P169" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q169">
         <v>4</v>
@@ -36659,7 +36665,7 @@
         <v>203</v>
       </c>
       <c r="P172" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q172">
         <v>5</v>
@@ -37483,7 +37489,7 @@
         <v>206</v>
       </c>
       <c r="P176" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q176">
         <v>3.8</v>
@@ -37770,7 +37776,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ177">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR177">
         <v>1.39</v>
@@ -37895,7 +37901,7 @@
         <v>91</v>
       </c>
       <c r="P178" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q178">
         <v>4.75</v>
@@ -38101,7 +38107,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q179">
         <v>2.45</v>
@@ -38719,7 +38725,7 @@
         <v>91</v>
       </c>
       <c r="P182" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q182">
         <v>2.4</v>
@@ -39003,7 +39009,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39131,7 +39137,7 @@
         <v>96</v>
       </c>
       <c r="P184" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -39337,7 +39343,7 @@
         <v>210</v>
       </c>
       <c r="P185" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q185">
         <v>2.75</v>
@@ -39543,7 +39549,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q186">
         <v>3</v>
@@ -39955,7 +39961,7 @@
         <v>149</v>
       </c>
       <c r="P188" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40161,7 +40167,7 @@
         <v>212</v>
       </c>
       <c r="P189" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q189">
         <v>2.8</v>
@@ -40573,7 +40579,7 @@
         <v>154</v>
       </c>
       <c r="P191" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q191">
         <v>4.33</v>
@@ -40985,7 +40991,7 @@
         <v>91</v>
       </c>
       <c r="P193" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q193">
         <v>4</v>
@@ -41191,7 +41197,7 @@
         <v>215</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q194">
         <v>3.35</v>
@@ -41809,7 +41815,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q197">
         <v>3.3</v>
@@ -42015,7 +42021,7 @@
         <v>91</v>
       </c>
       <c r="P198" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q198">
         <v>4</v>
@@ -42427,7 +42433,7 @@
         <v>218</v>
       </c>
       <c r="P200" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q200">
         <v>3.1</v>
@@ -42505,7 +42511,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ200">
         <v>0.67</v>
@@ -42633,7 +42639,7 @@
         <v>219</v>
       </c>
       <c r="P201" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q201">
         <v>2.75</v>
@@ -42839,7 +42845,7 @@
         <v>220</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q202">
         <v>2.65</v>
@@ -43045,7 +43051,7 @@
         <v>91</v>
       </c>
       <c r="P203" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43251,7 +43257,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q204">
         <v>2.8</v>
@@ -43457,7 +43463,7 @@
         <v>221</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q205">
         <v>2.7</v>
@@ -43538,7 +43544,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ205">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR205">
         <v>1.55</v>
@@ -43663,7 +43669,7 @@
         <v>167</v>
       </c>
       <c r="P206" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q206">
         <v>3</v>
@@ -43869,7 +43875,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q207">
         <v>4.33</v>
@@ -44487,7 +44493,7 @@
         <v>91</v>
       </c>
       <c r="P210" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q210">
         <v>2.92</v>
@@ -44693,7 +44699,7 @@
         <v>224</v>
       </c>
       <c r="P211" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q211">
         <v>2.5</v>
@@ -44899,7 +44905,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q212">
         <v>3.5</v>
@@ -45105,7 +45111,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q213">
         <v>3</v>
@@ -45595,7 +45601,7 @@
         <v>1.9</v>
       </c>
       <c r="AP215">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ215">
         <v>1.92</v>
@@ -45723,7 +45729,7 @@
         <v>227</v>
       </c>
       <c r="P216" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q216">
         <v>3.18</v>
@@ -45929,7 +45935,7 @@
         <v>128</v>
       </c>
       <c r="P217" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q217">
         <v>2.7</v>
@@ -46341,7 +46347,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46959,7 +46965,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q222">
         <v>4.95</v>
@@ -47989,7 +47995,7 @@
         <v>231</v>
       </c>
       <c r="P227" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q227">
         <v>2.75</v>
@@ -48607,7 +48613,7 @@
         <v>233</v>
       </c>
       <c r="P230" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q230">
         <v>3.2</v>
@@ -48813,7 +48819,7 @@
         <v>234</v>
       </c>
       <c r="P231" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q231">
         <v>3.35</v>
@@ -49019,7 +49025,7 @@
         <v>235</v>
       </c>
       <c r="P232" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q232">
         <v>3.2</v>
@@ -49225,7 +49231,7 @@
         <v>91</v>
       </c>
       <c r="P233" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q233">
         <v>5</v>
@@ -49843,7 +49849,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q236">
         <v>4.75</v>
@@ -50049,7 +50055,7 @@
         <v>238</v>
       </c>
       <c r="P237" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q237">
         <v>3.25</v>
@@ -50255,7 +50261,7 @@
         <v>124</v>
       </c>
       <c r="P238" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q238">
         <v>4.8</v>
@@ -50412,6 +50418,212 @@
       </c>
       <c r="BP238">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7778312</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45859.25</v>
+      </c>
+      <c r="F239">
+        <v>24</v>
+      </c>
+      <c r="G239" t="s">
+        <v>71</v>
+      </c>
+      <c r="H239" t="s">
+        <v>83</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>2</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>4</v>
+      </c>
+      <c r="O239" t="s">
+        <v>239</v>
+      </c>
+      <c r="P239" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q239">
+        <v>3.6</v>
+      </c>
+      <c r="R239">
+        <v>1.95</v>
+      </c>
+      <c r="S239">
+        <v>3.4</v>
+      </c>
+      <c r="T239">
+        <v>1.53</v>
+      </c>
+      <c r="U239">
+        <v>2.38</v>
+      </c>
+      <c r="V239">
+        <v>3.5</v>
+      </c>
+      <c r="W239">
+        <v>1.29</v>
+      </c>
+      <c r="X239">
+        <v>11</v>
+      </c>
+      <c r="Y239">
+        <v>1.05</v>
+      </c>
+      <c r="Z239">
+        <v>2.72</v>
+      </c>
+      <c r="AA239">
+        <v>2.83</v>
+      </c>
+      <c r="AB239">
+        <v>2.51</v>
+      </c>
+      <c r="AC239">
+        <v>1.1</v>
+      </c>
+      <c r="AD239">
+        <v>6.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.5</v>
+      </c>
+      <c r="AF239">
+        <v>2.55</v>
+      </c>
+      <c r="AG239">
+        <v>2.4</v>
+      </c>
+      <c r="AH239">
+        <v>1.5</v>
+      </c>
+      <c r="AI239">
+        <v>2.05</v>
+      </c>
+      <c r="AJ239">
+        <v>1.7</v>
+      </c>
+      <c r="AK239">
+        <v>1.47</v>
+      </c>
+      <c r="AL239">
+        <v>1.36</v>
+      </c>
+      <c r="AM239">
+        <v>1.4</v>
+      </c>
+      <c r="AN239">
+        <v>1.42</v>
+      </c>
+      <c r="AO239">
+        <v>1.67</v>
+      </c>
+      <c r="AP239">
+        <v>1.38</v>
+      </c>
+      <c r="AQ239">
+        <v>1.62</v>
+      </c>
+      <c r="AR239">
+        <v>1.54</v>
+      </c>
+      <c r="AS239">
+        <v>1.34</v>
+      </c>
+      <c r="AT239">
+        <v>2.88</v>
+      </c>
+      <c r="AU239">
+        <v>8</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>9</v>
+      </c>
+      <c r="AX239">
+        <v>2</v>
+      </c>
+      <c r="AY239">
+        <v>17</v>
+      </c>
+      <c r="AZ239">
+        <v>7</v>
+      </c>
+      <c r="BA239">
+        <v>7</v>
+      </c>
+      <c r="BB239">
+        <v>3</v>
+      </c>
+      <c r="BC239">
+        <v>10</v>
+      </c>
+      <c r="BD239">
+        <v>2.1</v>
+      </c>
+      <c r="BE239">
+        <v>8.5</v>
+      </c>
+      <c r="BF239">
+        <v>2.07</v>
+      </c>
+      <c r="BG239">
+        <v>1.27</v>
+      </c>
+      <c r="BH239">
+        <v>3.2</v>
+      </c>
+      <c r="BI239">
+        <v>1.48</v>
+      </c>
+      <c r="BJ239">
+        <v>2.35</v>
+      </c>
+      <c r="BK239">
+        <v>1.78</v>
+      </c>
+      <c r="BL239">
+        <v>1.86</v>
+      </c>
+      <c r="BM239">
+        <v>2.23</v>
+      </c>
+      <c r="BN239">
+        <v>1.54</v>
+      </c>
+      <c r="BO239">
+        <v>2.85</v>
+      </c>
+      <c r="BP239">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>
